--- a/radar.xlsx
+++ b/radar.xlsx
@@ -686,7 +686,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-10</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>11166.42</v>
+        <v>11115.26</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>11100.32</v>
+        <v>11017.82</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>11044.93</v>
+        <v>10936.16</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>11046.7</v>
+        <v>10928.06</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>11086.14</v>
+        <v>10991.55</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>11020.04</v>
+        <v>10894.11</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>10980.6</v>
+        <v>10830.62</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>10953.94</v>
+        <v>10796.67</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>11007.91</v>
+        <v>10881.6</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>10952.52</v>
+        <v>10799.94</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>10886.42</v>
+        <v>10702.5</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>11016.55</v>
+        <v>10891.65</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>11013.07</v>
+        <v>10889.2</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>11007.27</v>
+        <v>10864.57</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>2.68</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -856,54 +856,54 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>21.04</v>
+        <v>20.67</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>20.78</v>
+        <v>20.48</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.56</v>
+        <v>20.32</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>20.54</v>
+        <v>20.32</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20.71</v>
+        <v>20.43</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>20.45</v>
+        <v>20.24</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>20.28</v>
+        <v>20.13</v>
       </c>
       <c r="J4" s="29" t="n">
-        <v>20.19</v>
+        <v>20.05</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>20.42</v>
+        <v>20.21</v>
       </c>
       <c r="L4" s="31" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="N4" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="33" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="P4" s="33" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="Q4" s="34" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="31" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="N4" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O4" s="33" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="P4" s="33" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="Q4" s="34" t="n">
-        <v>20.37</v>
-      </c>
       <c r="R4" s="35" t="n">
-        <v>-1.36</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="5">
@@ -918,37 +918,37 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>12.27</v>
+        <v>12.12</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>12.15</v>
+        <v>12.03</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>12.05</v>
+        <v>11.97</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>12.12</v>
+        <v>12.01</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>11.93</v>
+        <v>11.88</v>
       </c>
       <c r="J5" s="29" t="n">
-        <v>11.88</v>
+        <v>11.83</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>11.99</v>
+        <v>11.9</v>
       </c>
       <c r="L5" s="31" t="n">
-        <v>11.89</v>
+        <v>11.82</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>11.77</v>
+        <v>11.73</v>
       </c>
       <c r="N5" s="32" t="inlineStr">
         <is>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="O5" s="33" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="P5" s="33" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>11.97</v>
+        <v>11.92</v>
       </c>
       <c r="R5" s="35" t="n">
-        <v>-1.07</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="6">
@@ -980,54 +980,54 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>15.09</v>
+        <v>14.95</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14.97</v>
+        <v>14.87</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>14.87</v>
+        <v>14.8</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>14.93</v>
+        <v>14.82</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>14.98</v>
+        <v>14.86</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>14.86</v>
+        <v>14.78</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>14.81</v>
+        <v>14.74</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>14.74</v>
+        <v>14.7</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>14.81</v>
+        <v>14.76</v>
       </c>
       <c r="L6" s="31" t="n">
-        <v>14.71</v>
+        <v>14.69</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.61</v>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="33" t="n">
-        <v>14.84</v>
+        <v>14.77</v>
       </c>
       <c r="P6" s="33" t="n">
-        <v>14.82</v>
+        <v>14.76</v>
       </c>
       <c r="Q6" s="34" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="R6" s="36" t="n">
-        <v>0.61</v>
+        <v>14.78</v>
+      </c>
+      <c r="R6" s="35" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="7">
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>22.58</v>
+        <v>22.66</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>22.19</v>
+        <v>22.12</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>21.86</v>
+        <v>21.67</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>21.97</v>
+        <v>21.71</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>22.16</v>
+        <v>22.02</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>21.77</v>
+        <v>21.48</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>21.58</v>
+        <v>21.17</v>
       </c>
       <c r="J7" s="29" t="n">
-        <v>21.38</v>
+        <v>20.94</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>21.65</v>
+        <v>21.37</v>
       </c>
       <c r="L7" s="31" t="n">
-        <v>21.32</v>
+        <v>20.92</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>20.93</v>
+        <v>20.38</v>
       </c>
       <c r="N7" s="32" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="O7" s="33" t="n">
-        <v>21.72</v>
+        <v>21.45</v>
       </c>
       <c r="P7" s="33" t="n">
-        <v>21.68</v>
+        <v>21.41</v>
       </c>
       <c r="Q7" s="34" t="n">
-        <v>21.79</v>
+        <v>21.4</v>
       </c>
       <c r="R7" s="35" t="n">
-        <v>-0.82</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="8">
@@ -1104,37 +1104,37 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>34.78</v>
+        <v>34.12</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>34.3</v>
+        <v>33.86</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>33.89</v>
+        <v>33.64</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>34.01</v>
+        <v>33.77</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>34.25</v>
+        <v>33.87</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>33.77</v>
+        <v>33.61</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>33.53</v>
+        <v>33.51</v>
       </c>
       <c r="J8" s="29" t="n">
-        <v>33.29</v>
+        <v>33.35</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>33.63</v>
+        <v>33.5</v>
       </c>
       <c r="L8" s="31" t="n">
-        <v>33.22</v>
+        <v>33.28</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>32.74</v>
+        <v>33.02</v>
       </c>
       <c r="N8" s="32" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="O8" s="33" t="n">
-        <v>33.71</v>
+        <v>33.56</v>
       </c>
       <c r="P8" s="33" t="n">
-        <v>33.66</v>
+        <v>33.52</v>
       </c>
       <c r="Q8" s="34" t="n">
-        <v>33.78</v>
-      </c>
-      <c r="R8" s="36" t="n">
-        <v>0</v>
+        <v>33.68</v>
+      </c>
+      <c r="R8" s="35" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="9">
@@ -1166,54 +1166,54 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>23.58</v>
+        <v>23.36</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>23.27</v>
+        <v>23.09</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>23.01</v>
+        <v>22.86</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>23.11</v>
+        <v>22.9</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>23.25</v>
+        <v>23.05</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>22.94</v>
+        <v>22.78</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>22.8</v>
+        <v>22.63</v>
       </c>
       <c r="J9" s="29" t="n">
-        <v>22.63</v>
+        <v>22.51</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>22.84</v>
+        <v>22.71</v>
       </c>
       <c r="L9" s="31" t="n">
-        <v>22.58</v>
+        <v>22.48</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>22.21</v>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="33" t="n">
-        <v>22.9</v>
+        <v>22.75</v>
       </c>
       <c r="P9" s="33" t="n">
-        <v>22.86</v>
+        <v>22.73</v>
       </c>
       <c r="Q9" s="34" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="R9" s="36" t="n">
-        <v>0.75</v>
+        <v>22.76</v>
+      </c>
+      <c r="R9" s="35" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="10">
@@ -1228,37 +1228,37 @@
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>133.07</v>
+        <v>130.47</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>131.17</v>
+        <v>129.07</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>129.58</v>
+        <v>127.89</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>129.5</v>
+        <v>127.73</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>130.7</v>
+        <v>128.67</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>128.8</v>
+        <v>127.27</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>127.6</v>
+        <v>126.33</v>
       </c>
       <c r="J10" s="29" t="n">
-        <v>126.9</v>
+        <v>125.87</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>128.52</v>
+        <v>127.11</v>
       </c>
       <c r="L10" s="31" t="n">
-        <v>126.93</v>
+        <v>125.93</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>125.03</v>
+        <v>124.53</v>
       </c>
       <c r="N10" s="32" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="O10" s="33" t="n">
-        <v>128.73</v>
+        <v>127.24</v>
       </c>
       <c r="P10" s="33" t="n">
-        <v>128.67</v>
+        <v>127.22</v>
       </c>
       <c r="Q10" s="34" t="n">
-        <v>128.3</v>
+        <v>126.8</v>
       </c>
       <c r="R10" s="35" t="n">
-        <v>-0.39</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="11">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>68.75</v>
+        <v>66.77</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>67.7</v>
+        <v>66.17</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>66.81999999999999</v>
+        <v>65.67</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>66.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>66.34999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>65.65000000000001</v>
+        <v>65</v>
       </c>
       <c r="J11" s="29" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>66.23</v>
+        <v>65.33</v>
       </c>
       <c r="L11" s="31" t="n">
-        <v>65.34999999999999</v>
+        <v>64.83</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>64.3</v>
+        <v>64.23</v>
       </c>
       <c r="N11" s="32" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="O11" s="33" t="n">
-        <v>66.33</v>
+        <v>65.39</v>
       </c>
       <c r="P11" s="33" t="n">
-        <v>66.31</v>
+        <v>65.38</v>
       </c>
       <c r="Q11" s="34" t="n">
-        <v>66</v>
+        <v>65.2</v>
       </c>
       <c r="R11" s="35" t="n">
-        <v>-0.15</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="12">
@@ -1352,37 +1352,37 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>26.02</v>
+        <v>25.76</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>25.76</v>
+        <v>25.5</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>25.54</v>
+        <v>25.28</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>25.58</v>
+        <v>25.27</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>25.72</v>
+        <v>25.43</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>25.46</v>
+        <v>25.17</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>25.32</v>
+        <v>25.01</v>
       </c>
       <c r="J12" s="29" t="n">
-        <v>25.2</v>
+        <v>24.91</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>25.4</v>
+        <v>25.14</v>
       </c>
       <c r="L12" s="31" t="n">
-        <v>25.18</v>
+        <v>24.92</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>24.92</v>
+        <v>24.66</v>
       </c>
       <c r="N12" s="32" t="inlineStr">
         <is>
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="O12" s="33" t="n">
-        <v>25.44</v>
+        <v>25.17</v>
       </c>
       <c r="P12" s="33" t="n">
-        <v>25.42</v>
+        <v>25.16</v>
       </c>
       <c r="Q12" s="34" t="n">
-        <v>25.44</v>
+        <v>25.1</v>
       </c>
       <c r="R12" s="35" t="n">
-        <v>-0.7</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="13">
@@ -1414,54 +1414,54 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>25.7</v>
+        <v>25.86</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>25.44</v>
+        <v>25.43</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>25.22</v>
+        <v>25.07</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>25.29</v>
+        <v>25.04</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>25.41</v>
+        <v>25.32</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>25.15</v>
+        <v>24.89</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>25.03</v>
+        <v>24.61</v>
       </c>
       <c r="J13" s="29" t="n">
-        <v>24.89</v>
+        <v>24.46</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>25.08</v>
+        <v>24.82</v>
       </c>
       <c r="L13" s="31" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="N13" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O13" s="33" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="P13" s="33" t="n">
         <v>24.86</v>
       </c>
-      <c r="M13" s="31" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O13" s="33" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="P13" s="33" t="n">
-        <v>25.1</v>
-      </c>
       <c r="Q13" s="34" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="R13" s="36" t="n">
-        <v>0</v>
+        <v>24.77</v>
+      </c>
+      <c r="R13" s="35" t="n">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="14">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="C14" s="25" t="n">
-        <v>43.01</v>
+        <v>42.52</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>42.45</v>
+        <v>41.88</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>41.98</v>
+        <v>41.34</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>41.95</v>
+        <v>41.52</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>42.31</v>
+        <v>41.82</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>41.75</v>
+        <v>41.18</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>41.39</v>
+        <v>40.88</v>
       </c>
       <c r="J14" s="29" t="n">
-        <v>41.19</v>
+        <v>40.54</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>41.66</v>
+        <v>40.98</v>
       </c>
       <c r="L14" s="31" t="n">
-        <v>41.19</v>
+        <v>40.44</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>40.63</v>
+        <v>39.8</v>
       </c>
       <c r="N14" s="32" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="O14" s="33" t="n">
-        <v>41.73</v>
+        <v>41.11</v>
       </c>
       <c r="P14" s="33" t="n">
-        <v>41.71</v>
+        <v>41.03</v>
       </c>
       <c r="Q14" s="34" t="n">
-        <v>41.6</v>
+        <v>41.22</v>
       </c>
       <c r="R14" s="35" t="n">
-        <v>-0.24</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="15">
@@ -1538,54 +1538,54 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8.960000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8.890000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>8.83</v>
+        <v>8.75</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>8.85</v>
+        <v>8.75</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H15" s="28" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>8.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J15" s="29" t="n">
-        <v>8.75</v>
+        <v>8.58</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="L15" s="31" t="n">
-        <v>8.74</v>
+        <v>8.59</v>
       </c>
       <c r="M15" s="31" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="N15" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O15" s="33" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="P15" s="33" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q15" s="34" t="n">
         <v>8.67</v>
       </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O15" s="33" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="P15" s="33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q15" s="34" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>0</v>
+      <c r="R15" s="35" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16">
@@ -1600,54 +1600,54 @@
         </is>
       </c>
       <c r="C16" s="25" t="n">
-        <v>14.92</v>
+        <v>14.73</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>14.76</v>
+        <v>14.59</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>14.62</v>
+        <v>14.47</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>14.61</v>
+        <v>14.53</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>14.71</v>
+        <v>14.59</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>14.55</v>
+        <v>14.45</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>14.45</v>
+        <v>14.39</v>
       </c>
       <c r="J16" s="29" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="K16" s="30" t="n">
         <v>14.39</v>
       </c>
-      <c r="K16" s="30" t="n">
-        <v>14.54</v>
-      </c>
       <c r="L16" s="31" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="M16" s="31" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O16" s="33" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="P16" s="33" t="n">
         <v>14.4</v>
       </c>
-      <c r="M16" s="31" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="N16" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O16" s="33" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="P16" s="33" t="n">
-        <v>14.55</v>
-      </c>
       <c r="Q16" s="34" t="n">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="R16" s="35" t="n">
-        <v>-0.34</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="17">
@@ -1662,54 +1662,54 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>4.76</v>
+        <v>4.71</v>
       </c>
       <c r="E17" s="26" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G17" s="27" t="n">
         <v>4.67</v>
       </c>
-      <c r="F17" s="27" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>4.74</v>
-      </c>
       <c r="H17" s="28" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="J17" s="29" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L17" s="31" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="M17" s="31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="P17" s="33" t="n">
         <v>4.52</v>
       </c>
-      <c r="K17" s="30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L17" s="31" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="M17" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N17" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O17" s="33" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="P17" s="33" t="n">
-        <v>4.61</v>
-      </c>
       <c r="Q17" s="34" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="R17" s="35" t="n">
-        <v>-1.28</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="18">
@@ -1724,54 +1724,54 @@
         </is>
       </c>
       <c r="C18" s="25" t="n">
-        <v>18.28</v>
+        <v>19.08</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>18.04</v>
+        <v>18.4</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>17.84</v>
+        <v>17.83</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>17.84</v>
+        <v>18.2</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>17.99</v>
+        <v>18.43</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>17.75</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>17.6</v>
+        <v>17.52</v>
       </c>
       <c r="J18" s="29" t="n">
-        <v>17.51</v>
+        <v>17.07</v>
       </c>
       <c r="K18" s="30" t="n">
-        <v>17.7</v>
+        <v>17.45</v>
       </c>
       <c r="L18" s="31" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O18" s="33" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="P18" s="33" t="n">
         <v>17.5</v>
       </c>
-      <c r="M18" s="31" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="N18" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O18" s="33" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="P18" s="33" t="n">
-        <v>17.72</v>
-      </c>
       <c r="Q18" s="34" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="R18" s="35" t="n">
-        <v>-0.84</v>
+        <v>17.97</v>
+      </c>
+      <c r="R18" s="36" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="19">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>27.07</v>
+        <v>26.15</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>26.31</v>
+        <v>25.43</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25.67</v>
+        <v>24.83</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25.59</v>
+        <v>24.75</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>26.09</v>
+        <v>25.23</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>25.33</v>
+        <v>24.51</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>24.83</v>
+        <v>24.03</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>24.57</v>
+        <v>23.79</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>25.25</v>
+        <v>24.43</v>
       </c>
       <c r="L19" s="31" t="n">
-        <v>24.61</v>
+        <v>23.83</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>23.85</v>
+        <v>23.11</v>
       </c>
       <c r="N19" s="32" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="O19" s="33" t="n">
-        <v>25.32</v>
+        <v>24.5</v>
       </c>
       <c r="P19" s="33" t="n">
-        <v>25.31</v>
+        <v>24.48</v>
       </c>
       <c r="Q19" s="34" t="n">
-        <v>25.08</v>
+        <v>24.27</v>
       </c>
       <c r="R19" s="35" t="n">
-        <v>-1.57</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="20">
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="C20" s="25" t="n">
-        <v>69</v>
+        <v>67.83</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>67.7</v>
+        <v>66.33</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>66.61</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>66.73</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>67.47</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H20" s="28" t="n">
-        <v>66.17</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>65.43000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="J20" s="29" t="n">
-        <v>64.87</v>
+        <v>62.9</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>65.89</v>
+        <v>64.23</v>
       </c>
       <c r="L20" s="31" t="n">
-        <v>64.8</v>
+        <v>62.97</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>63.5</v>
+        <v>61.47</v>
       </c>
       <c r="N20" s="32" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="O20" s="33" t="n">
-        <v>66.08</v>
+        <v>64.37</v>
       </c>
       <c r="P20" s="33" t="n">
-        <v>65.98999999999999</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="Q20" s="34" t="n">
-        <v>66</v>
+        <v>63.9</v>
       </c>
       <c r="R20" s="35" t="n">
-        <v>-1.05</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="21">
@@ -1910,54 +1910,54 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>12.26</v>
+        <v>12.34</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>12.09</v>
+        <v>12.02</v>
       </c>
       <c r="E21" s="26" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="G21" s="27" t="n">
         <v>11.94</v>
       </c>
-      <c r="F21" s="27" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>12.04</v>
-      </c>
       <c r="H21" s="28" t="n">
-        <v>11.87</v>
+        <v>11.62</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>11.77</v>
+        <v>11.41</v>
       </c>
       <c r="J21" s="29" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>11.85</v>
+        <v>11.57</v>
       </c>
       <c r="L21" s="31" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="M21" s="31" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="N21" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O21" s="33" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="P21" s="33" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q21" s="34" t="n">
         <v>11.53</v>
       </c>
-      <c r="N21" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O21" s="33" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="P21" s="33" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="Q21" s="34" t="n">
-        <v>11.83</v>
-      </c>
       <c r="R21" s="35" t="n">
-        <v>-1.25</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="22">
@@ -1972,37 +1972,37 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>18.67</v>
+        <v>18.72</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>18.41</v>
+        <v>18.32</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.19</v>
+        <v>17.98</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>18.22</v>
+        <v>17.99</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>18.36</v>
+        <v>18.23</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>18.1</v>
+        <v>17.83</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>17.96</v>
+        <v>17.59</v>
       </c>
       <c r="J22" s="29" t="n">
-        <v>17.84</v>
+        <v>17.43</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>18.05</v>
+        <v>17.76</v>
       </c>
       <c r="L22" s="31" t="n">
-        <v>17.83</v>
+        <v>17.42</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>17.57</v>
+        <v>17.02</v>
       </c>
       <c r="N22" s="32" t="inlineStr">
         <is>
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="O22" s="33" t="n">
-        <v>18.09</v>
+        <v>17.81</v>
       </c>
       <c r="P22" s="33" t="n">
-        <v>18.07</v>
+        <v>17.79</v>
       </c>
       <c r="Q22" s="34" t="n">
-        <v>18.07</v>
+        <v>17.75</v>
       </c>
       <c r="R22" s="35" t="n">
-        <v>-0.39</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="23">
@@ -2034,37 +2034,37 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>39.81</v>
+        <v>37.62</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>38.69</v>
+        <v>37.14</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>37.75</v>
+        <v>36.73</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>37.76</v>
+        <v>36.97</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>38.44</v>
+        <v>37.15</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>37.32</v>
+        <v>36.67</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>36.64</v>
+        <v>36.49</v>
       </c>
       <c r="J23" s="29" t="n">
-        <v>36.2</v>
+        <v>36.19</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>37.13</v>
+        <v>36.47</v>
       </c>
       <c r="L23" s="31" t="n">
-        <v>36.19</v>
+        <v>36.06</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>35.07</v>
+        <v>35.58</v>
       </c>
       <c r="N23" s="32" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="O23" s="33" t="n">
-        <v>37.27</v>
+        <v>36.58</v>
       </c>
       <c r="P23" s="33" t="n">
-        <v>37.21</v>
+        <v>36.5</v>
       </c>
       <c r="Q23" s="34" t="n">
-        <v>37.08</v>
+        <v>36.8</v>
       </c>
       <c r="R23" s="35" t="n">
-        <v>-2.37</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="24">
@@ -2096,37 +2096,37 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>15.75</v>
+        <v>16.02</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>15.5</v>
+        <v>15.66</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>15.3</v>
+        <v>15.36</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>15.39</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>15.49</v>
+        <v>15.59</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>15.24</v>
+        <v>15.23</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>15.14</v>
+        <v>15.03</v>
       </c>
       <c r="J24" s="29" t="n">
-        <v>14.99</v>
+        <v>14.87</v>
       </c>
       <c r="K24" s="30" t="n">
         <v>15.16</v>
       </c>
       <c r="L24" s="31" t="n">
-        <v>14.95</v>
+        <v>14.86</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="N24" s="32" t="inlineStr">
         <is>
@@ -2137,13 +2137,13 @@
         <v>15.21</v>
       </c>
       <c r="P24" s="33" t="n">
-        <v>15.17</v>
+        <v>15.19</v>
       </c>
       <c r="Q24" s="34" t="n">
-        <v>15.28</v>
-      </c>
-      <c r="R24" s="36" t="n">
-        <v>0.2</v>
+        <v>15.18</v>
+      </c>
+      <c r="R24" s="35" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="25">
@@ -2158,54 +2158,54 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>37.53</v>
+        <v>37.55</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>36.93</v>
+        <v>36.73</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>36.43</v>
+        <v>36.04</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>36.64</v>
+        <v>35.95</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>36.9</v>
+        <v>36.49</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>36.3</v>
+        <v>35.67</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>36.04</v>
+        <v>35.13</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>35.7</v>
+        <v>34.85</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>36.09</v>
+        <v>35.58</v>
       </c>
       <c r="L25" s="31" t="n">
-        <v>35.59</v>
+        <v>34.89</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>34.07</v>
+      </c>
+      <c r="N25" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="33" t="n">
-        <v>36.22</v>
+        <v>35.66</v>
       </c>
       <c r="P25" s="33" t="n">
-        <v>36.14</v>
+        <v>35.64</v>
       </c>
       <c r="Q25" s="34" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="R25" s="36" t="n">
-        <v>0.9399999999999999</v>
+        <v>35.4</v>
+      </c>
+      <c r="R25" s="35" t="n">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="26">
@@ -2220,54 +2220,54 @@
         </is>
       </c>
       <c r="C26" s="25" t="n">
-        <v>59.55</v>
+        <v>64.14</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>58.5</v>
+        <v>60.84</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>57.62</v>
+        <v>58.07</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>57.73</v>
+        <v>57.8</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>58.32</v>
+        <v>59.95</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>57.27</v>
+        <v>56.65</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>56.68</v>
+        <v>54.5</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>56.22</v>
+        <v>53.35</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>57.03</v>
+        <v>56.23</v>
       </c>
       <c r="L26" s="31" t="n">
-        <v>56.15</v>
+        <v>53.46</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>50.16</v>
+      </c>
+      <c r="N26" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="33" t="n">
-        <v>57.19</v>
+        <v>56.57</v>
       </c>
       <c r="P26" s="33" t="n">
-        <v>57.11</v>
+        <v>56.48</v>
       </c>
       <c r="Q26" s="34" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="R26" s="36" t="n">
-        <v>0.09</v>
+        <v>55.65</v>
+      </c>
+      <c r="R26" s="35" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="27">
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>220.97</v>
+        <v>231.53</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>214.87</v>
+        <v>221.13</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>209.76</v>
+        <v>212.41</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>209.4</v>
+        <v>211.37</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>213.3</v>
+        <v>218.23</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>207.2</v>
+        <v>207.83</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>203.3</v>
+        <v>200.97</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>201.1</v>
+        <v>197.43</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>206.34</v>
+        <v>206.59</v>
       </c>
       <c r="L27" s="31" t="n">
-        <v>201.23</v>
+        <v>197.87</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>195.13</v>
+        <v>187.47</v>
       </c>
       <c r="N27" s="32" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="O27" s="33" t="n">
-        <v>207.01</v>
+        <v>207.62</v>
       </c>
       <c r="P27" s="33" t="n">
-        <v>206.82</v>
+        <v>207.4</v>
       </c>
       <c r="Q27" s="34" t="n">
-        <v>205.5</v>
+        <v>204.5</v>
       </c>
       <c r="R27" s="35" t="n">
-        <v>-0.72</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="28">
@@ -2344,37 +2344,37 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>89.66</v>
+        <v>85.92</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>87.45999999999999</v>
+        <v>84.27</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>85.62</v>
+        <v>82.89</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>85.37</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>86.83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>84.63</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>83.17</v>
+        <v>81.45</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>82.43000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>84.38</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="L28" s="31" t="n">
-        <v>82.54000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>80.34</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N28" s="32" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="O28" s="33" t="n">
-        <v>84.59</v>
+        <v>82.22</v>
       </c>
       <c r="P28" s="33" t="n">
-        <v>84.56</v>
+        <v>82.09</v>
       </c>
       <c r="Q28" s="34" t="n">
-        <v>83.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="R28" s="35" t="n">
-        <v>-0.18</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="29">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>23.49</v>
+        <v>23.05</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>22.89</v>
+        <v>22.33</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>22.39</v>
+        <v>21.73</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>22.37</v>
+        <v>21.74</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>22.75</v>
+        <v>22.17</v>
       </c>
       <c r="H29" s="28" t="n">
-        <v>22.15</v>
+        <v>21.45</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>21.77</v>
+        <v>21.02</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>21.55</v>
+        <v>20.73</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>22.05</v>
+        <v>21.33</v>
       </c>
       <c r="L29" s="31" t="n">
-        <v>21.55</v>
+        <v>20.73</v>
       </c>
       <c r="M29" s="31" t="n">
-        <v>20.95</v>
+        <v>20.01</v>
       </c>
       <c r="N29" s="32" t="inlineStr">
         <is>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="O29" s="33" t="n">
-        <v>22.12</v>
+        <v>21.42</v>
       </c>
       <c r="P29" s="33" t="n">
-        <v>22.1</v>
+        <v>21.38</v>
       </c>
       <c r="Q29" s="34" t="n">
-        <v>22</v>
+        <v>21.3</v>
       </c>
       <c r="R29" s="35" t="n">
-        <v>-1.96</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="30">
@@ -2468,54 +2468,54 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>84.89</v>
+        <v>85.27</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>83.29000000000001</v>
+        <v>83.37</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>81.95</v>
+        <v>81.78</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>82.7</v>
+        <v>82.23</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>83.3</v>
+        <v>83.17</v>
       </c>
       <c r="H30" s="28" t="n">
-        <v>81.7</v>
+        <v>81.27</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>81.09999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>80.09999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>81.05</v>
+        <v>80.72</v>
       </c>
       <c r="L30" s="31" t="n">
-        <v>79.70999999999999</v>
+        <v>79.13</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>77.23</v>
+      </c>
+      <c r="N30" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="33" t="n">
-        <v>81.44</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="P30" s="33" t="n">
-        <v>81.18000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="Q30" s="34" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="R30" s="36" t="n">
-        <v>0.67</v>
+        <v>81.3</v>
+      </c>
+      <c r="R30" s="35" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="31">
@@ -2530,37 +2530,37 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>31.36</v>
+        <v>30.24</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>30.32</v>
+        <v>29.3</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>29.45</v>
+        <v>28.51</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>29.52</v>
+        <v>28.41</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>30.12</v>
+        <v>29.03</v>
       </c>
       <c r="H31" s="28" t="n">
-        <v>29.08</v>
+        <v>28.09</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>28.48</v>
+        <v>27.47</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>28.04</v>
+        <v>27.15</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>28.87</v>
+        <v>27.99</v>
       </c>
       <c r="L31" s="31" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>26.96</v>
+        <v>26.26</v>
       </c>
       <c r="N31" s="32" t="inlineStr">
         <is>
@@ -2568,16 +2568,16 @@
         </is>
       </c>
       <c r="O31" s="33" t="n">
-        <v>29.01</v>
+        <v>28.08</v>
       </c>
       <c r="P31" s="33" t="n">
-        <v>28.95</v>
+        <v>28.06</v>
       </c>
       <c r="Q31" s="34" t="n">
-        <v>28.92</v>
+        <v>27.78</v>
       </c>
       <c r="R31" s="35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="32">
@@ -2592,54 +2592,54 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>50.71</v>
+        <v>51.22</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>50.3</v>
+        <v>50.34</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>49.96</v>
+        <v>49.61</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>50.02</v>
+        <v>49.89</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>50.24</v>
+        <v>50.29</v>
       </c>
       <c r="H32" s="28" t="n">
-        <v>49.83</v>
+        <v>49.41</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>49.61</v>
+        <v>49.01</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>49.42</v>
+        <v>48.53</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>49.73</v>
+        <v>49.11</v>
       </c>
       <c r="L32" s="31" t="n">
-        <v>49.39</v>
+        <v>48.38</v>
       </c>
       <c r="M32" s="31" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>47.5</v>
+      </c>
+      <c r="N32" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="33" t="n">
-        <v>49.8</v>
+        <v>49.29</v>
       </c>
       <c r="P32" s="33" t="n">
-        <v>49.76</v>
+        <v>49.18</v>
       </c>
       <c r="Q32" s="34" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="R32" s="36" t="n">
-        <v>0.65</v>
+        <v>49.5</v>
+      </c>
+      <c r="R32" s="35" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="33">
@@ -2654,54 +2654,54 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>131.46</v>
+        <v>130.8</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>129.26</v>
+        <v>128.7</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>127.42</v>
+        <v>126.94</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>127.97</v>
+        <v>127.37</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>129.03</v>
+        <v>128.43</v>
       </c>
       <c r="H33" s="28" t="n">
-        <v>126.83</v>
+        <v>126.33</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>125.77</v>
+        <v>125.27</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>124.63</v>
+        <v>124.23</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>126.18</v>
+        <v>125.76</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>124.34</v>
+        <v>124</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>122.14</v>
-      </c>
-      <c r="N33" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>121.9</v>
+      </c>
+      <c r="N33" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="33" t="n">
-        <v>126.59</v>
+        <v>126.13</v>
       </c>
       <c r="P33" s="33" t="n">
-        <v>126.36</v>
+        <v>125.93</v>
       </c>
       <c r="Q33" s="34" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="R33" s="36" t="n">
-        <v>0.87</v>
+        <v>126.3</v>
+      </c>
+      <c r="R33" s="35" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="34">
@@ -2716,37 +2716,37 @@
         </is>
       </c>
       <c r="C34" s="25" t="n">
-        <v>59.41</v>
+        <v>57.71</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>57.61</v>
+        <v>55.91</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>56.1</v>
+        <v>54.4</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>56</v>
+        <v>54.6</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>57.15</v>
+        <v>55.6</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>55.35</v>
+        <v>53.8</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>54.2</v>
+        <v>52.8</v>
       </c>
       <c r="J34" s="29" t="n">
-        <v>53.55</v>
+        <v>52</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>55.1</v>
+        <v>53.4</v>
       </c>
       <c r="L34" s="31" t="n">
-        <v>53.59</v>
+        <v>51.89</v>
       </c>
       <c r="M34" s="31" t="n">
-        <v>51.79</v>
+        <v>50.09</v>
       </c>
       <c r="N34" s="32" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="O34" s="33" t="n">
-        <v>55.29</v>
+        <v>53.67</v>
       </c>
       <c r="P34" s="33" t="n">
-        <v>55.24</v>
+        <v>53.54</v>
       </c>
       <c r="Q34" s="34" t="n">
-        <v>54.85</v>
+        <v>53.6</v>
       </c>
       <c r="R34" s="35" t="n">
-        <v>-1.35</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="35">
@@ -2778,54 +2778,54 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>25.22</v>
+        <v>25.24</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>25.02</v>
+        <v>24.86</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>24.86</v>
+        <v>24.55</v>
       </c>
       <c r="F35" s="27" t="n">
-        <v>24.97</v>
+        <v>24.5</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>25.03</v>
+        <v>24.76</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>24.83</v>
+        <v>24.38</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>24.77</v>
+        <v>24.12</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>24.63</v>
+        <v>24</v>
       </c>
       <c r="K35" s="30" t="n">
-        <v>24.74</v>
+        <v>24.33</v>
       </c>
       <c r="L35" s="31" t="n">
-        <v>24.58</v>
+        <v>24.02</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>24.38</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>23.64</v>
+      </c>
+      <c r="N35" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="33" t="n">
-        <v>24.8</v>
+        <v>24.37</v>
       </c>
       <c r="P35" s="33" t="n">
-        <v>24.76</v>
+        <v>24.36</v>
       </c>
       <c r="Q35" s="34" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="R35" s="36" t="n">
-        <v>0.44</v>
+        <v>24.25</v>
+      </c>
+      <c r="R35" s="35" t="n">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="36">
@@ -2840,37 +2840,37 @@
         </is>
       </c>
       <c r="C36" s="25" t="n">
-        <v>27.3</v>
+        <v>27.08</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>26.72</v>
+        <v>26.4</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>26.23</v>
+        <v>25.83</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>26.3</v>
+        <v>25.89</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>26.62</v>
+        <v>26.27</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>26.04</v>
+        <v>25.59</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>25.72</v>
+        <v>25.21</v>
       </c>
       <c r="J36" s="29" t="n">
-        <v>25.46</v>
+        <v>24.91</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>25.91</v>
+        <v>25.45</v>
       </c>
       <c r="L36" s="31" t="n">
-        <v>25.42</v>
+        <v>24.88</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>24.84</v>
+        <v>24.2</v>
       </c>
       <c r="N36" s="32" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="O36" s="33" t="n">
-        <v>26</v>
+        <v>25.55</v>
       </c>
       <c r="P36" s="33" t="n">
-        <v>25.95</v>
+        <v>25.5</v>
       </c>
       <c r="Q36" s="34" t="n">
-        <v>25.98</v>
+        <v>25.5</v>
       </c>
       <c r="R36" s="35" t="n">
-        <v>-1.29</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="37">
@@ -2902,54 +2902,54 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>9.26</v>
+        <v>9.27</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>9.16</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>9.17</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>9.24</v>
+        <v>9.23</v>
       </c>
       <c r="H37" s="28" t="n">
-        <v>9.119999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I37" s="29" t="n">
-        <v>9.050000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="J37" s="29" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="K37" s="30" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="L37" s="31" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="N37" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O37" s="33" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="P37" s="33" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="Q37" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="K37" s="30" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="L37" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="M37" s="31" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="N37" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O37" s="33" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="P37" s="33" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="Q37" s="34" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="R37" s="36" t="n">
-        <v>0.22</v>
+      <c r="R37" s="35" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="38">
@@ -2964,54 +2964,54 @@
         </is>
       </c>
       <c r="C38" s="25" t="n">
-        <v>33.15</v>
+        <v>33.3</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>32.49</v>
+        <v>32.3</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>31.93</v>
+        <v>31.46</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>32.15</v>
+        <v>31.49</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>32.45</v>
+        <v>32.09</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>31.79</v>
+        <v>31.09</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>31.49</v>
+        <v>30.49</v>
       </c>
       <c r="J38" s="29" t="n">
-        <v>31.13</v>
+        <v>30.09</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>31.57</v>
+        <v>30.9</v>
       </c>
       <c r="L38" s="31" t="n">
-        <v>31.01</v>
+        <v>30.06</v>
       </c>
       <c r="M38" s="31" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>29.06</v>
+      </c>
+      <c r="N38" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="33" t="n">
-        <v>31.7</v>
+        <v>31.03</v>
       </c>
       <c r="P38" s="33" t="n">
-        <v>31.62</v>
+        <v>30.98</v>
       </c>
       <c r="Q38" s="34" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="R38" s="36" t="n">
-        <v>0.7</v>
+        <v>30.9</v>
+      </c>
+      <c r="R38" s="35" t="n">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="39">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>194.97</v>
+        <v>197.83</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>193.07</v>
+        <v>192.93</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>191.48</v>
+        <v>188.82</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>191.87</v>
+        <v>188.33</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>192.83</v>
+        <v>191.57</v>
       </c>
       <c r="H39" s="28" t="n">
-        <v>190.93</v>
+        <v>186.67</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>189.97</v>
+        <v>183.43</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>189.03</v>
+        <v>181.77</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>190.42</v>
+        <v>186.08</v>
       </c>
       <c r="L39" s="31" t="n">
-        <v>188.83</v>
+        <v>181.97</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>186.93</v>
+        <v>177.07</v>
       </c>
       <c r="N39" s="32" t="inlineStr">
         <is>
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="O39" s="33" t="n">
-        <v>190.75</v>
+        <v>186.56</v>
       </c>
       <c r="P39" s="33" t="n">
-        <v>190.57</v>
+        <v>186.46</v>
       </c>
       <c r="Q39" s="34" t="n">
-        <v>190.9</v>
+        <v>185.1</v>
       </c>
       <c r="R39" s="35" t="n">
-        <v>-0.62</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="40">
@@ -3088,37 +3088,37 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>13.05</v>
+        <v>12.6</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>12.86</v>
+        <v>12.6</v>
       </c>
       <c r="E40" s="26" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>12.71</v>
+        <v>12.6</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>12.82</v>
+        <v>12.6</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>12.63</v>
+        <v>12.6</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>12.52</v>
+        <v>12.6</v>
       </c>
       <c r="J40" s="29" t="n">
-        <v>12.44</v>
+        <v>12.6</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>12.59</v>
+        <v>12.6</v>
       </c>
       <c r="L40" s="31" t="n">
-        <v>12.43</v>
+        <v>12.6</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>12.24</v>
+        <v>12.6</v>
       </c>
       <c r="N40" s="32" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="O40" s="33" t="n">
-        <v>12.62</v>
+        <v>12.6</v>
       </c>
       <c r="P40" s="33" t="n">
-        <v>12.61</v>
+        <v>12.6</v>
       </c>
       <c r="Q40" s="34" t="n">
         <v>12.6</v>
       </c>
-      <c r="R40" s="35" t="n">
-        <v>-0.79</v>
+      <c r="R40" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3150,37 +3150,37 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>23.56</v>
+        <v>22.87</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>22.91</v>
+        <v>22.32</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>22.37</v>
+        <v>21.86</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>22.39</v>
+        <v>21.8</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>22.78</v>
+        <v>22.16</v>
       </c>
       <c r="H41" s="28" t="n">
-        <v>22.13</v>
+        <v>21.61</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>21.74</v>
+        <v>21.25</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>21.48</v>
+        <v>21.06</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>22</v>
+        <v>21.55</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>21.46</v>
+        <v>21.09</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>20.81</v>
+        <v>20.54</v>
       </c>
       <c r="N41" s="32" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="O41" s="33" t="n">
-        <v>22.09</v>
+        <v>21.6</v>
       </c>
       <c r="P41" s="33" t="n">
-        <v>22.05</v>
+        <v>21.59</v>
       </c>
       <c r="Q41" s="34" t="n">
-        <v>22.01</v>
+        <v>21.43</v>
       </c>
       <c r="R41" s="35" t="n">
-        <v>-2.22</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="42">
@@ -3212,37 +3212,37 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>193.74</v>
+        <v>190.67</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>191.24</v>
+        <v>189.27</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>189.15</v>
+        <v>188.09</v>
       </c>
       <c r="F42" s="27" t="n">
+        <v>187.93</v>
+      </c>
+      <c r="G42" s="27" t="n">
         <v>188.87</v>
       </c>
-      <c r="G42" s="27" t="n">
-        <v>190.53</v>
-      </c>
       <c r="H42" s="28" t="n">
-        <v>188.03</v>
+        <v>187.47</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>186.37</v>
+        <v>186.53</v>
       </c>
       <c r="J42" s="29" t="n">
-        <v>185.53</v>
+        <v>186.07</v>
       </c>
       <c r="K42" s="30" t="n">
-        <v>187.75</v>
+        <v>187.31</v>
       </c>
       <c r="L42" s="31" t="n">
-        <v>185.65</v>
+        <v>186.13</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>183.15</v>
+        <v>184.73</v>
       </c>
       <c r="N42" s="32" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
         </is>
       </c>
       <c r="O42" s="33" t="n">
-        <v>187.99</v>
+        <v>187.44</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>187.94</v>
+        <v>187.42</v>
       </c>
       <c r="Q42" s="34" t="n">
-        <v>187.2</v>
+        <v>187</v>
       </c>
       <c r="R42" s="35" t="n">
-        <v>-0.27</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="43">
@@ -3274,54 +3274,54 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>37.72</v>
+        <v>37.68</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>37.2</v>
+        <v>37.04</v>
       </c>
       <c r="E43" s="26" t="n">
-        <v>36.77</v>
+        <v>36.5</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>36.77</v>
+        <v>36.81</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>37.09</v>
+        <v>37.05</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>36.57</v>
+        <v>36.41</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>36.25</v>
+        <v>36.17</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>36.05</v>
+        <v>35.77</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>36.47</v>
+        <v>36.14</v>
       </c>
       <c r="L43" s="31" t="n">
-        <v>36.04</v>
+        <v>35.6</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="N43" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>34.96</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="33" t="n">
-        <v>36.54</v>
+        <v>36.3</v>
       </c>
       <c r="P43" s="33" t="n">
-        <v>36.51</v>
+        <v>36.19</v>
       </c>
       <c r="Q43" s="34" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="R43" s="35" t="n">
-        <v>-0.33</v>
+        <v>36.58</v>
+      </c>
+      <c r="R43" s="36" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="44">
@@ -3336,54 +3336,54 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>29.79</v>
+        <v>30.02</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>29.35</v>
+        <v>28.96</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>28.98</v>
+        <v>28.07</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>28.99</v>
+        <v>28.03</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>29.25</v>
+        <v>28.69</v>
       </c>
       <c r="H44" s="28" t="n">
-        <v>28.81</v>
+        <v>27.63</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>28.55</v>
+        <v>26.97</v>
       </c>
       <c r="J44" s="29" t="n">
-        <v>28.37</v>
+        <v>26.57</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>28.74</v>
+        <v>27.47</v>
       </c>
       <c r="L44" s="31" t="n">
-        <v>28.37</v>
+        <v>26.58</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>27.93</v>
-      </c>
-      <c r="N44" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.52</v>
+      </c>
+      <c r="N44" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O44" s="33" t="n">
-        <v>28.79</v>
+        <v>27.59</v>
       </c>
       <c r="P44" s="33" t="n">
-        <v>28.77</v>
+        <v>27.56</v>
       </c>
       <c r="Q44" s="34" t="n">
-        <v>28.72</v>
+        <v>27.36</v>
       </c>
       <c r="R44" s="35" t="n">
-        <v>-0.83</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="45">
@@ -3398,54 +3398,54 @@
         </is>
       </c>
       <c r="C45" s="25" t="n">
-        <v>26.44</v>
+        <v>26.66</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>26.28</v>
+        <v>26.3</v>
       </c>
       <c r="E45" s="26" t="n">
-        <v>26.14</v>
+        <v>26</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>26.21</v>
+        <v>25.96</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>26.27</v>
+        <v>26.2</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>26.11</v>
+        <v>25.84</v>
       </c>
       <c r="I45" s="29" t="n">
-        <v>26.05</v>
+        <v>25.6</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>25.95</v>
+        <v>25.48</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>26.06</v>
+        <v>25.8</v>
       </c>
       <c r="L45" s="31" t="n">
-        <v>25.92</v>
+        <v>25.5</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.14</v>
+      </c>
+      <c r="N45" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="33" t="n">
-        <v>26.09</v>
+        <v>25.83</v>
       </c>
       <c r="P45" s="33" t="n">
-        <v>26.07</v>
+        <v>25.83</v>
       </c>
       <c r="Q45" s="34" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="R45" s="36" t="n">
-        <v>0.38</v>
+        <v>25.72</v>
+      </c>
+      <c r="R45" s="35" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="46">
@@ -3460,37 +3460,37 @@
         </is>
       </c>
       <c r="C46" s="25" t="n">
-        <v>8.33</v>
+        <v>8.35</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>8.210000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E46" s="26" t="n">
-        <v>8.109999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="F46" s="27" t="n">
-        <v>8.130000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>8.19</v>
+        <v>8.08</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>8.07</v>
+        <v>7.86</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>8.01</v>
+        <v>7.72</v>
       </c>
       <c r="J46" s="29" t="n">
-        <v>7.95</v>
+        <v>7.64</v>
       </c>
       <c r="K46" s="30" t="n">
-        <v>8.050000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="L46" s="31" t="n">
-        <v>7.95</v>
+        <v>7.63</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>7.83</v>
+        <v>7.41</v>
       </c>
       <c r="N46" s="32" t="inlineStr">
         <is>
@@ -3498,16 +3498,16 @@
         </is>
       </c>
       <c r="O46" s="33" t="n">
-        <v>8.06</v>
+        <v>7.85</v>
       </c>
       <c r="P46" s="33" t="n">
-        <v>8.06</v>
+        <v>7.84</v>
       </c>
       <c r="Q46" s="34" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="R46" s="36" t="n">
-        <v>0</v>
+        <v>7.81</v>
+      </c>
+      <c r="R46" s="35" t="n">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="47">
@@ -3522,37 +3522,37 @@
         </is>
       </c>
       <c r="C47" s="25" t="n">
-        <v>12.87</v>
+        <v>12.67</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>12.65</v>
+        <v>12.43</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>12.46</v>
+        <v>12.23</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>12.45</v>
+        <v>12.23</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>12.59</v>
+        <v>12.38</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>12.37</v>
+        <v>12.14</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>12.23</v>
+        <v>11.99</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>12.15</v>
+        <v>11.9</v>
       </c>
       <c r="K47" s="30" t="n">
-        <v>12.34</v>
+        <v>12.09</v>
       </c>
       <c r="L47" s="31" t="n">
-        <v>12.15</v>
+        <v>11.89</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>11.93</v>
+        <v>11.65</v>
       </c>
       <c r="N47" s="32" t="inlineStr">
         <is>
@@ -3560,16 +3560,16 @@
         </is>
       </c>
       <c r="O47" s="33" t="n">
-        <v>12.36</v>
+        <v>12.12</v>
       </c>
       <c r="P47" s="33" t="n">
-        <v>12.36</v>
+        <v>12.11</v>
       </c>
       <c r="Q47" s="34" t="n">
-        <v>12.31</v>
+        <v>12.09</v>
       </c>
       <c r="R47" s="35" t="n">
-        <v>-1.44</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="48">
@@ -3584,37 +3584,37 @@
         </is>
       </c>
       <c r="C48" s="25" t="n">
-        <v>206.74</v>
+        <v>209.85</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>205.54</v>
+        <v>206.85</v>
       </c>
       <c r="E48" s="26" t="n">
-        <v>204.54</v>
+        <v>204.34</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>205</v>
+        <v>205.67</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>205.5</v>
+        <v>206.83</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>204.3</v>
+        <v>203.83</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>203.8</v>
+        <v>202.67</v>
       </c>
       <c r="J48" s="29" t="n">
-        <v>203.1</v>
+        <v>200.83</v>
       </c>
       <c r="K48" s="30" t="n">
-        <v>203.86</v>
+        <v>202.66</v>
       </c>
       <c r="L48" s="31" t="n">
-        <v>202.86</v>
+        <v>200.15</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>201.66</v>
+        <v>197.15</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="O48" s="33" t="n">
-        <v>204.13</v>
+        <v>203.36</v>
       </c>
       <c r="P48" s="33" t="n">
-        <v>203.96</v>
+        <v>202.89</v>
       </c>
       <c r="Q48" s="34" t="n">
         <v>204.5</v>
       </c>
-      <c r="R48" s="35" t="n">
-        <v>-0.15</v>
+      <c r="R48" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3646,54 +3646,54 @@
         </is>
       </c>
       <c r="C49" s="25" t="n">
-        <v>48.27</v>
+        <v>49.85</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>47.97</v>
+        <v>48.57</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>47.71</v>
+        <v>47.5</v>
       </c>
       <c r="F49" s="27" t="n">
-        <v>47.84</v>
+        <v>47.61</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>47.96</v>
+        <v>48.33</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>47.66</v>
+        <v>47.05</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>47.54</v>
+        <v>46.33</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>47.36</v>
+        <v>45.77</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>47.55</v>
+        <v>46.78</v>
       </c>
       <c r="L49" s="31" t="n">
-        <v>47.29</v>
+        <v>45.71</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>46.99</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>44.43</v>
+      </c>
+      <c r="N49" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="33" t="n">
-        <v>47.61</v>
+        <v>46.97</v>
       </c>
       <c r="P49" s="33" t="n">
-        <v>47.57</v>
+        <v>46.88</v>
       </c>
       <c r="Q49" s="34" t="n">
-        <v>47.72</v>
+        <v>46.88</v>
       </c>
       <c r="R49" s="35" t="n">
-        <v>-0.04</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="50">
@@ -3708,54 +3708,54 @@
         </is>
       </c>
       <c r="C50" s="25" t="n">
-        <v>35.37</v>
+        <v>36.78</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>34.81</v>
+        <v>35.26</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>34.34</v>
+        <v>33.99</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>34.65</v>
+        <v>33.81</v>
       </c>
       <c r="G50" s="27" t="n">
         <v>34.83</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>34.27</v>
+        <v>33.31</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>34.09</v>
+        <v>32.29</v>
       </c>
       <c r="J50" s="29" t="n">
-        <v>33.71</v>
+        <v>31.79</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>34.02</v>
+        <v>33.13</v>
       </c>
       <c r="L50" s="31" t="n">
-        <v>33.55</v>
+        <v>31.86</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>30.34</v>
+      </c>
+      <c r="N50" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O50" s="33" t="n">
-        <v>34.17</v>
+        <v>33.28</v>
       </c>
       <c r="P50" s="33" t="n">
-        <v>34.07</v>
+        <v>33.25</v>
       </c>
       <c r="Q50" s="34" t="n">
-        <v>34.46</v>
+        <v>32.8</v>
       </c>
       <c r="R50" s="35" t="n">
-        <v>-0.12</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="51">
@@ -3770,54 +3770,54 @@
         </is>
       </c>
       <c r="C51" s="25" t="n">
-        <v>13.57</v>
+        <v>13.54</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>13.39</v>
+        <v>13.27</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>13.24</v>
+        <v>13.04</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>13.36</v>
+        <v>13.23</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>13.18</v>
+        <v>12.96</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>13.07</v>
+        <v>12.81</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="K51" s="30" t="n">
-        <v>13.14</v>
+        <v>12.89</v>
       </c>
       <c r="L51" s="31" t="n">
-        <v>12.99</v>
+        <v>12.66</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>12.39</v>
+      </c>
+      <c r="N51" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="33" t="n">
-        <v>13.17</v>
+        <v>12.93</v>
       </c>
       <c r="P51" s="33" t="n">
-        <v>13.15</v>
+        <v>12.91</v>
       </c>
       <c r="Q51" s="34" t="n">
-        <v>13.15</v>
+        <v>12.94</v>
       </c>
       <c r="R51" s="35" t="n">
-        <v>-0.15</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="52">
@@ -3832,37 +3832,37 @@
         </is>
       </c>
       <c r="C52" s="25" t="n">
-        <v>61.6</v>
+        <v>61.62</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>60.95</v>
+        <v>60.37</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>60.41</v>
+        <v>59.32</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>60.4</v>
+        <v>59.55</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>60.15</v>
+        <v>58.95</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>59.75</v>
+        <v>58.3</v>
       </c>
       <c r="J52" s="29" t="n">
-        <v>59.5</v>
+        <v>57.7</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>60.04</v>
+        <v>58.62</v>
       </c>
       <c r="L52" s="31" t="n">
-        <v>59.5</v>
+        <v>57.58</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>58.85</v>
+        <v>56.33</v>
       </c>
       <c r="N52" s="32" t="inlineStr">
         <is>
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="O52" s="33" t="n">
-        <v>60.12</v>
+        <v>58.84</v>
       </c>
       <c r="P52" s="33" t="n">
-        <v>60.09</v>
+        <v>58.72</v>
       </c>
       <c r="Q52" s="34" t="n">
-        <v>60</v>
+        <v>58.9</v>
       </c>
       <c r="R52" s="35" t="n">
-        <v>-0.58</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="53">
@@ -3894,37 +3894,37 @@
         </is>
       </c>
       <c r="C53" s="25" t="n">
-        <v>24.93</v>
+        <v>24.83</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>24.3</v>
+        <v>23.87</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>23.77</v>
+        <v>23.07</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>23.81</v>
+        <v>23.05</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>24.18</v>
+        <v>23.65</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>23.55</v>
+        <v>22.69</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>23.18</v>
+        <v>22.09</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>22.92</v>
+        <v>21.73</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>23.42</v>
+        <v>22.53</v>
       </c>
       <c r="L53" s="31" t="n">
-        <v>22.89</v>
+        <v>21.73</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>22.26</v>
+        <v>20.77</v>
       </c>
       <c r="N53" s="32" t="inlineStr">
         <is>
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="O53" s="33" t="n">
-        <v>23.51</v>
+        <v>22.65</v>
       </c>
       <c r="P53" s="33" t="n">
-        <v>23.47</v>
+        <v>22.61</v>
       </c>
       <c r="Q53" s="34" t="n">
-        <v>23.45</v>
+        <v>22.46</v>
       </c>
       <c r="R53" s="35" t="n">
-        <v>-1.51</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="54">
@@ -3956,37 +3956,37 @@
         </is>
       </c>
       <c r="C54" s="25" t="n">
-        <v>5.62</v>
+        <v>5.51</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>5.52</v>
+        <v>5.39</v>
       </c>
       <c r="E54" s="26" t="n">
-        <v>5.44</v>
+        <v>5.29</v>
       </c>
       <c r="F54" s="27" t="n">
-        <v>5.44</v>
+        <v>5.31</v>
       </c>
       <c r="G54" s="27" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="J54" s="29" t="n">
-        <v>5.3</v>
+        <v>5.13</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>5.38</v>
+        <v>5.23</v>
       </c>
       <c r="L54" s="31" t="n">
-        <v>5.3</v>
+        <v>5.13</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>5.2</v>
+        <v>5.01</v>
       </c>
       <c r="N54" s="32" t="inlineStr">
         <is>
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="O54" s="33" t="n">
-        <v>5.39</v>
+        <v>5.24</v>
       </c>
       <c r="P54" s="33" t="n">
-        <v>5.39</v>
+        <v>5.24</v>
       </c>
       <c r="Q54" s="34" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="R54" s="35" t="n">
-        <v>-1.28</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="55">
@@ -4018,54 +4018,54 @@
         </is>
       </c>
       <c r="C55" s="25" t="n">
-        <v>19.21</v>
+        <v>20.1</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>18.74</v>
+        <v>18.8</v>
       </c>
       <c r="E55" s="26" t="n">
-        <v>18.35</v>
+        <v>17.71</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>18.57</v>
+        <v>18.18</v>
       </c>
       <c r="G55" s="27" t="n">
         <v>18.74</v>
       </c>
       <c r="H55" s="28" t="n">
-        <v>18.27</v>
+        <v>17.44</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>18.1</v>
+        <v>16.88</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>17.8</v>
+        <v>16.14</v>
       </c>
       <c r="K55" s="30" t="n">
-        <v>18.08</v>
+        <v>16.99</v>
       </c>
       <c r="L55" s="31" t="n">
-        <v>17.69</v>
+        <v>15.9</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.6</v>
+      </c>
+      <c r="N55" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="33" t="n">
-        <v>18.2</v>
+        <v>17.26</v>
       </c>
       <c r="P55" s="33" t="n">
-        <v>18.12</v>
+        <v>17.09</v>
       </c>
       <c r="Q55" s="34" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="R55" s="36" t="n">
-        <v>1.6</v>
+        <v>17.62</v>
+      </c>
+      <c r="R55" s="35" t="n">
+        <v>-4.19</v>
       </c>
     </row>
     <row r="56">
@@ -4080,37 +4080,37 @@
         </is>
       </c>
       <c r="C56" s="25" t="n">
-        <v>98.41</v>
+        <v>100.29</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>97.51000000000001</v>
+        <v>97.39</v>
       </c>
       <c r="E56" s="26" t="n">
-        <v>96.75</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>96.88</v>
+        <v>95.2</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>97.37</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="H56" s="28" t="n">
-        <v>96.47</v>
+        <v>93.95</v>
       </c>
       <c r="I56" s="29" t="n">
-        <v>95.98</v>
+        <v>92.3</v>
       </c>
       <c r="J56" s="29" t="n">
-        <v>95.56999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>96.25</v>
+        <v>93.34</v>
       </c>
       <c r="L56" s="31" t="n">
-        <v>95.48999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>94.59</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="N56" s="32" t="inlineStr">
         <is>
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="O56" s="33" t="n">
-        <v>96.39</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="P56" s="33" t="n">
-        <v>96.31999999999999</v>
+        <v>93.56</v>
       </c>
       <c r="Q56" s="34" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="R56" s="36" t="n">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="R56" s="35" t="n">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="57">
@@ -4142,54 +4142,54 @@
         </is>
       </c>
       <c r="C57" s="25" t="n">
-        <v>19.24</v>
+        <v>18.1</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>18.6</v>
+        <v>17.98</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>18.06</v>
+        <v>17.88</v>
       </c>
       <c r="F57" s="27" t="n">
-        <v>18.27</v>
+        <v>17.91</v>
       </c>
       <c r="G57" s="27" t="n">
-        <v>18.56</v>
+        <v>17.97</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>17.92</v>
+        <v>17.85</v>
       </c>
       <c r="I57" s="29" t="n">
-        <v>17.63</v>
+        <v>17.79</v>
       </c>
       <c r="J57" s="29" t="n">
-        <v>17.28</v>
+        <v>17.73</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>17.7</v>
+        <v>17.82</v>
       </c>
       <c r="L57" s="31" t="n">
-        <v>17.16</v>
+        <v>17.72</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>16.52</v>
-      </c>
-      <c r="N57" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.6</v>
+      </c>
+      <c r="N57" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="33" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="P57" s="33" t="n">
         <v>17.83</v>
       </c>
-      <c r="P57" s="33" t="n">
-        <v>17.75</v>
-      </c>
       <c r="Q57" s="34" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="R57" s="36" t="n">
-        <v>2.04</v>
+        <v>17.85</v>
+      </c>
+      <c r="R57" s="35" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="58">
@@ -4204,54 +4204,54 @@
         </is>
       </c>
       <c r="C58" s="25" t="n">
-        <v>21.95</v>
+        <v>21.92</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>21.82</v>
+        <v>21.77</v>
       </c>
       <c r="E58" s="26" t="n">
-        <v>21.71</v>
+        <v>21.65</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>21.72</v>
+        <v>21.67</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>21.8</v>
+        <v>21.75</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>21.67</v>
+        <v>21.6</v>
       </c>
       <c r="I58" s="29" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="J58" s="29" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="K58" s="30" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="L58" s="31" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="M58" s="31" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="N58" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O58" s="33" t="n">
         <v>21.59</v>
       </c>
-      <c r="J58" s="29" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="K58" s="30" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="L58" s="31" t="n">
-        <v>21.53</v>
-      </c>
-      <c r="M58" s="31" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O58" s="33" t="n">
-        <v>21.66</v>
-      </c>
       <c r="P58" s="33" t="n">
-        <v>21.65</v>
+        <v>21.57</v>
       </c>
       <c r="Q58" s="34" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="R58" s="36" t="n">
-        <v>0.14</v>
+        <v>21.59</v>
+      </c>
+      <c r="R58" s="35" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="59">
@@ -4266,37 +4266,37 @@
         </is>
       </c>
       <c r="C59" s="25" t="n">
-        <v>23.59</v>
+        <v>23.32</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>23.35</v>
+        <v>23.11</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>23.15</v>
+        <v>22.93</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>23.13</v>
+        <v>23</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>23.29</v>
+        <v>23.09</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>23.05</v>
+        <v>22.88</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>22.89</v>
+        <v>22.79</v>
       </c>
       <c r="J59" s="29" t="n">
-        <v>22.81</v>
+        <v>22.67</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>23.01</v>
+        <v>22.82</v>
       </c>
       <c r="L59" s="31" t="n">
-        <v>22.81</v>
+        <v>22.64</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>22.57</v>
+        <v>22.43</v>
       </c>
       <c r="N59" s="32" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="O59" s="33" t="n">
-        <v>23.04</v>
+        <v>22.86</v>
       </c>
       <c r="P59" s="33" t="n">
-        <v>23.03</v>
+        <v>22.83</v>
       </c>
       <c r="Q59" s="34" t="n">
-        <v>22.98</v>
+        <v>22.9</v>
       </c>
       <c r="R59" s="35" t="n">
-        <v>-0.73</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="60">
@@ -4328,54 +4328,54 @@
         </is>
       </c>
       <c r="C60" s="25" t="n">
-        <v>28.81</v>
+        <v>28.65</v>
       </c>
       <c r="D60" s="25" t="n">
-        <v>28.51</v>
+        <v>28.37</v>
       </c>
       <c r="E60" s="26" t="n">
-        <v>28.25</v>
+        <v>28.14</v>
       </c>
       <c r="F60" s="27" t="n">
-        <v>28.26</v>
+        <v>28.29</v>
       </c>
       <c r="G60" s="27" t="n">
-        <v>28.44</v>
+        <v>28.39</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>28.14</v>
+        <v>28.11</v>
       </c>
       <c r="I60" s="29" t="n">
-        <v>27.96</v>
+        <v>28.01</v>
       </c>
       <c r="J60" s="29" t="n">
-        <v>27.84</v>
+        <v>27.83</v>
       </c>
       <c r="K60" s="30" t="n">
-        <v>28.09</v>
+        <v>27.98</v>
       </c>
       <c r="L60" s="31" t="n">
-        <v>27.83</v>
+        <v>27.75</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="N60" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>27.47</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O60" s="33" t="n">
-        <v>28.12</v>
+        <v>28.06</v>
       </c>
       <c r="P60" s="33" t="n">
-        <v>28.11</v>
+        <v>28</v>
       </c>
       <c r="Q60" s="34" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="R60" s="35" t="n">
-        <v>-0.71</v>
+        <v>28.2</v>
+      </c>
+      <c r="R60" s="36" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="61">
@@ -4390,54 +4390,54 @@
         </is>
       </c>
       <c r="C61" s="25" t="n">
-        <v>46.69</v>
+        <v>46.25</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>46.25</v>
+        <v>45.97</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>45.88</v>
+        <v>45.74</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>46.01</v>
+        <v>45.8</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>46.21</v>
+        <v>45.94</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>45.77</v>
+        <v>45.66</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>45.57</v>
+        <v>45.52</v>
       </c>
       <c r="J61" s="29" t="n">
-        <v>45.33</v>
+        <v>45.38</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>45.64</v>
+        <v>45.58</v>
       </c>
       <c r="L61" s="31" t="n">
-        <v>45.27</v>
+        <v>45.35</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="N61" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>45.07</v>
+      </c>
+      <c r="N61" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O61" s="33" t="n">
-        <v>45.72</v>
+        <v>45.63</v>
       </c>
       <c r="P61" s="33" t="n">
-        <v>45.67</v>
+        <v>45.6</v>
       </c>
       <c r="Q61" s="34" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="R61" s="36" t="n">
-        <v>0.04</v>
+        <v>45.66</v>
+      </c>
+      <c r="R61" s="35" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="62">
@@ -4452,37 +4452,37 @@
         </is>
       </c>
       <c r="C62" s="25" t="n">
-        <v>20.28</v>
+        <v>19.93</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>19.96</v>
+        <v>19.57</v>
       </c>
       <c r="E62" s="26" t="n">
-        <v>19.69</v>
+        <v>19.27</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>19.65</v>
+        <v>19.28</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>19.87</v>
+        <v>19.49</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>19.55</v>
+        <v>19.13</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>19.33</v>
+        <v>18.92</v>
       </c>
       <c r="J62" s="29" t="n">
-        <v>19.23</v>
+        <v>18.77</v>
       </c>
       <c r="K62" s="30" t="n">
-        <v>19.51</v>
+        <v>19.07</v>
       </c>
       <c r="L62" s="31" t="n">
-        <v>19.24</v>
+        <v>18.77</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>18.92</v>
+        <v>18.41</v>
       </c>
       <c r="N62" s="32" t="inlineStr">
         <is>
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="O62" s="33" t="n">
-        <v>19.54</v>
+        <v>19.12</v>
       </c>
       <c r="P62" s="33" t="n">
-        <v>19.54</v>
+        <v>19.1</v>
       </c>
       <c r="Q62" s="34" t="n">
-        <v>19.44</v>
+        <v>19.06</v>
       </c>
       <c r="R62" s="35" t="n">
-        <v>-1.52</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="63">
@@ -4514,54 +4514,54 @@
         </is>
       </c>
       <c r="C63" s="25" t="n">
-        <v>15.53</v>
+        <v>15.49</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>15.38</v>
+        <v>15.35</v>
       </c>
       <c r="E63" s="26" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>15.31</v>
+        <v>15.27</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>15.37</v>
+        <v>15.33</v>
       </c>
       <c r="H63" s="28" t="n">
-        <v>15.22</v>
+        <v>15.19</v>
       </c>
       <c r="I63" s="29" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="J63" s="29" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="K63" s="30" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="L63" s="31" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="M63" s="31" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O63" s="33" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="P63" s="33" t="n">
         <v>15.16</v>
       </c>
-      <c r="J63" s="29" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="K63" s="30" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N63" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O63" s="33" t="n">
+      <c r="Q63" s="34" t="n">
         <v>15.2</v>
       </c>
-      <c r="P63" s="33" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="Q63" s="34" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="R63" s="36" t="n">
-        <v>0.26</v>
+      <c r="R63" s="35" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="64">
@@ -4576,37 +4576,37 @@
         </is>
       </c>
       <c r="C64" s="25" t="n">
-        <v>25.24</v>
+        <v>25.12</v>
       </c>
       <c r="D64" s="25" t="n">
-        <v>25.14</v>
+        <v>25</v>
       </c>
       <c r="E64" s="26" t="n">
-        <v>25.06</v>
+        <v>24.9</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>25.06</v>
+        <v>24.95</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>25.12</v>
+        <v>25</v>
       </c>
       <c r="H64" s="28" t="n">
-        <v>25.02</v>
+        <v>24.88</v>
       </c>
       <c r="I64" s="29" t="n">
-        <v>24.96</v>
+        <v>24.83</v>
       </c>
       <c r="J64" s="29" t="n">
-        <v>24.92</v>
+        <v>24.76</v>
       </c>
       <c r="K64" s="30" t="n">
-        <v>25</v>
+        <v>24.84</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>24.92</v>
+        <v>24.74</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>24.82</v>
+        <v>24.62</v>
       </c>
       <c r="N64" s="32" t="inlineStr">
         <is>
@@ -4614,16 +4614,16 @@
         </is>
       </c>
       <c r="O64" s="33" t="n">
-        <v>25.01</v>
+        <v>24.86</v>
       </c>
       <c r="P64" s="33" t="n">
-        <v>25.01</v>
+        <v>24.85</v>
       </c>
       <c r="Q64" s="34" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="R64" s="35" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="65">
@@ -4638,37 +4638,37 @@
         </is>
       </c>
       <c r="C65" s="25" t="n">
-        <v>7.58</v>
+        <v>7.51</v>
       </c>
       <c r="D65" s="25" t="n">
-        <v>7.46</v>
+        <v>7.36</v>
       </c>
       <c r="E65" s="26" t="n">
-        <v>7.36</v>
+        <v>7.24</v>
       </c>
       <c r="F65" s="27" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="G65" s="27" t="n">
         <v>7.35</v>
       </c>
-      <c r="G65" s="27" t="n">
-        <v>7.43</v>
-      </c>
       <c r="H65" s="28" t="n">
-        <v>7.31</v>
+        <v>7.2</v>
       </c>
       <c r="I65" s="29" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="J65" s="29" t="n">
-        <v>7.19</v>
+        <v>7.05</v>
       </c>
       <c r="K65" s="30" t="n">
-        <v>7.3</v>
+        <v>7.15</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>7.2</v>
+        <v>7.03</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7.08</v>
+        <v>6.88</v>
       </c>
       <c r="N65" s="32" t="inlineStr">
         <is>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="O65" s="33" t="n">
-        <v>7.31</v>
+        <v>7.18</v>
       </c>
       <c r="P65" s="33" t="n">
-        <v>7.31</v>
+        <v>7.16</v>
       </c>
       <c r="Q65" s="34" t="n">
-        <v>7.27</v>
+        <v>7.22</v>
       </c>
       <c r="R65" s="35" t="n">
-        <v>-1.76</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4700,54 +4700,54 @@
         </is>
       </c>
       <c r="C66" s="25" t="n">
-        <v>4.97</v>
+        <v>5.06</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
       <c r="E66" s="26" t="n">
-        <v>4.94</v>
+        <v>4.91</v>
       </c>
       <c r="F66" s="27" t="n">
-        <v>4.94</v>
+        <v>4.91</v>
       </c>
       <c r="G66" s="27" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="H66" s="28" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="I66" s="29" t="n">
-        <v>4.92</v>
+        <v>4.83</v>
       </c>
       <c r="J66" s="29" t="n">
-        <v>4.91</v>
+        <v>4.8</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>4.92</v>
+        <v>4.87</v>
       </c>
       <c r="L66" s="31" t="n">
-        <v>4.91</v>
+        <v>4.8</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.72</v>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O66" s="33" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="P66" s="33" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="Q66" s="34" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="R66" s="36" t="n">
-        <v>0.2</v>
+        <v>4.86</v>
+      </c>
+      <c r="R66" s="35" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="67">
@@ -4762,54 +4762,54 @@
         </is>
       </c>
       <c r="C67" s="25" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
       <c r="D67" s="25" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E67" s="26" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G67" s="27" t="n">
         <v>4.98</v>
       </c>
-      <c r="E67" s="26" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="F67" s="27" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="G67" s="27" t="n">
-        <v>4.97</v>
-      </c>
       <c r="H67" s="28" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="I67" s="29" t="n">
-        <v>4.91</v>
+        <v>4.79</v>
       </c>
       <c r="J67" s="29" t="n">
-        <v>4.89</v>
+        <v>4.76</v>
       </c>
       <c r="K67" s="30" t="n">
-        <v>4.93</v>
+        <v>4.85</v>
       </c>
       <c r="L67" s="31" t="n">
-        <v>4.9</v>
+        <v>4.76</v>
       </c>
       <c r="M67" s="31" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O67" s="33" t="n">
         <v>4.86</v>
       </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O67" s="33" t="n">
-        <v>4.93</v>
-      </c>
       <c r="P67" s="33" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="Q67" s="34" t="n">
-        <v>4.92</v>
+        <v>4.83</v>
       </c>
       <c r="R67" s="35" t="n">
-        <v>-0.4</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="68">
@@ -4824,54 +4824,54 @@
         </is>
       </c>
       <c r="C68" s="25" t="n">
-        <v>67.45999999999999</v>
+        <v>66.55</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>66.70999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E68" s="26" t="n">
-        <v>66.08</v>
+        <v>65.36</v>
       </c>
       <c r="F68" s="27" t="n">
-        <v>66.13</v>
+        <v>65.48</v>
       </c>
       <c r="G68" s="27" t="n">
-        <v>66.56999999999999</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>65.81999999999999</v>
+        <v>65.17</v>
       </c>
       <c r="I68" s="29" t="n">
-        <v>65.38</v>
+        <v>64.83</v>
       </c>
       <c r="J68" s="29" t="n">
-        <v>65.06999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="K68" s="30" t="n">
-        <v>65.67</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="L68" s="31" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O68" s="33" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="P68" s="33" t="n">
         <v>65.04000000000001</v>
       </c>
-      <c r="M68" s="31" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O68" s="33" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="P68" s="33" t="n">
-        <v>65.72</v>
-      </c>
       <c r="Q68" s="34" t="n">
-        <v>65.7</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="R68" s="35" t="n">
-        <v>-0.38</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="69">
@@ -4886,37 +4886,37 @@
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>73.23</v>
+        <v>70.52</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>71.73</v>
+        <v>69.52</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>70.47</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F69" s="27" t="n">
-        <v>70.43000000000001</v>
+        <v>68.63</v>
       </c>
       <c r="G69" s="27" t="n">
-        <v>71.37</v>
+        <v>69.27</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>69.87</v>
+        <v>68.27</v>
       </c>
       <c r="I69" s="29" t="n">
-        <v>68.93000000000001</v>
+        <v>67.63</v>
       </c>
       <c r="J69" s="29" t="n">
-        <v>68.37</v>
+        <v>67.27</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>69.63</v>
+        <v>68.12</v>
       </c>
       <c r="L69" s="31" t="n">
-        <v>68.37</v>
+        <v>67.28</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>66.87</v>
+        <v>66.28</v>
       </c>
       <c r="N69" s="32" t="inlineStr">
         <is>
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="O69" s="33" t="n">
-        <v>69.81</v>
+        <v>68.23</v>
       </c>
       <c r="P69" s="33" t="n">
-        <v>69.75</v>
+        <v>68.2</v>
       </c>
       <c r="Q69" s="34" t="n">
-        <v>69.5</v>
+        <v>68</v>
       </c>
       <c r="R69" s="35" t="n">
-        <v>-0.86</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="70">
@@ -4948,54 +4948,54 @@
         </is>
       </c>
       <c r="C70" s="25" t="n">
-        <v>85.23999999999999</v>
+        <v>84.36</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>84.29000000000001</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="E70" s="26" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="F70" s="27" t="n">
-        <v>83.75</v>
+        <v>82.63</v>
       </c>
       <c r="G70" s="27" t="n">
-        <v>84.2</v>
+        <v>83.22</v>
       </c>
       <c r="H70" s="28" t="n">
-        <v>83.25</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I70" s="29" t="n">
-        <v>82.8</v>
+        <v>81.73</v>
       </c>
       <c r="J70" s="29" t="n">
-        <v>82.3</v>
+        <v>81.42</v>
       </c>
       <c r="K70" s="30" t="n">
-        <v>82.95999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="L70" s="31" t="n">
-        <v>82.16</v>
+        <v>81.44</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>80.54000000000001</v>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="33" t="n">
-        <v>83.14</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="P70" s="33" t="n">
-        <v>83.03</v>
+        <v>82.27</v>
       </c>
       <c r="Q70" s="34" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="R70" s="36" t="n">
-        <v>0.36</v>
+        <v>82.05</v>
+      </c>
+      <c r="R70" s="35" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="71">
@@ -5010,37 +5010,37 @@
         </is>
       </c>
       <c r="C71" s="25" t="n">
-        <v>126.83</v>
+        <v>124.28</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>122.73</v>
+        <v>121.88</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>119.3</v>
+        <v>119.87</v>
       </c>
       <c r="F71" s="27" t="n">
-        <v>120.7</v>
+        <v>120.2</v>
       </c>
       <c r="G71" s="27" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="H71" s="28" t="n">
-        <v>118.4</v>
+        <v>119.1</v>
       </c>
       <c r="I71" s="29" t="n">
-        <v>116.6</v>
+        <v>117.8</v>
       </c>
       <c r="J71" s="29" t="n">
-        <v>114.3</v>
+        <v>116.7</v>
       </c>
       <c r="K71" s="30" t="n">
-        <v>117</v>
+        <v>118.53</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>113.57</v>
+        <v>116.52</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>109.47</v>
+        <v>114.12</v>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
@@ -5048,16 +5048,16 @@
         </is>
       </c>
       <c r="O71" s="33" t="n">
-        <v>117.86</v>
+        <v>118.91</v>
       </c>
       <c r="P71" s="33" t="n">
-        <v>117.32</v>
+        <v>118.72</v>
       </c>
       <c r="Q71" s="34" t="n">
         <v>118.9</v>
       </c>
       <c r="R71" s="36" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5072,54 +5072,54 @@
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>24.44</v>
+        <v>25.9</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>24.29</v>
+        <v>25.19</v>
       </c>
       <c r="E72" s="26" t="n">
-        <v>24.17</v>
+        <v>24.59</v>
       </c>
       <c r="F72" s="27" t="n">
-        <v>24.18</v>
+        <v>24.77</v>
       </c>
       <c r="G72" s="27" t="n">
-        <v>24.27</v>
+        <v>25.12</v>
       </c>
       <c r="H72" s="28" t="n">
-        <v>24.12</v>
+        <v>24.41</v>
       </c>
       <c r="I72" s="29" t="n">
-        <v>24.03</v>
+        <v>24.06</v>
       </c>
       <c r="J72" s="29" t="n">
-        <v>23.97</v>
+        <v>23.7</v>
       </c>
       <c r="K72" s="30" t="n">
-        <v>24.08</v>
+        <v>24.2</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>23.96</v>
+        <v>23.6</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>22.89</v>
+      </c>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O72" s="33" t="n">
-        <v>24.11</v>
+        <v>24.33</v>
       </c>
       <c r="P72" s="33" t="n">
-        <v>24.09</v>
+        <v>24.25</v>
       </c>
       <c r="Q72" s="34" t="n">
-        <v>24.1</v>
+        <v>24.43</v>
       </c>
       <c r="R72" s="36" t="n">
-        <v>0.04</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="73">
@@ -5134,37 +5134,37 @@
         </is>
       </c>
       <c r="C73" s="25" t="n">
-        <v>19.96</v>
+        <v>20.1</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>19.78</v>
+        <v>19.64</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>19.63</v>
+        <v>19.26</v>
       </c>
       <c r="F73" s="27" t="n">
-        <v>19.62</v>
+        <v>19.21</v>
       </c>
       <c r="G73" s="27" t="n">
-        <v>19.73</v>
+        <v>19.51</v>
       </c>
       <c r="H73" s="28" t="n">
-        <v>19.55</v>
+        <v>19.05</v>
       </c>
       <c r="I73" s="29" t="n">
-        <v>19.44</v>
+        <v>18.75</v>
       </c>
       <c r="J73" s="29" t="n">
-        <v>19.37</v>
+        <v>18.59</v>
       </c>
       <c r="K73" s="30" t="n">
-        <v>19.53</v>
+        <v>19</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>19.38</v>
+        <v>18.62</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>19.2</v>
+        <v>18.16</v>
       </c>
       <c r="N73" s="32" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="O73" s="33" t="n">
-        <v>19.55</v>
+        <v>19.05</v>
       </c>
       <c r="P73" s="33" t="n">
-        <v>19.54</v>
+        <v>19.04</v>
       </c>
       <c r="Q73" s="34" t="n">
-        <v>19.5</v>
+        <v>18.9</v>
       </c>
       <c r="R73" s="35" t="n">
-        <v>-0.86</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="74">
@@ -5196,54 +5196,54 @@
         </is>
       </c>
       <c r="C74" s="25" t="n">
-        <v>238.71</v>
+        <v>235.24</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>236.11</v>
+        <v>233.24</v>
       </c>
       <c r="E74" s="26" t="n">
-        <v>233.93</v>
+        <v>231.56</v>
       </c>
       <c r="F74" s="27" t="n">
-        <v>234.17</v>
+        <v>231.53</v>
       </c>
       <c r="G74" s="27" t="n">
-        <v>235.63</v>
+        <v>232.77</v>
       </c>
       <c r="H74" s="28" t="n">
-        <v>233.03</v>
+        <v>230.77</v>
       </c>
       <c r="I74" s="29" t="n">
-        <v>231.57</v>
+        <v>229.53</v>
       </c>
       <c r="J74" s="29" t="n">
-        <v>230.43</v>
+        <v>228.77</v>
       </c>
       <c r="K74" s="30" t="n">
-        <v>232.47</v>
+        <v>230.44</v>
       </c>
       <c r="L74" s="31" t="n">
-        <v>230.29</v>
+        <v>228.76</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>227.69</v>
-      </c>
-      <c r="N74" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>226.76</v>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O74" s="33" t="n">
-        <v>232.85</v>
+        <v>230.68</v>
       </c>
       <c r="P74" s="33" t="n">
-        <v>232.67</v>
+        <v>230.6</v>
       </c>
       <c r="Q74" s="34" t="n">
-        <v>232.7</v>
+        <v>230.3</v>
       </c>
       <c r="R74" s="35" t="n">
-        <v>-0.13</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="75">
@@ -5258,54 +5258,54 @@
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>15.53</v>
+        <v>16.16</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>15.36</v>
+        <v>15.72</v>
       </c>
       <c r="E75" s="26" t="n">
-        <v>15.21</v>
+        <v>15.35</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>15.25</v>
+        <v>15.51</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>15.34</v>
+        <v>15.7</v>
       </c>
       <c r="H75" s="28" t="n">
-        <v>15.17</v>
+        <v>15.26</v>
       </c>
       <c r="I75" s="29" t="n">
-        <v>15.08</v>
+        <v>15.07</v>
       </c>
       <c r="J75" s="29" t="n">
-        <v>15</v>
+        <v>14.82</v>
       </c>
       <c r="K75" s="30" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="L75" s="31" t="n">
-        <v>14.97</v>
+        <v>14.74</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.3</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="33" t="n">
-        <v>15.15</v>
+        <v>15.2</v>
       </c>
       <c r="P75" s="33" t="n">
-        <v>15.13</v>
+        <v>15.14</v>
       </c>
       <c r="Q75" s="34" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="R75" s="35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>15.32</v>
+      </c>
+      <c r="R75" s="36" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="76">
@@ -5320,54 +5320,54 @@
         </is>
       </c>
       <c r="C76" s="25" t="n">
-        <v>37.25</v>
+        <v>36.5</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>36.87</v>
+        <v>35.88</v>
       </c>
       <c r="E76" s="26" t="n">
-        <v>36.56</v>
+        <v>35.36</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>36.77</v>
+        <v>35.37</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>36.89</v>
+        <v>35.75</v>
       </c>
       <c r="H76" s="28" t="n">
-        <v>36.51</v>
+        <v>35.13</v>
       </c>
       <c r="I76" s="29" t="n">
-        <v>36.39</v>
+        <v>34.75</v>
       </c>
       <c r="J76" s="29" t="n">
-        <v>36.13</v>
+        <v>34.51</v>
       </c>
       <c r="K76" s="30" t="n">
-        <v>36.34</v>
+        <v>35.02</v>
       </c>
       <c r="L76" s="31" t="n">
-        <v>36.03</v>
+        <v>34.5</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="N76" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>33.88</v>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O76" s="33" t="n">
-        <v>36.44</v>
+        <v>35.1</v>
       </c>
       <c r="P76" s="33" t="n">
-        <v>36.37</v>
+        <v>35.06</v>
       </c>
       <c r="Q76" s="34" t="n">
-        <v>36.64</v>
-      </c>
-      <c r="R76" s="36" t="n">
-        <v>1.27</v>
+        <v>35</v>
+      </c>
+      <c r="R76" s="35" t="n">
+        <v>-4.48</v>
       </c>
     </row>
     <row r="77">
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="C77" s="25" t="n">
-        <v>24.53</v>
+        <v>23.43</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>23.85</v>
+        <v>22.88</v>
       </c>
       <c r="E77" s="26" t="n">
-        <v>23.28</v>
+        <v>22.42</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>23.66</v>
+        <v>22.79</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>22.98</v>
+        <v>22.24</v>
       </c>
       <c r="I77" s="29" t="n">
-        <v>22.52</v>
+        <v>21.95</v>
       </c>
       <c r="J77" s="29" t="n">
-        <v>22.3</v>
+        <v>21.69</v>
       </c>
       <c r="K77" s="30" t="n">
-        <v>22.9</v>
+        <v>22.11</v>
       </c>
       <c r="L77" s="31" t="n">
-        <v>22.33</v>
+        <v>21.65</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>21.65</v>
+        <v>21.1</v>
       </c>
       <c r="N77" s="32" t="inlineStr">
         <is>
@@ -5420,16 +5420,16 @@
         </is>
       </c>
       <c r="O77" s="33" t="n">
-        <v>22.96</v>
+        <v>22.2</v>
       </c>
       <c r="P77" s="33" t="n">
-        <v>22.95</v>
+        <v>22.15</v>
       </c>
       <c r="Q77" s="34" t="n">
-        <v>22.75</v>
+        <v>22.2</v>
       </c>
       <c r="R77" s="35" t="n">
-        <v>-2.53</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="78">
@@ -5444,54 +5444,54 @@
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>46.25</v>
+        <v>51.34</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>45.43</v>
+        <v>48.04</v>
       </c>
       <c r="E78" s="26" t="n">
-        <v>44.74</v>
+        <v>45.27</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>44.66</v>
+        <v>46.85</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>45.2</v>
+        <v>48.07</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>44.38</v>
+        <v>44.77</v>
       </c>
       <c r="I78" s="29" t="n">
-        <v>43.84</v>
+        <v>43.55</v>
       </c>
       <c r="J78" s="29" t="n">
-        <v>43.56</v>
+        <v>41.47</v>
       </c>
       <c r="K78" s="30" t="n">
-        <v>44.28</v>
+        <v>43.43</v>
       </c>
       <c r="L78" s="31" t="n">
-        <v>43.59</v>
+        <v>40.66</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>37.36</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O78" s="33" t="n">
-        <v>44.36</v>
+        <v>44.23</v>
       </c>
       <c r="P78" s="33" t="n">
-        <v>44.34</v>
+        <v>43.68</v>
       </c>
       <c r="Q78" s="34" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="R78" s="35" t="n">
-        <v>-1.56</v>
+        <v>45.62</v>
+      </c>
+      <c r="R78" s="36" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="79">
@@ -5506,54 +5506,54 @@
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>5.68</v>
+        <v>5.54</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>5.58</v>
+        <v>5.49</v>
       </c>
       <c r="F79" s="27" t="n">
-        <v>5.6</v>
+        <v>5.51</v>
       </c>
       <c r="G79" s="27" t="n">
-        <v>5.66</v>
+        <v>5.53</v>
       </c>
       <c r="H79" s="28" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="I79" s="29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="J79" s="29" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="K79" s="30" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O79" s="33" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="P79" s="33" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Q79" s="34" t="n">
         <v>5.48</v>
       </c>
-      <c r="J79" s="29" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="K79" s="30" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O79" s="33" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="P79" s="33" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="Q79" s="34" t="n">
-        <v>5.53</v>
-      </c>
       <c r="R79" s="35" t="n">
-        <v>-1.25</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="80">
@@ -5568,54 +5568,54 @@
         </is>
       </c>
       <c r="C80" s="25" t="n">
-        <v>19.41</v>
+        <v>19.32</v>
       </c>
       <c r="D80" s="25" t="n">
-        <v>19.15</v>
+        <v>19.03</v>
       </c>
       <c r="E80" s="26" t="n">
-        <v>18.93</v>
+        <v>18.79</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>19.05</v>
+        <v>18.82</v>
       </c>
       <c r="G80" s="27" t="n">
-        <v>19.15</v>
+        <v>18.98</v>
       </c>
       <c r="H80" s="28" t="n">
-        <v>18.89</v>
+        <v>18.69</v>
       </c>
       <c r="I80" s="29" t="n">
-        <v>18.79</v>
+        <v>18.53</v>
       </c>
       <c r="J80" s="29" t="n">
-        <v>18.63</v>
+        <v>18.4</v>
       </c>
       <c r="K80" s="30" t="n">
-        <v>18.79</v>
+        <v>18.62</v>
       </c>
       <c r="L80" s="31" t="n">
-        <v>18.57</v>
+        <v>18.38</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>18.31</v>
-      </c>
-      <c r="N80" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>18.09</v>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O80" s="33" t="n">
-        <v>18.85</v>
+        <v>18.67</v>
       </c>
       <c r="P80" s="33" t="n">
-        <v>18.81</v>
+        <v>18.65</v>
       </c>
       <c r="Q80" s="34" t="n">
-        <v>18.95</v>
-      </c>
-      <c r="R80" s="36" t="n">
-        <v>0.8</v>
+        <v>18.66</v>
+      </c>
+      <c r="R80" s="35" t="n">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="81">
@@ -5630,54 +5630,54 @@
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>82.34</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="D81" s="25" t="n">
-        <v>81.39</v>
+        <v>81.09</v>
       </c>
       <c r="E81" s="26" t="n">
-        <v>80.59</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>80.92</v>
+        <v>80.55</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>81.33</v>
+        <v>81</v>
       </c>
       <c r="H81" s="28" t="n">
-        <v>80.38</v>
+        <v>80.05</v>
       </c>
       <c r="I81" s="29" t="n">
-        <v>79.97</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J81" s="29" t="n">
-        <v>79.43000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K81" s="30" t="n">
-        <v>80.06</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="L81" s="31" t="n">
-        <v>79.26000000000001</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>78.31</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>78.01000000000001</v>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O81" s="33" t="n">
-        <v>80.26000000000001</v>
+        <v>79.94</v>
       </c>
       <c r="P81" s="33" t="n">
-        <v>80.13</v>
+        <v>79.83</v>
       </c>
       <c r="Q81" s="34" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="R81" s="36" t="n">
-        <v>0.5</v>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="R81" s="35" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="82">
@@ -5692,54 +5692,54 @@
         </is>
       </c>
       <c r="C82" s="25" t="n">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="D82" s="25" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="E82" s="26" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="F82" s="27" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="G82" s="27" t="n">
         <v>4.67</v>
       </c>
       <c r="H82" s="28" t="n">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="J82" s="29" t="n">
-        <v>4.59</v>
+        <v>4.47</v>
       </c>
       <c r="K82" s="30" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="L82" s="31" t="n">
-        <v>4.6</v>
+        <v>4.47</v>
       </c>
       <c r="M82" s="31" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O82" s="33" t="n">
         <v>4.56</v>
       </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O82" s="33" t="n">
-        <v>4.63</v>
-      </c>
       <c r="P82" s="33" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="Q82" s="34" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="R82" s="35" t="n">
-        <v>-0.65</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="83">
@@ -5754,54 +5754,54 @@
         </is>
       </c>
       <c r="C83" s="25" t="n">
-        <v>62.19</v>
+        <v>62.22</v>
       </c>
       <c r="D83" s="25" t="n">
-        <v>61.24</v>
+        <v>60.82</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>60.44</v>
+        <v>59.64</v>
       </c>
       <c r="F83" s="27" t="n">
-        <v>60.4</v>
+        <v>59.85</v>
       </c>
       <c r="G83" s="27" t="n">
-        <v>61</v>
+        <v>60.6</v>
       </c>
       <c r="H83" s="28" t="n">
-        <v>60.05</v>
+        <v>59.2</v>
       </c>
       <c r="I83" s="29" t="n">
-        <v>59.45</v>
+        <v>58.45</v>
       </c>
       <c r="J83" s="29" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="K83" s="30" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="L83" s="31" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="M83" s="31" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="N83" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O83" s="33" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="P83" s="33" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="Q83" s="34" t="n">
         <v>59.1</v>
       </c>
-      <c r="K83" s="30" t="n">
-        <v>59.91</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="N83" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O83" s="33" t="n">
-        <v>60.02</v>
-      </c>
-      <c r="P83" s="33" t="n">
-        <v>59.98</v>
-      </c>
-      <c r="Q83" s="34" t="n">
-        <v>59.8</v>
-      </c>
       <c r="R83" s="35" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="84">
@@ -5816,54 +5816,54 @@
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>39.5</v>
+        <v>39.05</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>39.18</v>
+        <v>38.67</v>
       </c>
       <c r="E84" s="26" t="n">
-        <v>38.91</v>
+        <v>38.36</v>
       </c>
       <c r="F84" s="27" t="n">
-        <v>38.94</v>
+        <v>38.35</v>
       </c>
       <c r="G84" s="27" t="n">
-        <v>39.12</v>
+        <v>38.59</v>
       </c>
       <c r="H84" s="28" t="n">
-        <v>38.8</v>
+        <v>38.21</v>
       </c>
       <c r="I84" s="29" t="n">
-        <v>38.62</v>
+        <v>37.97</v>
       </c>
       <c r="J84" s="29" t="n">
-        <v>38.48</v>
+        <v>37.83</v>
       </c>
       <c r="K84" s="30" t="n">
-        <v>38.73</v>
+        <v>38.14</v>
       </c>
       <c r="L84" s="31" t="n">
-        <v>38.46</v>
+        <v>37.83</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="N84" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>37.45</v>
+      </c>
+      <c r="N84" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="33" t="n">
-        <v>38.78</v>
+        <v>38.19</v>
       </c>
       <c r="P84" s="33" t="n">
-        <v>38.76</v>
+        <v>38.17</v>
       </c>
       <c r="Q84" s="34" t="n">
-        <v>38.76</v>
+        <v>38.12</v>
       </c>
       <c r="R84" s="35" t="n">
-        <v>-0.62</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="85">
@@ -5878,37 +5878,37 @@
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>94.59</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>93.39</v>
+        <v>92.08</v>
       </c>
       <c r="E85" s="26" t="n">
-        <v>92.39</v>
+        <v>91.36</v>
       </c>
       <c r="F85" s="27" t="n">
-        <v>92.38</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G85" s="27" t="n">
-        <v>93.12</v>
+        <v>92</v>
       </c>
       <c r="H85" s="28" t="n">
-        <v>91.92</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I85" s="29" t="n">
-        <v>91.18000000000001</v>
+        <v>90.75</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>90.72</v>
+        <v>90.3</v>
       </c>
       <c r="K85" s="30" t="n">
-        <v>91.70999999999999</v>
+        <v>90.89</v>
       </c>
       <c r="L85" s="31" t="n">
-        <v>90.70999999999999</v>
+        <v>90.17</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>89.51000000000001</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="N85" s="32" t="inlineStr">
         <is>
@@ -5916,16 +5916,16 @@
         </is>
       </c>
       <c r="O85" s="33" t="n">
-        <v>91.86</v>
+        <v>91.05</v>
       </c>
       <c r="P85" s="33" t="n">
-        <v>91.81</v>
+        <v>90.95</v>
       </c>
       <c r="Q85" s="34" t="n">
-        <v>91.65000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="R85" s="35" t="n">
-        <v>-1.35</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="86">
@@ -5940,41 +5940,41 @@
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>17.03</v>
+        <v>16.5</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>16.67</v>
+        <v>16.37</v>
       </c>
       <c r="E86" s="26" t="n">
-        <v>16.37</v>
+        <v>16.26</v>
       </c>
       <c r="F86" s="27" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="G86" s="27" t="n">
         <v>16.38</v>
       </c>
-      <c r="G86" s="27" t="n">
-        <v>16.59</v>
-      </c>
       <c r="H86" s="28" t="n">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="I86" s="29" t="n">
-        <v>16.02</v>
+        <v>16.2</v>
       </c>
       <c r="J86" s="29" t="n">
-        <v>15.87</v>
+        <v>16.12</v>
       </c>
       <c r="K86" s="30" t="n">
-        <v>16.17</v>
+        <v>16.19</v>
       </c>
       <c r="L86" s="31" t="n">
-        <v>15.87</v>
+        <v>16.08</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="N86" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.95</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="33" t="n">
@@ -5984,10 +5984,10 @@
         <v>16.2</v>
       </c>
       <c r="Q86" s="34" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="R86" s="35" t="n">
-        <v>-1.76</v>
+        <v>16.29</v>
+      </c>
+      <c r="R86" s="36" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="87">
@@ -6002,54 +6002,54 @@
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>123.57</v>
+        <v>123.05</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>121.67</v>
+        <v>121.35</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>120.08</v>
+        <v>119.93</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>120.87</v>
+        <v>120.2</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>121.63</v>
+        <v>121.1</v>
       </c>
       <c r="H87" s="28" t="n">
-        <v>119.73</v>
+        <v>119.4</v>
       </c>
       <c r="I87" s="29" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="J87" s="29" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="K87" s="30" t="n">
         <v>118.97</v>
       </c>
-      <c r="J87" s="29" t="n">
-        <v>117.83</v>
-      </c>
-      <c r="K87" s="30" t="n">
-        <v>119.02</v>
-      </c>
       <c r="L87" s="31" t="n">
-        <v>117.43</v>
+        <v>117.55</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>115.53</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>115.85</v>
+      </c>
+      <c r="N87" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="33" t="n">
-        <v>119.45</v>
+        <v>119.25</v>
       </c>
       <c r="P87" s="33" t="n">
-        <v>119.17</v>
+        <v>119.11</v>
       </c>
       <c r="Q87" s="34" t="n">
-        <v>120.1</v>
-      </c>
-      <c r="R87" s="36" t="n">
-        <v>0.67</v>
+        <v>119.3</v>
+      </c>
+      <c r="R87" s="35" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="88">
@@ -6064,54 +6064,54 @@
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>66.65000000000001</v>
+        <v>65.67</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>64.3</v>
+        <v>64.02</v>
       </c>
       <c r="E88" s="26" t="n">
-        <v>62.33</v>
+        <v>62.64</v>
       </c>
       <c r="F88" s="27" t="n">
-        <v>63.33</v>
+        <v>62.78</v>
       </c>
       <c r="G88" s="27" t="n">
-        <v>64.27</v>
+        <v>63.72</v>
       </c>
       <c r="H88" s="28" t="n">
-        <v>61.92</v>
+        <v>62.07</v>
       </c>
       <c r="I88" s="29" t="n">
-        <v>60.98</v>
+        <v>61.13</v>
       </c>
       <c r="J88" s="29" t="n">
-        <v>59.57</v>
+        <v>60.42</v>
       </c>
       <c r="K88" s="30" t="n">
-        <v>61.02</v>
+        <v>61.71</v>
       </c>
       <c r="L88" s="31" t="n">
-        <v>59.05</v>
+        <v>60.33</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="N88" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>58.68</v>
+      </c>
+      <c r="N88" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="33" t="n">
-        <v>61.56</v>
+        <v>61.95</v>
       </c>
       <c r="P88" s="33" t="n">
-        <v>61.2</v>
+        <v>61.84</v>
       </c>
       <c r="Q88" s="34" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="R88" s="36" t="n">
-        <v>3.14</v>
+        <v>61.85</v>
+      </c>
+      <c r="R88" s="35" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="89">
@@ -6126,37 +6126,37 @@
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>10.07</v>
+        <v>9.91</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="E89" s="26" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>9.82</v>
+        <v>9.69</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>9.91</v>
+        <v>9.76</v>
       </c>
       <c r="H89" s="28" t="n">
-        <v>9.779999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I89" s="29" t="n">
-        <v>9.69</v>
+        <v>9.57</v>
       </c>
       <c r="J89" s="29" t="n">
-        <v>9.65</v>
+        <v>9.52</v>
       </c>
       <c r="K89" s="30" t="n">
-        <v>9.76</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L89" s="31" t="n">
-        <v>9.65</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>9.52</v>
+        <v>9.41</v>
       </c>
       <c r="N89" s="32" t="inlineStr">
         <is>
@@ -6164,16 +6164,16 @@
         </is>
       </c>
       <c r="O89" s="33" t="n">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="P89" s="33" t="n">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q89" s="34" t="n">
-        <v>9.74</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R89" s="35" t="n">
-        <v>-0.71</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="90">
@@ -6188,37 +6188,37 @@
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>18.14</v>
+        <v>18.09</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>17.71</v>
+        <v>17.53</v>
       </c>
       <c r="E90" s="26" t="n">
-        <v>17.35</v>
+        <v>17.06</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>17.38</v>
+        <v>17.28</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>17.62</v>
+        <v>17.51</v>
       </c>
       <c r="H90" s="28" t="n">
-        <v>17.19</v>
+        <v>16.95</v>
       </c>
       <c r="I90" s="29" t="n">
-        <v>16.95</v>
+        <v>16.72</v>
       </c>
       <c r="J90" s="29" t="n">
-        <v>16.76</v>
+        <v>16.39</v>
       </c>
       <c r="K90" s="30" t="n">
-        <v>17.1</v>
+        <v>16.74</v>
       </c>
       <c r="L90" s="31" t="n">
-        <v>16.74</v>
+        <v>16.27</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>16.31</v>
+        <v>15.71</v>
       </c>
       <c r="N90" s="32" t="inlineStr">
         <is>
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="O90" s="33" t="n">
-        <v>17.17</v>
+        <v>16.87</v>
       </c>
       <c r="P90" s="33" t="n">
-        <v>17.14</v>
+        <v>16.79</v>
       </c>
       <c r="Q90" s="34" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="R90" s="36" t="n">
-        <v>0.06</v>
+        <v>17.05</v>
+      </c>
+      <c r="R90" s="35" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="91">
@@ -6250,37 +6250,37 @@
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>18.37</v>
+        <v>18.35</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>18.1</v>
+        <v>17.88</v>
       </c>
       <c r="E91" s="26" t="n">
-        <v>17.87</v>
+        <v>17.49</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>17.84</v>
+        <v>17.61</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>18.02</v>
+        <v>17.83</v>
       </c>
       <c r="H91" s="28" t="n">
-        <v>17.75</v>
+        <v>17.36</v>
       </c>
       <c r="I91" s="29" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>17.48</v>
+        <v>16.89</v>
       </c>
       <c r="K91" s="30" t="n">
-        <v>17.72</v>
+        <v>17.22</v>
       </c>
       <c r="L91" s="31" t="n">
-        <v>17.49</v>
+        <v>16.83</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>17.22</v>
+        <v>16.36</v>
       </c>
       <c r="N91" s="32" t="inlineStr">
         <is>
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="O91" s="33" t="n">
-        <v>17.75</v>
+        <v>17.31</v>
       </c>
       <c r="P91" s="33" t="n">
-        <v>17.74</v>
+        <v>17.26</v>
       </c>
       <c r="Q91" s="34" t="n">
-        <v>17.66</v>
+        <v>17.38</v>
       </c>
       <c r="R91" s="35" t="n">
-        <v>-1.45</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="92">
@@ -6312,37 +6312,37 @@
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>31.67</v>
+        <v>31.64</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>31.29</v>
+        <v>31.02</v>
       </c>
       <c r="E92" s="26" t="n">
-        <v>30.98</v>
+        <v>30.5</v>
       </c>
       <c r="F92" s="27" t="n">
-        <v>30.96</v>
+        <v>30.51</v>
       </c>
       <c r="G92" s="27" t="n">
-        <v>31.2</v>
+        <v>30.89</v>
       </c>
       <c r="H92" s="28" t="n">
-        <v>30.82</v>
+        <v>30.27</v>
       </c>
       <c r="I92" s="29" t="n">
-        <v>30.58</v>
+        <v>29.89</v>
       </c>
       <c r="J92" s="29" t="n">
-        <v>30.44</v>
+        <v>29.65</v>
       </c>
       <c r="K92" s="30" t="n">
-        <v>30.76</v>
+        <v>30.16</v>
       </c>
       <c r="L92" s="31" t="n">
-        <v>30.45</v>
+        <v>29.64</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>30.07</v>
+        <v>29.02</v>
       </c>
       <c r="N92" s="32" t="inlineStr">
         <is>
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="O92" s="33" t="n">
-        <v>30.81</v>
+        <v>30.24</v>
       </c>
       <c r="P92" s="33" t="n">
-        <v>30.79</v>
+        <v>30.2</v>
       </c>
       <c r="Q92" s="34" t="n">
-        <v>30.72</v>
+        <v>30.14</v>
       </c>
       <c r="R92" s="35" t="n">
-        <v>-0.9</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="93">
@@ -6374,37 +6374,37 @@
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>21.73</v>
+        <v>21.33</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>21.36</v>
+        <v>20.91</v>
       </c>
       <c r="E93" s="26" t="n">
-        <v>21.05</v>
+        <v>20.56</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>21.03</v>
+        <v>20.69</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>21.27</v>
+        <v>20.88</v>
       </c>
       <c r="H93" s="28" t="n">
-        <v>20.9</v>
+        <v>20.46</v>
       </c>
       <c r="I93" s="29" t="n">
-        <v>20.66</v>
+        <v>20.27</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>20.53</v>
+        <v>20.04</v>
       </c>
       <c r="K93" s="30" t="n">
-        <v>20.84</v>
+        <v>20.32</v>
       </c>
       <c r="L93" s="31" t="n">
-        <v>20.53</v>
+        <v>19.97</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>20.16</v>
+        <v>19.55</v>
       </c>
       <c r="N93" s="32" t="inlineStr">
         <is>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="O93" s="33" t="n">
-        <v>20.88</v>
+        <v>20.41</v>
       </c>
       <c r="P93" s="33" t="n">
-        <v>20.87</v>
+        <v>20.36</v>
       </c>
       <c r="Q93" s="34" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="R93" s="35" t="n">
-        <v>-1.42</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="94">
@@ -6436,37 +6436,37 @@
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>28.3</v>
+        <v>28.01</v>
       </c>
       <c r="D94" s="25" t="n">
-        <v>27.88</v>
+        <v>27.51</v>
       </c>
       <c r="E94" s="26" t="n">
-        <v>27.53</v>
+        <v>27.09</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>27.51</v>
+        <v>27.17</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>27.77</v>
+        <v>27.43</v>
       </c>
       <c r="H94" s="28" t="n">
-        <v>27.35</v>
+        <v>26.93</v>
       </c>
       <c r="I94" s="29" t="n">
-        <v>27.09</v>
+        <v>26.67</v>
       </c>
       <c r="J94" s="29" t="n">
-        <v>26.93</v>
+        <v>26.43</v>
       </c>
       <c r="K94" s="30" t="n">
-        <v>27.29</v>
+        <v>26.81</v>
       </c>
       <c r="L94" s="31" t="n">
-        <v>26.94</v>
+        <v>26.39</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>26.52</v>
+        <v>25.89</v>
       </c>
       <c r="N94" s="32" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="O94" s="33" t="n">
-        <v>27.34</v>
+        <v>26.89</v>
       </c>
       <c r="P94" s="33" t="n">
-        <v>27.33</v>
+        <v>26.85</v>
       </c>
       <c r="Q94" s="34" t="n">
-        <v>27.24</v>
+        <v>26.9</v>
       </c>
       <c r="R94" s="35" t="n">
-        <v>-0.66</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="95">
@@ -6498,37 +6498,37 @@
         </is>
       </c>
       <c r="C95" s="25" t="n">
-        <v>175.07</v>
+        <v>175.38</v>
       </c>
       <c r="D95" s="25" t="n">
-        <v>172.37</v>
+        <v>172.18</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>170.11</v>
+        <v>169.5</v>
       </c>
       <c r="F95" s="27" t="n">
-        <v>170.33</v>
+        <v>171.13</v>
       </c>
       <c r="G95" s="27" t="n">
-        <v>171.87</v>
+        <v>172.27</v>
       </c>
       <c r="H95" s="28" t="n">
-        <v>169.17</v>
+        <v>169.07</v>
       </c>
       <c r="I95" s="29" t="n">
-        <v>167.63</v>
+        <v>167.93</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>166.47</v>
+        <v>165.87</v>
       </c>
       <c r="K95" s="30" t="n">
-        <v>168.59</v>
+        <v>167.7</v>
       </c>
       <c r="L95" s="31" t="n">
-        <v>166.33</v>
+        <v>165.02</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>163.63</v>
+        <v>161.82</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="O95" s="33" t="n">
-        <v>168.99</v>
+        <v>168.51</v>
       </c>
       <c r="P95" s="33" t="n">
-        <v>168.8</v>
+        <v>167.95</v>
       </c>
       <c r="Q95" s="34" t="n">
-        <v>168.8</v>
+        <v>170</v>
       </c>
       <c r="R95" s="36" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="96">
@@ -6560,37 +6560,37 @@
         </is>
       </c>
       <c r="C96" s="25" t="n">
-        <v>14.07</v>
+        <v>14.32</v>
       </c>
       <c r="D96" s="25" t="n">
-        <v>13.89</v>
+        <v>13.93</v>
       </c>
       <c r="E96" s="26" t="n">
-        <v>13.74</v>
+        <v>13.6</v>
       </c>
       <c r="F96" s="27" t="n">
-        <v>13.77</v>
+        <v>13.61</v>
       </c>
       <c r="G96" s="27" t="n">
-        <v>13.87</v>
+        <v>13.85</v>
       </c>
       <c r="H96" s="28" t="n">
-        <v>13.69</v>
+        <v>13.46</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>13.59</v>
+        <v>13.22</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>13.51</v>
+        <v>13.07</v>
       </c>
       <c r="K96" s="30" t="n">
-        <v>13.64</v>
+        <v>13.39</v>
       </c>
       <c r="L96" s="31" t="n">
-        <v>13.49</v>
+        <v>13.06</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>13.31</v>
+        <v>12.67</v>
       </c>
       <c r="N96" s="32" t="inlineStr">
         <is>
@@ -6598,16 +6598,16 @@
         </is>
       </c>
       <c r="O96" s="33" t="n">
-        <v>13.67</v>
+        <v>13.44</v>
       </c>
       <c r="P96" s="33" t="n">
-        <v>13.65</v>
+        <v>13.42</v>
       </c>
       <c r="Q96" s="34" t="n">
-        <v>13.68</v>
+        <v>13.38</v>
       </c>
       <c r="R96" s="35" t="n">
-        <v>-0.15</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="97">
@@ -6622,37 +6622,37 @@
         </is>
       </c>
       <c r="C97" s="25" t="n">
-        <v>20.81</v>
+        <v>20.8</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>20.39</v>
+        <v>20.19</v>
       </c>
       <c r="E97" s="26" t="n">
-        <v>20.04</v>
+        <v>19.68</v>
       </c>
       <c r="F97" s="27" t="n">
-        <v>20.04</v>
+        <v>19.63</v>
       </c>
       <c r="G97" s="27" t="n">
-        <v>20.29</v>
+        <v>20.03</v>
       </c>
       <c r="H97" s="28" t="n">
-        <v>19.87</v>
+        <v>19.42</v>
       </c>
       <c r="I97" s="29" t="n">
-        <v>19.62</v>
+        <v>19.02</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>19.45</v>
+        <v>18.81</v>
       </c>
       <c r="K97" s="30" t="n">
-        <v>19.8</v>
+        <v>19.33</v>
       </c>
       <c r="L97" s="31" t="n">
-        <v>19.45</v>
+        <v>18.82</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>19.03</v>
+        <v>18.21</v>
       </c>
       <c r="N97" s="32" t="inlineStr">
         <is>
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="O97" s="33" t="n">
-        <v>19.85</v>
+        <v>19.4</v>
       </c>
       <c r="P97" s="33" t="n">
-        <v>19.84</v>
+        <v>19.38</v>
       </c>
       <c r="Q97" s="34" t="n">
-        <v>19.78</v>
+        <v>19.24</v>
       </c>
       <c r="R97" s="35" t="n">
-        <v>-1.93</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="98">
@@ -6684,54 +6684,54 @@
         </is>
       </c>
       <c r="C98" s="25" t="n">
-        <v>16.34</v>
+        <v>16.32</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>16.18</v>
+        <v>16.12</v>
       </c>
       <c r="E98" s="26" t="n">
-        <v>16.04</v>
+        <v>15.96</v>
       </c>
       <c r="F98" s="27" t="n">
-        <v>16.03</v>
+        <v>16.06</v>
       </c>
       <c r="G98" s="27" t="n">
-        <v>16.14</v>
+        <v>16.13</v>
       </c>
       <c r="H98" s="28" t="n">
-        <v>15.98</v>
+        <v>15.93</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>15.87</v>
+        <v>15.86</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>15.82</v>
+        <v>15.73</v>
       </c>
       <c r="K98" s="30" t="n">
-        <v>15.96</v>
+        <v>15.84</v>
       </c>
       <c r="L98" s="31" t="n">
-        <v>15.82</v>
+        <v>15.68</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="N98" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.48</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O98" s="33" t="n">
-        <v>15.97</v>
+        <v>15.89</v>
       </c>
       <c r="P98" s="33" t="n">
-        <v>15.97</v>
+        <v>15.86</v>
       </c>
       <c r="Q98" s="34" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="R98" s="35" t="n">
-        <v>-0.62</v>
+        <v>15.99</v>
+      </c>
+      <c r="R98" s="36" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="99">
@@ -6746,54 +6746,54 @@
         </is>
       </c>
       <c r="C99" s="25" t="n">
-        <v>9.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>9.74</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F99" s="27" t="n">
-        <v>9.630000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="G99" s="27" t="n">
-        <v>9.710000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="H99" s="28" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="I99" s="29" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="J99" s="29" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="K99" s="30" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="L99" s="31" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="M99" s="31" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O99" s="33" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="P99" s="33" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q99" s="34" t="n">
         <v>9.6</v>
       </c>
-      <c r="I99" s="29" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="J99" s="29" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="K99" s="30" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="L99" s="31" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="M99" s="31" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="N99" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O99" s="33" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="P99" s="33" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="Q99" s="34" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="R99" s="35" t="n">
-        <v>-0.93</v>
+      <c r="R99" s="36" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="100">
@@ -6808,37 +6808,37 @@
         </is>
       </c>
       <c r="C100" s="25" t="n">
-        <v>27.3</v>
+        <v>27.82</v>
       </c>
       <c r="D100" s="25" t="n">
-        <v>26.88</v>
+        <v>27.2</v>
       </c>
       <c r="E100" s="26" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="F100" s="27" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="G100" s="27" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="H100" s="28" t="n">
         <v>26.53</v>
       </c>
-      <c r="F100" s="27" t="n">
-        <v>26.63</v>
-      </c>
-      <c r="G100" s="27" t="n">
-        <v>26.83</v>
-      </c>
-      <c r="H100" s="28" t="n">
-        <v>26.41</v>
-      </c>
       <c r="I100" s="29" t="n">
-        <v>26.21</v>
+        <v>26.23</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>25.99</v>
+        <v>25.91</v>
       </c>
       <c r="K100" s="30" t="n">
-        <v>26.29</v>
+        <v>26.34</v>
       </c>
       <c r="L100" s="31" t="n">
-        <v>25.94</v>
+        <v>25.82</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>25.52</v>
+        <v>25.2</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
@@ -6846,16 +6846,16 @@
         </is>
       </c>
       <c r="O100" s="33" t="n">
-        <v>26.37</v>
+        <v>26.46</v>
       </c>
       <c r="P100" s="33" t="n">
-        <v>26.33</v>
+        <v>26.38</v>
       </c>
       <c r="Q100" s="34" t="n">
-        <v>26.42</v>
+        <v>26.56</v>
       </c>
       <c r="R100" s="36" t="n">
-        <v>0.84</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="101">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="C101" s="25" t="n">
-        <v>16.91</v>
+        <v>16.52</v>
       </c>
       <c r="D101" s="25" t="n">
-        <v>16.67</v>
+        <v>16.32</v>
       </c>
       <c r="E101" s="26" t="n">
-        <v>16.47</v>
+        <v>16.16</v>
       </c>
       <c r="F101" s="27" t="n">
-        <v>16.44</v>
+        <v>16.13</v>
       </c>
       <c r="G101" s="27" t="n">
-        <v>16.6</v>
+        <v>16.27</v>
       </c>
       <c r="H101" s="28" t="n">
-        <v>16.36</v>
+        <v>16.07</v>
       </c>
       <c r="I101" s="29" t="n">
-        <v>16.2</v>
+        <v>15.93</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>16.12</v>
+        <v>15.87</v>
       </c>
       <c r="K101" s="30" t="n">
-        <v>16.33</v>
+        <v>16.04</v>
       </c>
       <c r="L101" s="31" t="n">
-        <v>16.13</v>
+        <v>15.88</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>15.89</v>
+        <v>15.68</v>
       </c>
       <c r="N101" s="32" t="inlineStr">
         <is>
@@ -6908,16 +6908,16 @@
         </is>
       </c>
       <c r="O101" s="33" t="n">
-        <v>16.36</v>
+        <v>16.06</v>
       </c>
       <c r="P101" s="33" t="n">
-        <v>16.35</v>
+        <v>16.06</v>
       </c>
       <c r="Q101" s="34" t="n">
-        <v>16.28</v>
+        <v>16</v>
       </c>
       <c r="R101" s="35" t="n">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="102">
@@ -6932,54 +6932,54 @@
         </is>
       </c>
       <c r="C102" s="25" t="n">
-        <v>32.21</v>
+        <v>32.27</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>31.77</v>
+        <v>31.73</v>
       </c>
       <c r="E102" s="26" t="n">
-        <v>31.4</v>
+        <v>31.28</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>31.58</v>
+        <v>31.29</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>31.76</v>
+        <v>31.61</v>
       </c>
       <c r="H102" s="28" t="n">
-        <v>31.32</v>
+        <v>31.07</v>
       </c>
       <c r="I102" s="29" t="n">
-        <v>31.14</v>
+        <v>30.75</v>
       </c>
       <c r="J102" s="29" t="n">
-        <v>30.88</v>
+        <v>30.53</v>
       </c>
       <c r="K102" s="30" t="n">
-        <v>31.16</v>
+        <v>30.98</v>
       </c>
       <c r="L102" s="31" t="n">
-        <v>30.79</v>
+        <v>30.53</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>29.99</v>
+      </c>
+      <c r="N102" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="33" t="n">
-        <v>31.26</v>
+        <v>31.05</v>
       </c>
       <c r="P102" s="33" t="n">
-        <v>31.19</v>
+        <v>31.02</v>
       </c>
       <c r="Q102" s="34" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R102" s="36" t="n">
-        <v>0.77</v>
+        <v>30.96</v>
+      </c>
+      <c r="R102" s="35" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="103">
@@ -6994,37 +6994,37 @@
         </is>
       </c>
       <c r="C103" s="25" t="n">
-        <v>15.97</v>
+        <v>15.92</v>
       </c>
       <c r="D103" s="25" t="n">
-        <v>15.62</v>
+        <v>15.47</v>
       </c>
       <c r="E103" s="26" t="n">
-        <v>15.32</v>
+        <v>15.09</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>15.38</v>
+        <v>15.14</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>15.56</v>
+        <v>15.39</v>
       </c>
       <c r="H103" s="28" t="n">
-        <v>15.21</v>
+        <v>14.94</v>
       </c>
       <c r="I103" s="29" t="n">
-        <v>15.03</v>
+        <v>14.69</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>14.86</v>
+        <v>14.49</v>
       </c>
       <c r="K103" s="30" t="n">
-        <v>15.13</v>
+        <v>14.84</v>
       </c>
       <c r="L103" s="31" t="n">
-        <v>14.83</v>
+        <v>14.46</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>14.48</v>
+        <v>14.01</v>
       </c>
       <c r="N103" s="32" t="inlineStr">
         <is>
@@ -7032,16 +7032,16 @@
         </is>
       </c>
       <c r="O103" s="33" t="n">
-        <v>15.18</v>
+        <v>14.91</v>
       </c>
       <c r="P103" s="33" t="n">
-        <v>15.15</v>
+        <v>14.87</v>
       </c>
       <c r="Q103" s="34" t="n">
-        <v>15.19</v>
+        <v>14.89</v>
       </c>
       <c r="R103" s="35" t="n">
-        <v>-1.17</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="104">
@@ -7056,37 +7056,37 @@
         </is>
       </c>
       <c r="C104" s="25" t="n">
-        <v>70.8</v>
+        <v>72.94</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09</v>
       </c>
       <c r="E104" s="26" t="n">
-        <v>70.06</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F104" s="27" t="n">
-        <v>70.08</v>
+        <v>70.37</v>
       </c>
       <c r="G104" s="27" t="n">
-        <v>70.31999999999999</v>
+        <v>71.08</v>
       </c>
       <c r="H104" s="28" t="n">
-        <v>69.92</v>
+        <v>69.23</v>
       </c>
       <c r="I104" s="29" t="n">
-        <v>69.68000000000001</v>
+        <v>68.52</v>
       </c>
       <c r="J104" s="29" t="n">
-        <v>69.52</v>
+        <v>67.38</v>
       </c>
       <c r="K104" s="30" t="n">
-        <v>69.84</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L104" s="31" t="n">
-        <v>69.5</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>69.09999999999999</v>
+        <v>65.11</v>
       </c>
       <c r="N104" s="32" t="inlineStr">
         <is>
@@ -7094,13 +7094,13 @@
         </is>
       </c>
       <c r="O104" s="33" t="n">
-        <v>69.89</v>
+        <v>68.94</v>
       </c>
       <c r="P104" s="33" t="n">
-        <v>69.87</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="Q104" s="34" t="n">
-        <v>69.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="R104" s="35" t="n">
         <v>-0.29</v>
@@ -7118,54 +7118,54 @@
         </is>
       </c>
       <c r="C105" s="25" t="n">
-        <v>15.31</v>
+        <v>15.05</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>15.08</v>
+        <v>14.84</v>
       </c>
       <c r="E105" s="26" t="n">
-        <v>14.89</v>
+        <v>14.66</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>14.92</v>
+        <v>14.68</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>15.05</v>
+        <v>14.8</v>
       </c>
       <c r="H105" s="28" t="n">
-        <v>14.82</v>
+        <v>14.59</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>14.69</v>
+        <v>14.47</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>14.59</v>
+        <v>14.38</v>
       </c>
       <c r="K105" s="30" t="n">
-        <v>14.76</v>
+        <v>14.55</v>
       </c>
       <c r="L105" s="31" t="n">
-        <v>14.57</v>
+        <v>14.37</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.16</v>
+      </c>
+      <c r="N105" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="33" t="n">
-        <v>14.8</v>
+        <v>14.58</v>
       </c>
       <c r="P105" s="33" t="n">
-        <v>14.78</v>
+        <v>14.56</v>
       </c>
       <c r="Q105" s="34" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="R105" s="36" t="n">
-        <v>0.54</v>
+        <v>14.56</v>
+      </c>
+      <c r="R105" s="35" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="106">
@@ -7180,37 +7180,37 @@
         </is>
       </c>
       <c r="C106" s="25" t="n">
-        <v>16.61</v>
+        <v>17.38</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>16.3</v>
+        <v>16.47</v>
       </c>
       <c r="E106" s="26" t="n">
-        <v>16.04</v>
+        <v>15.71</v>
       </c>
       <c r="F106" s="27" t="n">
-        <v>16.07</v>
+        <v>15.88</v>
       </c>
       <c r="G106" s="27" t="n">
-        <v>16.25</v>
+        <v>16.35</v>
       </c>
       <c r="H106" s="28" t="n">
-        <v>15.94</v>
+        <v>15.44</v>
       </c>
       <c r="I106" s="29" t="n">
-        <v>15.76</v>
+        <v>14.97</v>
       </c>
       <c r="J106" s="29" t="n">
-        <v>15.63</v>
+        <v>14.53</v>
       </c>
       <c r="K106" s="30" t="n">
-        <v>15.87</v>
+        <v>15.2</v>
       </c>
       <c r="L106" s="31" t="n">
-        <v>15.61</v>
+        <v>14.44</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>15.3</v>
+        <v>13.53</v>
       </c>
       <c r="N106" s="32" t="inlineStr">
         <is>
@@ -7218,16 +7218,16 @@
         </is>
       </c>
       <c r="O106" s="33" t="n">
-        <v>15.91</v>
+        <v>15.36</v>
       </c>
       <c r="P106" s="33" t="n">
-        <v>15.89</v>
+        <v>15.27</v>
       </c>
       <c r="Q106" s="34" t="n">
-        <v>15.9</v>
+        <v>15.41</v>
       </c>
       <c r="R106" s="35" t="n">
-        <v>-0.75</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="107">
@@ -7242,37 +7242,37 @@
         </is>
       </c>
       <c r="C107" s="25" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="E107" s="26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F107" s="27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G107" s="27" t="n">
         <v>2.49</v>
       </c>
-      <c r="F107" s="27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="G107" s="27" t="n">
-        <v>2.51</v>
-      </c>
       <c r="H107" s="28" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="I107" s="29" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="K107" s="30" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="L107" s="31" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="N107" s="32" t="inlineStr">
         <is>
@@ -7280,16 +7280,16 @@
         </is>
       </c>
       <c r="O107" s="33" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="P107" s="33" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="Q107" s="34" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="R107" s="35" t="n">
-        <v>-1.2</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="108">
@@ -7304,37 +7304,37 @@
         </is>
       </c>
       <c r="C108" s="25" t="n">
-        <v>42.8</v>
+        <v>39.56</v>
       </c>
       <c r="D108" s="25" t="n">
-        <v>41.22</v>
+        <v>39.14</v>
       </c>
       <c r="E108" s="26" t="n">
-        <v>39.89</v>
+        <v>38.79</v>
       </c>
       <c r="F108" s="27" t="n">
-        <v>39.81</v>
+        <v>38.89</v>
       </c>
       <c r="G108" s="27" t="n">
-        <v>40.81</v>
+        <v>39.09</v>
       </c>
       <c r="H108" s="28" t="n">
-        <v>39.23</v>
+        <v>38.67</v>
       </c>
       <c r="I108" s="29" t="n">
-        <v>38.23</v>
+        <v>38.47</v>
       </c>
       <c r="J108" s="29" t="n">
-        <v>37.65</v>
+        <v>38.25</v>
       </c>
       <c r="K108" s="30" t="n">
-        <v>39.01</v>
+        <v>38.55</v>
       </c>
       <c r="L108" s="31" t="n">
-        <v>37.68</v>
+        <v>38.2</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>36.1</v>
+        <v>37.78</v>
       </c>
       <c r="N108" s="32" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         </is>
       </c>
       <c r="O108" s="33" t="n">
-        <v>39.18</v>
+        <v>38.63</v>
       </c>
       <c r="P108" s="33" t="n">
-        <v>39.13</v>
+        <v>38.59</v>
       </c>
       <c r="Q108" s="34" t="n">
-        <v>38.8</v>
+        <v>38.68</v>
       </c>
       <c r="R108" s="35" t="n">
-        <v>-2.85</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="109">
@@ -7366,54 +7366,54 @@
         </is>
       </c>
       <c r="C109" s="25" t="n">
-        <v>8.56</v>
+        <v>8.27</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>8.380000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="E109" s="26" t="n">
-        <v>8.23</v>
+        <v>8.09</v>
       </c>
       <c r="F109" s="27" t="n">
-        <v>8.24</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G109" s="27" t="n">
-        <v>8.35</v>
+        <v>8.16</v>
       </c>
       <c r="H109" s="28" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="I109" s="29" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="J109" s="29" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="K109" s="30" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="L109" s="31" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="M109" s="31" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="N109" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O109" s="33" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="P109" s="33" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="Q109" s="34" t="n">
         <v>8.06</v>
       </c>
-      <c r="J109" s="29" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="K109" s="30" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="L109" s="31" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="M109" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="N109" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O109" s="33" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="P109" s="33" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="Q109" s="34" t="n">
-        <v>8.140000000000001</v>
-      </c>
       <c r="R109" s="35" t="n">
-        <v>-0.73</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="110">
@@ -7428,54 +7428,54 @@
         </is>
       </c>
       <c r="C110" s="25" t="n">
-        <v>44.5</v>
+        <v>44.49</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>44.18</v>
+        <v>44.11</v>
       </c>
       <c r="E110" s="26" t="n">
-        <v>43.91</v>
+        <v>43.8</v>
       </c>
       <c r="F110" s="27" t="n">
-        <v>44.01</v>
+        <v>43.95</v>
       </c>
       <c r="G110" s="27" t="n">
-        <v>44.15</v>
+        <v>44.11</v>
       </c>
       <c r="H110" s="28" t="n">
-        <v>43.83</v>
+        <v>43.73</v>
       </c>
       <c r="I110" s="29" t="n">
-        <v>43.69</v>
+        <v>43.57</v>
       </c>
       <c r="J110" s="29" t="n">
-        <v>43.51</v>
+        <v>43.35</v>
       </c>
       <c r="K110" s="30" t="n">
-        <v>43.73</v>
+        <v>43.58</v>
       </c>
       <c r="L110" s="31" t="n">
-        <v>43.46</v>
+        <v>43.27</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="N110" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>42.89</v>
+      </c>
+      <c r="N110" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="33" t="n">
-        <v>43.79</v>
+        <v>43.67</v>
       </c>
       <c r="P110" s="33" t="n">
-        <v>43.76</v>
+        <v>43.61</v>
       </c>
       <c r="Q110" s="34" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="R110" s="36" t="n">
-        <v>0.83</v>
+        <v>43.8</v>
+      </c>
+      <c r="R110" s="35" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="111">
@@ -7490,54 +7490,54 @@
         </is>
       </c>
       <c r="C111" s="25" t="n">
-        <v>67.31</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>66.41</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="E111" s="26" t="n">
-        <v>65.65000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F111" s="27" t="n">
-        <v>65.65000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="G111" s="27" t="n">
-        <v>66.2</v>
+        <v>66.37</v>
       </c>
       <c r="H111" s="28" t="n">
-        <v>65.3</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="I111" s="29" t="n">
-        <v>64.75</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>64.40000000000001</v>
+        <v>64.27</v>
       </c>
       <c r="K111" s="30" t="n">
-        <v>65.15000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="L111" s="31" t="n">
-        <v>64.39</v>
+        <v>64</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="N111" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>62.95</v>
+      </c>
+      <c r="N111" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="33" t="n">
-        <v>65.26000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="P111" s="33" t="n">
-        <v>65.22</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="Q111" s="34" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="R111" s="35" t="n">
-        <v>-0.91</v>
+        <v>65.59999999999999</v>
+      </c>
+      <c r="R111" s="36" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="112">
@@ -7552,37 +7552,37 @@
         </is>
       </c>
       <c r="C112" s="25" t="n">
-        <v>10.34</v>
+        <v>10.36</v>
       </c>
       <c r="D112" s="25" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="E112" s="26" t="n">
-        <v>10.27</v>
+        <v>10.23</v>
       </c>
       <c r="F112" s="27" t="n">
-        <v>10.27</v>
+        <v>10.23</v>
       </c>
       <c r="G112" s="27" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="H112" s="28" t="n">
-        <v>10.26</v>
+        <v>10.21</v>
       </c>
       <c r="I112" s="29" t="n">
-        <v>10.23</v>
+        <v>10.16</v>
       </c>
       <c r="J112" s="29" t="n">
-        <v>10.22</v>
+        <v>10.14</v>
       </c>
       <c r="K112" s="30" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="L112" s="31" t="n">
-        <v>10.22</v>
+        <v>10.14</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>10.18</v>
+        <v>10.07</v>
       </c>
       <c r="N112" s="32" t="inlineStr">
         <is>
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="O112" s="33" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="P112" s="33" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="Q112" s="34" t="n">
-        <v>10.25</v>
+        <v>10.19</v>
       </c>
       <c r="R112" s="35" t="n">
-        <v>-0.1</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="113">
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>327.81</v>
+        <v>329.02</v>
       </c>
       <c r="D113" s="25" t="n">
-        <v>318.41</v>
+        <v>321.22</v>
       </c>
       <c r="E113" s="26" t="n">
-        <v>310.53</v>
+        <v>314.68</v>
       </c>
       <c r="F113" s="27" t="n">
-        <v>313.6</v>
+        <v>317.93</v>
       </c>
       <c r="G113" s="27" t="n">
-        <v>317.8</v>
+        <v>321.07</v>
       </c>
       <c r="H113" s="28" t="n">
-        <v>308.4</v>
+        <v>313.27</v>
       </c>
       <c r="I113" s="29" t="n">
-        <v>304.2</v>
+        <v>310.13</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>299</v>
+        <v>305.47</v>
       </c>
       <c r="K113" s="30" t="n">
-        <v>305.27</v>
+        <v>310.32</v>
       </c>
       <c r="L113" s="31" t="n">
-        <v>297.39</v>
+        <v>303.78</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>287.99</v>
+        <v>295.98</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7652,16 +7652,16 @@
         </is>
       </c>
       <c r="O113" s="33" t="n">
-        <v>307.2</v>
+        <v>312.1</v>
       </c>
       <c r="P113" s="33" t="n">
-        <v>306</v>
+        <v>310.92</v>
       </c>
       <c r="Q113" s="34" t="n">
-        <v>309.4</v>
+        <v>314.8</v>
       </c>
       <c r="R113" s="36" t="n">
-        <v>0.91</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="114">
@@ -7676,54 +7676,54 @@
         </is>
       </c>
       <c r="C114" s="25" t="n">
-        <v>236.16</v>
+        <v>226.48</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>228.46</v>
+        <v>223.28</v>
       </c>
       <c r="E114" s="26" t="n">
-        <v>222.01</v>
+        <v>220.6</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>223.13</v>
+        <v>220.7</v>
       </c>
       <c r="G114" s="27" t="n">
-        <v>227.27</v>
+        <v>222.6</v>
       </c>
       <c r="H114" s="28" t="n">
-        <v>219.57</v>
+        <v>219.4</v>
       </c>
       <c r="I114" s="29" t="n">
-        <v>215.43</v>
+        <v>217.5</v>
       </c>
       <c r="J114" s="29" t="n">
-        <v>211.87</v>
+        <v>216.2</v>
       </c>
       <c r="K114" s="30" t="n">
-        <v>217.69</v>
+        <v>218.8</v>
       </c>
       <c r="L114" s="31" t="n">
-        <v>211.24</v>
+        <v>216.12</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>203.54</v>
-      </c>
-      <c r="N114" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>212.92</v>
+      </c>
+      <c r="N114" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="33" t="n">
-        <v>218.93</v>
+        <v>219.23</v>
       </c>
       <c r="P114" s="33" t="n">
-        <v>218.29</v>
+        <v>219.05</v>
       </c>
       <c r="Q114" s="34" t="n">
-        <v>219</v>
-      </c>
-      <c r="R114" s="36" t="n">
-        <v>1.86</v>
+        <v>218.8</v>
+      </c>
+      <c r="R114" s="35" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="115">
@@ -7738,37 +7738,37 @@
         </is>
       </c>
       <c r="C115" s="25" t="n">
-        <v>644.92</v>
+        <v>645.11</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>632.92</v>
+        <v>633.61</v>
       </c>
       <c r="E115" s="26" t="n">
-        <v>622.86</v>
+        <v>623.97</v>
       </c>
       <c r="F115" s="27" t="n">
-        <v>625.17</v>
+        <v>628</v>
       </c>
       <c r="G115" s="27" t="n">
-        <v>631.33</v>
+        <v>633</v>
       </c>
       <c r="H115" s="28" t="n">
-        <v>619.33</v>
+        <v>621.5</v>
       </c>
       <c r="I115" s="29" t="n">
-        <v>613.17</v>
+        <v>616.5</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>607.33</v>
+        <v>610</v>
       </c>
       <c r="K115" s="30" t="n">
-        <v>616.14</v>
+        <v>617.53</v>
       </c>
       <c r="L115" s="31" t="n">
-        <v>606.08</v>
+        <v>607.89</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>594.08</v>
+        <v>596.39</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7776,16 +7776,16 @@
         </is>
       </c>
       <c r="O115" s="33" t="n">
-        <v>618.2</v>
+        <v>619.96</v>
       </c>
       <c r="P115" s="33" t="n">
-        <v>617.08</v>
+        <v>618.4299999999999</v>
       </c>
       <c r="Q115" s="34" t="n">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="R115" s="36" t="n">
-        <v>0.41</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="116">
@@ -7800,37 +7800,37 @@
         </is>
       </c>
       <c r="C116" s="25" t="n">
-        <v>6.79</v>
+        <v>6.67</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>6.69</v>
+        <v>6.56</v>
       </c>
       <c r="E116" s="26" t="n">
-        <v>6.61</v>
+        <v>6.47</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="G116" s="27" t="n">
-        <v>6.66</v>
+        <v>6.54</v>
       </c>
       <c r="H116" s="28" t="n">
-        <v>6.56</v>
+        <v>6.43</v>
       </c>
       <c r="I116" s="29" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
       <c r="J116" s="29" t="n">
-        <v>6.46</v>
+        <v>6.32</v>
       </c>
       <c r="K116" s="30" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="L116" s="31" t="n">
-        <v>6.47</v>
+        <v>6.31</v>
       </c>
       <c r="M116" s="31" t="n">
-        <v>6.37</v>
+        <v>6.2</v>
       </c>
       <c r="N116" s="32" t="inlineStr">
         <is>
@@ -7838,16 +7838,16 @@
         </is>
       </c>
       <c r="O116" s="33" t="n">
-        <v>6.56</v>
+        <v>6.42</v>
       </c>
       <c r="P116" s="33" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="Q116" s="34" t="n">
-        <v>6.53</v>
+        <v>6.41</v>
       </c>
       <c r="R116" s="35" t="n">
-        <v>-0.15</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="117">
@@ -7862,54 +7862,54 @@
         </is>
       </c>
       <c r="C117" s="25" t="n">
-        <v>107.34</v>
+        <v>98.64</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>100.64</v>
+        <v>96.14</v>
       </c>
       <c r="E117" s="26" t="n">
-        <v>95.03</v>
+        <v>94.05</v>
       </c>
       <c r="F117" s="27" t="n">
-        <v>96.87</v>
+        <v>94.2</v>
       </c>
       <c r="G117" s="27" t="n">
-        <v>100.03</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H117" s="28" t="n">
-        <v>93.33</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="I117" s="29" t="n">
-        <v>90.17</v>
+        <v>91.7</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>86.63</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>91.27</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="L117" s="31" t="n">
-        <v>85.66</v>
+        <v>90.55</v>
       </c>
       <c r="M117" s="31" t="n">
-        <v>78.95999999999999</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>88.05</v>
+      </c>
+      <c r="N117" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="33" t="n">
-        <v>92.56</v>
+        <v>93</v>
       </c>
       <c r="P117" s="33" t="n">
-        <v>91.8</v>
+        <v>92.84</v>
       </c>
       <c r="Q117" s="34" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="R117" s="36" t="n">
-        <v>4.75</v>
+        <v>92.75</v>
+      </c>
+      <c r="R117" s="35" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="118">
@@ -7924,54 +7924,54 @@
         </is>
       </c>
       <c r="C118" s="25" t="n">
-        <v>10.84</v>
+        <v>10.4</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>10.5</v>
+        <v>10.23</v>
       </c>
       <c r="E118" s="26" t="n">
-        <v>10.22</v>
+        <v>10.08</v>
       </c>
       <c r="F118" s="27" t="n">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="G118" s="27" t="n">
-        <v>10.47</v>
+        <v>10.19</v>
       </c>
       <c r="H118" s="28" t="n">
-        <v>10.13</v>
+        <v>10.02</v>
       </c>
       <c r="I118" s="29" t="n">
-        <v>9.960000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="J118" s="29" t="n">
-        <v>9.789999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="K118" s="30" t="n">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="L118" s="31" t="n">
-        <v>9.74</v>
+        <v>9.84</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N118" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.67</v>
+      </c>
+      <c r="N118" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="33" t="n">
-        <v>10.09</v>
+        <v>10.01</v>
       </c>
       <c r="P118" s="33" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="Q118" s="34" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="R118" s="36" t="n">
-        <v>2.22</v>
+        <v>9.98</v>
+      </c>
+      <c r="R118" s="35" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="119">
@@ -7986,37 +7986,37 @@
         </is>
       </c>
       <c r="C119" s="25" t="n">
-        <v>18.12</v>
+        <v>18.45</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>17.54</v>
+        <v>17.8</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>17.05</v>
+        <v>17.26</v>
       </c>
       <c r="F119" s="27" t="n">
-        <v>17.25</v>
+        <v>17.33</v>
       </c>
       <c r="G119" s="27" t="n">
-        <v>17.51</v>
+        <v>17.69</v>
       </c>
       <c r="H119" s="28" t="n">
-        <v>16.93</v>
+        <v>17.04</v>
       </c>
       <c r="I119" s="29" t="n">
-        <v>16.67</v>
+        <v>16.68</v>
       </c>
       <c r="J119" s="29" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="K119" s="30" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="L119" s="31" t="n">
         <v>16.35</v>
       </c>
-      <c r="K119" s="30" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="L119" s="31" t="n">
-        <v>16.24</v>
-      </c>
       <c r="M119" s="31" t="n">
-        <v>15.66</v>
+        <v>15.7</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
@@ -8024,16 +8024,16 @@
         </is>
       </c>
       <c r="O119" s="33" t="n">
-        <v>16.85</v>
+        <v>16.99</v>
       </c>
       <c r="P119" s="33" t="n">
-        <v>16.77</v>
+        <v>16.94</v>
       </c>
       <c r="Q119" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="R119" s="36" t="n">
-        <v>3.66</v>
+        <v>16.97</v>
+      </c>
+      <c r="R119" s="35" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="120">
@@ -8048,54 +8048,54 @@
         </is>
       </c>
       <c r="C120" s="25" t="n">
-        <v>12.54</v>
+        <v>11.93</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>12.05</v>
+        <v>11.68</v>
       </c>
       <c r="E120" s="26" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="F120" s="27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G120" s="27" t="n">
         <v>11.64</v>
       </c>
-      <c r="F120" s="27" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="G120" s="27" t="n">
-        <v>11.99</v>
-      </c>
       <c r="H120" s="28" t="n">
-        <v>11.5</v>
+        <v>11.39</v>
       </c>
       <c r="I120" s="29" t="n">
         <v>11.25</v>
       </c>
       <c r="J120" s="29" t="n">
-        <v>11.01</v>
+        <v>11.14</v>
       </c>
       <c r="K120" s="30" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="L120" s="31" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="M120" s="31" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="N120" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O120" s="33" t="n">
         <v>11.37</v>
       </c>
-      <c r="L120" s="31" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="M120" s="31" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="N120" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O120" s="33" t="n">
-        <v>11.45</v>
-      </c>
       <c r="P120" s="33" t="n">
-        <v>11.41</v>
+        <v>11.35</v>
       </c>
       <c r="Q120" s="34" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="R120" s="36" t="n">
-        <v>2.32</v>
+        <v>11.36</v>
+      </c>
+      <c r="R120" s="35" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="121">
@@ -8110,54 +8110,54 @@
         </is>
       </c>
       <c r="C121" s="25" t="n">
-        <v>13.2</v>
+        <v>12.54</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>12.74</v>
+        <v>12.33</v>
       </c>
       <c r="E121" s="26" t="n">
-        <v>12.36</v>
+        <v>12.15</v>
       </c>
       <c r="F121" s="27" t="n">
-        <v>12.47</v>
+        <v>12.13</v>
       </c>
       <c r="G121" s="27" t="n">
-        <v>12.7</v>
+        <v>12.27</v>
       </c>
       <c r="H121" s="28" t="n">
-        <v>12.24</v>
+        <v>12.06</v>
       </c>
       <c r="I121" s="29" t="n">
-        <v>12.01</v>
+        <v>11.92</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>11.78</v>
+        <v>11.85</v>
       </c>
       <c r="K121" s="30" t="n">
-        <v>12.1</v>
+        <v>12.04</v>
       </c>
       <c r="L121" s="31" t="n">
-        <v>11.72</v>
+        <v>11.86</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>11.65</v>
+      </c>
+      <c r="N121" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="33" t="n">
-        <v>12.19</v>
+        <v>12.06</v>
       </c>
       <c r="P121" s="33" t="n">
-        <v>12.14</v>
+        <v>12.05</v>
       </c>
       <c r="Q121" s="34" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="R121" s="36" t="n">
-        <v>2.51</v>
+        <v>11.99</v>
+      </c>
+      <c r="R121" s="35" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="122">
@@ -8172,37 +8172,37 @@
         </is>
       </c>
       <c r="C122" s="25" t="n">
-        <v>8.73</v>
+        <v>9</v>
       </c>
       <c r="D122" s="25" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="E122" s="26" t="n">
-        <v>8.380000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="F122" s="27" t="n">
-        <v>8.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G122" s="27" t="n">
-        <v>8.49</v>
+        <v>8.43</v>
       </c>
       <c r="H122" s="28" t="n">
-        <v>8.300000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="I122" s="29" t="n">
-        <v>8.19</v>
+        <v>7.68</v>
       </c>
       <c r="J122" s="29" t="n">
-        <v>8.109999999999999</v>
+        <v>7.51</v>
       </c>
       <c r="K122" s="30" t="n">
-        <v>8.27</v>
+        <v>7.9</v>
       </c>
       <c r="L122" s="31" t="n">
-        <v>8.109999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>7.92</v>
+        <v>7.06</v>
       </c>
       <c r="N122" s="32" t="inlineStr">
         <is>
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="O122" s="33" t="n">
-        <v>8.289999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="P122" s="33" t="n">
-        <v>8.289999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="Q122" s="34" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="R122" s="36" t="n">
-        <v>0</v>
+        <v>7.85</v>
+      </c>
+      <c r="R122" s="35" t="n">
+        <v>-4.96</v>
       </c>
     </row>
     <row r="123">
@@ -8234,37 +8234,37 @@
         </is>
       </c>
       <c r="C123" s="25" t="n">
-        <v>8.98</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>8.529999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>8.15</v>
+        <v>7.95</v>
       </c>
       <c r="F123" s="27" t="n">
-        <v>8.17</v>
+        <v>7.95</v>
       </c>
       <c r="G123" s="27" t="n">
-        <v>8.44</v>
+        <v>8.07</v>
       </c>
       <c r="H123" s="28" t="n">
-        <v>7.99</v>
+        <v>7.88</v>
       </c>
       <c r="I123" s="29" t="n">
-        <v>7.72</v>
+        <v>7.76</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>7.54</v>
+        <v>7.69</v>
       </c>
       <c r="K123" s="30" t="n">
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="L123" s="31" t="n">
-        <v>7.52</v>
+        <v>7.68</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>7.07</v>
+        <v>7.49</v>
       </c>
       <c r="N123" s="32" t="inlineStr">
         <is>
@@ -8272,16 +8272,16 @@
         </is>
       </c>
       <c r="O123" s="33" t="n">
-        <v>7.96</v>
+        <v>7.87</v>
       </c>
       <c r="P123" s="33" t="n">
-        <v>7.93</v>
+        <v>7.86</v>
       </c>
       <c r="Q123" s="34" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="R123" s="36" t="n">
-        <v>0.13</v>
+        <v>7.84</v>
+      </c>
+      <c r="R123" s="35" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="124">
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="C124" s="25" t="n">
-        <v>30.65</v>
+        <v>30.82</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>28.89</v>
+        <v>29.82</v>
       </c>
       <c r="E124" s="26" t="n">
-        <v>27.41</v>
+        <v>28.98</v>
       </c>
       <c r="F124" s="27" t="n">
-        <v>28.39</v>
+        <v>29.28</v>
       </c>
       <c r="G124" s="27" t="n">
-        <v>28.97</v>
+        <v>29.74</v>
       </c>
       <c r="H124" s="28" t="n">
-        <v>27.21</v>
+        <v>28.74</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>26.63</v>
+        <v>28.28</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>25.45</v>
+        <v>27.74</v>
       </c>
       <c r="K124" s="30" t="n">
-        <v>26.43</v>
+        <v>28.42</v>
       </c>
       <c r="L124" s="31" t="n">
-        <v>24.95</v>
+        <v>27.58</v>
       </c>
       <c r="M124" s="31" t="n">
-        <v>23.19</v>
+        <v>26.58</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
@@ -8334,16 +8334,16 @@
         </is>
       </c>
       <c r="O124" s="33" t="n">
-        <v>26.89</v>
+        <v>28.62</v>
       </c>
       <c r="P124" s="33" t="n">
-        <v>26.56</v>
+        <v>28.5</v>
       </c>
       <c r="Q124" s="34" t="n">
-        <v>27.8</v>
+        <v>28.82</v>
       </c>
       <c r="R124" s="36" t="n">
-        <v>9.970000000000001</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="125">
@@ -8358,54 +8358,54 @@
         </is>
       </c>
       <c r="C125" s="25" t="n">
-        <v>174.38</v>
+        <v>170.47</v>
       </c>
       <c r="D125" s="25" t="n">
-        <v>167.78</v>
+        <v>166.47</v>
       </c>
       <c r="E125" s="26" t="n">
-        <v>162.25</v>
+        <v>163.12</v>
       </c>
       <c r="F125" s="27" t="n">
-        <v>164.9</v>
+        <v>162.73</v>
       </c>
       <c r="G125" s="27" t="n">
-        <v>167.6</v>
+        <v>165.37</v>
       </c>
       <c r="H125" s="28" t="n">
-        <v>161</v>
+        <v>161.37</v>
       </c>
       <c r="I125" s="29" t="n">
-        <v>158.3</v>
+        <v>158.73</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>154.4</v>
+        <v>157.37</v>
       </c>
       <c r="K125" s="30" t="n">
-        <v>158.55</v>
+        <v>160.88</v>
       </c>
       <c r="L125" s="31" t="n">
-        <v>153.02</v>
+        <v>157.53</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>146.42</v>
-      </c>
-      <c r="N125" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>153.53</v>
+      </c>
+      <c r="N125" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="33" t="n">
-        <v>160.03</v>
+        <v>161.28</v>
       </c>
       <c r="P125" s="33" t="n">
-        <v>159.07</v>
+        <v>161.19</v>
       </c>
       <c r="Q125" s="34" t="n">
-        <v>162.2</v>
-      </c>
-      <c r="R125" s="36" t="n">
-        <v>3.25</v>
+        <v>160.1</v>
+      </c>
+      <c r="R125" s="35" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="126">
@@ -8420,54 +8420,54 @@
         </is>
       </c>
       <c r="C126" s="25" t="n">
-        <v>61.73</v>
+        <v>57.2</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>59.18</v>
+        <v>56.55</v>
       </c>
       <c r="E126" s="26" t="n">
-        <v>57.04</v>
+        <v>56.01</v>
       </c>
       <c r="F126" s="27" t="n">
-        <v>57.65</v>
+        <v>56.17</v>
       </c>
       <c r="G126" s="27" t="n">
-        <v>58.9</v>
+        <v>56.48</v>
       </c>
       <c r="H126" s="28" t="n">
-        <v>56.35</v>
+        <v>55.83</v>
       </c>
       <c r="I126" s="29" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="J126" s="29" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="K126" s="30" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="L126" s="31" t="n">
         <v>55.1</v>
       </c>
-      <c r="J126" s="29" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="K126" s="30" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="L126" s="31" t="n">
-        <v>53.47</v>
-      </c>
       <c r="M126" s="31" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>54.45</v>
+      </c>
+      <c r="N126" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="33" t="n">
-        <v>56.08</v>
+        <v>55.76</v>
       </c>
       <c r="P126" s="33" t="n">
-        <v>55.81</v>
+        <v>55.69</v>
       </c>
       <c r="Q126" s="34" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="R126" s="36" t="n">
-        <v>2.17</v>
+        <v>55.85</v>
+      </c>
+      <c r="R126" s="35" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="127">
@@ -8482,37 +8482,37 @@
         </is>
       </c>
       <c r="C127" s="25" t="n">
-        <v>17.04</v>
+        <v>16.02</v>
       </c>
       <c r="D127" s="25" t="n">
-        <v>16.2</v>
+        <v>15.67</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>15.5</v>
+        <v>15.37</v>
       </c>
       <c r="F127" s="27" t="n">
-        <v>15.8</v>
+        <v>15.53</v>
       </c>
       <c r="G127" s="27" t="n">
-        <v>16.16</v>
+        <v>15.66</v>
       </c>
       <c r="H127" s="28" t="n">
-        <v>15.32</v>
+        <v>15.31</v>
       </c>
       <c r="I127" s="29" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="J127" s="29" t="n">
         <v>14.96</v>
       </c>
-      <c r="J127" s="29" t="n">
-        <v>14.48</v>
-      </c>
       <c r="K127" s="30" t="n">
-        <v>15.02</v>
+        <v>15.18</v>
       </c>
       <c r="L127" s="31" t="n">
-        <v>14.32</v>
+        <v>14.88</v>
       </c>
       <c r="M127" s="31" t="n">
-        <v>13.48</v>
+        <v>14.53</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="O127" s="33" t="n">
-        <v>15.21</v>
+        <v>15.26</v>
       </c>
       <c r="P127" s="33" t="n">
-        <v>15.09</v>
+        <v>15.2</v>
       </c>
       <c r="Q127" s="34" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="R127" s="36" t="n">
-        <v>3.42</v>
+        <v>15.39</v>
+      </c>
+      <c r="R127" s="35" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="128">
@@ -8544,37 +8544,37 @@
         </is>
       </c>
       <c r="C128" s="25" t="n">
-        <v>16.02</v>
+        <v>16.08</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>15.61</v>
+        <v>15.77</v>
       </c>
       <c r="E128" s="26" t="n">
-        <v>15.27</v>
+        <v>15.51</v>
       </c>
       <c r="F128" s="27" t="n">
-        <v>15.45</v>
+        <v>15.56</v>
       </c>
       <c r="G128" s="27" t="n">
-        <v>15.61</v>
+        <v>15.73</v>
       </c>
       <c r="H128" s="28" t="n">
-        <v>15.2</v>
+        <v>15.42</v>
       </c>
       <c r="I128" s="29" t="n">
-        <v>15.04</v>
+        <v>15.25</v>
       </c>
       <c r="J128" s="29" t="n">
-        <v>14.79</v>
+        <v>15.11</v>
       </c>
       <c r="K128" s="30" t="n">
-        <v>15.04</v>
+        <v>15.34</v>
       </c>
       <c r="L128" s="31" t="n">
-        <v>14.7</v>
+        <v>15.08</v>
       </c>
       <c r="M128" s="31" t="n">
-        <v>14.29</v>
+        <v>14.77</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
@@ -8582,16 +8582,16 @@
         </is>
       </c>
       <c r="O128" s="33" t="n">
-        <v>15.14</v>
+        <v>15.39</v>
       </c>
       <c r="P128" s="33" t="n">
-        <v>15.07</v>
+        <v>15.36</v>
       </c>
       <c r="Q128" s="34" t="n">
-        <v>15.29</v>
+        <v>15.4</v>
       </c>
       <c r="R128" s="36" t="n">
-        <v>2.62</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="129">
@@ -8606,54 +8606,54 @@
         </is>
       </c>
       <c r="C129" s="25" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
       <c r="E129" s="26" t="n">
-        <v>7.79</v>
+        <v>7.56</v>
       </c>
       <c r="F129" s="27" t="n">
-        <v>7.77</v>
+        <v>7.56</v>
       </c>
       <c r="G129" s="27" t="n">
-        <v>7.93</v>
+        <v>7.67</v>
       </c>
       <c r="H129" s="28" t="n">
-        <v>7.68</v>
+        <v>7.49</v>
       </c>
       <c r="I129" s="29" t="n">
-        <v>7.52</v>
+        <v>7.38</v>
       </c>
       <c r="J129" s="29" t="n">
-        <v>7.43</v>
+        <v>7.31</v>
       </c>
       <c r="K129" s="30" t="n">
-        <v>7.65</v>
+        <v>7.46</v>
       </c>
       <c r="L129" s="31" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="M129" s="31" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="N129" s="32" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O129" s="33" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="P129" s="33" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="Q129" s="34" t="n">
         <v>7.45</v>
       </c>
-      <c r="M129" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N129" s="32" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O129" s="33" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="P129" s="33" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="Q129" s="34" t="n">
-        <v>7.6</v>
-      </c>
       <c r="R129" s="35" t="n">
-        <v>-0.65</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="130">
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C130" s="25" t="n">
-        <v>11.66</v>
+        <v>10.83</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>11.18</v>
+        <v>10.57</v>
       </c>
       <c r="E130" s="26" t="n">
-        <v>10.77</v>
+        <v>10.35</v>
       </c>
       <c r="F130" s="27" t="n">
-        <v>10.72</v>
+        <v>10.39</v>
       </c>
       <c r="G130" s="27" t="n">
-        <v>11.04</v>
+        <v>10.53</v>
       </c>
       <c r="H130" s="28" t="n">
-        <v>10.56</v>
+        <v>10.27</v>
       </c>
       <c r="I130" s="29" t="n">
-        <v>10.24</v>
+        <v>10.13</v>
       </c>
       <c r="J130" s="29" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="K130" s="30" t="n">
-        <v>10.51</v>
+        <v>10.21</v>
       </c>
       <c r="L130" s="31" t="n">
-        <v>10.1</v>
+        <v>9.99</v>
       </c>
       <c r="M130" s="31" t="n">
-        <v>9.619999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="N130" s="32" t="inlineStr">
         <is>
@@ -8706,16 +8706,16 @@
         </is>
       </c>
       <c r="O130" s="33" t="n">
-        <v>10.55</v>
+        <v>10.25</v>
       </c>
       <c r="P130" s="33" t="n">
-        <v>10.54</v>
+        <v>10.23</v>
       </c>
       <c r="Q130" s="34" t="n">
-        <v>10.4</v>
+        <v>10.25</v>
       </c>
       <c r="R130" s="35" t="n">
-        <v>-2.89</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="131">
@@ -8730,37 +8730,37 @@
         </is>
       </c>
       <c r="C131" s="25" t="n">
-        <v>146.78</v>
+        <v>144.29</v>
       </c>
       <c r="D131" s="25" t="n">
-        <v>142.28</v>
+        <v>141.39</v>
       </c>
       <c r="E131" s="26" t="n">
-        <v>138.51</v>
+        <v>138.96</v>
       </c>
       <c r="F131" s="27" t="n">
-        <v>139.73</v>
+        <v>139.17</v>
       </c>
       <c r="G131" s="27" t="n">
-        <v>141.87</v>
+        <v>140.83</v>
       </c>
       <c r="H131" s="28" t="n">
-        <v>137.37</v>
+        <v>137.93</v>
       </c>
       <c r="I131" s="29" t="n">
-        <v>135.23</v>
+        <v>136.27</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>132.87</v>
+        <v>135.03</v>
       </c>
       <c r="K131" s="30" t="n">
-        <v>135.99</v>
+        <v>137.34</v>
       </c>
       <c r="L131" s="31" t="n">
-        <v>132.22</v>
+        <v>134.91</v>
       </c>
       <c r="M131" s="31" t="n">
-        <v>127.72</v>
+        <v>132.01</v>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
@@ -8768,16 +8768,16 @@
         </is>
       </c>
       <c r="O131" s="33" t="n">
-        <v>136.85</v>
+        <v>137.75</v>
       </c>
       <c r="P131" s="33" t="n">
-        <v>136.34</v>
+        <v>137.56</v>
       </c>
       <c r="Q131" s="34" t="n">
-        <v>137.6</v>
-      </c>
-      <c r="R131" s="36" t="n">
-        <v>0.44</v>
+        <v>137.5</v>
+      </c>
+      <c r="R131" s="35" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -250,13 +250,13 @@
     <xf numFmtId="2" fontId="0" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-16</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.61</v>
+        <v>20.47</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.41</v>
+        <v>20.33</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="F3" s="15" t="n">
         <v>20.25</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.37</v>
+        <v>20.31</v>
       </c>
       <c r="H3" s="16" t="n">
         <v>20.17</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20.05</v>
+        <v>20.11</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>19.97</v>
+        <v>20.03</v>
       </c>
       <c r="K3" s="18" t="n">
         <v>20.13</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>19.97</v>
+        <v>20.01</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.77</v>
+        <v>19.87</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O3" s="21" t="n">
         <v>20.16</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.15</v>
+        <v>20.14</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.13</v>
+        <v>20.18</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -820,51 +820,51 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.05</v>
+        <v>12.06</v>
       </c>
       <c r="D4" s="13" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="G4" s="15" t="n">
         <v>11.93</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>11.92</v>
-      </c>
       <c r="H4" s="16" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>11.8</v>
       </c>
-      <c r="I4" s="17" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="N4" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>11.78</v>
-      </c>
       <c r="Q4" s="22" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="R4" s="23" t="n">
         <v>0.08</v>
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15.12</v>
+        <v>15.14</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.8</v>
+        <v>14.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.9</v>
+        <v>14.81</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.95</v>
+        <v>14.91</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.73</v>
+        <v>14.6</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>14.61</v>
+        <v>14.49</v>
       </c>
       <c r="K5" s="18" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="M5" s="19" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="N5" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="P5" s="21" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="Q5" s="22" t="n">
         <v>14.71</v>
       </c>
-      <c r="L5" s="19" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="M5" s="19" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="N5" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="P5" s="21" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="Q5" s="22" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="R5" s="23" t="n">
-        <v>0.54</v>
+      <c r="R5" s="25" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>22.36</v>
+        <v>22.35</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.7</v>
+        <v>21.52</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.9</v>
+        <v>21.56</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>22.02</v>
+        <v>21.82</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>21.66</v>
+        <v>21.37</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>21.54</v>
+        <v>21.11</v>
       </c>
       <c r="J6" s="17" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="L6" s="19" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="M6" s="19" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="P6" s="21" t="n">
         <v>21.3</v>
       </c>
-      <c r="K6" s="18" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="L6" s="19" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M6" s="19" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="N6" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O6" s="21" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="P6" s="21" t="n">
-        <v>21.53</v>
-      </c>
       <c r="Q6" s="22" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="R6" s="23" t="n">
-        <v>0.83</v>
+        <v>21.31</v>
+      </c>
+      <c r="R6" s="25" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.06</v>
+        <v>34.08</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.7</v>
+        <v>33.76</v>
       </c>
       <c r="E7" s="14" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="H7" s="16" t="n">
         <v>33.4</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>33.48</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>33.66</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I7" s="17" t="n">
-        <v>33.12</v>
+        <v>33.24</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>32.94</v>
+        <v>33.08</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.2</v>
+        <v>33.31</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.9</v>
+        <v>33.04</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.54</v>
+        <v>32.72</v>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.26</v>
+        <v>33.37</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.23</v>
+        <v>33.34</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R7" s="25" t="n">
-        <v>-0.54</v>
+        <v>33.4</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>24.48</v>
+        <v>23.31</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.81</v>
+        <v>23.05</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>23.25</v>
+        <v>22.83</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>23.24</v>
+        <v>22.88</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.65</v>
+        <v>23.02</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.98</v>
+        <v>22.76</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.57</v>
+        <v>22.62</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.31</v>
+        <v>22.5</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>22.88</v>
+        <v>22.69</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>22.32</v>
+        <v>22.47</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
+        <v>22.21</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>22.96</v>
+        <v>22.73</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>22.93</v>
+        <v>22.71</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.82</v>
+        <v>22.75</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>-2.48</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>129.04</v>
+        <v>128.45</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>126.55</v>
+        <v>125.45</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>124.45</v>
+        <v>122.94</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>124.57</v>
+        <v>122.6</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>126.03</v>
+        <v>124.6</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>123.53</v>
+        <v>121.6</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>122.07</v>
+        <v>119.6</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>121.03</v>
+        <v>118.6</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>123.05</v>
+        <v>121.26</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>120.95</v>
+        <v>118.75</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>118.45</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
+        <v>115.75</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>123.39</v>
+        <v>121.55</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>123.25</v>
+        <v>121.49</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>123.1</v>
-      </c>
-      <c r="R9" s="23" t="n">
-        <v>0.65</v>
+        <v>120.6</v>
+      </c>
+      <c r="R9" s="25" t="n">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>67.63</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>66.93000000000001</v>
+        <v>66.72</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>66.34999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>66.33</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>66.77</v>
+        <v>66.63</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>66.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>65.63</v>
+        <v>65.72</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>65.37</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>65.95</v>
+        <v>65.88</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>65.37</v>
+        <v>65.38</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+        <v>64.78</v>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>66.04000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>66.01000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="R10" s="25" t="n">
-        <v>-0.45</v>
+        <v>66</v>
+      </c>
+      <c r="R10" s="23" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25.45</v>
+        <v>25.65</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>25.21</v>
+        <v>25.27</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>25.01</v>
+        <v>24.96</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>25.1</v>
+        <v>24.97</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>25.2</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.96</v>
+        <v>24.82</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.86</v>
+        <v>24.59</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.72</v>
+        <v>24.44</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.87</v>
+        <v>24.74</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>24.67</v>
+        <v>24.43</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
+        <v>24.05</v>
+      </c>
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.93</v>
+        <v>24.79</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.89</v>
+        <v>24.77</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>25</v>
+        <v>24.75</v>
       </c>
       <c r="R11" s="25" t="n">
-        <v>-0.08</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.04</v>
+        <v>25.81</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>24.83</v>
+        <v>25.37</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.65</v>
+        <v>25</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.75</v>
+        <v>25.17</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.83</v>
+        <v>25.36</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.62</v>
+        <v>24.92</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.54</v>
+        <v>24.73</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.41</v>
+        <v>24.48</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>24.54</v>
+        <v>24.76</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.36</v>
+        <v>24.39</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="N12" s="24" t="inlineStr">
+        <v>23.95</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.59</v>
+        <v>24.85</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.55</v>
+        <v>24.79</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.67</v>
+        <v>24.99</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>0.65</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>42.83</v>
+        <v>42.07</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>41.75</v>
+        <v>41.31</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.84</v>
+        <v>40.67</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>41.19</v>
+        <v>40.64</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>41.67</v>
+        <v>41.12</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.59</v>
+        <v>40.36</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>40.11</v>
+        <v>39.88</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.51</v>
+        <v>39.6</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.24</v>
+        <v>40.25</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.33</v>
+        <v>39.61</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
+        <v>38.85</v>
+      </c>
+      <c r="N13" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.46</v>
+        <v>40.33</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.32</v>
+        <v>40.31</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40.7</v>
+        <v>40.16</v>
       </c>
       <c r="R13" s="25" t="n">
-        <v>-0.25</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.779999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.52</v>
+        <v>8.49</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>8.52</v>
+        <v>8.49</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>8.609999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>8.470000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J14" s="17" t="n">
         <v>8.33</v>
       </c>
       <c r="K14" s="18" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
         <v>8.44</v>
       </c>
-      <c r="L14" s="19" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.460000000000001</v>
-      </c>
       <c r="P14" s="21" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.44</v>
+        <v>8.42</v>
       </c>
       <c r="R14" s="25" t="n">
-        <v>-0.71</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>15.27</v>
+        <v>15.19</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.72</v>
+        <v>14.57</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>14.26</v>
+        <v>14.05</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>14.24</v>
+        <v>14.4</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>14.58</v>
+        <v>14.6</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>14.03</v>
+        <v>13.98</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.69</v>
+        <v>13.78</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.48</v>
+        <v>13.36</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.95</v>
+        <v>13.71</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.49</v>
+        <v>13.19</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>12.94</v>
+        <v>12.57</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>14.01</v>
+        <v>13.87</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.99</v>
+        <v>13.75</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="R15" s="25" t="n">
-        <v>-2.39</v>
+        <v>14.19</v>
+      </c>
+      <c r="R15" s="23" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.54</v>
+        <v>4.73</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.31</v>
+        <v>4.18</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>4.18</v>
+        <v>3.89</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>4.12</v>
+        <v>3.79</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>4.12</v>
+        <v>3.79</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>4.24</v>
+        <v>4.06</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="R16" s="25" t="n">
-        <v>-1.86</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.55</v>
+        <v>17.46</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.27</v>
+        <v>17.22</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>17.04</v>
+        <v>17.02</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.03</v>
+        <v>17.06</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.2</v>
+        <v>17.18</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.92</v>
+        <v>16.94</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.75</v>
+        <v>16.82</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.64</v>
+        <v>16.7</v>
       </c>
       <c r="K17" s="18" t="n">
         <v>16.88</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.65</v>
+        <v>16.68</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>16.37</v>
+        <v>16.44</v>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.91</v>
+        <v>16.92</v>
       </c>
       <c r="P17" s="21" t="n">
         <v>16.9</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="R17" s="25" t="n">
-        <v>-0.12</v>
+        <v>16.93</v>
+      </c>
+      <c r="R17" s="23" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.36</v>
+        <v>24.38</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.06</v>
+        <v>24.1</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>23.8</v>
+        <v>23.87</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>23.94</v>
+        <v>24.02</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.05</v>
+        <v>24.12</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>23.75</v>
+        <v>23.84</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.64</v>
+        <v>23.74</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>23.45</v>
+        <v>23.56</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.64</v>
+        <v>23.71</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>23.38</v>
+        <v>23.48</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="N18" s="24" t="inlineStr">
+        <v>23.2</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.71</v>
+        <v>23.79</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.66</v>
+        <v>23.73</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.82</v>
+        <v>23.93</v>
       </c>
       <c r="R18" s="23" t="n">
-        <v>1.06</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>66.45</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>64.75</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>63.33</v>
+        <v>63.17</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>63.8</v>
+        <v>63</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>64.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>62.9</v>
+        <v>62.5</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>62.1</v>
+        <v>61.5</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>62.37</v>
+        <v>62.33</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.95</v>
+        <v>61.07</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>59.25</v>
+        <v>59.57</v>
       </c>
       <c r="N19" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>62.7</v>
+        <v>62.47</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>62.51</v>
+        <v>62.45</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="R19" s="23" t="n">
-        <v>1.37</v>
+        <v>62</v>
+      </c>
+      <c r="R19" s="25" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.21</v>
+        <v>11.32</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.99</v>
+        <v>10.96</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>11.07</v>
+        <v>11.11</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>10.95</v>
+        <v>10.91</v>
       </c>
       <c r="I20" s="17" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="N20" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n">
         <v>10.88</v>
       </c>
-      <c r="J20" s="17" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>10.94</v>
-      </c>
       <c r="P20" s="21" t="n">
-        <v>10.94</v>
+        <v>10.86</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="R20" s="23" t="n">
-        <v>0</v>
+        <v>10.92</v>
+      </c>
+      <c r="R20" s="25" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>18.3</v>
+        <v>17.94</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.85</v>
+        <v>17.64</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>17.47</v>
+        <v>17.38</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>17.61</v>
+        <v>17.35</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.81</v>
+        <v>17.55</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>17.36</v>
+        <v>17.25</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>17.16</v>
+        <v>17.05</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.91</v>
+        <v>16.95</v>
       </c>
       <c r="K21" s="18" t="n">
         <v>17.22</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.84</v>
+        <v>16.96</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.39</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
+        <v>16.66</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>17.31</v>
+        <v>17.24</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="R21" s="23" t="n">
-        <v>0.35</v>
+        <v>17.15</v>
+      </c>
+      <c r="R21" s="25" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F22" s="15" t="n">
         <v>36.51</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>35.55</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>34.75</v>
-      </c>
-      <c r="F22" s="15" t="n">
+      <c r="G22" s="15" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="n">
         <v>35.11</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="J22" s="17" t="n">
-        <v>33.59</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="L22" s="19" t="n">
-        <v>33.41</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>34.42</v>
-      </c>
       <c r="P22" s="21" t="n">
-        <v>34.29</v>
+        <v>34.81</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>34.7</v>
+        <v>35.96</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>0.29</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>15.5</v>
+        <v>16.32</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.14</v>
+        <v>15.75</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>14.84</v>
+        <v>15.27</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>14.98</v>
+        <v>15.59</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.13</v>
+        <v>15.78</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>14.77</v>
+        <v>15.21</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>14.62</v>
+        <v>15.02</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.41</v>
+        <v>14.64</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>14.64</v>
+        <v>14.96</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.34</v>
+        <v>14.48</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="N23" s="24" t="inlineStr">
+        <v>13.91</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>14.72</v>
+        <v>15.1</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>14.83</v>
+        <v>15.4</v>
       </c>
       <c r="R23" s="23" t="n">
-        <v>1.58</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>36.76</v>
+        <v>37.48</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>35.98</v>
+        <v>36.58</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.33</v>
+        <v>35.82</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.4</v>
+        <v>35.95</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>35.84</v>
+        <v>36.43</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.06</v>
+        <v>35.53</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>34.62</v>
+        <v>35.05</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>34.28</v>
+        <v>34.63</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>34.89</v>
+        <v>35.32</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.24</v>
+        <v>34.56</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33.46</v>
+        <v>33.66</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.01</v>
+        <v>35.46</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>34.95</v>
+        <v>35.39</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>34.96</v>
-      </c>
-      <c r="R24" s="25" t="n">
-        <v>-0.29</v>
+        <v>35.46</v>
+      </c>
+      <c r="R24" s="23" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>60.38</v>
+        <v>58.32</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>58.63</v>
+        <v>57.32</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>57.16</v>
+        <v>56.48</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>56.97</v>
+        <v>56.53</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>58.13</v>
+        <v>57.12</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>56.38</v>
+        <v>56.12</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>55.22</v>
+        <v>55.53</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>54.63</v>
+        <v>55.12</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>56.18</v>
+        <v>55.92</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.72</v>
+        <v>55.08</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
+        <v>54.08</v>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>56.35</v>
+        <v>56.06</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="R25" s="25" t="n">
-        <v>-2.28</v>
+        <v>55.95</v>
+      </c>
+      <c r="R25" s="23" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>216.11</v>
+        <v>221.6</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>210.91</v>
+        <v>214.8</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>206.56</v>
+        <v>209.1</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>206.9</v>
+        <v>211.6</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>209.9</v>
+        <v>214.5</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>204.7</v>
+        <v>207.7</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>201.7</v>
+        <v>204.8</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>199.5</v>
+        <v>200.9</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>203.64</v>
+        <v>205.3</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>199.29</v>
+        <v>199.6</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>194.09</v>
+        <v>192.8</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>204.37</v>
+        <v>206.76</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>204.05</v>
+        <v>205.83</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>203.9</v>
-      </c>
-      <c r="R26" s="25" t="n">
-        <v>-0.44</v>
+        <v>208.7</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>86.8</v>
+        <v>82.23</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>83.8</v>
+        <v>80.73</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>81.29000000000001</v>
+        <v>79.47</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>81.15000000000001</v>
+        <v>79.47</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>83.05</v>
+        <v>80.38</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>80.05</v>
+        <v>78.88</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>78.15000000000001</v>
+        <v>77.97</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>77.05</v>
+        <v>77.38</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>79.61</v>
+        <v>78.63</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>77.09999999999999</v>
+        <v>77.37</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
+        <v>75.87</v>
+      </c>
+      <c r="N27" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>79.95</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>79.84</v>
+        <v>78.75</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>79.25</v>
+        <v>78.55</v>
       </c>
       <c r="R27" s="25" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>20.86</v>
+        <v>21</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.55</v>
+        <v>20.66</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.29</v>
+        <v>20.38</v>
       </c>
       <c r="F28" s="15" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="Q28" s="22" t="n">
         <v>20.38</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="J28" s="17" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="L28" s="19" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="Q28" s="22" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="R28" s="25" t="n">
-        <v>-0.15</v>
+      <c r="R28" s="23" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>81.59999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>80.3</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>79.20999999999999</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>79.7</v>
+        <v>81.45</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>80.25</v>
+        <v>82.3</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>78.95</v>
+        <v>79.75</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>78.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>77.65000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>78.48999999999999</v>
+        <v>78.61</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>77.40000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="N29" s="24" t="inlineStr">
+        <v>73.92</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>78.77</v>
+        <v>79.28</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>78.59</v>
+        <v>78.81</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="R29" s="25" t="n">
-        <v>-0.31</v>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R29" s="23" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>30.32</v>
+        <v>29.88</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>29.38</v>
+        <v>28.78</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>28.59</v>
+        <v>27.86</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>28.53</v>
+        <v>27.93</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>29.13</v>
+        <v>28.57</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>28.19</v>
+        <v>27.47</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>27.59</v>
+        <v>26.83</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>27.25</v>
+        <v>26.37</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>28.07</v>
+        <v>27.24</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>27.28</v>
+        <v>26.32</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>26.34</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
+        <v>25.22</v>
+      </c>
+      <c r="N30" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>28.17</v>
+        <v>27.4</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>28.14</v>
+        <v>27.33</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <v>0.36</v>
+        <v>27.3</v>
+      </c>
+      <c r="R30" s="25" t="n">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.06</v>
+        <v>49.38</v>
       </c>
       <c r="D31" s="13" t="n">
         <v>48.64</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>48.29</v>
+        <v>48.02</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>48.29</v>
+        <v>48.31</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>48.55</v>
+        <v>48.61</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>48.13</v>
+        <v>47.87</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.87</v>
+        <v>47.57</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>47.71</v>
+        <v>47.13</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>48.05</v>
+        <v>47.6</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>47.7</v>
+        <v>46.98</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
+        <v>46.24</v>
+      </c>
+      <c r="N31" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>48.11</v>
+        <v>47.77</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>48.09</v>
+        <v>47.66</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>48.04</v>
+        <v>48</v>
       </c>
       <c r="R31" s="25" t="n">
-        <v>-0.25</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>129.11</v>
+        <v>134.12</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>126.51</v>
+        <v>129.72</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>124.33</v>
+        <v>126.03</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>124.17</v>
+        <v>128.47</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>125.83</v>
+        <v>129.93</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>123.23</v>
+        <v>125.53</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>121.57</v>
+        <v>124.07</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>120.63</v>
+        <v>121.13</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>122.87</v>
+        <v>123.57</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>120.69</v>
+        <v>119.88</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>118.09</v>
+        <v>115.48</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>123.15</v>
+        <v>124.72</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>123.07</v>
+        <v>123.91</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="R32" s="25" t="n">
-        <v>-1.92</v>
+        <v>127</v>
+      </c>
+      <c r="R32" s="23" t="n">
+        <v>3.67</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>63.66</v>
+        <v>61.61</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>60.81</v>
+        <v>59.41</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>58.42</v>
+        <v>57.57</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>58.67</v>
+        <v>57.55</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>60.28</v>
+        <v>58.9</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>57.43</v>
+        <v>56.7</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>55.82</v>
+        <v>55.35</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>54.58</v>
+        <v>54.5</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>56.83</v>
+        <v>56.33</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>54.44</v>
+        <v>54.49</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>51.59</v>
-      </c>
-      <c r="N33" s="20" t="inlineStr">
+        <v>52.29</v>
+      </c>
+      <c r="N33" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>57.24</v>
+        <v>56.6</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>57.05</v>
+        <v>56.51</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>57.05</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>0.18</v>
+        <v>56.2</v>
+      </c>
+      <c r="R33" s="25" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.99</v>
+        <v>24.7</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>24.15</v>
+        <v>23.99</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.45</v>
+        <v>23.39</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.38</v>
+        <v>23.79</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.93</v>
+        <v>24.02</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.09</v>
+        <v>23.31</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>22.54</v>
+        <v>23.08</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.25</v>
+        <v>22.6</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>22.97</v>
+        <v>23</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.27</v>
+        <v>22.4</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>21.43</v>
+        <v>21.69</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>23.06</v>
+        <v>23.18</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.04</v>
+        <v>23.05</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>22.84</v>
-      </c>
-      <c r="R34" s="25" t="n">
-        <v>-2.39</v>
+        <v>23.55</v>
+      </c>
+      <c r="R34" s="23" t="n">
+        <v>3.11</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.19</v>
+        <v>26.52</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.85</v>
+        <v>26.06</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.57</v>
+        <v>25.68</v>
       </c>
       <c r="F35" s="15" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="K35" s="18" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="n">
         <v>25.54</v>
       </c>
-      <c r="G35" s="15" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>25.42</v>
-      </c>
-      <c r="I35" s="17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="J35" s="17" t="n">
-        <v>25.08</v>
-      </c>
-      <c r="K35" s="18" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>25.41</v>
-      </c>
       <c r="P35" s="21" t="n">
-        <v>25.4</v>
+        <v>25.46</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="R35" s="25" t="n">
-        <v>-0.78</v>
+        <v>25.78</v>
+      </c>
+      <c r="R35" s="23" t="n">
+        <v>1.82</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>9.039999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.91</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="F36" s="15" t="n">
         <v>8.81</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H36" s="16" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="Q36" s="22" t="n">
         <v>8.76</v>
       </c>
-      <c r="I36" s="17" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="J36" s="17" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="P36" s="21" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="Q36" s="22" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="R36" s="25" t="n">
-        <v>-0.23</v>
+      <c r="R36" s="23" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>32.31</v>
+        <v>37.5</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>31.49</v>
+        <v>34.72</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>30.8</v>
+        <v>32.39</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>30.79</v>
+        <v>33.89</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>31.29</v>
+        <v>34.83</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>30.47</v>
+        <v>32.05</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>29.97</v>
+        <v>31.11</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>29.65</v>
+        <v>29.27</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>30.34</v>
+        <v>30.83</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>29.65</v>
+        <v>28.5</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>28.83</v>
+        <v>25.72</v>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>30.44</v>
+        <v>31.55</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>30.4</v>
+        <v>31.05</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>30.28</v>
-      </c>
-      <c r="R37" s="25" t="n">
-        <v>-1.43</v>
+        <v>32.94</v>
+      </c>
+      <c r="R37" s="23" t="n">
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>196.71</v>
+        <v>191.91</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>189.41</v>
+        <v>186.71</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>183.29</v>
+        <v>182.36</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185.07</v>
+        <v>182.9</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>188.63</v>
+        <v>185.8</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>181.33</v>
+        <v>180.6</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>177.77</v>
+        <v>177.7</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>174.03</v>
+        <v>175.4</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>179.21</v>
+        <v>179.44</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>173.09</v>
+        <v>175.09</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>165.79</v>
+        <v>169.89</v>
       </c>
       <c r="N38" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>180.55</v>
+        <v>180.22</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>179.78</v>
+        <v>179.85</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="R38" s="23" t="n">
-        <v>1.57</v>
+        <v>180</v>
+      </c>
+      <c r="R38" s="25" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="N39" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>23.5</v>
+        <v>24.23</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>22.7</v>
+        <v>23.19</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>22.03</v>
+        <v>22.32</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>22.07</v>
+        <v>22.41</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>22.54</v>
+        <v>23</v>
       </c>
       <c r="H40" s="16" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="K40" s="18" t="n">
         <v>21.74</v>
       </c>
-      <c r="I40" s="17" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="J40" s="17" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>21.59</v>
-      </c>
       <c r="L40" s="19" t="n">
-        <v>20.92</v>
+        <v>20.87</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>20.12</v>
+        <v>19.83</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.69</v>
+        <v>21.89</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.65</v>
+        <v>21.82</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R40" s="25" t="n">
-        <v>-0.46</v>
+        <v>21.82</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>198</v>
+        <v>200.68</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>190.4</v>
+        <v>192.78</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>184.03</v>
+        <v>186.16</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>184.43</v>
+        <v>188.33</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>188.87</v>
+        <v>192.07</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>181.27</v>
+        <v>184.17</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>176.83</v>
+        <v>180.43</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>173.67</v>
+        <v>176.27</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>179.77</v>
+        <v>181.74</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>173.4</v>
+        <v>175.12</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>165.8</v>
+        <v>167.22</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>180.82</v>
+        <v>183.26</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>180.36</v>
+        <v>182.35</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R41" s="25" t="n">
-        <v>-3.12</v>
+        <v>184.6</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>2.56</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>37.08</v>
+        <v>37.3</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.66</v>
+        <v>36.84</v>
       </c>
       <c r="E42" s="14" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O42" s="21" t="n">
         <v>36.31</v>
       </c>
-      <c r="F42" s="15" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>36.63</v>
-      </c>
-      <c r="H42" s="16" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="I42" s="17" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="J42" s="17" t="n">
-        <v>35.79</v>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>35.72</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="N42" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="n">
-        <v>36.16</v>
-      </c>
       <c r="P42" s="21" t="n">
-        <v>36.11</v>
+        <v>36.24</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>36.26</v>
+        <v>36.46</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.33</v>
+        <v>27.55</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.51</v>
+        <v>27.15</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>26.82</v>
+        <v>26.81</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.07</v>
+        <v>26.97</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.45</v>
+        <v>27.13</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>26.63</v>
+        <v>26.73</v>
       </c>
       <c r="I43" s="17" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="L43" s="19" t="n">
         <v>26.25</v>
       </c>
-      <c r="J43" s="17" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="K43" s="18" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>25.67</v>
-      </c>
       <c r="M43" s="19" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="N43" s="24" t="inlineStr">
+        <v>25.85</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>26.53</v>
+        <v>26.68</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>26.42</v>
+        <v>26.62</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="R43" s="23" t="n">
-        <v>1.91</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.19</v>
+        <v>25.98</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.91</v>
+        <v>25.82</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>25.68</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.79</v>
+        <v>25.67</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>25.91</v>
+        <v>25.77</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.63</v>
+        <v>25.61</v>
       </c>
       <c r="I44" s="17" t="n">
         <v>25.51</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.35</v>
+        <v>25.45</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.52</v>
+        <v>25.6</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.29</v>
+        <v>25.46</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>25.01</v>
+        <v>25.3</v>
       </c>
       <c r="N44" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.59</v>
+        <v>25.61</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.54</v>
+        <v>25.61</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.68</v>
-      </c>
-      <c r="R44" s="23" t="n">
-        <v>0.63</v>
+        <v>25.56</v>
+      </c>
+      <c r="R44" s="25" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.78</v>
+        <v>7.73</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.66</v>
+        <v>7.64</v>
       </c>
       <c r="E45" s="14" t="n">
         <v>7.56</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.65</v>
+        <v>7.63</v>
       </c>
       <c r="H45" s="16" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="n">
         <v>7.53</v>
       </c>
-      <c r="I45" s="17" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="K45" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O45" s="21" t="n">
+      <c r="P45" s="21" t="n">
         <v>7.52</v>
       </c>
-      <c r="P45" s="21" t="n">
-        <v>7.51</v>
-      </c>
       <c r="Q45" s="22" t="n">
-        <v>7.53</v>
+        <v>7.54</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>0.67</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>11.91</v>
+        <v>11.97</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>11.79</v>
+        <v>11.82</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.71</v>
+        <v>11.73</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.63</v>
+        <v>11.61</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.53</v>
+        <v>11.49</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
+        <v>11.34</v>
+      </c>
+      <c r="N46" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.65</v>
+        <v>11.64</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.64</v>
+        <v>11.62</v>
       </c>
       <c r="Q46" s="22" t="n">
         <v>11.65</v>
       </c>
       <c r="R46" s="23" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>211.1</v>
+        <v>207.92</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>207.7</v>
+        <v>205.62</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>204.85</v>
+        <v>203.69</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>205.07</v>
+        <v>204.57</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>207.03</v>
+        <v>205.53</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>203.63</v>
+        <v>203.23</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>201.67</v>
+        <v>202.27</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>200.23</v>
+        <v>200.93</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>202.95</v>
+        <v>202.41</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>200.1</v>
+        <v>200.48</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>196.7</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
+        <v>198.18</v>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>203.42</v>
+        <v>202.91</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>203.21</v>
+        <v>202.59</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>203.1</v>
-      </c>
-      <c r="R47" s="25" t="n">
-        <v>-0.44</v>
+        <v>203.6</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>49.37</v>
+        <v>47.38</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>47.89</v>
+        <v>46.5</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>46.65</v>
+        <v>45.77</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>46.61</v>
+        <v>46.07</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>47.53</v>
+        <v>46.45</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>46.05</v>
+        <v>45.57</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>45.13</v>
+        <v>45.19</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>44.57</v>
+        <v>44.69</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>45.83</v>
+        <v>45.27</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>44.59</v>
+        <v>44.54</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="N48" s="20" t="inlineStr">
+        <v>43.66</v>
+      </c>
+      <c r="N48" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>46</v>
+        <v>45.46</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>45.94</v>
+        <v>45.34</v>
       </c>
       <c r="Q48" s="22" t="n">
         <v>45.68</v>
       </c>
-      <c r="R48" s="25" t="n">
-        <v>-2.1</v>
+      <c r="R48" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>32.66</v>
+        <v>32.74</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>32.07</v>
+        <v>31.85</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>32.14</v>
+        <v>32.08</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>32.3</v>
+        <v>32.26</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.98</v>
+        <v>31.78</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.82</v>
+        <v>31.6</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.66</v>
+        <v>31.3</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.89</v>
+        <v>31.59</v>
       </c>
       <c r="L49" s="19" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="M49" s="19" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O49" s="21" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="P49" s="21" t="n">
         <v>31.62</v>
       </c>
-      <c r="M49" s="19" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O49" s="21" t="n">
-        <v>31.95</v>
-      </c>
-      <c r="P49" s="21" t="n">
-        <v>31.92</v>
-      </c>
       <c r="Q49" s="22" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="R49" s="23" t="n">
-        <v>0.19</v>
+        <v>31.9</v>
+      </c>
+      <c r="R49" s="25" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>13.12</v>
+        <v>12.98</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.86</v>
+        <v>12.71</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.64</v>
+        <v>12.48</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.68</v>
+        <v>12.45</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.82</v>
+        <v>12.63</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.56</v>
+        <v>12.36</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>12.42</v>
+        <v>12.18</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>12.3</v>
+        <v>12.09</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>12.28</v>
+        <v>12.1</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
+        <v>11.83</v>
+      </c>
+      <c r="N50" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12.54</v>
+        <v>12.36</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>12.52</v>
+        <v>12.35</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="R50" s="23" t="n">
-        <v>0.08</v>
+        <v>12.27</v>
+      </c>
+      <c r="R50" s="25" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>61.03</v>
+        <v>60.01</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>59.28</v>
+        <v>58.86</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>57.82</v>
+        <v>57.9</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.32</v>
+        <v>58.43</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>59.13</v>
+        <v>58.87</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>57.38</v>
+        <v>57.72</v>
       </c>
       <c r="I51" s="17" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="J51" s="17" t="n">
         <v>56.57</v>
       </c>
-      <c r="J51" s="17" t="n">
-        <v>55.63</v>
-      </c>
       <c r="K51" s="18" t="n">
-        <v>56.84</v>
+        <v>57.25</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>55.37</v>
+        <v>56.29</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>53.62</v>
+        <v>55.14</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.18</v>
+        <v>57.53</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>56.97</v>
+        <v>57.34</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>23.49</v>
+        <v>23.3</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.83</v>
+        <v>22.84</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.27</v>
+        <v>22.46</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.54</v>
+        <v>22.61</v>
       </c>
       <c r="G52" s="15" t="n">
         <v>22.81</v>
       </c>
       <c r="H52" s="16" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="I52" s="17" t="n">
         <v>22.15</v>
       </c>
-      <c r="I52" s="17" t="n">
-        <v>21.88</v>
-      </c>
       <c r="J52" s="17" t="n">
-        <v>21.49</v>
+        <v>21.89</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.91</v>
+        <v>22.2</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.35</v>
+        <v>21.82</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="N52" s="24" t="inlineStr">
+        <v>21.36</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>22.05</v>
+        <v>22.3</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>21.96</v>
+        <v>22.24</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>22.27</v>
+        <v>22.4</v>
       </c>
       <c r="R52" s="23" t="n">
-        <v>1.64</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
       <c r="E53" s="14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>5.15</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>5.2</v>
-      </c>
       <c r="H53" s="16" t="n">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>5.08</v>
+        <v>5.01</v>
       </c>
       <c r="J53" s="17" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K53" s="18" t="n">
         <v>5.06</v>
       </c>
-      <c r="K53" s="18" t="n">
-        <v>5.12</v>
-      </c>
       <c r="L53" s="19" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="N53" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O53" s="21" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="P53" s="21" t="n">
         <v>5.06</v>
       </c>
-      <c r="M53" s="19" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="N53" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O53" s="21" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="P53" s="21" t="n">
-        <v>5.12</v>
-      </c>
       <c r="Q53" s="22" t="n">
-        <v>5.11</v>
+        <v>5.04</v>
       </c>
       <c r="R53" s="25" t="n">
-        <v>-0.39</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>19.12</v>
+        <v>19.57</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.81</v>
+        <v>18.98</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>18.55</v>
+        <v>18.49</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>18.62</v>
+        <v>18.58</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.78</v>
+        <v>18.89</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>18.47</v>
+        <v>18.3</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>18.31</v>
+        <v>17.99</v>
       </c>
       <c r="J54" s="17" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="K54" s="18" t="n">
         <v>18.16</v>
       </c>
-      <c r="K54" s="18" t="n">
-        <v>18.38</v>
-      </c>
       <c r="L54" s="19" t="n">
-        <v>18.12</v>
+        <v>17.67</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>17.81</v>
+        <v>17.08</v>
       </c>
       <c r="N54" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>18.43</v>
+        <v>18.25</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>18.4</v>
+        <v>18.21</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="R54" s="23" t="n">
-        <v>0.49</v>
+        <v>18.26</v>
+      </c>
+      <c r="R54" s="25" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>97.97</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>96.06999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>94.48</v>
+        <v>93.92</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>94.27</v>
+        <v>94.12</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>95.53</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>93.63</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>92.37</v>
+        <v>92.62</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>91.73</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>93.42</v>
+        <v>93.08</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>91.83</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>89.93000000000001</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="N55" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>93.59999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>93.56999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>93</v>
-      </c>
-      <c r="R55" s="25" t="n">
-        <v>-0.85</v>
+        <v>93.3</v>
+      </c>
+      <c r="R55" s="23" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.24</v>
+        <v>17.59</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.06</v>
+        <v>17.29</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>16.91</v>
+        <v>17.03</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>17</v>
+        <v>17.12</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>17.07</v>
+        <v>17.26</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.89</v>
+        <v>16.96</v>
       </c>
       <c r="I56" s="17" t="n">
         <v>16.82</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>16.71</v>
+        <v>16.66</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>16.81</v>
+        <v>16.87</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>16.66</v>
+        <v>16.61</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>16.48</v>
+        <v>16.31</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.86</v>
+        <v>16.92</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.82</v>
+        <v>16.89</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="R56" s="25" t="n">
-        <v>-0.06</v>
+        <v>16.98</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>22.27</v>
+        <v>21.78</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>21.82</v>
+        <v>21.36</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>21.44</v>
+        <v>21.01</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>21.4</v>
+        <v>20.96</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>21.7</v>
+        <v>21.24</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>21.25</v>
+        <v>20.82</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.95</v>
+        <v>20.54</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>21.19</v>
+        <v>20.77</v>
       </c>
       <c r="L57" s="19" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O57" s="21" t="n">
         <v>20.81</v>
       </c>
-      <c r="M57" s="19" t="n">
-        <v>20.36</v>
-      </c>
-      <c r="N57" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="21" t="n">
-        <v>21.24</v>
-      </c>
       <c r="P57" s="21" t="n">
-        <v>21.22</v>
+        <v>20.81</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>21.11</v>
+        <v>20.68</v>
       </c>
       <c r="R57" s="25" t="n">
-        <v>-2.22</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="58">
@@ -4168,48 +4168,48 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>23.03</v>
+        <v>22.91</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.81</v>
+        <v>22.74</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.62</v>
+        <v>22.59</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.67</v>
+        <v>22.64</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.78</v>
+        <v>22.72</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.56</v>
+        <v>22.55</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>22.45</v>
+        <v>22.47</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="K58" s="18" t="n">
         <v>22.5</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>22.31</v>
+        <v>22.35</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>22.09</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
+        <v>22.18</v>
+      </c>
+      <c r="N58" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>22.52</v>
+        <v>22.51</v>
       </c>
       <c r="Q58" s="22" t="n">
         <v>22.56</v>
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.28</v>
+        <v>28.34</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>28.06</v>
+        <v>28.08</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.87</v>
+        <v>27.86</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.89</v>
+        <v>27.83</v>
       </c>
       <c r="G59" s="15" t="n">
         <v>28.01</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.79</v>
+        <v>27.75</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.67</v>
+        <v>27.57</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.57</v>
+        <v>27.49</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.75</v>
+        <v>27.72</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.56</v>
+        <v>27.5</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="N59" s="20" t="inlineStr">
+        <v>27.24</v>
+      </c>
+      <c r="N59" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.78</v>
+        <v>27.74</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.77</v>
+        <v>27.74</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.76</v>
+        <v>27.66</v>
       </c>
       <c r="R59" s="25" t="n">
-        <v>-0.43</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.72</v>
+        <v>46.65</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.36</v>
+        <v>45.83</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.06</v>
+        <v>45.14</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.25</v>
+        <v>45.37</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45.37</v>
+        <v>45.75</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>45.01</v>
+        <v>44.93</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>44.89</v>
+        <v>44.55</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>44.65</v>
+        <v>44.11</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>44.86</v>
+        <v>44.68</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>44.56</v>
+        <v>43.99</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.2</v>
+        <v>43.17</v>
       </c>
       <c r="N60" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>44.95</v>
+        <v>44.84</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>44.89</v>
+        <v>44.74</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="R60" s="23" t="n">
-        <v>0.49</v>
+        <v>44.98</v>
+      </c>
+      <c r="R60" s="25" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>19.33</v>
+        <v>19.41</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>19.15</v>
+        <v>19.09</v>
       </c>
       <c r="E61" s="14" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G61" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="F61" s="15" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="G61" s="15" t="n">
-        <v>19.1</v>
-      </c>
       <c r="H61" s="16" t="n">
-        <v>18.92</v>
+        <v>18.68</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>18.8</v>
+        <v>18.46</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>18.74</v>
+        <v>18.36</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18.9</v>
+        <v>18.64</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>18.75</v>
+        <v>18.37</v>
       </c>
       <c r="M61" s="19" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="N61" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O61" s="21" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="P61" s="21" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="Q61" s="22" t="n">
         <v>18.57</v>
       </c>
-      <c r="N61" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O61" s="21" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="P61" s="21" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="Q61" s="22" t="n">
-        <v>18.86</v>
-      </c>
       <c r="R61" s="25" t="n">
-        <v>-0.32</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.4</v>
+        <v>15.44</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.21</v>
+        <v>15.23</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>15.05</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.06</v>
+        <v>15.03</v>
       </c>
       <c r="G62" s="15" t="n">
         <v>15.17</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.98</v>
+        <v>14.96</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.87</v>
+        <v>14.82</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.79</v>
+        <v>14.75</v>
       </c>
       <c r="K62" s="18" t="n">
         <v>14.94</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
+        <v>14.55</v>
+      </c>
+      <c r="N62" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.97</v>
+        <v>14.96</v>
       </c>
       <c r="P62" s="21" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.95</v>
+        <v>14.89</v>
       </c>
       <c r="R62" s="25" t="n">
-        <v>-0.93</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>25.33</v>
+        <v>24.92</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.9</v>
+        <v>24.51</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>24.54</v>
+        <v>24.17</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>24.53</v>
+        <v>24.23</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.79</v>
+        <v>24.45</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>24.36</v>
+        <v>24.04</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>24.1</v>
+        <v>23.82</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.93</v>
+        <v>23.63</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>24.29</v>
+        <v>23.94</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.93</v>
+        <v>23.6</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N63" s="20" t="inlineStr">
+        <v>23.19</v>
+      </c>
+      <c r="N63" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>24.35</v>
+        <v>24.01</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>24.33</v>
+        <v>23.97</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>24.26</v>
+        <v>24.01</v>
       </c>
       <c r="R63" s="25" t="n">
-        <v>-1.3</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.12</v>
+        <v>7.13</v>
       </c>
       <c r="F64" s="15" t="n">
-        <v>7.15</v>
+        <v>7.11</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>7.18</v>
+        <v>7.19</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="J64" s="17" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="K64" s="18" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="Q64" s="22" t="n">
         <v>7.04</v>
       </c>
-      <c r="K64" s="18" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="P64" s="21" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="Q64" s="22" t="n">
-        <v>7.12</v>
-      </c>
       <c r="R64" s="25" t="n">
-        <v>-0.14</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="65">
@@ -4602,54 +4602,54 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E65" s="14" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>4.9</v>
       </c>
-      <c r="D65" s="13" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E65" s="14" t="n">
+      <c r="H65" s="16" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I65" s="17" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J65" s="17" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K65" s="18" t="n">
         <v>4.81</v>
-      </c>
-      <c r="F65" s="15" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="G65" s="15" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="H65" s="16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I65" s="17" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="J65" s="17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K65" s="18" t="n">
-        <v>4.78</v>
       </c>
       <c r="L65" s="19" t="n">
         <v>4.74</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="N65" s="24" t="inlineStr">
+        <v>4.66</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="R65" s="23" t="n">
-        <v>0.42</v>
+        <v>4.8</v>
+      </c>
+      <c r="R65" s="25" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>5.05</v>
+        <v>4.82</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.72</v>
+        <v>4.64</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.82</v>
+        <v>4.73</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>4.46</v>
+        <v>4.53</v>
       </c>
       <c r="K66" s="18" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="P66" s="21" t="n">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="R66" s="25" t="n">
-        <v>-3.38</v>
+        <v>4.66</v>
+      </c>
+      <c r="R66" s="23" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>68.41</v>
+        <v>67.2</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>66.61</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>65.09999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>66.3</v>
+        <v>65.95</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>64.5</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>62.7</v>
+        <v>63.35</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>64.09999999999999</v>
+        <v>64.09</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>62.59</v>
+        <v>63</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>60.79</v>
+        <v>61.7</v>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>64.37</v>
+        <v>64.42</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>64.23999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="R67" s="25" t="n">
-        <v>-1.08</v>
+        <v>65.05</v>
+      </c>
+      <c r="R67" s="23" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>70.66</v>
+        <v>68.2</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>68.70999999999999</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>67.06999999999999</v>
+        <v>66.27</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>66.98</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>68.22</v>
+        <v>67.2</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>66.27</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>65.03</v>
+        <v>65.8</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>64.31999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>65.98</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>64.34</v>
+        <v>64.8</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>62.39</v>
+        <v>63.75</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>66.2</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>66.13</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="R68" s="25" t="n">
-        <v>-1.57</v>
+        <v>66.5</v>
+      </c>
+      <c r="R68" s="23" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>82.92</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>81.27</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>79.89</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>80.7</v>
+        <v>80.78</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>81.3</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>79.65000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>79.05</v>
+        <v>79.03</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>78</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>78.95999999999999</v>
+        <v>79.23</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>77.58</v>
+        <v>77.77</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>75.93000000000001</v>
+        <v>76.02</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="P69" s="21" t="n">
         <v>79.37</v>
       </c>
-      <c r="P69" s="21" t="n">
-        <v>79.09</v>
-      </c>
       <c r="Q69" s="22" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="R69" s="23" t="n">
-        <v>0.12</v>
+        <v>80</v>
+      </c>
+      <c r="R69" s="25" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>121.52</v>
+        <v>130.48</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>117.92</v>
+        <v>123.88</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>114.91</v>
+        <v>118.35</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>116.3</v>
+        <v>121.93</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>117.8</v>
+        <v>124.17</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>114.2</v>
+        <v>117.57</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>112.7</v>
+        <v>115.33</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>110.6</v>
+        <v>110.97</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>112.89</v>
+        <v>114.65</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>109.88</v>
+        <v>109.12</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>106.28</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
+        <v>102.52</v>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>113.69</v>
+        <v>116.37</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>113.17</v>
+        <v>115.17</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>114.8</v>
+        <v>119.7</v>
       </c>
       <c r="R70" s="23" t="n">
-        <v>2.04</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.83</v>
+        <v>23.84</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.55</v>
+        <v>23.45</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>23.32</v>
+        <v>23.12</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>23.29</v>
+        <v>23.09</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>23.47</v>
+        <v>23.35</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>23.19</v>
+        <v>22.96</v>
       </c>
       <c r="I71" s="17" t="n">
-        <v>23.01</v>
+        <v>22.7</v>
       </c>
       <c r="J71" s="17" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="K71" s="18" t="n">
         <v>22.91</v>
       </c>
-      <c r="K71" s="18" t="n">
-        <v>23.16</v>
-      </c>
       <c r="L71" s="19" t="n">
-        <v>22.93</v>
+        <v>22.58</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
+        <v>22.19</v>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>23.19</v>
+        <v>22.95</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>23.18</v>
+        <v>22.94</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>23.1</v>
+        <v>22.84</v>
       </c>
       <c r="R71" s="25" t="n">
-        <v>-0.77</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>18.8</v>
+        <v>21.15</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.15</v>
+        <v>19.6</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>17.61</v>
+        <v>18.3</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>17.53</v>
+        <v>18.48</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>17.97</v>
+        <v>19.33</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.32</v>
+        <v>17.78</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>16.88</v>
+        <v>16.93</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>16.67</v>
+        <v>16.23</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.24</v>
+        <v>17.43</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>16.7</v>
+        <v>16.13</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>16.05</v>
+        <v>14.58</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.31</v>
+        <v>17.67</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.29</v>
+        <v>17.55</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="R72" s="25" t="n">
-        <v>-2.56</v>
+        <v>17.62</v>
+      </c>
+      <c r="R72" s="23" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>233.27</v>
+        <v>240.64</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>231.87</v>
+        <v>235.24</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>230.69</v>
+        <v>230.71</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>231.2</v>
+        <v>231.1</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>231.8</v>
+        <v>234.2</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>230.4</v>
+        <v>228.8</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>229.8</v>
+        <v>225.7</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>229</v>
+        <v>223.4</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>229.91</v>
+        <v>227.69</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>228.73</v>
+        <v>223.16</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>227.33</v>
+        <v>217.76</v>
       </c>
       <c r="N73" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>230.21</v>
+        <v>228.45</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>230.02</v>
+        <v>228.11</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="R73" s="23" t="n">
-        <v>0.13</v>
+        <v>228</v>
+      </c>
+      <c r="R73" s="25" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.98</v>
+        <v>15.91</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.65</v>
+        <v>15.63</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.38</v>
+        <v>15.4</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.52</v>
+        <v>15.55</v>
       </c>
       <c r="G74" s="15" t="n">
         <v>15.65</v>
       </c>
       <c r="H74" s="16" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="I74" s="17" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="J74" s="17" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="K74" s="18" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="M74" s="19" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="N74" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O74" s="21" t="n">
         <v>15.32</v>
       </c>
-      <c r="I74" s="17" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="J74" s="17" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="K74" s="18" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="L74" s="19" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="N74" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O74" s="21" t="n">
-        <v>15.27</v>
-      </c>
       <c r="P74" s="21" t="n">
-        <v>15.22</v>
+        <v>15.26</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.39</v>
+        <v>15.46</v>
       </c>
       <c r="R74" s="23" t="n">
-        <v>1.58</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>37.32</v>
+        <v>36.33</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>36.18</v>
+        <v>35.67</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>35.23</v>
+        <v>35.11</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>35.21</v>
+        <v>35.44</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>35.91</v>
+        <v>35.68</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>34.77</v>
+        <v>35.02</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>34.07</v>
+        <v>34.78</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>33.63</v>
+        <v>34.36</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>34.59</v>
+        <v>34.75</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>33.64</v>
+        <v>34.19</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="N75" s="24" t="inlineStr">
+        <v>33.53</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>34.73</v>
+        <v>34.91</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>34.68</v>
+        <v>34.8</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>34.5</v>
+        <v>35.2</v>
       </c>
       <c r="R75" s="23" t="n">
-        <v>0.47</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>22.49</v>
+        <v>23.17</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>21.99</v>
+        <v>22.44</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>21.57</v>
+        <v>21.83</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>21.59</v>
+        <v>22.17</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>21.88</v>
+        <v>22.44</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>21.38</v>
+        <v>21.71</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>21.09</v>
+        <v>21.44</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>20.88</v>
+        <v>20.98</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>21.29</v>
+        <v>21.42</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>20.87</v>
+        <v>20.81</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>20.37</v>
+        <v>20.08</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>21.36</v>
+        <v>21.6</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>21.33</v>
+        <v>21.48</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="R76" s="25" t="n">
-        <v>-0.37</v>
+        <v>21.89</v>
+      </c>
+      <c r="R76" s="23" t="n">
+        <v>2.82</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>45.69</v>
+        <v>45.18</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>44.29</v>
+        <v>44.14</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>43.11</v>
+        <v>43.27</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>43.27</v>
+        <v>43.51</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>44.05</v>
+        <v>44.03</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.65</v>
+        <v>42.99</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>41.87</v>
+        <v>42.47</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>41.25</v>
+        <v>41.95</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.33</v>
+        <v>42.69</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>41.15</v>
+        <v>41.82</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.75</v>
+        <v>40.78</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.54</v>
+        <v>42.88</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.44</v>
+        <v>42.77</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="R77" s="25" t="n">
-        <v>-0.47</v>
+        <v>43</v>
+      </c>
+      <c r="R77" s="23" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="F78" s="15" t="n">
         <v>5.43</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="I78" s="17" t="n">
         <v>5.35</v>
       </c>
       <c r="J78" s="17" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L78" s="19" t="n">
         <v>5.3</v>
       </c>
-      <c r="K78" s="18" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.29</v>
-      </c>
       <c r="M78" s="19" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="P78" s="21" t="n">
         <v>5.37</v>
-      </c>
-      <c r="P78" s="21" t="n">
-        <v>5.36</v>
       </c>
       <c r="Q78" s="22" t="n">
         <v>5.39</v>
       </c>
-      <c r="R78" s="25" t="n">
-        <v>-0.19</v>
+      <c r="R78" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>18.53</v>
+        <v>19.42</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.35</v>
+        <v>18.91</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.2</v>
+        <v>18.48</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.24</v>
+        <v>18.76</v>
       </c>
       <c r="G79" s="15" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="H79" s="16" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="J79" s="17" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="K79" s="18" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="n">
         <v>18.33</v>
       </c>
-      <c r="H79" s="16" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="I79" s="17" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="J79" s="17" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="K79" s="18" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O79" s="21" t="n">
-        <v>18.13</v>
-      </c>
       <c r="P79" s="21" t="n">
-        <v>18.11</v>
+        <v>18.23</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="R79" s="25" t="n">
-        <v>-0.49</v>
+        <v>18.59</v>
+      </c>
+      <c r="R79" s="23" t="n">
+        <v>2.42</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>80.72</v>
+        <v>81.7</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>79.31999999999999</v>
+        <v>80.25</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>78.14</v>
+        <v>79.03</v>
       </c>
       <c r="F80" s="15" t="n">
+        <v>79.83</v>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="H80" s="16" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="I80" s="17" t="n">
         <v>78.38</v>
       </c>
-      <c r="G80" s="15" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="H80" s="16" t="n">
-        <v>77.72</v>
-      </c>
-      <c r="I80" s="17" t="n">
-        <v>76.98</v>
-      </c>
       <c r="J80" s="17" t="n">
-        <v>76.31999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>77.36</v>
+        <v>78.22</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>76.18000000000001</v>
+        <v>77</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>74.78</v>
+        <v>75.55</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>77.59</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>77.47</v>
+        <v>78.33</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>77.65000000000001</v>
-      </c>
-      <c r="R80" s="25" t="n">
-        <v>-0.64</v>
+        <v>79.34999999999999</v>
+      </c>
+      <c r="R80" s="23" t="n">
+        <v>2.19</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.57</v>
+        <v>4.86</v>
       </c>
       <c r="D81" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H81" s="16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I81" s="17" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K81" s="18" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="L81" s="19" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M81" s="19" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N81" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="n">
         <v>4.52</v>
       </c>
-      <c r="E81" s="14" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="F81" s="15" t="n">
+      <c r="P81" s="21" t="n">
         <v>4.49</v>
       </c>
-      <c r="G81" s="15" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="H81" s="16" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="I81" s="17" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="J81" s="17" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="K81" s="18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="L81" s="19" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="M81" s="19" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O81" s="21" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="P81" s="21" t="n">
-        <v>4.45</v>
-      </c>
       <c r="Q81" s="22" t="n">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="R81" s="23" t="n">
-        <v>0.45</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>58.49</v>
+        <v>59.32</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>57.54</v>
+        <v>58.07</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>56.74</v>
+        <v>57.02</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>56.83</v>
+        <v>57.42</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>57.37</v>
+        <v>57.98</v>
       </c>
       <c r="H82" s="16" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="J82" s="17" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="K82" s="18" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="L82" s="19" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="M82" s="19" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="N82" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O82" s="21" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="P82" s="21" t="n">
         <v>56.42</v>
       </c>
-      <c r="I82" s="17" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="J82" s="17" t="n">
-        <v>55.47</v>
-      </c>
-      <c r="K82" s="18" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="L82" s="19" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="M82" s="19" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="N82" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O82" s="21" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="P82" s="21" t="n">
-        <v>56.28</v>
-      </c>
       <c r="Q82" s="22" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="R82" s="25" t="n">
-        <v>-0.53</v>
+        <v>56.85</v>
+      </c>
+      <c r="R82" s="23" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="83">
@@ -5718,54 +5718,54 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>38.31</v>
+        <v>38.67</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.97</v>
+        <v>38.13</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.69</v>
+        <v>37.68</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.71</v>
+        <v>37.62</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.91</v>
+        <v>37.98</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>37.57</v>
+        <v>37.44</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>37.37</v>
+        <v>37.08</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>37.23</v>
+        <v>36.9</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>37.49</v>
+        <v>37.38</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>37.21</v>
+        <v>36.93</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.87</v>
-      </c>
-      <c r="N83" s="20" t="inlineStr">
+        <v>36.39</v>
+      </c>
+      <c r="N83" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>37.54</v>
+        <v>37.43</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>37.52</v>
+        <v>37.42</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>37.52</v>
+        <v>37.26</v>
       </c>
       <c r="R83" s="25" t="n">
-        <v>-0.58</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>92.39</v>
+        <v>96.72</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>91.59</v>
+        <v>94.42</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>90.92</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>91.2</v>
+        <v>92.23</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>91.55</v>
+        <v>93.77</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>90.75</v>
+        <v>91.47</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>90.40000000000001</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>89.95</v>
+        <v>89.17</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>90.48</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>89.81</v>
+        <v>89.28</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>89.01000000000001</v>
+        <v>86.98</v>
       </c>
       <c r="N84" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>90.64</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>90.54000000000001</v>
+        <v>91.39</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>90.84999999999999</v>
-      </c>
-      <c r="R84" s="23" t="n">
-        <v>0.61</v>
+        <v>90.7</v>
+      </c>
+      <c r="R84" s="25" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>16.54</v>
+        <v>17.33</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.3</v>
+        <v>16.78</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.1</v>
+        <v>16.32</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.08</v>
+        <v>16.62</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.23</v>
+        <v>16.81</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>15.99</v>
+        <v>16.26</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>15.84</v>
+        <v>16.07</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>15.75</v>
+        <v>15.71</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>15.96</v>
+        <v>16.01</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>15.76</v>
+        <v>15.55</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.52</v>
+        <v>15</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>15.99</v>
+        <v>16.16</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>15.98</v>
+        <v>16.05</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="R85" s="25" t="n">
-        <v>-0.62</v>
+        <v>16.44</v>
+      </c>
+      <c r="R85" s="23" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>126.28</v>
+        <v>130.86</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>123.88</v>
+        <v>127.36</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>121.87</v>
+        <v>124.43</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>123.07</v>
+        <v>124.77</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>123.93</v>
+        <v>126.73</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>121.53</v>
+        <v>123.23</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>120.67</v>
+        <v>121.27</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>119.13</v>
+        <v>119.73</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>120.53</v>
+        <v>122.47</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>118.52</v>
+        <v>119.54</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>116.12</v>
-      </c>
-      <c r="N86" s="24" t="inlineStr">
+        <v>116.04</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>121.12</v>
+        <v>122.99</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>120.72</v>
+        <v>122.74</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>122.2</v>
+        <v>122.8</v>
       </c>
       <c r="R86" s="23" t="n">
-        <v>1.16</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>62.36</v>
+        <v>60.44</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>60.41</v>
+        <v>59.24</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>58.77</v>
+        <v>58.24</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>59.25</v>
+        <v>58.9</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>60.2</v>
+        <v>59.3</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>58.25</v>
+        <v>58.1</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>57.3</v>
+        <v>57.7</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>56.3</v>
+        <v>56.9</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>57.68</v>
+        <v>57.56</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>56.04</v>
+        <v>56.56</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>54.09</v>
+        <v>55.36</v>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>58.04</v>
+        <v>57.88</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>57.83</v>
+        <v>57.66</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="88">
@@ -6028,54 +6028,54 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>9.710000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.550000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E88" s="14" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="F88" s="15" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H88" s="16" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="J88" s="17" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K88" s="18" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="L88" s="19" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M88" s="19" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O88" s="21" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="P88" s="21" t="n">
         <v>9.41</v>
       </c>
-      <c r="F88" s="15" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="G88" s="15" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="H88" s="16" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="I88" s="17" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J88" s="17" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="K88" s="18" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="L88" s="19" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="M88" s="19" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="N88" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O88" s="21" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="P88" s="21" t="n">
-        <v>9.34</v>
-      </c>
       <c r="Q88" s="22" t="n">
-        <v>9.380000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>0.86</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>17.38</v>
+        <v>16.91</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.79</v>
+        <v>16.47</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="F89" s="15" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="G89" s="15" t="n">
         <v>16.41</v>
       </c>
-      <c r="G89" s="15" t="n">
-        <v>16.71</v>
-      </c>
       <c r="H89" s="16" t="n">
-        <v>16.12</v>
+        <v>15.97</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.82</v>
+        <v>15.75</v>
       </c>
       <c r="J89" s="17" t="n">
         <v>15.53</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>15.97</v>
+        <v>15.86</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15.48</v>
+        <v>15.49</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="N89" s="20" t="inlineStr">
+        <v>15.05</v>
+      </c>
+      <c r="N89" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>16.07</v>
+        <v>15.93</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>16.02</v>
+        <v>15.89</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>16.1</v>
+        <v>15.96</v>
       </c>
       <c r="R89" s="25" t="n">
-        <v>-1.53</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>17.51</v>
+        <v>17.86</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.27</v>
+        <v>17.48</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>17.07</v>
+        <v>17.17</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>17.07</v>
+        <v>17.25</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>17.22</v>
+        <v>17.44</v>
       </c>
       <c r="H90" s="16" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="J90" s="17" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="K90" s="18" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="L90" s="19" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="M90" s="19" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O90" s="21" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="P90" s="21" t="n">
         <v>16.98</v>
       </c>
-      <c r="I90" s="17" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="J90" s="17" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="K90" s="18" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="L90" s="19" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="M90" s="19" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O90" s="21" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="P90" s="21" t="n">
-        <v>16.95</v>
-      </c>
       <c r="Q90" s="22" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="R90" s="25" t="n">
-        <v>-0.41</v>
+        <v>17.06</v>
+      </c>
+      <c r="R90" s="23" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.74</v>
+        <v>31.22</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>30.2</v>
+        <v>30.08</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>30.19</v>
+        <v>30.23</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.71</v>
+        <v>30.53</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.87</v>
+        <v>29.91</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.35</v>
+        <v>29.61</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>29.03</v>
+        <v>29.29</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.72</v>
+        <v>29.74</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>29.02</v>
+        <v>29.22</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>28.18</v>
+        <v>28.6</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.83</v>
+        <v>29.85</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.79</v>
+        <v>29.78</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="R91" s="25" t="n">
-        <v>-1.26</v>
+        <v>29.92</v>
+      </c>
+      <c r="R91" s="23" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.45</v>
+        <v>20.62</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>20.17</v>
+        <v>20.22</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.94</v>
+        <v>19.88</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.97</v>
+        <v>19.86</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>20.13</v>
+        <v>20.12</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.85</v>
+        <v>19.72</v>
       </c>
       <c r="I92" s="17" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="J92" s="17" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="K92" s="18" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="N92" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O92" s="21" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P92" s="21" t="n">
         <v>19.69</v>
       </c>
-      <c r="J92" s="17" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="K92" s="18" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="L92" s="19" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="M92" s="19" t="n">
-        <v>19.27</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O92" s="21" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="P92" s="21" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Q92" s="22" t="n">
-        <v>19.82</v>
+        <v>19.61</v>
       </c>
       <c r="R92" s="25" t="n">
-        <v>-0.4</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>27.27</v>
+        <v>26.4</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.71</v>
+        <v>26.14</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>26.24</v>
+        <v>25.92</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>26.19</v>
+        <v>25.93</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.55</v>
+        <v>26.09</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.99</v>
+        <v>25.83</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.63</v>
+        <v>25.67</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.43</v>
+        <v>25.57</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.92</v>
+        <v>25.78</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.45</v>
+        <v>25.56</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="N93" s="20" t="inlineStr">
+        <v>25.3</v>
+      </c>
+      <c r="N93" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.98</v>
+        <v>25.81</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.97</v>
+        <v>25.8</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.82</v>
+        <v>25.78</v>
       </c>
       <c r="R93" s="25" t="n">
-        <v>-1.38</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>177.92</v>
+        <v>176.47</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>174.82</v>
+        <v>173.77</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>172.22</v>
+        <v>171.51</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>171.87</v>
+        <v>173</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>173.93</v>
+        <v>173.9</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>170.83</v>
+        <v>171.2</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>168.77</v>
+        <v>170.3</v>
       </c>
       <c r="J94" s="17" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="K94" s="18" t="n">
+        <v>169.99</v>
+      </c>
+      <c r="L94" s="19" t="n">
         <v>167.73</v>
       </c>
-      <c r="K94" s="18" t="n">
-        <v>170.48</v>
-      </c>
-      <c r="L94" s="19" t="n">
-        <v>167.88</v>
-      </c>
       <c r="M94" s="19" t="n">
-        <v>164.78</v>
+        <v>165.03</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>170.78</v>
+        <v>170.7</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>170.72</v>
+        <v>170.2</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>169.8</v>
-      </c>
-      <c r="R94" s="25" t="n">
-        <v>-0.7</v>
+        <v>172.1</v>
+      </c>
+      <c r="R94" s="23" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>13.2</v>
+        <v>14.29</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>13.02</v>
+        <v>13.65</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>12.87</v>
+        <v>13.11</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>12.95</v>
+        <v>13.36</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>13.02</v>
+        <v>13.63</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>12.84</v>
+        <v>12.99</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>12.77</v>
+        <v>12.72</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>12.66</v>
+        <v>12.35</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>12.77</v>
+        <v>12.75</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>12.62</v>
+        <v>12.21</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>12.44</v>
+        <v>11.57</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>12.81</v>
+        <v>12.89</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>12.78</v>
+        <v>12.8</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>12.88</v>
+        <v>13.1</v>
       </c>
       <c r="R95" s="23" t="n">
-        <v>0.31</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>20.66</v>
+        <v>20.28</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>20.03</v>
+        <v>19.8</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>19.5</v>
+        <v>19.39</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.75</v>
+        <v>19.34</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>20.01</v>
+        <v>19.66</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>19.38</v>
+        <v>19.18</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>19.12</v>
+        <v>18.86</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.75</v>
+        <v>18.7</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>19.15</v>
+        <v>19.13</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.62</v>
+        <v>18.72</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="N96" s="20" t="inlineStr">
+        <v>18.24</v>
+      </c>
+      <c r="N96" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>19.29</v>
+        <v>19.17</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>19.2</v>
+        <v>19.16</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>19.49</v>
+        <v>19.02</v>
       </c>
       <c r="R96" s="25" t="n">
-        <v>-0.2</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>15.93</v>
+        <v>16.17</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>15.74</v>
+        <v>15.91</v>
       </c>
       <c r="E97" s="14" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="F97" s="15" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="I97" s="17" t="n">
         <v>15.58</v>
       </c>
-      <c r="F97" s="15" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="G97" s="15" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="H97" s="16" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="I97" s="17" t="n">
-        <v>15.41</v>
-      </c>
       <c r="J97" s="17" t="n">
-        <v>15.32</v>
+        <v>15.4</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>15.47</v>
+        <v>15.55</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>15.31</v>
+        <v>15.33</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.12</v>
+        <v>15.07</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.49</v>
+        <v>15.57</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="R97" s="25" t="n">
-        <v>-0.32</v>
+        <v>15.75</v>
+      </c>
+      <c r="R97" s="23" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>10.09</v>
+        <v>9.6</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.74</v>
+        <v>9.44</v>
       </c>
       <c r="E98" s="14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="G98" s="15" t="n">
         <v>9.44</v>
       </c>
-      <c r="F98" s="15" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="G98" s="15" t="n">
-        <v>9.67</v>
-      </c>
       <c r="H98" s="16" t="n">
-        <v>9.32</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>8.970000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K98" s="18" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="L98" s="19" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M98" s="19" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="N98" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O98" s="21" t="n">
         <v>9.25</v>
       </c>
-      <c r="L98" s="19" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="M98" s="19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O98" s="21" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="P98" s="21" t="n">
-        <v>9.27</v>
+        <v>9.23</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="R98" s="25" t="n">
-        <v>-0.32</v>
+        <v>9.31</v>
+      </c>
+      <c r="R98" s="23" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>26.84</v>
+        <v>26.69</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>26.06</v>
+        <v>25.94</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>25.41</v>
+        <v>25.31</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>25.51</v>
+        <v>25.68</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.93</v>
+        <v>25.95</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>25.15</v>
+        <v>25.2</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.73</v>
+        <v>24.93</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.37</v>
+        <v>24.45</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.97</v>
+        <v>24.89</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>24.32</v>
+        <v>24.27</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>23.54</v>
+        <v>23.52</v>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>25.09</v>
+        <v>25.08</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>25.03</v>
+        <v>24.95</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>25.08</v>
-      </c>
-      <c r="R99" s="25" t="n">
-        <v>-4.13</v>
+        <v>25.4</v>
+      </c>
+      <c r="R99" s="23" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="D100" s="13" t="n">
         <v>16.36</v>
       </c>
-      <c r="D100" s="13" t="n">
-        <v>16.18</v>
-      </c>
       <c r="E100" s="14" t="n">
-        <v>16.03</v>
+        <v>16.14</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>16.12</v>
+        <v>16.24</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.19</v>
+        <v>16.35</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>16.01</v>
+        <v>16.09</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>15.94</v>
+        <v>15.98</v>
       </c>
       <c r="J100" s="17" t="n">
         <v>15.83</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>15.93</v>
+        <v>16</v>
       </c>
       <c r="L100" s="19" t="n">
         <v>15.78</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="N100" s="24" t="inlineStr">
+        <v>15.52</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>15.98</v>
+        <v>16.05</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>15.94</v>
+        <v>16.02</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.06</v>
+        <v>16.13</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>31.32</v>
+        <v>31.18</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.64</v>
+        <v>30.56</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>30.07</v>
+        <v>30.04</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>30.42</v>
+        <v>30.27</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.66</v>
+        <v>30.53</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.98</v>
+        <v>29.91</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>29.74</v>
+        <v>29.65</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.69</v>
+        <v>29.7</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>29.12</v>
+        <v>29.18</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>28.44</v>
+        <v>28.56</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.86</v>
+        <v>29.83</v>
       </c>
       <c r="P101" s="21" t="n">
         <v>29.74</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="R101" s="23" t="n">
-        <v>0.47</v>
+        <v>30</v>
+      </c>
+      <c r="R101" s="25" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>16.25</v>
+        <v>15.64</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>15.53</v>
+        <v>15.13</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.93</v>
+        <v>14.7</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.94</v>
+        <v>14.64</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>15.38</v>
+        <v>14.98</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.66</v>
+        <v>14.47</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.22</v>
+        <v>14.13</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.53</v>
+        <v>14.41</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.93</v>
+        <v>13.98</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
+        <v>13.47</v>
+      </c>
+      <c r="N102" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.62</v>
+        <v>14.46</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.58</v>
+        <v>14.45</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>14.51</v>
+        <v>14.3</v>
       </c>
       <c r="R102" s="25" t="n">
-        <v>-0.68</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>70.63</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>69.28</v>
+        <v>68.86</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>68.15000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>68.09999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>68.95</v>
+        <v>68.92</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>67.59999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>66.75</v>
+        <v>67.38</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>66.25</v>
+        <v>66.62</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>67.40000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>66.27</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>64.92</v>
+        <v>65.14</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
         <v>67.55</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>67.5</v>
+        <v>67.34</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="R103" s="25" t="n">
-        <v>-0.74</v>
+        <v>68.15000000000001</v>
+      </c>
+      <c r="R103" s="23" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.37</v>
+        <v>14.36</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.22</v>
+        <v>14.24</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>14.25</v>
+        <v>14.23</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="H104" s="16" t="n">
         <v>14.17</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>13.99</v>
+        <v>14.02</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>14.12</v>
+        <v>14.15</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>13.97</v>
+        <v>14.03</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
+        <v>13.88</v>
+      </c>
+      <c r="N104" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>14.15</v>
+        <v>14.17</v>
       </c>
       <c r="P104" s="21" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="Q104" s="22" t="n">
         <v>14.13</v>
       </c>
-      <c r="Q104" s="22" t="n">
-        <v>14.16</v>
-      </c>
       <c r="R104" s="25" t="n">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>18.53</v>
+        <v>19.23</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>17.14</v>
+        <v>18.15</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>15.97</v>
+        <v>17.24</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>16.74</v>
+        <v>17.19</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>17.21</v>
+        <v>17.88</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>15.82</v>
+        <v>16.8</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>15.35</v>
+        <v>16.11</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>14.43</v>
+        <v>15.72</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>15.2</v>
+        <v>16.64</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>14.03</v>
+        <v>15.73</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="N105" s="24" t="inlineStr">
+        <v>14.65</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>15.56</v>
+        <v>16.76</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>15.3</v>
+        <v>16.72</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>16.28</v>
+        <v>16.51</v>
       </c>
       <c r="R105" s="23" t="n">
-        <v>10</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="106">
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="D106" s="13" t="n">
         <v>2.47</v>
@@ -7153,10 +7153,10 @@
         <v>2.44</v>
       </c>
       <c r="F106" s="15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G106" s="15" t="n">
         <v>2.46</v>
-      </c>
-      <c r="G106" s="15" t="n">
-        <v>2.47</v>
       </c>
       <c r="H106" s="16" t="n">
         <v>2.43</v>
@@ -7165,30 +7165,30 @@
         <v>2.42</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="N106" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
         <v>2.43</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R106" s="25" t="n">
         <v>-0.41</v>
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>40.6</v>
+        <v>39.01</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>39.18</v>
+        <v>38.21</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>37.99</v>
+        <v>37.54</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>38.04</v>
+        <v>37.61</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>38.88</v>
+        <v>38.07</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>37.46</v>
+        <v>37.27</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>36.62</v>
+        <v>36.81</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>36.04</v>
+        <v>36.47</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>37.19</v>
+        <v>37.1</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>36</v>
+        <v>36.43</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
+        <v>35.63</v>
+      </c>
+      <c r="N107" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>37.38</v>
+        <v>37.21</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>37.3</v>
+        <v>37.16</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>37.2</v>
+        <v>37.16</v>
       </c>
       <c r="R107" s="25" t="n">
-        <v>-1.12</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.27</v>
+        <v>7.95</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>8.07</v>
+        <v>7.86</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.91</v>
+        <v>7.78</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.92</v>
+        <v>7.81</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>8.029999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.83</v>
+        <v>7.76</v>
       </c>
       <c r="I108" s="17" t="n">
         <v>7.72</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.63</v>
+        <v>7.67</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.79</v>
+        <v>7.73</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
+        <v>7.56</v>
+      </c>
+      <c r="N108" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="P108" s="21" t="n">
-        <v>7.81</v>
+        <v>7.74</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.8</v>
+        <v>7.77</v>
       </c>
       <c r="R108" s="25" t="n">
-        <v>-1.64</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.29</v>
+        <v>44.31</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>43.99</v>
+        <v>44.01</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.73</v>
+        <v>43.75</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>44</v>
+        <v>43.96</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.7</v>
+        <v>43.66</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>43.4</v>
+        <v>43.36</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>43.57</v>
+        <v>43.59</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>43.31</v>
+        <v>43.33</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>43.01</v>
+        <v>43.03</v>
       </c>
       <c r="N109" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="P109" s="21" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="Q109" s="22" t="n">
         <v>43.64</v>
       </c>
-      <c r="P109" s="21" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="Q109" s="22" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="R109" s="23" t="n">
-        <v>0.46</v>
+      <c r="R109" s="25" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>66.09</v>
+        <v>65.84</v>
       </c>
       <c r="D110" s="13" t="n">
         <v>65.29000000000001</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.62</v>
+        <v>64.83</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G110" s="15" t="n">
         <v>65.2</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.40000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>64</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>63.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>64.18000000000001</v>
+        <v>64.52</v>
       </c>
       <c r="L110" s="19" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="M110" s="19" t="n">
         <v>63.51</v>
       </c>
-      <c r="M110" s="19" t="n">
-        <v>62.71</v>
-      </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>64.31999999999999</v>
+        <v>64.61</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>64.23999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="R110" s="25" t="n">
-        <v>-0.92</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="R110" s="23" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.29</v>
+        <v>10.26</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="E111" s="14" t="n">
         <v>10.09</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>10.07</v>
+        <v>10.14</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>10.15</v>
+        <v>10.17</v>
       </c>
       <c r="H111" s="16" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I111" s="17" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="J111" s="17" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K111" s="18" t="n">
         <v>10.04</v>
       </c>
-      <c r="I111" s="17" t="n">
+      <c r="L111" s="19" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="J111" s="17" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="K111" s="18" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="L111" s="19" t="n">
-        <v>9.93</v>
-      </c>
       <c r="M111" s="19" t="n">
-        <v>9.82</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.03</v>
+        <v>10.06</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.03</v>
+        <v>10.05</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="R111" s="25" t="n">
-        <v>-0.6</v>
+        <v>10.11</v>
+      </c>
+      <c r="R111" s="23" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>322.04</v>
+        <v>321.42</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>313.24</v>
+        <v>313.62</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>305.86</v>
+        <v>307.08</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>306.87</v>
+        <v>309</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>311.73</v>
+        <v>312.8</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>302.93</v>
+        <v>305</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>298.07</v>
+        <v>301.2</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>294.13</v>
+        <v>297.2</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>300.94</v>
+        <v>302.72</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>293.56</v>
+        <v>296.18</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>284.76</v>
+        <v>288.38</v>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>302.28</v>
+        <v>304.16</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>301.62</v>
+        <v>303.32</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>302</v>
-      </c>
-      <c r="R112" s="25" t="n">
-        <v>-1.82</v>
+        <v>305.2</v>
+      </c>
+      <c r="R112" s="23" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>226.13</v>
+        <v>233.09</v>
       </c>
       <c r="D113" s="13" t="n">
+        <v>228.09</v>
+      </c>
+      <c r="E113" s="14" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>226.67</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>228.33</v>
+      </c>
+      <c r="H113" s="16" t="n">
         <v>223.33</v>
       </c>
-      <c r="E113" s="14" t="n">
-        <v>220.98</v>
-      </c>
-      <c r="F113" s="15" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>223.4</v>
-      </c>
-      <c r="H113" s="16" t="n">
-        <v>220.6</v>
-      </c>
       <c r="I113" s="17" t="n">
-        <v>219.6</v>
+        <v>221.67</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>217.8</v>
+        <v>218.33</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>219.42</v>
+        <v>221.1</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>217.07</v>
+        <v>216.91</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>214.27</v>
-      </c>
-      <c r="N113" s="24" t="inlineStr">
+        <v>211.91</v>
+      </c>
+      <c r="N113" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>220.12</v>
+        <v>222.41</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>219.63</v>
+        <v>221.49</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>221.4</v>
+        <v>225</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>0.68</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>636.0599999999999</v>
+        <v>632.02</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>627.0599999999999</v>
+        <v>625.52</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>619.52</v>
+        <v>620.0700000000001</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>621.5</v>
+        <v>621.67</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>626</v>
+        <v>624.83</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>617</v>
+        <v>618.33</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>612.5</v>
+        <v>615.17</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>608</v>
+        <v>611.83</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>614.48</v>
+        <v>616.4299999999999</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>606.9400000000001</v>
+        <v>610.98</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>597.9400000000001</v>
-      </c>
-      <c r="N114" s="24" t="inlineStr">
+        <v>604.48</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>616.09</v>
+        <v>617.64</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>615.1799999999999</v>
+        <v>616.9400000000001</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>617</v>
+        <v>618.5</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.48</v>
+        <v>6.75</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.34</v>
+        <v>6.45</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>6.22</v>
+        <v>6.19</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>6.26</v>
+        <v>6.16</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>6.19</v>
+        <v>6.06</v>
       </c>
       <c r="I115" s="17" t="n">
-        <v>6.12</v>
+        <v>5.86</v>
       </c>
       <c r="J115" s="17" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K115" s="18" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L115" s="19" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M115" s="19" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N115" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O115" s="21" t="n">
         <v>6.05</v>
       </c>
-      <c r="K115" s="18" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="L115" s="19" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="M115" s="19" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="N115" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O115" s="21" t="n">
-        <v>6.17</v>
-      </c>
       <c r="P115" s="21" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R115" s="23" t="n">
-        <v>0.49</v>
+        <v>5.96</v>
+      </c>
+      <c r="R115" s="25" t="n">
+        <v>-3.87</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>99.25</v>
+        <v>96.73</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>96.25</v>
+        <v>94.98</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>93.73999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>93.83</v>
+        <v>93.75</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>95.62</v>
+        <v>94.7</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>92.62</v>
+        <v>92.95</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>90.83</v>
+        <v>92</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>89.62</v>
+        <v>91.2</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>92.06</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>89.55</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>86.55</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>92.45999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>92.29000000000001</v>
+        <v>92.67</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="R116" s="25" t="n">
-        <v>-1.92</v>
+        <v>92.8</v>
+      </c>
+      <c r="R116" s="23" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>10.26</v>
+        <v>10.19</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>10.09</v>
+        <v>10.04</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.94</v>
+        <v>9.92</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.94</v>
+        <v>9.9</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.880000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="J117" s="17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K117" s="18" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="L117" s="19" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="K117" s="18" t="n">
+      <c r="M117" s="19" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="N117" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O117" s="21" t="n">
         <v>9.85</v>
       </c>
-      <c r="L117" s="19" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="M117" s="19" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="N117" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O117" s="21" t="n">
-        <v>9.869999999999999</v>
-      </c>
       <c r="P117" s="21" t="n">
-        <v>9.859999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="R117" s="23" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R117" s="25" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>17</v>
+        <v>17.58</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.75</v>
+        <v>17.11</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.55</v>
+        <v>16.72</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.54</v>
+        <v>16.9</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="H118" s="16" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I118" s="17" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="J118" s="17" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="K118" s="18" t="n">
         <v>16.45</v>
       </c>
-      <c r="I118" s="17" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="J118" s="17" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K118" s="18" t="n">
-        <v>16.41</v>
-      </c>
       <c r="L118" s="19" t="n">
-        <v>16.2</v>
+        <v>16.06</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.95</v>
+        <v>15.59</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.44</v>
+        <v>16.56</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.42</v>
+        <v>16.49</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.39</v>
-      </c>
-      <c r="R118" s="25" t="n">
-        <v>-0.06</v>
+        <v>16.71</v>
+      </c>
+      <c r="R118" s="23" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.56</v>
+        <v>11.87</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.36</v>
+        <v>11.54</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.34</v>
+        <v>11.54</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>11.14</v>
+        <v>11.21</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>11.05</v>
+        <v>11.07</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.94</v>
+        <v>10.88</v>
       </c>
       <c r="K119" s="18" t="n">
         <v>11.08</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.92</v>
+        <v>10.81</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.72</v>
+        <v>10.48</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>11.12</v>
+        <v>11.16</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>11.1</v>
+        <v>11.11</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="R119" s="25" t="n">
-        <v>-0.54</v>
+        <v>11.27</v>
+      </c>
+      <c r="R119" s="23" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.83</v>
+        <v>12.82</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.44</v>
+        <v>12.56</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.11</v>
+        <v>12.34</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.28</v>
+        <v>12.38</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.44</v>
+        <v>12.52</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>12.05</v>
+        <v>12.26</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>11.89</v>
+        <v>12.12</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>11.66</v>
+        <v>12</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>11.57</v>
+        <v>11.98</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="N120" s="24" t="inlineStr">
+        <v>11.72</v>
+      </c>
+      <c r="N120" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.99</v>
+        <v>12.24</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.93</v>
+        <v>12.22</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>12.13</v>
+        <v>12.24</v>
       </c>
       <c r="R120" s="23" t="n">
-        <v>0.41</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.98</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.74</v>
+        <v>7.88</v>
       </c>
       <c r="E121" s="14" t="n">
         <v>7.54</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.56</v>
+        <v>7.55</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.7</v>
+        <v>7.79</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.46</v>
+        <v>7.39</v>
       </c>
       <c r="I121" s="17" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J121" s="17" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K121" s="18" t="n">
         <v>7.32</v>
       </c>
-      <c r="J121" s="17" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="K121" s="18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="L121" s="19" t="n">
-        <v>7.2</v>
+        <v>6.98</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
+        <v>6.58</v>
+      </c>
+      <c r="N121" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>7.44</v>
+        <v>7.37</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>7.42</v>
+        <v>7.35</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>7.43</v>
+        <v>7.31</v>
       </c>
       <c r="R121" s="25" t="n">
-        <v>-0.93</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>8.09</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>7.79</v>
+        <v>7.95</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>7.53</v>
+        <v>7.46</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>7.61</v>
+        <v>7.52</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>7.76</v>
+        <v>7.85</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>7.46</v>
+        <v>7.26</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>7.31</v>
+        <v>6.93</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>7.16</v>
+        <v>6.67</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>7.37</v>
+        <v>7.13</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>7.11</v>
+        <v>6.64</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="N122" s="20" t="inlineStr">
+        <v>6.05</v>
+      </c>
+      <c r="N122" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>7.42</v>
+        <v>7.22</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>7.39</v>
+        <v>7.18</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>7.47</v>
+        <v>7.19</v>
       </c>
       <c r="R122" s="25" t="n">
-        <v>-0.13</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>30.11</v>
+        <v>30.5</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>29.41</v>
+        <v>29.76</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.83</v>
+        <v>29.14</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.87</v>
+        <v>29.23</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>29.27</v>
+        <v>29.63</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.57</v>
+        <v>28.89</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>28.17</v>
+        <v>28.49</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>27.87</v>
+        <v>28.15</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>28.43</v>
+        <v>28.72</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>27.85</v>
+        <v>28.1</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>27.15</v>
+        <v>27.36</v>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>28.53</v>
+        <v>28.84</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>28.49</v>
+        <v>28.78</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>28.46</v>
+        <v>28.82</v>
       </c>
       <c r="R123" s="23" t="n">
-        <v>0.57</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>168.68</v>
+        <v>172.5</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>165.48</v>
+        <v>167.8</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>162.8</v>
+        <v>163.87</v>
       </c>
       <c r="F124" s="15" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>167.13</v>
+      </c>
+      <c r="H124" s="16" t="n">
         <v>162.43</v>
       </c>
-      <c r="G124" s="15" t="n">
-        <v>164.57</v>
-      </c>
-      <c r="H124" s="16" t="n">
-        <v>161.37</v>
-      </c>
       <c r="I124" s="17" t="n">
-        <v>159.23</v>
+        <v>159.97</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>158.17</v>
+        <v>157.73</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>161</v>
+        <v>161.23</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>158.32</v>
+        <v>157.3</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>155.12</v>
+        <v>152.6</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>161.31</v>
+        <v>162.02</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>161.25</v>
+        <v>161.6</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="R124" s="25" t="n">
-        <v>-2.55</v>
+        <v>162.2</v>
+      </c>
+      <c r="R124" s="23" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>56.9</v>
+        <v>59.79</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>55.85</v>
+        <v>57.94</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>54.97</v>
+        <v>56.39</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>55.42</v>
+        <v>56.28</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>55.83</v>
+        <v>57.47</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>54.78</v>
+        <v>55.62</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>54.37</v>
+        <v>54.43</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>53.73</v>
+        <v>53.77</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>54.38</v>
+        <v>55.36</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>53.5</v>
+        <v>53.81</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>52.45</v>
+        <v>51.96</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>54.62</v>
+        <v>55.56</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>54.46</v>
+        <v>55.5</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>0.64</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.95</v>
+        <v>15.44</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>14.45</v>
+        <v>14.55</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>14.03</v>
+        <v>13.8</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.98</v>
+        <v>13.93</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>14.31</v>
+        <v>14.41</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13.81</v>
+        <v>13.52</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.48</v>
+        <v>13.04</v>
       </c>
       <c r="J126" s="17" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="K126" s="18" t="n">
         <v>13.31</v>
       </c>
-      <c r="K126" s="18" t="n">
-        <v>13.75</v>
-      </c>
       <c r="L126" s="19" t="n">
-        <v>13.33</v>
+        <v>12.56</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
+        <v>11.67</v>
+      </c>
+      <c r="N126" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.8</v>
+        <v>13.45</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.79</v>
+        <v>13.38</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.65</v>
+        <v>13.45</v>
       </c>
       <c r="R126" s="25" t="n">
-        <v>-2.22</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.78</v>
+        <v>16.12</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15.29</v>
+        <v>15.6</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.88</v>
+        <v>15.17</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>15</v>
+        <v>15.36</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>15.24</v>
+        <v>15.58</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.75</v>
+        <v>15.06</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.51</v>
+        <v>14.84</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>14.26</v>
+        <v>14.54</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.61</v>
+        <v>14.87</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>14.2</v>
+        <v>14.44</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13.71</v>
+        <v>13.92</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.7</v>
+        <v>14.99</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.65</v>
+        <v>14.91</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="R127" s="25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>15.14</v>
+      </c>
+      <c r="R127" s="23" t="n">
+        <v>2.57</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>7.45</v>
+        <v>7.69</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>7.2</v>
+        <v>7.28</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>7.03</v>
+        <v>6.91</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.78</v>
+        <v>6.5</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>6.67</v>
+        <v>6.36</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.86</v>
+        <v>6.71</v>
       </c>
       <c r="L128" s="19" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M128" s="19" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="N128" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O128" s="21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P128" s="21" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="Q128" s="22" t="n">
         <v>6.65</v>
       </c>
-      <c r="M128" s="19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N128" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O128" s="21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P128" s="21" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="Q128" s="22" t="n">
-        <v>6.9</v>
-      </c>
       <c r="R128" s="25" t="n">
-        <v>-0.86</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>11.03</v>
+        <v>10.32</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>10.33</v>
+        <v>9.93</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.93</v>
+        <v>9.59</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>9.57</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>9.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>8.869999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="K129" s="18" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="L129" s="19" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M129" s="19" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="N129" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O129" s="21" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="P129" s="21" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="Q129" s="22" t="n">
         <v>9.35</v>
       </c>
-      <c r="L129" s="19" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="M129" s="19" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O129" s="21" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="P129" s="21" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>9.6</v>
-      </c>
       <c r="R129" s="25" t="n">
-        <v>-2.24</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>147.83</v>
+        <v>155.4</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>145.03</v>
+        <v>150.7</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>142.68</v>
+        <v>146.77</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>143.23</v>
+        <v>148.97</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>144.67</v>
+        <v>150.73</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>141.87</v>
+        <v>146.03</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>140.43</v>
+        <v>144.27</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>139.07</v>
+        <v>141.33</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>141.12</v>
+        <v>144.13</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>138.77</v>
+        <v>140.2</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>135.97</v>
+        <v>135.5</v>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>141.6</v>
+        <v>145.27</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>141.33</v>
+        <v>144.5</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>141.8</v>
-      </c>
-      <c r="R130" s="25" t="n">
-        <v>-1.18</v>
+        <v>147.2</v>
+      </c>
+      <c r="R130" s="23" t="n">
+        <v>3.81</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-17</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.47</v>
+        <v>20.5</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.33</v>
+        <v>20.31</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.21</v>
+        <v>20.15</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.25</v>
+        <v>20.16</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.31</v>
+        <v>20.27</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.17</v>
+        <v>20.08</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20.11</v>
+        <v>19.97</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>20.03</v>
+        <v>19.89</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.13</v>
+        <v>20.04</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>20.01</v>
+        <v>19.88</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.87</v>
+        <v>19.69</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>20.16</v>
+        <v>20.07</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.14</v>
+        <v>20.06</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.18</v>
+        <v>20.05</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>0.25</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.06</v>
+        <v>11.97</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.95</v>
+        <v>11.86</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.86</v>
+        <v>11.77</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.87</v>
+        <v>11.77</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.93</v>
+        <v>11.83</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>11.82</v>
+        <v>11.72</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.76</v>
+        <v>11.66</v>
       </c>
       <c r="J4" s="17" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>11.71</v>
       </c>
-      <c r="K4" s="18" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="L4" s="19" t="n">
+      <c r="Q4" s="22" t="n">
         <v>11.7</v>
       </c>
-      <c r="M4" s="19" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.81</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q4" s="22" t="n">
-        <v>11.81</v>
-      </c>
       <c r="R4" s="23" t="n">
-        <v>0.08</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15.14</v>
+        <v>15.16</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.93</v>
+        <v>14.88</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.75</v>
+        <v>14.65</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.81</v>
+        <v>14.64</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.91</v>
+        <v>14.82</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.7</v>
+        <v>14.54</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.6</v>
+        <v>14.36</v>
       </c>
       <c r="J5" s="17" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="K5" s="18" t="n">
         <v>14.49</v>
       </c>
-      <c r="K5" s="18" t="n">
-        <v>14.64</v>
-      </c>
       <c r="L5" s="19" t="n">
-        <v>14.46</v>
+        <v>14.26</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="N5" s="24" t="inlineStr">
+        <v>13.98</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.68</v>
+        <v>14.53</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.65</v>
+        <v>14.51</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="R5" s="25" t="n">
-        <v>-0.88</v>
+        <v>14.47</v>
+      </c>
+      <c r="R5" s="23" t="n">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>22.35</v>
+        <v>22.33</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.9</v>
+        <v>21.73</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.52</v>
+        <v>21.23</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.56</v>
+        <v>21.17</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.82</v>
+        <v>21.57</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>21.37</v>
+        <v>20.97</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>21.11</v>
+        <v>20.57</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>20.92</v>
+        <v>20.37</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>21.27</v>
+        <v>20.89</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.89</v>
+        <v>20.39</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="N6" s="24" t="inlineStr">
+        <v>19.79</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>21.34</v>
+        <v>20.95</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>21.3</v>
+        <v>20.94</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="R6" s="25" t="n">
-        <v>-2.16</v>
+        <v>20.78</v>
+      </c>
+      <c r="R6" s="23" t="n">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.08</v>
+        <v>34.37</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.76</v>
+        <v>33.81</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.49</v>
+        <v>33.34</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.56</v>
+        <v>33.27</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>33.72</v>
+        <v>33.65</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.4</v>
+        <v>33.09</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>33.24</v>
+        <v>32.71</v>
       </c>
       <c r="J7" s="17" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="M7" s="19" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="n">
         <v>33.08</v>
       </c>
-      <c r="K7" s="18" t="n">
-        <v>33.31</v>
-      </c>
-      <c r="L7" s="19" t="n">
-        <v>33.04</v>
-      </c>
-      <c r="M7" s="19" t="n">
-        <v>32.72</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="n">
-        <v>33.37</v>
-      </c>
       <c r="P7" s="21" t="n">
-        <v>33.34</v>
+        <v>33.07</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.4</v>
+        <v>32.9</v>
       </c>
       <c r="R7" s="23" t="n">
-        <v>0.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="G8" s="15" t="n">
         <v>23.31</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>23.02</v>
-      </c>
       <c r="H8" s="16" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n">
         <v>22.76</v>
       </c>
-      <c r="I8" s="17" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>22.69</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>22.47</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="N8" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>22.73</v>
-      </c>
       <c r="P8" s="21" t="n">
-        <v>22.71</v>
+        <v>22.67</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.75</v>
+        <v>23</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>-0.31</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>128.45</v>
+        <v>123.63</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>125.45</v>
+        <v>122.13</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>122.94</v>
+        <v>120.87</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>122.6</v>
+        <v>121.7</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>124.6</v>
+        <v>122.2</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>121.6</v>
+        <v>120.7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>119.6</v>
+        <v>120.2</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>118.6</v>
+        <v>119.2</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>121.26</v>
+        <v>120.03</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>118.75</v>
+        <v>118.77</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>115.75</v>
-      </c>
-      <c r="N9" s="24" t="inlineStr">
+        <v>117.27</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>121.55</v>
+        <v>120.42</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>121.49</v>
+        <v>120.15</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="R9" s="25" t="n">
-        <v>-2.03</v>
+        <v>121.2</v>
+      </c>
+      <c r="R9" s="23" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>67.31999999999999</v>
+        <v>67.11</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>66.72</v>
+        <v>66.61</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>66.22</v>
+        <v>66.19</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>66.31999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>66.63</v>
+        <v>66.58</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>66.03</v>
+        <v>66.08</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>65.72</v>
+        <v>65.87</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>65.43000000000001</v>
+        <v>65.58</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>65.88</v>
+        <v>65.91</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>65.38</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>65.98</v>
+        <v>66.02</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>65.93000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>66</v>
-      </c>
-      <c r="R10" s="23" t="n">
-        <v>0.15</v>
+        <v>66.15000000000001</v>
+      </c>
+      <c r="R10" s="25" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25.65</v>
+        <v>24.98</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>25.27</v>
+        <v>24.74</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.96</v>
+        <v>24.54</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.97</v>
+        <v>24.54</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>25.2</v>
+        <v>24.68</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.82</v>
+        <v>24.44</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.59</v>
+        <v>24.3</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.44</v>
+        <v>24.2</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.74</v>
+        <v>24.4</v>
       </c>
       <c r="L11" s="19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="n">
         <v>24.43</v>
       </c>
-      <c r="M11" s="19" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="N11" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>24.79</v>
-      </c>
       <c r="P11" s="21" t="n">
-        <v>24.77</v>
+        <v>24.42</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="R11" s="25" t="n">
-        <v>-1</v>
+        <v>24.39</v>
+      </c>
+      <c r="R11" s="23" t="n">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.81</v>
+        <v>25.25</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25.37</v>
+        <v>25.03</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>25</v>
+        <v>24.84</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>25.17</v>
+        <v>24.82</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>25.36</v>
+        <v>24.96</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.92</v>
+        <v>24.74</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.73</v>
+        <v>24.6</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.48</v>
+        <v>24.52</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>24.76</v>
+        <v>24.72</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.39</v>
+        <v>24.53</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+        <v>24.31</v>
+      </c>
+      <c r="N12" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.85</v>
+        <v>24.74</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.79</v>
+        <v>24.74</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="R12" s="23" t="n">
-        <v>1.3</v>
+        <v>24.67</v>
+      </c>
+      <c r="R12" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>42.07</v>
+        <v>40.81</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>41.31</v>
+        <v>40.43</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.67</v>
+        <v>40.12</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>40.64</v>
+        <v>40.33</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>41.12</v>
+        <v>40.45</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.36</v>
+        <v>40.07</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>39.88</v>
+        <v>39.95</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.6</v>
+        <v>39.69</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.25</v>
+        <v>39.9</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.61</v>
+        <v>39.59</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>38.85</v>
-      </c>
-      <c r="N13" s="24" t="inlineStr">
+        <v>39.21</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.33</v>
+        <v>40</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.31</v>
+        <v>39.93</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="R13" s="25" t="n">
-        <v>-1.33</v>
+        <v>40.2</v>
+      </c>
+      <c r="R13" s="23" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.59</v>
+        <v>8.49</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.49</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>8.49</v>
+        <v>8.41</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>8.57</v>
+        <v>8.48</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>8.449999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.369999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J14" s="17" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="K14" s="18" t="n">
         <v>8.33</v>
       </c>
-      <c r="K14" s="18" t="n">
-        <v>8.43</v>
-      </c>
       <c r="L14" s="19" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="N14" s="24" t="inlineStr">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O14" s="21" t="n">
-        <v>8.44</v>
+        <v>8.35</v>
       </c>
       <c r="P14" s="21" t="n">
-        <v>8.44</v>
+        <v>8.34</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="R14" s="25" t="n">
-        <v>-0.24</v>
+        <v>8.35</v>
+      </c>
+      <c r="R14" s="23" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>15.19</v>
+        <v>14.85</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.57</v>
+        <v>14.44</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>14.05</v>
+        <v>14.1</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>14.4</v>
+        <v>14.11</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.98</v>
+        <v>13.94</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.36</v>
+        <v>13.53</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.71</v>
+        <v>13.87</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.19</v>
+        <v>13.53</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>12.57</v>
+        <v>13.12</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.87</v>
+        <v>13.92</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.75</v>
+        <v>13.9</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>14.19</v>
+        <v>13.86</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>2.16</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.73</v>
+        <v>4.33</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.44</v>
+        <v>4.11</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.37</v>
+        <v>4.05</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>4.08</v>
+        <v>3.83</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>3.89</v>
+        <v>3.69</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>3.79</v>
+        <v>3.61</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>3.79</v>
+        <v>3.61</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N16" s="24" t="inlineStr">
+        <v>3.39</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>4.06</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" s="25" t="n">
-        <v>-5.44</v>
+        <v>3.77</v>
+      </c>
+      <c r="R16" s="23" t="n">
+        <v>-10.87</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.46</v>
+        <v>17.18</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.22</v>
+        <v>17.01</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>17.02</v>
+        <v>16.86</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.06</v>
+        <v>16.9</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.18</v>
+        <v>16.99</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.94</v>
+        <v>16.82</v>
       </c>
       <c r="I17" s="17" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="Q17" s="22" t="n">
         <v>16.82</v>
       </c>
-      <c r="J17" s="17" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q17" s="22" t="n">
-        <v>16.93</v>
-      </c>
       <c r="R17" s="23" t="n">
-        <v>0.47</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.38</v>
+        <v>24.82</v>
       </c>
       <c r="D18" s="13" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="G18" s="15" t="n">
         <v>24.1</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>24.12</v>
-      </c>
       <c r="H18" s="16" t="n">
-        <v>23.84</v>
+        <v>23.53</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.74</v>
+        <v>23.15</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>23.56</v>
+        <v>22.96</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.71</v>
+        <v>23.46</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>23.48</v>
+        <v>22.98</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>23.2</v>
+        <v>22.41</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.79</v>
+        <v>23.51</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.73</v>
+        <v>23.5</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.93</v>
+        <v>23.35</v>
       </c>
       <c r="R18" s="23" t="n">
-        <v>0.46</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>65.93000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>64.43000000000001</v>
+        <v>63.73</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>63.17</v>
+        <v>62.6</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>63</v>
+        <v>63.35</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>64</v>
+        <v>63.8</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>62.5</v>
+        <v>62.45</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>62.33</v>
+        <v>61.85</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>61.07</v>
+        <v>60.72</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>59.57</v>
+        <v>59.37</v>
       </c>
       <c r="N19" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>62.47</v>
+        <v>62.2</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>62.45</v>
+        <v>61.95</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>62</v>
-      </c>
-      <c r="R19" s="25" t="n">
-        <v>-1.59</v>
+        <v>62.9</v>
+      </c>
+      <c r="R19" s="23" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.32</v>
+        <v>11.29</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>11.12</v>
+        <v>11.04</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.96</v>
+        <v>10.84</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>11.01</v>
+        <v>10.85</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>10.81</v>
+        <v>10.6</v>
       </c>
       <c r="J20" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="P20" s="21" t="n">
         <v>10.71</v>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="N20" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>10.86</v>
-      </c>
       <c r="Q20" s="22" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="R20" s="25" t="n">
-        <v>-0.09</v>
+        <v>10.71</v>
+      </c>
+      <c r="R20" s="23" t="n">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.94</v>
+        <v>17.72</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.64</v>
+        <v>17.33</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>17.38</v>
+        <v>17</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>17.35</v>
+        <v>16.96</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.55</v>
+        <v>17.22</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>17.25</v>
+        <v>16.83</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>17.05</v>
+        <v>16.57</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.95</v>
+        <v>16.44</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>17.22</v>
+        <v>16.79</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.96</v>
+        <v>16.46</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
+        <v>16.07</v>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>17.24</v>
+        <v>16.82</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>17.24</v>
+        <v>16.82</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="R21" s="25" t="n">
-        <v>-1.44</v>
+        <v>16.7</v>
+      </c>
+      <c r="R21" s="23" t="n">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>38.61</v>
+        <v>37.48</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.97</v>
+        <v>36.54</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.6</v>
+        <v>35.75</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>36.51</v>
+        <v>36.1</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>37.05</v>
+        <v>36.5</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.41</v>
+        <v>35.56</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>34.87</v>
+        <v>35.16</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>33.77</v>
+        <v>34.62</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>34.68</v>
+        <v>35.23</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>33.31</v>
+        <v>34.44</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
+        <v>33.5</v>
+      </c>
+      <c r="N22" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>35.11</v>
+        <v>35.43</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>34.81</v>
+        <v>35.3</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="R22" s="23" t="n">
-        <v>3.63</v>
+        <v>35.7</v>
+      </c>
+      <c r="R22" s="25" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.32</v>
+        <v>16.61</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.75</v>
+        <v>16.11</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.27</v>
+        <v>15.69</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.59</v>
+        <v>15.97</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.78</v>
+        <v>16.13</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.21</v>
+        <v>15.63</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.02</v>
+        <v>15.47</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.64</v>
+        <v>15.13</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>14.96</v>
+        <v>15.41</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.48</v>
+        <v>14.99</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
+        <v>14.49</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.1</v>
+        <v>15.54</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15</v>
+        <v>15.45</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="R23" s="23" t="n">
-        <v>3.84</v>
+        <v>15.8</v>
+      </c>
+      <c r="R23" s="25" t="n">
+        <v>6.54</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.48</v>
+        <v>37.09</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.58</v>
+        <v>36.29</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.82</v>
+        <v>35.62</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.95</v>
+        <v>35.91</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.43</v>
+        <v>36.25</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.53</v>
+        <v>35.45</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>35.05</v>
+        <v>35.11</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>34.63</v>
+        <v>34.65</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>35.32</v>
+        <v>35.18</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.56</v>
+        <v>34.51</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33.66</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
+        <v>33.71</v>
+      </c>
+      <c r="N24" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.46</v>
+        <v>35.35</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>35.39</v>
+        <v>35.24</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="R24" s="23" t="n">
-        <v>1.43</v>
+        <v>35.56</v>
+      </c>
+      <c r="R24" s="25" t="n">
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>58.32</v>
+        <v>58.56</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.32</v>
+        <v>57.66</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.48</v>
+        <v>56.9</v>
       </c>
       <c r="F25" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L25" s="19" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="n">
         <v>56.53</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>56.12</v>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>55.53</v>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="K25" s="18" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="L25" s="19" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="M25" s="19" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="N25" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O25" s="21" t="n">
-        <v>56.06</v>
-      </c>
       <c r="P25" s="21" t="n">
-        <v>56</v>
+        <v>56.47</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="R25" s="23" t="n">
-        <v>0.27</v>
+        <v>56.5</v>
+      </c>
+      <c r="R25" s="25" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>221.6</v>
+        <v>227.87</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>214.8</v>
+        <v>221.77</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>209.1</v>
+        <v>216.66</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>211.6</v>
+        <v>217.37</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>214.5</v>
+        <v>220.73</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>207.7</v>
+        <v>214.63</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>204.8</v>
+        <v>211.27</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>200.9</v>
+        <v>208.53</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>205.3</v>
+        <v>213.24</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>199.6</v>
+        <v>208.13</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
+        <v>202.03</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>206.76</v>
+        <v>214.18</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>205.83</v>
+        <v>213.72</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>208.7</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>2.35</v>
+        <v>214</v>
+      </c>
+      <c r="R26" s="25" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>82.23</v>
+        <v>81.45</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>80.73</v>
+        <v>80</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>79.47</v>
+        <v>78.78</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>79.47</v>
+        <v>79.52</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>80.38</v>
+        <v>80.03</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>78.88</v>
+        <v>78.58</v>
       </c>
       <c r="I27" s="17" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>77.13</v>
+      </c>
+      <c r="K27" s="18" t="n">
         <v>77.97</v>
       </c>
-      <c r="J27" s="17" t="n">
-        <v>77.38</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>78.63</v>
-      </c>
       <c r="L27" s="19" t="n">
-        <v>77.37</v>
+        <v>76.75</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>75.87</v>
-      </c>
-      <c r="N27" s="24" t="inlineStr">
+        <v>75.3</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>78.81999999999999</v>
+        <v>78.33</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>78.75</v>
+        <v>78.08</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="R27" s="25" t="n">
-        <v>-0.88</v>
+        <v>79</v>
+      </c>
+      <c r="R27" s="23" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21</v>
+        <v>20.69</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.66</v>
+        <v>20.42</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.38</v>
+        <v>20.19</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.52</v>
+        <v>20.21</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.65</v>
+        <v>20.37</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.31</v>
+        <v>20.1</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.18</v>
+        <v>19.94</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.97</v>
+        <v>19.83</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>20.18</v>
+        <v>20.04</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>19.9</v>
+        <v>19.81</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>19.56</v>
+        <v>19.54</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O28" s="21" t="n">
-        <v>20.26</v>
+        <v>20.08</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>20.21</v>
+        <v>20.06</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>20.38</v>
+        <v>20.06</v>
       </c>
       <c r="R28" s="23" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>84.73</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>82.18000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>80.04000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>81.45</v>
+        <v>79.5</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>82.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>79.75</v>
+        <v>78.3</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>78.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>77.2</v>
+        <v>75</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>78.61</v>
+        <v>77.83</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>76.47</v>
+        <v>75.06</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>73.92</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>79.28</v>
+        <v>78.19</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>78.81</v>
+        <v>78.08</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>80.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>1.83</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>29.88</v>
+        <v>28.59</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>28.78</v>
+        <v>27.79</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>27.86</v>
+        <v>27.12</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.93</v>
+        <v>27.09</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>28.57</v>
+        <v>27.59</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>27.47</v>
+        <v>26.79</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>26.83</v>
+        <v>26.29</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>26.37</v>
+        <v>25.99</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>27.24</v>
+        <v>26.68</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>26.32</v>
+        <v>26.01</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
+        <v>25.21</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>27.4</v>
+        <v>26.77</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>27.33</v>
+        <v>26.74</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="R30" s="25" t="n">
-        <v>-2.22</v>
+        <v>26.58</v>
+      </c>
+      <c r="R30" s="23" t="n">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.38</v>
+        <v>49.05</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>48.64</v>
+        <v>48.39</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>48.02</v>
+        <v>47.83</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>48.31</v>
+        <v>47.89</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>48.61</v>
+        <v>48.27</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.87</v>
+        <v>47.61</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.57</v>
+        <v>47.23</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>47.13</v>
+        <v>46.95</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.6</v>
+        <v>47.47</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.98</v>
+        <v>46.91</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="N31" s="24" t="inlineStr">
+        <v>46.25</v>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.77</v>
+        <v>47.56</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.66</v>
+        <v>47.52</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="R31" s="25" t="n">
-        <v>-0.08</v>
+        <v>47.52</v>
+      </c>
+      <c r="R31" s="23" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>134.12</v>
+        <v>130.4</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>129.72</v>
+        <v>128.3</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>126.03</v>
+        <v>126.54</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>128.47</v>
+        <v>126.3</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>129.93</v>
+        <v>127.7</v>
       </c>
       <c r="H32" s="16" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>125.36</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="N32" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O32" s="21" t="n">
+        <v>125.56</v>
+      </c>
+      <c r="P32" s="21" t="n">
         <v>125.53</v>
       </c>
-      <c r="I32" s="17" t="n">
-        <v>124.07</v>
-      </c>
-      <c r="J32" s="17" t="n">
-        <v>121.13</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>123.57</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>119.88</v>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>115.48</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O32" s="21" t="n">
-        <v>124.72</v>
-      </c>
-      <c r="P32" s="21" t="n">
-        <v>123.91</v>
-      </c>
       <c r="Q32" s="22" t="n">
-        <v>127</v>
-      </c>
-      <c r="R32" s="23" t="n">
-        <v>3.67</v>
+        <v>124.9</v>
+      </c>
+      <c r="R32" s="25" t="n">
+        <v>1.96</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>61.61</v>
+        <v>59.57</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>59.41</v>
+        <v>57.67</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>57.57</v>
+        <v>56.08</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>57.55</v>
+        <v>56.13</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>58.9</v>
+        <v>57.27</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>56.7</v>
+        <v>55.37</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>55.35</v>
+        <v>54.23</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>54.5</v>
+        <v>53.47</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>56.33</v>
+        <v>55.02</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>54.49</v>
+        <v>53.43</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="N33" s="24" t="inlineStr">
+        <v>51.53</v>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>56.6</v>
+        <v>55.27</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>56.51</v>
+        <v>55.17</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="R33" s="25" t="n">
-        <v>-1.49</v>
+        <v>55</v>
+      </c>
+      <c r="R33" s="23" t="n">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.7</v>
+        <v>24.55</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.99</v>
+        <v>23.96</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.39</v>
+        <v>23.47</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.79</v>
+        <v>23.48</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>24.02</v>
+        <v>23.83</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.31</v>
+        <v>23.24</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>23.08</v>
+        <v>22.89</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.6</v>
+        <v>22.65</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.4</v>
+        <v>22.65</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
+        <v>22.06</v>
+      </c>
+      <c r="N34" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>23.18</v>
+        <v>23.21</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.05</v>
+        <v>23.19</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="R34" s="23" t="n">
-        <v>3.11</v>
+        <v>23.12</v>
+      </c>
+      <c r="R34" s="25" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.52</v>
+        <v>26.54</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>26.06</v>
+        <v>26.08</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.68</v>
+        <v>25.7</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.93</v>
+        <v>25.65</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>26.09</v>
+        <v>25.95</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.63</v>
+        <v>25.49</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.47</v>
+        <v>25.19</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>25.17</v>
+        <v>25.03</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>25.42</v>
+        <v>25.44</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>25.04</v>
+        <v>25.06</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>24.58</v>
+        <v>24.6</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>25.54</v>
+        <v>25.49</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>25.46</v>
+        <v>25.48</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="R35" s="23" t="n">
-        <v>1.82</v>
+        <v>25.34</v>
+      </c>
+      <c r="R35" s="25" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.960000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.880000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.81</v>
+        <v>8.73</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.81</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G36" s="15" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>8.73</v>
+        <v>8.48</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="M36" s="19" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>8.779999999999999</v>
-      </c>
       <c r="P36" s="21" t="n">
-        <v>8.77</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.76</v>
+        <v>8.56</v>
       </c>
       <c r="R36" s="23" t="n">
-        <v>0.23</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>37.5</v>
+        <v>34.16</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>34.72</v>
+        <v>33.28</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>32.39</v>
+        <v>32.55</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>33.89</v>
+        <v>32.45</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>34.83</v>
+        <v>33.03</v>
       </c>
       <c r="H37" s="16" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="K37" s="18" t="n">
         <v>32.05</v>
       </c>
-      <c r="I37" s="17" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="J37" s="17" t="n">
-        <v>29.27</v>
-      </c>
-      <c r="K37" s="18" t="n">
-        <v>30.83</v>
-      </c>
       <c r="L37" s="19" t="n">
-        <v>28.5</v>
+        <v>31.32</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>25.72</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
+        <v>30.44</v>
+      </c>
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.55</v>
+        <v>32.14</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.05</v>
+        <v>32.12</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>32.94</v>
-      </c>
-      <c r="R37" s="23" t="n">
-        <v>8.779999999999999</v>
+        <v>31.86</v>
+      </c>
+      <c r="R37" s="25" t="n">
+        <v>5.22</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>191.91</v>
+        <v>186</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>186.71</v>
+        <v>181.8</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>182.36</v>
+        <v>178.28</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>182.9</v>
+        <v>177.8</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>185.8</v>
+        <v>180.6</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>180.6</v>
+        <v>176.4</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>177.7</v>
+        <v>173.6</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>175.4</v>
+        <v>172.2</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>179.44</v>
+        <v>175.92</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>175.09</v>
+        <v>172.4</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>169.89</v>
-      </c>
-      <c r="N38" s="24" t="inlineStr">
+        <v>168.2</v>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>180.22</v>
+        <v>176.33</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>179.85</v>
+        <v>176.25</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R38" s="25" t="n">
-        <v>-0.83</v>
+        <v>175</v>
+      </c>
+      <c r="R38" s="23" t="n">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="20" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="Q39" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="R39" s="23" t="n">
+      <c r="R39" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>24.23</v>
+        <v>23.62</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>23.19</v>
+        <v>22.62</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>22.32</v>
+        <v>21.78</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>22.41</v>
+        <v>21.67</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>23</v>
+        <v>22.33</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.96</v>
+        <v>21.33</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>21.37</v>
+        <v>20.67</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.92</v>
+        <v>20.33</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>21.74</v>
+        <v>21.22</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.87</v>
+        <v>20.38</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>19.83</v>
+        <v>19.38</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.89</v>
+        <v>21.32</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.82</v>
+        <v>21.3</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.82</v>
+        <v>21</v>
       </c>
       <c r="R40" s="23" t="n">
-        <v>1.02</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>200.68</v>
+        <v>194.98</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>192.78</v>
+        <v>189.68</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>186.16</v>
+        <v>185.23</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>188.33</v>
+        <v>185.23</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>192.07</v>
+        <v>188.47</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>184.17</v>
+        <v>183.17</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>180.43</v>
+        <v>179.93</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>176.27</v>
+        <v>177.87</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>181.74</v>
+        <v>182.27</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>175.12</v>
+        <v>177.82</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>167.22</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
+        <v>172.52</v>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>183.26</v>
+        <v>182.92</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>182.35</v>
+        <v>182.68</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>2.56</v>
+        <v>182</v>
+      </c>
+      <c r="R41" s="25" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.84</v>
+        <v>36.82</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.46</v>
+        <v>36.33</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>36.65</v>
+        <v>36.35</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>36.83</v>
+        <v>36.69</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>36.37</v>
+        <v>36.11</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>36.19</v>
+        <v>35.77</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.91</v>
+        <v>35.53</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>36.2</v>
+        <v>36.01</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>35.82</v>
+        <v>35.52</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>35.36</v>
+        <v>34.94</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>36.31</v>
+        <v>36.08</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>36.24</v>
+        <v>36.05</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>36.46</v>
+        <v>36</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>0.55</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27.55</v>
+        <v>27.87</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.15</v>
+        <v>27.27</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>26.81</v>
+        <v>26.77</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>26.97</v>
+        <v>26.98</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.13</v>
+        <v>27.24</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>26.73</v>
+        <v>26.64</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>26.57</v>
+        <v>26.38</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.33</v>
+        <v>26.04</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>26.59</v>
+        <v>26.43</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>26.25</v>
+        <v>25.93</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
+        <v>25.33</v>
+      </c>
+      <c r="N43" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>26.68</v>
+        <v>26.56</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>26.62</v>
+        <v>26.48</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>0.37</v>
+        <v>26.72</v>
+      </c>
+      <c r="R43" s="25" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>25.98</v>
+        <v>26.77</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.82</v>
+        <v>26.23</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.68</v>
+        <v>25.78</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.67</v>
+        <v>26.08</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>25.77</v>
+        <v>26.26</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.61</v>
+        <v>25.72</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.51</v>
+        <v>25.54</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.45</v>
+        <v>25.18</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.6</v>
+        <v>25.48</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.46</v>
+        <v>25.03</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>25.3</v>
+        <v>24.49</v>
       </c>
       <c r="N44" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.61</v>
+        <v>25.62</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.61</v>
+        <v>25.52</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.56</v>
+        <v>25.9</v>
       </c>
       <c r="R44" s="25" t="n">
-        <v>-0.47</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.64</v>
+        <v>7.61</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.56</v>
+        <v>7.49</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.58</v>
+        <v>7.53</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.54</v>
+        <v>7.46</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.49</v>
+        <v>7.39</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.45</v>
+        <v>7.32</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.51</v>
+        <v>7.41</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.43</v>
+        <v>7.29</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7.34</v>
+        <v>7.15</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.52</v>
+        <v>7.42</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.54</v>
+        <v>7.47</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>0.13</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>11.97</v>
+        <v>12.09</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>11.82</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.7</v>
+        <v>11.59</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.73</v>
+        <v>11.57</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.8</v>
+        <v>11.75</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.65</v>
+        <v>11.48</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.58</v>
+        <v>11.3</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.5</v>
+        <v>11.21</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.61</v>
+        <v>11.44</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.49</v>
+        <v>11.21</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="N46" s="24" t="inlineStr">
+        <v>10.94</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.64</v>
+        <v>11.47</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.62</v>
+        <v>11.46</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.65</v>
+        <v>11.4</v>
       </c>
       <c r="R46" s="23" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>207.92</v>
+        <v>203.44</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>205.62</v>
+        <v>201.44</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>203.69</v>
+        <v>199.76</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>204.57</v>
+        <v>200.4</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>205.53</v>
+        <v>201.3</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>203.23</v>
+        <v>199.3</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>202.27</v>
+        <v>198.4</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>200.93</v>
+        <v>197.3</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>202.41</v>
+        <v>198.64</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>200.48</v>
+        <v>196.96</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>198.18</v>
-      </c>
-      <c r="N47" s="24" t="inlineStr">
+        <v>194.96</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>202.91</v>
+        <v>199.05</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>202.59</v>
+        <v>198.8</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>203.6</v>
+        <v>199.5</v>
       </c>
       <c r="R47" s="23" t="n">
-        <v>0.25</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>47.38</v>
+        <v>46.57</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>46.5</v>
+        <v>46.01</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>45.77</v>
+        <v>45.54</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>46.07</v>
+        <v>45.74</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>46.45</v>
+        <v>45.98</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>45.57</v>
+        <v>45.42</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>45.19</v>
+        <v>45.18</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>44.69</v>
+        <v>44.86</v>
       </c>
       <c r="K48" s="18" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="L48" s="19" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O48" s="21" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="P48" s="21" t="n">
         <v>45.27</v>
       </c>
-      <c r="L48" s="19" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>43.66</v>
-      </c>
-      <c r="N48" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O48" s="21" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="P48" s="21" t="n">
-        <v>45.34</v>
-      </c>
       <c r="Q48" s="22" t="n">
-        <v>45.68</v>
+        <v>45.5</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>32.74</v>
+        <v>33.63</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32.26</v>
+        <v>32.71</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>31.85</v>
+        <v>31.94</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>32.08</v>
+        <v>32.15</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>32.26</v>
+        <v>32.61</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.78</v>
+        <v>31.69</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.6</v>
+        <v>31.23</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.3</v>
+        <v>30.77</v>
       </c>
       <c r="K49" s="18" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="L49" s="19" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="M49" s="19" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O49" s="21" t="n">
         <v>31.59</v>
       </c>
-      <c r="L49" s="19" t="n">
-        <v>31.18</v>
-      </c>
-      <c r="M49" s="19" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="N49" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O49" s="21" t="n">
+      <c r="P49" s="21" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="Q49" s="22" t="n">
         <v>31.7</v>
       </c>
-      <c r="P49" s="21" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="Q49" s="22" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R49" s="25" t="n">
-        <v>-0.25</v>
+      <c r="R49" s="23" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.98</v>
+        <v>12.64</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.71</v>
+        <v>12.42</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.48</v>
+        <v>12.23</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.45</v>
+        <v>12.21</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.63</v>
+        <v>12.35</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.36</v>
+        <v>12.13</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>12.18</v>
+        <v>11.99</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>12.09</v>
+        <v>11.91</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>12.33</v>
+        <v>12.11</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>12.1</v>
+        <v>11.92</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="N50" s="24" t="inlineStr">
+        <v>11.7</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12.36</v>
+        <v>12.13</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>12.35</v>
+        <v>12.13</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="R50" s="25" t="n">
-        <v>-2.15</v>
+        <v>12.06</v>
+      </c>
+      <c r="R50" s="23" t="n">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="51">
@@ -3734,19 +3734,19 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>60.01</v>
+        <v>59.61</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>58.86</v>
+        <v>58.71</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>57.9</v>
+        <v>57.95</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.43</v>
+        <v>58.18</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>58.87</v>
+        <v>58.62</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>57.72</v>
@@ -3755,33 +3755,33 @@
         <v>57.28</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>56.57</v>
+        <v>56.82</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.25</v>
+        <v>57.45</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>56.29</v>
+        <v>56.69</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
+        <v>55.79</v>
+      </c>
+      <c r="N51" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.53</v>
+        <v>57.62</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.34</v>
+        <v>57.52</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="R51" s="23" t="n">
-        <v>0.87</v>
+        <v>57.75</v>
+      </c>
+      <c r="R51" s="25" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>23.3</v>
+        <v>23.33</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.84</v>
+        <v>22.82</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.46</v>
+        <v>22.39</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.61</v>
+        <v>22.34</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.81</v>
+        <v>22.67</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22.35</v>
+        <v>22.16</v>
       </c>
       <c r="I52" s="17" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L52" s="19" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O52" s="21" t="n">
         <v>22.15</v>
       </c>
-      <c r="J52" s="17" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="L52" s="19" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="N52" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O52" s="21" t="n">
-        <v>22.3</v>
-      </c>
       <c r="P52" s="21" t="n">
-        <v>22.24</v>
+        <v>22.14</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="R52" s="23" t="n">
-        <v>0.58</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>5.15</v>
+        <v>5.12</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="I53" s="17" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K53" s="18" t="n">
         <v>5.01</v>
       </c>
-      <c r="J53" s="17" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="K53" s="18" t="n">
-        <v>5.06</v>
-      </c>
       <c r="L53" s="19" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N53" s="24" t="inlineStr">
+        <v>4.84</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
       <c r="P53" s="21" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="R53" s="25" t="n">
-        <v>-1.37</v>
+        <v>5.02</v>
+      </c>
+      <c r="R53" s="23" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>19.57</v>
+        <v>18.54</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.98</v>
+        <v>18.3</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>18.49</v>
+        <v>18.1</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>18.58</v>
+        <v>18.13</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.89</v>
+        <v>18.26</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>18.3</v>
+        <v>18.02</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.99</v>
+        <v>17.89</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>17.71</v>
+        <v>17.78</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>18.16</v>
+        <v>17.96</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>17.67</v>
+        <v>17.76</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="N54" s="24" t="inlineStr">
+        <v>17.52</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>18.25</v>
+        <v>18</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>18.21</v>
+        <v>17.98</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="R54" s="25" t="n">
-        <v>-1.14</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="23" t="n">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>96.68000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>95.18000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E55" s="14" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="F55" s="15" t="n">
         <v>93.92</v>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>94.12</v>
       </c>
       <c r="G55" s="15" t="n">
         <v>94.93000000000001</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>93.43000000000001</v>
+        <v>93.13</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>92.62</v>
+        <v>92.12</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>91.93000000000001</v>
+        <v>91.33</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>93.08</v>
+        <v>92.75</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>91.81999999999999</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>90.31999999999999</v>
-      </c>
-      <c r="N55" s="24" t="inlineStr">
+        <v>89.44</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>93.31999999999999</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>93.2</v>
+        <v>92.89</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>93.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R55" s="23" t="n">
-        <v>0.32</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.59</v>
+        <v>17.51</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.29</v>
+        <v>17.23</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>17.03</v>
+        <v>17</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>17.12</v>
+        <v>17.13</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>17.26</v>
+        <v>17.24</v>
       </c>
       <c r="H56" s="16" t="n">
         <v>16.96</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.82</v>
+        <v>16.85</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>16.66</v>
+        <v>16.68</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>16.87</v>
+        <v>16.84</v>
       </c>
       <c r="L56" s="19" t="n">
         <v>16.61</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
+        <v>16.33</v>
+      </c>
+      <c r="N56" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.92</v>
+        <v>16.91</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.89</v>
+        <v>16.86</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="R56" s="23" t="n">
-        <v>0.24</v>
+        <v>17.03</v>
+      </c>
+      <c r="R56" s="25" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.78</v>
+        <v>20.81</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>21.36</v>
+        <v>20.73</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>21.01</v>
+        <v>20.66</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.96</v>
+        <v>20.65</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>21.24</v>
+        <v>20.71</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.82</v>
+        <v>20.63</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.54</v>
+        <v>20.57</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.4</v>
+        <v>20.55</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20.77</v>
+        <v>20.62</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>20.42</v>
+        <v>20.55</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="N57" s="24" t="inlineStr">
+        <v>20.47</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.81</v>
+        <v>20.63</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.81</v>
+        <v>20.62</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="R57" s="25" t="n">
-        <v>-2.04</v>
+        <v>20.6</v>
+      </c>
+      <c r="R57" s="23" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.91</v>
+        <v>23.06</v>
       </c>
       <c r="D58" s="13" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="G58" s="15" t="n">
         <v>22.74</v>
       </c>
-      <c r="E58" s="14" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F58" s="15" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>22.72</v>
-      </c>
       <c r="H58" s="16" t="n">
-        <v>22.55</v>
+        <v>22.4</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>22.47</v>
+        <v>22.28</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>22.38</v>
+        <v>22.06</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>22.5</v>
+        <v>22.24</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>22.35</v>
+        <v>21.96</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="N58" s="24" t="inlineStr">
+        <v>21.62</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22.53</v>
+        <v>22.33</v>
       </c>
       <c r="P58" s="21" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="Q58" s="22" t="n">
         <v>22.51</v>
       </c>
-      <c r="Q58" s="22" t="n">
-        <v>22.56</v>
-      </c>
       <c r="R58" s="23" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.34</v>
+        <v>28.28</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>28.08</v>
+        <v>27.92</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.86</v>
+        <v>27.62</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.83</v>
+        <v>27.65</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>28.01</v>
+        <v>27.85</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.75</v>
+        <v>27.49</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.57</v>
+        <v>27.29</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.49</v>
+        <v>27.13</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.72</v>
+        <v>27.42</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.5</v>
+        <v>27.12</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="N59" s="24" t="inlineStr">
+        <v>26.76</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.74</v>
+        <v>27.47</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.74</v>
+        <v>27.45</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="R59" s="25" t="n">
-        <v>-0.36</v>
+        <v>27.44</v>
+      </c>
+      <c r="R59" s="23" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>46.65</v>
+        <v>45.77</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.83</v>
+        <v>45.47</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.14</v>
+        <v>45.21</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.37</v>
+        <v>45.19</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45.75</v>
+        <v>45.39</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>44.93</v>
+        <v>45.09</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>44.55</v>
+        <v>44.89</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>44.11</v>
+        <v>44.79</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>44.68</v>
+        <v>45.05</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>43.99</v>
+        <v>44.79</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="N60" s="24" t="inlineStr">
+        <v>44.49</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>44.84</v>
+        <v>45.08</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>44.74</v>
+        <v>45.07</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="R60" s="25" t="n">
-        <v>-0.31</v>
+        <v>45</v>
+      </c>
+      <c r="R60" s="23" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="61">
@@ -4357,51 +4357,51 @@
         <v>19.41</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>19.09</v>
+        <v>18.92</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.82</v>
+        <v>18.51</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.78</v>
+        <v>18.48</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>19</v>
+        <v>18.79</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.68</v>
+        <v>18.3</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>18.46</v>
+        <v>17.99</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>18.36</v>
+        <v>17.81</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18.64</v>
+        <v>18.24</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>18.37</v>
+        <v>17.83</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="N61" s="24" t="inlineStr">
+        <v>17.34</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.67</v>
+        <v>18.29</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.67</v>
+        <v>18.28</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="R61" s="25" t="n">
-        <v>-1.54</v>
+        <v>18.16</v>
+      </c>
+      <c r="R61" s="23" t="n">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.44</v>
+        <v>15.23</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.23</v>
+        <v>15.08</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>15.05</v>
+        <v>14.96</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.03</v>
+        <v>15.01</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.17</v>
+        <v>15.08</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.82</v>
+        <v>14.86</v>
       </c>
       <c r="J62" s="17" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="K62" s="18" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="L62" s="19" t="n">
         <v>14.75</v>
       </c>
-      <c r="K62" s="18" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>14.76</v>
-      </c>
       <c r="M62" s="19" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="N62" s="24" t="inlineStr">
+        <v>14.6</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.96</v>
+        <v>14.91</v>
       </c>
       <c r="P62" s="21" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="Q62" s="22" t="n">
         <v>14.95</v>
       </c>
-      <c r="Q62" s="22" t="n">
-        <v>14.89</v>
-      </c>
       <c r="R62" s="25" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.92</v>
+        <v>24.79</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.51</v>
+        <v>24.39</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>24.17</v>
+        <v>24.05</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>24.23</v>
+        <v>24.01</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.45</v>
+        <v>24.28</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>24.04</v>
+        <v>23.88</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.82</v>
+        <v>23.61</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.63</v>
+        <v>23.48</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.94</v>
+        <v>23.83</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.6</v>
+        <v>23.49</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.19</v>
-      </c>
-      <c r="N63" s="24" t="inlineStr">
+        <v>23.09</v>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>24.01</v>
+        <v>23.87</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.97</v>
+        <v>23.86</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="R63" s="25" t="n">
-        <v>-1.03</v>
+        <v>23.75</v>
+      </c>
+      <c r="R63" s="23" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.33</v>
+        <v>7.26</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.22</v>
+        <v>7.16</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.13</v>
+        <v>7.08</v>
       </c>
       <c r="F64" s="15" t="n">
         <v>7.11</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>7.19</v>
+        <v>7.15</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>7.08</v>
+        <v>7.05</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7</v>
+        <v>7.01</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>6.97</v>
+        <v>6.95</v>
       </c>
       <c r="K64" s="18" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="Q64" s="22" t="n">
         <v>7.06</v>
       </c>
-      <c r="L64" s="19" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="N64" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="P64" s="21" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="Q64" s="22" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="R64" s="25" t="n">
-        <v>-1.12</v>
+      <c r="R64" s="23" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="65">
@@ -4602,54 +4602,54 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="E65" s="14" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>4.85</v>
       </c>
-      <c r="F65" s="15" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="G65" s="15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="H65" s="16" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="I65" s="17" t="n">
         <v>4.77</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R65" s="25" t="n">
-        <v>-0.21</v>
+        <v>4.79</v>
+      </c>
+      <c r="R65" s="23" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.82</v>
+        <v>4.88</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="E66" s="14" t="n">
         <v>4.64</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="K66" s="18" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n">
         <v>4.58</v>
       </c>
-      <c r="L66" s="19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>4.61</v>
-      </c>
       <c r="P66" s="21" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.66</v>
+        <v>4.54</v>
       </c>
       <c r="R66" s="23" t="n">
-        <v>1.75</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>65.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>64.81</v>
+        <v>64.63</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>65.5</v>
+        <v>64.8</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>65.95</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>64.65000000000001</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>64.2</v>
+        <v>63.35</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>63.35</v>
+        <v>62.7</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>64.09</v>
+        <v>63.82</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>61.7</v>
+        <v>61.15</v>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>64.42</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>64.19</v>
+        <v>63.93</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>65.05</v>
+        <v>64</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>1.17</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>68.2</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>67.15000000000001</v>
+        <v>67.58</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>66.27</v>
+        <v>66.66</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>66.84999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>67.2</v>
+        <v>67.63</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>66.15000000000001</v>
+        <v>66.53</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>65.8</v>
+        <v>66.17</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>65.09999999999999</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>65.68000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>64.8</v>
+        <v>65.12</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
+        <v>64.02</v>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>65.95999999999999</v>
+        <v>66.33</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>65.76000000000001</v>
+        <v>66.13</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="R68" s="23" t="n">
-        <v>1.14</v>
+        <v>66.90000000000001</v>
+      </c>
+      <c r="R68" s="25" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>83.43000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>81.68000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>80.20999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>80.78</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>81.56999999999999</v>
+        <v>80.97</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>79.81999999999999</v>
+        <v>78.47</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>79.03</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>78.06999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>79.23</v>
+        <v>77.8</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>77.77</v>
+        <v>75.7</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>76.02</v>
+        <v>73.2</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>79.59</v>
+        <v>78.23</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>79.37</v>
+        <v>78</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>80</v>
-      </c>
-      <c r="R69" s="25" t="n">
-        <v>-0.12</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="R69" s="23" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>130.48</v>
+        <v>121.84</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>123.88</v>
+        <v>119.84</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>118.35</v>
+        <v>118.16</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>121.93</v>
+        <v>118.87</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>124.17</v>
+        <v>119.73</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>117.57</v>
+        <v>117.73</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>115.33</v>
+        <v>116.87</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>110.97</v>
+        <v>115.73</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>114.65</v>
+        <v>117.04</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>109.12</v>
+        <v>115.36</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>102.52</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
+        <v>113.36</v>
+      </c>
+      <c r="N70" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>116.37</v>
+        <v>117.46</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>115.17</v>
+        <v>117.2</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="R70" s="23" t="n">
-        <v>4.27</v>
+        <v>118</v>
+      </c>
+      <c r="R70" s="25" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.84</v>
+        <v>23.34</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.45</v>
+        <v>23.01</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>23.12</v>
+        <v>22.74</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>23.09</v>
+        <v>22.83</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>23.35</v>
+        <v>22.98</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>22.96</v>
+        <v>22.65</v>
       </c>
       <c r="I71" s="17" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>22.57</v>
+        <v>22.32</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>22.91</v>
+        <v>22.55</v>
       </c>
       <c r="L71" s="19" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="M71" s="19" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="P71" s="21" t="n">
         <v>22.58</v>
       </c>
-      <c r="M71" s="19" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="N71" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>22.94</v>
-      </c>
       <c r="Q71" s="22" t="n">
-        <v>22.84</v>
-      </c>
-      <c r="R71" s="25" t="n">
-        <v>-1.13</v>
+        <v>22.67</v>
+      </c>
+      <c r="R71" s="23" t="n">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>21.15</v>
+        <v>19.61</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>19.6</v>
+        <v>18.82</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>18.3</v>
+        <v>18.16</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>18.48</v>
+        <v>18.16</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>19.33</v>
+        <v>18.64</v>
       </c>
       <c r="H72" s="16" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="J72" s="17" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="K72" s="18" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="L72" s="19" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="M72" s="19" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="N72" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O72" s="21" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="P72" s="21" t="n">
         <v>17.78</v>
       </c>
-      <c r="I72" s="17" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="J72" s="17" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="K72" s="18" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="L72" s="19" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="M72" s="19" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="N72" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O72" s="21" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="P72" s="21" t="n">
-        <v>17.55</v>
-      </c>
       <c r="Q72" s="22" t="n">
-        <v>17.62</v>
-      </c>
-      <c r="R72" s="23" t="n">
-        <v>3.04</v>
+        <v>17.68</v>
+      </c>
+      <c r="R72" s="25" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>240.64</v>
+        <v>236.63</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>235.24</v>
+        <v>232.53</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>230.71</v>
+        <v>229.1</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>231.1</v>
+        <v>231.37</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>234.2</v>
+        <v>232.73</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>228.8</v>
+        <v>228.63</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>225.7</v>
+        <v>227.27</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>223.4</v>
+        <v>224.53</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>227.69</v>
+        <v>226.8</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>223.16</v>
+        <v>223.37</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>217.76</v>
-      </c>
-      <c r="N73" s="24" t="inlineStr">
+        <v>219.27</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>228.45</v>
+        <v>227.88</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>228.11</v>
+        <v>227.12</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>228</v>
-      </c>
-      <c r="R73" s="25" t="n">
-        <v>-1.13</v>
+        <v>230</v>
+      </c>
+      <c r="R73" s="23" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.91</v>
+        <v>15.87</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.63</v>
+        <v>15.59</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.55</v>
+        <v>15.34</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.65</v>
+        <v>15.52</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.37</v>
+        <v>15.24</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.27</v>
+        <v>15.06</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>15.09</v>
+        <v>14.96</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.24</v>
+        <v>15.2</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>15.01</v>
+        <v>14.97</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.32</v>
+        <v>15.23</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.26</v>
+        <v>15.22</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.46</v>
+        <v>15.16</v>
       </c>
       <c r="R74" s="23" t="n">
-        <v>0.45</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>36.33</v>
+        <v>35.79</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>35.67</v>
+        <v>35.45</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>35.11</v>
+        <v>35.17</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>35.44</v>
+        <v>35.23</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>35.68</v>
+        <v>35.41</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>35.02</v>
+        <v>35.07</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>34.78</v>
+        <v>34.89</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>34.36</v>
+        <v>34.73</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>34.75</v>
+        <v>34.97</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>34.19</v>
+        <v>34.69</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
+        <v>34.35</v>
+      </c>
+      <c r="N75" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>34.91</v>
+        <v>35.03</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="R75" s="23" t="n">
-        <v>2.03</v>
+        <v>35.06</v>
+      </c>
+      <c r="R75" s="25" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>23.17</v>
+        <v>22.92</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>22.44</v>
+        <v>22.32</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>22.17</v>
+        <v>21.84</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>22.44</v>
+        <v>22.19</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>21.71</v>
+        <v>21.59</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>21.44</v>
+        <v>21.24</v>
       </c>
       <c r="J76" s="17" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K76" s="18" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="L76" s="19" t="n">
         <v>20.98</v>
       </c>
-      <c r="K76" s="18" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="L76" s="19" t="n">
-        <v>20.81</v>
-      </c>
       <c r="M76" s="19" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="N76" s="20" t="inlineStr">
+        <v>20.38</v>
+      </c>
+      <c r="N76" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>21.6</v>
+        <v>21.56</v>
       </c>
       <c r="P76" s="21" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="Q76" s="22" t="n">
         <v>21.48</v>
       </c>
-      <c r="Q76" s="22" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="R76" s="23" t="n">
-        <v>2.82</v>
+      <c r="R76" s="25" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>45.18</v>
+        <v>44.71</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>44.14</v>
+        <v>43.59</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>43.27</v>
+        <v>42.65</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>43.51</v>
+        <v>42.86</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>44.03</v>
+        <v>43.44</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.99</v>
+        <v>42.32</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>42.47</v>
+        <v>41.74</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>41.95</v>
+        <v>41.2</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.69</v>
+        <v>42.03</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>41.82</v>
+        <v>41.09</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>40.78</v>
+        <v>39.97</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.88</v>
+        <v>42.22</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.77</v>
+        <v>42.11</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>43</v>
+        <v>42.28</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>1.18</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.56</v>
+        <v>5.57</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.41</v>
+        <v>5.37</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="J78" s="17" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L78" s="19" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="M78" s="19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="P78" s="21" t="n">
         <v>5.31</v>
       </c>
-      <c r="K78" s="18" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M78" s="19" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O78" s="21" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="P78" s="21" t="n">
-        <v>5.37</v>
-      </c>
       <c r="Q78" s="22" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>19.42</v>
+        <v>18.81</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.91</v>
+        <v>18.54</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.48</v>
+        <v>18.31</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.76</v>
+        <v>18.29</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>18.93</v>
+        <v>18.46</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>18.42</v>
+        <v>18.19</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>18.25</v>
+        <v>18.02</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>17.91</v>
+        <v>17.92</v>
       </c>
       <c r="K79" s="18" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="n">
         <v>18.19</v>
       </c>
-      <c r="L79" s="19" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O79" s="21" t="n">
-        <v>18.33</v>
-      </c>
       <c r="P79" s="21" t="n">
-        <v>18.23</v>
+        <v>18.18</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.59</v>
+        <v>18.11</v>
       </c>
       <c r="R79" s="23" t="n">
-        <v>2.42</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>81.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>80.25</v>
+        <v>79.55</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>79.03</v>
+        <v>78.67</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>79.83</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>80.31999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>78.87</v>
+        <v>78.33</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>78.38</v>
+        <v>77.77</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>77.42</v>
+        <v>77.28</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>78.22</v>
+        <v>78.08</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="N80" s="20" t="inlineStr">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="N80" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>78.59999999999999</v>
+        <v>78.25</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>78.33</v>
+        <v>78.16</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="R80" s="23" t="n">
-        <v>2.19</v>
+        <v>78.25</v>
+      </c>
+      <c r="R80" s="25" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="G81" s="15" t="n">
-        <v>4.71</v>
+        <v>4.59</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="I81" s="17" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="K81" s="18" t="n">
         <v>4.48</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
+        <v>4.31</v>
+      </c>
+      <c r="N81" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="P81" s="21" t="n">
         <v>4.49</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R81" s="23" t="n">
-        <v>3.14</v>
+        <v>4.49</v>
+      </c>
+      <c r="R81" s="25" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>59.32</v>
+        <v>58.46</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>57.02</v>
+        <v>56.8</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>57.42</v>
+        <v>57.17</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>57.98</v>
+        <v>57.53</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>56.73</v>
+        <v>56.63</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>56.17</v>
+        <v>56.27</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>55.48</v>
+        <v>55.73</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>56.32</v>
+        <v>56.3</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>55.28</v>
+        <v>55.54</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>54.03</v>
-      </c>
-      <c r="N82" s="20" t="inlineStr">
+        <v>54.64</v>
+      </c>
+      <c r="N82" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>56.58</v>
+        <v>56.5</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>56.42</v>
+        <v>56.37</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="R82" s="23" t="n">
-        <v>0.98</v>
+        <v>56.8</v>
+      </c>
+      <c r="R82" s="25" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="83">
@@ -5718,54 +5718,54 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>38.67</v>
+        <v>37.79</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>38.13</v>
+        <v>37.49</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.68</v>
+        <v>37.23</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.62</v>
+        <v>37.29</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.98</v>
+        <v>37.45</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>37.44</v>
+        <v>37.15</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>37.08</v>
+        <v>36.99</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.9</v>
+        <v>36.85</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>37.38</v>
+        <v>37.07</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.93</v>
+        <v>36.81</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="N83" s="24" t="inlineStr">
+        <v>36.51</v>
+      </c>
+      <c r="N83" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>37.43</v>
+        <v>37.12</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>37.42</v>
+        <v>37.09</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>37.26</v>
-      </c>
-      <c r="R83" s="25" t="n">
-        <v>-0.6899999999999999</v>
+        <v>37.14</v>
+      </c>
+      <c r="R83" s="23" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>96.72</v>
+        <v>92.39</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>94.42</v>
+        <v>91.44</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>92.48999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>92.23</v>
+        <v>90.97</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>93.77</v>
+        <v>91.38</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>91.47</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>89.93000000000001</v>
+        <v>90.02</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>89.17</v>
+        <v>89.48</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>91.20999999999999</v>
+        <v>90.11</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>89.28</v>
+        <v>89.31</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>86.98</v>
-      </c>
-      <c r="N84" s="24" t="inlineStr">
+        <v>88.36</v>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>91.43000000000001</v>
+        <v>90.31</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.39</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="R84" s="25" t="n">
-        <v>-0.17</v>
+        <v>90.55</v>
+      </c>
+      <c r="R84" s="23" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.33</v>
+        <v>17.23</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.78</v>
+        <v>16.84</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.32</v>
+        <v>16.51</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.62</v>
+        <v>16.68</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.81</v>
+        <v>16.84</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.26</v>
+        <v>16.45</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.07</v>
+        <v>16.29</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>15.71</v>
+        <v>16.06</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>16.01</v>
+        <v>16.3</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>15.55</v>
+        <v>15.97</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
+        <v>15.58</v>
+      </c>
+      <c r="N85" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.16</v>
+        <v>16.39</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.05</v>
+        <v>16.33</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="R85" s="23" t="n">
-        <v>3.27</v>
+        <v>16.53</v>
+      </c>
+      <c r="R85" s="25" t="n">
+        <v>3.83</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>130.86</v>
+        <v>128.04</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>127.36</v>
+        <v>125.55</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>124.43</v>
+        <v>123.45</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>124.77</v>
+        <v>123.23</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>126.73</v>
+        <v>124.87</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>123.23</v>
+        <v>122.37</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>121.27</v>
+        <v>120.73</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>119.73</v>
+        <v>119.87</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>122.47</v>
+        <v>122.05</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>119.54</v>
+        <v>119.95</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>116.04</v>
-      </c>
-      <c r="N86" s="20" t="inlineStr">
+        <v>117.45</v>
+      </c>
+      <c r="N86" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>122.99</v>
+        <v>122.31</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>122.74</v>
+        <v>122.25</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>122.8</v>
+        <v>121.6</v>
       </c>
       <c r="R86" s="23" t="n">
-        <v>0.49</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>60.44</v>
+        <v>59.2</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>59.24</v>
+        <v>58.55</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>58.24</v>
+        <v>58.01</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>58.9</v>
+        <v>58.27</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>59.3</v>
+        <v>58.53</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>58.1</v>
+        <v>57.88</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>57.7</v>
+        <v>57.62</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>56.9</v>
+        <v>57.23</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>57.56</v>
+        <v>57.64</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>56.56</v>
+        <v>57.1</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>55.36</v>
+        <v>56.45</v>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>57.88</v>
+        <v>57.79</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>57.66</v>
+        <v>57.69</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>0.34</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="88">
@@ -6028,54 +6028,54 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>10.23</v>
+        <v>11.08</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.880000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>9.58</v>
+        <v>9.9</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>9.779999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>9.890000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.43</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J88" s="17" t="n">
         <v>9.19</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="N88" s="20" t="inlineStr">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="N88" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.48</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.41</v>
+        <v>9.59</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="R88" s="23" t="n">
-        <v>2.99</v>
+        <v>10.04</v>
+      </c>
+      <c r="R88" s="25" t="n">
+        <v>7.04</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>16.91</v>
+        <v>18.7</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.47</v>
+        <v>17.58</v>
       </c>
       <c r="E89" s="14" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I89" s="17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J89" s="17" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="K89" s="18" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="L89" s="19" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="M89" s="19" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O89" s="21" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="P89" s="21" t="n">
         <v>16.1</v>
       </c>
-      <c r="F89" s="15" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="G89" s="15" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="H89" s="16" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="I89" s="17" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="J89" s="17" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="K89" s="18" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="L89" s="19" t="n">
-        <v>15.49</v>
-      </c>
-      <c r="M89" s="19" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="N89" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O89" s="21" t="n">
+      <c r="Q89" s="22" t="n">
         <v>15.93</v>
       </c>
-      <c r="P89" s="21" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="Q89" s="22" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="R89" s="25" t="n">
-        <v>-0.87</v>
+      <c r="R89" s="23" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>17.86</v>
+        <v>21.72</v>
       </c>
       <c r="D90" s="13" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="F90" s="15" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J90" s="17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K90" s="18" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="L90" s="19" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M90" s="19" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="N90" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O90" s="21" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="P90" s="21" t="n">
         <v>17.48</v>
       </c>
-      <c r="E90" s="14" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="F90" s="15" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="G90" s="15" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="H90" s="16" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="I90" s="17" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="J90" s="17" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="K90" s="18" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="L90" s="19" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="M90" s="19" t="n">
-        <v>16.26</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O90" s="21" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="P90" s="21" t="n">
-        <v>16.98</v>
-      </c>
       <c r="Q90" s="22" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="R90" s="23" t="n">
-        <v>0.77</v>
+        <v>17.2</v>
+      </c>
+      <c r="R90" s="25" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.22</v>
+        <v>31.64</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.6</v>
+        <v>30.76</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>30.08</v>
+        <v>30.03</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>30.23</v>
+        <v>30.27</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.53</v>
+        <v>30.69</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.91</v>
+        <v>29.81</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.61</v>
+        <v>29.39</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>29.29</v>
+        <v>28.93</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.74</v>
+        <v>29.53</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>29.22</v>
+        <v>28.8</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>28.6</v>
+        <v>27.92</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.85</v>
+        <v>29.7</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.78</v>
+        <v>29.6</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.92</v>
-      </c>
-      <c r="R91" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>29.86</v>
+      </c>
+      <c r="R91" s="25" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.62</v>
+        <v>20.17</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>20.22</v>
+        <v>19.82</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.88</v>
+        <v>19.52</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.86</v>
+        <v>19.54</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>20.12</v>
+        <v>19.74</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.72</v>
+        <v>19.39</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>19.46</v>
+        <v>19.19</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>19.32</v>
+        <v>19.04</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>19.66</v>
+        <v>19.33</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>19.32</v>
+        <v>19.03</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="N92" s="24" t="inlineStr">
+        <v>18.68</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>19.7</v>
+        <v>19.37</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>19.69</v>
+        <v>19.35</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="R92" s="25" t="n">
-        <v>-1.06</v>
+        <v>19.33</v>
+      </c>
+      <c r="R92" s="23" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.14</v>
+        <v>26.08</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.92</v>
+        <v>25.65</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>25.93</v>
+        <v>25.67</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.09</v>
+        <v>25.97</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.83</v>
+        <v>25.45</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.67</v>
+        <v>25.15</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.57</v>
+        <v>24.93</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.78</v>
+        <v>25.35</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.56</v>
+        <v>24.92</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="N93" s="24" t="inlineStr">
+        <v>24.4</v>
+      </c>
+      <c r="N93" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.81</v>
+        <v>25.42</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.8</v>
+        <v>25.39</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="R93" s="25" t="n">
-        <v>-0.15</v>
+        <v>25.36</v>
+      </c>
+      <c r="R93" s="23" t="n">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>176.47</v>
+        <v>177.81</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>173.77</v>
+        <v>173.91</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>171.51</v>
+        <v>170.64</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>173.9</v>
+        <v>173.7</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>171.2</v>
+        <v>169.8</v>
       </c>
       <c r="I94" s="17" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="J94" s="17" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="K94" s="18" t="n">
+        <v>168.46</v>
+      </c>
+      <c r="L94" s="19" t="n">
+        <v>165.19</v>
+      </c>
+      <c r="M94" s="19" t="n">
+        <v>161.29</v>
+      </c>
+      <c r="N94" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O94" s="21" t="n">
+        <v>169.28</v>
+      </c>
+      <c r="P94" s="21" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="Q94" s="22" t="n">
         <v>170.3</v>
       </c>
-      <c r="J94" s="17" t="n">
-        <v>168.5</v>
-      </c>
-      <c r="K94" s="18" t="n">
-        <v>169.99</v>
-      </c>
-      <c r="L94" s="19" t="n">
-        <v>167.73</v>
-      </c>
-      <c r="M94" s="19" t="n">
-        <v>165.03</v>
-      </c>
-      <c r="N94" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O94" s="21" t="n">
-        <v>170.7</v>
-      </c>
-      <c r="P94" s="21" t="n">
-        <v>170.2</v>
-      </c>
-      <c r="Q94" s="22" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="R94" s="23" t="n">
-        <v>1.35</v>
+      <c r="R94" s="25" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>14.29</v>
+        <v>14.64</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>13.65</v>
+        <v>13.88</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>13.11</v>
+        <v>13.24</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>13.36</v>
+        <v>13.2</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>13.63</v>
+        <v>13.68</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>12.99</v>
+        <v>12.92</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>12.72</v>
+        <v>12.44</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>12.35</v>
+        <v>12.16</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>12.75</v>
+        <v>12.82</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>12.21</v>
+        <v>12.18</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>11.57</v>
+        <v>11.42</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>12.8</v>
+        <v>12.88</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>13.1</v>
+        <v>12.71</v>
       </c>
       <c r="R95" s="23" t="n">
-        <v>1.71</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>20.28</v>
+        <v>19.97</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>19.39</v>
+        <v>19.29</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.34</v>
+        <v>19.25</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.66</v>
+        <v>19.49</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>19.18</v>
+        <v>19.12</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>18.86</v>
+        <v>18.88</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.7</v>
+        <v>18.75</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>19.13</v>
+        <v>19.08</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.72</v>
+        <v>18.77</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="N96" s="24" t="inlineStr">
+        <v>18.4</v>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>19.17</v>
+        <v>19.12</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>19.16</v>
+        <v>19.11</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="R96" s="25" t="n">
-        <v>-2.41</v>
+        <v>19</v>
+      </c>
+      <c r="R96" s="23" t="n">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.17</v>
+        <v>18.59</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>15.91</v>
+        <v>17.4</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>15.69</v>
+        <v>16.4</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>15.84</v>
+        <v>17.06</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>15.92</v>
+        <v>17.45</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>15.66</v>
+        <v>16.26</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>15.58</v>
+        <v>15.87</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>15.4</v>
+        <v>15.07</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>15.55</v>
+        <v>15.73</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>15.33</v>
+        <v>14.73</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="N97" s="20" t="inlineStr">
+        <v>13.54</v>
+      </c>
+      <c r="N97" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>15.62</v>
+        <v>16.04</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.57</v>
+        <v>15.82</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="R97" s="23" t="n">
-        <v>1.68</v>
+        <v>16.66</v>
+      </c>
+      <c r="R97" s="25" t="n">
+        <v>7.55</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>9.369999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.44</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>9.279999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.210000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.220000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>9.08</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="N98" s="24" t="inlineStr">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.23</v>
+        <v>9.19</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R98" s="23" t="n">
-        <v>0.54</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>26.69</v>
+        <v>26.68</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25.94</v>
+        <v>25.89</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>25.31</v>
+        <v>25.23</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>25.68</v>
+        <v>25.48</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.95</v>
+        <v>25.83</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>25.2</v>
+        <v>25.04</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.93</v>
+        <v>24.69</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.45</v>
+        <v>24.25</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.89</v>
+        <v>24.78</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>24.27</v>
+        <v>24.12</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>23.52</v>
+        <v>23.33</v>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>25.08</v>
+        <v>24.94</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>24.95</v>
+        <v>24.85</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R99" s="23" t="n">
-        <v>1.28</v>
+        <v>25.12</v>
+      </c>
+      <c r="R99" s="25" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="100">
@@ -6781,19 +6781,19 @@
         <v>16.14</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>16.24</v>
+        <v>16.29</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.35</v>
+        <v>16.37</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>16.09</v>
+        <v>16.11</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>15.98</v>
+        <v>16.03</v>
       </c>
       <c r="J100" s="17" t="n">
-        <v>15.83</v>
+        <v>15.85</v>
       </c>
       <c r="K100" s="18" t="n">
         <v>16</v>
@@ -6804,22 +6804,22 @@
       <c r="M100" s="19" t="n">
         <v>15.52</v>
       </c>
-      <c r="N100" s="20" t="inlineStr">
+      <c r="N100" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>16.05</v>
+        <v>16.07</v>
       </c>
       <c r="P100" s="21" t="n">
         <v>16.02</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="R100" s="23" t="n">
-        <v>0.44</v>
+        <v>16.2</v>
+      </c>
+      <c r="R100" s="25" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>31.18</v>
+        <v>30.97</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.56</v>
+        <v>30.41</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>30.04</v>
+        <v>29.94</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>30.27</v>
+        <v>29.89</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.53</v>
+        <v>30.25</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.91</v>
+        <v>29.69</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>29.65</v>
+        <v>29.33</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>29.29</v>
+        <v>29.13</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.7</v>
+        <v>29.62</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>29.18</v>
+        <v>29.15</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>28.56</v>
+        <v>28.59</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.83</v>
+        <v>29.68</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>29.74</v>
+        <v>29.67</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="R101" s="25" t="n">
-        <v>-0.6</v>
+        <v>29.52</v>
+      </c>
+      <c r="R101" s="23" t="n">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="102">
@@ -6896,53 +6896,53 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="D102" s="13" t="n">
         <v>15.64</v>
       </c>
-      <c r="D102" s="13" t="n">
-        <v>15.13</v>
-      </c>
       <c r="E102" s="14" t="n">
-        <v>14.7</v>
+        <v>14.81</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.64</v>
+        <v>14.87</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>14.98</v>
+        <v>15.44</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.13</v>
+        <v>13.89</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>13.96</v>
+        <v>13.48</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.41</v>
+        <v>14.27</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.98</v>
+        <v>13.44</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="N102" s="24" t="inlineStr">
+        <v>12.46</v>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.46</v>
+        <v>14.4</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.45</v>
+        <v>14.34</v>
       </c>
       <c r="Q102" s="22" t="n">
         <v>14.3</v>
       </c>
-      <c r="R102" s="25" t="n">
+      <c r="R102" s="23" t="n">
         <v>-1.45</v>
       </c>
     </row>
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>70.01000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>68.86</v>
+        <v>68.77</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59</v>
       </c>
       <c r="F103" s="15" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="G103" s="15" t="n">
         <v>68.53</v>
       </c>
-      <c r="G103" s="15" t="n">
-        <v>68.92</v>
-      </c>
       <c r="H103" s="16" t="n">
-        <v>67.77</v>
+        <v>67.13</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>67.38</v>
+        <v>66.37</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>66.62</v>
+        <v>65.73</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>67.25</v>
+        <v>66.81</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>66.29000000000001</v>
+        <v>65.63</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>65.14</v>
+        <v>64.23</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>67.55</v>
+        <v>67.03</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>67.34</v>
+        <v>66.92</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>68.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>1.34</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.51</v>
+        <v>14.61</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.36</v>
+        <v>14.32</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.24</v>
+        <v>14.08</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>14.23</v>
+        <v>14.09</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.32</v>
+        <v>14.26</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>14.17</v>
+        <v>13.97</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>14.08</v>
+        <v>13.8</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>14.02</v>
+        <v>13.68</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>14.15</v>
+        <v>13.91</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>14.03</v>
+        <v>13.67</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="N104" s="24" t="inlineStr">
+        <v>13.38</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>14.17</v>
+        <v>13.95</v>
       </c>
       <c r="P104" s="21" t="n">
-        <v>14.16</v>
+        <v>13.94</v>
       </c>
       <c r="Q104" s="22" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="R104" s="25" t="n">
-        <v>-0.21</v>
+        <v>13.92</v>
+      </c>
+      <c r="R104" s="23" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>19.23</v>
+        <v>18.09</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>18.15</v>
+        <v>17.29</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>17.24</v>
+        <v>16.62</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.19</v>
+        <v>16.54</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>17.88</v>
+        <v>17.07</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>16.8</v>
+        <v>16.27</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>16.11</v>
+        <v>15.74</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.72</v>
+        <v>15.47</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>16.64</v>
+        <v>16.18</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.73</v>
+        <v>15.51</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.65</v>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
+        <v>14.71</v>
+      </c>
+      <c r="N105" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>16.76</v>
+        <v>16.25</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>16.72</v>
+        <v>16.24</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>16.51</v>
+        <v>16.01</v>
       </c>
       <c r="R105" s="23" t="n">
-        <v>1.41</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="106">
@@ -7147,51 +7147,51 @@
         <v>2.5</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="G106" s="15" t="n">
         <v>2.46</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="N106" s="24" t="inlineStr">
+        <v>2.34</v>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R106" s="25" t="n">
-        <v>-0.41</v>
+        <v>2.41</v>
+      </c>
+      <c r="R106" s="23" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>39.01</v>
+        <v>40.42</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>38.21</v>
+        <v>38.74</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>37.54</v>
+        <v>37.33</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>37.61</v>
+        <v>37.14</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>38.07</v>
+        <v>38.26</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>37.27</v>
+        <v>36.58</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>36.81</v>
+        <v>35.46</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>36.47</v>
+        <v>34.9</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>37.1</v>
+        <v>36.39</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>36.43</v>
+        <v>34.98</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>35.63</v>
-      </c>
-      <c r="N107" s="24" t="inlineStr">
+        <v>33.3</v>
+      </c>
+      <c r="N107" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>37.21</v>
+        <v>36.55</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>37.16</v>
+        <v>36.52</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="R107" s="25" t="n">
-        <v>-0.11</v>
+        <v>36.02</v>
+      </c>
+      <c r="R107" s="23" t="n">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.78</v>
+        <v>7.73</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.81</v>
+        <v>7.71</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>7.85</v>
+        <v>7.83</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.76</v>
+        <v>7.66</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.67</v>
+        <v>7.49</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.73</v>
+        <v>7.64</v>
       </c>
       <c r="L108" s="19" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O108" s="21" t="n">
         <v>7.65</v>
       </c>
-      <c r="M108" s="19" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="N108" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O108" s="21" t="n">
-        <v>7.75</v>
-      </c>
       <c r="P108" s="21" t="n">
-        <v>7.74</v>
+        <v>7.65</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="R108" s="25" t="n">
-        <v>-0.38</v>
+        <v>7.6</v>
+      </c>
+      <c r="R108" s="23" t="n">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.31</v>
+        <v>44.49</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>44.01</v>
+        <v>44.11</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.75</v>
+        <v>43.8</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.8</v>
+        <v>43.83</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.96</v>
+        <v>44.05</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.66</v>
+        <v>43.67</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>43.36</v>
+        <v>43.29</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>43.59</v>
+        <v>43.58</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>43.33</v>
+        <v>43.27</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="N109" s="24" t="inlineStr">
+        <v>42.89</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>43.63</v>
+        <v>43.64</v>
       </c>
       <c r="P109" s="21" t="n">
         <v>43.61</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="R109" s="25" t="n">
-        <v>-0.37</v>
+        <v>43.62</v>
+      </c>
+      <c r="R109" s="23" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>65.84</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>65.29000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.83</v>
+        <v>65.09</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>65.2</v>
+        <v>66.12</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.65000000000001</v>
+        <v>64.27</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>64.34999999999999</v>
+        <v>63.03</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>64.09999999999999</v>
+        <v>62.42</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>64.52</v>
+        <v>64.06</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>64.06</v>
+        <v>62.51</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>63.51</v>
+        <v>60.66</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>64.61</v>
+        <v>64.23</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>64.56</v>
+        <v>64.2</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>64.59999999999999</v>
+        <v>63.65</v>
       </c>
       <c r="R110" s="23" t="n">
-        <v>0.31</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="111">
@@ -7454,41 +7454,41 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
       <c r="E111" s="14" t="n">
         <v>10.09</v>
       </c>
       <c r="F111" s="15" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="G111" s="15" t="n">
         <v>10.14</v>
       </c>
-      <c r="G111" s="15" t="n">
-        <v>10.17</v>
-      </c>
       <c r="H111" s="16" t="n">
-        <v>10.08</v>
+        <v>10.06</v>
       </c>
       <c r="I111" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="17" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="K111" s="18" t="n">
         <v>10.05</v>
       </c>
-      <c r="J111" s="17" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="K111" s="18" t="n">
-        <v>10.04</v>
-      </c>
       <c r="L111" s="19" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>9.869999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
@@ -7498,10 +7498,10 @@
         <v>10.05</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="R111" s="23" t="n">
-        <v>1.1</v>
+        <v>10.03</v>
+      </c>
+      <c r="R111" s="25" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>321.42</v>
+        <v>332.62</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>313.62</v>
+        <v>318.02</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>307.08</v>
+        <v>305.79</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>309</v>
+        <v>304.93</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>312.8</v>
+        <v>314.27</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>305</v>
+        <v>299.67</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>301.2</v>
+        <v>290.33</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>297.2</v>
+        <v>285.07</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>302.72</v>
+        <v>297.61</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>296.18</v>
+        <v>285.38</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>288.38</v>
+        <v>270.78</v>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>304.16</v>
+        <v>299.21</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>303.32</v>
+        <v>298.75</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>305.2</v>
+        <v>295.6</v>
       </c>
       <c r="R112" s="23" t="n">
-        <v>1.06</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>233.09</v>
+        <v>230.59</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>228.09</v>
+        <v>226.89</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>223.9</v>
+        <v>223.79</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>226.67</v>
+        <v>223.83</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>228.33</v>
+        <v>226.07</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>223.33</v>
+        <v>222.37</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>221.67</v>
+        <v>220.13</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>218.33</v>
+        <v>218.67</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>221.1</v>
+        <v>221.71</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>216.91</v>
+        <v>218.61</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>211.91</v>
-      </c>
-      <c r="N113" s="20" t="inlineStr">
+        <v>214.91</v>
+      </c>
+      <c r="N113" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>222.41</v>
+        <v>222.18</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>221.49</v>
+        <v>222</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="R113" s="23" t="n">
-        <v>1.63</v>
+        <v>221.6</v>
+      </c>
+      <c r="R113" s="25" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>632.02</v>
+        <v>646.2</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>625.52</v>
+        <v>629.7</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>620.0700000000001</v>
+        <v>615.87</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>621.67</v>
+        <v>614</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>624.83</v>
+        <v>625</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>618.33</v>
+        <v>608.5</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>615.17</v>
+        <v>597.5</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>611.83</v>
+        <v>592</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>616.4299999999999</v>
+        <v>606.63</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>610.98</v>
+        <v>592.8</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>604.48</v>
+        <v>576.3</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>617.64</v>
+        <v>608.21</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>616.9400000000001</v>
+        <v>607.92</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>618.5</v>
+        <v>603</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>0.24</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.75</v>
+        <v>6.29</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.45</v>
+        <v>6.12</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>6.19</v>
+        <v>5.97</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>6.16</v>
+        <v>6.05</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>6.36</v>
+        <v>6.11</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="I115" s="17" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>6.03</v>
+        <v>5.88</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>5.77</v>
+        <v>5.73</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="N115" s="24" t="inlineStr">
+        <v>5.56</v>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>6.05</v>
+        <v>5.92</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>6.05</v>
+        <v>5.89</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="R115" s="25" t="n">
-        <v>-3.87</v>
+        <v>5.98</v>
+      </c>
+      <c r="R115" s="23" t="n">
+        <v>-3.55</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>96.73</v>
+        <v>96.02</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>94.98</v>
+        <v>93.72</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>93.52</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>93.75</v>
+        <v>91.53</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>94.7</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>92.95</v>
+        <v>90.77</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>92</v>
+        <v>89.23</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>91.2</v>
+        <v>88.47</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>92.54000000000001</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>91.06999999999999</v>
+        <v>88.58</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>89.31999999999999</v>
+        <v>86.28</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>92.81</v>
+        <v>90.73</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>92.67</v>
+        <v>90.69</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>92.8</v>
+        <v>90</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>10.19</v>
+        <v>10.62</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>10.04</v>
+        <v>10.11</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.92</v>
+        <v>9.68</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.9</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.85</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>9.75</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>9.699999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>9.83</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>9.710000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="N117" s="24" t="inlineStr">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>9.85</v>
+        <v>9.44</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>9.84</v>
+        <v>9.43</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="R117" s="25" t="n">
-        <v>-0.41</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R117" s="23" t="n">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>17.58</v>
+        <v>17.35</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>17.11</v>
+        <v>16.89</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.72</v>
+        <v>16.51</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.9</v>
+        <v>16.48</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>17.1</v>
+        <v>16.78</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>16.63</v>
+        <v>16.32</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>16.43</v>
+        <v>16.02</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>16.16</v>
+        <v>15.86</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>16.45</v>
+        <v>16.25</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>16.06</v>
+        <v>15.87</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.59</v>
+        <v>15.41</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.56</v>
+        <v>16.3</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.49</v>
+        <v>16.29</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.71</v>
+        <v>16.19</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>1.95</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.87</v>
+        <v>11.85</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.54</v>
+        <v>11.41</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>11.27</v>
+        <v>11.04</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>11.4</v>
+        <v>10.99</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.54</v>
+        <v>11.29</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>11.21</v>
+        <v>10.85</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>11.07</v>
+        <v>10.55</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.88</v>
+        <v>10.41</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>11.08</v>
+        <v>10.8</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.81</v>
+        <v>10.43</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.48</v>
+        <v>9.99</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>11.16</v>
+        <v>10.84</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>11.11</v>
+        <v>10.83</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>11.27</v>
+        <v>10.7</v>
       </c>
       <c r="R119" s="23" t="n">
-        <v>1.08</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.82</v>
+        <v>13.07</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.34</v>
+        <v>12.12</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.38</v>
+        <v>12.06</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.52</v>
+        <v>12.41</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>12.26</v>
+        <v>11.89</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>12.12</v>
+        <v>11.54</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>12</v>
+        <v>11.37</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>12.2</v>
+        <v>11.82</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>11.98</v>
+        <v>11.39</v>
       </c>
       <c r="M120" s="19" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="N120" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O120" s="21" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="P120" s="21" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="Q120" s="22" t="n">
         <v>11.72</v>
       </c>
-      <c r="N120" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O120" s="21" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="P120" s="21" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>12.24</v>
-      </c>
       <c r="R120" s="23" t="n">
-        <v>0.91</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>8.279999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.88</v>
+        <v>7.51</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>7.54</v>
+        <v>7.23</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.55</v>
+        <v>7.21</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.79</v>
+        <v>7.43</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.39</v>
+        <v>7.09</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>7.15</v>
+        <v>6.87</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.99</v>
+        <v>6.75</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>7.32</v>
+        <v>7.03</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>6.98</v>
+        <v>6.75</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="N121" s="24" t="inlineStr">
+        <v>6.41</v>
+      </c>
+      <c r="N121" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>7.37</v>
+        <v>7.07</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>7.35</v>
+        <v>7.06</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="R121" s="25" t="n">
-        <v>-1.62</v>
+        <v>7</v>
+      </c>
+      <c r="R121" s="23" t="n">
+        <v>-5.79</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>7.95</v>
+        <v>7.64</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>7.46</v>
+        <v>7.15</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>7.52</v>
+        <v>7.09</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>7.85</v>
+        <v>7.47</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>7.26</v>
+        <v>6.89</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.93</v>
+        <v>6.51</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>6.67</v>
+        <v>6.31</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>7.13</v>
+        <v>6.83</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>6.64</v>
+        <v>6.34</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="N122" s="24" t="inlineStr">
+        <v>5.76</v>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>7.22</v>
+        <v>6.88</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>7.18</v>
+        <v>6.87</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="R122" s="25" t="n">
-        <v>-3.75</v>
+        <v>6.7</v>
+      </c>
+      <c r="R122" s="23" t="n">
+        <v>-10.31</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>30.5</v>
+        <v>30.49</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>29.76</v>
+        <v>29.57</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>29.14</v>
+        <v>28.8</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>29.23</v>
+        <v>28.8</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>29.63</v>
+        <v>29.36</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.89</v>
+        <v>28.44</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>28.49</v>
+        <v>27.88</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>28.15</v>
+        <v>27.52</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>28.72</v>
+        <v>28.28</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>28.1</v>
+        <v>27.51</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>27.36</v>
+        <v>26.59</v>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>28.84</v>
+        <v>28.4</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>28.78</v>
+        <v>28.35</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>28.82</v>
+        <v>28.24</v>
       </c>
       <c r="R123" s="23" t="n">
-        <v>1.26</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>172.5</v>
+        <v>171.1</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>167.8</v>
+        <v>165.6</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>163.87</v>
+        <v>160.99</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>164.67</v>
+        <v>160.37</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>167.13</v>
+        <v>164.03</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>162.43</v>
+        <v>158.53</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>159.97</v>
+        <v>154.87</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>157.73</v>
+        <v>153.03</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>161.23</v>
+        <v>157.91</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>157.3</v>
+        <v>153.3</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>152.6</v>
+        <v>147.8</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>162.02</v>
+        <v>158.44</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>161.6</v>
+        <v>158.34</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>162.2</v>
+        <v>156.7</v>
       </c>
       <c r="R124" s="23" t="n">
-        <v>1.19</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>59.79</v>
+        <v>56.97</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>57.94</v>
+        <v>55.72</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>56.39</v>
+        <v>54.68</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>56.28</v>
+        <v>54.73</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>57.47</v>
+        <v>55.47</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>55.62</v>
+        <v>54.22</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>54.43</v>
+        <v>53.48</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>53.77</v>
+        <v>52.97</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>55.36</v>
+        <v>53.98</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>53.81</v>
+        <v>52.93</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>51.96</v>
+        <v>51.68</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>55.56</v>
+        <v>54.14</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>55.5</v>
+        <v>54.07</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>55.1</v>
+        <v>54</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>0.18</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>15.44</v>
+        <v>14.16</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>14.55</v>
+        <v>13.62</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.8</v>
+        <v>13.17</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.93</v>
+        <v>13.14</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>14.41</v>
+        <v>13.49</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13.52</v>
+        <v>12.95</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.04</v>
+        <v>12.6</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.63</v>
+        <v>12.41</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>13.31</v>
+        <v>12.87</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.56</v>
+        <v>12.42</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="N126" s="24" t="inlineStr">
+        <v>11.88</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.45</v>
+        <v>12.93</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.38</v>
+        <v>12.91</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="R126" s="25" t="n">
-        <v>-1.47</v>
+        <v>12.8</v>
+      </c>
+      <c r="R126" s="23" t="n">
+        <v>-6.23</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>16.12</v>
+        <v>16.15</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15.6</v>
+        <v>15.48</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>15.17</v>
+        <v>14.92</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>15.36</v>
+        <v>14.85</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>15.58</v>
+        <v>15.29</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>15.06</v>
+        <v>14.62</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.84</v>
+        <v>14.18</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>14.54</v>
+        <v>13.95</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.87</v>
+        <v>14.55</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>14.44</v>
+        <v>13.99</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13.92</v>
+        <v>13.32</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.99</v>
+        <v>14.61</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.91</v>
+        <v>14.6</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>15.14</v>
+        <v>14.4</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>2.57</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>7.69</v>
+        <v>7.48</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>7.28</v>
+        <v>6.97</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>6.94</v>
+        <v>6.54</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>6.91</v>
+        <v>6.53</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>7.18</v>
+        <v>6.85</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.77</v>
+        <v>6.34</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.5</v>
+        <v>6.02</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>6.36</v>
+        <v>5.83</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>6.37</v>
+        <v>5.82</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="N128" s="24" t="inlineStr">
+        <v>5.31</v>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.75</v>
+        <v>6.31</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.74</v>
+        <v>6.29</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="R128" s="25" t="n">
-        <v>-3.62</v>
+        <v>6.22</v>
+      </c>
+      <c r="R128" s="23" t="n">
+        <v>-9.859999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>10.32</v>
+        <v>10.7</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.93</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.6</v>
+        <v>9.16</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>9.449999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>9.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.390000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>9.06</v>
+        <v>7.98</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="N129" s="24" t="inlineStr">
+        <v>7.14</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>9.43</v>
+        <v>8.85</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.42</v>
+        <v>8.75</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="R129" s="25" t="n">
-        <v>-2.6</v>
+        <v>9</v>
+      </c>
+      <c r="R129" s="23" t="n">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>155.4</v>
+        <v>150.76</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>150.7</v>
+        <v>148.56</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>146.77</v>
+        <v>146.72</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>148.97</v>
+        <v>147.8</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>150.73</v>
+        <v>148.6</v>
       </c>
       <c r="H130" s="16" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="J130" s="17" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="K130" s="18" t="n">
+        <v>145.48</v>
+      </c>
+      <c r="L130" s="19" t="n">
+        <v>143.64</v>
+      </c>
+      <c r="M130" s="19" t="n">
+        <v>141.44</v>
+      </c>
+      <c r="N130" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O130" s="21" t="n">
         <v>146.03</v>
       </c>
-      <c r="I130" s="17" t="n">
-        <v>144.27</v>
-      </c>
-      <c r="J130" s="17" t="n">
-        <v>141.33</v>
-      </c>
-      <c r="K130" s="18" t="n">
-        <v>144.13</v>
-      </c>
-      <c r="L130" s="19" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="M130" s="19" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="N130" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O130" s="21" t="n">
-        <v>145.27</v>
-      </c>
       <c r="P130" s="21" t="n">
-        <v>144.5</v>
+        <v>145.66</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>147.2</v>
+        <v>147</v>
       </c>
       <c r="R130" s="23" t="n">
-        <v>3.81</v>
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -253,10 +253,10 @@
     <xf numFmtId="2" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-20</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.5</v>
+        <v>20.39</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.31</v>
+        <v>20.24</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.15</v>
+        <v>20.12</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.16</v>
+        <v>20.11</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.27</v>
+        <v>20.2</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.08</v>
+        <v>20.05</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>19.97</v>
+        <v>19.96</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>19.89</v>
+        <v>19.9</v>
       </c>
       <c r="K3" s="18" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="L3" s="19" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M3" s="19" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="N3" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="P3" s="21" t="n">
         <v>20.04</v>
       </c>
-      <c r="L3" s="19" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O3" s="21" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="P3" s="21" t="n">
-        <v>20.06</v>
-      </c>
       <c r="Q3" s="22" t="n">
-        <v>20.05</v>
+        <v>20.01</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>11.97</v>
+        <v>12.07</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.86</v>
+        <v>11.91</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>11.77</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.77</v>
+        <v>11.79</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.83</v>
+        <v>11.88</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>11.72</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.66</v>
+        <v>11.63</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>11.61</v>
+        <v>11.56</v>
       </c>
       <c r="K4" s="18" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>11.7</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>11.61</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>11.71</v>
       </c>
       <c r="Q4" s="22" t="n">
         <v>11.7</v>
       </c>
-      <c r="R4" s="23" t="n">
-        <v>-0.85</v>
+      <c r="R4" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15.16</v>
+        <v>14.97</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.88</v>
+        <v>14.79</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.65</v>
+        <v>14.64</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.64</v>
+        <v>14.71</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.82</v>
+        <v>14.78</v>
       </c>
       <c r="H5" s="16" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="K5" s="18" t="n">
         <v>14.54</v>
       </c>
-      <c r="I5" s="17" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>14.26</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>14.49</v>
-      </c>
       <c r="L5" s="19" t="n">
-        <v>14.26</v>
+        <v>14.39</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>14.21</v>
+      </c>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.53</v>
+        <v>14.58</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.51</v>
+        <v>14.55</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="R5" s="23" t="n">
-        <v>-2.49</v>
+        <v>14.63</v>
+      </c>
+      <c r="R5" s="24" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>22.33</v>
+        <v>21.81</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.73</v>
+        <v>21.36</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.23</v>
+        <v>20.98</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.17</v>
+        <v>21.21</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.57</v>
+        <v>21.37</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>20.97</v>
+        <v>20.92</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>20.57</v>
+        <v>20.76</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>20.37</v>
+        <v>20.47</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>20.89</v>
+        <v>20.73</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.39</v>
+        <v>20.35</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>19.9</v>
+      </c>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>20.95</v>
+        <v>20.84</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>20.94</v>
+        <v>20.76</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="R6" s="23" t="n">
-        <v>-4.59</v>
+        <v>21.05</v>
+      </c>
+      <c r="R6" s="24" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.37</v>
+        <v>34.01</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.81</v>
+        <v>33.63</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.34</v>
+        <v>33.32</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.27</v>
+        <v>33.45</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>33.65</v>
+        <v>33.61</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.09</v>
+        <v>33.23</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>32.71</v>
+        <v>33.07</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>32.53</v>
+        <v>32.85</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.02</v>
+        <v>33.1</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.55</v>
+        <v>32.79</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>32.41</v>
+      </c>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.08</v>
+        <v>33.18</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.07</v>
+        <v>33.13</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R7" s="23" t="n">
-        <v>-1.2</v>
+        <v>33.28</v>
+      </c>
+      <c r="R7" s="24" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.76</v>
+        <v>23.29</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.29</v>
+        <v>23.05</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.9</v>
+        <v>22.85</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>23.16</v>
+        <v>22.93</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.31</v>
+        <v>23.03</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.84</v>
+        <v>22.79</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>22.69</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.37</v>
+        <v>22.55</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>22.63</v>
+        <v>22.71</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>22.24</v>
+        <v>22.51</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>21.77</v>
-      </c>
-      <c r="N8" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>22.27</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
         <v>22.76</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>22.67</v>
+        <v>22.73</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="R8" s="25" t="n">
-        <v>0.79</v>
+        <v>22.82</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="9">
@@ -1130,37 +1130,37 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>123.63</v>
+        <v>123.65</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>122.13</v>
+        <v>121.95</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>120.87</v>
+        <v>120.53</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>121.7</v>
+        <v>120.47</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>122.2</v>
+        <v>121.53</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>120.7</v>
+        <v>119.83</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>120.2</v>
+        <v>118.77</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>119.2</v>
+        <v>118.13</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>120.03</v>
+        <v>119.57</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>118.77</v>
+        <v>118.15</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>117.27</v>
+        <v>116.45</v>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>120.42</v>
+        <v>119.77</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>120.15</v>
+        <v>119.71</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>121.2</v>
+        <v>119.4</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>-1.54</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>67.11</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>66.61</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>66.19</v>
+        <v>66.34</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>66.37</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>66.08</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>65.87</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>65.58</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>65.91</v>
+        <v>66.06</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>65.48999999999999</v>
+        <v>65.64</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="N10" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>65.14</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>65.95</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="R10" s="25" t="n">
-        <v>0.38</v>
+        <v>66.05</v>
+      </c>
+      <c r="R10" s="23" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>24.98</v>
+        <v>25.22</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.74</v>
+        <v>24.85</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>24.54</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.54</v>
+        <v>24.58</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.68</v>
+        <v>24.78</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.44</v>
+        <v>24.41</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.3</v>
+        <v>24.21</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.2</v>
+        <v>24.04</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.4</v>
+        <v>24.33</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>24.2</v>
+        <v>24.02</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>23.96</v>
+        <v>23.65</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.43</v>
+        <v>24.39</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.42</v>
+        <v>24.36</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.39</v>
+        <v>24.37</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>-2.44</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.25</v>
+        <v>25.38</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25.03</v>
+        <v>25.02</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.84</v>
+        <v>24.72</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.82</v>
+        <v>24.72</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.96</v>
+        <v>24.94</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.74</v>
+        <v>24.58</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.6</v>
+        <v>24.36</v>
       </c>
       <c r="J12" s="17" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="K12" s="18" t="n">
         <v>24.52</v>
       </c>
-      <c r="K12" s="18" t="n">
-        <v>24.72</v>
-      </c>
       <c r="L12" s="19" t="n">
-        <v>24.53</v>
+        <v>24.22</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>24.31</v>
-      </c>
-      <c r="N12" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>23.86</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.74</v>
+        <v>24.56</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.74</v>
+        <v>24.55</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="R12" s="25" t="n">
-        <v>0</v>
+        <v>24.5</v>
+      </c>
+      <c r="R12" s="23" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>40.81</v>
+        <v>41.44</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>40.43</v>
+        <v>40.86</v>
       </c>
       <c r="E13" s="14" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="n">
         <v>40.12</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>40.33</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>40.07</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="L13" s="19" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O13" s="21" t="n">
+      <c r="P13" s="21" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="Q13" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="P13" s="21" t="n">
-        <v>39.93</v>
-      </c>
-      <c r="Q13" s="22" t="n">
-        <v>40.2</v>
-      </c>
       <c r="R13" s="23" t="n">
-        <v>-1.23</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1440,37 +1440,37 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.609999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.49</v>
+        <v>8.43</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.390000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="F14" s="15" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>8.41</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>8.48</v>
-      </c>
       <c r="H14" s="16" t="n">
-        <v>8.359999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="O14" s="21" t="n">
-        <v>8.35</v>
+        <v>8.31</v>
       </c>
       <c r="P14" s="21" t="n">
-        <v>8.34</v>
+        <v>8.31</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.35</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R14" s="23" t="n">
-        <v>-1.07</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="15">
@@ -1502,37 +1502,37 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>14.85</v>
+        <v>14.79</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.44</v>
+        <v>14.22</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>14.1</v>
+        <v>13.74</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>14.11</v>
+        <v>13.75</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>14.35</v>
+        <v>14.09</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.94</v>
+        <v>13.52</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.7</v>
+        <v>13.18</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.53</v>
+        <v>12.95</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.87</v>
+        <v>13.43</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.53</v>
+        <v>12.95</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>13.12</v>
+        <v>12.38</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.92</v>
+        <v>13.5</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.9</v>
+        <v>13.47</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.86</v>
+        <v>13.4</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>-0.22</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="K16" s="18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="P16" s="21" t="n">
         <v>3.8</v>
       </c>
-      <c r="L16" s="19" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>3.82</v>
-      </c>
       <c r="Q16" s="22" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>-10.87</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.18</v>
+        <v>17.68</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.01</v>
+        <v>17.23</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>16.86</v>
+        <v>16.85</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>16.9</v>
+        <v>17.03</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>16.99</v>
+        <v>17.21</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.82</v>
+        <v>16.76</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.73</v>
+        <v>16.58</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.65</v>
+        <v>16.31</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>16.77</v>
+        <v>16.6</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.62</v>
+        <v>16.22</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>15.77</v>
+      </c>
+      <c r="N17" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>16.78</v>
+        <v>16.63</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="R17" s="23" t="n">
-        <v>-0.18</v>
+        <v>16.84</v>
+      </c>
+      <c r="R17" s="24" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -1688,37 +1688,37 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.82</v>
+        <v>23.82</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.25</v>
+        <v>23.63</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>23.77</v>
+        <v>23.47</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>23.72</v>
+        <v>23.5</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>23.53</v>
+        <v>23.41</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.15</v>
+        <v>23.31</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>22.96</v>
+        <v>23.22</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.46</v>
+        <v>23.36</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>22.98</v>
+        <v>23.2</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>22.41</v>
+        <v>23.01</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.51</v>
+        <v>23.39</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.5</v>
+        <v>23.38</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.35</v>
-      </c>
-      <c r="R18" s="23" t="n">
-        <v>-1.97</v>
+        <v>23.4</v>
+      </c>
+      <c r="R18" s="24" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>65.08</v>
+        <v>65.33</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>63.73</v>
+        <v>63.98</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>62.6</v>
+        <v>62.85</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>63.35</v>
+        <v>63.2</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.8</v>
+        <v>63.85</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>62.45</v>
+        <v>62.5</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>62</v>
+        <v>61.85</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61.1</v>
+        <v>61.15</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>61.85</v>
+        <v>62.1</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.72</v>
+        <v>60.97</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="N19" s="24" t="inlineStr">
+        <v>59.62</v>
+      </c>
+      <c r="N19" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="P19" s="21" t="n">
         <v>62.2</v>
       </c>
-      <c r="P19" s="21" t="n">
-        <v>61.95</v>
-      </c>
       <c r="Q19" s="22" t="n">
-        <v>62.9</v>
+        <v>62.55</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>-0.16</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1812,37 +1812,37 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.29</v>
+        <v>11.06</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>11.04</v>
+        <v>10.89</v>
       </c>
       <c r="E20" s="14" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="G20" s="15" t="n">
         <v>10.84</v>
       </c>
-      <c r="F20" s="15" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>11</v>
-      </c>
       <c r="H20" s="16" t="n">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>10.6</v>
+        <v>10.56</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>10.5</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>10.7</v>
+        <v>10.65</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>10.49</v>
+        <v>10.5</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>10.24</v>
+        <v>10.33</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="O20" s="21" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="P20" s="21" t="n">
-        <v>10.71</v>
+        <v>10.66</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="R20" s="23" t="n">
-        <v>-2.01</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="21">
@@ -1874,19 +1874,19 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.72</v>
+        <v>17.69</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.33</v>
+        <v>17.31</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>17</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>16.96</v>
+        <v>16.95</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.22</v>
+        <v>17.21</v>
       </c>
       <c r="H21" s="16" t="n">
         <v>16.83</v>
@@ -1895,16 +1895,16 @@
         <v>16.57</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.44</v>
+        <v>16.45</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.46</v>
+        <v>16.47</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.07</v>
+        <v>16.09</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
@@ -1915,13 +1915,13 @@
         <v>16.82</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>16.82</v>
+        <v>16.81</v>
       </c>
       <c r="Q21" s="22" t="n">
         <v>16.7</v>
       </c>
-      <c r="R21" s="23" t="n">
-        <v>-4.02</v>
+      <c r="R21" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37.48</v>
+        <v>36.88</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.54</v>
+        <v>36.14</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.75</v>
+        <v>35.52</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>36.1</v>
+        <v>35.57</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>36.5</v>
+        <v>35.99</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.56</v>
+        <v>35.25</v>
       </c>
       <c r="I22" s="17" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="P22" s="21" t="n">
         <v>35.16</v>
       </c>
-      <c r="J22" s="17" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="L22" s="19" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="N22" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>35.43</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>35.3</v>
-      </c>
       <c r="Q22" s="22" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="R22" s="25" t="n">
-        <v>2.88</v>
+        <v>35.14</v>
+      </c>
+      <c r="R22" s="23" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.61</v>
+        <v>16.52</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>16.11</v>
+        <v>16.08</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.69</v>
+        <v>15.71</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.97</v>
+        <v>15.66</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>16.13</v>
+        <v>15.96</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.63</v>
+        <v>15.52</v>
       </c>
       <c r="I23" s="17" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="K23" s="18" t="n">
         <v>15.47</v>
       </c>
-      <c r="J23" s="17" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>15.41</v>
-      </c>
       <c r="L23" s="19" t="n">
-        <v>14.99</v>
+        <v>15.1</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="N23" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.66</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.54</v>
+        <v>15.51</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15.45</v>
+        <v>15.5</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="R23" s="25" t="n">
-        <v>6.54</v>
+        <v>15.37</v>
+      </c>
+      <c r="R23" s="23" t="n">
+        <v>-2.72</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.09</v>
+        <v>37</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.29</v>
+        <v>36.28</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.62</v>
+        <v>35.68</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.91</v>
+        <v>35.79</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.25</v>
+        <v>36.17</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>35.45</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>35.11</v>
+        <v>35.07</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>34.65</v>
+        <v>34.73</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>35.18</v>
+        <v>35.28</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.51</v>
+        <v>34.68</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="N24" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>33.96</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.35</v>
+        <v>35.39</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>35.24</v>
+        <v>35.33</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="R24" s="25" t="n">
-        <v>1.72</v>
+        <v>35.4</v>
+      </c>
+      <c r="R24" s="23" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>58.56</v>
+        <v>61.51</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.66</v>
+        <v>59.31</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.9</v>
+        <v>57.47</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>57</v>
+        <v>57.95</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>57.5</v>
+        <v>59.05</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>56.6</v>
+        <v>56.85</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>56.1</v>
+        <v>55.75</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>55.7</v>
+        <v>54.65</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>56.4</v>
+        <v>56.23</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>55.64</v>
+        <v>54.39</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="N25" s="24" t="inlineStr">
+        <v>52.19</v>
+      </c>
+      <c r="N25" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>56.53</v>
+        <v>56.63</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>56.47</v>
+        <v>56.41</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="R25" s="25" t="n">
-        <v>1.25</v>
+        <v>56.85</v>
+      </c>
+      <c r="R25" s="24" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>227.87</v>
+        <v>226.69</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>221.77</v>
+        <v>220.39</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>216.66</v>
+        <v>215.11</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>217.37</v>
+        <v>216.27</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>220.73</v>
+        <v>219.53</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>214.63</v>
+        <v>213.23</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>211.27</v>
+        <v>209.97</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>208.53</v>
+        <v>206.93</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>213.24</v>
+        <v>211.59</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>208.13</v>
+        <v>206.31</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>202.03</v>
-      </c>
-      <c r="N26" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>200.01</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>214.18</v>
+        <v>212.66</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>213.72</v>
+        <v>212.08</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>214</v>
-      </c>
-      <c r="R26" s="25" t="n">
-        <v>4.95</v>
+        <v>213</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="27">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>81.45</v>
+        <v>84.33</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>80</v>
+        <v>81.78</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>78.78</v>
+        <v>79.64</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>79.52</v>
+        <v>79.48</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>80.03</v>
+        <v>81.12</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>78.58</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>78.06999999999999</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>77.13</v>
+        <v>76.02</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>77.97</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>76.75</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>75.3</v>
+        <v>73.52</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>78.33</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>78.08</v>
+        <v>78.41</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>79</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="R27" s="23" t="n">
-        <v>-0.32</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>20.69</v>
+        <v>21.4</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.42</v>
+        <v>20.89</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.19</v>
+        <v>20.46</v>
       </c>
       <c r="F28" s="15" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="N28" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="P28" s="21" t="n">
         <v>20.21</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="J28" s="17" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="L28" s="19" t="n">
-        <v>19.81</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>20.06</v>
-      </c>
       <c r="Q28" s="22" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>-0.89</v>
+        <v>20.3</v>
+      </c>
+      <c r="R28" s="24" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="29">
@@ -2370,37 +2370,37 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>85.73999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>82.44</v>
+        <v>79.48</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>79.67</v>
+        <v>77.47</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>79.5</v>
+        <v>77.73</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>81.59999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>78.3</v>
+        <v>76.67</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>76.2</v>
+        <v>75.33</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>75</v>
+        <v>74.27</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>77.83</v>
+        <v>76.13</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>75.06</v>
+        <v>74.12</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>71.76000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -2408,16 +2408,16 @@
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>78.19</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>78.08</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>77.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>-2.21</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>28.59</v>
+        <v>28.24</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>27.79</v>
+        <v>27.4</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>27.12</v>
+        <v>26.7</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.09</v>
+        <v>27.11</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>27.59</v>
+        <v>27.41</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>26.79</v>
+        <v>26.57</v>
       </c>
       <c r="I30" s="17" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O30" s="21" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="P30" s="21" t="n">
         <v>26.29</v>
       </c>
-      <c r="J30" s="17" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>26.68</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>26.01</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O30" s="21" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>26.74</v>
-      </c>
       <c r="Q30" s="22" t="n">
-        <v>26.58</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <v>-4.8</v>
+        <v>26.8</v>
+      </c>
+      <c r="R30" s="24" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="31">
@@ -2494,37 +2494,37 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.05</v>
+        <v>48.35</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>48.39</v>
+        <v>47.85</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.83</v>
+        <v>47.43</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.89</v>
+        <v>47.68</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>48.27</v>
+        <v>47.86</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.61</v>
+        <v>47.36</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.23</v>
+        <v>47.18</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>46.95</v>
+        <v>46.86</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.47</v>
+        <v>47.15</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.91</v>
+        <v>46.73</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.25</v>
+        <v>46.23</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.56</v>
+        <v>47.27</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.52</v>
+        <v>47.19</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.52</v>
+        <v>47.5</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>-1.08</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>130.4</v>
+        <v>129.81</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>128.3</v>
+        <v>127.21</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>126.54</v>
+        <v>125.03</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>126.3</v>
+        <v>124.73</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>127.7</v>
+        <v>126.47</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>125.6</v>
+        <v>123.87</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>124.2</v>
+        <v>122.13</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>123.5</v>
+        <v>121.27</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>125.36</v>
+        <v>123.57</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>123.6</v>
+        <v>121.39</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="N32" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>118.79</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>125.56</v>
+        <v>123.82</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>125.53</v>
+        <v>123.77</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="R32" s="25" t="n">
-        <v>1.96</v>
+        <v>123</v>
+      </c>
+      <c r="R32" s="23" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="33">
@@ -2618,37 +2618,37 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>59.57</v>
+        <v>58.52</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>57.67</v>
+        <v>56.47</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>56.08</v>
+        <v>54.75</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>56.13</v>
+        <v>54.62</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>57.27</v>
+        <v>55.93</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>55.37</v>
+        <v>53.88</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>54.23</v>
+        <v>52.57</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>53.47</v>
+        <v>51.83</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>55.02</v>
+        <v>53.6</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>53.43</v>
+        <v>51.88</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>51.53</v>
+        <v>49.83</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>55.27</v>
+        <v>53.82</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>55.17</v>
+        <v>53.76</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>55</v>
+        <v>53.3</v>
       </c>
       <c r="R33" s="23" t="n">
-        <v>-3.59</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.55</v>
+        <v>23.84</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.96</v>
+        <v>23.44</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.47</v>
+        <v>23.1</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.48</v>
+        <v>23.22</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.83</v>
+        <v>23.4</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.24</v>
+        <v>23</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>22.89</v>
+        <v>22.82</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>23.14</v>
+        <v>22.88</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.65</v>
+        <v>22.54</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="N34" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>22.14</v>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>23.21</v>
+        <v>22.96</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.19</v>
+        <v>22.91</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="R34" s="25" t="n">
-        <v>1.23</v>
+        <v>23.03</v>
+      </c>
+      <c r="R34" s="23" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.54</v>
+        <v>26.11</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>26.08</v>
+        <v>25.66</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.7</v>
+        <v>25.28</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.65</v>
+        <v>25.23</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.95</v>
+        <v>25.53</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.49</v>
+        <v>25.08</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.19</v>
+        <v>24.78</v>
       </c>
       <c r="J35" s="17" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="K35" s="18" t="n">
         <v>25.03</v>
       </c>
-      <c r="K35" s="18" t="n">
-        <v>25.44</v>
-      </c>
       <c r="L35" s="19" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="P35" s="21" t="n">
         <v>25.06</v>
       </c>
-      <c r="M35" s="19" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="P35" s="21" t="n">
-        <v>25.48</v>
-      </c>
       <c r="Q35" s="22" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="R35" s="25" t="n">
-        <v>0.08</v>
+        <v>24.93</v>
+      </c>
+      <c r="R35" s="23" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="36">
@@ -2804,37 +2804,37 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>9.15</v>
+        <v>8.94</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.92</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.73</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.710000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.630000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>8.48</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>8.4</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>8.6</v>
+        <v>8.41</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>8.41</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.56</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="R36" s="23" t="n">
-        <v>-2.06</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>34.16</v>
+        <v>33.99</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>33.28</v>
+        <v>33.03</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>32.55</v>
+        <v>32.23</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>32.45</v>
+        <v>32.64</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>33.03</v>
+        <v>33.02</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>32.15</v>
+        <v>32.06</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>31.57</v>
+        <v>31.68</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.27</v>
+        <v>31.1</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>32.05</v>
+        <v>31.69</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.32</v>
+        <v>30.89</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="N37" s="24" t="inlineStr">
+        <v>29.93</v>
+      </c>
+      <c r="N37" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>32.14</v>
+        <v>31.91</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>32.12</v>
+        <v>31.77</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="R37" s="25" t="n">
-        <v>5.22</v>
+        <v>32.26</v>
+      </c>
+      <c r="R37" s="24" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="38">
@@ -2928,37 +2928,37 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>186</v>
+        <v>189.54</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>181.8</v>
+        <v>181.54</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>178.28</v>
+        <v>174.84</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>177.8</v>
+        <v>174.2</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>180.6</v>
+        <v>179.4</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>176.4</v>
+        <v>171.4</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>173.6</v>
+        <v>166.2</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>172.2</v>
+        <v>163.4</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>175.92</v>
+        <v>170.36</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>172.4</v>
+        <v>163.66</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>168.2</v>
+        <v>155.66</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>176.33</v>
+        <v>171.19</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>176.25</v>
+        <v>170.98</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="R38" s="23" t="n">
-        <v>-3.58</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="N39" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="Q39" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="R39" s="25" t="n">
+      <c r="R39" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,37 +3052,37 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>23.62</v>
+        <v>22.05</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>22.62</v>
+        <v>21.65</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.78</v>
+        <v>21.31</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.67</v>
+        <v>21.3</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>22.33</v>
+        <v>21.55</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.33</v>
+        <v>21.15</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>20.67</v>
+        <v>20.9</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.33</v>
+        <v>20.75</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>21.22</v>
+        <v>21.09</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.38</v>
+        <v>20.75</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>19.38</v>
+        <v>20.35</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.32</v>
+        <v>21.13</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.3</v>
+        <v>21.12</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>-2.78</v>
+        <v>21.05</v>
+      </c>
+      <c r="R40" s="24" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>194.98</v>
+        <v>189.82</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>189.68</v>
+        <v>186.22</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>185.23</v>
+        <v>183.21</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>185.23</v>
+        <v>183.2</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>188.47</v>
+        <v>185.4</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>183.17</v>
+        <v>181.8</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>179.93</v>
+        <v>179.6</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>177.87</v>
+        <v>178.2</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>182.27</v>
+        <v>181.19</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>177.82</v>
+        <v>178.18</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>172.52</v>
-      </c>
-      <c r="N41" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>174.58</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>182.92</v>
+        <v>181.64</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>182.68</v>
+        <v>181.47</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>182</v>
-      </c>
-      <c r="R41" s="25" t="n">
-        <v>1.11</v>
+        <v>181</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="42">
@@ -3176,37 +3176,37 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>37.4</v>
+        <v>36.99</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.82</v>
+        <v>36.55</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.33</v>
+        <v>36.18</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>36.35</v>
+        <v>36.21</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>36.11</v>
+        <v>36.03</v>
       </c>
       <c r="I42" s="17" t="n">
         <v>35.77</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.53</v>
+        <v>35.59</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>36.01</v>
+        <v>35.94</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>35.52</v>
+        <v>35.57</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>34.94</v>
+        <v>35.13</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>36.08</v>
+        <v>36</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>36.05</v>
+        <v>35.97</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>36</v>
+        <v>35.96</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>-0.72</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27.87</v>
+        <v>27.75</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.27</v>
+        <v>27.25</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>26.77</v>
+        <v>26.83</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>26.98</v>
+        <v>26.85</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.24</v>
+        <v>27.15</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>26.64</v>
+        <v>26.65</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>26.38</v>
+        <v>26.35</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.04</v>
+        <v>26.15</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>26.43</v>
+        <v>26.55</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>25.93</v>
+        <v>26.13</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="N43" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.63</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="Q43" s="22" t="n">
         <v>26.56</v>
       </c>
-      <c r="P43" s="21" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="Q43" s="22" t="n">
-        <v>26.72</v>
-      </c>
-      <c r="R43" s="25" t="n">
-        <v>0.07000000000000001</v>
+      <c r="R43" s="23" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.77</v>
+        <v>26.09</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>26.23</v>
+        <v>25.91</v>
       </c>
       <c r="E44" s="14" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="F44" s="15" t="n">
         <v>25.78</v>
       </c>
-      <c r="F44" s="15" t="n">
-        <v>26.08</v>
-      </c>
       <c r="G44" s="15" t="n">
-        <v>26.26</v>
+        <v>25.88</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.72</v>
+        <v>25.7</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.54</v>
+        <v>25.6</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.18</v>
+        <v>25.52</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.48</v>
+        <v>25.66</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.03</v>
+        <v>25.51</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>24.49</v>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>25.33</v>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.62</v>
+        <v>25.69</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.52</v>
+        <v>25.67</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R44" s="25" t="n">
-        <v>0.86</v>
+        <v>25.68</v>
+      </c>
+      <c r="R44" s="23" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="45">
@@ -3371,19 +3371,19 @@
         <v>7.49</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.53</v>
+        <v>7.47</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.6</v>
+        <v>7.57</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.39</v>
+        <v>7.33</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.32</v>
+        <v>7.29</v>
       </c>
       <c r="K45" s="18" t="n">
         <v>7.41</v>
@@ -3400,16 +3400,16 @@
         </is>
       </c>
       <c r="O45" s="21" t="n">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="P45" s="21" t="n">
         <v>7.42</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.09</v>
+        <v>12.07</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>11.82</v>
+        <v>11.84</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.57</v>
+        <v>11.76</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.75</v>
+        <v>11.85</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.48</v>
+        <v>11.62</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.3</v>
+        <v>11.53</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.21</v>
+        <v>11.39</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.44</v>
+        <v>11.52</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.21</v>
+        <v>11.33</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>11.1</v>
+      </c>
+      <c r="N46" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.47</v>
+        <v>11.58</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.46</v>
+        <v>11.54</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="R46" s="23" t="n">
-        <v>-2.15</v>
+        <v>11.68</v>
+      </c>
+      <c r="R46" s="24" t="n">
+        <v>2.46</v>
       </c>
     </row>
     <row r="47">
@@ -3486,37 +3486,37 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>203.44</v>
+        <v>214.45</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>201.44</v>
+        <v>205.15</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>199.76</v>
+        <v>197.35</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>200.4</v>
+        <v>196.3</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>201.3</v>
+        <v>202.5</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>199.3</v>
+        <v>193.2</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>198.4</v>
+        <v>187</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>197.3</v>
+        <v>183.9</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>198.64</v>
+        <v>192.15</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>196.96</v>
+        <v>184.35</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>194.96</v>
+        <v>175.05</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -3524,16 +3524,16 @@
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>199.05</v>
+        <v>193.04</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>198.8</v>
+        <v>192.87</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>199.5</v>
+        <v>190.1</v>
       </c>
       <c r="R47" s="23" t="n">
-        <v>-1.77</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="48">
@@ -3548,37 +3548,37 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>46.57</v>
+        <v>46.72</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>46.01</v>
+        <v>46</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>45.54</v>
+        <v>45.4</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>45.74</v>
+        <v>45.39</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>45.98</v>
+        <v>45.83</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>45.42</v>
+        <v>45.11</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>45.18</v>
+        <v>44.67</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>44.86</v>
+        <v>44.39</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>45.22</v>
+        <v>45</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>44.75</v>
+        <v>44.4</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>44.19</v>
+        <v>43.68</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>45.34</v>
+        <v>45.08</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>45.27</v>
+        <v>45.05</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>45.5</v>
+        <v>44.94</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>-0.39</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="49">
@@ -3610,37 +3610,37 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>33.63</v>
+        <v>32.42</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32.71</v>
+        <v>31.9</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>31.94</v>
+        <v>31.47</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>32.15</v>
+        <v>31.41</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>32.61</v>
+        <v>31.75</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.69</v>
+        <v>31.23</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.23</v>
+        <v>30.89</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>30.77</v>
+        <v>30.71</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.42</v>
+        <v>31.17</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>30.65</v>
+        <v>30.74</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>29.73</v>
+        <v>30.22</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
@@ -3648,16 +3648,16 @@
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>31.59</v>
+        <v>31.22</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>31.49</v>
+        <v>31.21</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>31.7</v>
+        <v>31.06</v>
       </c>
       <c r="R49" s="23" t="n">
-        <v>-0.88</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="50">
@@ -3672,37 +3672,37 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.64</v>
+        <v>12.39</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.42</v>
+        <v>12.21</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.23</v>
+        <v>12.06</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.35</v>
+        <v>12.2</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.13</v>
+        <v>12.02</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>11.99</v>
+        <v>11.95</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>11.91</v>
+        <v>11.84</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>12.11</v>
+        <v>11.96</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>11.92</v>
+        <v>11.81</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>11.7</v>
+        <v>11.63</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>12.13</v>
+        <v>11.97</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.06</v>
+        <v>12.05</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>-3.83</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>59.61</v>
+        <v>59.49</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>58.71</v>
+        <v>58.69</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>57.95</v>
+        <v>58.02</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.18</v>
+        <v>58.03</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>58.62</v>
+        <v>58.52</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>57.72</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>57.28</v>
+        <v>57.23</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>56.82</v>
+        <v>56.92</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.45</v>
+        <v>57.58</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>56.69</v>
+        <v>56.91</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="N51" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>56.11</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.62</v>
+        <v>57.68</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.52</v>
+        <v>57.64</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>57.75</v>
-      </c>
-      <c r="R51" s="25" t="n">
-        <v>0.43</v>
+        <v>57.55</v>
+      </c>
+      <c r="R51" s="23" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="52">
@@ -3796,37 +3796,37 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>23.33</v>
+        <v>22.51</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.82</v>
+        <v>22.27</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.39</v>
+        <v>22.07</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.34</v>
+        <v>22.09</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.67</v>
+        <v>22.23</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22.16</v>
+        <v>21.99</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.65</v>
+        <v>21.75</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>22.1</v>
+        <v>21.93</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.67</v>
+        <v>21.73</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>21.16</v>
+        <v>21.49</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
@@ -3834,16 +3834,16 @@
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>22.15</v>
+        <v>21.97</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>22.14</v>
+        <v>21.95</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>22</v>
+        <v>21.96</v>
       </c>
       <c r="R52" s="23" t="n">
-        <v>-1.21</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="53">
@@ -3858,37 +3858,37 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="F53" s="15" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>5.07</v>
       </c>
-      <c r="G53" s="15" t="n">
-        <v>5.12</v>
-      </c>
       <c r="H53" s="16" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="P53" s="21" t="n">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
       <c r="R53" s="23" t="n">
-        <v>-1.76</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.54</v>
+        <v>18.85</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.3</v>
+        <v>18.42</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>18.1</v>
+        <v>18.06</v>
       </c>
       <c r="F54" s="15" t="n">
         <v>18.13</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.26</v>
+        <v>18.36</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>18.02</v>
+        <v>17.93</v>
       </c>
       <c r="I54" s="17" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K54" s="18" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O54" s="21" t="n">
         <v>17.89</v>
       </c>
-      <c r="J54" s="17" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="K54" s="18" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="L54" s="19" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="N54" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O54" s="21" t="n">
-        <v>18</v>
-      </c>
       <c r="P54" s="21" t="n">
-        <v>17.98</v>
+        <v>17.85</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>18</v>
+        <v>17.91</v>
       </c>
       <c r="R54" s="23" t="n">
-        <v>-2.54</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>97.06</v>
+        <v>96.83</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>95.26000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>93.75</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>93.92</v>
+        <v>94.77</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>94.93000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>93.13</v>
+        <v>93.83</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>92.12</v>
+        <v>93.27</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>91.33</v>
+        <v>92.33</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>92.75</v>
+        <v>93.23</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>91.23999999999999</v>
+        <v>91.97</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>89.44</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>90.47</v>
+      </c>
+      <c r="N55" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>93.01000000000001</v>
+        <v>93.59</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>92.89</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="R55" s="23" t="n">
-        <v>-0.11</v>
+        <v>94.2</v>
+      </c>
+      <c r="R55" s="24" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.51</v>
+        <v>17.65</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.23</v>
+        <v>17.25</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>17</v>
+        <v>16.91</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>17.13</v>
+        <v>17.01</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>17.24</v>
+        <v>17.2</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.96</v>
+        <v>16.8</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.85</v>
+        <v>16.61</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>16.68</v>
+        <v>16.4</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>16.84</v>
+        <v>16.69</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>16.61</v>
+        <v>16.35</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="N56" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.95</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.91</v>
+        <v>16.76</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.86</v>
+        <v>16.72</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>17.03</v>
-      </c>
-      <c r="R56" s="25" t="n">
-        <v>0.53</v>
+        <v>16.81</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>20.81</v>
+        <v>21.01</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.73</v>
+        <v>20.84</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.66</v>
+        <v>20.69</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.65</v>
+        <v>20.69</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.71</v>
+        <v>20.8</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>20.63</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.57</v>
+        <v>20.52</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.55</v>
+        <v>20.46</v>
       </c>
       <c r="K57" s="18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L57" s="19" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O57" s="21" t="n">
         <v>20.62</v>
       </c>
-      <c r="L57" s="19" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="M57" s="19" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="N57" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O57" s="21" t="n">
-        <v>20.63</v>
-      </c>
       <c r="P57" s="21" t="n">
-        <v>20.62</v>
+        <v>20.61</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.6</v>
+        <v>20.59</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>-2.42</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="58">
@@ -4168,37 +4168,37 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>23.06</v>
+        <v>23.08</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.72</v>
+        <v>22.66</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.44</v>
+        <v>22.31</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.62</v>
+        <v>22.29</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.74</v>
+        <v>22.56</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.4</v>
+        <v>22.14</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>22.28</v>
+        <v>21.87</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>22.06</v>
+        <v>21.72</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>22.24</v>
+        <v>22.07</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>21.96</v>
+        <v>21.72</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>21.62</v>
+        <v>21.3</v>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
@@ -4206,16 +4206,16 @@
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22.33</v>
+        <v>22.12</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>22.27</v>
+        <v>22.11</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>22.51</v>
+        <v>22.03</v>
       </c>
       <c r="R58" s="23" t="n">
-        <v>-0.22</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="59">
@@ -4230,37 +4230,37 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.28</v>
+        <v>27.72</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>27.92</v>
+        <v>27.56</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.62</v>
+        <v>27.42</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.65</v>
+        <v>27.42</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27.85</v>
+        <v>27.52</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.49</v>
+        <v>27.36</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.29</v>
+        <v>27.26</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.13</v>
+        <v>27.2</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.42</v>
+        <v>27.34</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.12</v>
+        <v>27.2</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>26.76</v>
+        <v>27.04</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.47</v>
+        <v>27.35</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.45</v>
+        <v>27.35</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.44</v>
+        <v>27.32</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>-1.15</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="60">
@@ -4292,37 +4292,37 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.77</v>
+        <v>45.65</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.47</v>
+        <v>45.31</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.21</v>
+        <v>45.03</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.19</v>
+        <v>45.04</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45.39</v>
+        <v>45.24</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>45.09</v>
+        <v>44.9</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>44.89</v>
+        <v>44.7</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>44.79</v>
+        <v>44.56</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>45.05</v>
+        <v>44.83</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>44.79</v>
+        <v>44.55</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.49</v>
+        <v>44.21</v>
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
@@ -4330,16 +4330,16 @@
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>45.08</v>
+        <v>44.88</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>45.07</v>
+        <v>44.86</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>45</v>
+        <v>44.84</v>
       </c>
       <c r="R60" s="23" t="n">
-        <v>-0.27</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="61">
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>19.41</v>
+        <v>18.6</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.92</v>
+        <v>18.38</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.51</v>
+        <v>18.19</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.48</v>
+        <v>18.19</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.79</v>
+        <v>18.32</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>17.99</v>
+        <v>17.97</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>17.81</v>
+        <v>17.88</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18.24</v>
+        <v>18.07</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>17.83</v>
+        <v>17.88</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.34</v>
+        <v>17.66</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4392,16 +4392,16 @@
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.29</v>
+        <v>18.09</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.28</v>
+        <v>18.09</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>18.16</v>
+        <v>18.05</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>-3.71</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="62">
@@ -4416,37 +4416,37 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.23</v>
+        <v>15.25</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.08</v>
+        <v>15.09</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.01</v>
+        <v>14.97</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.08</v>
+        <v>15.06</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.93</v>
+        <v>14.9</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.86</v>
+        <v>14.81</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.78</v>
+        <v>14.74</v>
       </c>
       <c r="K62" s="18" t="n">
         <v>14.87</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.75</v>
+        <v>14.73</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="P62" s="21" t="n">
         <v>14.88</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="R62" s="25" t="n">
-        <v>0</v>
+        <v>14.88</v>
+      </c>
+      <c r="R62" s="23" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="63">
@@ -4478,37 +4478,37 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.79</v>
+        <v>24.53</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.39</v>
+        <v>24.2</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>24.05</v>
+        <v>23.93</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>24.01</v>
+        <v>23.96</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.28</v>
+        <v>24.15</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.88</v>
+        <v>23.82</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.61</v>
+        <v>23.63</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.48</v>
+        <v>23.49</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.83</v>
+        <v>23.74</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.49</v>
+        <v>23.47</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.09</v>
+        <v>23.14</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
@@ -4516,16 +4516,16 @@
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.87</v>
+        <v>23.79</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.86</v>
+        <v>23.77</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="R63" s="23" t="n">
-        <v>-2.1</v>
+        <v>23.78</v>
+      </c>
+      <c r="R63" s="24" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="64">
@@ -4540,25 +4540,25 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.16</v>
+        <v>7.13</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.08</v>
+        <v>7.06</v>
       </c>
       <c r="F64" s="15" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="G64" s="15" t="n">
         <v>7.11</v>
       </c>
-      <c r="G64" s="15" t="n">
-        <v>7.15</v>
-      </c>
       <c r="H64" s="16" t="n">
-        <v>7.05</v>
+        <v>7.03</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7.01</v>
+        <v>6.99</v>
       </c>
       <c r="J64" s="17" t="n">
         <v>6.95</v>
@@ -4567,10 +4567,10 @@
         <v>7.02</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="M64" s="19" t="n">
-        <v>6.84</v>
+        <v>6.87</v>
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
@@ -4578,16 +4578,16 @@
         </is>
       </c>
       <c r="O64" s="21" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="P64" s="21" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="Q64" s="22" t="n">
-        <v>7.06</v>
+        <v>7.02</v>
       </c>
       <c r="R64" s="23" t="n">
-        <v>-0.84</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="65">
@@ -4602,37 +4602,37 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="E65" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G65" s="15" t="n">
         <v>4.82</v>
       </c>
-      <c r="F65" s="15" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="G65" s="15" t="n">
-        <v>4.85</v>
-      </c>
       <c r="H65" s="16" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="L65" s="19" t="n">
         <v>4.75</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="N65" s="20" t="inlineStr">
         <is>
@@ -4640,13 +4640,13 @@
         </is>
       </c>
       <c r="O65" s="21" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="R65" s="23" t="n">
         <v>-0.42</v>
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="F66" s="15" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G66" s="15" t="n">
         <v>4.63</v>
       </c>
-      <c r="G66" s="15" t="n">
-        <v>4.71</v>
-      </c>
       <c r="H66" s="16" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.5</v>
+        <v>4.34</v>
       </c>
       <c r="J66" s="17" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="K66" s="18" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n">
         <v>4.45</v>
       </c>
-      <c r="K66" s="18" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>4.58</v>
-      </c>
       <c r="P66" s="21" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="R66" s="23" t="n">
-        <v>-0.87</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="67">
@@ -4726,37 +4726,37 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>67.3</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>65.84999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E67" s="14" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="G67" s="15" t="n">
         <v>64.63</v>
       </c>
-      <c r="F67" s="15" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="G67" s="15" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H67" s="16" t="n">
-        <v>64.15000000000001</v>
+        <v>63.93</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>63.35</v>
+        <v>63.57</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>62.7</v>
+        <v>63.23</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>63.82</v>
+        <v>63.75</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>62.6</v>
+        <v>63.17</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>61.15</v>
+        <v>62.47</v>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>64.04000000000001</v>
+        <v>63.87</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>63.93</v>
+        <v>63.81</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>-0.47</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>68.68000000000001</v>
+        <v>69.91</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>67.58</v>
+        <v>68.11</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>66.66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>67.27</v>
+        <v>66.5</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>67.63</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>66.53</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>66.17</v>
+        <v>64.7</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>65.43000000000001</v>
+        <v>64.05</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>66.04000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>65.12</v>
+        <v>64.09</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="N68" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>62.29</v>
+      </c>
+      <c r="N68" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>66.33</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>66.13</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="R68" s="25" t="n">
-        <v>1.75</v>
+        <v>65.34999999999999</v>
+      </c>
+      <c r="R68" s="23" t="n">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="69">
@@ -4850,37 +4850,37 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>83.8</v>
+        <v>81.23</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>81.3</v>
+        <v>79.08</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>79.2</v>
+        <v>77.28</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>79.68000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>80.97</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>78.47</v>
+        <v>76.42</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>77.18000000000001</v>
+        <v>75.08</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>75.97</v>
+        <v>74.27</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>77.8</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>75.7</v>
+        <v>74.27</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>73.2</v>
+        <v>72.12</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
@@ -4888,16 +4888,16 @@
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>78.23</v>
+        <v>76.33</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>78</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>78.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="R69" s="23" t="n">
-        <v>-2.12</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>121.84</v>
+        <v>124.45</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>119.84</v>
+        <v>120.65</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>118.16</v>
+        <v>117.46</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>118.87</v>
+        <v>118.03</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>119.73</v>
+        <v>120.07</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>117.73</v>
+        <v>116.27</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>116.87</v>
+        <v>114.23</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>115.73</v>
+        <v>112.47</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>117.04</v>
+        <v>115.34</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>115.36</v>
+        <v>112.15</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>113.36</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>108.35</v>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>117.46</v>
+        <v>115.95</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>117.2</v>
+        <v>115.63</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>118</v>
-      </c>
-      <c r="R70" s="25" t="n">
-        <v>2.79</v>
+        <v>116</v>
+      </c>
+      <c r="R70" s="23" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.34</v>
+        <v>23.15</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.01</v>
+        <v>22.85</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>22.74</v>
+        <v>22.59</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>22.83</v>
+        <v>22.65</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>22.98</v>
+        <v>22.81</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>22.65</v>
+        <v>22.51</v>
       </c>
       <c r="I71" s="17" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="J71" s="17" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="K71" s="18" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L71" s="19" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="M71" s="19" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="P71" s="21" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="Q71" s="22" t="n">
         <v>22.5</v>
       </c>
-      <c r="J71" s="17" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="K71" s="18" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="L71" s="19" t="n">
-        <v>22.28</v>
-      </c>
-      <c r="M71" s="19" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="Q71" s="22" t="n">
-        <v>22.67</v>
-      </c>
       <c r="R71" s="23" t="n">
-        <v>-1.86</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>19.61</v>
+        <v>18.7</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.82</v>
+        <v>18.27</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>18.16</v>
+        <v>17.91</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>18.16</v>
+        <v>17.94</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.64</v>
+        <v>18.19</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.85</v>
+        <v>17.76</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.37</v>
+        <v>17.51</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>17.06</v>
+        <v>17.33</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.71</v>
+        <v>17.66</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>17.05</v>
+        <v>17.3</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>16.26</v>
-      </c>
-      <c r="N72" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.87</v>
+      </c>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.81</v>
+        <v>17.73</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.78</v>
+        <v>17.7</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="R72" s="25" t="n">
-        <v>3.39</v>
+        <v>17.7</v>
+      </c>
+      <c r="R72" s="24" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="73">
@@ -5098,37 +5098,37 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>236.63</v>
+        <v>234.33</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>232.53</v>
+        <v>231.53</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>229.1</v>
+        <v>229.18</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>231.37</v>
+        <v>229.33</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>232.73</v>
+        <v>230.97</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>228.63</v>
+        <v>228.17</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>227.27</v>
+        <v>226.53</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>224.53</v>
+        <v>225.37</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>226.8</v>
+        <v>227.62</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>223.37</v>
+        <v>225.27</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>219.27</v>
+        <v>222.47</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>227.88</v>
+        <v>228</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>227.12</v>
+        <v>227.83</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>230</v>
+        <v>227.7</v>
       </c>
       <c r="R73" s="23" t="n">
-        <v>-0.26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
@@ -5160,37 +5160,37 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.87</v>
+        <v>15.56</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.59</v>
+        <v>15.36</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.36</v>
+        <v>15.2</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.34</v>
+        <v>15.22</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.52</v>
+        <v>15.33</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.24</v>
+        <v>15.13</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.06</v>
+        <v>15.02</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.2</v>
+        <v>15.08</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>14.97</v>
+        <v>14.92</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>14.69</v>
+        <v>14.72</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.23</v>
+        <v>15.11</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.22</v>
+        <v>15.1</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.16</v>
+        <v>15.11</v>
       </c>
       <c r="R74" s="23" t="n">
-        <v>-1.49</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>35.79</v>
+        <v>36.78</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>35.45</v>
+        <v>36.14</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>35.17</v>
+        <v>35.6</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>35.23</v>
+        <v>35.74</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>35.41</v>
+        <v>36.06</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>35.07</v>
+        <v>35.42</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>34.89</v>
+        <v>35.1</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>34.73</v>
+        <v>34.78</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>34.97</v>
+        <v>35.24</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>34.69</v>
+        <v>34.7</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>34.35</v>
-      </c>
-      <c r="N75" s="24" t="inlineStr">
+        <v>34.06</v>
+      </c>
+      <c r="N75" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>35.03</v>
+        <v>35.36</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>35</v>
+        <v>35.29</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>35.06</v>
-      </c>
-      <c r="R75" s="25" t="n">
-        <v>1.62</v>
+        <v>35.42</v>
+      </c>
+      <c r="R75" s="24" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>22.92</v>
+        <v>22.69</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>22.32</v>
+        <v>21.94</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>21.82</v>
+        <v>21.31</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>21.84</v>
+        <v>21.24</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>22.19</v>
+        <v>21.74</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>21.59</v>
+        <v>20.99</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>21.24</v>
+        <v>20.49</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>20.99</v>
+        <v>20.24</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>21.48</v>
+        <v>20.89</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>20.98</v>
+        <v>20.27</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="N76" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>19.52</v>
+      </c>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>21.56</v>
+        <v>20.97</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>21.53</v>
+        <v>20.95</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="R76" s="25" t="n">
-        <v>0.89</v>
+        <v>20.75</v>
+      </c>
+      <c r="R76" s="23" t="n">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="77">
@@ -5346,37 +5346,37 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.71</v>
+        <v>44.24</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.59</v>
+        <v>43.08</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>42.65</v>
+        <v>42.1</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>42.86</v>
+        <v>42.11</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>43.44</v>
+        <v>42.81</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>42.32</v>
+        <v>41.65</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>41.74</v>
+        <v>40.95</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>41.2</v>
+        <v>40.49</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>42.03</v>
+        <v>41.46</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>41.09</v>
+        <v>40.48</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.97</v>
+        <v>39.32</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>42.22</v>
+        <v>41.6</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>42.11</v>
+        <v>41.55</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>42.28</v>
+        <v>41.4</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>-0.52</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.46</v>
+        <v>5.37</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.37</v>
+        <v>5.3</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.39</v>
+        <v>5.32</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
       <c r="I78" s="17" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J78" s="17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="L78" s="19" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M78" s="19" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="P78" s="21" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="Q78" s="22" t="n">
         <v>5.28</v>
       </c>
-      <c r="J78" s="17" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="K78" s="18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="M78" s="19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O78" s="21" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="P78" s="21" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="Q78" s="22" t="n">
-        <v>5.33</v>
-      </c>
       <c r="R78" s="23" t="n">
-        <v>-1.11</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>18.81</v>
+        <v>19.61</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.54</v>
+        <v>19.04</v>
       </c>
       <c r="E79" s="14" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="H79" s="16" t="n">
         <v>18.31</v>
       </c>
-      <c r="F79" s="15" t="n">
+      <c r="I79" s="17" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="J79" s="17" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="K79" s="18" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P79" s="21" t="n">
         <v>18.29</v>
       </c>
-      <c r="G79" s="15" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="H79" s="16" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="I79" s="17" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="J79" s="17" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="K79" s="18" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O79" s="21" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="P79" s="21" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q79" s="22" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="R79" s="23" t="n">
-        <v>-0.22</v>
+        <v>18.13</v>
+      </c>
+      <c r="R79" s="24" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>80.59999999999999</v>
+        <v>82.47</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>79.55</v>
+        <v>80.42</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>78.67</v>
+        <v>78.7</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>78.81999999999999</v>
+        <v>78.47</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>79.38</v>
+        <v>79.83</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>78.33</v>
+        <v>77.78</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>77.77</v>
+        <v>76.42</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>77.28</v>
+        <v>75.73</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>78.08</v>
+        <v>77.55</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>77.2</v>
+        <v>75.83</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>76.15000000000001</v>
-      </c>
-      <c r="N80" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>73.78</v>
+      </c>
+      <c r="N80" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>78.25</v>
+        <v>77.75</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>78.16</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>78.25</v>
-      </c>
-      <c r="R80" s="25" t="n">
-        <v>0.77</v>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="R80" s="23" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="E81" s="14" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G81" s="15" t="n">
         <v>4.53</v>
       </c>
-      <c r="F81" s="15" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="G81" s="15" t="n">
-        <v>4.59</v>
-      </c>
       <c r="H81" s="16" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="I81" s="17" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K81" s="18" t="n">
         <v>4.45</v>
       </c>
-      <c r="J81" s="17" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="K81" s="18" t="n">
-        <v>4.48</v>
-      </c>
       <c r="L81" s="19" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="N81" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.32</v>
+      </c>
+      <c r="N81" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="R81" s="25" t="n">
-        <v>0.67</v>
+        <v>4.45</v>
+      </c>
+      <c r="R81" s="23" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>58.46</v>
+        <v>59.92</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>57.56</v>
+        <v>58.67</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>56.8</v>
+        <v>57.63</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>57.17</v>
+        <v>58.18</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>57.53</v>
+        <v>58.67</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>56.63</v>
+        <v>57.42</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>56.27</v>
+        <v>56.93</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>55.73</v>
+        <v>56.17</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>56.3</v>
+        <v>56.93</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>55.54</v>
+        <v>55.88</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>54.64</v>
-      </c>
-      <c r="N82" s="24" t="inlineStr">
+        <v>54.63</v>
+      </c>
+      <c r="N82" s="25" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>56.5</v>
+        <v>57.22</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>56.37</v>
+        <v>57.02</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="R82" s="25" t="n">
-        <v>0.89</v>
+        <v>57.7</v>
+      </c>
+      <c r="R82" s="24" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="83">
@@ -5718,37 +5718,37 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>37.79</v>
+        <v>38.08</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.49</v>
+        <v>37.6</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.23</v>
+        <v>37.19</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.29</v>
+        <v>37.14</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.45</v>
+        <v>37.46</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>37.15</v>
+        <v>36.98</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.99</v>
+        <v>36.66</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.85</v>
+        <v>36.5</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>37.07</v>
+        <v>36.93</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.81</v>
+        <v>36.52</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.51</v>
+        <v>36.04</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
@@ -5756,16 +5756,16 @@
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>37.12</v>
+        <v>36.97</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>37.09</v>
+        <v>36.96</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>37.14</v>
+        <v>36.82</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>-1.01</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>92.39</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>91.44</v>
+        <v>94.06</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>90.64</v>
+        <v>92.22</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>90.97</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>91.38</v>
+        <v>94.17</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>90.43000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>90.02</v>
+        <v>91.23</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>89.48</v>
+        <v>89.77</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>90.11</v>
+        <v>90.98</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>89.31</v>
+        <v>89.14</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>88.36</v>
-      </c>
-      <c r="N84" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>86.94</v>
+      </c>
+      <c r="N84" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>90.31</v>
+        <v>91.56</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>90.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>90.55</v>
-      </c>
-      <c r="R84" s="23" t="n">
-        <v>-0.33</v>
+        <v>92.7</v>
+      </c>
+      <c r="R84" s="24" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.23</v>
+        <v>17.11</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.84</v>
+        <v>16.71</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.51</v>
+        <v>16.37</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.68</v>
+        <v>16.35</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.84</v>
+        <v>16.61</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.45</v>
+        <v>16.21</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.29</v>
+        <v>15.95</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>16.06</v>
+        <v>15.81</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>16.3</v>
+        <v>16.15</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>15.97</v>
+        <v>15.81</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="N85" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.41</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.39</v>
+        <v>16.19</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.33</v>
+        <v>16.18</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="R85" s="25" t="n">
-        <v>3.83</v>
+        <v>16.1</v>
+      </c>
+      <c r="R85" s="23" t="n">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>128.04</v>
+        <v>126.84</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>125.55</v>
+        <v>124.84</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>123.45</v>
+        <v>123.16</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>123.23</v>
+        <v>123.2</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>124.87</v>
+        <v>124.4</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>122.37</v>
+        <v>122.4</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>120.73</v>
+        <v>121.2</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>119.87</v>
+        <v>120.4</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>122.05</v>
+        <v>122.04</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>119.95</v>
+        <v>120.36</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>117.45</v>
-      </c>
-      <c r="N86" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>118.36</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>122.31</v>
+        <v>122.3</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>122.25</v>
+        <v>122.2</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="R86" s="23" t="n">
-        <v>-0.49</v>
+        <v>122</v>
+      </c>
+      <c r="R86" s="24" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="87">
@@ -5966,37 +5966,37 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>59.2</v>
+        <v>62.29</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>58.55</v>
+        <v>59.64</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>58.01</v>
+        <v>57.42</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>58.27</v>
+        <v>57.25</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>58.53</v>
+        <v>58.95</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>57.88</v>
+        <v>56.3</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>57.62</v>
+        <v>54.6</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>57.23</v>
+        <v>53.65</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>57.64</v>
+        <v>55.93</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>57.1</v>
+        <v>53.71</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>56.45</v>
+        <v>51.06</v>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
@@ -6004,16 +6004,16 @@
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>57.79</v>
+        <v>56.22</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>57.69</v>
+        <v>56.14</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>58</v>
+        <v>55.55</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>-0.51</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="88">
@@ -6028,54 +6028,54 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>11.08</v>
+        <v>10.25</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>10.44</v>
+        <v>9.98</v>
       </c>
       <c r="E88" s="14" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F88" s="15" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G88" s="15" t="n">
         <v>9.9</v>
       </c>
-      <c r="F88" s="15" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="G88" s="15" t="n">
-        <v>10.47</v>
-      </c>
       <c r="H88" s="16" t="n">
-        <v>9.83</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.609999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J88" s="17" t="n">
-        <v>9.19</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.539999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="N88" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>9.1</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.710000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="R88" s="25" t="n">
-        <v>7.04</v>
+        <v>9.550000000000001</v>
+      </c>
+      <c r="R88" s="23" t="n">
+        <v>-4.88</v>
       </c>
     </row>
     <row r="89">
@@ -6090,37 +6090,37 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>18.7</v>
+        <v>17.63</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>17.58</v>
+        <v>16.86</v>
       </c>
       <c r="E89" s="14" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="G89" s="15" t="n">
         <v>16.64</v>
       </c>
-      <c r="F89" s="15" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="G89" s="15" t="n">
-        <v>17.32</v>
-      </c>
       <c r="H89" s="16" t="n">
-        <v>16.2</v>
+        <v>15.87</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.5</v>
+        <v>15.35</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>15.08</v>
+        <v>15.1</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>16.02</v>
+        <v>15.78</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15.08</v>
+        <v>15.13</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>13.96</v>
+        <v>14.36</v>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
@@ -6128,16 +6128,16 @@
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>16.15</v>
+        <v>15.85</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>16.1</v>
+        <v>15.84</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>15.93</v>
+        <v>15.61</v>
       </c>
       <c r="R89" s="23" t="n">
-        <v>-1.06</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>21.72</v>
+        <v>18</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>19.89</v>
+        <v>17.63</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>18.36</v>
+        <v>17.32</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>18.33</v>
+        <v>17.28</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>19.46</v>
+        <v>17.53</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.63</v>
+        <v>17.16</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>16.5</v>
+        <v>16.91</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>15.8</v>
+        <v>16.79</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.33</v>
+        <v>17.11</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="N90" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.43</v>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>17.55</v>
+        <v>17.15</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.48</v>
+        <v>17.14</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="R90" s="25" t="n">
-        <v>1.59</v>
+        <v>17.04</v>
+      </c>
+      <c r="R90" s="23" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.64</v>
+        <v>31.14</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.76</v>
+        <v>30.56</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>30.03</v>
+        <v>30.07</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>30.27</v>
+        <v>30.14</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.69</v>
+        <v>30.46</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.81</v>
+        <v>29.88</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.39</v>
+        <v>29.56</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>28.93</v>
+        <v>29.3</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.53</v>
+        <v>29.75</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>28.8</v>
+        <v>29.26</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="N91" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>28.68</v>
+      </c>
+      <c r="N91" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.7</v>
+        <v>29.84</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.6</v>
+        <v>29.79</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="R91" s="25" t="n">
-        <v>0.61</v>
+        <v>29.82</v>
+      </c>
+      <c r="R91" s="23" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.17</v>
+        <v>19.84</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>19.82</v>
+        <v>19.62</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.52</v>
+        <v>19.43</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.54</v>
+        <v>19.45</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>19.74</v>
+        <v>19.57</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.39</v>
+        <v>19.35</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>19.19</v>
+        <v>19.23</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>19.04</v>
+        <v>19.13</v>
       </c>
       <c r="K92" s="18" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O92" s="21" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="P92" s="21" t="n">
         <v>19.33</v>
       </c>
-      <c r="L92" s="19" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="M92" s="19" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O92" s="21" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="P92" s="21" t="n">
-        <v>19.35</v>
-      </c>
       <c r="Q92" s="22" t="n">
-        <v>19.33</v>
+        <v>19.32</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>-2.47</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="93">
@@ -6338,37 +6338,37 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.08</v>
+        <v>26.04</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.65</v>
+        <v>25.66</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>25.67</v>
+        <v>25.66</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>25.97</v>
+        <v>25.94</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.45</v>
+        <v>25.48</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.15</v>
+        <v>25.2</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>24.93</v>
+        <v>25.02</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.35</v>
+        <v>25.4</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>24.92</v>
+        <v>25.02</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>24.4</v>
+        <v>24.56</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.42</v>
+        <v>25.46</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.39</v>
+        <v>25.44</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.36</v>
-      </c>
-      <c r="R93" s="23" t="n">
-        <v>-1.78</v>
+        <v>25.38</v>
+      </c>
+      <c r="R93" s="24" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>177.81</v>
+        <v>177.72</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>173.91</v>
+        <v>174.62</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>170.64</v>
+        <v>172.02</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>172</v>
+        <v>173.4</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>173.7</v>
+        <v>174.6</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>169.8</v>
+        <v>171.5</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>168.1</v>
+        <v>170.3</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>165.9</v>
+        <v>168.4</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>168.46</v>
+        <v>170.28</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>165.19</v>
+        <v>167.68</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>161.29</v>
-      </c>
-      <c r="N94" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>164.58</v>
+      </c>
+      <c r="N94" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>169.28</v>
+        <v>171.01</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>168.76</v>
+        <v>170.52</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="R94" s="25" t="n">
-        <v>0.29</v>
+        <v>172.2</v>
+      </c>
+      <c r="R94" s="24" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="95">
@@ -6462,37 +6462,37 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>14.64</v>
+        <v>13.34</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>13.88</v>
+        <v>13.1</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>13.24</v>
+        <v>12.9</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>13.2</v>
+        <v>12.87</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>13.68</v>
+        <v>13.03</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>12.92</v>
+        <v>12.79</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>12.44</v>
+        <v>12.63</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>12.16</v>
+        <v>12.55</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>12.82</v>
+        <v>12.76</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>12.18</v>
+        <v>12.56</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>11.42</v>
+        <v>12.32</v>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
@@ -6500,16 +6500,16 @@
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>12.9</v>
+        <v>12.79</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="Q95" s="22" t="n">
         <v>12.71</v>
       </c>
-      <c r="R95" s="23" t="n">
-        <v>-1.32</v>
+      <c r="R95" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -6524,37 +6524,37 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>19.97</v>
+        <v>20.05</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.6</v>
+        <v>19.46</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>19.29</v>
+        <v>18.97</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.25</v>
+        <v>18.93</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.49</v>
+        <v>19.31</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>19.12</v>
+        <v>18.72</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>18.88</v>
+        <v>18.34</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.75</v>
+        <v>18.13</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>19.08</v>
+        <v>18.64</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.77</v>
+        <v>18.15</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>18.4</v>
+        <v>17.56</v>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>19.12</v>
+        <v>18.7</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>19.11</v>
+        <v>18.69</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>19</v>
+        <v>18.55</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>-2.51</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>18.59</v>
+        <v>16.57</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>17.4</v>
+        <v>16.22</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>16.4</v>
+        <v>15.92</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>17.06</v>
+        <v>15.92</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>17.45</v>
+        <v>16.13</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>16.26</v>
+        <v>15.78</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>15.87</v>
+        <v>15.57</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>15.07</v>
+        <v>15.43</v>
       </c>
       <c r="K97" s="18" t="n">
         <v>15.73</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>14.73</v>
+        <v>15.43</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="N97" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.08</v>
+      </c>
+      <c r="N97" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>16.04</v>
+        <v>15.77</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.82</v>
+        <v>15.75</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="R97" s="25" t="n">
-        <v>7.55</v>
+        <v>15.7</v>
+      </c>
+      <c r="R97" s="23" t="n">
+        <v>-5.76</v>
       </c>
     </row>
     <row r="98">
@@ -6648,37 +6648,37 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.59</v>
+        <v>9.74</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.390000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>9.220000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>9.050000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.18</v>
+        <v>9.16</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>9.029999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.859999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
@@ -6689,13 +6689,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="R98" s="23" t="n">
-        <v>-0.65</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="99">
@@ -6710,37 +6710,37 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>26.68</v>
+        <v>25.73</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25.89</v>
+        <v>25.34</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>25.23</v>
+        <v>25.01</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>25.48</v>
+        <v>25.04</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.83</v>
+        <v>25.27</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>25.04</v>
+        <v>24.88</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.69</v>
+        <v>24.65</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.25</v>
+        <v>24.49</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.78</v>
+        <v>24.8</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>24.12</v>
+        <v>24.47</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>23.33</v>
+        <v>24.08</v>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>24.94</v>
+        <v>24.85</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>24.85</v>
+        <v>24.83</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="R99" s="25" t="n">
-        <v>0.16</v>
+        <v>24.82</v>
+      </c>
+      <c r="R99" s="23" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.62</v>
+        <v>16.44</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>16.36</v>
+        <v>16.26</v>
       </c>
       <c r="E100" s="14" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="F100" s="15" t="n">
         <v>16.14</v>
       </c>
-      <c r="F100" s="15" t="n">
-        <v>16.29</v>
-      </c>
       <c r="G100" s="15" t="n">
-        <v>16.37</v>
+        <v>16.24</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>16.11</v>
+        <v>16.06</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>16.03</v>
+        <v>15.96</v>
       </c>
       <c r="J100" s="17" t="n">
-        <v>15.85</v>
+        <v>15.88</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>15.78</v>
+        <v>15.86</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="N100" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>15.68</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>16.07</v>
+        <v>16.04</v>
       </c>
       <c r="P100" s="21" t="n">
         <v>16.02</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="R100" s="25" t="n">
-        <v>0.87</v>
+        <v>16.05</v>
+      </c>
+      <c r="R100" s="23" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="101">
@@ -6834,37 +6834,37 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>30.97</v>
+        <v>31.08</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.41</v>
+        <v>30.34</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.94</v>
+        <v>29.72</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.89</v>
+        <v>29.66</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.25</v>
+        <v>30.14</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.69</v>
+        <v>29.4</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>29.33</v>
+        <v>28.92</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>29.13</v>
+        <v>28.66</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.62</v>
+        <v>29.3</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>29.15</v>
+        <v>28.68</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>28.59</v>
+        <v>27.94</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
@@ -6872,16 +6872,16 @@
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.68</v>
+        <v>29.38</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>29.67</v>
+        <v>29.36</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>29.52</v>
+        <v>29.18</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>-2.19</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="102">
@@ -6896,37 +6896,37 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>16.62</v>
+        <v>14.96</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>15.64</v>
+        <v>14.63</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.81</v>
+        <v>14.36</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.87</v>
+        <v>14.35</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>15.44</v>
+        <v>14.56</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.46</v>
+        <v>14.23</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>13.89</v>
+        <v>14.02</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>13.48</v>
+        <v>13.9</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.27</v>
+        <v>14.17</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.44</v>
+        <v>13.9</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>12.46</v>
+        <v>13.57</v>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
@@ -6934,16 +6934,16 @@
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.4</v>
+        <v>14.21</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.34</v>
+        <v>14.2</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>14.3</v>
+        <v>14.15</v>
       </c>
       <c r="R102" s="23" t="n">
-        <v>-1.45</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="103">
@@ -6958,37 +6958,37 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>70.17</v>
+        <v>68.44</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>68.77</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>67.59</v>
+        <v>66.69</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>67.77</v>
+        <v>66.58</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>68.53</v>
+        <v>67.22</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>67.13</v>
+        <v>66.27</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>66.37</v>
+        <v>65.63</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>65.73</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>66.81</v>
+        <v>66.16</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>65.63</v>
+        <v>65.36</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>64.23</v>
+        <v>64.41</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>67.03</v>
+        <v>66.25</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>66.92</v>
+        <v>66.23</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>67</v>
+        <v>65.95</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>-0.37</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.61</v>
+        <v>14.38</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.32</v>
+        <v>14.15</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.08</v>
+        <v>13.96</v>
       </c>
       <c r="F104" s="15" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G104" s="15" t="n">
         <v>14.09</v>
       </c>
-      <c r="G104" s="15" t="n">
-        <v>14.26</v>
-      </c>
       <c r="H104" s="16" t="n">
-        <v>13.97</v>
+        <v>13.86</v>
       </c>
       <c r="I104" s="17" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J104" s="17" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="L104" s="19" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="M104" s="19" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O104" s="21" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="P104" s="21" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="Q104" s="22" t="n">
         <v>13.8</v>
       </c>
-      <c r="J104" s="17" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="K104" s="18" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="L104" s="19" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="M104" s="19" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O104" s="21" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="P104" s="21" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="Q104" s="22" t="n">
-        <v>13.92</v>
-      </c>
       <c r="R104" s="23" t="n">
-        <v>-1.69</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>18.09</v>
+        <v>17.2</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>17.29</v>
+        <v>16.55</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>16.62</v>
+        <v>16.01</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>16.54</v>
+        <v>15.93</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>17.07</v>
+        <v>16.37</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>16.27</v>
+        <v>15.72</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>15.74</v>
+        <v>15.28</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.47</v>
+        <v>15.07</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>16.18</v>
+        <v>15.64</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.51</v>
+        <v>15.1</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="N105" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.45</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>16.25</v>
+        <v>15.71</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>16.24</v>
+        <v>15.69</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>16.01</v>
+        <v>15.5</v>
       </c>
       <c r="R105" s="23" t="n">
-        <v>-1.66</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="106">
@@ -7153,7 +7153,7 @@
         <v>2.43</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="G106" s="15" t="n">
         <v>2.46</v>
@@ -7162,7 +7162,7 @@
         <v>2.42</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="J106" s="17" t="n">
         <v>2.38</v>
@@ -7176,22 +7176,22 @@
       <c r="M106" s="19" t="n">
         <v>2.34</v>
       </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+      <c r="N106" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="P106" s="21" t="n">
         <v>2.41</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R106" s="23" t="n">
-        <v>-1.23</v>
+        <v>2.42</v>
+      </c>
+      <c r="R106" s="24" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="107">
@@ -7206,37 +7206,37 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>40.42</v>
+        <v>37.72</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>38.74</v>
+        <v>37.08</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>37.33</v>
+        <v>36.54</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>37.14</v>
+        <v>36.55</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>38.26</v>
+        <v>36.93</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.58</v>
+        <v>36.29</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>35.46</v>
+        <v>35.91</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>34.9</v>
+        <v>35.65</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>36.39</v>
+        <v>36.18</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>34.98</v>
+        <v>35.64</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
@@ -7244,16 +7244,16 @@
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>36.55</v>
+        <v>36.26</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>36.52</v>
+        <v>36.23</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>36.02</v>
-      </c>
-      <c r="R107" s="23" t="n">
-        <v>-3.17</v>
+        <v>36.16</v>
+      </c>
+      <c r="R107" s="24" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.050000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.73</v>
+        <v>7.7</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>7.83</v>
+        <v>7.77</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.66</v>
+        <v>7.67</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.54</v>
+        <v>7.62</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.49</v>
+        <v>7.57</v>
       </c>
       <c r="K108" s="18" t="n">
         <v>7.64</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>7.49</v>
+        <v>7.56</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>7.46</v>
+      </c>
+      <c r="N108" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>7.65</v>
+        <v>7.66</v>
       </c>
       <c r="P108" s="21" t="n">
         <v>7.65</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="R108" s="23" t="n">
-        <v>-2.56</v>
+        <v>7.67</v>
+      </c>
+      <c r="R108" s="24" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.49</v>
+        <v>44.31</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>44.11</v>
+        <v>44.03</v>
       </c>
       <c r="E109" s="14" t="n">
         <v>43.8</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.83</v>
+        <v>43.78</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>44.05</v>
+        <v>43.96</v>
       </c>
       <c r="H109" s="16" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J109" s="17" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="K109" s="18" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="L109" s="19" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="M109" s="19" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O109" s="21" t="n">
         <v>43.67</v>
       </c>
-      <c r="I109" s="17" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="J109" s="17" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="K109" s="18" t="n">
-        <v>43.58</v>
-      </c>
-      <c r="L109" s="19" t="n">
-        <v>43.27</v>
-      </c>
-      <c r="M109" s="19" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="N109" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O109" s="21" t="n">
-        <v>43.64</v>
-      </c>
       <c r="P109" s="21" t="n">
-        <v>43.61</v>
+        <v>43.66</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>43.62</v>
+        <v>43.6</v>
       </c>
       <c r="R109" s="23" t="n">
-        <v>-0.41</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="110">
@@ -7392,37 +7392,37 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>68.48999999999999</v>
+        <v>67.27</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>66.64</v>
+        <v>66.02</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>65.09</v>
+        <v>64.97</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.88</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>66.12</v>
+        <v>65.72</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.27</v>
+        <v>64.47</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.03</v>
+        <v>63.68</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>62.42</v>
+        <v>63.22</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>64.06</v>
+        <v>64.28</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>62.51</v>
+        <v>63.23</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>60.66</v>
+        <v>61.98</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>64.23</v>
+        <v>64.42</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>64.2</v>
+        <v>64.37</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>63.65</v>
-      </c>
-      <c r="R110" s="23" t="n">
-        <v>-1.16</v>
+        <v>64.15000000000001</v>
+      </c>
+      <c r="R110" s="24" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="111">
@@ -7454,34 +7454,34 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.24</v>
+        <v>10.16</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>10.09</v>
+        <v>10.05</v>
       </c>
       <c r="F111" s="15" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="G111" s="15" t="n">
         <v>10.08</v>
       </c>
-      <c r="G111" s="15" t="n">
-        <v>10.14</v>
-      </c>
       <c r="H111" s="16" t="n">
-        <v>10.06</v>
+        <v>10.02</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K111" s="18" t="n">
-        <v>10.05</v>
+        <v>10.01</v>
       </c>
       <c r="L111" s="19" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M111" s="19" t="n">
         <v>9.9</v>
@@ -7492,16 +7492,16 @@
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.06</v>
+        <v>10.02</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="R111" s="25" t="n">
-        <v>0.3</v>
+        <v>10.01</v>
+      </c>
+      <c r="R111" s="23" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="112">
@@ -7516,37 +7516,37 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>332.62</v>
+        <v>318.02</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>318.02</v>
+        <v>306.02</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>305.79</v>
+        <v>295.96</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>304.93</v>
+        <v>295.53</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>314.27</v>
+        <v>303.07</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>299.67</v>
+        <v>291.07</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>290.33</v>
+        <v>283.53</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>285.07</v>
+        <v>279.07</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>297.61</v>
+        <v>289.24</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>285.38</v>
+        <v>279.18</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>270.78</v>
+        <v>267.18</v>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
@@ -7554,16 +7554,16 @@
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>299.21</v>
+        <v>290.62</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>298.75</v>
+        <v>290.18</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>295.6</v>
+        <v>288</v>
       </c>
       <c r="R112" s="23" t="n">
-        <v>-2.12</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>230.59</v>
+        <v>226.23</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>226.89</v>
+        <v>223.43</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>223.79</v>
+        <v>221.08</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>223.83</v>
+        <v>222.17</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>226.07</v>
+        <v>223.33</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>222.37</v>
+        <v>220.53</v>
       </c>
       <c r="I113" s="17" t="n">
+        <v>219.37</v>
+      </c>
+      <c r="J113" s="17" t="n">
+        <v>217.73</v>
+      </c>
+      <c r="K113" s="18" t="n">
+        <v>219.52</v>
+      </c>
+      <c r="L113" s="19" t="n">
+        <v>217.17</v>
+      </c>
+      <c r="M113" s="19" t="n">
+        <v>214.37</v>
+      </c>
+      <c r="N113" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O113" s="21" t="n">
         <v>220.13</v>
       </c>
-      <c r="J113" s="17" t="n">
-        <v>218.67</v>
-      </c>
-      <c r="K113" s="18" t="n">
-        <v>221.71</v>
-      </c>
-      <c r="L113" s="19" t="n">
-        <v>218.61</v>
-      </c>
-      <c r="M113" s="19" t="n">
-        <v>214.91</v>
-      </c>
-      <c r="N113" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O113" s="21" t="n">
-        <v>222.18</v>
-      </c>
       <c r="P113" s="21" t="n">
-        <v>222</v>
+        <v>219.73</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>221.6</v>
-      </c>
-      <c r="R113" s="25" t="n">
-        <v>0.09</v>
+        <v>221</v>
+      </c>
+      <c r="R113" s="23" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="114">
@@ -7640,37 +7640,37 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>646.2</v>
+        <v>624.99</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>629.7</v>
+        <v>614.49</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>615.87</v>
+        <v>605.6900000000001</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>614</v>
+        <v>605.5</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>608.5</v>
+        <v>601.5</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>597.5</v>
+        <v>595</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>606.63</v>
+        <v>599.8099999999999</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>592.8</v>
+        <v>591.01</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>576.3</v>
+        <v>580.51</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7678,16 +7678,16 @@
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>608.21</v>
+        <v>601.0599999999999</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>607.92</v>
+        <v>600.63</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>-2.27</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="115">
@@ -7702,37 +7702,37 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.29</v>
+        <v>6.59</v>
       </c>
       <c r="D115" s="13" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G115" s="15" t="n">
         <v>6.12</v>
       </c>
-      <c r="E115" s="14" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="G115" s="15" t="n">
-        <v>6.11</v>
-      </c>
       <c r="H115" s="16" t="n">
-        <v>5.94</v>
+        <v>5.74</v>
       </c>
       <c r="I115" s="17" t="n">
-        <v>5.88</v>
+        <v>5.49</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>5.77</v>
+        <v>5.36</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>5.88</v>
+        <v>5.68</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>5.73</v>
+        <v>5.37</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>5.56</v>
+        <v>4.99</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>5.92</v>
+        <v>5.72</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>5.89</v>
+        <v>5.71</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>5.98</v>
+        <v>5.63</v>
       </c>
       <c r="R115" s="23" t="n">
-        <v>-3.55</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="116">
@@ -7764,37 +7764,37 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>96.02</v>
+        <v>95.39</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>93.72</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>91.79000000000001</v>
+        <v>90.52</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>91.53</v>
+        <v>90.25</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>93.06999999999999</v>
+        <v>92</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>90.77</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>89.23</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>88.47</v>
+        <v>86.7</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>90.51000000000001</v>
+        <v>89.03</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>88.58</v>
+        <v>86.81</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>86.28</v>
+        <v>84.16</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
@@ -7802,16 +7802,16 @@
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>90.73</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>90.69</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>90</v>
+        <v>88.5</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>-2.23</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="117">
@@ -7826,37 +7826,37 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>10.62</v>
+        <v>10.03</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>10.11</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.68</v>
+        <v>9.44</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>9.970000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.460000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>8.949999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>8.960000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>8.449999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>9.44</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R117" s="23" t="n">
-        <v>-5.49</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="118">
@@ -7888,37 +7888,37 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>17.35</v>
+        <v>16.81</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.89</v>
+        <v>16.5</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.51</v>
+        <v>16.24</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.48</v>
+        <v>16.25</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.78</v>
+        <v>16.44</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>16.32</v>
+        <v>16.13</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>16.02</v>
+        <v>15.94</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.86</v>
+        <v>15.82</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>16.25</v>
+        <v>16.07</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.87</v>
+        <v>15.81</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.41</v>
+        <v>15.5</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
@@ -7926,16 +7926,16 @@
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.3</v>
+        <v>16.11</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.29</v>
+        <v>16.09</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.19</v>
+        <v>16.07</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>-1.22</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="119">
@@ -7950,37 +7950,37 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.85</v>
+        <v>11.27</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.41</v>
+        <v>11.04</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>11.04</v>
+        <v>10.85</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.99</v>
+        <v>10.87</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>10.85</v>
+        <v>10.77</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.55</v>
+        <v>10.64</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.41</v>
+        <v>10.54</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>10.8</v>
+        <v>10.72</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.43</v>
+        <v>10.53</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>9.99</v>
+        <v>10.3</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
@@ -7988,16 +7988,16 @@
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>10.84</v>
+        <v>10.75</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>10.83</v>
+        <v>10.74</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="R119" s="23" t="n">
-        <v>-4.04</v>
+        <v>10.74</v>
+      </c>
+      <c r="R119" s="24" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>13.07</v>
+        <v>12.31</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.55</v>
+        <v>12.09</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.12</v>
+        <v>11.9</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.06</v>
+        <v>11.92</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.41</v>
+        <v>12.05</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>11.89</v>
+        <v>11.83</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>11.54</v>
+        <v>11.7</v>
       </c>
       <c r="J120" s="17" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="K120" s="18" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="L120" s="19" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="M120" s="19" t="n">
         <v>11.37</v>
       </c>
-      <c r="K120" s="18" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="L120" s="19" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="M120" s="19" t="n">
-        <v>10.87</v>
-      </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.88</v>
+        <v>11.81</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.86</v>
+        <v>11.8</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="R120" s="23" t="n">
-        <v>-3.38</v>
+        <v>11.8</v>
+      </c>
+      <c r="R120" s="24" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="121">
@@ -8074,37 +8074,37 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.85</v>
+        <v>7.55</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.51</v>
+        <v>7.33</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.21</v>
+        <v>7.12</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.09</v>
+        <v>7.04</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>6.87</v>
+        <v>6.9</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.75</v>
+        <v>6.82</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>6.75</v>
+        <v>6.83</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>6.41</v>
+        <v>6.61</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
@@ -8112,16 +8112,16 @@
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
       <c r="R121" s="23" t="n">
-        <v>-5.79</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="122">
@@ -8136,37 +8136,37 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>8.220000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>7.64</v>
+        <v>7.04</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>7.15</v>
+        <v>6.74</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>7.09</v>
+        <v>6.72</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>7.47</v>
+        <v>6.94</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>6.89</v>
+        <v>6.59</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.51</v>
+        <v>6.37</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>6.83</v>
+        <v>6.55</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>6.34</v>
+        <v>6.25</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>5.76</v>
+        <v>5.9</v>
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
@@ -8174,16 +8174,16 @@
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>6.88</v>
+        <v>6.58</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>6.87</v>
+        <v>6.57</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>6.7</v>
+        <v>6.49</v>
       </c>
       <c r="R122" s="23" t="n">
-        <v>-10.31</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="123">
@@ -8198,37 +8198,37 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>30.49</v>
+        <v>29.13</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>29.57</v>
+        <v>28.79</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.8</v>
+        <v>28.51</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.8</v>
+        <v>28.59</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>29.36</v>
+        <v>28.75</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.44</v>
+        <v>28.41</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>27.88</v>
+        <v>28.25</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>27.52</v>
+        <v>28.07</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>28.28</v>
+        <v>28.31</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>27.51</v>
+        <v>28.03</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>26.59</v>
+        <v>27.69</v>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
@@ -8236,16 +8236,16 @@
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>28.4</v>
+        <v>28.38</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>28.35</v>
+        <v>28.34</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="R123" s="23" t="n">
-        <v>-0.77</v>
+        <v>28.42</v>
+      </c>
+      <c r="R123" s="24" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="124">
@@ -8260,37 +8260,37 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>171.1</v>
+        <v>169.96</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>165.6</v>
+        <v>163.56</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>160.99</v>
+        <v>158.19</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>160.37</v>
+        <v>158.67</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>164.03</v>
+        <v>162.33</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>158.53</v>
+        <v>155.93</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>154.87</v>
+        <v>152.27</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>153.03</v>
+        <v>149.53</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>157.91</v>
+        <v>154.61</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>153.3</v>
+        <v>149.24</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>147.8</v>
+        <v>142.84</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
@@ -8298,16 +8298,16 @@
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>158.44</v>
+        <v>155.52</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>158.34</v>
+        <v>155.11</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>156.7</v>
+        <v>155</v>
       </c>
       <c r="R124" s="23" t="n">
-        <v>-2.25</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="125">
@@ -8322,37 +8322,37 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>56.97</v>
+        <v>56.35</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>55.72</v>
+        <v>54.9</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>54.68</v>
+        <v>53.68</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>54.73</v>
+        <v>53.52</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>55.47</v>
+        <v>54.48</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>54.22</v>
+        <v>53.03</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>53.48</v>
+        <v>52.07</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>52.97</v>
+        <v>51.58</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>53.98</v>
+        <v>52.87</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>52.93</v>
+        <v>51.65</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>51.68</v>
+        <v>50.2</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8360,16 +8360,16 @@
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>54.14</v>
+        <v>53.01</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>54.07</v>
+        <v>52.98</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>54</v>
+        <v>52.55</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>-1.82</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.16</v>
+        <v>14.14</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>13.62</v>
+        <v>13.59</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.17</v>
+        <v>13.13</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.14</v>
+        <v>13.31</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>13.49</v>
+        <v>13.55</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>12.6</v>
+        <v>12.76</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.41</v>
+        <v>12.45</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>12.87</v>
+        <v>12.82</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.42</v>
+        <v>12.36</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>11.81</v>
+      </c>
+      <c r="N126" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
         <v>12.93</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>12.91</v>
+        <v>12.86</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R126" s="23" t="n">
-        <v>-6.23</v>
+        <v>13.06</v>
+      </c>
+      <c r="R126" s="24" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="127">
@@ -8446,34 +8446,34 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>16.15</v>
+        <v>15.52</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15.48</v>
+        <v>15</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.92</v>
+        <v>14.57</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.85</v>
+        <v>14.58</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>15.29</v>
+        <v>14.89</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.62</v>
+        <v>14.37</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.18</v>
+        <v>14.06</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>13.95</v>
+        <v>13.85</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.55</v>
+        <v>14.27</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>13.99</v>
+        <v>13.84</v>
       </c>
       <c r="M127" s="19" t="n">
         <v>13.32</v>
@@ -8484,16 +8484,16 @@
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.61</v>
+        <v>14.34</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.6</v>
+        <v>14.31</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>-2.44</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="128">
@@ -8508,37 +8508,37 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>7.48</v>
+        <v>6.75</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.97</v>
+        <v>6.5</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>6.54</v>
+        <v>6.29</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>6.53</v>
+        <v>6.33</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>6.85</v>
+        <v>6.46</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.34</v>
+        <v>6.21</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.02</v>
+        <v>6.08</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>5.83</v>
+        <v>5.96</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>5.82</v>
+        <v>5.95</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.31</v>
+        <v>5.7</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
@@ -8546,16 +8546,16 @@
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.31</v>
+        <v>6.19</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.22</v>
+        <v>6.19</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>-9.859999999999999</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>10.7</v>
+        <v>10.26</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.859999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.16</v>
+        <v>9.34</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.390000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.789999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>8.949999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>8.109999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>7.98</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>8.140000000000001</v>
+      </c>
+      <c r="N129" s="25" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>8.85</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>8.75</v>
+        <v>9.1</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="R129" s="23" t="n">
-        <v>-6.25</v>
+        <v>9.17</v>
+      </c>
+      <c r="R129" s="24" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>150.76</v>
+        <v>158.68</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>148.56</v>
+        <v>152.88</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>146.72</v>
+        <v>148.02</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>147.8</v>
+        <v>147.9</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>148.6</v>
+        <v>151.5</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>146.4</v>
+        <v>145.7</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>145.6</v>
+        <v>142.1</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>144.2</v>
+        <v>139.9</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>145.48</v>
+        <v>144.78</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>143.64</v>
+        <v>139.92</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>141.44</v>
-      </c>
-      <c r="N130" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>134.12</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>146.03</v>
+        <v>145.46</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>145.66</v>
+        <v>145.23</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>147</v>
+        <v>144.3</v>
       </c>
       <c r="R130" s="23" t="n">
-        <v>-0.14</v>
+        <v>-1.84</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -253,10 +253,10 @@
     <xf numFmtId="2" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-21</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -761,51 +761,51 @@
         <v>20.39</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.24</v>
+        <v>20.25</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.12</v>
+        <v>20.13</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.11</v>
+        <v>20.17</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.2</v>
+        <v>20.23</v>
       </c>
       <c r="H3" s="16" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="K3" s="18" t="n">
         <v>20.05</v>
       </c>
-      <c r="I3" s="17" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="J3" s="17" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="K3" s="18" t="n">
-        <v>20.03</v>
-      </c>
       <c r="L3" s="19" t="n">
-        <v>19.91</v>
+        <v>19.93</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.76</v>
+        <v>19.79</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>20.05</v>
+        <v>20.08</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.04</v>
+        <v>20.06</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.01</v>
+        <v>20.1</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>-0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.07</v>
+        <v>11.92</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.91</v>
+        <v>11.82</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.77</v>
+        <v>11.74</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.79</v>
+        <v>11.78</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.88</v>
+        <v>11.82</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>11.72</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.63</v>
+        <v>11.68</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>11.56</v>
+        <v>11.62</v>
       </c>
       <c r="K4" s="18" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>11.69</v>
       </c>
-      <c r="L4" s="19" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>11.7</v>
-      </c>
       <c r="Q4" s="22" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="R4" s="24" t="n">
-        <v>0</v>
+        <v>11.74</v>
+      </c>
+      <c r="R4" s="23" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>14.97</v>
+        <v>14.98</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.79</v>
+        <v>14.81</v>
       </c>
       <c r="E5" s="14" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="H5" s="16" t="n">
         <v>14.64</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>14.6</v>
-      </c>
       <c r="I5" s="17" t="n">
-        <v>14.53</v>
+        <v>14.59</v>
       </c>
       <c r="J5" s="17" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="L5" s="19" t="n">
         <v>14.42</v>
       </c>
-      <c r="K5" s="18" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="L5" s="19" t="n">
-        <v>14.39</v>
-      </c>
       <c r="M5" s="19" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="N5" s="25" t="inlineStr">
+        <v>14.25</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="P5" s="21" t="n">
         <v>14.58</v>
       </c>
-      <c r="P5" s="21" t="n">
-        <v>14.55</v>
-      </c>
       <c r="Q5" s="22" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="R5" s="24" t="n">
-        <v>1.11</v>
+        <v>14.7</v>
+      </c>
+      <c r="R5" s="23" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.81</v>
+        <v>21.71</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.36</v>
+        <v>21.4</v>
       </c>
       <c r="E6" s="14" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I6" s="17" t="n">
         <v>20.98</v>
       </c>
-      <c r="F6" s="15" t="n">
-        <v>21.21</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>21.37</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>20.76</v>
-      </c>
       <c r="J6" s="17" t="n">
-        <v>20.47</v>
+        <v>20.79</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>20.73</v>
+        <v>20.97</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.35</v>
+        <v>20.71</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N6" s="25" t="inlineStr">
+        <v>20.4</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>20.84</v>
+        <v>21.04</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>20.76</v>
+        <v>20.99</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="R6" s="24" t="n">
-        <v>1.3</v>
+        <v>21.18</v>
+      </c>
+      <c r="R6" s="23" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.01</v>
+        <v>34.25</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.63</v>
+        <v>33.85</v>
       </c>
       <c r="E7" s="14" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="M7" s="19" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="P7" s="21" t="n">
         <v>33.32</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>33.61</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>33.23</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>33.07</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="L7" s="19" t="n">
-        <v>32.79</v>
-      </c>
-      <c r="M7" s="19" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="N7" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="n">
-        <v>33.18</v>
-      </c>
-      <c r="P7" s="21" t="n">
-        <v>33.13</v>
-      </c>
       <c r="Q7" s="22" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="R7" s="24" t="n">
-        <v>1.16</v>
+        <v>33.6</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.29</v>
+        <v>23.06</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.05</v>
+        <v>22.92</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.85</v>
+        <v>22.8</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>22.93</v>
+        <v>22.82</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.03</v>
+        <v>22.89</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.79</v>
+        <v>22.75</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.69</v>
+        <v>22.68</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.55</v>
+        <v>22.61</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>22.71</v>
+        <v>22.72</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>22.51</v>
+        <v>22.6</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
+        <v>22.46</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>22.76</v>
+        <v>22.74</v>
       </c>
       <c r="P8" s="21" t="n">
         <v>22.73</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="R8" s="23" t="n">
-        <v>-0.78</v>
+        <v>22.74</v>
+      </c>
+      <c r="R8" s="25" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>123.65</v>
+        <v>124.06</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>121.95</v>
+        <v>121.86</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>120.53</v>
+        <v>120.02</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>120.47</v>
+        <v>120.57</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>121.53</v>
+        <v>121.63</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>119.83</v>
+        <v>119.43</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>118.77</v>
+        <v>118.37</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>118.13</v>
+        <v>117.23</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>119.57</v>
+        <v>118.78</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>118.15</v>
+        <v>116.94</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>116.45</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
+        <v>114.74</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>119.77</v>
+        <v>119.19</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>119.71</v>
+        <v>118.96</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>119.4</v>
+        <v>119.5</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>-1.49</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>67.26000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>66.76000000000001</v>
+        <v>65.48</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>66.34</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>66.34999999999999</v>
+        <v>64.88</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>66.65000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>66.15000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>65.84999999999999</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>65.65000000000001</v>
+        <v>63.92</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>66.06</v>
+        <v>64.5</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>65.64</v>
+        <v>63.92</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>65.14</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+        <v>63.22</v>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>66.12</v>
+        <v>64.59</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>66.09999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>66.05</v>
-      </c>
-      <c r="R10" s="23" t="n">
-        <v>-0.15</v>
+        <v>64.45</v>
+      </c>
+      <c r="R10" s="25" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25.22</v>
+        <v>25.1</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.85</v>
+        <v>24.77</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.54</v>
+        <v>24.5</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.58</v>
+        <v>24.68</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.78</v>
+        <v>24.79</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.41</v>
+        <v>24.46</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.21</v>
+        <v>24.35</v>
       </c>
       <c r="J11" s="17" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="L11" s="19" t="n">
         <v>24.04</v>
       </c>
-      <c r="K11" s="18" t="n">
-        <v>24.33</v>
-      </c>
-      <c r="L11" s="19" t="n">
-        <v>24.02</v>
-      </c>
       <c r="M11" s="19" t="n">
-        <v>23.65</v>
+        <v>23.71</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.39</v>
+        <v>24.4</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.36</v>
+        <v>24.34</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.37</v>
+        <v>24.57</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>-0.08</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.38</v>
+        <v>25.02</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25.02</v>
+        <v>24.8</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.72</v>
+        <v>24.61</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.72</v>
+        <v>24.73</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.94</v>
+        <v>24.81</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.58</v>
+        <v>24.59</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.36</v>
+        <v>24.51</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.22</v>
+        <v>24.37</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>24.52</v>
+        <v>24.49</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.22</v>
+        <v>24.3</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>23.86</v>
+        <v>24.08</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.56</v>
+        <v>24.55</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.55</v>
+        <v>24.51</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.5</v>
+        <v>24.66</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>41.44</v>
+        <v>41.18</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>40.86</v>
+        <v>40.76</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.37</v>
+        <v>40.41</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>40.36</v>
+        <v>40.48</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>40.72</v>
+        <v>40.7</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.14</v>
+        <v>40.28</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>39.78</v>
+        <v>40.06</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.56</v>
+        <v>39.86</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.05</v>
+        <v>40.17</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.56</v>
+        <v>39.82</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>38.98</v>
+        <v>39.4</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.12</v>
+        <v>40.24</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.09</v>
+        <v>40.21</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40</v>
+        <v>40.26</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>-0.5</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.52</v>
+        <v>9.07</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.43</v>
+        <v>8.77</v>
       </c>
       <c r="E14" s="14" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K14" s="18" t="n">
         <v>8.35</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="L14" s="19" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Q14" s="22" t="n">
         <v>8.35</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="Q14" s="22" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="R14" s="23" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>14.79</v>
+        <v>13.93</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.22</v>
+        <v>13.7</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.74</v>
+        <v>13.51</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>14.09</v>
+        <v>13.7</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.52</v>
+        <v>13.47</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.18</v>
+        <v>13.39</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>12.95</v>
+        <v>13.24</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.43</v>
+        <v>13.38</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>12.95</v>
+        <v>13.19</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>12.38</v>
+        <v>12.96</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.5</v>
+        <v>13.44</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.47</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.4</v>
+        <v>13.53</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>-3.32</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="I16" s="17" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="J16" s="17" t="n">
         <v>3.63</v>
       </c>
-      <c r="J16" s="17" t="n">
-        <v>3.51</v>
-      </c>
       <c r="K16" s="18" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>3.74</v>
+        <v>3.93</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>-0.8</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.68</v>
+        <v>17.65</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.23</v>
+        <v>17.34</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>16.85</v>
+        <v>17.08</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.03</v>
+        <v>17.18</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.21</v>
+        <v>17.32</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.76</v>
+        <v>17.01</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.58</v>
+        <v>16.87</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.31</v>
+        <v>16.7</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>16.6</v>
+        <v>16.91</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.22</v>
+        <v>16.65</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="N17" s="25" t="inlineStr">
+        <v>16.34</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.7</v>
+        <v>16.97</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>16.63</v>
+        <v>16.93</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="R17" s="24" t="n">
-        <v>0.12</v>
+        <v>17.04</v>
+      </c>
+      <c r="R17" s="23" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>23.82</v>
+        <v>24.94</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>23.63</v>
+        <v>24.36</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>23.47</v>
+        <v>23.87</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>23.5</v>
+        <v>24.02</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>23.6</v>
+        <v>24.3</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>23.41</v>
+        <v>23.72</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.31</v>
+        <v>23.44</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>23.22</v>
+        <v>23.14</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.36</v>
+        <v>23.55</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>23.2</v>
+        <v>23.06</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>23.01</v>
+        <v>22.48</v>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.39</v>
+        <v>23.66</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.38</v>
+        <v>23.59</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="R18" s="24" t="n">
-        <v>0.21</v>
+        <v>23.74</v>
+      </c>
+      <c r="R18" s="23" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="19">
@@ -1750,39 +1750,39 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>65.33</v>
+        <v>64.86</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>63.98</v>
+        <v>63.71</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>62.85</v>
+        <v>62.75</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>63.2</v>
+        <v>63.18</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.85</v>
+        <v>63.67</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>62.5</v>
+        <v>62.52</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>61.85</v>
+        <v>62.03</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61.15</v>
+        <v>61.37</v>
       </c>
       <c r="K19" s="18" t="n">
         <v>62.1</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.97</v>
+        <v>61.14</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>59.62</v>
-      </c>
-      <c r="N19" s="25" t="inlineStr">
+        <v>59.99</v>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -1791,13 +1791,13 @@
         <v>62.35</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>62.2</v>
+        <v>62.19</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>62.55</v>
+        <v>62.7</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.06</v>
+        <v>11.07</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="F20" s="15" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H20" s="16" t="n">
         <v>10.73</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="H20" s="16" t="n">
+      <c r="I20" s="17" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="P20" s="21" t="n">
         <v>10.67</v>
       </c>
-      <c r="I20" s="17" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>10.66</v>
-      </c>
       <c r="Q20" s="22" t="n">
-        <v>10.62</v>
+        <v>10.79</v>
       </c>
       <c r="R20" s="23" t="n">
-        <v>-0.84</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.69</v>
+        <v>17.23</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.31</v>
+        <v>17.02</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>17</v>
+        <v>16.84</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>16.95</v>
+        <v>16.91</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.21</v>
+        <v>17.01</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>16.83</v>
+        <v>16.8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>16.57</v>
+        <v>16.7</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.45</v>
+        <v>16.59</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.78</v>
+        <v>16.73</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.47</v>
+        <v>16.55</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
+        <v>16.34</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="Q21" s="22" t="n">
         <v>16.82</v>
       </c>
-      <c r="P21" s="21" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="Q21" s="22" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="R21" s="24" t="n">
-        <v>0</v>
+      <c r="R21" s="23" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.88</v>
+        <v>36.83</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.14</v>
+        <v>36.13</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.52</v>
+        <v>35.55</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.57</v>
+        <v>35.89</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>35.99</v>
+        <v>36.15</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.25</v>
+        <v>35.45</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>34.83</v>
+        <v>35.19</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.51</v>
+        <v>34.75</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>35.1</v>
+        <v>35.15</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.48</v>
+        <v>34.57</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>33.74</v>
+        <v>33.87</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="P22" s="21" t="n">
         <v>35.21</v>
       </c>
-      <c r="P22" s="21" t="n">
-        <v>35.16</v>
-      </c>
       <c r="Q22" s="22" t="n">
-        <v>35.14</v>
+        <v>35.64</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>-1.57</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.52</v>
+        <v>16.24</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>16.08</v>
+        <v>15.85</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.71</v>
+        <v>15.52</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.66</v>
+        <v>15.53</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.96</v>
+        <v>15.77</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.52</v>
+        <v>15.38</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.22</v>
+        <v>15.14</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>15.08</v>
+        <v>14.99</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>15.47</v>
+        <v>15.31</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>15.1</v>
+        <v>14.98</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
+        <v>14.59</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15.5</v>
+        <v>15.34</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="R23" s="23" t="n">
-        <v>-2.72</v>
+        <v>15.3</v>
+      </c>
+      <c r="R23" s="25" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37</v>
+        <v>37.6</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.28</v>
+        <v>36.76</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.68</v>
+        <v>36.06</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.79</v>
+        <v>36.43</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.17</v>
+        <v>36.75</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.45</v>
+        <v>35.91</v>
       </c>
       <c r="I24" s="17" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="J24" s="17" t="n">
         <v>35.07</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <v>34.73</v>
-      </c>
       <c r="K24" s="18" t="n">
-        <v>35.28</v>
+        <v>35.58</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.68</v>
+        <v>34.88</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33.96</v>
+        <v>34.04</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.39</v>
+        <v>35.78</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>35.33</v>
+        <v>35.65</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>35.4</v>
+        <v>36.1</v>
       </c>
       <c r="R24" s="23" t="n">
-        <v>-0.45</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>61.51</v>
+        <v>59.1</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>59.31</v>
+        <v>57.8</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>57.47</v>
+        <v>56.71</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>57.95</v>
+        <v>57.27</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>59.05</v>
+        <v>57.78</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>56.85</v>
+        <v>56.48</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>55.75</v>
+        <v>55.97</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>54.65</v>
+        <v>55.18</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>56.23</v>
+        <v>55.99</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.39</v>
+        <v>54.9</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="N25" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>53.6</v>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>56.63</v>
+        <v>56.29</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>56.41</v>
+        <v>56.09</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>56.85</v>
-      </c>
-      <c r="R25" s="24" t="n">
-        <v>0.62</v>
+        <v>56.75</v>
+      </c>
+      <c r="R25" s="25" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>226.69</v>
+        <v>227.62</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>220.39</v>
+        <v>219.82</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>215.11</v>
+        <v>213.28</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>216.27</v>
+        <v>212.93</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>219.53</v>
+        <v>217.87</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>213.23</v>
+        <v>210.07</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>209.97</v>
+        <v>205.13</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>206.93</v>
+        <v>202.27</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>211.59</v>
+        <v>208.92</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>206.31</v>
+        <v>202.38</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>200.01</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
+        <v>194.58</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>212.66</v>
+        <v>209.8</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>212.08</v>
+        <v>209.52</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>213</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>-0.47</v>
+        <v>208</v>
+      </c>
+      <c r="R26" s="25" t="n">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>84.33</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>81.78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>79.64</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>79.48</v>
+        <v>77.63</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>81.12</v>
+        <v>78.37</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>78.56999999999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>76.93000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>76.02</v>
+        <v>75.77</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>78.20999999999999</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>76.06999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>73.52</v>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="N27" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>78.48999999999999</v>
+        <v>76.98</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>78.41</v>
+        <v>76.89</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>77.84999999999999</v>
-      </c>
-      <c r="R27" s="23" t="n">
-        <v>-1.46</v>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="R27" s="25" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21.4</v>
+        <v>21.16</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.89</v>
+        <v>20.83</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.46</v>
+        <v>20.56</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.56</v>
+        <v>20.71</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.82</v>
+        <v>20.84</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.31</v>
+        <v>20.51</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.05</v>
+        <v>20.38</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.8</v>
+        <v>20.18</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>20.17</v>
+        <v>20.37</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>19.74</v>
+        <v>20.1</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="N28" s="25" t="inlineStr">
+        <v>19.77</v>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O28" s="21" t="n">
-        <v>20.26</v>
+        <v>20.45</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>20.21</v>
+        <v>20.4</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="R28" s="24" t="n">
-        <v>1.2</v>
+        <v>20.59</v>
+      </c>
+      <c r="R28" s="23" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>81.88</v>
+        <v>83.13</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>79.48</v>
+        <v>80.33</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>77.47</v>
+        <v>77.98</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>79.06999999999999</v>
+        <v>79.63</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>76.67</v>
+        <v>76.83</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>75.33</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>74.27</v>
+        <v>74.03</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>76.13</v>
+        <v>76.42</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>74.12</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>71.72</v>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
+        <v>71.27</v>
+      </c>
+      <c r="N29" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>76.48999999999999</v>
+        <v>76.73</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>76.31999999999999</v>
+        <v>76.63</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="R29" s="23" t="n">
-        <v>-1.29</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="R29" s="25" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>28.24</v>
+        <v>28.31</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>27.4</v>
+        <v>27.49</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.11</v>
+        <v>26.75</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>27.41</v>
+        <v>27.27</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>26.57</v>
+        <v>26.45</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>26.27</v>
+        <v>25.93</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>25.73</v>
+        <v>25.63</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>26.22</v>
+        <v>26.34</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>25.52</v>
+        <v>25.65</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="N30" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>24.83</v>
+      </c>
+      <c r="N30" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
         <v>26.43</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>26.29</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R30" s="24" t="n">
-        <v>0.83</v>
+        <v>26.22</v>
+      </c>
+      <c r="R30" s="25" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>48.35</v>
+        <v>49.38</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>47.85</v>
+        <v>48.66</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.43</v>
+        <v>48.06</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.68</v>
+        <v>48.25</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>47.86</v>
+        <v>48.59</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.36</v>
+        <v>47.87</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.18</v>
+        <v>47.53</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>46.86</v>
+        <v>47.15</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.15</v>
+        <v>47.66</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.73</v>
+        <v>47.06</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.23</v>
+        <v>46.34</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.27</v>
+        <v>47.79</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.19</v>
+        <v>47.71</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>-0.04</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>129.81</v>
+        <v>127.45</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>127.21</v>
+        <v>125.75</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>125.03</v>
+        <v>124.33</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>124.73</v>
+        <v>124.8</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>126.47</v>
+        <v>125.6</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>123.87</v>
+        <v>123.9</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>122.13</v>
+        <v>123.1</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>121.27</v>
+        <v>122.2</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>123.57</v>
+        <v>123.37</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>121.39</v>
+        <v>121.95</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>118.79</v>
+        <v>120.25</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>123.82</v>
+        <v>123.7</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>123.77</v>
+        <v>123.51</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>-1.52</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>58.52</v>
+        <v>59.48</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>56.47</v>
+        <v>57.08</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>54.75</v>
+        <v>55.07</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>54.62</v>
+        <v>56.1</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>55.93</v>
+        <v>57.05</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>53.88</v>
+        <v>54.65</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>52.57</v>
+        <v>53.7</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>51.83</v>
+        <v>52.25</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>53.6</v>
+        <v>53.73</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>51.88</v>
+        <v>51.72</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>49.83</v>
+        <v>49.32</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>53.82</v>
+        <v>54.28</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>53.76</v>
+        <v>53.92</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>53.3</v>
+        <v>55.15</v>
       </c>
       <c r="R33" s="23" t="n">
-        <v>-3.09</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>23.84</v>
+        <v>24.24</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.44</v>
+        <v>23.73</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="F34" s="15" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="H34" s="16" t="n">
         <v>23.22</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>23</v>
-      </c>
       <c r="I34" s="17" t="n">
-        <v>22.82</v>
+        <v>23.04</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.6</v>
+        <v>22.71</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>22.88</v>
+        <v>23.01</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.54</v>
+        <v>22.58</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>22.14</v>
+        <v>22.07</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>22.96</v>
+        <v>23.14</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>22.91</v>
+        <v>23.05</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23.03</v>
+        <v>23.36</v>
       </c>
       <c r="R34" s="23" t="n">
-        <v>-0.39</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.11</v>
+        <v>25.85</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.66</v>
+        <v>25.45</v>
       </c>
       <c r="E35" s="14" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="F35" s="15" t="n">
         <v>25.28</v>
       </c>
-      <c r="F35" s="15" t="n">
-        <v>25.23</v>
-      </c>
       <c r="G35" s="15" t="n">
-        <v>25.53</v>
+        <v>25.44</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.08</v>
+        <v>25.04</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>24.78</v>
+        <v>24.88</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>24.63</v>
+        <v>24.64</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>25.03</v>
+        <v>24.89</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>24.65</v>
+        <v>24.55</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>24.2</v>
+        <v>24.15</v>
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>25.07</v>
+        <v>24.98</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>25.06</v>
+        <v>24.92</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>24.93</v>
+        <v>25.12</v>
       </c>
       <c r="R35" s="23" t="n">
-        <v>-1.62</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.94</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.529999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.51</v>
+        <v>8.56</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.43</v>
+        <v>8.44</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="J36" s="17" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="L36" s="19" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="K36" s="18" t="n">
+      <c r="M36" s="19" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="n">
         <v>8.41</v>
       </c>
-      <c r="L36" s="19" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>8.43</v>
-      </c>
       <c r="P36" s="21" t="n">
-        <v>8.43</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="R36" s="23" t="n">
-        <v>-2.34</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>33.99</v>
+        <v>34.04</v>
       </c>
       <c r="D37" s="13" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="F37" s="15" t="n">
         <v>33.03</v>
       </c>
-      <c r="E37" s="14" t="n">
-        <v>32.23</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>32.64</v>
-      </c>
       <c r="G37" s="15" t="n">
-        <v>33.02</v>
+        <v>33.31</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>32.06</v>
+        <v>32.59</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>31.68</v>
+        <v>32.31</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.1</v>
+        <v>31.87</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>31.69</v>
+        <v>32.32</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>30.89</v>
+        <v>31.72</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="N37" s="25" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.91</v>
+        <v>32.48</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.77</v>
+        <v>32.37</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="R37" s="24" t="n">
-        <v>1.26</v>
+        <v>32.74</v>
+      </c>
+      <c r="R37" s="23" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>189.54</v>
+        <v>178.82</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>181.54</v>
+        <v>175.22</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>174.84</v>
+        <v>172.21</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>174.2</v>
+        <v>173.87</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>179.4</v>
+        <v>175.23</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>171.4</v>
+        <v>171.63</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>166.2</v>
+        <v>170.27</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>163.4</v>
+        <v>168.03</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>170.36</v>
+        <v>170.19</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>163.66</v>
+        <v>167.18</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>155.66</v>
+        <v>163.58</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>171.19</v>
+        <v>171.05</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>170.98</v>
+        <v>170.47</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>169</v>
+        <v>172.5</v>
       </c>
       <c r="R38" s="23" t="n">
-        <v>-3.43</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="25" t="inlineStr">
+      <c r="N39" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="Q39" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="R39" s="24" t="n">
+      <c r="R39" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22.05</v>
+        <v>22.25</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>21.65</v>
+        <v>21.72</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.31</v>
+        <v>21.27</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.55</v>
+        <v>21.64</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>20.9</v>
+        <v>20.83</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.75</v>
+        <v>20.58</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>21.09</v>
+        <v>20.98</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.75</v>
+        <v>20.53</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="N40" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.13</v>
+        <v>21.06</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.12</v>
+        <v>21.02</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="R40" s="24" t="n">
-        <v>0.24</v>
+        <v>21.08</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>189.82</v>
+        <v>189.69</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>186.22</v>
+        <v>185.99</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>183.21</v>
+        <v>182.89</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>183.2</v>
+        <v>184.93</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>185.4</v>
+        <v>186.17</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>181.8</v>
+        <v>182.47</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>179.6</v>
+        <v>181.23</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>178.2</v>
+        <v>178.77</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>181.19</v>
+        <v>180.81</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>178.18</v>
+        <v>177.71</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>174.58</v>
+        <v>174.01</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>181.64</v>
+        <v>181.78</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>181.47</v>
+        <v>181.1</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>181</v>
+        <v>183.7</v>
       </c>
       <c r="R41" s="23" t="n">
-        <v>-0.55</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>36.99</v>
+        <v>36.65</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.55</v>
+        <v>36.37</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.18</v>
+        <v>36.14</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>36.21</v>
+        <v>36.29</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>36.47</v>
+        <v>36.39</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>36.03</v>
+        <v>36.11</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>35.77</v>
+        <v>36.01</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.59</v>
+        <v>35.83</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>35.94</v>
+        <v>35.98</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>35.57</v>
+        <v>35.75</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>35.13</v>
+        <v>35.47</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="P42" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="P42" s="21" t="n">
-        <v>35.97</v>
-      </c>
       <c r="Q42" s="22" t="n">
-        <v>35.96</v>
+        <v>36.2</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>-0.11</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>27.75</v>
+        <v>28.07</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.25</v>
+        <v>27.47</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>26.83</v>
+        <v>26.97</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>26.85</v>
+        <v>27.27</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.15</v>
+        <v>27.49</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>26.65</v>
+        <v>26.89</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>26.35</v>
+        <v>26.67</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.15</v>
+        <v>26.29</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>26.55</v>
+        <v>26.63</v>
       </c>
       <c r="L43" s="19" t="n">
         <v>26.13</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>25.63</v>
+        <v>25.53</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>26.62</v>
+        <v>26.78</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>26.59</v>
+        <v>26.68</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>26.56</v>
+        <v>27.06</v>
       </c>
       <c r="R43" s="23" t="n">
-        <v>-0.6</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.09</v>
+        <v>26</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.91</v>
+        <v>25.84</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.76</v>
+        <v>25.7</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.78</v>
+        <v>25.73</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>25.88</v>
+        <v>25.81</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.7</v>
+        <v>25.65</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.6</v>
+        <v>25.57</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.52</v>
+        <v>25.49</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.66</v>
+        <v>25.62</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.51</v>
+        <v>25.48</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="N44" s="20" t="inlineStr">
+        <v>25.32</v>
+      </c>
+      <c r="N44" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.69</v>
+        <v>25.64</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.67</v>
+        <v>25.63</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.68</v>
-      </c>
-      <c r="R44" s="23" t="n">
-        <v>-0.85</v>
+        <v>25.64</v>
+      </c>
+      <c r="R44" s="25" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.61</v>
+        <v>7.5</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.49</v>
+        <v>7.4</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="I45" s="17" t="n">
         <v>7.33</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.29</v>
+        <v>7.26</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.41</v>
+        <v>7.34</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
+        <v>7.12</v>
+      </c>
+      <c r="N45" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
-        <v>7.42</v>
+        <v>7.36</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.42</v>
+        <v>7.35</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>-1.2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.07</v>
+        <v>12.45</v>
       </c>
       <c r="D46" s="13" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H46" s="16" t="n">
         <v>11.84</v>
       </c>
-      <c r="E46" s="14" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>11.62</v>
-      </c>
       <c r="I46" s="17" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="J46" s="17" t="n">
         <v>11.53</v>
       </c>
-      <c r="J46" s="17" t="n">
-        <v>11.39</v>
-      </c>
       <c r="K46" s="18" t="n">
-        <v>11.52</v>
+        <v>11.71</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.33</v>
+        <v>11.45</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N46" s="25" t="inlineStr">
+        <v>11.14</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.58</v>
+        <v>11.79</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.54</v>
+        <v>11.73</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="R46" s="24" t="n">
-        <v>2.46</v>
+        <v>11.94</v>
+      </c>
+      <c r="R46" s="23" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>214.45</v>
+        <v>197.42</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>205.15</v>
+        <v>194.32</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>197.35</v>
+        <v>191.72</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>196.3</v>
+        <v>191.83</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>202.5</v>
+        <v>193.67</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>193.2</v>
+        <v>190.57</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>187</v>
+        <v>188.73</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>183.9</v>
+        <v>187.47</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>192.15</v>
+        <v>189.98</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>184.35</v>
+        <v>187.38</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>175.05</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
+        <v>184.28</v>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>193.04</v>
+        <v>190.4</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>192.87</v>
+        <v>190.22</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="R47" s="23" t="n">
-        <v>-4.71</v>
+        <v>190</v>
+      </c>
+      <c r="R47" s="25" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>46.72</v>
+        <v>45.94</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>46</v>
+        <v>45.52</v>
       </c>
       <c r="E48" s="14" t="n">
+        <v>45.17</v>
+      </c>
+      <c r="F48" s="15" t="n">
         <v>45.4</v>
       </c>
-      <c r="F48" s="15" t="n">
-        <v>45.39</v>
-      </c>
       <c r="G48" s="15" t="n">
-        <v>45.83</v>
+        <v>45.54</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>45.11</v>
+        <v>45.12</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>44.67</v>
+        <v>44.98</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>44.39</v>
+        <v>44.7</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>45</v>
+        <v>44.93</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>44.4</v>
+        <v>44.58</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>43.68</v>
+        <v>44.16</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>45.08</v>
+        <v>45.04</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>45.05</v>
+        <v>44.97</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>44.94</v>
+        <v>45.26</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>-1.23</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>32.42</v>
+        <v>32.7</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>31.9</v>
+        <v>32.12</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>31.47</v>
+        <v>31.63</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>31.41</v>
+        <v>31.94</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>31.75</v>
+        <v>32.14</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.23</v>
+        <v>31.56</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>30.89</v>
+        <v>31.36</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>30.71</v>
+        <v>30.98</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.17</v>
+        <v>31.31</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.22</v>
+        <v>30.24</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>31.22</v>
+        <v>31.46</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>31.21</v>
+        <v>31.35</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>31.06</v>
+        <v>31.74</v>
       </c>
       <c r="R49" s="23" t="n">
-        <v>-2.02</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.39</v>
+        <v>12.92</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.21</v>
+        <v>12.57</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.06</v>
+        <v>12.27</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.13</v>
+        <v>12.44</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.2</v>
+        <v>12.57</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.02</v>
+        <v>12.22</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>11.95</v>
+        <v>12.09</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>11.84</v>
+        <v>11.87</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>11.96</v>
+        <v>12.08</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>11.81</v>
+        <v>11.78</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>11.63</v>
+        <v>11.43</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12</v>
+        <v>12.16</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>11.97</v>
+        <v>12.1</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.05</v>
+        <v>12.31</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>-0.08</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>59.49</v>
+        <v>59.96</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>58.69</v>
+        <v>59.06</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>58.02</v>
+        <v>58.3</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.03</v>
+        <v>58.63</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>58.52</v>
+        <v>59.02</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>57.72</v>
+        <v>58.12</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>57.23</v>
+        <v>57.73</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>56.92</v>
+        <v>57.22</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.58</v>
+        <v>57.8</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>56.91</v>
+        <v>57.04</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>56.11</v>
+        <v>56.14</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.68</v>
+        <v>57.99</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.64</v>
+        <v>57.87</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>57.55</v>
+        <v>58.25</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>-0.35</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.51</v>
+        <v>22.59</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.27</v>
+        <v>22.3</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.07</v>
+        <v>22.06</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.09</v>
+        <v>22.22</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.23</v>
+        <v>22.31</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>21.99</v>
+        <v>22.02</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.85</v>
+        <v>21.93</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.75</v>
+        <v>21.73</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.93</v>
+        <v>21.89</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.73</v>
+        <v>21.65</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>21.49</v>
+        <v>21.36</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
         <v>21.97</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>21.95</v>
+        <v>21.92</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>21.96</v>
+        <v>22.12</v>
       </c>
       <c r="R52" s="23" t="n">
-        <v>-0.18</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="D53" s="13" t="n">
         <v>5.09</v>
       </c>
       <c r="E53" s="14" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="H53" s="16" t="n">
         <v>5.01</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H53" s="16" t="n">
+      <c r="I53" s="17" t="n">
         <v>4.98</v>
       </c>
-      <c r="I53" s="17" t="n">
-        <v>4.92</v>
-      </c>
       <c r="J53" s="17" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>4.97</v>
+        <v>5</v>
       </c>
       <c r="P53" s="21" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>4.96</v>
+        <v>5.03</v>
       </c>
       <c r="R53" s="23" t="n">
-        <v>-1.2</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.85</v>
+        <v>19.62</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.42</v>
+        <v>18.62</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>18.06</v>
+        <v>17.78</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>18.13</v>
+        <v>17.8</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.36</v>
+        <v>18.4</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.93</v>
+        <v>17.4</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.81</v>
+        <v>17.22</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>17.45</v>
+        <v>16.38</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="N54" s="20" t="inlineStr">
+        <v>15.38</v>
+      </c>
+      <c r="N54" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.89</v>
+        <v>17.35</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.85</v>
+        <v>17.3</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="R54" s="23" t="n">
-        <v>-0.5</v>
+        <v>17.2</v>
+      </c>
+      <c r="R54" s="25" t="n">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>96.83</v>
+        <v>97.67</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>95.33</v>
+        <v>96.02</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>94.06999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>94.77</v>
+        <v>94.95</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>95.33</v>
+        <v>95.8</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>93.83</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>93.27</v>
+        <v>93.3</v>
       </c>
       <c r="J55" s="17" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="K55" s="18" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="L55" s="19" t="n">
         <v>92.33</v>
       </c>
-      <c r="K55" s="18" t="n">
-        <v>93.23</v>
-      </c>
-      <c r="L55" s="19" t="n">
-        <v>91.97</v>
-      </c>
       <c r="M55" s="19" t="n">
-        <v>90.47</v>
-      </c>
-      <c r="N55" s="25" t="inlineStr">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>93.59</v>
+        <v>94</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>93.34999999999999</v>
+        <v>93.84</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="R55" s="24" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="R55" s="25" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.65</v>
+        <v>18.37</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.25</v>
+        <v>17.74</v>
       </c>
       <c r="E56" s="14" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="K56" s="18" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N56" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O56" s="21" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="P56" s="21" t="n">
         <v>16.91</v>
       </c>
-      <c r="F56" s="15" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="G56" s="15" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H56" s="16" t="n">
+      <c r="Q56" s="22" t="n">
         <v>16.8</v>
       </c>
-      <c r="I56" s="17" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="J56" s="17" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="K56" s="18" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O56" s="21" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="P56" s="21" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="Q56" s="22" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="R56" s="23" t="n">
-        <v>-1.29</v>
+      <c r="R56" s="25" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.01</v>
+        <v>21.15</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.84</v>
+        <v>20.9</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.69</v>
+        <v>20.7</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.69</v>
+        <v>20.81</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.8</v>
+        <v>20.91</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.63</v>
+        <v>20.66</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.52</v>
+        <v>20.56</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.46</v>
+        <v>20.41</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20.6</v>
+        <v>20.55</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>20.45</v>
+        <v>20.35</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>20.28</v>
+        <v>20.1</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
         <v>20.62</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.61</v>
+        <v>20.57</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.59</v>
+        <v>20.72</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>-0.05</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>23.08</v>
+        <v>22.41</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.66</v>
+        <v>22.22</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.31</v>
+        <v>22.06</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.29</v>
+        <v>22.16</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.56</v>
+        <v>22.23</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.14</v>
+        <v>22.04</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>21.87</v>
+        <v>21.97</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>21.72</v>
+        <v>21.85</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>22.07</v>
+        <v>21.95</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>21.72</v>
+        <v>21.79</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
+        <v>21.6</v>
+      </c>
+      <c r="N58" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22.12</v>
+        <v>22</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>22.11</v>
+        <v>21.97</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>22.03</v>
+        <v>22.1</v>
       </c>
       <c r="R58" s="23" t="n">
-        <v>-2.13</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>27.72</v>
+        <v>27.75</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>27.56</v>
+        <v>27.57</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>27.42</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.42</v>
+        <v>27.52</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27.52</v>
+        <v>27.58</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.36</v>
+        <v>27.4</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.26</v>
+        <v>27.34</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.2</v>
+        <v>27.22</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.34</v>
+        <v>27.32</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.2</v>
+        <v>27.17</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>27.04</v>
+        <v>26.99</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.35</v>
+        <v>27.37</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.35</v>
+        <v>27.33</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.32</v>
+        <v>27.46</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>-0.44</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.65</v>
+        <v>45.18</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.31</v>
+        <v>44.98</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>45.03</v>
+        <v>44.82</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>45.04</v>
+        <v>44.79</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>45.24</v>
+        <v>44.93</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>44.9</v>
+        <v>44.73</v>
       </c>
       <c r="I60" s="17" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="K60" s="18" t="n">
         <v>44.7</v>
       </c>
-      <c r="J60" s="17" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="K60" s="18" t="n">
-        <v>44.83</v>
-      </c>
       <c r="L60" s="19" t="n">
-        <v>44.55</v>
+        <v>44.54</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
+        <v>44.34</v>
+      </c>
+      <c r="N60" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>44.88</v>
+        <v>44.72</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>44.86</v>
+        <v>44.72</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="R60" s="23" t="n">
-        <v>-0.36</v>
+        <v>44.66</v>
+      </c>
+      <c r="R60" s="25" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>18.6</v>
+        <v>18.47</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.38</v>
+        <v>18.33</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.19</v>
+        <v>18.21</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.19</v>
+        <v>18.23</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.32</v>
+        <v>18.3</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.1</v>
+        <v>18.16</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>17.97</v>
+        <v>18.09</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>17.88</v>
+        <v>18.02</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18.07</v>
+        <v>18.13</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>17.88</v>
+        <v>18.01</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.66</v>
+        <v>17.87</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.09</v>
+        <v>18.15</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.09</v>
+        <v>18.14</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>18.05</v>
+        <v>18.15</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>-0.61</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.25</v>
+        <v>15.08</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.09</v>
+        <v>14.99</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>14.95</v>
+        <v>14.91</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>14.97</v>
+        <v>14.94</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.06</v>
+        <v>14.98</v>
       </c>
       <c r="H62" s="16" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K62" s="18" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="N62" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O62" s="21" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="P62" s="21" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="Q62" s="22" t="n">
         <v>14.9</v>
       </c>
-      <c r="I62" s="17" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="J62" s="17" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="K62" s="18" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O62" s="21" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="P62" s="21" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="Q62" s="22" t="n">
-        <v>14.88</v>
-      </c>
       <c r="R62" s="23" t="n">
-        <v>-0.47</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.53</v>
+        <v>24.92</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.2</v>
+        <v>24.42</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>23.93</v>
+        <v>24</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>23.96</v>
+        <v>24.21</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.15</v>
+        <v>24.41</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.82</v>
+        <v>23.91</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.63</v>
+        <v>23.71</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.49</v>
+        <v>23.41</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.74</v>
+        <v>23.72</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.47</v>
+        <v>23.3</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.14</v>
+        <v>22.8</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.79</v>
+        <v>23.83</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.77</v>
+        <v>23.76</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>23.78</v>
-      </c>
-      <c r="R63" s="24" t="n">
-        <v>0.13</v>
+        <v>24.01</v>
+      </c>
+      <c r="R63" s="23" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="64">
@@ -4549,19 +4549,19 @@
         <v>7.06</v>
       </c>
       <c r="F64" s="15" t="n">
-        <v>7.07</v>
+        <v>7.08</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>7.11</v>
+        <v>7.12</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>7.02</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O64" s="21" t="n">
@@ -4584,10 +4584,10 @@
         <v>7.02</v>
       </c>
       <c r="Q64" s="22" t="n">
-        <v>7.02</v>
+        <v>7.04</v>
       </c>
       <c r="R64" s="23" t="n">
-        <v>-0.57</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="65">
@@ -4614,16 +4614,16 @@
         <v>4.8</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="I65" s="17" t="n">
         <v>4.76</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="K65" s="18" t="n">
         <v>4.78</v>
@@ -4634,7 +4634,7 @@
       <c r="M65" s="19" t="n">
         <v>4.71</v>
       </c>
-      <c r="N65" s="20" t="inlineStr">
+      <c r="N65" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -4646,10 +4646,10 @@
         <v>4.78</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="R65" s="23" t="n">
-        <v>-0.42</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.86</v>
+        <v>4.58</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.68</v>
+        <v>4.52</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.63</v>
+        <v>4.51</v>
       </c>
       <c r="H66" s="16" t="n">
         <v>4.45</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="K66" s="18" t="n">
         <v>4.43</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>4.28</v>
+        <v>4.38</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
+        <v>4.32</v>
+      </c>
+      <c r="N66" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="P66" s="21" t="n">
         <v>4.44</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="R66" s="23" t="n">
-        <v>-3.08</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="67">
@@ -4726,22 +4726,22 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>65.43000000000001</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>64.73</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>64.15000000000001</v>
+        <v>63.79</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>64.27</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>64.63</v>
+        <v>64.23</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>63.93</v>
+        <v>63.73</v>
       </c>
       <c r="I67" s="17" t="n">
         <v>63.57</v>
@@ -4750,30 +4750,30 @@
         <v>63.23</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>63.75</v>
+        <v>63.51</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>63.17</v>
+        <v>63.09</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>62.47</v>
-      </c>
-      <c r="N67" s="20" t="inlineStr">
+        <v>62.59</v>
+      </c>
+      <c r="N67" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>63.87</v>
+        <v>63.64</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>63.81</v>
+        <v>63.55</v>
       </c>
       <c r="Q67" s="22" t="n">
         <v>63.9</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>69.91</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>68.11</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>66.59999999999999</v>
+        <v>65.16</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>66.5</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>67.65000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>65.84999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>64.7</v>
+        <v>63.77</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>64.05</v>
+        <v>63.08</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>65.59999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>64.09</v>
+        <v>62.99</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
+        <v>61.44</v>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>65.79000000000001</v>
+        <v>64.52</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>65.73999999999999</v>
+        <v>64.41</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>65.34999999999999</v>
-      </c>
-      <c r="R68" s="23" t="n">
-        <v>-2.32</v>
+        <v>64.45</v>
+      </c>
+      <c r="R68" s="25" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>81.23</v>
+        <v>78.47</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>79.08</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>77.28</v>
+        <v>75.44</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>77.23</v>
+        <v>75.75</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>78.56999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>76.42</v>
+        <v>74.95</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>75.08</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>74.27</v>
+        <v>73.3</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>76.06999999999999</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>74.27</v>
+        <v>73.13</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="N69" s="20" t="inlineStr">
+        <v>71.48</v>
+      </c>
+      <c r="N69" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>76.33</v>
+        <v>74.8</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>76.23999999999999</v>
+        <v>74.64</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="R69" s="23" t="n">
-        <v>-3.19</v>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="R69" s="25" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>124.45</v>
+        <v>119.91</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>120.65</v>
+        <v>117.31</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>117.46</v>
+        <v>115.13</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>118.03</v>
+        <v>116.1</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>120.07</v>
+        <v>117.2</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>116.27</v>
+        <v>114.6</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>114.23</v>
+        <v>113.5</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>112.47</v>
+        <v>112</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>115.34</v>
+        <v>113.67</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>112.15</v>
+        <v>111.49</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>108.35</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
+        <v>108.89</v>
+      </c>
+      <c r="N70" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>115.95</v>
+        <v>114.24</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>115.63</v>
+        <v>113.87</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>116</v>
-      </c>
-      <c r="R70" s="23" t="n">
-        <v>-1.69</v>
+        <v>115</v>
+      </c>
+      <c r="R70" s="25" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.15</v>
+        <v>23.74</v>
       </c>
       <c r="D71" s="13" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="E71" s="14" t="n">
         <v>22.85</v>
       </c>
-      <c r="E71" s="14" t="n">
+      <c r="F71" s="15" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="G71" s="15" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="J71" s="17" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="K71" s="18" t="n">
         <v>22.59</v>
       </c>
-      <c r="F71" s="15" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="G71" s="15" t="n">
-        <v>22.81</v>
-      </c>
-      <c r="H71" s="16" t="n">
-        <v>22.51</v>
-      </c>
-      <c r="I71" s="17" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J71" s="17" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="K71" s="18" t="n">
-        <v>22.43</v>
-      </c>
       <c r="L71" s="19" t="n">
-        <v>22.17</v>
+        <v>22.18</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>21.87</v>
+        <v>21.7</v>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>22.48</v>
+        <v>22.69</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>22.45</v>
+        <v>22.62</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>22.5</v>
+        <v>22.86</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>-0.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>18.7</v>
+        <v>18.42</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.27</v>
+        <v>18.18</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>17.91</v>
+        <v>17.98</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>17.94</v>
+        <v>17.99</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.19</v>
+        <v>18.13</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.76</v>
+        <v>17.89</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.51</v>
+        <v>17.75</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>17.33</v>
+        <v>17.65</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.66</v>
+        <v>17.84</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>17.3</v>
+        <v>17.64</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>16.87</v>
+        <v>17.4</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.73</v>
+        <v>17.88</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.7</v>
+        <v>17.86</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="R72" s="24" t="n">
-        <v>0.11</v>
+        <v>17.85</v>
+      </c>
+      <c r="R72" s="23" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>234.33</v>
+        <v>233.85</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>231.53</v>
+        <v>231.35</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>229.18</v>
+        <v>229.25</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>229.33</v>
+        <v>229.1</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>230.97</v>
+        <v>230.7</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>228.17</v>
+        <v>228.2</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>226.53</v>
+        <v>226.6</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>225.37</v>
+        <v>225.7</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>227.62</v>
+        <v>227.85</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>225.27</v>
+        <v>225.76</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>222.47</v>
-      </c>
-      <c r="N73" s="20" t="inlineStr">
+        <v>223.26</v>
+      </c>
+      <c r="N73" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>228</v>
+        <v>228.12</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>227.83</v>
+        <v>228.05</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>227.7</v>
-      </c>
-      <c r="R73" s="23" t="n">
-        <v>-1</v>
+        <v>227.5</v>
+      </c>
+      <c r="R73" s="25" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.56</v>
+        <v>15.48</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.36</v>
+        <v>15.33</v>
       </c>
       <c r="E74" s="14" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="F74" s="15" t="n">
         <v>15.2</v>
       </c>
-      <c r="F74" s="15" t="n">
-        <v>15.22</v>
-      </c>
       <c r="G74" s="15" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="H74" s="16" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="I74" s="17" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="J74" s="17" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="K74" s="18" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="M74" s="19" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="N74" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O74" s="21" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="P74" s="21" t="n">
         <v>15.13</v>
       </c>
-      <c r="I74" s="17" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="J74" s="17" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="K74" s="18" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="L74" s="19" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="N74" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O74" s="21" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="P74" s="21" t="n">
+      <c r="Q74" s="22" t="n">
         <v>15.1</v>
       </c>
-      <c r="Q74" s="22" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="R74" s="23" t="n">
-        <v>-0.33</v>
+      <c r="R74" s="25" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>36.78</v>
+        <v>36.21</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>36.14</v>
+        <v>35.91</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>35.6</v>
+        <v>35.65</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>35.74</v>
+        <v>35.7</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>36.06</v>
+        <v>35.86</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>35.42</v>
+        <v>35.56</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>34.78</v>
+        <v>35.26</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>35.24</v>
+        <v>35.49</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>34.7</v>
+        <v>35.23</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="N75" s="25" t="inlineStr">
+        <v>34.93</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>35.36</v>
+        <v>35.53</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>35.29</v>
+        <v>35.51</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="R75" s="24" t="n">
-        <v>1.03</v>
+        <v>35.54</v>
+      </c>
+      <c r="R75" s="23" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>22.69</v>
+        <v>24.96</v>
       </c>
       <c r="D76" s="13" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="I76" s="17" t="n">
         <v>21.94</v>
       </c>
-      <c r="E76" s="14" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="F76" s="15" t="n">
-        <v>21.24</v>
-      </c>
-      <c r="G76" s="15" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="H76" s="16" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="17" t="n">
-        <v>20.49</v>
-      </c>
       <c r="J76" s="17" t="n">
-        <v>20.24</v>
+        <v>21.06</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>20.89</v>
+        <v>21.79</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>20.27</v>
+        <v>20.68</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>19.52</v>
+        <v>19.36</v>
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>20.97</v>
+        <v>22.14</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>20.95</v>
+        <v>21.89</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>20.75</v>
+        <v>22.82</v>
       </c>
       <c r="R76" s="23" t="n">
-        <v>-3.4</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.24</v>
+        <v>44.27</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.08</v>
+        <v>43.03</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>42.1</v>
+        <v>41.99</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>42.11</v>
+        <v>42.47</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>42.81</v>
+        <v>42.99</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>41.65</v>
+        <v>41.75</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>40.95</v>
+        <v>41.23</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>40.49</v>
+        <v>40.51</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>41.46</v>
+        <v>41.29</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>40.48</v>
+        <v>40.25</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.32</v>
+        <v>39.01</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>41.6</v>
+        <v>41.57</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>41.55</v>
+        <v>41.39</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>41.4</v>
+        <v>41.96</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>-2.08</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="78">
@@ -5411,51 +5411,51 @@
         <v>5.45</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="E78" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F78" s="15" t="n">
         <v>5.3</v>
       </c>
-      <c r="F78" s="15" t="n">
-        <v>5.32</v>
-      </c>
       <c r="G78" s="15" t="n">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="I78" s="17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J78" s="17" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L78" s="19" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M78" s="19" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="N78" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P78" s="21" t="n">
         <v>5.24</v>
       </c>
-      <c r="J78" s="17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K78" s="18" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="M78" s="19" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O78" s="21" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="P78" s="21" t="n">
-        <v>5.26</v>
-      </c>
       <c r="Q78" s="22" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="R78" s="23" t="n">
-        <v>-0.9399999999999999</v>
+        <v>5.25</v>
+      </c>
+      <c r="R78" s="25" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>19.61</v>
+        <v>18.63</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>19.04</v>
+        <v>18.43</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.56</v>
+        <v>18.27</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.51</v>
+        <v>18.3</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>18.88</v>
+        <v>18.41</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>18.31</v>
+        <v>18.21</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>17.94</v>
+        <v>18.1</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>17.74</v>
+        <v>18.01</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>18.25</v>
+        <v>18.15</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>17.77</v>
+        <v>17.99</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
+        <v>17.79</v>
+      </c>
+      <c r="N79" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O79" s="21" t="n">
-        <v>18.3</v>
+        <v>18.19</v>
       </c>
       <c r="P79" s="21" t="n">
-        <v>18.29</v>
+        <v>18.17</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="R79" s="24" t="n">
-        <v>0.11</v>
+        <v>18.2</v>
+      </c>
+      <c r="R79" s="23" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>82.47</v>
+        <v>79.19</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>80.42</v>
+        <v>78.39</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>78.7</v>
+        <v>77.72</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>78.47</v>
+        <v>78.13</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>79.83</v>
+        <v>78.42</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>77.78</v>
+        <v>77.62</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>76.42</v>
+        <v>77.33</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>75.73</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>77.55</v>
+        <v>77.28</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>75.83</v>
+        <v>76.61</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>73.78</v>
+        <v>75.81</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>77.75</v>
+        <v>77.48</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>77.70999999999999</v>
+        <v>77.34</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>77.09999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="R80" s="23" t="n">
-        <v>-1.47</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="D81" s="13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G81" s="15" t="n">
         <v>4.54</v>
       </c>
-      <c r="E81" s="14" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="F81" s="15" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="G81" s="15" t="n">
-        <v>4.53</v>
-      </c>
       <c r="H81" s="16" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="I81" s="17" t="n">
         <v>4.42</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="R81" s="23" t="n">
-        <v>-0.89</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="F82" s="15" t="n">
+        <v>59.13</v>
+      </c>
+      <c r="G82" s="15" t="n">
         <v>59.92</v>
       </c>
-      <c r="D82" s="13" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="F82" s="15" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="G82" s="15" t="n">
-        <v>58.67</v>
-      </c>
       <c r="H82" s="16" t="n">
-        <v>57.42</v>
+        <v>58.22</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>56.93</v>
+        <v>57.43</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>56.17</v>
+        <v>56.52</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>56.93</v>
+        <v>57.67</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>55.88</v>
+        <v>56.25</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>54.63</v>
-      </c>
-      <c r="N82" s="25" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="N82" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>57.22</v>
+        <v>58.01</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>57.02</v>
+        <v>57.81</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="R82" s="24" t="n">
-        <v>1.58</v>
+        <v>58.35</v>
+      </c>
+      <c r="R82" s="23" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="83">
@@ -5718,54 +5718,54 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>38.08</v>
+        <v>37.36</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.6</v>
+        <v>37.14</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.19</v>
+        <v>36.95</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.14</v>
+        <v>37.02</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.46</v>
+        <v>37.12</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>36.98</v>
+        <v>36.9</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.66</v>
+        <v>36.8</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.5</v>
+        <v>36.68</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>36.93</v>
+        <v>36.83</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.52</v>
+        <v>36.64</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="N83" s="20" t="inlineStr">
+        <v>36.42</v>
+      </c>
+      <c r="N83" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>36.97</v>
+        <v>36.87</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>36.96</v>
+        <v>36.85</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>36.82</v>
+        <v>36.92</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>-0.86</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>96.26000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>94.06</v>
+        <v>92.45</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>92.22</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>93.43000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>94.17</v>
+        <v>92.28</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>91.97</v>
+        <v>91.23</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>91.23</v>
+        <v>90.67</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>89.77</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="K84" s="18" t="n">
         <v>90.98</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>89.14</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>86.94</v>
-      </c>
-      <c r="N84" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>89.05</v>
+      </c>
+      <c r="N84" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>91.56</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.16</v>
+        <v>91.06</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="R84" s="24" t="n">
-        <v>2.37</v>
+        <v>91.15000000000001</v>
+      </c>
+      <c r="R84" s="25" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.11</v>
+        <v>17.32</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.71</v>
+        <v>16.84</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.37</v>
+        <v>16.43</v>
       </c>
       <c r="F85" s="15" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="I85" s="17" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="J85" s="17" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="K85" s="18" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="L85" s="19" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="M85" s="19" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="N85" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O85" s="21" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="P85" s="21" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Q85" s="22" t="n">
         <v>16.35</v>
       </c>
-      <c r="G85" s="15" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="H85" s="16" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="I85" s="17" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="J85" s="17" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="K85" s="18" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="L85" s="19" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="M85" s="19" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="N85" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O85" s="21" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="P85" s="21" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="Q85" s="22" t="n">
-        <v>16.1</v>
-      </c>
       <c r="R85" s="23" t="n">
-        <v>-2.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>126.84</v>
+        <v>124.38</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>124.84</v>
+        <v>123.28</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>123.16</v>
+        <v>122.36</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>123.2</v>
+        <v>122.23</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>124.4</v>
+        <v>122.97</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>122.4</v>
+        <v>121.87</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>121.2</v>
+        <v>121.13</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>120.4</v>
+        <v>120.77</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>122.04</v>
+        <v>121.74</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>120.36</v>
+        <v>120.82</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>118.36</v>
-      </c>
-      <c r="N86" s="20" t="inlineStr">
+        <v>119.72</v>
+      </c>
+      <c r="N86" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>122.3</v>
+        <v>121.85</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>122.2</v>
+        <v>121.83</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="R86" s="24" t="n">
-        <v>0.33</v>
+        <v>121.5</v>
+      </c>
+      <c r="R86" s="25" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>62.29</v>
+        <v>58.62</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>59.64</v>
+        <v>57.37</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>57.42</v>
+        <v>56.32</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>57.25</v>
+        <v>56.48</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>58.95</v>
+        <v>57.17</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>56.3</v>
+        <v>55.92</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>54.6</v>
+        <v>55.23</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>53.65</v>
+        <v>54.67</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>55.93</v>
+        <v>55.62</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>53.71</v>
+        <v>54.58</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>51.06</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
+        <v>53.33</v>
+      </c>
+      <c r="N87" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>56.22</v>
+        <v>55.82</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>56.14</v>
+        <v>55.72</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>55.55</v>
+        <v>55.8</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>-4.22</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="88">
@@ -6028,54 +6028,54 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>10.25</v>
+        <v>9.74</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.98</v>
+        <v>9.65</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>9.75</v>
+        <v>9.57</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>9.73</v>
+        <v>9.6</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>9.9</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.630000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I88" s="17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="J88" s="17" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J88" s="17" t="n">
-        <v>9.359999999999999</v>
-      </c>
       <c r="K88" s="18" t="n">
-        <v>9.6</v>
+        <v>9.52</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.369999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="N88" s="20" t="inlineStr">
+        <v>9.35</v>
+      </c>
+      <c r="N88" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.630000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.619999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>-4.88</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>17.63</v>
+        <v>16.65</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.86</v>
+        <v>16.26</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>16.21</v>
+        <v>15.93</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>16.12</v>
+        <v>16.04</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>16.64</v>
+        <v>16.23</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>15.87</v>
+        <v>15.84</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.35</v>
+        <v>15.65</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>15.1</v>
+        <v>15.45</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>15.78</v>
+        <v>15.72</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15.13</v>
+        <v>15.39</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="N89" s="20" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="N89" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>15.85</v>
+        <v>15.79</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>15.84</v>
+        <v>15.75</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>15.61</v>
+        <v>15.86</v>
       </c>
       <c r="R89" s="23" t="n">
-        <v>-2.01</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>18</v>
+        <v>17.76</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.63</v>
+        <v>17.46</v>
       </c>
       <c r="E90" s="14" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F90" s="15" t="n">
         <v>17.32</v>
       </c>
-      <c r="F90" s="15" t="n">
-        <v>17.28</v>
-      </c>
       <c r="G90" s="15" t="n">
-        <v>17.53</v>
+        <v>17.45</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.16</v>
+        <v>17.15</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>16.91</v>
+        <v>17.02</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>16.79</v>
+        <v>16.85</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.11</v>
+        <v>17.04</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>16.8</v>
+        <v>16.78</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>16.43</v>
+        <v>16.48</v>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>17.15</v>
+        <v>17.1</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.14</v>
+        <v>17.06</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.04</v>
+        <v>17.2</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>-0.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.14</v>
+        <v>31.22</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.56</v>
+        <v>30.48</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>30.07</v>
+        <v>29.86</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>30.14</v>
+        <v>30.04</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.46</v>
+        <v>30.4</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.88</v>
+        <v>29.66</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.56</v>
+        <v>29.3</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>29.3</v>
+        <v>28.92</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.75</v>
+        <v>29.44</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>29.26</v>
+        <v>28.82</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="N91" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>28.08</v>
+      </c>
+      <c r="N91" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.84</v>
+        <v>29.58</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.79</v>
+        <v>29.5</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="R91" s="23" t="n">
-        <v>-0.13</v>
+        <v>29.68</v>
+      </c>
+      <c r="R91" s="25" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>19.84</v>
+        <v>20.2</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>19.62</v>
+        <v>19.86</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.43</v>
+        <v>19.58</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.45</v>
+        <v>19.71</v>
       </c>
       <c r="G92" s="15" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="J92" s="17" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="K92" s="18" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O92" s="21" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="P92" s="21" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="Q92" s="22" t="n">
         <v>19.57</v>
       </c>
-      <c r="H92" s="16" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="I92" s="17" t="n">
-        <v>19.23</v>
-      </c>
-      <c r="J92" s="17" t="n">
-        <v>19.13</v>
-      </c>
-      <c r="K92" s="18" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="L92" s="19" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="M92" s="19" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O92" s="21" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="P92" s="21" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="Q92" s="22" t="n">
-        <v>19.32</v>
-      </c>
       <c r="R92" s="23" t="n">
-        <v>-0.05</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.5</v>
+        <v>28.18</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.04</v>
+        <v>27.08</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.66</v>
+        <v>26.16</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>25.66</v>
+        <v>26.47</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>25.94</v>
+        <v>26.99</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.48</v>
+        <v>25.89</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.2</v>
+        <v>25.37</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.02</v>
+        <v>24.79</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.4</v>
+        <v>25.54</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.02</v>
+        <v>24.62</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>24.56</v>
+        <v>23.52</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.46</v>
+        <v>25.76</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.44</v>
+        <v>25.63</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="R93" s="24" t="n">
-        <v>0.08</v>
+        <v>25.96</v>
+      </c>
+      <c r="R93" s="23" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>177.72</v>
+        <v>179.12</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>174.62</v>
+        <v>176.02</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>172.02</v>
+        <v>173.42</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>173.4</v>
+        <v>174.4</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>174.6</v>
+        <v>175.8</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>171.5</v>
+        <v>172.7</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>170.3</v>
+        <v>171.3</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>168.4</v>
+        <v>169.6</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>170.28</v>
+        <v>171.68</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>167.68</v>
+        <v>169.08</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>164.58</v>
-      </c>
-      <c r="N94" s="25" t="inlineStr">
+        <v>165.98</v>
+      </c>
+      <c r="N94" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>171.01</v>
+        <v>172.31</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>170.52</v>
+        <v>171.92</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="R94" s="24" t="n">
-        <v>1.12</v>
+        <v>173</v>
+      </c>
+      <c r="R94" s="23" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G95" s="15" t="n">
         <v>13.34</v>
       </c>
-      <c r="D95" s="13" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="E95" s="14" t="n">
+      <c r="H95" s="16" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="J95" s="17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K95" s="18" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M95" s="19" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O95" s="21" t="n">
         <v>12.9</v>
       </c>
-      <c r="F95" s="15" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="G95" s="15" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="H95" s="16" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="I95" s="17" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="J95" s="17" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="K95" s="18" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="L95" s="19" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="M95" s="19" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O95" s="21" t="n">
-        <v>12.79</v>
-      </c>
       <c r="P95" s="21" t="n">
-        <v>12.78</v>
+        <v>12.84</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="R95" s="24" t="n">
-        <v>0</v>
+        <v>13.07</v>
+      </c>
+      <c r="R95" s="23" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>20.05</v>
+        <v>19.61</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.46</v>
+        <v>19.2</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>18.97</v>
+        <v>18.86</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>18.93</v>
+        <v>19.09</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.31</v>
+        <v>19.22</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>18.72</v>
+        <v>18.81</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>18.34</v>
+        <v>18.68</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.13</v>
+        <v>18.4</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>18.64</v>
+        <v>18.63</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.15</v>
+        <v>18.29</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>17.56</v>
+        <v>17.88</v>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>18.7</v>
+        <v>18.74</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>18.69</v>
+        <v>18.66</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>18.55</v>
+        <v>18.95</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>-2.37</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.57</v>
+        <v>16.13</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>16.22</v>
+        <v>15.98</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>15.92</v>
+        <v>15.86</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>15.92</v>
+        <v>15.93</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>16.13</v>
+        <v>15.99</v>
       </c>
       <c r="H97" s="16" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="I97" s="17" t="n">
         <v>15.78</v>
       </c>
-      <c r="I97" s="17" t="n">
-        <v>15.57</v>
-      </c>
       <c r="J97" s="17" t="n">
-        <v>15.43</v>
+        <v>15.69</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>15.73</v>
+        <v>15.77</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>15.43</v>
+        <v>15.65</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.08</v>
+        <v>15.5</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>15.77</v>
+        <v>15.81</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.75</v>
+        <v>15.78</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>15.7</v>
+        <v>15.88</v>
       </c>
       <c r="R97" s="23" t="n">
-        <v>-5.76</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.74</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>9.210000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.07</v>
+        <v>9.09</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>8.970000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.16</v>
+        <v>9.08</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>8.960000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.18</v>
+        <v>9.1</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="R98" s="23" t="n">
-        <v>-0.33</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>25.73</v>
+        <v>25.49</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25.34</v>
+        <v>25.17</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>25.01</v>
+        <v>24.9</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>25.04</v>
+        <v>25</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.27</v>
+        <v>25.15</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>24.88</v>
+        <v>24.83</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.65</v>
+        <v>24.68</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.49</v>
+        <v>24.51</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.8</v>
+        <v>24.72</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>24.47</v>
+        <v>24.45</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>24.08</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
+        <v>24.13</v>
+      </c>
+      <c r="N99" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>24.85</v>
+        <v>24.79</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>24.83</v>
+        <v>24.75</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="R99" s="23" t="n">
-        <v>-1.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.44</v>
+        <v>16.35</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>16.26</v>
+        <v>16.22</v>
       </c>
       <c r="E100" s="14" t="n">
         <v>16.11</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>16.14</v>
+        <v>16.13</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="H100" s="16" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J100" s="17" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="K100" s="18" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="L100" s="19" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="M100" s="19" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O100" s="21" t="n">
         <v>16.06</v>
       </c>
-      <c r="I100" s="17" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="J100" s="17" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="K100" s="18" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="L100" s="19" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="M100" s="19" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="N100" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O100" s="21" t="n">
-        <v>16.04</v>
-      </c>
       <c r="P100" s="21" t="n">
-        <v>16.02</v>
+        <v>16.05</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.05</v>
+        <v>16.06</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>-0.93</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>31.08</v>
+        <v>30.54</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.34</v>
+        <v>30.02</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.72</v>
+        <v>29.59</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.66</v>
+        <v>29.71</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.14</v>
+        <v>29.97</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.4</v>
+        <v>29.45</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>28.92</v>
+        <v>29.19</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>28.66</v>
+        <v>28.93</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>28.68</v>
+        <v>28.86</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>27.94</v>
+        <v>28.34</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.38</v>
+        <v>29.39</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>29.36</v>
+        <v>29.33</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>29.18</v>
+        <v>29.46</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>-1.15</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>14.96</v>
+        <v>15.72</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>14.63</v>
+        <v>15.13</v>
       </c>
       <c r="E102" s="14" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="F102" s="15" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="G102" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" s="16" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="J102" s="17" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="K102" s="18" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="L102" s="19" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="M102" s="19" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O102" s="21" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="P102" s="21" t="n">
         <v>14.36</v>
       </c>
-      <c r="F102" s="15" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="G102" s="15" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="H102" s="16" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="I102" s="17" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="J102" s="17" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K102" s="18" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="L102" s="19" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M102" s="19" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O102" s="21" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="P102" s="21" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Q102" s="22" t="n">
-        <v>14.15</v>
+        <v>14.29</v>
       </c>
       <c r="R102" s="23" t="n">
-        <v>-1.05</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>68.44</v>
+        <v>69.48</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>67.48999999999999</v>
+        <v>68.13</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>66.69</v>
+        <v>67</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>66.58</v>
+        <v>67.75</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>67.22</v>
+        <v>68.2</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>66.27</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>65.63</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>65.31999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>66.16</v>
+        <v>66.25</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>65.36</v>
+        <v>65.12</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>64.41</v>
+        <v>63.77</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>66.25</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>66.23</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>65.95</v>
+        <v>67.3</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>-1.57</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.38</v>
+        <v>14.43</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.15</v>
+        <v>14.19</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>13.96</v>
+        <v>13.99</v>
       </c>
       <c r="F104" s="15" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="H104" s="16" t="n">
         <v>13.95</v>
       </c>
-      <c r="G104" s="15" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="H104" s="16" t="n">
-        <v>13.86</v>
-      </c>
       <c r="I104" s="17" t="n">
-        <v>13.72</v>
+        <v>13.85</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>13.63</v>
+        <v>13.71</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>13.64</v>
+        <v>13.65</v>
       </c>
       <c r="M104" s="19" t="n">
         <v>13.41</v>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>13.86</v>
+        <v>13.91</v>
       </c>
       <c r="P104" s="21" t="n">
-        <v>13.85</v>
+        <v>13.87</v>
       </c>
       <c r="Q104" s="22" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="R104" s="23" t="n">
-        <v>-0.86</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>17.2</v>
+        <v>16.36</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>16.55</v>
+        <v>15.98</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>16.01</v>
+        <v>15.67</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>15.93</v>
+        <v>15.82</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>16.37</v>
+        <v>15.98</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>15.72</v>
+        <v>15.6</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>15.28</v>
+        <v>15.44</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.07</v>
+        <v>15.22</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>15.64</v>
+        <v>15.45</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="N105" s="20" t="inlineStr">
+        <v>14.76</v>
+      </c>
+      <c r="N105" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>15.71</v>
+        <v>15.54</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>15.69</v>
+        <v>15.48</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="R105" s="23" t="n">
-        <v>-3.19</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="F106" s="15" t="n">
         <v>2.44</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="I106" s="17" t="n">
         <v>2.4</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="K106" s="18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L106" s="19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M106" s="19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O106" s="21" t="n">
         <v>2.41</v>
       </c>
-      <c r="L106" s="19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M106" s="19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="N106" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O106" s="21" t="n">
-        <v>2.42</v>
-      </c>
       <c r="P106" s="21" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q106" s="22" t="n">
         <v>2.42</v>
       </c>
-      <c r="R106" s="24" t="n">
-        <v>0.41</v>
+      <c r="R106" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>37.72</v>
+        <v>37.64</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>37.08</v>
+        <v>37.02</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>36.54</v>
+        <v>36.5</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>36.55</v>
+        <v>36.82</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>36.93</v>
+        <v>37.04</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.29</v>
+        <v>36.42</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>35.91</v>
+        <v>36.2</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>35.65</v>
+        <v>35.8</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>36.18</v>
+        <v>36.16</v>
       </c>
       <c r="L107" s="19" t="n">
         <v>35.64</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>35</v>
+        <v>35.02</v>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>36.26</v>
+        <v>36.31</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>36.23</v>
+        <v>36.2</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="R107" s="24" t="n">
-        <v>0.39</v>
+        <v>36.6</v>
+      </c>
+      <c r="R107" s="23" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>7.88</v>
+        <v>7.91</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.72</v>
+        <v>7.75</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>7.77</v>
+        <v>7.8</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.62</v>
+        <v>7.64</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.57</v>
+        <v>7.58</v>
       </c>
       <c r="K108" s="18" t="n">
         <v>7.64</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>7.56</v>
+        <v>7.55</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="N108" s="25" t="inlineStr">
+        <v>7.44</v>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>7.66</v>
+        <v>7.67</v>
       </c>
       <c r="P108" s="21" t="n">
         <v>7.65</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="R108" s="24" t="n">
-        <v>0.92</v>
+        <v>7.71</v>
+      </c>
+      <c r="R108" s="23" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.31</v>
+        <v>44.28</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>44.03</v>
+        <v>44.02</v>
       </c>
       <c r="E109" s="14" t="n">
         <v>43.8</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.78</v>
+        <v>43.81</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.96</v>
+        <v>43.97</v>
       </c>
       <c r="H109" s="16" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="J109" s="17" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="K109" s="18" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="L109" s="19" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="M109" s="19" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="N109" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O109" s="21" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="P109" s="21" t="n">
         <v>43.68</v>
       </c>
-      <c r="I109" s="17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J109" s="17" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="K109" s="18" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="L109" s="19" t="n">
-        <v>43.41</v>
-      </c>
-      <c r="M109" s="19" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="N109" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O109" s="21" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="P109" s="21" t="n">
+      <c r="Q109" s="22" t="n">
         <v>43.66</v>
       </c>
-      <c r="Q109" s="22" t="n">
-        <v>43.6</v>
-      </c>
       <c r="R109" s="23" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>67.27</v>
+        <v>66.14</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>66.02</v>
+        <v>65.19</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.97</v>
+        <v>64.39</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.93000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>65.72</v>
+        <v>64.92</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.47</v>
+        <v>63.97</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.68</v>
+        <v>63.33</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>63.22</v>
+        <v>63.02</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>64.28</v>
+        <v>63.86</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>63.23</v>
+        <v>63.06</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>61.98</v>
-      </c>
-      <c r="N110" s="20" t="inlineStr">
+        <v>62.11</v>
+      </c>
+      <c r="N110" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>64.42</v>
+        <v>63.95</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>64.37</v>
+        <v>63.93</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="R110" s="24" t="n">
-        <v>0.79</v>
+        <v>63.65</v>
+      </c>
+      <c r="R110" s="25" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.16</v>
+        <v>10.19</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.1</v>
+        <v>10.12</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>10.05</v>
+        <v>10.06</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>10.05</v>
+        <v>10.08</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="H111" s="16" t="n">
-        <v>10.02</v>
+        <v>10.04</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K111" s="18" t="n">
-        <v>10.01</v>
+        <v>10.03</v>
       </c>
       <c r="L111" s="19" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M111" s="19" t="n">
         <v>9.9</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.02</v>
+        <v>10.04</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.01</v>
+        <v>10.04</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>318.02</v>
+        <v>302.38</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>306.02</v>
+        <v>296.58</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>295.96</v>
+        <v>291.72</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>295.53</v>
+        <v>292.53</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>303.07</v>
+        <v>295.67</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>291.07</v>
+        <v>289.87</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>283.53</v>
+        <v>286.73</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>279.07</v>
+        <v>284.07</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>289.24</v>
+        <v>288.48</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>279.18</v>
+        <v>283.62</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>267.18</v>
-      </c>
-      <c r="N112" s="20" t="inlineStr">
+        <v>277.82</v>
+      </c>
+      <c r="N112" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>290.62</v>
+        <v>289.4</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>290.18</v>
+        <v>288.93</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>288</v>
+        <v>289.4</v>
       </c>
       <c r="R112" s="23" t="n">
-        <v>-2.57</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>226.23</v>
+        <v>228</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>223.43</v>
+        <v>224.6</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>221.08</v>
+        <v>221.75</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>222.17</v>
+        <v>223.63</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>223.33</v>
+        <v>224.77</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>220.53</v>
+        <v>221.37</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>219.37</v>
+        <v>220.23</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>217.73</v>
+        <v>217.97</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>219.52</v>
+        <v>219.85</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>217.17</v>
+        <v>217</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>214.37</v>
+        <v>213.6</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>220.13</v>
+        <v>220.74</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>219.73</v>
+        <v>220.11</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>221</v>
+        <v>222.5</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>-0.27</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>624.99</v>
+        <v>614.25</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>614.49</v>
+        <v>605.75</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>605.6900000000001</v>
+        <v>598.63</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>605.5</v>
+        <v>599.67</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>612</v>
+        <v>604.33</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>601.5</v>
+        <v>595.83</v>
       </c>
       <c r="I114" s="17" t="n">
+        <v>591.17</v>
+      </c>
+      <c r="J114" s="17" t="n">
+        <v>587.33</v>
+      </c>
+      <c r="K114" s="18" t="n">
+        <v>593.87</v>
+      </c>
+      <c r="L114" s="19" t="n">
+        <v>586.75</v>
+      </c>
+      <c r="M114" s="19" t="n">
+        <v>578.25</v>
+      </c>
+      <c r="N114" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O114" s="21" t="n">
+        <v>595.1799999999999</v>
+      </c>
+      <c r="P114" s="21" t="n">
+        <v>594.53</v>
+      </c>
+      <c r="Q114" s="22" t="n">
         <v>595</v>
       </c>
-      <c r="J114" s="17" t="n">
-        <v>591</v>
-      </c>
-      <c r="K114" s="18" t="n">
-        <v>599.8099999999999</v>
-      </c>
-      <c r="L114" s="19" t="n">
-        <v>591.01</v>
-      </c>
-      <c r="M114" s="19" t="n">
-        <v>580.51</v>
-      </c>
-      <c r="N114" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O114" s="21" t="n">
-        <v>601.0599999999999</v>
-      </c>
-      <c r="P114" s="21" t="n">
-        <v>600.63</v>
-      </c>
-      <c r="Q114" s="22" t="n">
-        <v>599</v>
-      </c>
-      <c r="R114" s="23" t="n">
-        <v>-0.66</v>
+      <c r="R114" s="25" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.59</v>
+        <v>5.92</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.21</v>
+        <v>5.8</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>5.87</v>
+        <v>5.71</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>5.74</v>
+        <v>5.66</v>
       </c>
       <c r="I115" s="17" t="n">
-        <v>5.49</v>
+        <v>5.59</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>5.36</v>
+        <v>5.54</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>5.37</v>
+        <v>5.54</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="N115" s="20" t="inlineStr">
+        <v>5.42</v>
+      </c>
+      <c r="N115" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>5.72</v>
+        <v>5.65</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>5.71</v>
+        <v>5.65</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="R115" s="23" t="n">
-        <v>-5.85</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>95.39</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>92.73999999999999</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>90.52</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>90.25</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>92</v>
+        <v>92.88</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>89.34999999999999</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>87.59999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>86.7</v>
+        <v>87.98</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>89.03</v>
+        <v>89.34</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>86.81</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>84.16</v>
+        <v>84.84</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>89.29000000000001</v>
+        <v>89.98</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>89.23999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>88.5</v>
+        <v>91.25</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>-1.67</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>10.03</v>
+        <v>10.16</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>9.710000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.44</v>
+        <v>9.18</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.41</v>
+        <v>9.43</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>9.09</v>
+        <v>8.9</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>8.98</v>
+        <v>8.57</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>9.26</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>8.99</v>
+        <v>8.44</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
+        <v>7.91</v>
+      </c>
+      <c r="N117" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>9.289999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>9.289999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="R117" s="23" t="n">
-        <v>-1.08</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>16.81</v>
+        <v>16.64</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.25</v>
+        <v>16.3</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.44</v>
+        <v>16.39</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>16.13</v>
+        <v>16.15</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>15.94</v>
+        <v>16.06</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.82</v>
+        <v>15.91</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>16.07</v>
+        <v>16.06</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.81</v>
+        <v>15.86</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.11</v>
+        <v>16.12</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.09</v>
+        <v>16.08</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.07</v>
+        <v>16.2</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>-0.74</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.27</v>
+        <v>11.22</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.04</v>
+        <v>11.01</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>10.85</v>
+        <v>10.83</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.87</v>
+        <v>10.94</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11</v>
+        <v>11.02</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>10.77</v>
+        <v>10.81</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.54</v>
+        <v>10.6</v>
       </c>
       <c r="K119" s="18" t="n">
         <v>10.72</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.53</v>
+        <v>10.54</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="R119" s="24" t="n">
-        <v>0.37</v>
+        <v>10.87</v>
+      </c>
+      <c r="R119" s="23" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.31</v>
+        <v>12.43</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.09</v>
+        <v>12.17</v>
       </c>
       <c r="E120" s="14" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="H120" s="16" t="n">
         <v>11.9</v>
       </c>
-      <c r="F120" s="15" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="G120" s="15" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="H120" s="16" t="n">
-        <v>11.83</v>
-      </c>
       <c r="I120" s="17" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>11.61</v>
+        <v>11.64</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>11.78</v>
+        <v>11.81</v>
       </c>
       <c r="L120" s="19" t="n">
         <v>11.59</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>11.37</v>
+        <v>11.33</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.81</v>
+        <v>11.87</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R120" s="24" t="n">
-        <v>0.68</v>
+        <v>11.95</v>
+      </c>
+      <c r="R120" s="23" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.55</v>
+        <v>7.4</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.33</v>
+        <v>7.24</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>7.14</v>
+        <v>7.1</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.12</v>
+        <v>7.16</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.26</v>
+        <v>7.23</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.04</v>
+        <v>7.07</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.82</v>
+        <v>6.91</v>
       </c>
       <c r="K121" s="18" t="n">
         <v>7.02</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>6.83</v>
+        <v>6.88</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>6.61</v>
+        <v>6.72</v>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>7.04</v>
+        <v>7.05</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>6.97</v>
+        <v>7.09</v>
       </c>
       <c r="R121" s="23" t="n">
-        <v>-0.43</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>7.39</v>
+        <v>6.95</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>7.04</v>
+        <v>6.74</v>
       </c>
       <c r="E122" s="14" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G122" s="15" t="n">
         <v>6.74</v>
       </c>
-      <c r="F122" s="15" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="G122" s="15" t="n">
-        <v>6.94</v>
-      </c>
       <c r="H122" s="16" t="n">
-        <v>6.59</v>
+        <v>6.53</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.37</v>
+        <v>6.45</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>6.24</v>
+        <v>6.32</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N122" s="20" t="inlineStr">
+        <v>6.06</v>
+      </c>
+      <c r="N122" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P122" s="21" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="Q122" s="22" t="n">
         <v>6.58</v>
       </c>
-      <c r="P122" s="21" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="Q122" s="22" t="n">
-        <v>6.49</v>
-      </c>
       <c r="R122" s="23" t="n">
-        <v>-3.13</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>29.13</v>
+        <v>29.3</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>28.79</v>
+        <v>28.84</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.51</v>
+        <v>28.46</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.59</v>
+        <v>28.43</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>28.75</v>
+        <v>28.73</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.41</v>
+        <v>28.27</v>
       </c>
       <c r="I123" s="17" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="J123" s="17" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="K123" s="18" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L123" s="19" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="M123" s="19" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O123" s="21" t="n">
         <v>28.25</v>
       </c>
-      <c r="J123" s="17" t="n">
-        <v>28.07</v>
-      </c>
-      <c r="K123" s="18" t="n">
-        <v>28.31</v>
-      </c>
-      <c r="L123" s="19" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="M123" s="19" t="n">
-        <v>27.69</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O123" s="21" t="n">
-        <v>28.38</v>
-      </c>
       <c r="P123" s="21" t="n">
-        <v>28.34</v>
+        <v>28.24</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>28.42</v>
-      </c>
-      <c r="R123" s="24" t="n">
-        <v>0.64</v>
+        <v>28.14</v>
+      </c>
+      <c r="R123" s="25" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>169.96</v>
+        <v>166.33</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>163.56</v>
+        <v>161.43</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>158.19</v>
+        <v>157.32</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>158.67</v>
+        <v>160.03</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>162.33</v>
+        <v>161.67</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>155.93</v>
+        <v>156.77</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>152.27</v>
+        <v>155.13</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>149.53</v>
+        <v>151.87</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>154.61</v>
+        <v>154.58</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>149.24</v>
+        <v>150.47</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>142.84</v>
+        <v>145.57</v>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>155.52</v>
+        <v>155.86</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>155.11</v>
+        <v>154.96</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>155</v>
+        <v>158.4</v>
       </c>
       <c r="R124" s="23" t="n">
-        <v>-1.08</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>56.35</v>
+        <v>53.87</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>54.9</v>
+        <v>53.27</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>53.68</v>
+        <v>52.77</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>53.52</v>
+        <v>52.9</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>54.48</v>
+        <v>53.2</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>53.03</v>
+        <v>52.6</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>52.07</v>
+        <v>52.3</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>51.58</v>
+        <v>52</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>52.87</v>
+        <v>52.43</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>51.65</v>
+        <v>51.93</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="N125" s="20" t="inlineStr">
+        <v>51.33</v>
+      </c>
+      <c r="N125" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>53.01</v>
+        <v>52.54</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>52.98</v>
+        <v>52.48</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>52.55</v>
+        <v>52.6</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>-2.69</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.14</v>
+        <v>15.54</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>13.59</v>
+        <v>14.53</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.13</v>
+        <v>13.69</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.31</v>
+        <v>14.09</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>13.55</v>
+        <v>14.5</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13</v>
+        <v>13.49</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>12.76</v>
+        <v>13.08</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.45</v>
+        <v>12.48</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>12.82</v>
+        <v>13.12</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.36</v>
+        <v>12.28</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>11.81</v>
-      </c>
-      <c r="N126" s="25" t="inlineStr">
+        <v>11.27</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>12.93</v>
+        <v>13.35</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>12.86</v>
+        <v>13.2</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="R126" s="24" t="n">
-        <v>2.03</v>
+        <v>13.67</v>
+      </c>
+      <c r="R126" s="23" t="n">
+        <v>4.67</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.52</v>
+        <v>16.05</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15</v>
+        <v>15.34</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.57</v>
+        <v>14.74</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.58</v>
+        <v>14.8</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>14.89</v>
+        <v>15.21</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.37</v>
+        <v>14.5</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.06</v>
+        <v>14.09</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>13.85</v>
+        <v>13.79</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.27</v>
+        <v>14.35</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>13.84</v>
+        <v>13.75</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13.32</v>
+        <v>13.04</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.34</v>
+        <v>14.45</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.31</v>
+        <v>14.4</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.27</v>
+        <v>14.4</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>-0.9</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="F128" s="15" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="H128" s="16" t="n">
         <v>6.33</v>
       </c>
-      <c r="G128" s="15" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="H128" s="16" t="n">
-        <v>6.21</v>
-      </c>
       <c r="I128" s="17" t="n">
-        <v>6.08</v>
+        <v>6.22</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>5.96</v>
+        <v>6.1</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>5.95</v>
+        <v>6.06</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.7</v>
+        <v>5.83</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.19</v>
+        <v>6.3</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.17</v>
+        <v>6.27</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.19</v>
+        <v>6.35</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>-0.48</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>10.26</v>
+        <v>10.08</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.76</v>
+        <v>9.68</v>
       </c>
       <c r="E129" s="14" t="n">
         <v>9.34</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.43</v>
+        <v>9.33</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.69</v>
+        <v>9.58</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="I129" s="17" t="n">
         <v>8.93</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>8.69</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="N129" s="25" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>8.380000000000001</v>
+      </c>
+      <c r="N129" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>9.140000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="R129" s="24" t="n">
-        <v>1.89</v>
+        <v>9.08</v>
+      </c>
+      <c r="R129" s="25" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>158.68</v>
+        <v>148.65</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>152.88</v>
+        <v>146.15</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>148.02</v>
+        <v>144.05</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>147.9</v>
+        <v>143.97</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>151.5</v>
+        <v>145.53</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>145.7</v>
+        <v>143.03</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>142.1</v>
+        <v>141.47</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>139.9</v>
+        <v>140.53</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>144.78</v>
+        <v>142.65</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>139.92</v>
+        <v>140.56</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>134.12</v>
-      </c>
-      <c r="N130" s="20" t="inlineStr">
+        <v>138.06</v>
+      </c>
+      <c r="N130" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>145.46</v>
+        <v>142.94</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>145.23</v>
+        <v>142.85</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="R130" s="23" t="n">
-        <v>-1.84</v>
+        <v>142.4</v>
+      </c>
+      <c r="R130" s="25" t="n">
+        <v>-1.32</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-22</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.39</v>
+        <v>20.42</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.25</v>
+        <v>20.28</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.13</v>
+        <v>20.16</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.23</v>
+        <v>20.24</v>
       </c>
       <c r="H3" s="16" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="K3" s="18" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L3" s="19" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="M3" s="19" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N3" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="n">
         <v>20.09</v>
       </c>
-      <c r="I3" s="17" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="J3" s="17" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="K3" s="18" t="n">
+      <c r="P3" s="21" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="Q3" s="22" t="n">
         <v>20.05</v>
       </c>
-      <c r="L3" s="19" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O3" s="21" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="P3" s="21" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="Q3" s="22" t="n">
-        <v>20.1</v>
-      </c>
       <c r="R3" s="23" t="n">
-        <v>0.45</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>11.92</v>
+        <v>12.06</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.82</v>
+        <v>11.91</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.74</v>
+        <v>11.79</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.82</v>
+        <v>11.88</v>
       </c>
       <c r="H4" s="16" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
         <v>11.72</v>
       </c>
-      <c r="I4" s="17" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>11.68</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.7</v>
-      </c>
       <c r="P4" s="21" t="n">
-        <v>11.69</v>
+        <v>11.71</v>
       </c>
       <c r="Q4" s="22" t="n">
-        <v>11.74</v>
+        <v>11.71</v>
       </c>
       <c r="R4" s="23" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>14.98</v>
+        <v>15.1</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.81</v>
+        <v>14.85</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.66</v>
+        <v>14.64</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.76</v>
+        <v>14.67</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>14.81</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.64</v>
+        <v>14.56</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.59</v>
+        <v>14.42</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>14.47</v>
+        <v>14.31</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>14.42</v>
+        <v>14.3</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>14.25</v>
+        <v>14.05</v>
       </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.61</v>
+        <v>14.54</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.58</v>
+        <v>14.52</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.7</v>
+        <v>14.53</v>
       </c>
       <c r="R5" s="23" t="n">
-        <v>0.48</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.71</v>
+        <v>21.87</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.4</v>
+        <v>21.46</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.14</v>
+        <v>21.12</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.29</v>
+        <v>21.09</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.41</v>
+        <v>21.36</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>21.1</v>
+        <v>20.95</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>20.98</v>
+        <v>20.68</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>20.97</v>
+        <v>20.89</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.71</v>
+        <v>20.55</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>20.4</v>
+        <v>20.14</v>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>21.04</v>
+        <v>20.93</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>20.99</v>
+        <v>20.92</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>21.18</v>
+        <v>20.83</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>0.62</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.25</v>
+        <v>35.06</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.85</v>
+        <v>34.34</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.51</v>
+        <v>33.74</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.73</v>
+        <v>33.79</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>33.87</v>
+        <v>34.21</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.47</v>
+        <v>33.49</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>33.33</v>
+        <v>33.07</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>33.07</v>
+        <v>32.77</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.29</v>
+        <v>33.34</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.95</v>
+        <v>32.74</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.55</v>
+        <v>32.02</v>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="P7" s="21" t="n">
         <v>33.39</v>
       </c>
-      <c r="P7" s="21" t="n">
-        <v>33.32</v>
-      </c>
       <c r="Q7" s="22" t="n">
-        <v>33.6</v>
+        <v>33.38</v>
       </c>
       <c r="R7" s="23" t="n">
-        <v>0.96</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.06</v>
+        <v>23.78</v>
       </c>
       <c r="D8" s="13" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="H8" s="16" t="n">
         <v>22.92</v>
       </c>
-      <c r="E8" s="14" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="H8" s="16" t="n">
+      <c r="I8" s="17" t="n">
         <v>22.75</v>
       </c>
-      <c r="I8" s="17" t="n">
-        <v>22.68</v>
-      </c>
       <c r="J8" s="17" t="n">
-        <v>22.61</v>
+        <v>22.5</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>22.72</v>
+        <v>22.77</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>22.6</v>
+        <v>22.42</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>22.46</v>
+        <v>22</v>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>22.74</v>
+        <v>22.86</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>22.73</v>
+        <v>22.81</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.74</v>
+        <v>22.99</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>-0.35</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>124.06</v>
+        <v>124.38</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>121.86</v>
+        <v>121.98</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>120.02</v>
+        <v>119.97</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>120.57</v>
+        <v>119.7</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>121.63</v>
+        <v>121.3</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>119.43</v>
+        <v>118.9</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>118.37</v>
+        <v>117.3</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>117.23</v>
+        <v>116.5</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>118.78</v>
+        <v>118.63</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>116.94</v>
+        <v>116.62</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>114.74</v>
-      </c>
-      <c r="N9" s="24" t="inlineStr">
+        <v>114.22</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>119.19</v>
+        <v>118.86</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>118.96</v>
+        <v>118.82</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>119.5</v>
+        <v>118.1</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>0.08</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>66.18000000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>65.48</v>
+        <v>65.33</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>64.88</v>
+        <v>64.05</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>65.31999999999999</v>
+        <v>64.95</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>64.62</v>
+        <v>63.6</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>64.18000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>63.92</v>
+        <v>62.25</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>64.5</v>
+        <v>63.45</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>63.92</v>
+        <v>62.32</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>63.22</v>
-      </c>
-      <c r="N10" s="24" t="inlineStr">
+        <v>60.97</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>64.59</v>
+        <v>63.58</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>64.56</v>
+        <v>63.55</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="R10" s="25" t="n">
-        <v>-2.42</v>
+        <v>63.15</v>
+      </c>
+      <c r="R10" s="23" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25.1</v>
+        <v>24.86</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.77</v>
+        <v>24.61</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.68</v>
+        <v>24.4</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.79</v>
+        <v>24.55</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.46</v>
+        <v>24.3</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.35</v>
+        <v>24.15</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.13</v>
+        <v>24.05</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.31</v>
+        <v>24.26</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>24.04</v>
+        <v>24.06</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>23.71</v>
+        <v>23.81</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.4</v>
+        <v>24.29</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.34</v>
+        <v>24.28</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.57</v>
+        <v>24.24</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>0.82</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.02</v>
+        <v>24.94</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>24.8</v>
+        <v>24.76</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>24.61</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.73</v>
+        <v>24.61</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.81</v>
+        <v>24.72</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.59</v>
+        <v>24.54</v>
       </c>
       <c r="I12" s="17" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="K12" s="18" t="n">
         <v>24.51</v>
       </c>
-      <c r="J12" s="17" t="n">
-        <v>24.37</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>24.49</v>
-      </c>
       <c r="L12" s="19" t="n">
-        <v>24.3</v>
+        <v>24.36</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>24.08</v>
+        <v>24.18</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.55</v>
+        <v>24.53</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.51</v>
+        <v>24.52</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.66</v>
+        <v>24.5</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>0.65</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>41.18</v>
+        <v>42.47</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>40.76</v>
+        <v>41.55</v>
       </c>
       <c r="E13" s="14" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="H13" s="16" t="n">
         <v>40.41</v>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>40.28</v>
-      </c>
       <c r="I13" s="17" t="n">
-        <v>40.06</v>
+        <v>39.85</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.86</v>
+        <v>39.49</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.17</v>
+        <v>40.26</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.82</v>
+        <v>39.49</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>39.4</v>
+        <v>38.57</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.24</v>
+        <v>40.37</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.21</v>
+        <v>40.33</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40.26</v>
+        <v>40.2</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>0.65</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>9.07</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.77</v>
+        <v>8.69</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>8.51</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>8.529999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H14" s="16" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="K14" s="18" t="n">
         <v>8.4</v>
       </c>
-      <c r="I14" s="17" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>8.35</v>
-      </c>
       <c r="L14" s="19" t="n">
-        <v>8.09</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>7.79</v>
+        <v>8.01</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O14" s="21" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="Q14" s="22" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="P14" s="21" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="Q14" s="22" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="R14" s="23" t="n">
-        <v>0.6</v>
+      <c r="R14" s="25" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>13.93</v>
+        <v>14.61</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>13.7</v>
+        <v>14.12</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.51</v>
+        <v>13.71</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>13.62</v>
+        <v>13.66</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>13.7</v>
+        <v>13.98</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.47</v>
+        <v>13.49</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.39</v>
+        <v>13.17</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.24</v>
+        <v>13</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.38</v>
+        <v>13.44</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.19</v>
+        <v>13.03</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>12.96</v>
+        <v>12.54</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.44</v>
+        <v>13.48</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.4</v>
+        <v>13.48</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.53</v>
+        <v>13.33</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>0.97</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.46</v>
+        <v>4.38</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3.96</v>
+        <v>4.06</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>4.17</v>
       </c>
       <c r="H16" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="17" t="n">
         <v>3.9</v>
       </c>
-      <c r="I16" s="17" t="n">
-        <v>3.78</v>
-      </c>
       <c r="J16" s="17" t="n">
-        <v>3.63</v>
+        <v>3.83</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>3.81</v>
+        <v>3.97</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
+        <v>3.65</v>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>3.87</v>
+        <v>3.99</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="R16" s="23" t="n">
-        <v>5.08</v>
+        <v>3.97</v>
+      </c>
+      <c r="R16" s="25" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.65</v>
+        <v>18.49</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.34</v>
+        <v>17.87</v>
       </c>
       <c r="E17" s="14" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H17" s="16" t="n">
         <v>17.08</v>
       </c>
-      <c r="F17" s="15" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="H17" s="16" t="n">
+      <c r="I17" s="17" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="K17" s="18" t="n">
         <v>17.01</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="L17" s="19" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="Q17" s="22" t="n">
         <v>16.87</v>
       </c>
-      <c r="J17" s="17" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="L17" s="19" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="M17" s="19" t="n">
-        <v>16.34</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="Q17" s="22" t="n">
-        <v>17.04</v>
-      </c>
       <c r="R17" s="23" t="n">
-        <v>1.19</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.94</v>
+        <v>25.16</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.36</v>
+        <v>24.62</v>
       </c>
       <c r="E18" s="14" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="K18" s="18" t="n">
         <v>23.87</v>
       </c>
-      <c r="F18" s="15" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>23.72</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>23.44</v>
-      </c>
-      <c r="J18" s="17" t="n">
-        <v>23.14</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>23.55</v>
-      </c>
       <c r="L18" s="19" t="n">
-        <v>23.06</v>
+        <v>23.42</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
+        <v>22.88</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.66</v>
+        <v>23.98</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.59</v>
+        <v>23.91</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="R18" s="23" t="n">
-        <v>1.45</v>
+        <v>24.1</v>
+      </c>
+      <c r="R18" s="25" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>64.86</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>63.71</v>
+        <v>63.69</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>62.75</v>
+        <v>62.35</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>63.18</v>
+        <v>62.17</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.67</v>
+        <v>63.23</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>62.52</v>
+        <v>61.63</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>62.03</v>
+        <v>60.57</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61.37</v>
+        <v>60.03</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>62.1</v>
+        <v>61.45</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>61.14</v>
+        <v>60.11</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>59.99</v>
+        <v>58.51</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>62.35</v>
+        <v>61.61</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>62.19</v>
+        <v>61.58</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>62.7</v>
+        <v>61.1</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>0.24</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.07</v>
+        <v>11.14</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.9</v>
+        <v>10.96</v>
       </c>
       <c r="E20" s="14" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="H20" s="16" t="n">
         <v>10.75</v>
       </c>
-      <c r="F20" s="15" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>10.73</v>
-      </c>
       <c r="I20" s="17" t="n">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="J20" s="17" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L20" s="19" t="n">
         <v>10.56</v>
       </c>
-      <c r="K20" s="18" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.51</v>
-      </c>
       <c r="M20" s="19" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
+        <v>10.38</v>
+      </c>
+      <c r="N20" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O20" s="21" t="n">
-        <v>10.7</v>
+        <v>10.74</v>
       </c>
       <c r="P20" s="21" t="n">
-        <v>10.67</v>
+        <v>10.72</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>10.79</v>
+        <v>10.74</v>
       </c>
       <c r="R20" s="23" t="n">
-        <v>1.6</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.23</v>
+        <v>17.29</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.02</v>
+        <v>17.11</v>
       </c>
       <c r="E21" s="14" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L21" s="19" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="M21" s="19" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="Q21" s="22" t="n">
         <v>16.84</v>
       </c>
-      <c r="F21" s="15" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>17.01</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>16.59</v>
-      </c>
-      <c r="K21" s="18" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="L21" s="19" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="M21" s="19" t="n">
-        <v>16.34</v>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O21" s="21" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="P21" s="21" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="Q21" s="22" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="R21" s="23" t="n">
-        <v>0.72</v>
+      <c r="R21" s="25" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.83</v>
+        <v>36.97</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.13</v>
+        <v>36.15</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.55</v>
+        <v>35.46</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.89</v>
+        <v>35.5</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>36.15</v>
+        <v>35.98</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.45</v>
+        <v>35.16</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>35.19</v>
+        <v>34.68</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.75</v>
+        <v>34.34</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>35.15</v>
+        <v>35</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.57</v>
+        <v>34.31</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>33.87</v>
+        <v>33.49</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>35.33</v>
+        <v>35.11</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>35.21</v>
+        <v>35.06</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>35.64</v>
+        <v>35.02</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>1.42</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="23">
@@ -1998,53 +1998,53 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.24</v>
+        <v>15.74</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.85</v>
+        <v>15.52</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.52</v>
+        <v>15.33</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.53</v>
+        <v>15.35</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.77</v>
+        <v>15.48</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.38</v>
+        <v>15.26</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.99</v>
+        <v>15.04</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>15.31</v>
+        <v>15.21</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.98</v>
+        <v>15.02</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="N23" s="24" t="inlineStr">
+        <v>14.8</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>15.36</v>
+        <v>15.24</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>15.34</v>
+        <v>15.23</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="R23" s="25" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="R23" s="23" t="n">
         <v>-0.46</v>
       </c>
     </row>
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.6</v>
+        <v>37.56</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.76</v>
+        <v>36.82</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>36.06</v>
+        <v>36.2</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>36.43</v>
+        <v>36.13</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.75</v>
+        <v>36.61</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.91</v>
+        <v>35.87</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>35.59</v>
+        <v>35.39</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>35.07</v>
+        <v>35.13</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>35.58</v>
+        <v>35.78</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.88</v>
+        <v>35.16</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>34.04</v>
+        <v>34.42</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.78</v>
+        <v>35.86</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>35.65</v>
+        <v>35.84</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>36.1</v>
+        <v>35.64</v>
       </c>
       <c r="R24" s="23" t="n">
-        <v>1.98</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>59.1</v>
+        <v>60.41</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.8</v>
+        <v>58.46</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.71</v>
+        <v>56.82</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>57.27</v>
+        <v>57.1</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>57.78</v>
+        <v>58.15</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>56.48</v>
+        <v>56.2</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>55.97</v>
+        <v>55.15</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>55.18</v>
+        <v>54.25</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>55.99</v>
+        <v>55.73</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.9</v>
+        <v>54.09</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="N25" s="24" t="inlineStr">
+        <v>52.14</v>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>56.29</v>
+        <v>56.04</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>56.09</v>
+        <v>55.88</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>56.75</v>
-      </c>
-      <c r="R25" s="25" t="n">
-        <v>-0.18</v>
+        <v>56.05</v>
+      </c>
+      <c r="R25" s="23" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>227.62</v>
+        <v>236.48</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>219.82</v>
+        <v>221.78</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>213.28</v>
+        <v>209.47</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>212.93</v>
+        <v>211.27</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>217.87</v>
+        <v>219.33</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>210.07</v>
+        <v>204.63</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>205.13</v>
+        <v>196.57</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>202.27</v>
+        <v>189.93</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>208.92</v>
+        <v>201.23</v>
       </c>
       <c r="L26" s="19" t="n">
+        <v>188.92</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>174.22</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="n">
+        <v>203.51</v>
+      </c>
+      <c r="P26" s="21" t="n">
         <v>202.38</v>
       </c>
-      <c r="M26" s="19" t="n">
-        <v>194.58</v>
-      </c>
-      <c r="N26" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O26" s="21" t="n">
-        <v>209.8</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <v>209.52</v>
-      </c>
       <c r="Q26" s="22" t="n">
-        <v>208</v>
-      </c>
-      <c r="R26" s="25" t="n">
-        <v>-2.35</v>
+        <v>203.2</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>79.90000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>78.59999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>77.51000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>77.63</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>78.37</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>77.06999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>76.33</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>75.77</v>
+        <v>73.5</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>76.79000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>75.7</v>
+        <v>73.59</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="N27" s="24" t="inlineStr">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>76.98</v>
+        <v>75.27</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>76.89</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="R27" s="25" t="n">
-        <v>-1.22</v>
+        <v>74.7</v>
+      </c>
+      <c r="R27" s="23" t="n">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21.16</v>
+        <v>21.31</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.83</v>
+        <v>20.89</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.56</v>
+        <v>20.54</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.71</v>
+        <v>20.52</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.84</v>
+        <v>20.79</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.51</v>
+        <v>20.37</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.38</v>
+        <v>20.1</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>20.18</v>
+        <v>19.95</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>20.37</v>
+        <v>20.3</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>20.1</v>
+        <v>19.95</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>19.77</v>
+        <v>19.53</v>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O28" s="21" t="n">
-        <v>20.45</v>
+        <v>20.35</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>20.4</v>
+        <v>20.34</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>20.59</v>
+        <v>20.26</v>
       </c>
       <c r="R28" s="23" t="n">
-        <v>1.43</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>83.13</v>
+        <v>79.63</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>80.33</v>
+        <v>77.88</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>77.98</v>
+        <v>76.42</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>77.87</v>
+        <v>76.22</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>79.63</v>
+        <v>77.38</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>76.83</v>
+        <v>75.63</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>75.06999999999999</v>
+        <v>74.47</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>74.03</v>
+        <v>73.88</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>76.42</v>
+        <v>75.44</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>74.06999999999999</v>
+        <v>73.97</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="N29" s="24" t="inlineStr">
+        <v>72.22</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>76.73</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>76.63</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="R29" s="25" t="n">
-        <v>-0.39</v>
+        <v>75.05</v>
+      </c>
+      <c r="R29" s="23" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>28.31</v>
+        <v>29.6</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>27.49</v>
+        <v>28.3</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>26.8</v>
+        <v>27.21</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>26.75</v>
+        <v>27.35</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>27.27</v>
+        <v>28.07</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>26.45</v>
+        <v>26.77</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>25.93</v>
+        <v>26.05</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>25.63</v>
+        <v>25.47</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>26.34</v>
+        <v>26.49</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>25.65</v>
+        <v>25.4</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>24.83</v>
+        <v>24.1</v>
       </c>
       <c r="N30" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>26.43</v>
+        <v>26.68</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>26.4</v>
+        <v>26.59</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>26.22</v>
+        <v>26.62</v>
       </c>
       <c r="R30" s="25" t="n">
-        <v>-2.16</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.38</v>
+        <v>49.14</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>48.66</v>
+        <v>48.4</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>48.06</v>
+        <v>47.78</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>48.25</v>
+        <v>47.69</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>48.59</v>
+        <v>48.19</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.87</v>
+        <v>47.45</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.53</v>
+        <v>46.95</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>47.15</v>
+        <v>46.71</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.66</v>
+        <v>47.36</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>47.06</v>
+        <v>46.74</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.34</v>
+        <v>46</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.79</v>
+        <v>47.43</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.71</v>
+        <v>47.42</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>0.84</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>127.45</v>
+        <v>129.28</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>125.75</v>
+        <v>126.88</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>124.33</v>
+        <v>124.87</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>124.8</v>
+        <v>125</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>125.6</v>
+        <v>126.4</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>123.9</v>
+        <v>124</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>123.1</v>
+        <v>122.6</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>122.2</v>
+        <v>121.6</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>123.37</v>
+        <v>123.53</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>121.95</v>
+        <v>121.52</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>120.25</v>
+        <v>119.12</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>123.7</v>
+        <v>123.86</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>123.51</v>
+        <v>123.72</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>124</v>
+        <v>123.6</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>59.48</v>
+        <v>60.02</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>57.08</v>
+        <v>57.72</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>55.07</v>
+        <v>55.79</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>57.05</v>
+        <v>57.2</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>54.65</v>
+        <v>54.9</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>52.25</v>
+        <v>52.6</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>53.73</v>
+        <v>54.51</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>51.72</v>
+        <v>52.58</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>49.32</v>
+        <v>50.28</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>54.28</v>
+        <v>54.79</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>53.92</v>
+        <v>54.69</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>55.15</v>
+        <v>54.4</v>
       </c>
       <c r="R33" s="23" t="n">
-        <v>3.47</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.24</v>
+        <v>23.97</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.73</v>
+        <v>23.56</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.3</v>
+        <v>23.22</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.55</v>
+        <v>23.24</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.73</v>
+        <v>23.48</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.22</v>
+        <v>23.07</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>23.04</v>
+        <v>22.83</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.71</v>
+        <v>22.66</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>23.01</v>
+        <v>22.99</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.58</v>
+        <v>22.65</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>22.07</v>
+        <v>22.24</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>23.14</v>
+        <v>23.05</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.05</v>
+        <v>23.02</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23.36</v>
+        <v>23</v>
       </c>
       <c r="R34" s="23" t="n">
-        <v>1.43</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>25.85</v>
+        <v>26.03</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.45</v>
+        <v>25.65</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.11</v>
+        <v>25.34</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.28</v>
+        <v>25.4</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.44</v>
+        <v>25.6</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.04</v>
+        <v>25.22</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>24.88</v>
+        <v>25.02</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>24.64</v>
+        <v>24.84</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>24.89</v>
+        <v>25.12</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>24.55</v>
+        <v>24.81</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
+        <v>24.43</v>
+      </c>
+      <c r="N35" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>24.98</v>
+        <v>25.19</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>24.92</v>
+        <v>25.15</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="R35" s="23" t="n">
-        <v>0.76</v>
+        <v>25.2</v>
+      </c>
+      <c r="R35" s="25" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.789999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.609999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.56</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.619999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I36" s="17" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="n">
         <v>8.380000000000001</v>
-      </c>
-      <c r="J36" s="17" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>8.41</v>
       </c>
       <c r="P36" s="21" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="R36" s="23" t="n">
-        <v>1.67</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>34.04</v>
+        <v>34.81</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>33.32</v>
+        <v>33.89</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>32.72</v>
+        <v>33.12</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>33.03</v>
+        <v>33.08</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>33.31</v>
+        <v>33.66</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>32.59</v>
+        <v>32.74</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>32.31</v>
+        <v>32.16</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.87</v>
+        <v>31.82</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>32.32</v>
+        <v>32.6</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.72</v>
+        <v>31.83</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>31</v>
+        <v>30.91</v>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>32.48</v>
+        <v>32.71</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>32.37</v>
+        <v>32.67</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>32.74</v>
+        <v>32.5</v>
       </c>
       <c r="R37" s="23" t="n">
-        <v>1.49</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>178.82</v>
+        <v>180.16</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>175.22</v>
+        <v>176.66</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>172.21</v>
+        <v>173.73</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>173.87</v>
+        <v>173.33</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>175.23</v>
+        <v>175.67</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>171.63</v>
+        <v>172.17</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>170.27</v>
+        <v>169.83</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>168.03</v>
+        <v>168.67</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>170.19</v>
+        <v>171.77</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>167.18</v>
+        <v>168.84</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>163.58</v>
+        <v>165.34</v>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>171.05</v>
+        <v>172.1</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>170.47</v>
+        <v>172.04</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>172.5</v>
+        <v>171</v>
       </c>
       <c r="R38" s="23" t="n">
-        <v>2.07</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="20" t="inlineStr">
+      <c r="N39" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="Q39" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="R39" s="23" t="n">
+      <c r="R39" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22.25</v>
+        <v>22.66</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>21.72</v>
+        <v>21.82</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.27</v>
+        <v>21.12</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.36</v>
+        <v>21.18</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.64</v>
+        <v>21.66</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21.11</v>
+        <v>20.82</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>20.83</v>
+        <v>20.34</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>20.58</v>
+        <v>19.98</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>20.98</v>
+        <v>20.64</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>20.53</v>
+        <v>19.94</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="N40" s="24" t="inlineStr">
+        <v>19.1</v>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>21.06</v>
+        <v>20.77</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>21.02</v>
+        <v>20.71</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>21.08</v>
+        <v>20.7</v>
       </c>
       <c r="R40" s="23" t="n">
-        <v>0.14</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>189.69</v>
+        <v>187.4</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>185.99</v>
+        <v>185.3</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>182.89</v>
+        <v>183.54</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>184.93</v>
+        <v>183.57</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>186.17</v>
+        <v>184.83</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>182.47</v>
+        <v>182.73</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>181.23</v>
+        <v>181.47</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>178.77</v>
+        <v>180.63</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>180.81</v>
+        <v>182.36</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>177.71</v>
+        <v>180.6</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>174.01</v>
+        <v>178.5</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>181.78</v>
+        <v>182.63</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>181.1</v>
+        <v>182.53</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>183.7</v>
+        <v>182.3</v>
       </c>
       <c r="R41" s="23" t="n">
-        <v>1.49</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>36.65</v>
+        <v>36.66</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.37</v>
+        <v>36.4</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.14</v>
+        <v>36.18</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>36.29</v>
+        <v>36.15</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>36.39</v>
+        <v>36.33</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>36.11</v>
+        <v>36.07</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>36.01</v>
+        <v>35.89</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.83</v>
+        <v>35.81</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>35.98</v>
+        <v>36.04</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>35.75</v>
+        <v>35.82</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>35.47</v>
+        <v>35.56</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
         <v>36.06</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>36</v>
+        <v>36.06</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>36.2</v>
+        <v>35.98</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>0.67</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.07</v>
+        <v>28.74</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.47</v>
+        <v>28.1</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>26.97</v>
+        <v>27.56</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.27</v>
+        <v>27.74</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.49</v>
+        <v>28.04</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>26.89</v>
+        <v>27.4</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>26.67</v>
+        <v>27.1</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.29</v>
+        <v>26.76</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>26.63</v>
+        <v>27.2</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>26.13</v>
+        <v>26.66</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>25.53</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
+        <v>26.02</v>
+      </c>
+      <c r="N43" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>26.78</v>
+        <v>27.33</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>26.68</v>
+        <v>27.25</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>27.06</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>1.88</v>
+        <v>27.44</v>
+      </c>
+      <c r="R43" s="25" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26</v>
+        <v>26.04</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.84</v>
+        <v>25.88</v>
       </c>
       <c r="E44" s="14" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="H44" s="16" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="L44" s="19" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="N44" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O44" s="21" t="n">
         <v>25.7</v>
       </c>
-      <c r="F44" s="15" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="H44" s="16" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="I44" s="17" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="J44" s="17" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="L44" s="19" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="n">
-        <v>25.64</v>
-      </c>
       <c r="P44" s="21" t="n">
-        <v>25.63</v>
+        <v>25.67</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.64</v>
+        <v>25.78</v>
       </c>
       <c r="R44" s="25" t="n">
-        <v>-0.16</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="45">
@@ -3362,39 +3362,39 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.62</v>
+        <v>7.66</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.4</v>
+        <v>7.42</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.45</v>
+        <v>7.42</v>
       </c>
       <c r="G45" s="15" t="n">
         <v>7.5</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.34</v>
+        <v>7.35</v>
       </c>
       <c r="L45" s="19" t="n">
         <v>7.24</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="N45" s="24" t="inlineStr">
+        <v>7.11</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -3403,13 +3403,13 @@
         <v>7.36</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.4</v>
+        <v>7.34</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>0.27</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.45</v>
+        <v>12.26</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>12.14</v>
+        <v>12.05</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.88</v>
+        <v>11.87</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>12.05</v>
+        <v>11.85</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>12.15</v>
+        <v>11.99</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.84</v>
+        <v>11.78</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.74</v>
+        <v>11.64</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.53</v>
+        <v>11.57</v>
       </c>
       <c r="K46" s="18" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="L46" s="19" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="M46" s="19" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O46" s="21" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="P46" s="21" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="Q46" s="22" t="n">
         <v>11.71</v>
       </c>
-      <c r="L46" s="19" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O46" s="21" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="P46" s="21" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="Q46" s="22" t="n">
-        <v>11.94</v>
-      </c>
       <c r="R46" s="23" t="n">
-        <v>2.23</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>197.42</v>
+        <v>195.44</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>194.32</v>
+        <v>192.94</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>191.72</v>
+        <v>190.85</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>191.83</v>
+        <v>191.3</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>193.67</v>
+        <v>192.6</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>190.57</v>
+        <v>190.1</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>188.73</v>
+        <v>188.8</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>187.47</v>
+        <v>187.6</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>189.98</v>
+        <v>189.45</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>187.38</v>
+        <v>187.35</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>184.28</v>
-      </c>
-      <c r="N47" s="24" t="inlineStr">
+        <v>184.85</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>190.4</v>
+        <v>189.87</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>190.22</v>
+        <v>189.64</v>
       </c>
       <c r="Q47" s="22" t="n">
         <v>190</v>
       </c>
       <c r="R47" s="25" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>45.94</v>
+        <v>46.81</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>45.52</v>
+        <v>45.85</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>45.17</v>
+        <v>45.05</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>45.4</v>
+        <v>45.01</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>45.54</v>
+        <v>45.61</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>45.12</v>
+        <v>44.65</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>44.98</v>
+        <v>44.05</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>44.7</v>
+        <v>43.69</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>44.93</v>
+        <v>44.51</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>44.58</v>
+        <v>43.71</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>44.16</v>
+        <v>42.75</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>45.04</v>
+        <v>44.62</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>44.97</v>
+        <v>44.59</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>45.26</v>
+        <v>44.4</v>
       </c>
       <c r="R48" s="23" t="n">
-        <v>0.71</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>32.7</v>
+        <v>32.85</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32.12</v>
+        <v>32.35</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>31.63</v>
+        <v>31.93</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>31.94</v>
+        <v>31.91</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>32.14</v>
+        <v>32.23</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.56</v>
+        <v>31.73</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>30.98</v>
+        <v>31.23</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.31</v>
+        <v>31.65</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>30.82</v>
+        <v>31.23</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.24</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
+        <v>30.73</v>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>31.46</v>
+        <v>31.71</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>31.35</v>
+        <v>31.69</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>31.74</v>
+        <v>31.6</v>
       </c>
       <c r="R49" s="23" t="n">
-        <v>2.19</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.92</v>
+        <v>12.85</v>
       </c>
       <c r="D50" s="13" t="n">
         <v>12.57</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.27</v>
+        <v>12.34</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.44</v>
+        <v>12.35</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.57</v>
+        <v>12.51</v>
       </c>
       <c r="H50" s="16" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O50" s="21" t="n">
         <v>12.22</v>
       </c>
-      <c r="I50" s="17" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O50" s="21" t="n">
-        <v>12.16</v>
-      </c>
       <c r="P50" s="21" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.31</v>
+        <v>12.18</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>2.16</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>59.96</v>
+        <v>59.93</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>59.06</v>
+        <v>59.08</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>58.3</v>
+        <v>58.36</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.63</v>
+        <v>58.43</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>59.02</v>
+        <v>58.92</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>58.12</v>
+        <v>58.07</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>57.73</v>
+        <v>57.58</v>
       </c>
       <c r="J51" s="17" t="n">
         <v>57.22</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.8</v>
+        <v>57.89</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>57.04</v>
+        <v>57.17</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>56.14</v>
+        <v>56.32</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.99</v>
+        <v>58.01</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.87</v>
+        <v>57.95</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>58.25</v>
+        <v>57.95</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>1.22</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.59</v>
+        <v>22.74</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.06</v>
+        <v>22.12</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.22</v>
+        <v>22.15</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22.02</v>
+        <v>22</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.93</v>
+        <v>21.81</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.73</v>
+        <v>21.66</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.89</v>
+        <v>21.92</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.65</v>
+        <v>21.64</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>21.36</v>
+        <v>21.3</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>21.97</v>
+        <v>21.98</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>21.92</v>
+        <v>21.95</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>22.12</v>
+        <v>21.96</v>
       </c>
       <c r="R52" s="23" t="n">
-        <v>0.73</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="E53" s="14" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I53" s="17" t="n">
         <v>5.02</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="H53" s="16" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="I53" s="17" t="n">
-        <v>4.98</v>
-      </c>
       <c r="J53" s="17" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M53" s="19" t="n">
         <v>4.93</v>
       </c>
-      <c r="K53" s="18" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="N53" s="20" t="inlineStr">
+      <c r="N53" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="P53" s="21" t="n">
-        <v>4.98</v>
+        <v>5.05</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="R53" s="23" t="n">
-        <v>1.41</v>
+        <v>5.04</v>
+      </c>
+      <c r="R53" s="25" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>19.62</v>
+        <v>18.98</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.62</v>
+        <v>18.27</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>17.78</v>
+        <v>17.67</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>17.8</v>
+        <v>17.91</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.4</v>
+        <v>18.22</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.4</v>
+        <v>17.51</v>
       </c>
       <c r="I54" s="17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J54" s="17" t="n">
         <v>16.8</v>
       </c>
-      <c r="J54" s="17" t="n">
-        <v>16.4</v>
-      </c>
       <c r="K54" s="18" t="n">
-        <v>17.22</v>
+        <v>17.28</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.38</v>
+        <v>16.68</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>15.38</v>
+        <v>15.97</v>
       </c>
       <c r="N54" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.35</v>
+        <v>17.42</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.3</v>
+        <v>17.33</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.2</v>
+        <v>17.59</v>
       </c>
       <c r="R54" s="25" t="n">
-        <v>-3.96</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>97.67</v>
+        <v>97.87</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>96.02</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>94.64</v>
+        <v>93.64</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>94.95</v>
+        <v>93.42</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>95.8</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>94.15000000000001</v>
+        <v>92.63</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>93.3</v>
+        <v>91.12</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>92.5</v>
+        <v>90.33</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>93.70999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>92.33</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>90.68000000000001</v>
+        <v>88.13</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>94</v>
+        <v>92.58</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>93.84</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="R55" s="25" t="n">
-        <v>-0.11</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R55" s="23" t="n">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>18.37</v>
+        <v>17.7</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.74</v>
+        <v>17.18</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>17.21</v>
+        <v>16.75</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>17.19</v>
+        <v>16.73</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>17.59</v>
+        <v>17.05</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.96</v>
+        <v>16.53</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.56</v>
+        <v>16.21</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>16.33</v>
+        <v>16.01</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>16.86</v>
+        <v>16.45</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>16.33</v>
+        <v>16.02</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="N56" s="24" t="inlineStr">
+        <v>15.5</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.93</v>
+        <v>16.51</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.91</v>
+        <v>16.49</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="R56" s="25" t="n">
-        <v>-0.06</v>
+        <v>16.4</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.15</v>
+        <v>20.94</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.9</v>
+        <v>20.81</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>20.7</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.81</v>
+        <v>20.69</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.91</v>
+        <v>20.77</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.66</v>
+        <v>20.64</v>
       </c>
       <c r="I57" s="17" t="n">
         <v>20.56</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.41</v>
+        <v>20.51</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20.55</v>
+        <v>20.63</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>20.35</v>
+        <v>20.52</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>20.1</v>
+        <v>20.39</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.62</v>
+        <v>20.64</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.57</v>
+        <v>20.64</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.72</v>
+        <v>20.6</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>0.63</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.41</v>
+        <v>22.47</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.22</v>
+        <v>22.29</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.06</v>
+        <v>22.14</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.16</v>
+        <v>22.19</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.23</v>
+        <v>22.27</v>
       </c>
       <c r="H58" s="16" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="K58" s="18" t="n">
         <v>22.04</v>
       </c>
-      <c r="I58" s="17" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="J58" s="17" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="K58" s="18" t="n">
-        <v>21.95</v>
-      </c>
       <c r="L58" s="19" t="n">
-        <v>21.79</v>
+        <v>21.89</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>21.6</v>
+        <v>21.71</v>
       </c>
       <c r="N58" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22</v>
+        <v>22.07</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>21.97</v>
+        <v>22.05</v>
       </c>
       <c r="Q58" s="22" t="n">
         <v>22.1</v>
       </c>
-      <c r="R58" s="23" t="n">
-        <v>0.32</v>
+      <c r="R58" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>27.75</v>
+        <v>28.04</v>
       </c>
       <c r="D59" s="13" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="E59" s="14" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="H59" s="16" t="n">
         <v>27.57</v>
       </c>
-      <c r="E59" s="14" t="n">
-        <v>27.42</v>
-      </c>
-      <c r="F59" s="15" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="G59" s="15" t="n">
+      <c r="I59" s="17" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="J59" s="17" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="K59" s="18" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="L59" s="19" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="M59" s="19" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="N59" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O59" s="21" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="P59" s="21" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="Q59" s="22" t="n">
         <v>27.58</v>
       </c>
-      <c r="H59" s="16" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="I59" s="17" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="J59" s="17" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="K59" s="18" t="n">
-        <v>27.32</v>
-      </c>
-      <c r="L59" s="19" t="n">
-        <v>27.17</v>
-      </c>
-      <c r="M59" s="19" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="N59" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O59" s="21" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="P59" s="21" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="Q59" s="22" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="R59" s="23" t="n">
-        <v>0.51</v>
+      <c r="R59" s="25" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.18</v>
+        <v>45.98</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>44.98</v>
+        <v>45.04</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>44.82</v>
+        <v>44.25</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>44.79</v>
+        <v>44.33</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>44.93</v>
+        <v>44.87</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>44.73</v>
+        <v>43.93</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>44.59</v>
+        <v>43.39</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>44.53</v>
+        <v>42.99</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>44.7</v>
+        <v>43.73</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>44.54</v>
+        <v>42.94</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="N60" s="24" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>44.72</v>
+        <v>43.86</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>44.72</v>
+        <v>43.8</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>44.66</v>
-      </c>
-      <c r="R60" s="25" t="n">
-        <v>-0.4</v>
+        <v>43.8</v>
+      </c>
+      <c r="R60" s="23" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>18.47</v>
+        <v>18.73</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.33</v>
+        <v>18.48</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.21</v>
+        <v>18.27</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.23</v>
+        <v>18.25</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="H61" s="16" t="n">
         <v>18.16</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>18.09</v>
+        <v>18</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>18.02</v>
+        <v>17.91</v>
       </c>
       <c r="K61" s="18" t="n">
         <v>18.13</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>18.01</v>
+        <v>17.93</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.87</v>
+        <v>17.68</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="P61" s="21" t="n">
         <v>18.15</v>
       </c>
-      <c r="P61" s="21" t="n">
-        <v>18.14</v>
-      </c>
       <c r="Q61" s="22" t="n">
-        <v>18.15</v>
+        <v>18.08</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>0.55</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.08</v>
+        <v>15.19</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>14.99</v>
+        <v>15.06</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>14.91</v>
+        <v>14.95</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>14.94</v>
+        <v>15.01</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>14.98</v>
+        <v>15.06</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.89</v>
+        <v>14.93</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.85</v>
+        <v>14.88</v>
       </c>
       <c r="J62" s="17" t="n">
         <v>14.8</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.78</v>
+        <v>14.77</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.69</v>
+        <v>14.64</v>
       </c>
       <c r="N62" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.88</v>
+        <v>14.91</v>
       </c>
       <c r="P62" s="21" t="n">
-        <v>14.87</v>
+        <v>14.89</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R62" s="23" t="n">
-        <v>0.13</v>
+        <v>14.96</v>
+      </c>
+      <c r="R62" s="25" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.92</v>
+        <v>24.56</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.42</v>
+        <v>24.25</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>24</v>
+        <v>23.99</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>24.21</v>
+        <v>23.97</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.41</v>
+        <v>24.17</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.91</v>
+        <v>23.86</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.71</v>
+        <v>23.66</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.41</v>
+        <v>23.55</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.72</v>
+        <v>23.82</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.3</v>
+        <v>23.56</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>22.8</v>
+        <v>23.25</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.83</v>
+        <v>23.85</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.76</v>
+        <v>23.84</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>24.01</v>
+        <v>23.77</v>
       </c>
       <c r="R63" s="23" t="n">
-        <v>0.97</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.21</v>
+        <v>7.13</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.13</v>
+        <v>7.08</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
       <c r="F64" s="15" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="G64" s="15" t="n">
         <v>7.08</v>
       </c>
-      <c r="G64" s="15" t="n">
-        <v>7.12</v>
-      </c>
       <c r="H64" s="16" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>6.96</v>
+        <v>6.98</v>
       </c>
       <c r="K64" s="18" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
         <v>7.02</v>
       </c>
-      <c r="L64" s="19" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>7.03</v>
-      </c>
       <c r="P64" s="21" t="n">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="Q64" s="22" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="R64" s="23" t="n">
-        <v>0.28</v>
+        <v>7.05</v>
+      </c>
+      <c r="R64" s="25" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="65">
@@ -4602,53 +4602,53 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="D65" s="13" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E65" s="14" t="n">
         <v>4.83</v>
       </c>
-      <c r="E65" s="14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="F65" s="15" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
       <c r="I65" s="17" t="n">
         <v>4.76</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="N65" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R65" s="23" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="R65" s="25" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="K66" s="18" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="L66" s="19" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P66" s="21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Q66" s="22" t="n">
         <v>4.38</v>
       </c>
-      <c r="M66" s="19" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N66" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="P66" s="21" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="Q66" s="22" t="n">
-        <v>4.45</v>
-      </c>
       <c r="R66" s="23" t="n">
-        <v>1.14</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>64.70999999999999</v>
+        <v>64.72</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>64.20999999999999</v>
+        <v>64.12</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>63.79</v>
+        <v>63.62</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>64.06999999999999</v>
+        <v>63.62</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>64.23</v>
+        <v>63.98</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>63.73</v>
+        <v>63.38</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>63.57</v>
+        <v>63.02</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>63.23</v>
+        <v>62.78</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>63.51</v>
+        <v>63.28</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>63.09</v>
+        <v>62.78</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>62.59</v>
-      </c>
-      <c r="N67" s="24" t="inlineStr">
+        <v>62.18</v>
+      </c>
+      <c r="N67" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>63.64</v>
+        <v>63.36</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>63.55</v>
+        <v>63.33</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>63.9</v>
+        <v>63.25</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>68.01000000000001</v>
+        <v>66.06</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>66.45999999999999</v>
+        <v>65.16</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>65.16</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>65.31999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>66.18000000000001</v>
+        <v>65</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>64.63</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>63.77</v>
+        <v>63.6</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>63.08</v>
+        <v>63.2</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>64.29000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>62.99</v>
+        <v>63.14</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>61.44</v>
-      </c>
-      <c r="N68" s="24" t="inlineStr">
+        <v>62.24</v>
+      </c>
+      <c r="N68" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>64.52</v>
+        <v>64.03</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>64.41</v>
+        <v>63.97</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="R68" s="25" t="n">
-        <v>-1.38</v>
+        <v>64</v>
+      </c>
+      <c r="R68" s="23" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>78.47</v>
+        <v>80.44</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>76.81999999999999</v>
+        <v>78.19</v>
       </c>
       <c r="E69" s="14" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="F69" s="15" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="G69" s="15" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>75.65000000000001</v>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J69" s="17" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="K69" s="18" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="L69" s="19" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="M69" s="19" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="N69" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O69" s="21" t="n">
         <v>75.44</v>
       </c>
-      <c r="F69" s="15" t="n">
-        <v>75.75</v>
-      </c>
-      <c r="G69" s="15" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="H69" s="16" t="n">
-        <v>74.95</v>
-      </c>
-      <c r="I69" s="17" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="J69" s="17" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="K69" s="18" t="n">
-        <v>74.51000000000001</v>
-      </c>
-      <c r="L69" s="19" t="n">
-        <v>73.13</v>
-      </c>
-      <c r="M69" s="19" t="n">
-        <v>71.48</v>
-      </c>
-      <c r="N69" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O69" s="21" t="n">
-        <v>74.8</v>
-      </c>
       <c r="P69" s="21" t="n">
-        <v>74.64</v>
+        <v>75.22</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>74.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="R69" s="25" t="n">
-        <v>-1.32</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>119.91</v>
+        <v>120.25</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>117.31</v>
+        <v>117.25</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>115.13</v>
+        <v>114.74</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>116.1</v>
+        <v>114.93</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>117.2</v>
+        <v>116.67</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>114.6</v>
+        <v>113.67</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>113.5</v>
+        <v>111.93</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>112</v>
+        <v>110.67</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>113.67</v>
+        <v>113.06</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>111.49</v>
+        <v>110.55</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>108.89</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
+        <v>107.55</v>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>114.24</v>
+        <v>113.48</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>113.87</v>
+        <v>113.29</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>115</v>
-      </c>
-      <c r="R70" s="25" t="n">
-        <v>-0.86</v>
+        <v>113.2</v>
+      </c>
+      <c r="R70" s="23" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.74</v>
+        <v>23.33</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.26</v>
+        <v>23.12</v>
       </c>
       <c r="E71" s="14" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="G71" s="15" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="H71" s="16" t="n">
         <v>22.85</v>
       </c>
-      <c r="F71" s="15" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="G71" s="15" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="H71" s="16" t="n">
-        <v>22.77</v>
-      </c>
       <c r="I71" s="17" t="n">
-        <v>22.57</v>
+        <v>22.72</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>22.29</v>
+        <v>22.64</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>22.59</v>
+        <v>22.83</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>22.18</v>
+        <v>22.65</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
+        <v>22.44</v>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>22.69</v>
+        <v>22.85</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>22.62</v>
+        <v>22.84</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>22.86</v>
+        <v>22.79</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>1.6</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>18.42</v>
+        <v>18.16</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.18</v>
+        <v>18</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>17.98</v>
+        <v>17.86</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>17.99</v>
+        <v>17.86</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.13</v>
+        <v>17.96</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.89</v>
+        <v>17.8</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>17.65</v>
+        <v>17.64</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.84</v>
+        <v>17.78</v>
       </c>
       <c r="L72" s="19" t="n">
         <v>17.64</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>17.4</v>
+        <v>17.48</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.88</v>
+        <v>17.79</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.86</v>
+        <v>17.79</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.85</v>
+        <v>17.76</v>
       </c>
       <c r="R72" s="23" t="n">
-        <v>0.85</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>233.85</v>
+        <v>235.96</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>231.35</v>
+        <v>231.66</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>229.25</v>
+        <v>228.05</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>229.1</v>
+        <v>227.77</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>230.7</v>
+        <v>230.53</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>228.2</v>
+        <v>226.23</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>226.6</v>
+        <v>223.47</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>225.7</v>
+        <v>221.93</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>227.85</v>
+        <v>225.65</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>225.76</v>
+        <v>222.04</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>223.26</v>
-      </c>
-      <c r="N73" s="24" t="inlineStr">
+        <v>217.74</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>228.12</v>
+        <v>226.11</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>228.05</v>
+        <v>225.98</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>227.5</v>
-      </c>
-      <c r="R73" s="25" t="n">
-        <v>-0.09</v>
+        <v>225</v>
+      </c>
+      <c r="R73" s="23" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.48</v>
+        <v>15.71</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.33</v>
+        <v>15.44</v>
       </c>
       <c r="E74" s="14" t="n">
         <v>15.21</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.2</v>
+        <v>15.33</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.29</v>
+        <v>15.43</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.14</v>
+        <v>15.16</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.05</v>
+        <v>15.06</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>14.99</v>
+        <v>14.89</v>
       </c>
       <c r="K74" s="18" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="M74" s="19" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="N74" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O74" s="21" t="n">
         <v>15.12</v>
       </c>
-      <c r="L74" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="N74" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O74" s="21" t="n">
-        <v>15.14</v>
-      </c>
       <c r="P74" s="21" t="n">
-        <v>15.13</v>
+        <v>15.08</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.1</v>
+        <v>15.22</v>
       </c>
       <c r="R74" s="25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>36.21</v>
+        <v>37.42</v>
       </c>
       <c r="D75" s="13" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I75" s="17" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="J75" s="17" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="K75" s="18" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="L75" s="19" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="M75" s="19" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="N75" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O75" s="21" t="n">
         <v>35.91</v>
       </c>
-      <c r="E75" s="14" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="F75" s="15" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G75" s="15" t="n">
-        <v>35.86</v>
-      </c>
-      <c r="H75" s="16" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="I75" s="17" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="J75" s="17" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="K75" s="18" t="n">
-        <v>35.49</v>
-      </c>
-      <c r="L75" s="19" t="n">
-        <v>35.23</v>
-      </c>
-      <c r="M75" s="19" t="n">
-        <v>34.93</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O75" s="21" t="n">
-        <v>35.53</v>
-      </c>
       <c r="P75" s="21" t="n">
-        <v>35.51</v>
+        <v>35.84</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>35.54</v>
-      </c>
-      <c r="R75" s="23" t="n">
-        <v>0.34</v>
+        <v>36</v>
+      </c>
+      <c r="R75" s="25" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>24.96</v>
+        <v>24.91</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>23.64</v>
+        <v>24.08</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>22.53</v>
+        <v>23.39</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>23.26</v>
+        <v>23.32</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>23.7</v>
+        <v>23.86</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>22.38</v>
+        <v>23.03</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>21.94</v>
+        <v>22.49</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>21.06</v>
+        <v>22.2</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>21.79</v>
+        <v>22.92</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>20.68</v>
+        <v>22.23</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="N76" s="20" t="inlineStr">
+        <v>21.4</v>
+      </c>
+      <c r="N76" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>22.14</v>
+        <v>23.01</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>21.89</v>
+        <v>22.99</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>22.82</v>
+        <v>22.78</v>
       </c>
       <c r="R76" s="23" t="n">
-        <v>9.98</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.27</v>
+        <v>44.11</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>43.03</v>
+        <v>42.93</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>41.99</v>
+        <v>41.94</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>42.47</v>
+        <v>41.81</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>42.99</v>
+        <v>42.59</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>41.75</v>
+        <v>41.41</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>41.23</v>
+        <v>40.63</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>40.51</v>
+        <v>40.23</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>41.29</v>
+        <v>41.28</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>40.25</v>
+        <v>40.29</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.01</v>
+        <v>39.11</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>41.57</v>
+        <v>41.39</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>41.39</v>
+        <v>41.37</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>41.96</v>
+        <v>41.02</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>1.35</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.36</v>
+        <v>5.31</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.34</v>
+        <v>5.29</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.21</v>
+        <v>5.16</v>
       </c>
       <c r="J78" s="17" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="N78" s="24" t="inlineStr">
+        <v>5.01</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="P78" s="21" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
       <c r="Q78" s="22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R78" s="25" t="n">
-        <v>-0.57</v>
+        <v>5.2</v>
+      </c>
+      <c r="R78" s="23" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>18.63</v>
+        <v>18.8</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.43</v>
+        <v>18.48</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.27</v>
+        <v>18.21</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.3</v>
+        <v>18.21</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>18.41</v>
+        <v>18.4</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>18.21</v>
+        <v>18.08</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>18.1</v>
+        <v>17.89</v>
       </c>
       <c r="J79" s="17" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="K79" s="18" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="P79" s="21" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="Q79" s="22" t="n">
         <v>18.01</v>
       </c>
-      <c r="K79" s="18" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="N79" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O79" s="21" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="P79" s="21" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="Q79" s="22" t="n">
-        <v>18.2</v>
-      </c>
       <c r="R79" s="23" t="n">
-        <v>0.39</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>79.19</v>
+        <v>81.16</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>78.39</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>77.72</v>
+        <v>77.12</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>78.13</v>
+        <v>76.87</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>78.42</v>
+        <v>78.33</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>77.62</v>
+        <v>76.13</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>77.33</v>
+        <v>74.67</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>76.81999999999999</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>77.28</v>
+        <v>75.88</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>76.61</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>75.81</v>
+        <v>71.84</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>77.48</v>
+        <v>76.09</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>77.34</v>
+        <v>76.06</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>77.84999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="R80" s="23" t="n">
-        <v>0.97</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.64</v>
+        <v>5.33</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.55</v>
+        <v>4.99</v>
       </c>
       <c r="E81" s="14" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H81" s="16" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="I81" s="17" t="n">
         <v>4.47</v>
       </c>
-      <c r="F81" s="15" t="n">
+      <c r="J81" s="17" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K81" s="18" t="n">
         <v>4.51</v>
       </c>
-      <c r="G81" s="15" t="n">
+      <c r="L81" s="19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M81" s="19" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="N81" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O81" s="21" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="P81" s="21" t="n">
         <v>4.54</v>
       </c>
-      <c r="H81" s="16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="I81" s="17" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="J81" s="17" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="K81" s="18" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="L81" s="19" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="M81" s="19" t="n">
+      <c r="Q81" s="22" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R81" s="25" t="n">
         <v>4.25</v>
-      </c>
-      <c r="N81" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O81" s="21" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="P81" s="21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="Q81" s="22" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="R81" s="23" t="n">
-        <v>0.45</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>61.75</v>
+        <v>60.32</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>60.05</v>
+        <v>59.32</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>58.63</v>
+        <v>58.48</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>59.13</v>
+        <v>58.4</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>59.92</v>
+        <v>59.05</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>58.22</v>
+        <v>58.05</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>57.43</v>
+        <v>57.4</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>56.52</v>
+        <v>57.05</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>57.67</v>
+        <v>57.92</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>56.25</v>
+        <v>57.08</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>54.55</v>
+        <v>56.08</v>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>58.01</v>
+        <v>58.02</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>57.81</v>
+        <v>58</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>58.35</v>
+        <v>57.75</v>
       </c>
       <c r="R82" s="23" t="n">
-        <v>1.13</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="83">
@@ -5718,54 +5718,54 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>37.36</v>
+        <v>38.06</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.14</v>
+        <v>37.64</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>36.95</v>
+        <v>37.29</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.02</v>
+        <v>37.27</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.12</v>
+        <v>37.53</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>36.9</v>
+        <v>37.11</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.8</v>
+        <v>36.85</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.68</v>
+        <v>36.69</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>36.83</v>
+        <v>37.05</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.64</v>
+        <v>36.7</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.42</v>
+        <v>36.28</v>
       </c>
       <c r="N83" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>36.87</v>
+        <v>37.1</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>36.85</v>
+        <v>37.09</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="R83" s="23" t="n">
-        <v>0.27</v>
+        <v>37</v>
+      </c>
+      <c r="R83" s="25" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>93.5</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>92.45</v>
+        <v>91.97</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>91.56999999999999</v>
+        <v>91.47</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>91.72</v>
+        <v>91.7</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>92.28</v>
+        <v>91.95</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>91.23</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>90.67</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>90.18000000000001</v>
+        <v>90.75</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>90.98</v>
+        <v>91.13</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>90.09999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>89.05</v>
+        <v>90.03</v>
       </c>
       <c r="N84" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>91.15000000000001</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.06</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>91.15000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="R84" s="25" t="n">
-        <v>-1.67</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.32</v>
+        <v>17.48</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.84</v>
+        <v>17</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.43</v>
+        <v>16.59</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.57</v>
+        <v>16.54</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.8</v>
+        <v>16.86</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.32</v>
+        <v>16.38</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.09</v>
+        <v>16.06</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>15.84</v>
+        <v>15.9</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>16.17</v>
+        <v>16.33</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>15.76</v>
+        <v>15.92</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.28</v>
+        <v>15.44</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.26</v>
+        <v>16.37</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.35</v>
+        <v>16.22</v>
       </c>
       <c r="R85" s="23" t="n">
-        <v>1.55</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="86">
@@ -5904,19 +5904,19 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>124.38</v>
+        <v>125.03</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>123.28</v>
+        <v>123.53</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>122.36</v>
+        <v>122.27</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>122.23</v>
+        <v>122.63</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>122.97</v>
+        <v>123.37</v>
       </c>
       <c r="H86" s="16" t="n">
         <v>121.87</v>
@@ -5925,33 +5925,33 @@
         <v>121.13</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>120.77</v>
+        <v>120.37</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>121.74</v>
+        <v>121.43</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>120.82</v>
+        <v>120.17</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>119.72</v>
+        <v>118.67</v>
       </c>
       <c r="N86" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>121.85</v>
+        <v>121.71</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>121.83</v>
+        <v>121.55</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>121.5</v>
+        <v>121.9</v>
       </c>
       <c r="R86" s="25" t="n">
-        <v>-0.41</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>58.62</v>
+        <v>58.58</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>57.37</v>
+        <v>56.83</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>56.32</v>
+        <v>55.37</v>
       </c>
       <c r="F87" s="15" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="G87" s="15" t="n">
         <v>56.48</v>
       </c>
-      <c r="G87" s="15" t="n">
-        <v>57.17</v>
-      </c>
       <c r="H87" s="16" t="n">
-        <v>55.92</v>
+        <v>54.73</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>55.23</v>
+        <v>53.72</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>54.67</v>
+        <v>52.98</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>55.62</v>
+        <v>54.38</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>54.58</v>
+        <v>52.92</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="N87" s="24" t="inlineStr">
+        <v>51.17</v>
+      </c>
+      <c r="N87" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>55.82</v>
+        <v>54.63</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>55.72</v>
+        <v>54.52</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>55.8</v>
+        <v>54.45</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>0.45</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="88">
@@ -6028,54 +6028,54 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>9.74</v>
+        <v>9.82</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.51</v>
+        <v>9.49</v>
       </c>
       <c r="J88" s="17" t="n">
-        <v>9.460000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L88" s="19" t="n">
         <v>9.44</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="N88" s="24" t="inlineStr">
+        <v>9.32</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="P88" s="21" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q88" s="22" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="P88" s="21" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="Q88" s="22" t="n">
-        <v>9.56</v>
-      </c>
       <c r="R88" s="23" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>16.65</v>
+        <v>16.51</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.26</v>
+        <v>16.18</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>15.93</v>
+        <v>15.91</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>16.04</v>
+        <v>15.87</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>16.23</v>
+        <v>16.09</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>15.84</v>
+        <v>15.76</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.65</v>
+        <v>15.54</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>15.45</v>
+        <v>15.43</v>
       </c>
       <c r="K89" s="18" t="n">
         <v>15.72</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15.39</v>
+        <v>15.45</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="N89" s="24" t="inlineStr">
+        <v>15.12</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>15.79</v>
+        <v>15.75</v>
       </c>
       <c r="P89" s="21" t="n">
         <v>15.75</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>15.86</v>
+        <v>15.65</v>
       </c>
       <c r="R89" s="23" t="n">
-        <v>1.6</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>17.76</v>
+        <v>17.88</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.46</v>
+        <v>17.61</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>17.2</v>
+        <v>17.38</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>17.32</v>
+        <v>17.35</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>17.45</v>
+        <v>17.53</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.15</v>
+        <v>17.26</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>17.02</v>
+        <v>17.08</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>16.85</v>
+        <v>16.99</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.04</v>
+        <v>17.23</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>16.78</v>
+        <v>17</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
+        <v>16.73</v>
+      </c>
+      <c r="N90" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>17.1</v>
+        <v>17.26</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.06</v>
+        <v>17.25</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.2</v>
+        <v>17.17</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.22</v>
+        <v>30.62</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.48</v>
+        <v>30.1</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>29.86</v>
+        <v>29.67</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>30.04</v>
+        <v>29.73</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.4</v>
+        <v>30.01</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.66</v>
+        <v>29.49</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.3</v>
+        <v>29.21</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>28.92</v>
+        <v>28.97</v>
       </c>
       <c r="K91" s="18" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="L91" s="19" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M91" s="19" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="N91" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O91" s="21" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="P91" s="21" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="Q91" s="22" t="n">
         <v>29.44</v>
       </c>
-      <c r="L91" s="19" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="M91" s="19" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="N91" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O91" s="21" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="P91" s="21" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="Q91" s="22" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="R91" s="25" t="n">
-        <v>-0.47</v>
+      <c r="R91" s="23" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.2</v>
+        <v>20.47</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>19.86</v>
+        <v>20.08</v>
       </c>
       <c r="E92" s="14" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="F92" s="15" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="G92" s="15" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="J92" s="17" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="K92" s="18" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O92" s="21" t="n">
         <v>19.58</v>
       </c>
-      <c r="F92" s="15" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="G92" s="15" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H92" s="16" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="I92" s="17" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="J92" s="17" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="K92" s="18" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="L92" s="19" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M92" s="19" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="N92" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O92" s="21" t="n">
-        <v>19.46</v>
-      </c>
       <c r="P92" s="21" t="n">
-        <v>19.41</v>
+        <v>19.57</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>19.57</v>
+        <v>19.5</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>1.29</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>28.18</v>
+        <v>26.67</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>27.08</v>
+        <v>26.29</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>26.16</v>
+        <v>25.98</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>26.47</v>
+        <v>25.99</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.99</v>
+        <v>26.21</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.89</v>
+        <v>25.83</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.37</v>
+        <v>25.61</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>24.79</v>
+        <v>25.45</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.54</v>
+        <v>25.76</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>24.62</v>
+        <v>25.45</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>23.52</v>
+        <v>25.07</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="P93" s="21" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="Q93" s="22" t="n">
         <v>25.76</v>
       </c>
-      <c r="P93" s="21" t="n">
-        <v>25.63</v>
-      </c>
-      <c r="Q93" s="22" t="n">
-        <v>25.96</v>
-      </c>
       <c r="R93" s="23" t="n">
-        <v>2.29</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>179.12</v>
+        <v>178.3</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>176.02</v>
+        <v>174.9</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>173.42</v>
+        <v>172.05</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>174.4</v>
+        <v>172.87</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>175.8</v>
+        <v>174.53</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>172.7</v>
+        <v>171.13</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>171.3</v>
+        <v>169.47</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>169.6</v>
+        <v>167.73</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>171.68</v>
+        <v>170.15</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>169.08</v>
+        <v>167.3</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>165.98</v>
+        <v>163.9</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>172.31</v>
+        <v>170.77</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>171.92</v>
+        <v>170.41</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>173</v>
+        <v>171.2</v>
       </c>
       <c r="R94" s="23" t="n">
-        <v>0.46</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>13.7</v>
+        <v>13.31</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>13.33</v>
+        <v>13.18</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>13.02</v>
+        <v>13.07</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>13.2</v>
+        <v>13.13</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>13.34</v>
+        <v>13.18</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>12.97</v>
+        <v>13.05</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="J95" s="17" t="n">
-        <v>12.6</v>
+        <v>12.92</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>12.81</v>
+        <v>13</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>12.5</v>
+        <v>12.89</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
+        <v>12.76</v>
+      </c>
+      <c r="N95" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>12.9</v>
+        <v>13.03</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>12.84</v>
+        <v>13.01</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="R95" s="23" t="n">
-        <v>2.83</v>
+        <v>13.08</v>
+      </c>
+      <c r="R95" s="25" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>19.61</v>
+        <v>19.24</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.2</v>
+        <v>19.06</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>18.86</v>
+        <v>18.91</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.09</v>
+        <v>18.96</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.22</v>
+        <v>19.05</v>
       </c>
       <c r="H96" s="16" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="I96" s="17" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="J96" s="17" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="K96" s="18" t="n">
         <v>18.81</v>
       </c>
-      <c r="I96" s="17" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="J96" s="17" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="K96" s="18" t="n">
-        <v>18.63</v>
-      </c>
       <c r="L96" s="19" t="n">
-        <v>18.29</v>
+        <v>18.66</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="N96" s="20" t="inlineStr">
+        <v>18.48</v>
+      </c>
+      <c r="N96" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>18.74</v>
+        <v>18.85</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>18.66</v>
+        <v>18.82</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>18.95</v>
+        <v>18.88</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>2.16</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.13</v>
+        <v>16.4</v>
       </c>
       <c r="D97" s="13" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="E97" s="14" t="n">
         <v>15.98</v>
       </c>
-      <c r="E97" s="14" t="n">
-        <v>15.86</v>
-      </c>
       <c r="F97" s="15" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="H97" s="16" t="n">
         <v>15.93</v>
       </c>
-      <c r="G97" s="15" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H97" s="16" t="n">
-        <v>15.84</v>
-      </c>
       <c r="I97" s="17" t="n">
-        <v>15.78</v>
+        <v>15.82</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>15.69</v>
+        <v>15.7</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>15.77</v>
+        <v>15.85</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>15.65</v>
+        <v>15.66</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="N97" s="20" t="inlineStr">
+        <v>15.43</v>
+      </c>
+      <c r="N97" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>15.81</v>
+        <v>15.9</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.78</v>
+        <v>15.87</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>15.88</v>
-      </c>
-      <c r="R97" s="23" t="n">
-        <v>1.15</v>
+        <v>15.95</v>
+      </c>
+      <c r="R97" s="25" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F98" s="15" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="G98" s="15" t="n">
         <v>9.32</v>
       </c>
-      <c r="G98" s="15" t="n">
-        <v>9.4</v>
-      </c>
       <c r="H98" s="16" t="n">
-        <v>9.17</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.09</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J98" s="17" t="n">
         <v>8.94</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>8.890000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.66</v>
+        <v>8.74</v>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.23</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="R98" s="23" t="n">
-        <v>0.65</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>25.49</v>
+        <v>25.66</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25.17</v>
+        <v>25.25</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>24.9</v>
+        <v>24.91</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>25</v>
+        <v>24.96</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.15</v>
+        <v>25.18</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>24.83</v>
+        <v>24.77</v>
       </c>
       <c r="I99" s="17" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="J99" s="17" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="K99" s="18" t="n">
         <v>24.68</v>
       </c>
-      <c r="J99" s="17" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="K99" s="18" t="n">
-        <v>24.72</v>
-      </c>
       <c r="L99" s="19" t="n">
-        <v>24.45</v>
+        <v>24.34</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>24.13</v>
-      </c>
-      <c r="N99" s="24" t="inlineStr">
+        <v>23.93</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>24.79</v>
+        <v>24.74</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>24.75</v>
+        <v>24.71</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>24.86</v>
+        <v>24.73</v>
       </c>
       <c r="R99" s="23" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.35</v>
+        <v>16.85</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>16.22</v>
+        <v>16.38</v>
       </c>
       <c r="E100" s="14" t="n">
-        <v>16.11</v>
+        <v>15.99</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>16.13</v>
+        <v>15.93</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.2</v>
+        <v>16.25</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>16.07</v>
+        <v>15.78</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>16</v>
+        <v>15.46</v>
       </c>
       <c r="J100" s="17" t="n">
-        <v>15.94</v>
+        <v>15.31</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>16.04</v>
+        <v>15.72</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>15.93</v>
+        <v>15.33</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>15.8</v>
+        <v>14.86</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>16.06</v>
+        <v>15.77</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>16.05</v>
+        <v>15.76</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>16.06</v>
+        <v>15.62</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>0.06</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>30.54</v>
+        <v>30.9</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.02</v>
+        <v>30.22</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.59</v>
+        <v>29.65</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.71</v>
+        <v>29.57</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>29.97</v>
+        <v>30.03</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.45</v>
+        <v>29.35</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>29.19</v>
+        <v>28.89</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>28.93</v>
+        <v>28.67</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.29</v>
+        <v>29.27</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>28.86</v>
+        <v>28.7</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>28.34</v>
+        <v>28.02</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.39</v>
+        <v>29.33</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>29.33</v>
+        <v>29.32</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>29.46</v>
+        <v>29.12</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>0.96</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>15.72</v>
+        <v>14.76</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>15.13</v>
+        <v>14.56</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.64</v>
+        <v>14.4</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.65</v>
+        <v>14.44</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.41</v>
+        <v>14.34</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.06</v>
+        <v>14.24</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>13.82</v>
+        <v>14.14</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.31</v>
+        <v>14.28</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.82</v>
+        <v>14.12</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>13.23</v>
+        <v>13.92</v>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.38</v>
+        <v>14.32</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.36</v>
+        <v>14.3</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="R102" s="23" t="n">
-        <v>0.99</v>
+        <v>14.34</v>
+      </c>
+      <c r="R102" s="25" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>69.48</v>
+        <v>69.31</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>68.13</v>
+        <v>68.16</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>67</v>
+        <v>67.2</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>67.75</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>68.2</v>
+        <v>67.83</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>66.84999999999999</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>66.40000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>65.5</v>
+        <v>65.53</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>66.25</v>
+        <v>66.55</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>65.12</v>
+        <v>65.59</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>63.77</v>
+        <v>64.44</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>66.59999999999999</v>
+        <v>66.66</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>66.34999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>67.3</v>
+        <v>66.3</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>2.05</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.19</v>
+        <v>14.2</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>13.99</v>
+        <v>14.04</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>14.09</v>
+        <v>14.07</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.19</v>
+        <v>14.17</v>
       </c>
       <c r="H104" s="16" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="I104" s="17" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="J104" s="17" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="L104" s="19" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="M104" s="19" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="N104" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O104" s="21" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="P104" s="21" t="n">
         <v>13.95</v>
       </c>
-      <c r="I104" s="17" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="J104" s="17" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="K104" s="18" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="L104" s="19" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="M104" s="19" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O104" s="21" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="P104" s="21" t="n">
-        <v>13.87</v>
-      </c>
       <c r="Q104" s="22" t="n">
-        <v>14</v>
+        <v>13.97</v>
       </c>
       <c r="R104" s="23" t="n">
-        <v>1.45</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>16.36</v>
+        <v>19.8</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>15.98</v>
+        <v>18.21</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>15.67</v>
+        <v>16.88</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>15.82</v>
+        <v>17.76</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>15.98</v>
+        <v>18.29</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>15.44</v>
+        <v>16.17</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>15.45</v>
+        <v>15.99</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.14</v>
+        <v>14.66</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.76</v>
+        <v>13.07</v>
       </c>
       <c r="N105" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>15.54</v>
+        <v>16.41</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>15.48</v>
+        <v>16.11</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="R105" s="23" t="n">
-        <v>1.1</v>
+        <v>17.23</v>
+      </c>
+      <c r="R105" s="25" t="n">
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="E106" s="14" t="n">
         <v>2.42</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="J106" s="17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K106" s="18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L106" s="19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M106" s="19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O106" s="21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P106" s="21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q106" s="22" t="n">
         <v>2.37</v>
       </c>
-      <c r="K106" s="18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L106" s="19" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="M106" s="19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O106" s="21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="P106" s="21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q106" s="22" t="n">
-        <v>2.42</v>
-      </c>
       <c r="R106" s="23" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>37.64</v>
+        <v>38.49</v>
       </c>
       <c r="D107" s="13" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="E107" s="14" t="n">
         <v>37.02</v>
       </c>
-      <c r="E107" s="14" t="n">
-        <v>36.5</v>
-      </c>
       <c r="F107" s="15" t="n">
-        <v>36.82</v>
+        <v>37.2</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>37.04</v>
+        <v>37.6</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.42</v>
+        <v>36.8</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>36.16</v>
+        <v>36.58</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>35.64</v>
+        <v>35.91</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>35.02</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
+        <v>35.11</v>
+      </c>
+      <c r="N107" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>36.31</v>
+        <v>36.72</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>36.2</v>
+        <v>36.64</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="R107" s="23" t="n">
-        <v>1.22</v>
+        <v>36.8</v>
+      </c>
+      <c r="R107" s="25" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>7.91</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D108" s="13" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F108" s="15" t="n">
         <v>7.8</v>
       </c>
-      <c r="E108" s="14" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="F108" s="15" t="n">
+      <c r="G108" s="15" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H108" s="16" t="n">
         <v>7.75</v>
       </c>
-      <c r="G108" s="15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H108" s="16" t="n">
-        <v>7.69</v>
-      </c>
       <c r="I108" s="17" t="n">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
       <c r="J108" s="17" t="n">
         <v>7.58</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.64</v>
+        <v>7.73</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>7.55</v>
+        <v>7.58</v>
       </c>
       <c r="M108" s="19" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
+        <v>7.41</v>
+      </c>
+      <c r="N108" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
       <c r="P108" s="21" t="n">
-        <v>7.65</v>
+        <v>7.74</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
       <c r="R108" s="23" t="n">
-        <v>0.52</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.28</v>
+        <v>44.42</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>44.02</v>
+        <v>43.96</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.8</v>
+        <v>43.58</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.81</v>
+        <v>43.53</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.97</v>
+        <v>43.83</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.71</v>
+        <v>43.37</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>43.55</v>
+        <v>43.07</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>43.45</v>
+        <v>42.91</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>43.66</v>
+        <v>43.32</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>43.44</v>
+        <v>42.94</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>43.18</v>
-      </c>
-      <c r="N109" s="24" t="inlineStr">
+        <v>42.48</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>43.69</v>
+        <v>43.37</v>
       </c>
       <c r="P109" s="21" t="n">
-        <v>43.68</v>
+        <v>43.36</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>43.66</v>
+        <v>43.22</v>
       </c>
       <c r="R109" s="23" t="n">
-        <v>0.14</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>66.14</v>
+        <v>67.05</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>65.19</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.39</v>
+        <v>64.38</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.28</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>64.92</v>
+        <v>65.48</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>63.97</v>
+        <v>64.03</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.33</v>
+        <v>63.37</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>63.02</v>
+        <v>62.58</v>
       </c>
       <c r="K110" s="18" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="L110" s="19" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="M110" s="19" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="N110" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O110" s="21" t="n">
         <v>63.86</v>
       </c>
-      <c r="L110" s="19" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="M110" s="19" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="N110" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O110" s="21" t="n">
-        <v>63.95</v>
-      </c>
       <c r="P110" s="21" t="n">
-        <v>63.93</v>
+        <v>63.68</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>63.65</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="R110" s="25" t="n">
-        <v>-0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="111">
@@ -7463,19 +7463,19 @@
         <v>10.06</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>10.08</v>
+        <v>10.06</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="H111" s="16" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K111" s="18" t="n">
         <v>10.03</v>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
       <c r="P111" s="21" t="n">
         <v>10.03</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.04</v>
+        <v>10.01</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>302.38</v>
+        <v>314.13</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>296.58</v>
+        <v>304.53</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>291.72</v>
+        <v>296.49</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>292.53</v>
+        <v>299.27</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>295.67</v>
+        <v>303.73</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>289.87</v>
+        <v>294.13</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>286.73</v>
+        <v>289.67</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>284.07</v>
+        <v>284.53</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>288.48</v>
+        <v>291.11</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>283.62</v>
+        <v>283.07</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>277.82</v>
+        <v>273.47</v>
       </c>
       <c r="N112" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>289.4</v>
+        <v>293</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>288.93</v>
+        <v>291.86</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>289.4</v>
-      </c>
-      <c r="R112" s="23" t="n">
-        <v>0.49</v>
+        <v>294.8</v>
+      </c>
+      <c r="R112" s="25" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>228</v>
+        <v>227.34</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>224.6</v>
+        <v>224.04</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>221.75</v>
+        <v>221.27</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>223.63</v>
+        <v>220.9</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>224.77</v>
+        <v>223.1</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>221.37</v>
+        <v>219.8</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>220.23</v>
+        <v>217.6</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>217.97</v>
+        <v>216.5</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>219.85</v>
+        <v>219.43</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>217</v>
+        <v>216.66</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>213.6</v>
+        <v>213.36</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>220.74</v>
+        <v>219.74</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>220.11</v>
+        <v>219.68</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>222.5</v>
+        <v>218.7</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>0.68</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>614.25</v>
+        <v>649.6900000000001</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>605.75</v>
+        <v>622.6900000000001</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>598.63</v>
+        <v>600.0599999999999</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>599.67</v>
+        <v>599</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>604.33</v>
+        <v>616</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>595.83</v>
+        <v>589</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>591.17</v>
+        <v>572</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>587.33</v>
+        <v>562</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>593.87</v>
+        <v>584.9400000000001</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>586.75</v>
+        <v>562.3099999999999</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>578.25</v>
-      </c>
-      <c r="N114" s="24" t="inlineStr">
+        <v>535.3099999999999</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>595.1799999999999</v>
+        <v>588.02</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>594.53</v>
+        <v>587.05</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>595</v>
-      </c>
-      <c r="R114" s="25" t="n">
-        <v>-0.67</v>
+        <v>582</v>
+      </c>
+      <c r="R114" s="23" t="n">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="G115" s="15" t="n">
         <v>5.78</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="I115" s="17" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="J115" s="17" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="K115" s="18" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L115" s="19" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M115" s="19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O115" s="21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P115" s="21" t="n">
         <v>5.59</v>
       </c>
-      <c r="J115" s="17" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="K115" s="18" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="L115" s="19" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="M115" s="19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="N115" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O115" s="21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="P115" s="21" t="n">
-        <v>5.65</v>
-      </c>
       <c r="Q115" s="22" t="n">
-        <v>5.64</v>
+        <v>5.55</v>
       </c>
       <c r="R115" s="23" t="n">
-        <v>0.18</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>95.20999999999999</v>
+        <v>94</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>92.76000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>90.70999999999999</v>
+        <v>90.88</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>92.06999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>92.88</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>90.43000000000001</v>
+        <v>90.12</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>89.62</v>
+        <v>88.98</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>87.98</v>
+        <v>88.42</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>89.34</v>
+        <v>89.92</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>87.29000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>84.84</v>
+        <v>86.8</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>89.98</v>
+        <v>90.09</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>89.53</v>
+        <v>90.06</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>91.25</v>
+        <v>89.55</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>3.11</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>10.16</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>9.630000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.18</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.43</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="H117" s="16" t="n">
         <v>9.1</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>8.57</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>8.890000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>8.44</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="N117" s="24" t="inlineStr">
+        <v>8.48</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>9.01</v>
+        <v>9.09</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>8.93</v>
+        <v>9.07</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.23</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="R117" s="23" t="n">
-        <v>0.33</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>16.64</v>
+        <v>16.79</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.4</v>
+        <v>16.49</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.2</v>
+        <v>16.23</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.3</v>
+        <v>16.22</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.39</v>
+        <v>16.41</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>16.15</v>
+        <v>16.11</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>16.06</v>
+        <v>15.92</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.91</v>
+        <v>15.81</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>16.06</v>
+        <v>16.07</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.86</v>
+        <v>15.81</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.62</v>
+        <v>15.51</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.12</v>
+        <v>16.1</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.08</v>
+        <v>16.09</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.2</v>
+        <v>16.03</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.22</v>
+        <v>11.44</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.01</v>
+        <v>11.13</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>10.83</v>
+        <v>10.87</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.94</v>
+        <v>10.88</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.02</v>
+        <v>11.07</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>10.81</v>
+        <v>10.76</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.73</v>
+        <v>10.57</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="K119" s="18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L119" s="19" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="M119" s="19" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O119" s="21" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="P119" s="21" t="n">
         <v>10.72</v>
       </c>
-      <c r="L119" s="19" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="M119" s="19" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="N119" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O119" s="21" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="P119" s="21" t="n">
-        <v>10.73</v>
-      </c>
       <c r="Q119" s="22" t="n">
-        <v>10.87</v>
+        <v>10.7</v>
       </c>
       <c r="R119" s="23" t="n">
-        <v>1.21</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="120">
@@ -8012,54 +8012,54 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.43</v>
+        <v>12.35</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>11.95</v>
+        <v>11.96</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.06</v>
+        <v>11.99</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.16</v>
+        <v>12.1</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>11.9</v>
+        <v>11.89</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>11.8</v>
+        <v>11.78</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>11.64</v>
+        <v>11.68</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>11.81</v>
+        <v>11.85</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>11.59</v>
+        <v>11.67</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="P120" s="21" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="Q120" s="22" t="n">
         <v>11.87</v>
       </c>
-      <c r="P120" s="21" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>11.95</v>
-      </c>
       <c r="R120" s="23" t="n">
-        <v>1.27</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.4</v>
+        <v>7.51</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>7.1</v>
+        <v>7.12</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.16</v>
+        <v>7.13</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.23</v>
+        <v>7.25</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="I121" s="17" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="J121" s="17" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="K121" s="18" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="L121" s="19" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M121" s="19" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="N121" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O121" s="21" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="P121" s="21" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="Q121" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="J121" s="17" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="K121" s="18" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="L121" s="19" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="M121" s="19" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O121" s="21" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="P121" s="21" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>7.09</v>
-      </c>
       <c r="R121" s="23" t="n">
-        <v>1.72</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>6.95</v>
+        <v>7.2</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>6.74</v>
+        <v>6.92</v>
       </c>
       <c r="E122" s="14" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="H122" s="16" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="I122" s="17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J122" s="17" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K122" s="18" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L122" s="19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M122" s="19" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O122" s="21" t="n">
         <v>6.56</v>
       </c>
-      <c r="F122" s="15" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="G122" s="15" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="H122" s="16" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="I122" s="17" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="J122" s="17" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="K122" s="18" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="L122" s="19" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="M122" s="19" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="N122" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O122" s="21" t="n">
+      <c r="P122" s="21" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Q122" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="P122" s="21" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="Q122" s="22" t="n">
-        <v>6.58</v>
-      </c>
       <c r="R122" s="23" t="n">
-        <v>1.39</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>29.3</v>
+        <v>31.25</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>28.84</v>
+        <v>29.91</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.46</v>
+        <v>28.79</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.43</v>
+        <v>28.63</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>28.73</v>
+        <v>29.53</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.27</v>
+        <v>28.19</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>27.97</v>
+        <v>27.29</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>27.81</v>
+        <v>26.85</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>28.2</v>
+        <v>28.03</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>27.82</v>
+        <v>26.91</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="N123" s="24" t="inlineStr">
+        <v>25.57</v>
+      </c>
+      <c r="N123" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>28.25</v>
+        <v>28.16</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>28.24</v>
+        <v>28.14</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="R123" s="25" t="n">
-        <v>-0.99</v>
+        <v>27.74</v>
+      </c>
+      <c r="R123" s="23" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>166.33</v>
+        <v>165.89</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>161.43</v>
+        <v>162.19</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>157.32</v>
+        <v>159.09</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>160.03</v>
+        <v>160.53</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>161.67</v>
+        <v>162.07</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>156.77</v>
+        <v>158.37</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>155.13</v>
+        <v>156.83</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>151.87</v>
+        <v>154.67</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>154.58</v>
+        <v>157.01</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>150.47</v>
+        <v>153.91</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>145.57</v>
-      </c>
-      <c r="N124" s="20" t="inlineStr">
+        <v>150.21</v>
+      </c>
+      <c r="N124" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>155.86</v>
+        <v>157.83</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>154.96</v>
+        <v>157.3</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="R124" s="23" t="n">
-        <v>2.19</v>
+        <v>159</v>
+      </c>
+      <c r="R124" s="25" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>53.87</v>
+        <v>54.67</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>53.27</v>
+        <v>53.42</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>52.77</v>
+        <v>52.38</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>52.9</v>
+        <v>52.3</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>52.6</v>
+        <v>51.85</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>52.3</v>
+        <v>51.05</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>52</v>
+        <v>50.6</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>52.43</v>
+        <v>51.68</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>51.93</v>
+        <v>50.63</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="N125" s="24" t="inlineStr">
+        <v>49.38</v>
+      </c>
+      <c r="N125" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>52.54</v>
+        <v>51.81</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>52.48</v>
+        <v>51.77</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>52.6</v>
+        <v>51.5</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>0.1</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>15.54</v>
+        <v>14.85</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>14.53</v>
+        <v>14.27</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.69</v>
+        <v>13.78</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>14.09</v>
+        <v>13.72</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13.49</v>
+        <v>13.52</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.08</v>
+        <v>13.14</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.48</v>
+        <v>12.94</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>13.12</v>
+        <v>13.46</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.28</v>
+        <v>12.97</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>11.27</v>
+        <v>12.39</v>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.35</v>
+        <v>13.51</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="R126" s="23" t="n">
-        <v>4.67</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>16.05</v>
+        <v>15.62</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15.34</v>
+        <v>15</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.74</v>
+        <v>14.48</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.8</v>
+        <v>14.43</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>15.21</v>
+        <v>14.83</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.5</v>
+        <v>14.21</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>14.09</v>
+        <v>13.81</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>13.79</v>
+        <v>13.59</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.35</v>
+        <v>14.14</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13.04</v>
+        <v>13</v>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.45</v>
+        <v>14.2</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.4</v>
+        <v>14.18</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.4</v>
+        <v>14.02</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>0.91</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.57</v>
+        <v>6.54</v>
       </c>
       <c r="E128" s="14" t="n">
         <v>6.38</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>6.06</v>
+        <v>6.11</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.83</v>
+        <v>5.92</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
         <v>6.3</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.27</v>
+        <v>6.29</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>2.58</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>10.08</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.68</v>
+        <v>9.42</v>
       </c>
       <c r="E129" s="14" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="G129" s="15" t="n">
         <v>9.34</v>
       </c>
-      <c r="F129" s="15" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="G129" s="15" t="n">
-        <v>9.58</v>
-      </c>
       <c r="H129" s="16" t="n">
-        <v>9.18</v>
+        <v>9.06</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="J129" s="17" t="n">
         <v>8.779999999999999</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.119999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="N129" s="24" t="inlineStr">
+        <v>8.52</v>
+      </c>
+      <c r="N129" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>9.16</v>
+        <v>9.06</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.15</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="R129" s="25" t="n">
-        <v>-0.98</v>
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R129" s="23" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>148.65</v>
+        <v>152.35</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>146.15</v>
+        <v>147.25</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>144.05</v>
+        <v>142.98</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>143.97</v>
+        <v>142.4</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>145.53</v>
+        <v>145.8</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>143.03</v>
+        <v>140.7</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>141.47</v>
+        <v>137.3</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>140.53</v>
+        <v>135.6</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>142.65</v>
+        <v>140.12</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>140.56</v>
+        <v>135.85</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>138.06</v>
-      </c>
-      <c r="N130" s="24" t="inlineStr">
+        <v>130.75</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>142.94</v>
+        <v>140.61</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>142.85</v>
+        <v>140.52</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="R130" s="25" t="n">
-        <v>-1.32</v>
+        <v>139</v>
+      </c>
+      <c r="R130" s="23" t="n">
+        <v>-2.39</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-24</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.42</v>
+        <v>20.49</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.28</v>
+        <v>20.31</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>20.16</v>
       </c>
       <c r="F3" s="15" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="H3" s="16" t="n">
         <v>20.14</v>
       </c>
-      <c r="G3" s="15" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="H3" s="16" t="n">
-        <v>20.1</v>
-      </c>
       <c r="I3" s="17" t="n">
-        <v>20</v>
+        <v>20.07</v>
       </c>
       <c r="J3" s="17" t="n">
         <v>19.96</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.08</v>
+        <v>20.06</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>19.96</v>
+        <v>19.91</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.82</v>
+        <v>19.73</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>20.09</v>
+        <v>20.11</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.09</v>
+        <v>20.07</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.05</v>
+        <v>20.19</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>-0.25</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.06</v>
+        <v>12.17</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.91</v>
+        <v>11.97</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.79</v>
+        <v>11.81</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.8</v>
+        <v>11.92</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.88</v>
+        <v>11.98</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>11.73</v>
+        <v>11.78</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.65</v>
+        <v>11.72</v>
       </c>
       <c r="J4" s="17" t="n">
         <v>11.58</v>
       </c>
       <c r="K4" s="18" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
       <c r="L4" s="19" t="n">
-        <v>11.58</v>
+        <v>11.53</v>
       </c>
       <c r="M4" s="19" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>11.72</v>
+        <v>11.75</v>
       </c>
       <c r="P4" s="21" t="n">
         <v>11.71</v>
       </c>
       <c r="Q4" s="22" t="n">
-        <v>11.71</v>
+        <v>11.85</v>
       </c>
       <c r="R4" s="23" t="n">
-        <v>-0.26</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15.1</v>
+        <v>15.02</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.85</v>
+        <v>14.82</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.64</v>
+        <v>14.66</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.67</v>
+        <v>14.75</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.81</v>
+        <v>14.83</v>
       </c>
       <c r="H5" s="16" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="M5" s="19" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="P5" s="21" t="n">
         <v>14.56</v>
       </c>
-      <c r="I5" s="17" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L5" s="19" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M5" s="19" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="P5" s="21" t="n">
-        <v>14.52</v>
-      </c>
       <c r="Q5" s="22" t="n">
-        <v>14.53</v>
+        <v>14.68</v>
       </c>
       <c r="R5" s="23" t="n">
-        <v>-1.16</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.87</v>
+        <v>21.68</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.46</v>
+        <v>21.23</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>21.12</v>
+        <v>20.85</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.09</v>
+        <v>21.1</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.36</v>
+        <v>21.25</v>
       </c>
       <c r="H6" s="16" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L6" s="19" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="M6" s="19" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="P6" s="21" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="Q6" s="22" t="n">
         <v>20.95</v>
       </c>
-      <c r="I6" s="17" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="L6" s="19" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="M6" s="19" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O6" s="21" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="P6" s="21" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="Q6" s="22" t="n">
-        <v>20.83</v>
-      </c>
       <c r="R6" s="23" t="n">
-        <v>-1.65</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>35.06</v>
+        <v>33.9</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>34.34</v>
+        <v>33.58</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.74</v>
+        <v>33.31</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.79</v>
+        <v>33.47</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>34.21</v>
+        <v>33.59</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.49</v>
+        <v>33.27</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>33.07</v>
+        <v>33.15</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>32.77</v>
+        <v>32.95</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.34</v>
+        <v>33.13</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.74</v>
+        <v>32.86</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
+        <v>32.54</v>
+      </c>
+      <c r="N7" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.44</v>
+        <v>33.21</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.39</v>
+        <v>33.16</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="R7" s="23" t="n">
-        <v>-0.65</v>
+        <v>33.36</v>
+      </c>
+      <c r="R7" s="25" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.78</v>
+        <v>23.53</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.36</v>
+        <v>23.2</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>23.01</v>
+        <v>22.93</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>23.17</v>
+        <v>23.1</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.34</v>
+        <v>23.21</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.92</v>
+        <v>22.88</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.75</v>
+        <v>22.77</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.5</v>
+        <v>22.55</v>
       </c>
       <c r="K8" s="18" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="P8" s="21" t="n">
         <v>22.77</v>
       </c>
-      <c r="L8" s="19" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="N8" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <v>22.81</v>
-      </c>
       <c r="Q8" s="22" t="n">
-        <v>22.99</v>
+        <v>22.98</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>1.1</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>124.38</v>
+        <v>129.36</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>121.98</v>
+        <v>125.06</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>119.97</v>
+        <v>121.45</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>119.7</v>
+        <v>123.57</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>121.3</v>
+        <v>125.13</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>118.9</v>
+        <v>120.83</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>117.3</v>
+        <v>119.27</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>116.5</v>
+        <v>116.53</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>118.63</v>
+        <v>119.05</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>116.62</v>
+        <v>115.44</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>114.22</v>
+        <v>111.14</v>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>118.86</v>
+        <v>120.11</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>118.82</v>
+        <v>119.38</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>118.1</v>
+        <v>122</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>-1.17</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>66.68000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>65.33</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>64.2</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>64.05</v>
+        <v>65.28</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>64.95</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>63.6</v>
+        <v>64.27</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>62.7</v>
+        <v>63.73</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>62.25</v>
+        <v>62.72</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>63.45</v>
+        <v>63.59</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>62.32</v>
+        <v>62.29</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>60.97</v>
+        <v>60.74</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>63.58</v>
+        <v>63.99</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>63.55</v>
+        <v>63.71</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>63.15</v>
+        <v>64.75</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>-2.02</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>24.86</v>
+        <v>25.35</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.61</v>
+        <v>24.88</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.4</v>
+        <v>24.49</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.4</v>
+        <v>24.75</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.55</v>
+        <v>24.9</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.3</v>
+        <v>24.43</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.15</v>
+        <v>24.28</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.05</v>
+        <v>23.96</v>
       </c>
       <c r="K11" s="18" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="P11" s="21" t="n">
         <v>24.26</v>
       </c>
-      <c r="L11" s="19" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="M11" s="19" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="P11" s="21" t="n">
-        <v>24.28</v>
-      </c>
       <c r="Q11" s="22" t="n">
-        <v>24.24</v>
+        <v>24.59</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>-1.34</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>24.94</v>
+        <v>25.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>24.76</v>
+        <v>25.04</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.61</v>
+        <v>24.66</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.61</v>
+        <v>24.91</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.72</v>
+        <v>25.06</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.54</v>
+        <v>24.6</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.43</v>
+        <v>24.45</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.36</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>24.51</v>
+        <v>24.4</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.36</v>
+        <v>24.02</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>24.18</v>
+        <v>23.56</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.53</v>
+        <v>24.52</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.52</v>
+        <v>24.44</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.5</v>
+        <v>24.75</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>-0.65</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>42.47</v>
+        <v>43.15</v>
       </c>
       <c r="D13" s="13" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>41.55</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>40.77</v>
-      </c>
       <c r="G13" s="15" t="n">
-        <v>41.33</v>
+        <v>41.97</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.41</v>
+        <v>40.73</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>39.85</v>
+        <v>40.31</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>39.49</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.26</v>
+        <v>40.17</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.49</v>
+        <v>39.13</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>38.57</v>
+        <v>37.89</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.37</v>
+        <v>40.5</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.33</v>
+        <v>40.27</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40.2</v>
+        <v>41.14</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>-0.15</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="14">
@@ -1440,39 +1440,39 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E14" s="14" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="F14" s="15" t="n">
         <v>8.51</v>
       </c>
-      <c r="F14" s="15" t="n">
-        <v>8.52</v>
-      </c>
       <c r="G14" s="15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="H14" s="16" t="n">
         <v>8.43</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.31</v>
+        <v>8.35</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="K14" s="18" t="n">
         <v>8.4</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
+        <v>8.1</v>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -1484,10 +1484,10 @@
         <v>8.41</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="R14" s="25" t="n">
-        <v>0.48</v>
+        <v>8.42</v>
+      </c>
+      <c r="R14" s="23" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>14.61</v>
+        <v>13.84</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>14.12</v>
+        <v>13.65</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.71</v>
+        <v>13.49</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>13.66</v>
+        <v>13.57</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>13.98</v>
+        <v>13.65</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.49</v>
+        <v>13.46</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.17</v>
+        <v>13.38</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13</v>
+        <v>13.27</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.44</v>
+        <v>13.38</v>
       </c>
       <c r="L15" s="19" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="M15" s="19" t="n">
         <v>13.03</v>
       </c>
-      <c r="M15" s="19" t="n">
-        <v>12.54</v>
-      </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.48</v>
+        <v>13.43</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.48</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>-1.48</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.21</v>
+        <v>4.12</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>4.07</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="H16" s="16" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="L16" s="19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N16" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O16" s="21" t="n">
+      <c r="P16" s="21" t="n">
         <v>3.99</v>
       </c>
-      <c r="P16" s="21" t="n">
-        <v>3.98</v>
-      </c>
       <c r="Q16" s="22" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="R16" s="25" t="n">
-        <v>1.02</v>
+        <v>4.03</v>
+      </c>
+      <c r="R16" s="23" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>18.49</v>
+        <v>17.5</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.87</v>
+        <v>17.23</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>17.35</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.28</v>
+        <v>17.11</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.7</v>
+        <v>17.22</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>17.08</v>
+        <v>16.95</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.66</v>
+        <v>16.84</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.46</v>
+        <v>16.68</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>17.01</v>
+        <v>16.85</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.49</v>
+        <v>16.62</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
+        <v>16.35</v>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>17.07</v>
+        <v>16.91</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>17.05</v>
+        <v>16.87</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.87</v>
+        <v>17</v>
       </c>
       <c r="R17" s="23" t="n">
-        <v>-1</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>25.16</v>
+        <v>24.89</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.62</v>
+        <v>24.4</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>24.17</v>
+        <v>23.99</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>24.34</v>
+        <v>24.2</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.59</v>
+        <v>24.39</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>24.05</v>
+        <v>23.9</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.8</v>
+        <v>23.71</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>23.51</v>
+        <v>23.41</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.87</v>
+        <v>23.72</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>23.42</v>
+        <v>23.31</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>22.88</v>
+        <v>22.82</v>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.98</v>
+        <v>23.83</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.91</v>
+        <v>23.76</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="R18" s="25" t="n">
-        <v>1.52</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>65.29000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>63.69</v>
+        <v>63.03</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>62.35</v>
+        <v>61.9</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>62.17</v>
+        <v>62.58</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.23</v>
+        <v>63.07</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>61.63</v>
+        <v>61.72</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>60.57</v>
+        <v>61.23</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>60.03</v>
+        <v>60.37</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>61.45</v>
+        <v>61.15</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.11</v>
+        <v>60.02</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>58.51</v>
+        <v>58.67</v>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>61.61</v>
+        <v>61.48</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>61.58</v>
+        <v>61.25</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>61.1</v>
+        <v>62.1</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>-2.55</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.96</v>
+        <v>10.89</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.81</v>
+        <v>10.73</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>10.84</v>
+        <v>10.82</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>10.93</v>
+        <v>10.9</v>
       </c>
       <c r="H20" s="16" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="N20" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="Q20" s="22" t="n">
         <v>10.75</v>
       </c>
-      <c r="I20" s="17" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="N20" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="Q20" s="22" t="n">
-        <v>10.74</v>
-      </c>
       <c r="R20" s="23" t="n">
-        <v>-0.46</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>17.29</v>
       </c>
-      <c r="D21" s="13" t="n">
-        <v>17.11</v>
-      </c>
       <c r="E21" s="14" t="n">
-        <v>16.96</v>
+        <v>16.98</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>16.95</v>
+        <v>17.1</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.07</v>
+        <v>17.27</v>
       </c>
       <c r="H21" s="16" t="n">
         <v>16.89</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>16.77</v>
+        <v>16.72</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.71</v>
+        <v>16.51</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.86</v>
+        <v>16.76</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.71</v>
+        <v>16.45</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
+        <v>16.07</v>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>16.88</v>
+        <v>16.84</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>16.87</v>
+        <v>16.79</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="R21" s="25" t="n">
-        <v>0.12</v>
+        <v>16.93</v>
+      </c>
+      <c r="R21" s="23" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.97</v>
+        <v>36.12</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>36.15</v>
+        <v>35.5</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>35.46</v>
+        <v>34.98</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.5</v>
+        <v>35.31</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>35.98</v>
+        <v>35.53</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>35.16</v>
+        <v>34.91</v>
       </c>
       <c r="I22" s="17" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="N22" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="P22" s="21" t="n">
         <v>34.68</v>
       </c>
-      <c r="J22" s="17" t="n">
-        <v>34.34</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="L22" s="19" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>33.49</v>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>35.06</v>
-      </c>
       <c r="Q22" s="22" t="n">
-        <v>35.02</v>
+        <v>35.1</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>-1.74</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>15.74</v>
+        <v>16</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.52</v>
+        <v>15.64</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.33</v>
+        <v>15.34</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.35</v>
+        <v>15.4</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.48</v>
+        <v>15.59</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.13</v>
+        <v>15.04</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>15.04</v>
+        <v>14.87</v>
       </c>
       <c r="K23" s="18" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="Q23" s="22" t="n">
         <v>15.21</v>
       </c>
-      <c r="L23" s="19" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O23" s="21" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="P23" s="21" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="Q23" s="22" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="R23" s="23" t="n">
-        <v>-0.46</v>
+      <c r="R23" s="25" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.56</v>
+        <v>37.19</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.82</v>
+        <v>36.37</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>36.2</v>
+        <v>35.68</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>36.13</v>
+        <v>35.96</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.61</v>
+        <v>36.32</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.87</v>
+        <v>35.5</v>
       </c>
       <c r="I24" s="17" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="L24" s="19" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="N24" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="n">
         <v>35.39</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="L24" s="19" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O24" s="21" t="n">
-        <v>35.86</v>
-      </c>
       <c r="P24" s="21" t="n">
-        <v>35.84</v>
+        <v>35.28</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="R24" s="23" t="n">
-        <v>-1.27</v>
+        <v>35.6</v>
+      </c>
+      <c r="R24" s="25" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>60.41</v>
+        <v>58.39</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>58.46</v>
+        <v>57.19</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.82</v>
+        <v>56.19</v>
       </c>
       <c r="F25" s="15" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G25" s="15" t="n">
         <v>57.1</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>58.15</v>
-      </c>
       <c r="H25" s="16" t="n">
-        <v>56.2</v>
+        <v>55.9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>55.15</v>
+        <v>55.35</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>54.25</v>
+        <v>54.7</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>55.73</v>
+        <v>55.51</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.09</v>
+        <v>54.51</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
+        <v>53.31</v>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>56.04</v>
+        <v>55.75</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>55.88</v>
+        <v>55.61</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="R25" s="23" t="n">
-        <v>-1.23</v>
+        <v>56</v>
+      </c>
+      <c r="R25" s="25" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>236.48</v>
+        <v>214.99</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>221.78</v>
+        <v>208.69</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>209.47</v>
+        <v>203.41</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>211.27</v>
+        <v>205.37</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>219.33</v>
+        <v>208.23</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>204.63</v>
+        <v>201.93</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>196.57</v>
+        <v>199.07</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>189.93</v>
+        <v>195.63</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>201.23</v>
+        <v>199.89</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>188.92</v>
+        <v>194.61</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>174.22</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
+        <v>188.31</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>203.51</v>
+        <v>201.16</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>202.38</v>
+        <v>200.38</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>203.2</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>-2.31</v>
+        <v>202.5</v>
+      </c>
+      <c r="R26" s="25" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>79.41</v>
+        <v>78.31</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>77.61</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>76.09999999999999</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>75.90000000000001</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>77.09999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>75.3</v>
+        <v>74.78</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>74.09999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>73.5</v>
+        <v>73.23</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>75.09999999999999</v>
+        <v>74.59</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>73.59</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>71.79000000000001</v>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
+        <v>71.73999999999999</v>
+      </c>
+      <c r="N27" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>75.27</v>
+        <v>74.75</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>75.23999999999999</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="R27" s="23" t="n">
-        <v>-2.86</v>
+        <v>74.3</v>
+      </c>
+      <c r="R27" s="25" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21.31</v>
+        <v>20.99</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.89</v>
+        <v>20.65</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.54</v>
+        <v>20.37</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.52</v>
+        <v>20.46</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.79</v>
+        <v>20.62</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.37</v>
+        <v>20.28</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.1</v>
+        <v>20.12</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.95</v>
+        <v>19.94</v>
       </c>
       <c r="K28" s="18" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="N28" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Q28" s="22" t="n">
         <v>20.3</v>
       </c>
-      <c r="L28" s="19" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="Q28" s="22" t="n">
-        <v>20.26</v>
-      </c>
       <c r="R28" s="23" t="n">
-        <v>-1.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>79.63</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>77.88</v>
+        <v>78.14</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>76.42</v>
+        <v>75.92</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>76.22</v>
+        <v>77.38</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>77.38</v>
+        <v>78.27</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>75.63</v>
+        <v>75.62</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>74.47</v>
+        <v>74.73</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>73.88</v>
+        <v>72.97</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>75.44</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>73.97</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>72.22</v>
+        <v>69.56</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>75.59999999999999</v>
+        <v>75.13</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>75.56999999999999</v>
+        <v>74.64</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>75.05</v>
+        <v>76.5</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>-1.38</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>29.6</v>
+        <v>29.55</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>28.3</v>
+        <v>28.31</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>27.21</v>
+        <v>27.27</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.35</v>
+        <v>27.81</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>28.07</v>
+        <v>28.29</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>26.77</v>
+        <v>27.05</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>26.05</v>
+        <v>26.57</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>25.47</v>
+        <v>25.81</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>26.49</v>
+        <v>26.57</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>25.4</v>
+        <v>25.53</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
+        <v>24.29</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>26.68</v>
+        <v>26.86</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>26.59</v>
+        <v>26.67</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="R30" s="25" t="n">
-        <v>1.53</v>
+        <v>27.32</v>
+      </c>
+      <c r="R30" s="23" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.14</v>
+        <v>48.29</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>48.4</v>
+        <v>47.89</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.78</v>
+        <v>47.55</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.69</v>
+        <v>47.77</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>48.19</v>
+        <v>47.91</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.45</v>
+        <v>47.51</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>46.95</v>
+        <v>47.37</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>46.71</v>
+        <v>47.11</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.36</v>
+        <v>47.33</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.74</v>
+        <v>46.99</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46</v>
+        <v>46.59</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
         <v>47.43</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.42</v>
+        <v>47.36</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.2</v>
+        <v>47.64</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>-1.46</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>129.28</v>
+        <v>126.4</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>126.88</v>
+        <v>125.1</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>124.87</v>
+        <v>124.01</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>125</v>
+        <v>124.53</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>126.4</v>
+        <v>125.07</v>
       </c>
       <c r="H32" s="16" t="n">
+        <v>123.77</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>123.23</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>122.47</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>123.29</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O32" s="21" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="P32" s="21" t="n">
+        <v>123.39</v>
+      </c>
+      <c r="Q32" s="22" t="n">
         <v>124</v>
       </c>
-      <c r="I32" s="17" t="n">
-        <v>122.6</v>
-      </c>
-      <c r="J32" s="17" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>123.53</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>121.52</v>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>119.12</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O32" s="21" t="n">
-        <v>123.86</v>
-      </c>
-      <c r="P32" s="21" t="n">
-        <v>123.72</v>
-      </c>
-      <c r="Q32" s="22" t="n">
-        <v>123.6</v>
-      </c>
       <c r="R32" s="23" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>60.02</v>
+        <v>56.92</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>57.72</v>
+        <v>55.52</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>55.79</v>
+        <v>54.34</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>55.8</v>
+        <v>54.88</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>57.2</v>
+        <v>55.47</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>54.9</v>
+        <v>54.07</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>53.5</v>
+        <v>53.48</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>52.6</v>
+        <v>52.67</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>54.51</v>
+        <v>53.56</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>52.58</v>
+        <v>52.38</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="N33" s="20" t="inlineStr">
+        <v>50.98</v>
+      </c>
+      <c r="N33" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>54.79</v>
+        <v>53.87</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>54.69</v>
+        <v>53.67</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>-1.36</v>
+        <v>54.3</v>
+      </c>
+      <c r="R33" s="25" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>23.97</v>
+        <v>24.01</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.56</v>
+        <v>23.51</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.22</v>
+        <v>23.09</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.24</v>
+        <v>23.33</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.48</v>
+        <v>23.51</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.07</v>
+        <v>23.01</v>
       </c>
       <c r="I34" s="17" t="n">
         <v>22.83</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.66</v>
+        <v>22.51</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>22.99</v>
+        <v>22.81</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.65</v>
+        <v>22.39</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>22.24</v>
+        <v>21.89</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>23.05</v>
+        <v>22.93</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.02</v>
+        <v>22.85</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
       <c r="R34" s="23" t="n">
-        <v>-1.54</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.03</v>
+        <v>25.89</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.65</v>
+        <v>25.54</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.34</v>
+        <v>25.24</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.4</v>
+        <v>25.36</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.6</v>
+        <v>25.51</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.22</v>
+        <v>25.16</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.02</v>
+        <v>25.01</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>24.84</v>
+        <v>24.81</v>
       </c>
       <c r="K35" s="18" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N35" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="n">
         <v>25.12</v>
       </c>
-      <c r="L35" s="19" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="N35" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>25.19</v>
-      </c>
       <c r="P35" s="21" t="n">
-        <v>25.15</v>
+        <v>25.07</v>
       </c>
       <c r="Q35" s="22" t="n">
         <v>25.2</v>
       </c>
-      <c r="R35" s="25" t="n">
-        <v>0.32</v>
+      <c r="R35" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.93</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.69</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.49</v>
+        <v>8.31</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.470000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.630000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.390000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="I36" s="17" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N36" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="P36" s="21" t="n">
         <v>8.23</v>
       </c>
-      <c r="J36" s="17" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="L36" s="19" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="P36" s="21" t="n">
-        <v>8.369999999999999</v>
-      </c>
       <c r="Q36" s="22" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="R36" s="23" t="n">
-        <v>-2.12</v>
+        <v>8.25</v>
+      </c>
+      <c r="R36" s="25" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>34.81</v>
+        <v>33.63</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>33.89</v>
+        <v>32.87</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>33.12</v>
+        <v>32.23</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>33.08</v>
+        <v>32.19</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>33.66</v>
+        <v>32.67</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>32.74</v>
+        <v>31.91</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>32.16</v>
+        <v>31.43</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.82</v>
+        <v>31.15</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>32.6</v>
+        <v>31.81</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.83</v>
+        <v>31.17</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.91</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
+        <v>30.41</v>
+      </c>
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>32.71</v>
+        <v>31.89</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>32.67</v>
+        <v>31.87</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="R37" s="23" t="n">
-        <v>-0.73</v>
+        <v>31.7</v>
+      </c>
+      <c r="R37" s="25" t="n">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>180.16</v>
+        <v>176.59</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>176.66</v>
+        <v>173.69</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>173.73</v>
+        <v>171.26</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>173.33</v>
+        <v>172</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>175.67</v>
+        <v>173.4</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>172.17</v>
+        <v>170.5</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>169.83</v>
+        <v>169.1</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>168.67</v>
+        <v>167.6</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>171.77</v>
+        <v>169.64</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>168.84</v>
+        <v>167.21</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>165.34</v>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
+        <v>164.31</v>
+      </c>
+      <c r="N38" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>172.1</v>
+        <v>170.18</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>172.04</v>
+        <v>169.86</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>171</v>
-      </c>
-      <c r="R38" s="23" t="n">
-        <v>-0.87</v>
+        <v>170.6</v>
+      </c>
+      <c r="R38" s="25" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="39">
@@ -3022,7 +3022,7 @@
       <c r="M39" s="19" t="n">
         <v>12.6</v>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="N39" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="Q39" s="22" t="n">
         <v>12.6</v>
       </c>
-      <c r="R39" s="25" t="n">
+      <c r="R39" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22.66</v>
+        <v>22.1</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>21.82</v>
+        <v>21.3</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>21.12</v>
+        <v>20.63</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>21.18</v>
+        <v>20.87</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.66</v>
+        <v>21.24</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>20.82</v>
+        <v>20.44</v>
       </c>
       <c r="I40" s="17" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="N40" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O40" s="21" t="n">
         <v>20.34</v>
       </c>
-      <c r="J40" s="17" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O40" s="21" t="n">
-        <v>20.77</v>
-      </c>
       <c r="P40" s="21" t="n">
-        <v>20.71</v>
+        <v>20.25</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>-1.8</v>
+        <v>20.5</v>
+      </c>
+      <c r="R40" s="25" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>187.4</v>
+        <v>190.31</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>185.3</v>
+        <v>186.41</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>183.54</v>
+        <v>183.14</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>183.57</v>
+        <v>182.83</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>184.83</v>
+        <v>185.37</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>182.73</v>
+        <v>181.47</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>181.47</v>
+        <v>178.93</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>180.63</v>
+        <v>177.57</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>182.36</v>
+        <v>180.96</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>180.6</v>
+        <v>177.69</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
+        <v>173.79</v>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>182.63</v>
+        <v>181.36</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>182.53</v>
+        <v>181.26</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>-0.76</v>
+        <v>180.3</v>
+      </c>
+      <c r="R41" s="25" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>36.66</v>
+        <v>37.17</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.4</v>
+        <v>36.61</v>
       </c>
       <c r="E42" s="14" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O42" s="21" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="P42" s="21" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="Q42" s="22" t="n">
         <v>36.18</v>
       </c>
-      <c r="F42" s="15" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>36.33</v>
-      </c>
-      <c r="H42" s="16" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="I42" s="17" t="n">
-        <v>35.89</v>
-      </c>
-      <c r="J42" s="17" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="L42" s="19" t="n">
-        <v>35.82</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="P42" s="21" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="Q42" s="22" t="n">
-        <v>35.98</v>
-      </c>
       <c r="R42" s="23" t="n">
-        <v>-0.61</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.74</v>
+        <v>28.71</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>28.1</v>
+        <v>28.15</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>27.56</v>
+        <v>27.68</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.74</v>
+        <v>27.8</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>28.04</v>
+        <v>28.08</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.4</v>
+        <v>27.52</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>27.1</v>
+        <v>27.24</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.76</v>
+        <v>26.96</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>27.2</v>
+        <v>27.36</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>26.66</v>
+        <v>26.89</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="N43" s="24" t="inlineStr">
+        <v>26.33</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>27.33</v>
+        <v>27.46</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>27.25</v>
+        <v>27.41</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>27.44</v>
-      </c>
-      <c r="R43" s="25" t="n">
-        <v>1.4</v>
+        <v>27.52</v>
+      </c>
+      <c r="R43" s="23" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.04</v>
+        <v>26.33</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.88</v>
+        <v>26.09</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.74</v>
+        <v>25.89</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.83</v>
+        <v>25.94</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>25.89</v>
+        <v>26.06</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.73</v>
+        <v>25.82</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.67</v>
+        <v>25.7</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.57</v>
+        <v>25.58</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.66</v>
+        <v>25.75</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.52</v>
+        <v>25.55</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>25.36</v>
-      </c>
-      <c r="N44" s="24" t="inlineStr">
+        <v>25.31</v>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.67</v>
+        <v>25.77</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="R44" s="25" t="n">
-        <v>0.55</v>
+        <v>25.82</v>
+      </c>
+      <c r="R44" s="23" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.66</v>
+        <v>7.73</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.53</v>
+        <v>7.56</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.42</v>
+        <v>7.41</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.42</v>
+        <v>7.48</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.37</v>
+        <v>7.38</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.35</v>
+        <v>7.32</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.24</v>
+        <v>7.17</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
         <v>7.36</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.34</v>
+        <v>7.41</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.26</v>
+        <v>12.23</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>12.05</v>
+        <v>12.03</v>
       </c>
       <c r="E46" s="14" t="n">
         <v>11.87</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.85</v>
+        <v>11.92</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.99</v>
+        <v>12.01</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.78</v>
+        <v>11.81</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.64</v>
+        <v>11.72</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.57</v>
+        <v>11.61</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.76</v>
+        <v>11.75</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.58</v>
+        <v>11.59</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>11.37</v>
+        <v>11.39</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="P46" s="21" t="n">
         <v>11.77</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.71</v>
+        <v>11.82</v>
       </c>
       <c r="R46" s="23" t="n">
-        <v>-1.93</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>195.44</v>
+        <v>196.02</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>192.94</v>
+        <v>192.92</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>190.85</v>
+        <v>190.32</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>191.3</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>192.6</v>
+        <v>192.7</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>190.1</v>
+        <v>189.6</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>188.8</v>
+        <v>188.2</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>187.6</v>
+        <v>186.5</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>189.45</v>
+        <v>188.58</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>187.35</v>
+        <v>185.98</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>184.85</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
+        <v>182.88</v>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>189.87</v>
+        <v>189.21</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>189.64</v>
+        <v>188.82</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>190</v>
+        <v>189.9</v>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>46.81</v>
+        <v>45.62</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>45.85</v>
+        <v>44.84</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>45.05</v>
+        <v>44.19</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>45.01</v>
+        <v>44.13</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>45.61</v>
+        <v>44.63</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>44.65</v>
+        <v>43.85</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>44.05</v>
+        <v>43.35</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>43.69</v>
+        <v>43.07</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>44.51</v>
+        <v>43.75</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>43.71</v>
+        <v>43.1</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="N48" s="20" t="inlineStr">
+        <v>42.32</v>
+      </c>
+      <c r="N48" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>44.62</v>
+        <v>43.83</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>44.59</v>
+        <v>43.81</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="R48" s="23" t="n">
-        <v>-1.9</v>
+        <v>43.62</v>
+      </c>
+      <c r="R48" s="25" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>32.85</v>
+        <v>32.32</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>32.35</v>
+        <v>32</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>31.93</v>
+        <v>31.73</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>31.91</v>
+        <v>31.87</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>32.23</v>
+        <v>31.99</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.73</v>
+        <v>31.67</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.41</v>
+        <v>31.55</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.23</v>
+        <v>31.35</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.65</v>
+        <v>31.55</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>31.23</v>
+        <v>31.28</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.73</v>
-      </c>
-      <c r="N49" s="24" t="inlineStr">
+        <v>30.96</v>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>31.71</v>
+        <v>31.62</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>31.69</v>
+        <v>31.58</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>31.6</v>
+        <v>31.74</v>
       </c>
       <c r="R49" s="23" t="n">
-        <v>-0.44</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.85</v>
+        <v>12.69</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="E50" s="14" t="n">
         <v>12.34</v>
       </c>
       <c r="F50" s="15" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O50" s="21" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="P50" s="21" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="Q50" s="22" t="n">
         <v>12.35</v>
       </c>
-      <c r="G50" s="15" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="H50" s="16" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="I50" s="17" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O50" s="21" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="P50" s="21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q50" s="22" t="n">
-        <v>12.18</v>
-      </c>
       <c r="R50" s="23" t="n">
-        <v>-1.06</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>59.93</v>
+        <v>60.18</v>
       </c>
       <c r="D51" s="13" t="n">
         <v>59.08</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>58.36</v>
+        <v>58.16</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.43</v>
+        <v>58.7</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>58.92</v>
+        <v>59.1</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>58.07</v>
+        <v>58</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>57.58</v>
+        <v>57.6</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>57.22</v>
+        <v>56.9</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.89</v>
+        <v>57.54</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>57.17</v>
+        <v>56.62</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>56.32</v>
+        <v>55.52</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>58.01</v>
+        <v>57.81</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.95</v>
+        <v>57.63</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>57.95</v>
+        <v>58.3</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>-0.52</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.74</v>
+        <v>22.55</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.4</v>
+        <v>22.26</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.12</v>
+        <v>22.02</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.15</v>
+        <v>22.09</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.34</v>
+        <v>22.23</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22</v>
+        <v>21.94</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.81</v>
+        <v>21.8</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.66</v>
+        <v>21.65</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.92</v>
+        <v>21.85</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.64</v>
+        <v>21.61</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="N52" s="20" t="inlineStr">
+        <v>21.32</v>
+      </c>
+      <c r="N52" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>21.98</v>
+        <v>21.91</v>
       </c>
       <c r="P52" s="21" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="Q52" s="22" t="n">
         <v>21.95</v>
       </c>
-      <c r="Q52" s="22" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="R52" s="23" t="n">
-        <v>-0.72</v>
+      <c r="R52" s="25" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="53">
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="F53" s="15" t="n">
         <v>5.08</v>
@@ -3873,39 +3873,39 @@
         <v>5.11</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="I53" s="17" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O53" s="21" t="n">
         <v>5.02</v>
       </c>
-      <c r="J53" s="17" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="K53" s="18" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="N53" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O53" s="21" t="n">
-        <v>5.05</v>
-      </c>
       <c r="P53" s="21" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="R53" s="25" t="n">
-        <v>0.2</v>
+        <v>5.06</v>
+      </c>
+      <c r="R53" s="23" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.98</v>
+        <v>18.34</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.27</v>
+        <v>17.89</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>17.67</v>
+        <v>17.51</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>17.91</v>
+        <v>17.57</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.22</v>
+        <v>17.81</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.51</v>
+        <v>17.36</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.2</v>
+        <v>17.12</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>16.8</v>
+        <v>16.91</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.28</v>
+        <v>17.26</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.68</v>
+        <v>16.88</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>15.97</v>
+        <v>16.43</v>
       </c>
       <c r="N54" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.42</v>
+        <v>17.33</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.33</v>
+        <v>17.29</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.59</v>
+        <v>17.32</v>
       </c>
       <c r="R54" s="25" t="n">
-        <v>2.27</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>97.87</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>95.56999999999999</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>93.64</v>
+        <v>92.67</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>93.42</v>
+        <v>93.17</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>94.93000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>92.63</v>
+        <v>92.33</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>91.12</v>
+        <v>91.67</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>90.33</v>
+        <v>90.83</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>92.36</v>
+        <v>91.83</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>90.43000000000001</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>88.13</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="N55" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>92.58</v>
+        <v>92.14</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>92.54000000000001</v>
+        <v>91.95</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>91.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="R55" s="23" t="n">
-        <v>-2.34</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.7</v>
+        <v>17.41</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>17.18</v>
+        <v>16.98</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>16.75</v>
+        <v>16.62</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>16.73</v>
+        <v>16.61</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>17.05</v>
+        <v>16.88</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.53</v>
+        <v>16.45</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.21</v>
+        <v>16.18</v>
       </c>
       <c r="J56" s="17" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="K56" s="18" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="L56" s="19" t="n">
         <v>16.01</v>
       </c>
-      <c r="K56" s="18" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>16.02</v>
-      </c>
       <c r="M56" s="19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
+        <v>15.58</v>
+      </c>
+      <c r="N56" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.51</v>
+        <v>16.43</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.49</v>
+        <v>16.41</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="R56" s="23" t="n">
-        <v>-2.38</v>
+        <v>16.35</v>
+      </c>
+      <c r="R56" s="25" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="57">
@@ -4106,19 +4106,19 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>20.94</v>
+        <v>21.08</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.81</v>
+        <v>20.86</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.7</v>
+        <v>20.67</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.69</v>
+        <v>20.78</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.77</v>
+        <v>20.86</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>20.64</v>
@@ -4127,33 +4127,33 @@
         <v>20.56</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.51</v>
+        <v>20.42</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20.63</v>
+        <v>20.55</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>20.52</v>
+        <v>20.36</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>20.39</v>
+        <v>20.14</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.64</v>
+        <v>20.6</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.64</v>
+        <v>20.57</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>-0.58</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="58">
@@ -4168,53 +4168,53 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.47</v>
+        <v>22.46</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.29</v>
+        <v>22.26</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.14</v>
+        <v>22.1</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.19</v>
+        <v>22.18</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.09</v>
+        <v>22.06</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>22.01</v>
+        <v>21.98</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>21.91</v>
+        <v>21.86</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>22.04</v>
+        <v>21.98</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>21.89</v>
+        <v>21.82</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="N58" s="24" t="inlineStr">
+        <v>21.62</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>22.07</v>
+        <v>22.03</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>22.05</v>
+        <v>22</v>
       </c>
       <c r="Q58" s="22" t="n">
         <v>22.1</v>
       </c>
-      <c r="R58" s="25" t="n">
+      <c r="R58" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.04</v>
+        <v>28.66</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>27.82</v>
+        <v>28.18</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.63</v>
+        <v>27.77</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.69</v>
+        <v>27.95</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27.79</v>
+        <v>28.15</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.57</v>
+        <v>27.67</v>
       </c>
       <c r="I59" s="17" t="n">
         <v>27.47</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.35</v>
+        <v>27.19</v>
       </c>
       <c r="K59" s="18" t="n">
         <v>27.51</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.32</v>
+        <v>27.1</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="N59" s="24" t="inlineStr">
+        <v>26.62</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.55</v>
+        <v>27.61</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.53</v>
+        <v>27.54</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.58</v>
-      </c>
-      <c r="R59" s="25" t="n">
-        <v>0.44</v>
+        <v>27.74</v>
+      </c>
+      <c r="R59" s="23" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>45.98</v>
+        <v>44.55</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>45.04</v>
+        <v>44.15</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>44.25</v>
+        <v>43.81</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>44.33</v>
+        <v>44.03</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>44.87</v>
+        <v>44.17</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>43.93</v>
+        <v>43.77</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>43.39</v>
+        <v>43.63</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>42.99</v>
+        <v>43.37</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>43.73</v>
+        <v>43.59</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>42.94</v>
+        <v>43.25</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
+        <v>42.85</v>
+      </c>
+      <c r="N60" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>43.86</v>
+        <v>43.69</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>43.8</v>
+        <v>43.62</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="R60" s="23" t="n">
-        <v>-1.93</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>18.73</v>
+        <v>18.91</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.48</v>
+        <v>18.53</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.27</v>
+        <v>18.22</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.25</v>
+        <v>18.43</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.41</v>
+        <v>18.55</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.16</v>
+        <v>18.17</v>
       </c>
       <c r="I61" s="17" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J61" s="17" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="K61" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="J61" s="17" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="K61" s="18" t="n">
-        <v>18.13</v>
-      </c>
       <c r="L61" s="19" t="n">
-        <v>17.93</v>
+        <v>17.69</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.68</v>
+        <v>17.31</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.16</v>
+        <v>18.1</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.15</v>
+        <v>18.03</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>18.08</v>
+        <v>18.3</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>-0.39</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="D62" s="13" t="n">
         <v>15.19</v>
       </c>
-      <c r="D62" s="13" t="n">
-        <v>15.06</v>
-      </c>
       <c r="E62" s="14" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="K62" s="18" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O62" s="21" t="n">
         <v>14.95</v>
       </c>
-      <c r="F62" s="15" t="n">
-        <v>15.01</v>
-      </c>
-      <c r="G62" s="15" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="H62" s="16" t="n">
+      <c r="P62" s="21" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="Q62" s="22" t="n">
         <v>14.93</v>
       </c>
-      <c r="I62" s="17" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="J62" s="17" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K62" s="18" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="N62" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O62" s="21" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="P62" s="21" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="Q62" s="22" t="n">
-        <v>14.96</v>
-      </c>
       <c r="R62" s="25" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.56</v>
+        <v>24.51</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.25</v>
+        <v>24.17</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>23.99</v>
+        <v>23.89</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>23.97</v>
+        <v>24.07</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.17</v>
+        <v>24.18</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.86</v>
+        <v>23.84</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.66</v>
+        <v>23.73</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.55</v>
+        <v>23.5</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.82</v>
+        <v>23.69</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.56</v>
+        <v>23.41</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.25</v>
+        <v>23.07</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.85</v>
+        <v>23.78</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.84</v>
+        <v>23.72</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>23.77</v>
+        <v>23.95</v>
       </c>
       <c r="R63" s="23" t="n">
-        <v>-1</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="64">
@@ -4540,53 +4540,53 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="D64" s="13" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F64" s="15" t="n">
         <v>7.08</v>
       </c>
-      <c r="E64" s="14" t="n">
+      <c r="G64" s="15" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="H64" s="16" t="n">
         <v>7.04</v>
       </c>
-      <c r="F64" s="15" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="G64" s="15" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="H64" s="16" t="n">
+      <c r="I64" s="17" t="n">
         <v>7.03</v>
       </c>
-      <c r="I64" s="17" t="n">
+      <c r="J64" s="17" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K64" s="18" t="n">
         <v>7.02</v>
       </c>
-      <c r="J64" s="17" t="n">
+      <c r="L64" s="19" t="n">
         <v>6.98</v>
       </c>
-      <c r="K64" s="18" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>6.97</v>
-      </c>
       <c r="M64" s="19" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="N64" s="24" t="inlineStr">
+        <v>6.93</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O64" s="21" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="P64" s="21" t="n">
         <v>7.02</v>
       </c>
-      <c r="P64" s="21" t="n">
-        <v>7.01</v>
-      </c>
       <c r="Q64" s="22" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="R64" s="25" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="R64" s="23" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -4602,53 +4602,53 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="F65" s="15" t="n">
         <v>4.83</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="J65" s="17" t="n">
         <v>4.74</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="M65" s="19" t="n">
         <v>4.67</v>
       </c>
       <c r="N65" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P65" s="21" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q65" s="22" t="n">
         <v>4.8</v>
       </c>
-      <c r="P65" s="21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q65" s="22" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="R65" s="25" t="n">
+      <c r="R65" s="23" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="I66" s="17" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="J66" s="17" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K66" s="18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N66" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O66" s="21" t="n">
         <v>4.35</v>
       </c>
-      <c r="J66" s="17" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="K66" s="18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O66" s="21" t="n">
-        <v>4.41</v>
-      </c>
       <c r="P66" s="21" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="R66" s="23" t="n">
-        <v>-1.57</v>
+        <v>4.33</v>
+      </c>
+      <c r="R66" s="25" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>64.72</v>
+        <v>64.5</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>64.12</v>
+        <v>63.85</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>63.62</v>
+        <v>63.31</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>63.62</v>
+        <v>63.57</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>63.98</v>
+        <v>63.83</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>63.38</v>
+        <v>63.18</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>63.02</v>
+        <v>62.92</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>62.78</v>
+        <v>62.53</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>63.28</v>
+        <v>62.94</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>62.78</v>
+        <v>62.4</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="N67" s="20" t="inlineStr">
+        <v>61.75</v>
+      </c>
+      <c r="N67" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>63.36</v>
+        <v>63.09</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>63.33</v>
+        <v>62.99</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>63.25</v>
+        <v>63.3</v>
       </c>
       <c r="R67" s="23" t="n">
-        <v>-1.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>66.06</v>
+        <v>66.13</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>65.16</v>
+        <v>64.78</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>64.40000000000001</v>
+        <v>63.65</v>
       </c>
       <c r="F68" s="15" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="G68" s="15" t="n">
         <v>64.5</v>
       </c>
-      <c r="G68" s="15" t="n">
-        <v>65</v>
-      </c>
       <c r="H68" s="16" t="n">
-        <v>64.09999999999999</v>
+        <v>63.15</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>63.6</v>
+        <v>62.35</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>63.2</v>
+        <v>61.8</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>63.9</v>
+        <v>62.9</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>63.14</v>
+        <v>61.77</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>62.24</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
+        <v>60.42</v>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>64.03</v>
+        <v>63.08</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>63.97</v>
+        <v>63</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>64</v>
-      </c>
-      <c r="R68" s="23" t="n">
-        <v>-0.7</v>
+        <v>62.9</v>
+      </c>
+      <c r="R68" s="25" t="n">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="69">
@@ -4850,53 +4850,53 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>80.44</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>78.19</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>76.31</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>76.75</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>75.65000000000001</v>
+        <v>75.95</v>
       </c>
       <c r="I69" s="17" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="J69" s="17" t="n">
         <v>74.5</v>
       </c>
-      <c r="J69" s="17" t="n">
-        <v>73.40000000000001</v>
-      </c>
       <c r="K69" s="18" t="n">
-        <v>75.05</v>
+        <v>75.37</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>73.16</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>70.91</v>
-      </c>
-      <c r="N69" s="24" t="inlineStr">
+        <v>72.7</v>
+      </c>
+      <c r="N69" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>75.44</v>
+        <v>75.72</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>75.22</v>
+        <v>75.48</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="R69" s="25" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="R69" s="23" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>120.25</v>
+        <v>118.4</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>117.25</v>
+        <v>116.3</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>114.74</v>
+        <v>114.54</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>114.93</v>
+        <v>114.3</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>116.67</v>
+        <v>115.7</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>113.67</v>
+        <v>113.6</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>111.93</v>
+        <v>112.2</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>110.67</v>
+        <v>111.5</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>113.06</v>
+        <v>113.36</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>110.55</v>
+        <v>111.6</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>107.55</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
+        <v>109.5</v>
+      </c>
+      <c r="N70" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>113.48</v>
+        <v>113.56</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>113.29</v>
+        <v>113.53</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="R70" s="23" t="n">
-        <v>-1.57</v>
+        <v>112.9</v>
+      </c>
+      <c r="R70" s="25" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="E71" s="14" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="F71" s="15" t="n">
         <v>23.33</v>
       </c>
-      <c r="D71" s="13" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="E71" s="14" t="n">
-        <v>22.94</v>
-      </c>
-      <c r="F71" s="15" t="n">
-        <v>22.93</v>
-      </c>
       <c r="G71" s="15" t="n">
-        <v>23.06</v>
+        <v>23.68</v>
       </c>
       <c r="H71" s="16" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="J71" s="17" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="K71" s="18" t="n">
         <v>22.85</v>
       </c>
-      <c r="I71" s="17" t="n">
-        <v>22.72</v>
-      </c>
-      <c r="J71" s="17" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="K71" s="18" t="n">
-        <v>22.83</v>
-      </c>
       <c r="L71" s="19" t="n">
-        <v>22.65</v>
+        <v>22.29</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="N71" s="24" t="inlineStr">
+        <v>21.63</v>
+      </c>
+      <c r="N71" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>22.85</v>
+        <v>22.96</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>22.84</v>
+        <v>22.9</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>22.79</v>
+        <v>22.99</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>-0.31</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>18.16</v>
+        <v>19.14</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18</v>
+        <v>18.54</v>
       </c>
       <c r="E72" s="14" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="F72" s="15" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="G72" s="15" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="H72" s="16" t="n">
         <v>17.86</v>
       </c>
-      <c r="F72" s="15" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="G72" s="15" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="H72" s="16" t="n">
+      <c r="I72" s="17" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="J72" s="17" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="K72" s="18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L72" s="19" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M72" s="19" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N72" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O72" s="21" t="n">
         <v>17.8</v>
       </c>
-      <c r="I72" s="17" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J72" s="17" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="K72" s="18" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="L72" s="19" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="M72" s="19" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="N72" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O72" s="21" t="n">
-        <v>17.79</v>
-      </c>
       <c r="P72" s="21" t="n">
-        <v>17.79</v>
+        <v>17.75</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.76</v>
+        <v>17.84</v>
       </c>
       <c r="R72" s="23" t="n">
-        <v>-0.5</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>235.96</v>
+        <v>229.41</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>231.66</v>
+        <v>226.81</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>228.05</v>
+        <v>224.63</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>227.77</v>
+        <v>224.6</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>230.53</v>
+        <v>226.2</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>226.23</v>
+        <v>223.6</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>223.47</v>
+        <v>222</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>221.93</v>
+        <v>221</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>225.65</v>
+        <v>223.17</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>222.04</v>
+        <v>220.99</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>217.74</v>
-      </c>
-      <c r="N73" s="20" t="inlineStr">
+        <v>218.39</v>
+      </c>
+      <c r="N73" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>226.11</v>
+        <v>223.49</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>225.98</v>
+        <v>223.37</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="R73" s="23" t="n">
-        <v>-1.1</v>
+        <v>223</v>
+      </c>
+      <c r="R73" s="25" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.71</v>
+        <v>15.57</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.44</v>
+        <v>15.41</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.21</v>
+        <v>15.27</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.33</v>
+        <v>15.34</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.43</v>
+        <v>15.41</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.16</v>
+        <v>15.25</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.06</v>
+        <v>15.18</v>
       </c>
       <c r="J74" s="17" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="K74" s="18" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="M74" s="19" t="n">
         <v>14.89</v>
       </c>
-      <c r="K74" s="18" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="L74" s="19" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="N74" s="24" t="inlineStr">
+      <c r="N74" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.08</v>
+        <v>15.2</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="R74" s="25" t="n">
-        <v>0.79</v>
+        <v>15.28</v>
+      </c>
+      <c r="R74" s="23" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>37.42</v>
+        <v>37.08</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>36.74</v>
+        <v>36.72</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.17</v>
+        <v>36.42</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>36.33</v>
+        <v>36.54</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>36.67</v>
+        <v>36.7</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>35.99</v>
+        <v>36.34</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>35.65</v>
+        <v>36.18</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>35.31</v>
+        <v>35.98</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>35.79</v>
+        <v>36.22</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>35.22</v>
+        <v>35.92</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>34.54</v>
-      </c>
-      <c r="N75" s="24" t="inlineStr">
+        <v>35.56</v>
+      </c>
+      <c r="N75" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>35.91</v>
+        <v>36.29</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>35.84</v>
+        <v>36.25</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="R75" s="25" t="n">
-        <v>1.29</v>
+        <v>36.38</v>
+      </c>
+      <c r="R75" s="23" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>24.91</v>
+        <v>23.65</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>24.08</v>
+        <v>23.24</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>23.39</v>
+        <v>22.9</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>23.32</v>
+        <v>23.04</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>23.86</v>
+        <v>23.22</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>23.03</v>
+        <v>22.81</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>22.49</v>
+        <v>22.63</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>22.92</v>
+        <v>22.67</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>22.23</v>
+        <v>22.33</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>21.4</v>
+        <v>21.92</v>
       </c>
       <c r="N76" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>23.01</v>
+        <v>22.76</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>22.99</v>
+        <v>22.7</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>22.78</v>
+        <v>22.86</v>
       </c>
       <c r="R76" s="23" t="n">
-        <v>-0.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>44.11</v>
+        <v>42.64</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>42.93</v>
+        <v>41.96</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>41.94</v>
+        <v>41.39</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>41.81</v>
+        <v>41.46</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>42.59</v>
+        <v>41.84</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>41.41</v>
+        <v>41.16</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>40.63</v>
+        <v>40.78</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>40.23</v>
+        <v>40.48</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>41.28</v>
+        <v>41.01</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>40.29</v>
+        <v>40.44</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.11</v>
-      </c>
-      <c r="N77" s="20" t="inlineStr">
+        <v>39.76</v>
+      </c>
+      <c r="N77" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>41.39</v>
+        <v>41.11</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>41.37</v>
+        <v>41.06</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>41.02</v>
+        <v>41.08</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>-2.24</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>5.31</v>
@@ -5417,45 +5417,45 @@
         <v>5.23</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.29</v>
+        <v>5.31</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.16</v>
+        <v>5.18</v>
       </c>
       <c r="J78" s="17" t="n">
         <v>5.11</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
         <v>5.2</v>
       </c>
       <c r="P78" s="21" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="Q78" s="22" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>-0.95</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>18.8</v>
+        <v>18.95</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.48</v>
+        <v>18.59</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.21</v>
+        <v>18.29</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.21</v>
+        <v>18.36</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>18.4</v>
+        <v>18.55</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>18.08</v>
+        <v>18.19</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>17.89</v>
+        <v>18</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>17.76</v>
+        <v>17.83</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>18.03</v>
+        <v>18.09</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>17.76</v>
+        <v>17.79</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>17.44</v>
+        <v>17.43</v>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O79" s="21" t="n">
-        <v>18.07</v>
+        <v>18.15</v>
       </c>
       <c r="P79" s="21" t="n">
-        <v>18.06</v>
+        <v>18.12</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.01</v>
+        <v>18.18</v>
       </c>
       <c r="R79" s="23" t="n">
-        <v>-1.04</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>81.16</v>
+        <v>78.02</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>78.95999999999999</v>
+        <v>77.02</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>77.12</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>76.87</v>
+        <v>76.63</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>78.33</v>
+        <v>77.02</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>76.13</v>
+        <v>76.02</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>74.67</v>
+        <v>75.63</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>73.93000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>75.88</v>
+        <v>75.62</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>74.04000000000001</v>
+        <v>74.78</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>71.84</v>
+        <v>73.78</v>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>76.09</v>
+        <v>75.86</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>76.06</v>
+        <v>75.7</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>75.40000000000001</v>
+        <v>76.25</v>
       </c>
       <c r="R80" s="23" t="n">
-        <v>-3.15</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="81">
@@ -5594,54 +5594,54 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>5.33</v>
+        <v>4.95</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.99</v>
+        <v>4.83</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="F81" s="15" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G81" s="15" t="n">
         <v>4.81</v>
       </c>
-      <c r="G81" s="15" t="n">
-        <v>4.97</v>
-      </c>
       <c r="H81" s="16" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="I81" s="17" t="n">
-        <v>4.47</v>
+        <v>4.62</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>4.29</v>
+        <v>4.57</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>4.51</v>
+        <v>4.67</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>4.23</v>
+        <v>4.57</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N81" s="24" t="inlineStr">
+        <v>4.45</v>
+      </c>
+      <c r="N81" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.54</v>
+        <v>4.68</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R81" s="25" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
+      </c>
+      <c r="R81" s="23" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="82">
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>60.32</v>
+        <v>60.41</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>59.32</v>
+        <v>59.26</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>58.48</v>
+        <v>58.3</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>58.4</v>
+        <v>58.73</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>59.05</v>
+        <v>59.22</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>58.05</v>
+        <v>58.07</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>57.4</v>
+        <v>57.58</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>57.05</v>
+        <v>56.92</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>57.92</v>
+        <v>57.65</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>57.08</v>
+        <v>56.69</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>56.08</v>
+        <v>55.54</v>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>58.02</v>
+        <v>57.9</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>58</v>
+        <v>57.74</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>57.75</v>
+        <v>58.25</v>
       </c>
       <c r="R82" s="23" t="n">
-        <v>-1.03</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="83">
@@ -5718,53 +5718,53 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>38.06</v>
+        <v>37.69</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.64</v>
+        <v>37.39</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.29</v>
+        <v>37.13</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.27</v>
+        <v>37.22</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.53</v>
+        <v>37.36</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>37.11</v>
+        <v>37.06</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.85</v>
+        <v>36.92</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.69</v>
+        <v>36.76</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>37.05</v>
+        <v>36.97</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.7</v>
+        <v>36.71</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.28</v>
+        <v>36.41</v>
       </c>
       <c r="N83" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>37.1</v>
+        <v>37.02</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>37.09</v>
+        <v>36.99</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>37</v>
-      </c>
-      <c r="R83" s="25" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="R83" s="23" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>92.56999999999999</v>
+        <v>93.23</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>91.97</v>
+        <v>92.38</v>
       </c>
       <c r="E84" s="14" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="F84" s="15" t="n">
+        <v>91.93000000000001</v>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="H84" s="16" t="n">
         <v>91.47</v>
       </c>
-      <c r="F84" s="15" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="G84" s="15" t="n">
-        <v>91.95</v>
-      </c>
-      <c r="H84" s="16" t="n">
-        <v>91.34999999999999</v>
-      </c>
       <c r="I84" s="17" t="n">
-        <v>91.09999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>91.13</v>
+        <v>91.19</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>90.63</v>
+        <v>90.47</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="N84" s="24" t="inlineStr">
+        <v>89.62</v>
+      </c>
+      <c r="N84" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>91.26000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.18000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>91.45</v>
-      </c>
-      <c r="R84" s="25" t="n">
-        <v>0.33</v>
+        <v>91.55</v>
+      </c>
+      <c r="R84" s="23" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>17.48</v>
+        <v>16.75</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>17</v>
+        <v>16.54</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.59</v>
+        <v>16.36</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.54</v>
+        <v>16.47</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.86</v>
+        <v>16.55</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.38</v>
+        <v>16.34</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.06</v>
+        <v>16.26</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>15.9</v>
+        <v>16.13</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>16.33</v>
+        <v>16.25</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>15.92</v>
+        <v>16.07</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.44</v>
+        <v>15.86</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.37</v>
+        <v>16.3</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.36</v>
+        <v>16.26</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.22</v>
+        <v>16.4</v>
       </c>
       <c r="R85" s="23" t="n">
-        <v>-0.8</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>125.03</v>
+        <v>125.58</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>123.53</v>
+        <v>123.18</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>122.27</v>
+        <v>121.17</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>122.63</v>
+        <v>121.23</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>123.37</v>
+        <v>122.67</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>121.87</v>
+        <v>120.27</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>121.13</v>
+        <v>118.83</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>120.37</v>
+        <v>117.87</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>121.43</v>
+        <v>119.83</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>120.17</v>
+        <v>117.82</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>118.67</v>
+        <v>115.42</v>
       </c>
       <c r="N86" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>121.71</v>
+        <v>120.14</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>121.55</v>
+        <v>120.02</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>121.9</v>
+        <v>119.8</v>
       </c>
       <c r="R86" s="25" t="n">
-        <v>0.33</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>58.58</v>
+        <v>57.93</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>56.83</v>
+        <v>56.43</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>55.37</v>
+        <v>55.17</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>55.47</v>
+        <v>55.33</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>56.48</v>
+        <v>56.17</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>54.73</v>
+        <v>54.67</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>53.72</v>
+        <v>53.83</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>52.98</v>
+        <v>53.17</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>54.38</v>
+        <v>54.33</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>52.92</v>
+        <v>53.07</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="N87" s="20" t="inlineStr">
+        <v>51.57</v>
+      </c>
+      <c r="N87" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>54.63</v>
+        <v>54.56</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>54.52</v>
+        <v>54.45</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>54.45</v>
+        <v>54.5</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>-2.42</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="88">
@@ -6028,22 +6028,22 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>9.82</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="E88" s="14" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="F88" s="15" t="n">
         <v>9.6</v>
       </c>
-      <c r="F88" s="15" t="n">
-        <v>9.609999999999999</v>
-      </c>
       <c r="G88" s="15" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="I88" s="17" t="n">
         <v>9.49</v>
@@ -6052,30 +6052,30 @@
         <v>9.44</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
       <c r="M88" s="19" t="n">
         <v>9.32</v>
       </c>
-      <c r="N88" s="20" t="inlineStr">
+      <c r="N88" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.550000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q88" s="22" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>16.51</v>
+        <v>16.98</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.18</v>
+        <v>16.27</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>15.91</v>
+        <v>15.67</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>15.87</v>
+        <v>15.89</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>16.09</v>
+        <v>16.21</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>15.76</v>
+        <v>15.5</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.54</v>
+        <v>15.18</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>15.43</v>
+        <v>14.79</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>15.72</v>
+        <v>15.28</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15.45</v>
+        <v>14.68</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="N89" s="20" t="inlineStr">
+        <v>13.97</v>
+      </c>
+      <c r="N89" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>15.75</v>
+        <v>15.42</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>15.75</v>
+        <v>15.33</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="R89" s="23" t="n">
-        <v>-1.32</v>
+        <v>15.56</v>
+      </c>
+      <c r="R89" s="25" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="90">
@@ -6152,39 +6152,39 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>17.88</v>
+        <v>17.99</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.61</v>
+        <v>17.65</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>17.38</v>
+        <v>17.37</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>17.35</v>
+        <v>17.55</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>17.53</v>
+        <v>17.66</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.26</v>
+        <v>17.32</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>17.08</v>
+        <v>17.21</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>16.99</v>
+        <v>16.98</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.23</v>
+        <v>17.17</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>17</v>
+        <v>16.89</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="N90" s="24" t="inlineStr">
+        <v>16.55</v>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
@@ -6193,13 +6193,13 @@
         <v>17.26</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.17</v>
+        <v>17.43</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>-0.17</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>30.62</v>
+        <v>30.87</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.1</v>
+        <v>30.21</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>29.67</v>
+        <v>29.65</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>29.73</v>
+        <v>29.82</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.01</v>
+        <v>30.14</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.49</v>
+        <v>29.48</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>29.21</v>
+        <v>29.16</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>28.97</v>
+        <v>28.82</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.37</v>
+        <v>29.29</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>28.94</v>
+        <v>28.73</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>28.42</v>
+        <v>28.07</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.45</v>
+        <v>29.41</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.41</v>
+        <v>29.34</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.44</v>
+        <v>29.5</v>
       </c>
       <c r="R91" s="23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.47</v>
+        <v>20.62</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>20.08</v>
+        <v>20.14</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.75</v>
+        <v>19.73</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.74</v>
+        <v>19.91</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>19.99</v>
+        <v>20.11</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.6</v>
+        <v>19.63</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>19.35</v>
+        <v>19.43</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>19.21</v>
+        <v>19.15</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>19.54</v>
+        <v>19.47</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>19.21</v>
+        <v>19.06</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>18.82</v>
+        <v>18.58</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>19.58</v>
+        <v>19.57</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>19.57</v>
+        <v>19.5</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>-0.36</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.67</v>
+        <v>26.54</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.29</v>
+        <v>26.18</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.98</v>
+        <v>25.88</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>25.99</v>
+        <v>26.08</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.21</v>
+        <v>26.2</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.83</v>
+        <v>25.84</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.61</v>
+        <v>25.72</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.45</v>
+        <v>25.48</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.76</v>
+        <v>25.68</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.45</v>
+        <v>25.38</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>25.07</v>
+        <v>25.02</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.81</v>
+        <v>25.77</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.79</v>
+        <v>25.71</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.76</v>
+        <v>25.96</v>
       </c>
       <c r="R93" s="23" t="n">
-        <v>-0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>178.3</v>
+        <v>174.74</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>174.9</v>
+        <v>172.74</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>172.05</v>
+        <v>171.06</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>172.87</v>
+        <v>172.17</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>174.53</v>
+        <v>172.83</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>171.13</v>
+        <v>170.83</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>169.47</v>
+        <v>170.17</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>167.73</v>
+        <v>168.83</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>170.15</v>
+        <v>169.94</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>167.3</v>
+        <v>168.26</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>163.9</v>
+        <v>166.26</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>170.77</v>
+        <v>170.46</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>170.41</v>
+        <v>170.1</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>171.2</v>
+        <v>171.5</v>
       </c>
       <c r="R94" s="23" t="n">
-        <v>-1.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="G95" s="15" t="n">
         <v>13.31</v>
       </c>
-      <c r="D95" s="13" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="E95" s="14" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="F95" s="15" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="G95" s="15" t="n">
-        <v>13.18</v>
-      </c>
       <c r="H95" s="16" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J95" s="17" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="K95" s="18" t="n">
         <v>13.05</v>
-      </c>
-      <c r="I95" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="J95" s="17" t="n">
-        <v>12.92</v>
-      </c>
-      <c r="K95" s="18" t="n">
-        <v>13</v>
       </c>
       <c r="L95" s="19" t="n">
         <v>12.89</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="N95" s="24" t="inlineStr">
+        <v>12.7</v>
+      </c>
+      <c r="N95" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.03</v>
+        <v>13.09</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>13.01</v>
+        <v>13.07</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="R95" s="25" t="n">
-        <v>0.08</v>
+        <v>13.14</v>
+      </c>
+      <c r="R95" s="23" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="F96" s="15" t="n">
         <v>19.24</v>
       </c>
-      <c r="D96" s="13" t="n">
-        <v>19.06</v>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="F96" s="15" t="n">
+      <c r="G96" s="15" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="H96" s="16" t="n">
         <v>18.96</v>
       </c>
-      <c r="G96" s="15" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="H96" s="16" t="n">
-        <v>18.87</v>
-      </c>
       <c r="I96" s="17" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.69</v>
+        <v>18.54</v>
       </c>
       <c r="K96" s="18" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="L96" s="19" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="M96" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O96" s="21" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="P96" s="21" t="n">
         <v>18.81</v>
       </c>
-      <c r="L96" s="19" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="M96" s="19" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="N96" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O96" s="21" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="P96" s="21" t="n">
-        <v>18.82</v>
-      </c>
       <c r="Q96" s="22" t="n">
-        <v>18.88</v>
+        <v>19.1</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>-0.37</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.4</v>
+        <v>16.42</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>16.17</v>
+        <v>16.19</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>15.98</v>
+        <v>16</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>16.05</v>
+        <v>15.97</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>16.16</v>
+        <v>16.13</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>15.93</v>
+        <v>15.9</v>
       </c>
       <c r="I97" s="17" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="J97" s="17" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="K97" s="18" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="L97" s="19" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="N97" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O97" s="21" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="P97" s="21" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="Q97" s="22" t="n">
         <v>15.82</v>
       </c>
-      <c r="J97" s="17" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="K97" s="18" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="L97" s="19" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="M97" s="19" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="N97" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O97" s="21" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="P97" s="21" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="Q97" s="22" t="n">
-        <v>15.95</v>
-      </c>
       <c r="R97" s="25" t="n">
-        <v>0.44</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.550000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.32</v>
+        <v>9.41</v>
       </c>
       <c r="H98" s="16" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="I98" s="17" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="J98" s="17" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="K98" s="18" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="L98" s="19" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="M98" s="19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O98" s="21" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="P98" s="21" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="I98" s="17" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="J98" s="17" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="K98" s="18" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="L98" s="19" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="M98" s="19" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O98" s="21" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="P98" s="21" t="n">
-        <v>9.109999999999999</v>
-      </c>
       <c r="Q98" s="22" t="n">
-        <v>9.109999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="R98" s="23" t="n">
-        <v>-1.3</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>25.66</v>
+        <v>25.2</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25.25</v>
+        <v>24.96</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>24.91</v>
+        <v>24.76</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>24.96</v>
+        <v>24.8</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>25.18</v>
+        <v>24.93</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>24.77</v>
+        <v>24.69</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.55</v>
+        <v>24.56</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.36</v>
+        <v>24.45</v>
       </c>
       <c r="K99" s="18" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="L99" s="19" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="M99" s="19" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="N99" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O99" s="21" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="P99" s="21" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="Q99" s="22" t="n">
         <v>24.68</v>
       </c>
-      <c r="L99" s="19" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="M99" s="19" t="n">
-        <v>23.93</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O99" s="21" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="P99" s="21" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="Q99" s="22" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="R99" s="23" t="n">
-        <v>-0.52</v>
+      <c r="R99" s="25" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.85</v>
+        <v>16.44</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>16.38</v>
+        <v>16.13</v>
       </c>
       <c r="E100" s="14" t="n">
-        <v>15.99</v>
+        <v>15.87</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>15.93</v>
+        <v>16.04</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.25</v>
+        <v>16.15</v>
       </c>
       <c r="H100" s="16" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="J100" s="17" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="K100" s="18" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L100" s="19" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="M100" s="19" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O100" s="21" t="n">
         <v>15.78</v>
       </c>
-      <c r="I100" s="17" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="J100" s="17" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="K100" s="18" t="n">
+      <c r="P100" s="21" t="n">
         <v>15.72</v>
       </c>
-      <c r="L100" s="19" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="M100" s="19" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="N100" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O100" s="21" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="P100" s="21" t="n">
-        <v>15.76</v>
-      </c>
       <c r="Q100" s="22" t="n">
-        <v>15.62</v>
+        <v>15.94</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>-2.74</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>30.9</v>
+        <v>31.74</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.22</v>
+        <v>30.64</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.65</v>
+        <v>29.72</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.57</v>
+        <v>29.83</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.03</v>
+        <v>30.45</v>
       </c>
       <c r="H101" s="16" t="n">
         <v>29.35</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>28.89</v>
+        <v>28.73</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>28.67</v>
+        <v>28.25</v>
       </c>
       <c r="K101" s="18" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="L101" s="19" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="M101" s="19" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="N101" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O101" s="21" t="n">
         <v>29.27</v>
       </c>
-      <c r="L101" s="19" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="M101" s="19" t="n">
-        <v>28.02</v>
-      </c>
-      <c r="N101" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O101" s="21" t="n">
-        <v>29.33</v>
-      </c>
       <c r="P101" s="21" t="n">
-        <v>29.32</v>
+        <v>29.19</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>29.12</v>
+        <v>29.22</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>-1.15</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>14.76</v>
+        <v>15.07</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>14.56</v>
+        <v>14.7</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.4</v>
+        <v>14.39</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.44</v>
+        <v>14.47</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>14.54</v>
+        <v>14.65</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.34</v>
+        <v>14.28</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.24</v>
+        <v>14.1</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>14.14</v>
+        <v>13.91</v>
       </c>
       <c r="K102" s="18" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="L102" s="19" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="M102" s="19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N102" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O102" s="21" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="P102" s="21" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="Q102" s="22" t="n">
         <v>14.28</v>
       </c>
-      <c r="L102" s="19" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="M102" s="19" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="N102" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O102" s="21" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="P102" s="21" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="Q102" s="22" t="n">
-        <v>14.34</v>
-      </c>
       <c r="R102" s="25" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>69.31</v>
+        <v>70.06</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>68.16</v>
+        <v>68.11</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>67.2</v>
+        <v>66.47</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>67.06999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>67.83</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>66.68000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>65.92</v>
+        <v>64.5</v>
       </c>
       <c r="J103" s="17" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="K103" s="18" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="L103" s="19" t="n">
+        <v>63.74</v>
+      </c>
+      <c r="M103" s="19" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="N103" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O103" s="21" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="P103" s="21" t="n">
         <v>65.53</v>
       </c>
-      <c r="K103" s="18" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="L103" s="19" t="n">
-        <v>65.59</v>
-      </c>
-      <c r="M103" s="19" t="n">
-        <v>64.44</v>
-      </c>
-      <c r="N103" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O103" s="21" t="n">
-        <v>66.66</v>
-      </c>
-      <c r="P103" s="21" t="n">
-        <v>66.64</v>
-      </c>
       <c r="Q103" s="22" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="R103" s="23" t="n">
-        <v>-1.49</v>
+        <v>65.25</v>
+      </c>
+      <c r="R103" s="25" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.39</v>
+        <v>14.35</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.2</v>
+        <v>14.18</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.04</v>
+        <v>14.03</v>
       </c>
       <c r="F104" s="15" t="n">
         <v>14.07</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>13.98</v>
+        <v>13.99</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>13.88</v>
+        <v>13.9</v>
       </c>
       <c r="J104" s="17" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="L104" s="19" t="n">
         <v>13.79</v>
       </c>
-      <c r="K104" s="18" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="L104" s="19" t="n">
-        <v>13.77</v>
-      </c>
       <c r="M104" s="19" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="N104" s="24" t="inlineStr">
+        <v>13.62</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>13.96</v>
+        <v>13.97</v>
       </c>
       <c r="P104" s="21" t="n">
         <v>13.95</v>
       </c>
       <c r="Q104" s="22" t="n">
-        <v>13.97</v>
+        <v>13.99</v>
       </c>
       <c r="R104" s="23" t="n">
-        <v>-0.21</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>19.8</v>
+        <v>19.75</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>18.21</v>
+        <v>18.47</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>16.88</v>
+        <v>17.4</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.76</v>
+        <v>17.41</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>18.29</v>
+        <v>18.18</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>16.17</v>
+        <v>16.13</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.11</v>
+        <v>15.62</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>15.99</v>
+        <v>16.68</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>14.66</v>
+        <v>15.61</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>13.07</v>
+        <v>14.33</v>
       </c>
       <c r="N105" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>16.41</v>
+        <v>16.84</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>16.11</v>
+        <v>16.78</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>17.23</v>
+        <v>16.63</v>
       </c>
       <c r="R105" s="25" t="n">
-        <v>9.960000000000001</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="L106" s="19" t="n">
         <v>2.33</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="N106" s="20" t="inlineStr">
+        <v>2.29</v>
+      </c>
+      <c r="N106" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R106" s="23" t="n">
-        <v>-2.07</v>
+        <v>2.36</v>
+      </c>
+      <c r="R106" s="25" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>38.49</v>
+        <v>37.82</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>37.69</v>
+        <v>37.4</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>37.02</v>
+        <v>37.05</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>37.2</v>
+        <v>37.12</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>37.6</v>
+        <v>37.34</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.8</v>
+        <v>36.92</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>36.58</v>
+        <v>36.81</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>35.91</v>
+        <v>36.46</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="N107" s="24" t="inlineStr">
+        <v>36.04</v>
+      </c>
+      <c r="N107" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>36.72</v>
+        <v>36.88</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>36.64</v>
+        <v>36.85</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="R107" s="25" t="n">
-        <v>0.55</v>
+        <v>36.9</v>
+      </c>
+      <c r="R107" s="23" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.97</v>
+        <v>7.93</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.82</v>
+        <v>7.79</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.75</v>
+        <v>7.74</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="J108" s="17" t="n">
         <v>7.58</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.73</v>
+        <v>7.71</v>
       </c>
       <c r="L108" s="19" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="M108" s="19" t="n">
         <v>7.41</v>
       </c>
       <c r="N108" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>7.74</v>
+        <v>7.73</v>
       </c>
       <c r="P108" s="21" t="n">
-        <v>7.74</v>
+        <v>7.72</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.69</v>
+        <v>7.72</v>
       </c>
       <c r="R108" s="23" t="n">
-        <v>-0.26</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.42</v>
+        <v>44.09</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>43.96</v>
+        <v>43.71</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.58</v>
+        <v>43.4</v>
       </c>
       <c r="F109" s="15" t="n">
         <v>43.53</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.83</v>
+        <v>43.69</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.37</v>
+        <v>43.31</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>43.07</v>
+        <v>43.15</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>42.91</v>
+        <v>42.93</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>43.32</v>
+        <v>43.18</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>42.94</v>
+        <v>42.87</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>42.48</v>
-      </c>
-      <c r="N109" s="20" t="inlineStr">
+        <v>42.49</v>
+      </c>
+      <c r="N109" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>43.37</v>
+        <v>43.26</v>
       </c>
       <c r="P109" s="21" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="Q109" s="22" t="n">
         <v>43.36</v>
       </c>
-      <c r="Q109" s="22" t="n">
-        <v>43.22</v>
-      </c>
       <c r="R109" s="23" t="n">
-        <v>-1.01</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>67.05</v>
+        <v>67.39</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>65.59999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.38</v>
+        <v>64.45</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.81999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>65.48</v>
+        <v>65.87</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.03</v>
+        <v>64.27</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.37</v>
+        <v>63.73</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>62.58</v>
+        <v>62.67</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>63.57</v>
+        <v>63.55</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>62.35</v>
+        <v>62.21</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N110" s="24" t="inlineStr">
+        <v>60.61</v>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>63.86</v>
+        <v>63.97</v>
       </c>
       <c r="P110" s="21" t="n">
         <v>63.68</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="R110" s="25" t="n">
-        <v>0.79</v>
+        <v>64.8</v>
+      </c>
+      <c r="R110" s="23" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="D111" s="13" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="F111" s="15" t="n">
         <v>10.12</v>
       </c>
-      <c r="E111" s="14" t="n">
+      <c r="G111" s="15" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H111" s="16" t="n">
         <v>10.06</v>
       </c>
-      <c r="F111" s="15" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H111" s="16" t="n">
-        <v>10.03</v>
-      </c>
       <c r="I111" s="17" t="n">
-        <v>9.99</v>
+        <v>10.04</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="K111" s="18" t="n">
         <v>10.03</v>
       </c>
       <c r="L111" s="19" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>9.9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.03</v>
+        <v>10.05</v>
       </c>
       <c r="P111" s="21" t="n">
         <v>10.03</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.01</v>
+        <v>10.09</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>314.13</v>
+        <v>320.19</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>304.53</v>
+        <v>307.59</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>296.49</v>
+        <v>297.03</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>299.27</v>
+        <v>297.6</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>303.73</v>
+        <v>305</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>294.13</v>
+        <v>292.4</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>289.67</v>
+        <v>285</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>284.53</v>
+        <v>279.8</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>291.11</v>
+        <v>289.97</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>283.07</v>
+        <v>279.41</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>273.47</v>
+        <v>266.81</v>
       </c>
       <c r="N112" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>293</v>
+        <v>291.68</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>291.86</v>
+        <v>290.95</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>294.8</v>
+        <v>290.2</v>
       </c>
       <c r="R112" s="25" t="n">
-        <v>1.87</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>227.34</v>
+        <v>225.16</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>224.04</v>
+        <v>221.66</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>221.27</v>
+        <v>218.73</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>220.9</v>
+        <v>219.87</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>223.1</v>
+        <v>221.43</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>219.8</v>
+        <v>217.93</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>217.6</v>
+        <v>216.37</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>216.5</v>
+        <v>214.43</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>219.43</v>
+        <v>216.77</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>216.66</v>
+        <v>213.84</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>213.36</v>
-      </c>
-      <c r="N113" s="20" t="inlineStr">
+        <v>210.34</v>
+      </c>
+      <c r="N113" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>219.74</v>
+        <v>217.49</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>219.68</v>
+        <v>217.04</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>218.7</v>
-      </c>
-      <c r="R113" s="23" t="n">
-        <v>-1.71</v>
+        <v>218.3</v>
+      </c>
+      <c r="R113" s="25" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>649.6900000000001</v>
+        <v>600.25</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>622.6900000000001</v>
+        <v>591.75</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>600.0599999999999</v>
+        <v>584.63</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>589</v>
+        <v>583.5</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>572</v>
+        <v>580.5</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>584.9400000000001</v>
+        <v>579.87</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>562.3099999999999</v>
+        <v>572.75</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>535.3099999999999</v>
-      </c>
-      <c r="N114" s="20" t="inlineStr">
+        <v>564.25</v>
+      </c>
+      <c r="N114" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>588.02</v>
+        <v>582.02</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>587.05</v>
+        <v>580.53</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>-2.18</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.01</v>
+        <v>6.45</v>
       </c>
       <c r="D115" s="13" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E115" s="14" t="n">
         <v>5.83</v>
       </c>
-      <c r="E115" s="14" t="n">
+      <c r="F115" s="15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H115" s="16" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I115" s="17" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="J115" s="17" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="K115" s="18" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L115" s="19" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="M115" s="19" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="N115" s="20" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O115" s="21" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="P115" s="21" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="Q115" s="22" t="n">
         <v>5.68</v>
       </c>
-      <c r="F115" s="15" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="G115" s="15" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="H115" s="16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I115" s="17" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="J115" s="17" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="K115" s="18" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="L115" s="19" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="M115" s="19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N115" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O115" s="21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P115" s="21" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="Q115" s="22" t="n">
-        <v>5.55</v>
-      </c>
       <c r="R115" s="23" t="n">
-        <v>-1.6</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>94</v>
+        <v>93.67</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>92.3</v>
+        <v>92.02</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>90.88</v>
+        <v>90.64</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>90.68000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>91.81999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>90.12</v>
+        <v>90.45</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>88.98</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>88.42</v>
+        <v>88.8</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>89.92</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>88.5</v>
+        <v>88.33</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>86.8</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>90.09</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>90.06</v>
+        <v>89.84</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>89.55</v>
+        <v>91</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>-1.86</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>9.789999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>9.48</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.220000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>9.41</v>
+        <v>9.25</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.1</v>
+        <v>9.02</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="J117" s="17" t="n">
         <v>8.789999999999999</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>8.789999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="N117" s="20" t="inlineStr">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="N117" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>9.07</v>
+        <v>8.98</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="R117" s="23" t="n">
-        <v>-2.17</v>
+        <v>9.01</v>
+      </c>
+      <c r="R117" s="25" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>16.79</v>
+        <v>16.59</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.49</v>
+        <v>16.24</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>16.23</v>
+        <v>15.94</v>
       </c>
       <c r="F118" s="15" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="G118" s="15" t="n">
         <v>16.22</v>
       </c>
-      <c r="G118" s="15" t="n">
-        <v>16.41</v>
-      </c>
       <c r="H118" s="16" t="n">
-        <v>16.11</v>
+        <v>15.87</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>15.92</v>
+        <v>15.73</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.81</v>
+        <v>15.52</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>16.07</v>
+        <v>15.75</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.81</v>
+        <v>15.45</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="N118" s="20" t="inlineStr">
+        <v>15.1</v>
+      </c>
+      <c r="N118" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>16.09</v>
+        <v>15.77</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="R118" s="23" t="n">
-        <v>-1.05</v>
+        <v>15.93</v>
+      </c>
+      <c r="R118" s="25" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.44</v>
+        <v>11.02</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>11.13</v>
+        <v>10.82</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>10.87</v>
+        <v>10.66</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.88</v>
+        <v>10.76</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>11.07</v>
+        <v>10.83</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>10.76</v>
+        <v>10.63</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>10.7</v>
+        <v>10.54</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.44</v>
+        <v>10.38</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="N119" s="20" t="inlineStr">
+        <v>10.18</v>
+      </c>
+      <c r="N119" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>10.74</v>
+        <v>10.59</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>10.72</v>
+        <v>10.56</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="R119" s="23" t="n">
-        <v>-1.56</v>
+        <v>10.69</v>
+      </c>
+      <c r="R119" s="25" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="120">
@@ -8015,51 +8015,51 @@
         <v>12.35</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.14</v>
+        <v>12.11</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>11.96</v>
+        <v>11.91</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>11.99</v>
+        <v>12.03</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.1</v>
+        <v>12.12</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>11.89</v>
+        <v>11.88</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>11.68</v>
+        <v>11.64</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>11.85</v>
+        <v>11.77</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>11.46</v>
+        <v>11.33</v>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.88</v>
+        <v>11.83</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.86</v>
+        <v>11.79</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>11.87</v>
+        <v>11.95</v>
       </c>
       <c r="R120" s="23" t="n">
-        <v>-0.67</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.51</v>
+        <v>7.63</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.3</v>
+        <v>7.15</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>7.12</v>
+        <v>6.74</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>7.13</v>
+        <v>6.94</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.25</v>
+        <v>7.14</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>7.04</v>
+        <v>6.66</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>6.92</v>
+        <v>6.46</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.83</v>
+        <v>6.18</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>7.01</v>
+        <v>6.48</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>6.83</v>
+        <v>6.07</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="N121" s="20" t="inlineStr">
+        <v>5.59</v>
+      </c>
+      <c r="N121" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>7.03</v>
+        <v>6.58</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>7.02</v>
+        <v>6.51</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="R121" s="23" t="n">
-        <v>-1.27</v>
+        <v>6.75</v>
+      </c>
+      <c r="R121" s="25" t="n">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>6.68</v>
+        <v>6.73</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>6.57</v>
+        <v>6.56</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.4</v>
+        <v>6.43</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>6.29</v>
+        <v>6.26</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>6.53</v>
+        <v>6.46</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>6.02</v>
+        <v>5.9</v>
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>6.56</v>
+        <v>6.52</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>6.55</v>
+        <v>6.48</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="R122" s="23" t="n">
-        <v>-1.22</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>31.25</v>
+        <v>29.72</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>29.91</v>
+        <v>28.66</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>28.79</v>
+        <v>27.77</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>28.63</v>
+        <v>27.89</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>29.53</v>
+        <v>28.47</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>28.19</v>
+        <v>27.41</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>27.29</v>
+        <v>26.83</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>26.85</v>
+        <v>26.35</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>28.03</v>
+        <v>27.17</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>26.91</v>
+        <v>26.28</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="N123" s="20" t="inlineStr">
+        <v>25.22</v>
+      </c>
+      <c r="N123" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>28.16</v>
+        <v>27.33</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>28.14</v>
+        <v>27.26</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="R123" s="23" t="n">
-        <v>-1.42</v>
+        <v>27.3</v>
+      </c>
+      <c r="R123" s="25" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>165.89</v>
+        <v>162.68</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>162.19</v>
+        <v>160.28</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>159.09</v>
+        <v>158.27</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>160.53</v>
+        <v>159.6</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>162.07</v>
+        <v>160.4</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>158.37</v>
+        <v>158</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>156.83</v>
+        <v>157.2</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>154.67</v>
+        <v>155.6</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>157.01</v>
+        <v>156.93</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>153.91</v>
+        <v>154.92</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>150.21</v>
-      </c>
-      <c r="N124" s="24" t="inlineStr">
+        <v>152.52</v>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>157.83</v>
+        <v>157.56</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>157.3</v>
+        <v>157.12</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>159</v>
+        <v>158.8</v>
       </c>
       <c r="R124" s="25" t="n">
-        <v>0.38</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>54.67</v>
+        <v>54.15</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>53.42</v>
+        <v>52.7</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>52.38</v>
+        <v>51.48</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>52.3</v>
+        <v>52.25</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>53.1</v>
+        <v>52.75</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>51.85</v>
+        <v>51.3</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>51.05</v>
+        <v>50.8</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>50.6</v>
+        <v>49.85</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>51.68</v>
+        <v>50.67</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>50.63</v>
+        <v>49.45</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>49.38</v>
-      </c>
-      <c r="N125" s="20" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="N125" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>51.81</v>
+        <v>51.04</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>51.77</v>
+        <v>50.78</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>51.5</v>
+        <v>51.75</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>-2.09</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.85</v>
+        <v>14.31</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>14.27</v>
+        <v>13.87</v>
       </c>
       <c r="E126" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="G126" s="15" t="n">
         <v>13.78</v>
       </c>
-      <c r="F126" s="15" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="G126" s="15" t="n">
-        <v>14.1</v>
-      </c>
       <c r="H126" s="16" t="n">
-        <v>13.52</v>
+        <v>13.34</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.14</v>
+        <v>13.07</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.94</v>
+        <v>12.9</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>13.46</v>
+        <v>13.26</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.97</v>
+        <v>12.89</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="N126" s="20" t="inlineStr">
+        <v>12.45</v>
+      </c>
+      <c r="N126" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.51</v>
+        <v>13.31</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="R126" s="23" t="n">
-        <v>-2.49</v>
+        <v>13.25</v>
+      </c>
+      <c r="R126" s="25" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.62</v>
+        <v>15.43</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.48</v>
+        <v>13.94</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.43</v>
+        <v>14.39</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>14.83</v>
+        <v>14.66</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>14.21</v>
+        <v>13.85</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>13.81</v>
+        <v>13.58</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>13.59</v>
+        <v>13.04</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>14.14</v>
+        <v>13.49</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>13.62</v>
+        <v>12.81</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="N127" s="20" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="N127" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>14.18</v>
+        <v>13.55</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>14.02</v>
+        <v>14.12</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>-2.64</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>6.73</v>
+        <v>6.86</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.54</v>
+        <v>6.61</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>6.4</v>
+        <v>6.51</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>6.51</v>
+        <v>6.61</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.21</v>
+        <v>6.26</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="K128" s="18" t="n">
         <v>6.27</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>6.11</v>
+        <v>6.06</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.92</v>
+        <v>5.81</v>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.3</v>
+        <v>6.32</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.3</v>
+        <v>6.41</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>-0.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.42</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.16</v>
+        <v>9.18</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>9.06</v>
+        <v>9</v>
       </c>
       <c r="I129" s="17" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="J129" s="17" t="n">
-        <v>8.779999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.029999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.52</v>
+        <v>8.32</v>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>9.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.050000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>8.970000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="R129" s="23" t="n">
-        <v>-1.21</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>152.35</v>
+        <v>146.56</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>147.25</v>
+        <v>143.06</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>142.98</v>
+        <v>140.13</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>142.4</v>
+        <v>140.33</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>145.8</v>
+        <v>142.37</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>140.7</v>
+        <v>138.87</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>137.3</v>
+        <v>136.83</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>135.6</v>
+        <v>135.37</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>140.12</v>
+        <v>138.17</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>135.85</v>
+        <v>135.24</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>130.75</v>
-      </c>
-      <c r="N130" s="20" t="inlineStr">
+        <v>131.74</v>
+      </c>
+      <c r="N130" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>140.61</v>
+        <v>138.65</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>140.52</v>
+        <v>138.44</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>139</v>
-      </c>
-      <c r="R130" s="23" t="n">
-        <v>-2.39</v>
+        <v>138.3</v>
+      </c>
+      <c r="R130" s="25" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-27</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.49</v>
+        <v>20.53</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.31</v>
+        <v>20.35</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.16</v>
+        <v>20.2</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.25</v>
+        <v>20.18</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.32</v>
+        <v>20.3</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20.07</v>
+        <v>20</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>19.96</v>
+        <v>19.94</v>
       </c>
       <c r="K3" s="18" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L3" s="19" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="M3" s="19" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="N3" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P3" s="21" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="Q3" s="22" t="n">
         <v>20.06</v>
       </c>
-      <c r="L3" s="19" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O3" s="21" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="P3" s="21" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="Q3" s="22" t="n">
-        <v>20.19</v>
-      </c>
       <c r="R3" s="23" t="n">
-        <v>0.7</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="4">
@@ -823,51 +823,51 @@
         <v>12.17</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.81</v>
+        <v>11.78</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.92</v>
+        <v>11.78</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.98</v>
+        <v>11.91</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.72</v>
+        <v>11.57</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>11.58</v>
+        <v>11.49</v>
       </c>
       <c r="K4" s="18" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
         <v>11.69</v>
       </c>
-      <c r="L4" s="19" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.75</v>
-      </c>
       <c r="P4" s="21" t="n">
-        <v>11.71</v>
+        <v>11.68</v>
       </c>
       <c r="Q4" s="22" t="n">
-        <v>11.85</v>
+        <v>11.65</v>
       </c>
       <c r="R4" s="23" t="n">
-        <v>1.2</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15.02</v>
+        <v>14.96</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.82</v>
+        <v>14.83</v>
       </c>
       <c r="E5" s="14" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="L5" s="19" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="M5" s="19" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="N5" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="P5" s="21" t="n">
         <v>14.66</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="L5" s="19" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="M5" s="19" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="P5" s="21" t="n">
-        <v>14.56</v>
-      </c>
       <c r="Q5" s="22" t="n">
-        <v>14.68</v>
+        <v>14.66</v>
       </c>
       <c r="R5" s="23" t="n">
-        <v>1.03</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.68</v>
+        <v>21.76</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.23</v>
+        <v>21.28</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20.85</v>
+        <v>20.87</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>21.1</v>
+        <v>20.87</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.25</v>
+        <v>21.16</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>20.8</v>
+        <v>20.68</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>20.65</v>
+        <v>20.39</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>20.35</v>
+        <v>20.2</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>20.6</v>
+        <v>20.61</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>20.22</v>
+        <v>20.2</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>19.77</v>
+        <v>19.72</v>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>20.72</v>
+        <v>20.66</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>20.63</v>
+        <v>20.64</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>20.95</v>
+        <v>20.57</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>0.58</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>33.9</v>
+        <v>34.05</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.58</v>
+        <v>33.67</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.31</v>
+        <v>33.36</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.47</v>
+        <v>33.41</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>33.59</v>
+        <v>33.61</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.27</v>
+        <v>33.23</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>33.15</v>
+        <v>33.03</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>32.95</v>
+        <v>32.85</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.13</v>
+        <v>33.14</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.86</v>
+        <v>32.83</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.54</v>
-      </c>
-      <c r="N7" s="24" t="inlineStr">
+        <v>32.45</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.21</v>
+        <v>33.2</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.16</v>
+        <v>33.17</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.36</v>
-      </c>
-      <c r="R7" s="25" t="n">
-        <v>-0.06</v>
+        <v>33.2</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.53</v>
+        <v>23.45</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.2</v>
+        <v>23.17</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.93</v>
+        <v>22.94</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>23.1</v>
+        <v>22.96</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.21</v>
+        <v>23.12</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.88</v>
+        <v>22.84</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.77</v>
+        <v>22.68</v>
       </c>
       <c r="J8" s="17" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="L8" s="19" t="n">
         <v>22.55</v>
       </c>
-      <c r="K8" s="18" t="n">
-        <v>22.74</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>22.47</v>
-      </c>
       <c r="M8" s="19" t="n">
-        <v>22.14</v>
+        <v>22.27</v>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>22.83</v>
+        <v>22.82</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="Q8" s="22" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="R8" s="25" t="n">
-        <v>-0.04</v>
+        <v>22.8</v>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>129.36</v>
+        <v>125.59</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>125.06</v>
+        <v>123.99</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>121.45</v>
+        <v>122.65</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>123.57</v>
+        <v>123</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>125.13</v>
+        <v>123.8</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>120.83</v>
+        <v>122.2</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>119.27</v>
+        <v>121.4</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>116.53</v>
+        <v>120.6</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>119.05</v>
+        <v>121.75</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>115.44</v>
+        <v>120.41</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>111.14</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
+        <v>118.81</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>120.11</v>
+        <v>122.04</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>119.38</v>
+        <v>121.88</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="R9" s="23" t="n">
-        <v>3.3</v>
+        <v>122.2</v>
+      </c>
+      <c r="R9" s="25" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>67.31</v>
+        <v>66.5</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>65.76000000000001</v>
+        <v>65.45</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>64.45999999999999</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>65.28</v>
+        <v>64.45</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>65.81999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>64.27</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>63.73</v>
+        <v>63.4</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>62.72</v>
+        <v>63.05</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>63.59</v>
+        <v>63.98</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>62.29</v>
+        <v>63.1</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>60.74</v>
+        <v>62.05</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>63.99</v>
+        <v>64.08</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>63.71</v>
+        <v>64.06</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>64.75</v>
+        <v>63.75</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>2.53</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25.35</v>
+        <v>24.85</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.88</v>
+        <v>24.64</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.49</v>
+        <v>24.46</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.75</v>
+        <v>24.5</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.9</v>
+        <v>24.61</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.43</v>
+        <v>24.4</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.28</v>
+        <v>24.29</v>
       </c>
       <c r="J11" s="17" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="L11" s="19" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="M11" s="19" t="n">
         <v>23.96</v>
       </c>
-      <c r="K11" s="18" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="L11" s="19" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="M11" s="19" t="n">
-        <v>23.36</v>
-      </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.35</v>
+        <v>24.38</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.26</v>
+        <v>24.36</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.59</v>
+        <v>24.39</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>1.44</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.5</v>
+        <v>25.25</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25.04</v>
+        <v>24.94</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.66</v>
+        <v>24.68</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.91</v>
+        <v>24.69</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>25.06</v>
+        <v>24.87</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.6</v>
+        <v>24.56</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.45</v>
+        <v>24.38</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>24.14</v>
+        <v>24.25</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>24.4</v>
+        <v>24.51</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>24.02</v>
+        <v>24.25</v>
       </c>
       <c r="M12" s="19" t="n">
-        <v>23.56</v>
+        <v>23.94</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.52</v>
+        <v>24.55</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.44</v>
+        <v>24.53</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.75</v>
+        <v>24.5</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>1.02</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>43.15</v>
+        <v>42.05</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>41.91</v>
+        <v>41.35</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.87</v>
+        <v>40.77</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>41.55</v>
+        <v>40.85</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>41.97</v>
+        <v>41.23</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.73</v>
+        <v>40.53</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>40.31</v>
+        <v>40.15</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.49</v>
+        <v>39.83</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.17</v>
+        <v>40.37</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.13</v>
+        <v>39.79</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>37.89</v>
+        <v>39.09</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.5</v>
+        <v>40.48</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.27</v>
+        <v>40.43</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>41.14</v>
+        <v>40.46</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>2.34</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.779999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.48</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>8.51</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>8.59</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>8.43</v>
+        <v>8.41</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>8.35</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.27</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K14" s="18" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
         <v>8.4</v>
       </c>
-      <c r="L14" s="19" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="N14" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.42</v>
-      </c>
       <c r="P14" s="21" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>8.42</v>
+        <v>8.4</v>
       </c>
       <c r="R14" s="23" t="n">
-        <v>0.36</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -1505,51 +1505,51 @@
         <v>13.84</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>13.65</v>
+        <v>13.69</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.49</v>
+        <v>13.57</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>13.57</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>13.65</v>
+        <v>13.66</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.46</v>
+        <v>13.51</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.38</v>
+        <v>13.42</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.27</v>
+        <v>13.36</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.38</v>
+        <v>13.48</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.22</v>
+        <v>13.36</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
+        <v>13.21</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.43</v>
+        <v>13.5</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.4</v>
+        <v>13.49</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.5</v>
+        <v>13.48</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>1.28</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="16">
@@ -1564,54 +1564,54 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="I16" s="17" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K16" s="18" t="n">
         <v>3.97</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>3.98</v>
       </c>
       <c r="L16" s="19" t="n">
         <v>3.9</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>4.03</v>
+        <v>3.95</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>1.51</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.5</v>
+        <v>17.63</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.23</v>
+        <v>17.28</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>17</v>
+        <v>16.98</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.11</v>
+        <v>16.97</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.22</v>
+        <v>17.19</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.95</v>
+        <v>16.84</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.84</v>
+        <v>16.62</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.68</v>
+        <v>16.49</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>16.85</v>
+        <v>16.79</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.62</v>
+        <v>16.49</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="N17" s="24" t="inlineStr">
+        <v>16.14</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.91</v>
+        <v>16.83</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>16.87</v>
+        <v>16.81</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="R17" s="23" t="n">
-        <v>0.77</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.89</v>
+        <v>24.64</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.4</v>
+        <v>24.32</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>23.99</v>
+        <v>24.05</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>24.2</v>
+        <v>24.21</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.39</v>
+        <v>24.32</v>
       </c>
       <c r="H18" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="P18" s="21" t="n">
         <v>23.9</v>
       </c>
-      <c r="I18" s="17" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="J18" s="17" t="n">
-        <v>23.41</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>23.72</v>
-      </c>
-      <c r="L18" s="19" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="N18" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>23.83</v>
-      </c>
-      <c r="P18" s="21" t="n">
-        <v>23.76</v>
-      </c>
       <c r="Q18" s="22" t="n">
-        <v>24</v>
+        <v>24.09</v>
       </c>
       <c r="R18" s="25" t="n">
-        <v>-0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>64.38</v>
+        <v>63</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>63.03</v>
+        <v>62.35</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>61.9</v>
+        <v>61.81</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>62.58</v>
+        <v>62.1</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>63.07</v>
+        <v>62.35</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>61.72</v>
+        <v>61.7</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>61.23</v>
+        <v>61.45</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>60.37</v>
+        <v>61.05</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>61.15</v>
+        <v>61.44</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.02</v>
+        <v>60.9</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
+        <v>60.25</v>
+      </c>
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>61.48</v>
+        <v>61.6</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>61.25</v>
+        <v>61.49</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>62.1</v>
+        <v>61.85</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>1.64</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.09</v>
+        <v>10.92</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.89</v>
+        <v>10.81</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>10.82</v>
+        <v>10.71</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>10.9</v>
+        <v>10.78</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>10.7</v>
+        <v>10.67</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>10.62</v>
+        <v>10.6</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>10.61</v>
+        <v>10.65</v>
       </c>
       <c r="L20" s="19" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M20" s="19" t="n">
         <v>10.45</v>
       </c>
-      <c r="M20" s="19" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O20" s="21" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="P20" s="21" t="n">
         <v>10.66</v>
       </c>
-      <c r="P20" s="21" t="n">
-        <v>10.63</v>
-      </c>
       <c r="Q20" s="22" t="n">
-        <v>10.75</v>
+        <v>10.64</v>
       </c>
       <c r="R20" s="23" t="n">
-        <v>0.09</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.67</v>
+        <v>17.63</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.29</v>
+        <v>17.24</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>16.98</v>
+        <v>16.91</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>17.1</v>
+        <v>16.87</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.27</v>
+        <v>17.13</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>16.89</v>
+        <v>16.74</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>16.72</v>
+        <v>16.48</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.51</v>
+        <v>16.35</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.76</v>
+        <v>16.7</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.45</v>
+        <v>16.37</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.07</v>
+        <v>15.98</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>16.84</v>
+        <v>16.73</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>16.79</v>
+        <v>16.73</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>16.93</v>
+        <v>16.61</v>
       </c>
       <c r="R21" s="23" t="n">
-        <v>0.53</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.12</v>
+        <v>36.09</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>35.5</v>
+        <v>35.53</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>34.98</v>
+        <v>35.06</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>35.31</v>
+        <v>35.22</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>35.53</v>
+        <v>35.48</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>34.91</v>
+        <v>34.92</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>34.69</v>
+        <v>34.66</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.29</v>
+        <v>34.36</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>34.64</v>
+        <v>34.74</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.12</v>
+        <v>34.27</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>33.5</v>
+        <v>33.71</v>
       </c>
       <c r="N22" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>34.8</v>
+        <v>34.85</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>34.68</v>
+        <v>34.79</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>35.1</v>
+        <v>34.96</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>0.23</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.64</v>
+        <v>15.68</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.34</v>
+        <v>15.14</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.4</v>
+        <v>15.08</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.59</v>
+        <v>15.51</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>15.23</v>
+        <v>14.86</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>15.04</v>
+        <v>14.43</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.87</v>
+        <v>14.21</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>15.14</v>
+        <v>14.77</v>
       </c>
       <c r="L23" s="19" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="n">
         <v>14.84</v>
       </c>
-      <c r="M23" s="19" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="N23" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O23" s="21" t="n">
-        <v>15.2</v>
-      </c>
       <c r="P23" s="21" t="n">
-        <v>15.17</v>
+        <v>14.82</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="R23" s="25" t="n">
-        <v>-0.13</v>
+        <v>14.66</v>
+      </c>
+      <c r="R23" s="23" t="n">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.19</v>
+        <v>37.69</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.37</v>
+        <v>36.47</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.68</v>
+        <v>35.45</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.96</v>
+        <v>35.31</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.32</v>
+        <v>36.13</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>35.5</v>
+        <v>34.91</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>35.14</v>
+        <v>34.09</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>34.68</v>
+        <v>33.69</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>35.22</v>
+        <v>34.77</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>34.53</v>
+        <v>33.75</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="N24" s="24" t="inlineStr">
+        <v>32.53</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>35.39</v>
+        <v>34.89</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>35.28</v>
+        <v>34.86</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="R24" s="25" t="n">
-        <v>-0.11</v>
+        <v>34.5</v>
+      </c>
+      <c r="R24" s="23" t="n">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>58.39</v>
+        <v>58.57</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.19</v>
+        <v>57.32</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.19</v>
+        <v>56.27</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>56.55</v>
+        <v>56.13</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>57.1</v>
+        <v>56.97</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>55.9</v>
+        <v>55.72</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>55.35</v>
+        <v>54.88</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>54.7</v>
+        <v>54.47</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>55.51</v>
+        <v>55.57</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.51</v>
+        <v>54.53</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>53.31</v>
-      </c>
-      <c r="N25" s="24" t="inlineStr">
+        <v>53.28</v>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>55.75</v>
+        <v>55.69</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>55.61</v>
+        <v>55.67</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>56</v>
-      </c>
-      <c r="R25" s="25" t="n">
-        <v>-0.09</v>
+        <v>55.3</v>
+      </c>
+      <c r="R25" s="23" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>214.99</v>
+        <v>218.61</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>208.69</v>
+        <v>209.21</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>203.41</v>
+        <v>201.33</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>205.37</v>
+        <v>201.33</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>208.23</v>
+        <v>207.07</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>201.93</v>
+        <v>197.67</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>199.07</v>
+        <v>191.93</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>195.63</v>
+        <v>188.27</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>199.89</v>
+        <v>196.07</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>194.61</v>
+        <v>188.19</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>188.31</v>
-      </c>
-      <c r="N26" s="24" t="inlineStr">
+        <v>178.79</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>201.16</v>
+        <v>197.23</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>200.38</v>
+        <v>196.8</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>202.5</v>
-      </c>
-      <c r="R26" s="25" t="n">
-        <v>-0.34</v>
+        <v>195.6</v>
+      </c>
+      <c r="R26" s="23" t="n">
+        <v>-3.41</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>78.31</v>
+        <v>76.13</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>76.76000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>75.45999999999999</v>
+        <v>74.11</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>75.31999999999999</v>
+        <v>74.08</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>76.33</v>
+        <v>74.77</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>74.78</v>
+        <v>73.67</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>73.77</v>
+        <v>72.98</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>73.23</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>74.59</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>73.29000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>71.73999999999999</v>
-      </c>
-      <c r="N27" s="24" t="inlineStr">
+        <v>71.47</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>74.75</v>
+        <v>73.62</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>74.70999999999999</v>
+        <v>73.58</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="R27" s="25" t="n">
-        <v>-0.54</v>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="R27" s="23" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>20.99</v>
+        <v>21.16</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.65</v>
+        <v>20.75</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.37</v>
+        <v>20.41</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.46</v>
+        <v>20.52</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.62</v>
+        <v>20.72</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.28</v>
+        <v>20.31</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.12</v>
+        <v>20.11</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>20.17</v>
+        <v>20.18</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>19.89</v>
+        <v>19.84</v>
       </c>
       <c r="M28" s="19" t="n">
-        <v>19.55</v>
+        <v>19.43</v>
       </c>
       <c r="N28" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O28" s="21" t="n">
-        <v>20.24</v>
+        <v>20.26</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>20.2</v>
+        <v>20.21</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>0.2</v>
+        <v>20.33</v>
+      </c>
+      <c r="R28" s="25" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>80.79000000000001</v>
+        <v>78.56</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>78.14</v>
+        <v>76.61</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>75.92</v>
+        <v>74.97</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>77.38</v>
+        <v>74.78</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>78.27</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>75.62</v>
+        <v>74.12</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>74.73</v>
+        <v>72.83</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>72.97</v>
+        <v>72.17</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>74.43000000000001</v>
+        <v>73.88</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>72.20999999999999</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>69.56</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>75.13</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>74.64</v>
+        <v>74.03</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>76.5</v>
+        <v>73.5</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>1.93</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>29.55</v>
+        <v>29.75</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>28.31</v>
+        <v>28.83</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>27.27</v>
+        <v>28.06</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.81</v>
+        <v>27.99</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>28.29</v>
+        <v>28.59</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>27.05</v>
+        <v>27.67</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>26.57</v>
+        <v>27.07</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>25.81</v>
+        <v>26.75</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>26.57</v>
+        <v>27.54</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>25.53</v>
+        <v>26.77</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
+        <v>25.85</v>
+      </c>
+      <c r="N30" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>26.86</v>
+        <v>27.64</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>26.67</v>
+        <v>27.61</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>27.32</v>
-      </c>
-      <c r="R30" s="23" t="n">
-        <v>2.63</v>
+        <v>27.4</v>
+      </c>
+      <c r="R30" s="25" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>48.29</v>
+        <v>48.57</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>47.89</v>
+        <v>47.97</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.55</v>
+        <v>47.47</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.77</v>
+        <v>47.72</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>47.91</v>
+        <v>47.96</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.51</v>
+        <v>47.36</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.37</v>
+        <v>47.12</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>47.11</v>
+        <v>46.76</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.33</v>
+        <v>47.13</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.99</v>
+        <v>46.63</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.59</v>
+        <v>46.03</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.43</v>
+        <v>47.27</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.36</v>
+        <v>47.18</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.64</v>
+        <v>47.48</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>0.93</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>126.4</v>
+        <v>129.05</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>125.1</v>
+        <v>126.05</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>124.01</v>
+        <v>123.54</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>124.53</v>
+        <v>124.07</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>125.07</v>
+        <v>125.63</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>123.77</v>
+        <v>122.63</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>123.23</v>
+        <v>121.07</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>122.47</v>
+        <v>119.63</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>123.29</v>
+        <v>121.86</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>122.2</v>
+        <v>119.35</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>120.9</v>
+        <v>116.35</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>123.58</v>
+        <v>122.36</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>123.39</v>
+        <v>122.09</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>124</v>
+        <v>122.5</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>0.32</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>56.92</v>
+        <v>57.68</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>55.52</v>
+        <v>55.93</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>54.34</v>
+        <v>54.46</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>54.88</v>
+        <v>54.57</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>55.47</v>
+        <v>55.58</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>54.07</v>
+        <v>53.83</v>
       </c>
       <c r="I33" s="17" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="K33" s="18" t="n">
         <v>53.48</v>
       </c>
-      <c r="J33" s="17" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="K33" s="18" t="n">
-        <v>53.56</v>
-      </c>
       <c r="L33" s="19" t="n">
-        <v>52.38</v>
+        <v>52.02</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="N33" s="24" t="inlineStr">
+        <v>50.27</v>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>53.87</v>
+        <v>53.73</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>53.67</v>
+        <v>53.62</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="R33" s="25" t="n">
-        <v>-0.18</v>
+        <v>53.55</v>
+      </c>
+      <c r="R33" s="23" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.01</v>
+        <v>24.51</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.51</v>
+        <v>23.72</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.09</v>
+        <v>23.06</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>23.33</v>
+        <v>22.97</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.51</v>
+        <v>23.49</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>23.01</v>
+        <v>22.7</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>22.83</v>
+        <v>22.18</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>22.51</v>
+        <v>21.91</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>22.81</v>
+        <v>22.61</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>22.39</v>
+        <v>21.95</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>21.89</v>
+        <v>21.16</v>
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>22.93</v>
+        <v>22.69</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>22.85</v>
+        <v>22.68</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>23.14</v>
+        <v>22.44</v>
       </c>
       <c r="R34" s="23" t="n">
-        <v>0.61</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>25.89</v>
+        <v>26.17</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.54</v>
+        <v>25.63</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.24</v>
+        <v>25.18</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.36</v>
+        <v>25.15</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.51</v>
+        <v>25.49</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>25.16</v>
+        <v>24.95</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>25.01</v>
+        <v>24.61</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>24.81</v>
+        <v>24.41</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>25.05</v>
+        <v>24.88</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>24.75</v>
+        <v>24.43</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N35" s="24" t="inlineStr">
+        <v>23.89</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>25.12</v>
+        <v>24.94</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>25.07</v>
+        <v>24.92</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="R35" s="23" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.630000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.460000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.31</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.34</v>
+        <v>8.23</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.43</v>
+        <v>8.33</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.26</v>
+        <v>8.16</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="J36" s="17" t="n">
-        <v>8.09</v>
+        <v>7.99</v>
       </c>
       <c r="K36" s="18" t="n">
-        <v>8.220000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>8.07</v>
+        <v>7.98</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="N36" s="24" t="inlineStr">
+        <v>7.81</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>8.23</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="R36" s="25" t="n">
-        <v>-0.84</v>
+        <v>8.130000000000001</v>
+      </c>
+      <c r="R36" s="23" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>33.63</v>
+        <v>33.17</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>32.87</v>
+        <v>32.51</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>32.23</v>
+        <v>31.95</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>32.19</v>
+        <v>31.92</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>32.67</v>
+        <v>32.34</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>31.91</v>
+        <v>31.68</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>31.43</v>
+        <v>31.26</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.15</v>
+        <v>31.02</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>31.81</v>
+        <v>31.59</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.17</v>
+        <v>31.03</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="N37" s="24" t="inlineStr">
+        <v>30.37</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.89</v>
+        <v>31.66</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.87</v>
+        <v>31.64</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="R37" s="25" t="n">
-        <v>-2.46</v>
+        <v>31.5</v>
+      </c>
+      <c r="R37" s="23" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>176.59</v>
+        <v>180.2</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>173.69</v>
+        <v>176</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>171.26</v>
+        <v>172.48</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>172</v>
+        <v>173.67</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>173.4</v>
+        <v>175.63</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>170.5</v>
+        <v>171.43</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>169.1</v>
+        <v>169.47</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>167.6</v>
+        <v>167.23</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>169.64</v>
+        <v>170.12</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>167.21</v>
+        <v>166.6</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>164.31</v>
+        <v>162.4</v>
       </c>
       <c r="N38" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>170.18</v>
+        <v>170.94</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>169.86</v>
+        <v>170.45</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>170.6</v>
+        <v>171.7</v>
       </c>
       <c r="R38" s="25" t="n">
-        <v>-0.23</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="39">
@@ -2990,54 +2990,54 @@
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>12.6</v>
+        <v>13.26</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>12.6</v>
+        <v>12.45</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>12.6</v>
+        <v>12.42</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>12.6</v>
+        <v>12.26</v>
       </c>
       <c r="I39" s="17" t="n">
-        <v>12.6</v>
+        <v>11.98</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>12.6</v>
+        <v>11.82</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>12.6</v>
+        <v>12.21</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>12.6</v>
+        <v>11.84</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>12.6</v>
+        <v>11.4</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O39" s="21" t="n">
-        <v>12.6</v>
+        <v>12.25</v>
       </c>
       <c r="P39" s="21" t="n">
-        <v>12.6</v>
+        <v>12.24</v>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>12.6</v>
+        <v>12.13</v>
       </c>
       <c r="R39" s="23" t="n">
-        <v>0</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="40">
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>22.1</v>
+        <v>21.17</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>21.3</v>
+        <v>20.77</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>20.63</v>
+        <v>20.43</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>20.87</v>
+        <v>20.41</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21.24</v>
+        <v>20.67</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>20.44</v>
+        <v>20.27</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>20.07</v>
+        <v>20.01</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>19.64</v>
+        <v>19.87</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>20.19</v>
+        <v>20.21</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>19.52</v>
+        <v>19.87</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>18.72</v>
-      </c>
-      <c r="N40" s="24" t="inlineStr">
+        <v>19.47</v>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>20.34</v>
+        <v>20.25</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>20.25</v>
+        <v>20.24</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R40" s="25" t="n">
-        <v>-0.97</v>
+        <v>20.16</v>
+      </c>
+      <c r="R40" s="23" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>190.31</v>
+        <v>192.7</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>186.41</v>
+        <v>185.9</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>183.14</v>
+        <v>180.2</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>182.83</v>
+        <v>182.23</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>185.37</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>181.47</v>
+        <v>178.57</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>178.93</v>
+        <v>175.43</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>177.57</v>
+        <v>171.77</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>180.96</v>
+        <v>176.4</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>177.69</v>
+        <v>170.7</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>173.79</v>
-      </c>
-      <c r="N41" s="24" t="inlineStr">
+        <v>163.9</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>181.36</v>
+        <v>177.75</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>181.26</v>
+        <v>176.93</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="R41" s="25" t="n">
-        <v>-1.1</v>
+        <v>179.1</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>37.17</v>
+        <v>37.23</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.61</v>
+        <v>36.57</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.14</v>
+        <v>36.01</v>
       </c>
       <c r="F42" s="15" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="G42" s="15" t="n">
         <v>36.39</v>
       </c>
-      <c r="G42" s="15" t="n">
-        <v>36.61</v>
-      </c>
       <c r="H42" s="16" t="n">
-        <v>36.05</v>
+        <v>35.73</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>35.83</v>
+        <v>35.29</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.49</v>
+        <v>35.07</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>35.82</v>
+        <v>35.65</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>35.35</v>
+        <v>35.09</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>34.79</v>
+        <v>34.43</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>35.96</v>
+        <v>35.71</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>35.87</v>
+        <v>35.7</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>36.18</v>
+        <v>35.52</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.71</v>
+        <v>29.31</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>28.15</v>
+        <v>28.55</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>27.68</v>
+        <v>27.91</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.8</v>
+        <v>27.85</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>28.08</v>
+        <v>28.35</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.52</v>
+        <v>27.59</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>27.24</v>
+        <v>27.09</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.96</v>
+        <v>26.83</v>
       </c>
       <c r="K43" s="18" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="L43" s="19" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="M43" s="19" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O43" s="21" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="Q43" s="22" t="n">
         <v>27.36</v>
       </c>
-      <c r="L43" s="19" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>26.33</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O43" s="21" t="n">
-        <v>27.46</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>27.41</v>
-      </c>
-      <c r="Q43" s="22" t="n">
-        <v>27.52</v>
-      </c>
       <c r="R43" s="23" t="n">
-        <v>0.29</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.33</v>
+        <v>26.46</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>26.09</v>
+        <v>26.1</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.89</v>
+        <v>25.8</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.94</v>
+        <v>25.77</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26.06</v>
+        <v>26.01</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.82</v>
+        <v>25.65</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.7</v>
+        <v>25.41</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.58</v>
+        <v>25.29</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.75</v>
+        <v>25.6</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.55</v>
+        <v>25.3</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>25.31</v>
+        <v>24.94</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.8</v>
+        <v>25.64</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.77</v>
+        <v>25.63</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.82</v>
+        <v>25.54</v>
       </c>
       <c r="R44" s="23" t="n">
-        <v>0.16</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.73</v>
+        <v>7.7</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.56</v>
+        <v>7.57</v>
       </c>
       <c r="E45" s="14" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H45" s="16" t="n">
         <v>7.41</v>
       </c>
-      <c r="F45" s="15" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="H45" s="16" t="n">
-        <v>7.38</v>
-      </c>
       <c r="I45" s="17" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.21</v>
+        <v>7.28</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.32</v>
+        <v>7.39</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
+        <v>7.15</v>
+      </c>
+      <c r="N45" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>0.95</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.23</v>
+        <v>12.38</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.87</v>
+        <v>11.72</v>
       </c>
       <c r="F46" s="15" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="G46" s="15" t="n">
         <v>11.92</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>12.01</v>
-      </c>
       <c r="H46" s="16" t="n">
-        <v>11.81</v>
+        <v>11.56</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.72</v>
+        <v>11.32</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.61</v>
+        <v>11.2</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.75</v>
+        <v>11.52</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.59</v>
+        <v>11.22</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>11.39</v>
+        <v>10.86</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.79</v>
+        <v>11.55</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.77</v>
+        <v>11.55</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.82</v>
+        <v>11.44</v>
       </c>
       <c r="R46" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>196.02</v>
+        <v>197.11</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>192.92</v>
+        <v>193.21</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>190.32</v>
+        <v>189.94</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>191.3</v>
+        <v>189.5</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>192.7</v>
+        <v>192.1</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>189.6</v>
+        <v>188.2</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>188.2</v>
+        <v>185.6</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>186.5</v>
+        <v>184.3</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>188.58</v>
+        <v>187.76</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>185.98</v>
+        <v>184.49</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>182.88</v>
-      </c>
-      <c r="N47" s="24" t="inlineStr">
+        <v>180.59</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>189.21</v>
+        <v>188.13</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>188.82</v>
+        <v>188.06</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="R47" s="25" t="n">
-        <v>-0.05</v>
+        <v>186.9</v>
+      </c>
+      <c r="R47" s="23" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>45.62</v>
+        <v>45.23</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>44.84</v>
+        <v>44.43</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>44.19</v>
+        <v>43.76</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>44.13</v>
+        <v>43.73</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>44.63</v>
+        <v>44.23</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>43.85</v>
+        <v>43.43</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>43.35</v>
+        <v>42.93</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>43.07</v>
+        <v>42.63</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>43.75</v>
+        <v>43.32</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>43.1</v>
+        <v>42.65</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="N48" s="24" t="inlineStr">
+        <v>41.85</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>43.83</v>
+        <v>43.41</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>43.81</v>
+        <v>43.38</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="R48" s="25" t="n">
-        <v>-1.76</v>
+        <v>43.22</v>
+      </c>
+      <c r="R48" s="23" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="H49" s="16" t="n">
         <v>32.32</v>
       </c>
-      <c r="D49" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>31.73</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>31.99</v>
-      </c>
-      <c r="H49" s="16" t="n">
-        <v>31.67</v>
-      </c>
       <c r="I49" s="17" t="n">
-        <v>31.55</v>
+        <v>31.96</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.35</v>
+        <v>31.36</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.55</v>
+        <v>31.93</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>31.28</v>
+        <v>31.13</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.96</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
+        <v>30.17</v>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>31.62</v>
+        <v>32.16</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>31.58</v>
+        <v>32.01</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>31.74</v>
-      </c>
-      <c r="R49" s="23" t="n">
-        <v>0.44</v>
+        <v>32.56</v>
+      </c>
+      <c r="R49" s="25" t="n">
+        <v>2.58</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.69</v>
+        <v>12.62</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.34</v>
+        <v>12.3</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.42</v>
+        <v>12.29</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.31</v>
+        <v>12.23</v>
       </c>
       <c r="I50" s="17" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O50" s="21" t="n">
         <v>12.23</v>
       </c>
-      <c r="J50" s="17" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="L50" s="19" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="M50" s="19" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O50" s="21" t="n">
-        <v>12.28</v>
-      </c>
       <c r="P50" s="21" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.35</v>
+        <v>12.18</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>1.4</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>60.18</v>
+        <v>62.8</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>59.08</v>
+        <v>60.3</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>58.16</v>
+        <v>58.2</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.7</v>
+        <v>58.08</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>59.1</v>
+        <v>59.67</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>58</v>
+        <v>57.17</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>57.6</v>
+        <v>55.58</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>56.9</v>
+        <v>54.67</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>57.54</v>
+        <v>56.8</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>56.62</v>
+        <v>54.7</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>55.52</v>
+        <v>52.2</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.81</v>
+        <v>57.08</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>57.63</v>
+        <v>56.99</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>58.3</v>
+        <v>56.5</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>0.6</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.55</v>
+        <v>22.93</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.26</v>
+        <v>22.52</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.02</v>
+        <v>22.18</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.09</v>
+        <v>22.21</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.23</v>
+        <v>22.44</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>21.94</v>
+        <v>22.03</v>
       </c>
       <c r="I52" s="17" t="n">
         <v>21.8</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.65</v>
+        <v>21.62</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.85</v>
+        <v>21.95</v>
       </c>
       <c r="L52" s="19" t="n">
         <v>21.61</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>21.32</v>
+        <v>21.2</v>
       </c>
       <c r="N52" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>21.91</v>
+        <v>22.01</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>21.88</v>
+        <v>21.98</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>21.95</v>
+        <v>21.97</v>
       </c>
       <c r="R52" s="25" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="E53" s="14" t="n">
         <v>5.04</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>5.01</v>
+        <v>4.98</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>4.97</v>
+        <v>4.95</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="L53" s="19" t="n">
         <v>4.95</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="P53" s="21" t="n">
         <v>5.01</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="R53" s="23" t="n">
-        <v>0.4</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.34</v>
+        <v>18.11</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>17.89</v>
+        <v>17.69</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>17.51</v>
+        <v>17.34</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>17.57</v>
+        <v>17.52</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>17.81</v>
+        <v>17.68</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.36</v>
+        <v>17.26</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>17.12</v>
+        <v>17.1</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>16.91</v>
+        <v>16.84</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.26</v>
+        <v>17.1</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.88</v>
+        <v>16.75</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="N54" s="24" t="inlineStr">
+        <v>16.33</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.33</v>
+        <v>17.2</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.29</v>
+        <v>17.14</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.32</v>
+        <v>17.35</v>
       </c>
       <c r="R54" s="25" t="n">
-        <v>-1.53</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>95.43000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>93.93000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>92.67</v>
+        <v>92.63</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>93.17</v>
+        <v>92.47</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>93.83</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>92.33</v>
+        <v>91.98</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>91.67</v>
+        <v>91.02</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>90.83</v>
+        <v>90.53</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>91.83</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>90.56999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="N55" s="24" t="inlineStr">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>92.14</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>91.95</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>92.5</v>
+        <v>91.5</v>
       </c>
       <c r="R55" s="23" t="n">
-        <v>0.65</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.41</v>
+        <v>17.35</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>16.98</v>
+        <v>16.97</v>
       </c>
       <c r="E56" s="14" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="F56" s="15" t="n">
         <v>16.62</v>
       </c>
-      <c r="F56" s="15" t="n">
-        <v>16.61</v>
-      </c>
       <c r="G56" s="15" t="n">
-        <v>16.88</v>
+        <v>16.87</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.45</v>
+        <v>16.49</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.18</v>
+        <v>16.24</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>16.02</v>
+        <v>16.11</v>
       </c>
       <c r="K56" s="18" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O56" s="21" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="P56" s="21" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="Q56" s="22" t="n">
         <v>16.37</v>
       </c>
-      <c r="L56" s="19" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="N56" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O56" s="21" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="P56" s="21" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="Q56" s="22" t="n">
-        <v>16.35</v>
-      </c>
       <c r="R56" s="25" t="n">
-        <v>-0.3</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.08</v>
+        <v>21.48</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.86</v>
+        <v>21.03</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.67</v>
+        <v>20.65</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.78</v>
+        <v>20.61</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.86</v>
+        <v>20.9</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.64</v>
+        <v>20.45</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.56</v>
+        <v>20.16</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>20.42</v>
+        <v>20</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20.55</v>
+        <v>20.4</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>20.36</v>
+        <v>20.02</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>20.14</v>
+        <v>19.57</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.6</v>
+        <v>20.44</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.57</v>
+        <v>20.43</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.7</v>
+        <v>20.31</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>0.49</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.26</v>
+        <v>22.34</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.1</v>
+        <v>22.11</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.18</v>
+        <v>22.14</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.26</v>
+        <v>22.29</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.06</v>
+        <v>22.01</v>
       </c>
       <c r="I58" s="17" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="K58" s="18" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O58" s="21" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="P58" s="21" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="Q58" s="22" t="n">
         <v>21.98</v>
       </c>
-      <c r="J58" s="17" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="K58" s="18" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="L58" s="19" t="n">
-        <v>21.82</v>
-      </c>
-      <c r="M58" s="19" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O58" s="21" t="n">
-        <v>22.03</v>
-      </c>
-      <c r="P58" s="21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q58" s="22" t="n">
-        <v>22.1</v>
-      </c>
       <c r="R58" s="23" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.66</v>
+        <v>28.65</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>28.18</v>
+        <v>28.09</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.77</v>
+        <v>27.62</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.95</v>
+        <v>27.58</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>28.15</v>
+        <v>27.94</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.67</v>
+        <v>27.38</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.47</v>
+        <v>27.02</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>27.19</v>
+        <v>26.82</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.51</v>
+        <v>27.3</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>27.1</v>
+        <v>26.83</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>26.62</v>
+        <v>26.27</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.61</v>
+        <v>27.36</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.54</v>
+        <v>27.35</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.74</v>
+        <v>27.22</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>0.58</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>44.55</v>
+        <v>44.87</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>44.15</v>
+        <v>44.37</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>43.81</v>
+        <v>43.95</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>44.03</v>
+        <v>43.92</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>44.17</v>
+        <v>44.24</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>43.77</v>
+        <v>43.74</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>43.63</v>
+        <v>43.42</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>43.37</v>
+        <v>43.24</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>43.59</v>
+        <v>43.67</v>
       </c>
       <c r="L60" s="19" t="n">
         <v>43.25</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="N60" s="24" t="inlineStr">
+        <v>42.75</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>43.69</v>
+        <v>43.72</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>43.62</v>
+        <v>43.71</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="R60" s="23" t="n">
-        <v>0.23</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>18.91</v>
+        <v>19.03</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.53</v>
+        <v>18.61</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.22</v>
+        <v>18.26</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.43</v>
+        <v>18.21</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.55</v>
+        <v>18.49</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.17</v>
+        <v>18.07</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>18.05</v>
+        <v>17.79</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>17.79</v>
+        <v>17.65</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18</v>
+        <v>18.02</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>17.69</v>
+        <v>17.67</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.31</v>
+        <v>17.25</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.1</v>
+        <v>18.06</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.03</v>
+        <v>18.06</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>18.3</v>
+        <v>17.93</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>1.22</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.38</v>
+        <v>15.76</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.19</v>
+        <v>15.34</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>15.03</v>
+        <v>14.99</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>15.04</v>
+        <v>14.97</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.15</v>
+        <v>15.23</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.96</v>
+        <v>14.81</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.85</v>
+        <v>14.55</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.77</v>
+        <v>14.39</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.92</v>
+        <v>14.75</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.76</v>
+        <v>14.4</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>14.57</v>
+        <v>13.98</v>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.95</v>
+        <v>14.8</v>
       </c>
       <c r="P62" s="21" t="n">
-        <v>14.94</v>
+        <v>14.79</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="R62" s="25" t="n">
-        <v>-0.2</v>
+        <v>14.7</v>
+      </c>
+      <c r="R62" s="23" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.51</v>
+        <v>24.45</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.17</v>
+        <v>24.16</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>23.89</v>
+        <v>23.92</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>24.07</v>
+        <v>23.92</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.18</v>
+        <v>24.09</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.84</v>
+        <v>23.8</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.73</v>
+        <v>23.63</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.5</v>
+        <v>23.51</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.69</v>
+        <v>23.75</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.41</v>
+        <v>23.51</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="P63" s="21" t="n">
         <v>23.78</v>
       </c>
-      <c r="P63" s="21" t="n">
-        <v>23.72</v>
-      </c>
       <c r="Q63" s="22" t="n">
-        <v>23.95</v>
+        <v>23.74</v>
       </c>
       <c r="R63" s="23" t="n">
-        <v>0.76</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="64">
@@ -4549,19 +4549,19 @@
         <v>7.05</v>
       </c>
       <c r="F64" s="15" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G64" s="15" t="n">
         <v>7.08</v>
       </c>
-      <c r="G64" s="15" t="n">
-        <v>7.09</v>
-      </c>
       <c r="H64" s="16" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>7.03</v>
+        <v>6.99</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>6.99</v>
+        <v>6.98</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>7.02</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O64" s="21" t="n">
@@ -4584,10 +4584,10 @@
         <v>7.02</v>
       </c>
       <c r="Q64" s="22" t="n">
-        <v>7.06</v>
+        <v>7.01</v>
       </c>
       <c r="R64" s="23" t="n">
-        <v>0.14</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="65">
@@ -4602,25 +4602,25 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.86</v>
+        <v>4.84</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="J65" s="17" t="n">
         <v>4.74</v>
@@ -4629,12 +4629,12 @@
         <v>4.78</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="N65" s="24" t="inlineStr">
+        <v>4.69</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -4643,13 +4643,13 @@
         <v>4.79</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="R65" s="23" t="n">
-        <v>0.21</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="66">
@@ -4664,41 +4664,41 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="H66" s="16" t="n">
         <v>4.35</v>
       </c>
       <c r="I66" s="17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J66" s="17" t="n">
         <v>4.29</v>
-      </c>
-      <c r="J66" s="17" t="n">
-        <v>4.24</v>
       </c>
       <c r="K66" s="18" t="n">
         <v>4.33</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="N66" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
@@ -4708,10 +4708,10 @@
         <v>4.34</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="R66" s="25" t="n">
-        <v>-1.14</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>64.5</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>63.85</v>
+        <v>63.99</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>63.31</v>
+        <v>63.32</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>63.57</v>
+        <v>63.63</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>63.83</v>
+        <v>63.97</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>63.18</v>
+        <v>63.17</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>62.92</v>
+        <v>62.83</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>62.53</v>
+        <v>62.37</v>
       </c>
       <c r="K67" s="18" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="L67" s="19" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="N67" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O67" s="21" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="P67" s="21" t="n">
         <v>62.94</v>
-      </c>
-      <c r="L67" s="19" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="M67" s="19" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="N67" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O67" s="21" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="P67" s="21" t="n">
-        <v>62.99</v>
       </c>
       <c r="Q67" s="22" t="n">
         <v>63.3</v>
       </c>
-      <c r="R67" s="23" t="n">
-        <v>0.08</v>
+      <c r="R67" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>66.13</v>
+        <v>70.23</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>64.78</v>
+        <v>66.38</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>63.65</v>
+        <v>63.15</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>63.7</v>
+        <v>63.58</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>64.5</v>
+        <v>65.72</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>63.15</v>
+        <v>61.87</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>62.35</v>
+        <v>59.73</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>61.8</v>
+        <v>58.02</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>62.9</v>
+        <v>61</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>61.77</v>
+        <v>57.77</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>60.42</v>
-      </c>
-      <c r="N68" s="24" t="inlineStr">
+        <v>53.92</v>
+      </c>
+      <c r="N68" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>63.08</v>
+        <v>61.58</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>63</v>
+        <v>61.3</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="R68" s="25" t="n">
-        <v>-1.72</v>
+        <v>61.45</v>
+      </c>
+      <c r="R68" s="23" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>78.84999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>77.40000000000001</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E69" s="14" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="F69" s="15" t="n">
         <v>76.18000000000001</v>
       </c>
-      <c r="F69" s="15" t="n">
-        <v>76.84999999999999</v>
-      </c>
       <c r="G69" s="15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.22</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>75.95</v>
+        <v>75.22</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>75.40000000000001</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>74.5</v>
+        <v>73.22</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>75.37</v>
+        <v>74.69</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>74.15000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>72.7</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>75.72</v>
+        <v>75.03</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>75.48</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>76.3</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="R69" s="23" t="n">
-        <v>0.93</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>118.4</v>
+        <v>119.68</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>116.3</v>
+        <v>116.48</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>114.54</v>
+        <v>113.8</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>114.3</v>
+        <v>113.97</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>115.7</v>
+        <v>115.83</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>113.6</v>
+        <v>112.63</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>112.2</v>
+        <v>110.77</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>111.5</v>
+        <v>109.43</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>113.36</v>
+        <v>112</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>111.6</v>
+        <v>109.32</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="N70" s="24" t="inlineStr">
+        <v>106.12</v>
+      </c>
+      <c r="N70" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>113.56</v>
+        <v>112.44</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>113.53</v>
+        <v>112.25</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="R70" s="25" t="n">
-        <v>-0.27</v>
+        <v>112.1</v>
+      </c>
+      <c r="R70" s="23" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>24.43</v>
+        <v>23.44</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.77</v>
+        <v>23.17</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>23.21</v>
+        <v>22.94</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>23.33</v>
+        <v>22.94</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>23.68</v>
+        <v>23.11</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>23.02</v>
+        <v>22.84</v>
       </c>
       <c r="I71" s="17" t="n">
         <v>22.67</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>22.36</v>
+        <v>22.57</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>22.85</v>
+        <v>22.79</v>
       </c>
       <c r="L71" s="19" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="M71" s="19" t="n">
         <v>22.29</v>
       </c>
-      <c r="M71" s="19" t="n">
-        <v>21.63</v>
-      </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>22.96</v>
+        <v>22.82</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>22.9</v>
+        <v>22.81</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>22.99</v>
+        <v>22.78</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>0.88</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="72">
@@ -5036,54 +5036,54 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>19.14</v>
+        <v>20.06</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.54</v>
+        <v>18.9</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>18.04</v>
+        <v>17.92</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>18.15</v>
+        <v>18.23</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.46</v>
+        <v>18.78</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.86</v>
+        <v>17.62</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.55</v>
+        <v>17.07</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>17.26</v>
+        <v>16.46</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.7</v>
+        <v>17.28</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>17.2</v>
+        <v>16.3</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>16.6</v>
+        <v>15.14</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.8</v>
+        <v>17.49</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.75</v>
+        <v>17.37</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.84</v>
+        <v>17.67</v>
       </c>
       <c r="R72" s="23" t="n">
-        <v>0.45</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>229.41</v>
+        <v>228.26</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>226.81</v>
+        <v>226.06</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>224.63</v>
+        <v>224.22</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>224.6</v>
+        <v>224.3</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>226.2</v>
+        <v>225.6</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>223.6</v>
+        <v>223.4</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>222</v>
+        <v>222.1</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>221</v>
+        <v>221.2</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>223.17</v>
+        <v>222.98</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>220.99</v>
+        <v>221.14</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>218.39</v>
-      </c>
-      <c r="N73" s="24" t="inlineStr">
+        <v>218.94</v>
+      </c>
+      <c r="N73" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>223.49</v>
+        <v>223.28</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>223.37</v>
+        <v>223.16</v>
       </c>
       <c r="Q73" s="22" t="n">
         <v>223</v>
       </c>
       <c r="R73" s="25" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.57</v>
+        <v>15.79</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.41</v>
+        <v>15.53</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.27</v>
+        <v>15.31</v>
       </c>
       <c r="F74" s="15" t="n">
         <v>15.34</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.41</v>
+        <v>15.49</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.25</v>
+        <v>15.23</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.18</v>
+        <v>15.08</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>15.09</v>
+        <v>14.97</v>
       </c>
       <c r="K74" s="18" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="M74" s="19" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="N74" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O74" s="21" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="P74" s="21" t="n">
         <v>15.19</v>
       </c>
-      <c r="L74" s="19" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="M74" s="19" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="N74" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O74" s="21" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="P74" s="21" t="n">
+      <c r="Q74" s="22" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q74" s="22" t="n">
-        <v>15.28</v>
-      </c>
       <c r="R74" s="23" t="n">
-        <v>0.39</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>37.08</v>
+        <v>36.99</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>36.72</v>
+        <v>36.69</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.42</v>
+        <v>36.43</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>36.54</v>
+        <v>36.6</v>
       </c>
       <c r="G75" s="15" t="n">
         <v>36.7</v>
       </c>
       <c r="H75" s="16" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I75" s="17" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="J75" s="17" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K75" s="18" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="L75" s="19" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="M75" s="19" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="N75" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O75" s="21" t="n">
         <v>36.34</v>
       </c>
-      <c r="I75" s="17" t="n">
-        <v>36.18</v>
-      </c>
-      <c r="J75" s="17" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="K75" s="18" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="L75" s="19" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="M75" s="19" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O75" s="21" t="n">
+      <c r="P75" s="21" t="n">
         <v>36.29</v>
       </c>
-      <c r="P75" s="21" t="n">
-        <v>36.25</v>
-      </c>
       <c r="Q75" s="22" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="R75" s="23" t="n">
-        <v>1.06</v>
+        <v>36.5</v>
+      </c>
+      <c r="R75" s="25" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>23.65</v>
+        <v>23.28</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>23.24</v>
+        <v>23.02</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>23.04</v>
+        <v>22.95</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>23.22</v>
+        <v>23.03</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>22.81</v>
+        <v>22.77</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>22.63</v>
+        <v>22.69</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>22.4</v>
+        <v>22.51</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>22.67</v>
+        <v>22.66</v>
       </c>
       <c r="L76" s="19" t="n">
-        <v>22.33</v>
+        <v>22.44</v>
       </c>
       <c r="M76" s="19" t="n">
-        <v>21.92</v>
+        <v>22.18</v>
       </c>
       <c r="N76" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>22.76</v>
+        <v>22.73</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>22.7</v>
+        <v>22.68</v>
       </c>
       <c r="Q76" s="22" t="n">
         <v>22.86</v>
       </c>
-      <c r="R76" s="23" t="n">
-        <v>0.35</v>
+      <c r="R76" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -5346,54 +5346,54 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>42.64</v>
+        <v>41.92</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>41.96</v>
+        <v>41.44</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>41.39</v>
+        <v>41.03</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>41.46</v>
+        <v>41.06</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>41.84</v>
+        <v>41.34</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>41.16</v>
+        <v>40.86</v>
       </c>
       <c r="I77" s="17" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="J77" s="17" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="K77" s="18" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="L77" s="19" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="M77" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="N77" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O77" s="21" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="P77" s="21" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Q77" s="22" t="n">
         <v>40.78</v>
       </c>
-      <c r="J77" s="17" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="K77" s="18" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="L77" s="19" t="n">
-        <v>40.44</v>
-      </c>
-      <c r="M77" s="19" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="N77" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O77" s="21" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="P77" s="21" t="n">
-        <v>41.06</v>
-      </c>
-      <c r="Q77" s="22" t="n">
-        <v>41.08</v>
-      </c>
       <c r="R77" s="23" t="n">
-        <v>0.15</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="78">
@@ -5408,25 +5408,25 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.41</v>
+        <v>5.36</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>5.31</v>
+        <v>5.28</v>
       </c>
       <c r="E78" s="14" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F78" s="15" t="n">
         <v>5.23</v>
       </c>
-      <c r="F78" s="15" t="n">
-        <v>5.28</v>
-      </c>
       <c r="G78" s="15" t="n">
-        <v>5.31</v>
+        <v>5.27</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.18</v>
+        <v>5.15</v>
       </c>
       <c r="J78" s="17" t="n">
         <v>5.11</v>
@@ -5435,27 +5435,27 @@
         <v>5.17</v>
       </c>
       <c r="L78" s="19" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="M78" s="19" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O78" s="21" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="P78" s="21" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="Q78" s="22" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>0.77</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>18.95</v>
+        <v>19</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.59</v>
+        <v>18.69</v>
       </c>
       <c r="E79" s="14" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="H79" s="16" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="J79" s="17" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="K79" s="18" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="L79" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="M79" s="19" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="N79" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O79" s="21" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P79" s="21" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="Q79" s="22" t="n">
         <v>18.29</v>
       </c>
-      <c r="F79" s="15" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="G79" s="15" t="n">
-        <v>18.55</v>
-      </c>
-      <c r="H79" s="16" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="I79" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="J79" s="17" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="K79" s="18" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="L79" s="19" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="M79" s="19" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="N79" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O79" s="21" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="P79" s="21" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="Q79" s="22" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="R79" s="23" t="n">
-        <v>0.9399999999999999</v>
+      <c r="R79" s="25" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="80">
@@ -5532,54 +5532,54 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>78.02</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>77.02</v>
+        <v>78.69</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>76.18000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>76.63</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>77.02</v>
+        <v>78.67</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>76.02</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>75.63</v>
+        <v>76.08</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>75.02</v>
+        <v>74.97</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>75.62</v>
+        <v>76.11</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>74.78</v>
+        <v>74.56</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>73.78</v>
-      </c>
-      <c r="N80" s="20" t="inlineStr">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="N80" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>75.86</v>
+        <v>76.53</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>75.7</v>
+        <v>76.25</v>
       </c>
       <c r="Q80" s="22" t="n">
-        <v>76.25</v>
-      </c>
-      <c r="R80" s="23" t="n">
-        <v>1.13</v>
+        <v>77.2</v>
+      </c>
+      <c r="R80" s="25" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="81">
@@ -5594,53 +5594,53 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>4.95</v>
+        <v>5.07</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.83</v>
+        <v>4.9</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="G81" s="15" t="n">
-        <v>4.81</v>
+        <v>4.87</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="I81" s="17" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>4.57</v>
+        <v>4.51</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O81" s="21" t="n">
         <v>4.68</v>
       </c>
       <c r="P81" s="21" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q81" s="22" t="n">
         <v>4.68</v>
       </c>
-      <c r="Q81" s="22" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="R81" s="23" t="n">
+      <c r="R81" s="25" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -5656,54 +5656,54 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>60.41</v>
+        <v>61.2</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>59.26</v>
+        <v>59.75</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>58.3</v>
+        <v>58.53</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>58.73</v>
+        <v>58.37</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>59.22</v>
+        <v>59.33</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>57.58</v>
+        <v>56.92</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>56.92</v>
+        <v>56.43</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>57.65</v>
+        <v>57.72</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>56.69</v>
+        <v>56.5</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>55.54</v>
+        <v>55.05</v>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>57.9</v>
+        <v>57.86</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>57.74</v>
+        <v>57.83</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>58.25</v>
+        <v>57.4</v>
       </c>
       <c r="R82" s="23" t="n">
-        <v>0.87</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="83">
@@ -5721,51 +5721,51 @@
         <v>37.69</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.39</v>
+        <v>37.35</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.13</v>
+        <v>37.07</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>37.22</v>
+        <v>37.15</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>37.36</v>
+        <v>37.31</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>37.06</v>
+        <v>36.97</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.92</v>
+        <v>36.81</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.76</v>
+        <v>36.63</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>36.97</v>
+        <v>36.87</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.71</v>
+        <v>36.59</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.41</v>
-      </c>
-      <c r="N83" s="24" t="inlineStr">
+        <v>36.25</v>
+      </c>
+      <c r="N83" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>37.02</v>
+        <v>36.94</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>36.99</v>
+        <v>36.9</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>37.08</v>
+        <v>36.98</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>0.22</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="84">
@@ -5780,54 +5780,54 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>93.23</v>
+        <v>93.75</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>92.38</v>
+        <v>92.7</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>91.66</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>91.93000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>92.31999999999999</v>
+        <v>92.47</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>91.47</v>
+        <v>91.42</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>91.08</v>
+        <v>90.78</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>90.62</v>
+        <v>90.37</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>91.19</v>
+        <v>91.23</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>90.47</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>89.62</v>
+        <v>89.3</v>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O84" s="21" t="n">
         <v>91.36</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.25</v>
+        <v>91.31</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>91.55</v>
+        <v>91.2</v>
       </c>
       <c r="R84" s="23" t="n">
-        <v>0.11</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="85">
@@ -5842,54 +5842,54 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>16.75</v>
+        <v>16.94</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.54</v>
+        <v>16.65</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.36</v>
+        <v>16.41</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.47</v>
+        <v>16.39</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.55</v>
+        <v>16.57</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.34</v>
+        <v>16.28</v>
       </c>
       <c r="I85" s="17" t="n">
-        <v>16.26</v>
+        <v>16.1</v>
       </c>
       <c r="J85" s="17" t="n">
-        <v>16.13</v>
+        <v>15.99</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>16.25</v>
+        <v>16.24</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>16.07</v>
+        <v>16</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.86</v>
+        <v>15.71</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.3</v>
+        <v>16.27</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.26</v>
+        <v>16.27</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="R85" s="23" t="n">
-        <v>1.11</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="86">
@@ -5904,54 +5904,54 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>125.58</v>
+        <v>122.79</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>123.18</v>
+        <v>121.19</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>121.17</v>
+        <v>119.85</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>121.23</v>
+        <v>119.8</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>122.67</v>
+        <v>120.8</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>120.27</v>
+        <v>119.2</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>118.83</v>
+        <v>118.2</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>117.87</v>
+        <v>117.6</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>119.83</v>
+        <v>118.95</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>117.82</v>
+        <v>117.61</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>115.42</v>
-      </c>
-      <c r="N86" s="24" t="inlineStr">
+        <v>116.01</v>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>120.14</v>
+        <v>119.14</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>120.02</v>
+        <v>119.08</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="R86" s="25" t="n">
-        <v>-1.72</v>
+        <v>118.8</v>
+      </c>
+      <c r="R86" s="23" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="87">
@@ -5966,54 +5966,54 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>57.93</v>
+        <v>57.3</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>56.43</v>
+        <v>55.85</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>55.17</v>
+        <v>54.63</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>55.33</v>
+        <v>54.9</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>56.17</v>
+        <v>55.65</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>54.67</v>
+        <v>54.2</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>53.83</v>
+        <v>53.45</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>53.17</v>
+        <v>52.75</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>54.33</v>
+        <v>53.82</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>53.07</v>
+        <v>52.6</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>51.57</v>
-      </c>
-      <c r="N87" s="24" t="inlineStr">
+        <v>51.15</v>
+      </c>
+      <c r="N87" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>54.56</v>
+        <v>54.07</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>54.45</v>
+        <v>53.93</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>54.5</v>
+        <v>54.15</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>0.09</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="88">
@@ -6028,39 +6028,39 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>9.789999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="E88" s="14" t="n">
         <v>9.59</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>9.6</v>
+        <v>9.58</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>9.66</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
       <c r="J88" s="17" t="n">
         <v>9.44</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.43</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="N88" s="24" t="inlineStr">
+        <v>9.35</v>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -6069,13 +6069,13 @@
         <v>9.539999999999999</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.529999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>16.98</v>
+        <v>16.42</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>16.27</v>
+        <v>15.98</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>15.67</v>
+        <v>15.61</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>15.89</v>
+        <v>15.56</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>15.5</v>
+        <v>15.42</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.18</v>
+        <v>15.12</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>14.79</v>
+        <v>14.98</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>15.28</v>
+        <v>15.37</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>14.68</v>
+        <v>15</v>
       </c>
       <c r="M89" s="19" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="N89" s="24" t="inlineStr">
+        <v>14.56</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O89" s="21" t="n">
-        <v>15.42</v>
+        <v>15.41</v>
       </c>
       <c r="P89" s="21" t="n">
-        <v>15.33</v>
+        <v>15.4</v>
       </c>
       <c r="Q89" s="22" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="R89" s="25" t="n">
-        <v>-0.58</v>
+        <v>15.27</v>
+      </c>
+      <c r="R89" s="23" t="n">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>17.99</v>
+        <v>18.22</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.65</v>
+        <v>17.86</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>17.37</v>
+        <v>17.56</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>17.55</v>
+        <v>17.59</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>17.66</v>
+        <v>17.79</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.32</v>
+        <v>17.43</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>17.21</v>
+        <v>17.23</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>16.98</v>
+        <v>17.07</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.17</v>
+        <v>17.36</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>16.89</v>
+        <v>17.06</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="N90" s="20" t="inlineStr">
+        <v>16.7</v>
+      </c>
+      <c r="N90" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>17.26</v>
+        <v>17.41</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.2</v>
+        <v>17.39</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.43</v>
+        <v>17.38</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>1.51</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="91">
@@ -6214,54 +6214,54 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>30.87</v>
+        <v>31.66</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.21</v>
+        <v>30.56</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>29.65</v>
+        <v>29.64</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>29.82</v>
+        <v>29.66</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.14</v>
+        <v>30.32</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.48</v>
+        <v>29.22</v>
       </c>
       <c r="I91" s="17" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="J91" s="17" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="K91" s="18" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="L91" s="19" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="M91" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="N91" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O91" s="21" t="n">
         <v>29.16</v>
       </c>
-      <c r="J91" s="17" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="K91" s="18" t="n">
-        <v>29.29</v>
-      </c>
-      <c r="L91" s="19" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="M91" s="19" t="n">
-        <v>28.07</v>
-      </c>
-      <c r="N91" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O91" s="21" t="n">
-        <v>29.41</v>
-      </c>
       <c r="P91" s="21" t="n">
-        <v>29.34</v>
+        <v>29.11</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="R91" s="23" t="n">
-        <v>0.2</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="92">
@@ -6276,54 +6276,54 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.62</v>
+        <v>20.36</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.73</v>
+        <v>19.7</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.91</v>
+        <v>19.7</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>20.11</v>
+        <v>19.92</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.63</v>
+        <v>19.56</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>19.43</v>
+        <v>19.34</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>19.15</v>
+        <v>19.2</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>19.47</v>
+        <v>19.5</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>19.06</v>
+        <v>19.2</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>18.58</v>
+        <v>18.84</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>19.57</v>
+        <v>19.54</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>19.5</v>
+        <v>19.53</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>19.7</v>
+        <v>19.48</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>1.03</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="93">
@@ -6338,54 +6338,54 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.54</v>
+        <v>26.9</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.18</v>
+        <v>26.32</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.88</v>
+        <v>25.83</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>26.08</v>
+        <v>25.81</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.2</v>
+        <v>26.17</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.84</v>
+        <v>25.59</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.72</v>
+        <v>25.23</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.48</v>
+        <v>25.01</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.68</v>
+        <v>25.51</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.38</v>
+        <v>25.02</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>25.02</v>
+        <v>24.44</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.77</v>
+        <v>25.57</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.71</v>
+        <v>25.55</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.96</v>
+        <v>25.44</v>
       </c>
       <c r="R93" s="23" t="n">
-        <v>0.78</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="94">
@@ -6400,54 +6400,54 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>174.74</v>
+        <v>175.02</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>172.74</v>
+        <v>172.72</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>171.06</v>
+        <v>170.79</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>172.17</v>
+        <v>171.13</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>172.83</v>
+        <v>172.37</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>170.83</v>
+        <v>170.07</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>170.17</v>
+        <v>168.83</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>168.83</v>
+        <v>167.77</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>169.94</v>
+        <v>169.51</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>168.26</v>
+        <v>167.58</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>166.26</v>
+        <v>165.28</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>170.46</v>
+        <v>169.88</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>170.1</v>
+        <v>169.69</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>171.5</v>
+        <v>169.9</v>
       </c>
       <c r="R94" s="23" t="n">
-        <v>0.18</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
-        <v>13.51</v>
+        <v>13.8</v>
       </c>
       <c r="D95" s="13" t="n">
-        <v>13.32</v>
+        <v>13.48</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>13.16</v>
+        <v>13.21</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>13.22</v>
+        <v>13.38</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>13.31</v>
+        <v>13.49</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>13.12</v>
+        <v>13.17</v>
       </c>
       <c r="I95" s="17" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="J95" s="17" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="K95" s="18" t="n">
         <v>13.03</v>
       </c>
-      <c r="J95" s="17" t="n">
-        <v>12.93</v>
-      </c>
-      <c r="K95" s="18" t="n">
-        <v>13.05</v>
-      </c>
       <c r="L95" s="19" t="n">
-        <v>12.89</v>
+        <v>12.76</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N95" s="20" t="inlineStr">
+        <v>12.44</v>
+      </c>
+      <c r="N95" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.09</v>
+        <v>13.11</v>
       </c>
       <c r="P95" s="21" t="n">
-        <v>13.07</v>
+        <v>13.06</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="R95" s="23" t="n">
-        <v>0.46</v>
+        <v>13.27</v>
+      </c>
+      <c r="R95" s="25" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>19.78</v>
+        <v>20.04</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.36</v>
+        <v>19.58</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>19.01</v>
+        <v>19.2</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.24</v>
+        <v>19.29</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.38</v>
+        <v>19.53</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>18.96</v>
+        <v>19.07</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>18.82</v>
+        <v>18.83</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.54</v>
+        <v>18.61</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>18.77</v>
+        <v>18.94</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.42</v>
+        <v>18.56</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="N96" s="20" t="inlineStr">
+        <v>18.1</v>
+      </c>
+      <c r="N96" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>18.88</v>
+        <v>19.02</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>18.81</v>
+        <v>18.98</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>1.17</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="97">
@@ -6586,54 +6586,54 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>16.42</v>
+        <v>15.85</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>16.19</v>
+        <v>15.2</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>16</v>
+        <v>14.66</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>15.97</v>
+        <v>14.59</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>16.13</v>
+        <v>15.02</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>15.9</v>
+        <v>14.37</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>15.74</v>
+        <v>13.94</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>15.67</v>
+        <v>13.72</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>15.87</v>
+        <v>14.29</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>15.68</v>
+        <v>13.75</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>15.45</v>
-      </c>
-      <c r="N97" s="24" t="inlineStr">
+        <v>13.1</v>
+      </c>
+      <c r="N97" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>15.89</v>
+        <v>14.36</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>15.89</v>
+        <v>14.34</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>15.82</v>
-      </c>
-      <c r="R97" s="25" t="n">
-        <v>-0.82</v>
+        <v>14.16</v>
+      </c>
+      <c r="R97" s="23" t="n">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.42</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E98" s="14" t="n">
-        <v>9.23</v>
+        <v>9.25</v>
       </c>
       <c r="F98" s="15" t="n">
         <v>9.33</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.41</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H98" s="16" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="I98" s="17" t="n">
         <v>9.19</v>
       </c>
-      <c r="I98" s="17" t="n">
-        <v>9.109999999999999</v>
-      </c>
       <c r="J98" s="17" t="n">
-        <v>8.970000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.109999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>8.92</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N98" s="20" t="inlineStr">
+        <v>8.91</v>
+      </c>
+      <c r="N98" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.130000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="R98" s="23" t="n">
-        <v>1.43</v>
+        <v>9.279999999999999</v>
+      </c>
+      <c r="R98" s="25" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>25.2</v>
+        <v>25.32</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>24.96</v>
+        <v>25</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>24.76</v>
+        <v>24.73</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>24.8</v>
+        <v>24.69</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>24.93</v>
+        <v>24.91</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>24.69</v>
+        <v>24.59</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.56</v>
+        <v>24.37</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.45</v>
+        <v>24.27</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.62</v>
+        <v>24.55</v>
       </c>
       <c r="L99" s="19" t="n">
-        <v>24.42</v>
+        <v>24.28</v>
       </c>
       <c r="M99" s="19" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="N99" s="24" t="inlineStr">
+        <v>23.96</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O99" s="21" t="n">
-        <v>24.66</v>
+        <v>24.58</v>
       </c>
       <c r="P99" s="21" t="n">
-        <v>24.64</v>
+        <v>24.58</v>
       </c>
       <c r="Q99" s="22" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="R99" s="25" t="n">
-        <v>-0.2</v>
+        <v>24.48</v>
+      </c>
+      <c r="R99" s="23" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6772,54 +6772,54 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.44</v>
+        <v>16.18</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>16.13</v>
+        <v>15.97</v>
       </c>
       <c r="E100" s="14" t="n">
-        <v>15.87</v>
+        <v>15.79</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>16.04</v>
+        <v>15.86</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>16.15</v>
+        <v>15.95</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>15.84</v>
+        <v>15.74</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>15.73</v>
+        <v>15.65</v>
       </c>
       <c r="J100" s="17" t="n">
         <v>15.53</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>15.7</v>
+        <v>15.68</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>15.44</v>
+        <v>15.5</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>15.13</v>
+        <v>15.29</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>15.78</v>
+        <v>15.72</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>15.72</v>
+        <v>15.69</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>15.94</v>
+        <v>15.76</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>2.05</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="101">
@@ -6834,54 +6834,54 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>31.74</v>
+        <v>30.64</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>30.64</v>
+        <v>29.9</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.72</v>
+        <v>29.28</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.83</v>
+        <v>29.19</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>30.45</v>
+        <v>29.69</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>29.35</v>
+        <v>28.95</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>28.73</v>
+        <v>28.45</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>28.25</v>
+        <v>28.21</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>29.1</v>
+        <v>28.86</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>28.18</v>
+        <v>28.24</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>27.08</v>
-      </c>
-      <c r="N101" s="24" t="inlineStr">
+        <v>27.5</v>
+      </c>
+      <c r="N101" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>29.27</v>
+        <v>28.93</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>29.19</v>
+        <v>28.92</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>29.22</v>
+        <v>28.7</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>0.34</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="102">
@@ -6896,54 +6896,54 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>15.07</v>
+        <v>14.89</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>14.7</v>
+        <v>14.59</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.39</v>
+        <v>14.33</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.47</v>
+        <v>14.32</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>14.65</v>
+        <v>14.51</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.28</v>
+        <v>14.21</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.1</v>
+        <v>14.02</v>
       </c>
       <c r="J102" s="17" t="n">
         <v>13.91</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.87</v>
+        <v>13.91</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="N102" s="24" t="inlineStr">
+        <v>13.61</v>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.25</v>
+        <v>14.2</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.21</v>
+        <v>14.19</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="R102" s="25" t="n">
-        <v>-0.42</v>
+        <v>14.13</v>
+      </c>
+      <c r="R102" s="23" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="103">
@@ -6958,54 +6958,54 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>70.06</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>68.11</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>66.47</v>
+        <v>64.86</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>66.45</v>
+        <v>65.3</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>67.65000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>65.7</v>
+        <v>64.3</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>64.5</v>
+        <v>63.3</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>63.75</v>
+        <v>62.3</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>65.38</v>
+        <v>63.74</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>63.74</v>
+        <v>62.06</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>61.79</v>
-      </c>
-      <c r="N103" s="24" t="inlineStr">
+        <v>60.06</v>
+      </c>
+      <c r="N103" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>65.62</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>65.53</v>
+        <v>63.9</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="R103" s="25" t="n">
-        <v>-1.58</v>
+        <v>64.3</v>
+      </c>
+      <c r="R103" s="23" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="104">
@@ -7020,54 +7020,54 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.35</v>
+        <v>14.29</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.18</v>
+        <v>14.14</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.03</v>
+        <v>14.02</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>14.07</v>
+        <v>14.01</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.16</v>
+        <v>14.11</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>13.99</v>
+        <v>13.96</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>13.9</v>
+        <v>13.86</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="K104" s="18" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="L104" s="19" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="M104" s="19" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O104" s="21" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="P104" s="21" t="n">
         <v>13.94</v>
       </c>
-      <c r="L104" s="19" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="M104" s="19" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="N104" s="20" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O104" s="21" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="P104" s="21" t="n">
-        <v>13.95</v>
-      </c>
       <c r="Q104" s="22" t="n">
-        <v>13.99</v>
+        <v>13.92</v>
       </c>
       <c r="R104" s="23" t="n">
-        <v>0.14</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="105">
@@ -7082,54 +7082,54 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>19.75</v>
+        <v>19.29</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>18.47</v>
+        <v>18.19</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>17.4</v>
+        <v>17.27</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.41</v>
+        <v>17.31</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>18.18</v>
+        <v>17.96</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>16.9</v>
+        <v>16.86</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>16.13</v>
+        <v>16.21</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.62</v>
+        <v>15.76</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>16.68</v>
+        <v>16.65</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.61</v>
+        <v>15.73</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="N105" s="24" t="inlineStr">
+        <v>14.63</v>
+      </c>
+      <c r="N105" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>16.84</v>
+        <v>16.8</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>16.78</v>
+        <v>16.74</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>16.63</v>
+        <v>16.66</v>
       </c>
       <c r="R105" s="25" t="n">
-        <v>-3.48</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="D106" s="13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="F106" s="15" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="H106" s="16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I106" s="17" t="n">
         <v>2.37</v>
       </c>
-      <c r="I106" s="17" t="n">
+      <c r="J106" s="17" t="n">
         <v>2.34</v>
       </c>
-      <c r="J106" s="17" t="n">
-        <v>2.33</v>
-      </c>
       <c r="K106" s="18" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="L106" s="19" t="n">
         <v>2.33</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="N106" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R106" s="25" t="n">
-        <v>-0.42</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>37.82</v>
+        <v>38.32</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>37.4</v>
+        <v>37.48</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>37.05</v>
+        <v>36.78</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>37.12</v>
+        <v>37.03</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>37.34</v>
+        <v>37.41</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.92</v>
+        <v>36.57</v>
       </c>
       <c r="I107" s="17" t="n">
-        <v>36.7</v>
+        <v>36.19</v>
       </c>
       <c r="J107" s="17" t="n">
-        <v>36.5</v>
+        <v>35.73</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>36.81</v>
+        <v>36.3</v>
       </c>
       <c r="L107" s="19" t="n">
-        <v>36.46</v>
+        <v>35.6</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>36.04</v>
+        <v>34.76</v>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>36.88</v>
+        <v>36.47</v>
       </c>
       <c r="P107" s="21" t="n">
-        <v>36.85</v>
+        <v>36.37</v>
       </c>
       <c r="Q107" s="22" t="n">
-        <v>36.9</v>
+        <v>36.64</v>
       </c>
       <c r="R107" s="23" t="n">
-        <v>0.27</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="108">
@@ -7271,51 +7271,51 @@
         <v>8.09</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.93</v>
+        <v>7.86</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.79</v>
+        <v>7.67</v>
       </c>
       <c r="F108" s="15" t="n">
-        <v>7.81</v>
+        <v>7.66</v>
       </c>
       <c r="G108" s="15" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>7.74</v>
+        <v>7.57</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.65</v>
+        <v>7.43</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.58</v>
+        <v>7.34</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.71</v>
+        <v>7.54</v>
       </c>
       <c r="L108" s="19" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O108" s="21" t="n">
         <v>7.57</v>
       </c>
-      <c r="M108" s="19" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="N108" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O108" s="21" t="n">
-        <v>7.73</v>
-      </c>
       <c r="P108" s="21" t="n">
-        <v>7.72</v>
+        <v>7.56</v>
       </c>
       <c r="Q108" s="22" t="n">
-        <v>7.72</v>
+        <v>7.51</v>
       </c>
       <c r="R108" s="23" t="n">
-        <v>0.39</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="109">
@@ -7330,54 +7330,54 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>44.09</v>
+        <v>43.99</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>43.71</v>
+        <v>43.65</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.4</v>
+        <v>43.37</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.53</v>
+        <v>43.33</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.69</v>
+        <v>43.55</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.31</v>
+        <v>43.21</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>43.15</v>
+        <v>42.99</v>
       </c>
       <c r="J109" s="17" t="n">
-        <v>42.93</v>
+        <v>42.87</v>
       </c>
       <c r="K109" s="18" t="n">
-        <v>43.18</v>
+        <v>43.17</v>
       </c>
       <c r="L109" s="19" t="n">
-        <v>42.87</v>
+        <v>42.89</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>42.49</v>
-      </c>
-      <c r="N109" s="24" t="inlineStr">
+        <v>42.55</v>
+      </c>
+      <c r="N109" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>43.26</v>
+        <v>43.21</v>
       </c>
       <c r="P109" s="21" t="n">
-        <v>43.21</v>
+        <v>43.2</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>43.36</v>
+        <v>43.1</v>
       </c>
       <c r="R109" s="23" t="n">
-        <v>0.32</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="110">
@@ -7392,54 +7392,54 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>67.39</v>
+        <v>66.45</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>65.79000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.45</v>
+        <v>64.52</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>65.33</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>65.87</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.27</v>
+        <v>64.13</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.73</v>
+        <v>63.52</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>62.67</v>
+        <v>63.08</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>63.55</v>
+        <v>63.93</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>62.21</v>
+        <v>63.05</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>60.61</v>
+        <v>62</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>63.97</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>63.68</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>64.8</v>
+        <v>63.95</v>
       </c>
       <c r="R110" s="23" t="n">
-        <v>1.01</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="111">
@@ -7454,54 +7454,54 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.22</v>
+        <v>10.23</v>
       </c>
       <c r="D111" s="13" t="n">
         <v>10.14</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>10.12</v>
+        <v>10.06</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>10.14</v>
+        <v>10.11</v>
       </c>
       <c r="H111" s="16" t="n">
-        <v>10.06</v>
+        <v>10.02</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>10.04</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J111" s="17" t="n">
-        <v>9.98</v>
+        <v>9.93</v>
       </c>
       <c r="K111" s="18" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="L111" s="19" t="n">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>0.8</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>320.19</v>
+        <v>309.79</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>307.59</v>
+        <v>301.39</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>297.03</v>
+        <v>294.35</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>297.6</v>
+        <v>299</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>305</v>
+        <v>301.8</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>292.4</v>
+        <v>293.4</v>
       </c>
       <c r="I112" s="17" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="J112" s="17" t="n">
         <v>285</v>
       </c>
-      <c r="J112" s="17" t="n">
-        <v>279.8</v>
-      </c>
       <c r="K112" s="18" t="n">
-        <v>289.97</v>
+        <v>289.65</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>279.41</v>
+        <v>282.61</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>266.81</v>
+        <v>274.21</v>
       </c>
       <c r="N112" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>291.68</v>
+        <v>291.85</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>290.95</v>
+        <v>290.3</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>290.2</v>
+        <v>296.2</v>
       </c>
       <c r="R112" s="25" t="n">
-        <v>-1.56</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="113">
@@ -7578,54 +7578,54 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>225.16</v>
+        <v>224.12</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>221.66</v>
+        <v>221.02</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>218.73</v>
+        <v>218.42</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>219.87</v>
+        <v>218.07</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>221.43</v>
+        <v>220.13</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>217.93</v>
+        <v>217.03</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>216.37</v>
+        <v>214.97</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>214.43</v>
+        <v>213.93</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>216.77</v>
+        <v>216.68</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>213.84</v>
+        <v>214.08</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>210.34</v>
-      </c>
-      <c r="N113" s="24" t="inlineStr">
+        <v>210.98</v>
+      </c>
+      <c r="N113" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>217.49</v>
+        <v>216.98</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>217.04</v>
+        <v>216.92</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>218.3</v>
-      </c>
-      <c r="R113" s="25" t="n">
-        <v>-0.18</v>
+        <v>216</v>
+      </c>
+      <c r="R113" s="23" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="114">
@@ -7640,54 +7640,54 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>600.25</v>
+        <v>598.33</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>591.75</v>
+        <v>591.33</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>584.63</v>
+        <v>585.46</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>589</v>
+        <v>584.67</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>592</v>
+        <v>589.33</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>583.5</v>
+        <v>582.33</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>580.5</v>
+        <v>577.67</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>575</v>
+        <v>575.33</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>579.87</v>
+        <v>581.54</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>572.75</v>
+        <v>575.67</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>564.25</v>
-      </c>
-      <c r="N114" s="24" t="inlineStr">
+        <v>568.67</v>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>582.02</v>
+        <v>582.21</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>580.53</v>
+        <v>582.09</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="115">
@@ -7702,54 +7702,54 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.45</v>
+        <v>6.1</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>6.11</v>
+        <v>5.84</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>5.87</v>
+        <v>5.6</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>6.05</v>
+        <v>5.77</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>5.71</v>
+        <v>5.51</v>
       </c>
       <c r="I115" s="17" t="n">
-        <v>5.53</v>
+        <v>5.34</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>5.63</v>
+        <v>5.48</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>5.35</v>
+        <v>5.26</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>5.68</v>
+        <v>5.43</v>
       </c>
       <c r="R115" s="23" t="n">
-        <v>2.34</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>93.67</v>
+        <v>96.94</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>92.02</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>90.64</v>
+        <v>91.61</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>91.55</v>
+        <v>92.05</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>92.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>90.45</v>
+        <v>90.7</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>89.90000000000001</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>88.8</v>
+        <v>87.8</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>89.70999999999999</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>88.33</v>
+        <v>87.56</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>86.68000000000001</v>
-      </c>
-      <c r="N116" s="20" t="inlineStr">
+        <v>84.66</v>
+      </c>
+      <c r="N116" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>90.15000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>89.84</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>91</v>
+        <v>90.5</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>1.62</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="117">
@@ -7826,54 +7826,54 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>9.51</v>
+        <v>9.59</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>9.279999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.130000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="G117" s="15" t="n">
         <v>9.25</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>9.02</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I117" s="17" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="J117" s="17" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="K117" s="18" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="L117" s="19" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="M117" s="19" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="N117" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O117" s="21" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="P117" s="21" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="Q117" s="22" t="n">
         <v>8.9</v>
       </c>
-      <c r="J117" s="17" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="K117" s="18" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="L117" s="19" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="M117" s="19" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="N117" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O117" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="P117" s="21" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="Q117" s="22" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="R117" s="25" t="n">
-        <v>-0.22</v>
+      <c r="R117" s="23" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="118">
@@ -7888,54 +7888,54 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>16.59</v>
+        <v>16.55</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.24</v>
+        <v>16.22</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>15.94</v>
+        <v>15.95</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>16.08</v>
+        <v>15.92</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.22</v>
+        <v>16.14</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>15.87</v>
+        <v>15.81</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>15.73</v>
+        <v>15.59</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.52</v>
+        <v>15.48</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>15.75</v>
+        <v>15.76</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.45</v>
+        <v>15.49</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="N118" s="24" t="inlineStr">
+        <v>15.16</v>
+      </c>
+      <c r="N118" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>15.82</v>
+        <v>15.8</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>15.77</v>
+        <v>15.79</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="R118" s="25" t="n">
-        <v>-0.62</v>
+        <v>15.71</v>
+      </c>
+      <c r="R118" s="23" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="119">
@@ -7950,54 +7950,54 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.02</v>
+        <v>11.03</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>10.82</v>
+        <v>10.86</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>10.66</v>
+        <v>10.71</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.76</v>
+        <v>10.71</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="H119" s="16" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="I119" s="17" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="J119" s="17" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="K119" s="18" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="L119" s="19" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="M119" s="19" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N119" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O119" s="21" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="P119" s="21" t="n">
         <v>10.63</v>
       </c>
-      <c r="I119" s="17" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="J119" s="17" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="K119" s="18" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="L119" s="19" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="M119" s="19" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="N119" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O119" s="21" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="P119" s="21" t="n">
-        <v>10.56</v>
-      </c>
       <c r="Q119" s="22" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="R119" s="25" t="n">
-        <v>-0.09</v>
+        <v>10.6</v>
+      </c>
+      <c r="R119" s="23" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="120">
@@ -8015,51 +8015,51 @@
         <v>12.35</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.11</v>
+        <v>12.18</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>11.91</v>
+        <v>12.03</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.03</v>
+        <v>12.05</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.12</v>
+        <v>12.14</v>
       </c>
       <c r="H120" s="16" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="I120" s="17" t="n">
         <v>11.88</v>
       </c>
-      <c r="I120" s="17" t="n">
+      <c r="J120" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K120" s="18" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="L120" s="19" t="n">
         <v>11.79</v>
       </c>
-      <c r="J120" s="17" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="K120" s="18" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="L120" s="19" t="n">
-        <v>11.57</v>
-      </c>
       <c r="M120" s="19" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="N120" s="20" t="inlineStr">
+        <v>11.62</v>
+      </c>
+      <c r="N120" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.83</v>
+        <v>11.96</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.79</v>
+        <v>11.95</v>
       </c>
       <c r="Q120" s="22" t="n">
         <v>11.95</v>
       </c>
-      <c r="R120" s="23" t="n">
-        <v>0.67</v>
+      <c r="R120" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.63</v>
+        <v>7.31</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.15</v>
+        <v>7.08</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>6.74</v>
+        <v>6.89</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>6.94</v>
+        <v>6.92</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>7.14</v>
+        <v>7.05</v>
       </c>
       <c r="H121" s="16" t="n">
-        <v>6.66</v>
+        <v>6.82</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>6.46</v>
+        <v>6.69</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.18</v>
+        <v>6.59</v>
       </c>
       <c r="K121" s="18" t="n">
-        <v>6.48</v>
+        <v>6.76</v>
       </c>
       <c r="L121" s="19" t="n">
-        <v>6.07</v>
+        <v>6.57</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>5.59</v>
+        <v>6.34</v>
       </c>
       <c r="N121" s="24" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O121" s="21" t="n">
-        <v>6.58</v>
+        <v>6.8</v>
       </c>
       <c r="P121" s="21" t="n">
-        <v>6.51</v>
+        <v>6.78</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="R121" s="25" t="n">
-        <v>-3.57</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>7.18</v>
+        <v>6.84</v>
       </c>
       <c r="D122" s="13" t="n">
-        <v>6.88</v>
+        <v>6.71</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>6.73</v>
+        <v>6.59</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>6.86</v>
+        <v>6.68</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.43</v>
+        <v>6.46</v>
       </c>
       <c r="J122" s="17" t="n">
-        <v>6.26</v>
+        <v>6.42</v>
       </c>
       <c r="K122" s="18" t="n">
-        <v>6.46</v>
+        <v>6.53</v>
       </c>
       <c r="L122" s="19" t="n">
-        <v>6.2</v>
+        <v>6.42</v>
       </c>
       <c r="M122" s="19" t="n">
-        <v>5.9</v>
+        <v>6.29</v>
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O122" s="21" t="n">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="P122" s="21" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>6.6</v>
+        <v>6.51</v>
       </c>
       <c r="R122" s="23" t="n">
-        <v>1.54</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="123">
@@ -8198,54 +8198,54 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>29.72</v>
+        <v>28.74</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>28.66</v>
+        <v>27.96</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>27.77</v>
+        <v>27.31</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>27.89</v>
+        <v>27.3</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>28.47</v>
+        <v>27.78</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>27.41</v>
+        <v>27</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>26.83</v>
+        <v>26.52</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>26.35</v>
+        <v>26.22</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>27.17</v>
+        <v>26.87</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>26.28</v>
+        <v>26.22</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="N123" s="24" t="inlineStr">
+        <v>25.44</v>
+      </c>
+      <c r="N123" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>27.33</v>
+        <v>26.97</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>27.26</v>
+        <v>26.93</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="R123" s="25" t="n">
-        <v>-1.59</v>
+        <v>26.82</v>
+      </c>
+      <c r="R123" s="23" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>162.68</v>
+        <v>165.41</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>160.28</v>
+        <v>161.51</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>158.27</v>
+        <v>158.24</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>158</v>
+        <v>157.8</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>157.2</v>
+        <v>156.5</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>155.6</v>
+        <v>153.9</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>156.93</v>
+        <v>156.06</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>154.92</v>
+        <v>152.79</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>152.52</v>
-      </c>
-      <c r="N124" s="20" t="inlineStr">
+        <v>148.89</v>
+      </c>
+      <c r="N124" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>157.56</v>
+        <v>157.08</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>157.12</v>
+        <v>156.36</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>158.8</v>
+        <v>159.1</v>
       </c>
       <c r="R124" s="25" t="n">
-        <v>-0.13</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="125">
@@ -8322,54 +8322,54 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>54.15</v>
+        <v>53.77</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>52.7</v>
+        <v>52.52</v>
       </c>
       <c r="E125" s="14" t="n">
         <v>51.48</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>52.25</v>
+        <v>51.33</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>52.75</v>
+        <v>52.17</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>51.3</v>
+        <v>50.92</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>50.8</v>
+        <v>50.08</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>49.85</v>
+        <v>49.67</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>50.67</v>
+        <v>50.77</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>49.45</v>
+        <v>49.73</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="N125" s="24" t="inlineStr">
+        <v>48.48</v>
+      </c>
+      <c r="N125" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>51.04</v>
+        <v>50.89</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>50.78</v>
+        <v>50.87</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>51.75</v>
+        <v>50.5</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>0.49</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="126">
@@ -8384,54 +8384,54 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.31</v>
+        <v>14.15</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>13.87</v>
+        <v>13.73</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.5</v>
+        <v>13.38</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.51</v>
+        <v>13.46</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13.34</v>
+        <v>13.26</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.07</v>
+        <v>13.04</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.9</v>
+        <v>12.84</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>13.26</v>
+        <v>13.14</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.89</v>
+        <v>12.79</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="N126" s="24" t="inlineStr">
+        <v>12.37</v>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.31</v>
+        <v>13.22</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.29</v>
+        <v>13.18</v>
       </c>
       <c r="Q126" s="22" t="n">
         <v>13.25</v>
       </c>
       <c r="R126" s="25" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>15.43</v>
+        <v>14.61</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>14.62</v>
+        <v>14.32</v>
       </c>
       <c r="E127" s="14" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="F127" s="15" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G127" s="15" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="H127" s="16" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="I127" s="17" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="J127" s="17" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="K127" s="18" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="L127" s="19" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="M127" s="19" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="N127" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O127" s="21" t="n">
         <v>13.94</v>
       </c>
-      <c r="F127" s="15" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="G127" s="15" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="H127" s="16" t="n">
+      <c r="P127" s="21" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="Q127" s="22" t="n">
         <v>13.85</v>
       </c>
-      <c r="I127" s="17" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="J127" s="17" t="n">
-        <v>13.04</v>
-      </c>
-      <c r="K127" s="18" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="L127" s="19" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="M127" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N127" s="24" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O127" s="21" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="P127" s="21" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="Q127" s="22" t="n">
-        <v>14.12</v>
-      </c>
       <c r="R127" s="23" t="n">
-        <v>0.71</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>6.86</v>
+        <v>6.99</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.61</v>
+        <v>6.75</v>
       </c>
       <c r="E128" s="14" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="F128" s="15" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H128" s="16" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I128" s="17" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="J128" s="17" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K128" s="18" t="n">
         <v>6.41</v>
       </c>
-      <c r="F128" s="15" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="G128" s="15" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="H128" s="16" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="I128" s="17" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="J128" s="17" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="K128" s="18" t="n">
-        <v>6.27</v>
-      </c>
       <c r="L128" s="19" t="n">
-        <v>6.06</v>
+        <v>6.21</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="N128" s="20" t="inlineStr">
+        <v>5.97</v>
+      </c>
+      <c r="N128" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.32</v>
+        <v>6.44</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.28</v>
+        <v>6.43</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.41</v>
+        <v>6.38</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>1.75</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="129">
@@ -8570,54 +8570,54 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.300000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.039999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.18</v>
+        <v>9.23</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="H129" s="16" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I129" s="17" t="n">
-        <v>8.880000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="J129" s="17" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K129" s="18" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="L129" s="19" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="M129" s="19" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K129" s="18" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="L129" s="19" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="M129" s="19" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="N129" s="20" t="inlineStr">
+      <c r="N129" s="24" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>8.949999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="R129" s="23" t="n">
-        <v>1.11</v>
+        <v>9.109999999999999</v>
+      </c>
+      <c r="R129" s="25" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>146.56</v>
+        <v>152.59</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>143.06</v>
+        <v>144.19</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>140.13</v>
+        <v>137.15</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>140.33</v>
+        <v>136.4</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>142.37</v>
+        <v>141.9</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>138.87</v>
+        <v>133.5</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>136.83</v>
+        <v>128</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>135.37</v>
+        <v>125.1</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>138.17</v>
+        <v>132.45</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>135.24</v>
+        <v>125.41</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>131.74</v>
-      </c>
-      <c r="N130" s="24" t="inlineStr">
+        <v>117.01</v>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>138.65</v>
+        <v>133.3</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>138.44</v>
+        <v>133.1</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>138.3</v>
-      </c>
-      <c r="R130" s="25" t="n">
-        <v>-0.5</v>
+        <v>130.9</v>
+      </c>
+      <c r="R130" s="23" t="n">
+        <v>-5.35</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-28</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -758,37 +758,37 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.53</v>
+        <v>20.38</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.35</v>
+        <v>20.25</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.2</v>
+        <v>20.14</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.18</v>
+        <v>20.13</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.3</v>
+        <v>20.21</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.12</v>
+        <v>20.08</v>
       </c>
       <c r="I3" s="17" t="n">
         <v>20</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>19.94</v>
+        <v>19.95</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.1</v>
+        <v>20.07</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>19.95</v>
+        <v>19.96</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="O3" s="21" t="n">
-        <v>20.12</v>
+        <v>20.08</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.11</v>
+        <v>20.08</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.06</v>
+        <v>20.04</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>-0.64</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="4">
@@ -820,37 +820,37 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12.17</v>
+        <v>11.79</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.96</v>
+        <v>11.7</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.78</v>
+        <v>11.62</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.78</v>
+        <v>11.66</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.91</v>
+        <v>11.7</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>11.7</v>
+        <v>11.61</v>
       </c>
       <c r="I4" s="17" t="n">
         <v>11.57</v>
       </c>
       <c r="J4" s="17" t="n">
-        <v>11.49</v>
+        <v>11.52</v>
       </c>
       <c r="K4" s="18" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
       <c r="L4" s="19" t="n">
         <v>11.49</v>
       </c>
       <c r="M4" s="19" t="n">
-        <v>11.28</v>
+        <v>11.4</v>
       </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>11.69</v>
+        <v>11.59</v>
       </c>
       <c r="P4" s="21" t="n">
-        <v>11.68</v>
+        <v>11.58</v>
       </c>
       <c r="Q4" s="22" t="n">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
       <c r="R4" s="23" t="n">
-        <v>-1.69</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="5">
@@ -882,54 +882,54 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>14.96</v>
+        <v>15</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.72</v>
+        <v>14.65</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.81</v>
+        <v>14.78</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.68</v>
+        <v>14.59</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>14.55</v>
+        <v>14.4</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>14.65</v>
+        <v>14.54</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>14.54</v>
+        <v>14.38</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>14.41</v>
-      </c>
-      <c r="N5" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>14.19</v>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O5" s="21" t="n">
-        <v>14.67</v>
+        <v>14.57</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.66</v>
+        <v>14.56</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.66</v>
+        <v>14.59</v>
       </c>
       <c r="R5" s="23" t="n">
-        <v>-0.14</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.76</v>
+        <v>21.39</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>21.28</v>
+        <v>20.96</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20.87</v>
+        <v>20.6</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>20.87</v>
+        <v>20.57</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>21.16</v>
+        <v>20.85</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>20.68</v>
+        <v>20.42</v>
       </c>
       <c r="I6" s="17" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="L6" s="19" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M6" s="19" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="P6" s="21" t="n">
         <v>20.39</v>
       </c>
-      <c r="J6" s="17" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>20.61</v>
-      </c>
-      <c r="L6" s="19" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="M6" s="19" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O6" s="21" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="P6" s="21" t="n">
-        <v>20.64</v>
-      </c>
       <c r="Q6" s="22" t="n">
-        <v>20.57</v>
+        <v>20.3</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>-1.81</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>34.05</v>
+        <v>33.77</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.67</v>
+        <v>33.47</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>33.36</v>
+        <v>33.21</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.41</v>
+        <v>33.35</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>33.61</v>
+        <v>33.47</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>33.23</v>
+        <v>33.17</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>33.03</v>
+        <v>33.05</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>32.85</v>
+        <v>32.87</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>33.14</v>
+        <v>33.05</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>32.83</v>
+        <v>32.79</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.45</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>32.49</v>
+      </c>
+      <c r="N7" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.2</v>
+        <v>33.12</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.17</v>
+        <v>33.07</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="R7" s="23" t="n">
-        <v>-0.48</v>
+        <v>33.24</v>
+      </c>
+      <c r="R7" s="25" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.45</v>
+        <v>23.42</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.17</v>
+        <v>23.16</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>22.94</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>22.96</v>
+        <v>22.98</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>23.12</v>
       </c>
       <c r="H8" s="16" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n">
         <v>22.84</v>
       </c>
-      <c r="I8" s="17" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>22.78</v>
-      </c>
-      <c r="L8" s="19" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
+      <c r="P8" s="21" t="n">
         <v>22.82</v>
       </c>
-      <c r="P8" s="21" t="n">
-        <v>22.8</v>
-      </c>
       <c r="Q8" s="22" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R8" s="23" t="n">
-        <v>-0.78</v>
+        <v>22.84</v>
+      </c>
+      <c r="R8" s="25" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>125.59</v>
+        <v>134.12</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>123.99</v>
+        <v>127.62</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>122.65</v>
+        <v>122.17</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>123</v>
+        <v>122.17</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>123.8</v>
+        <v>126.13</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>122.2</v>
+        <v>119.63</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>121.4</v>
+        <v>115.67</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>120.6</v>
+        <v>113.13</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>121.75</v>
+        <v>118.53</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>120.41</v>
+        <v>113.08</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>118.81</v>
-      </c>
-      <c r="N9" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>106.58</v>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>122.04</v>
+        <v>119.34</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>121.88</v>
+        <v>119.04</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="R9" s="25" t="n">
-        <v>0.16</v>
+        <v>118.2</v>
+      </c>
+      <c r="R9" s="23" t="n">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="10">
@@ -1192,37 +1192,37 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>66.5</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>65.45</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>64.56999999999999</v>
+        <v>63.84</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>64.45</v>
+        <v>63.75</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>65.15000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>63.05</v>
+        <v>62.75</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>63.98</v>
+        <v>63.41</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>63.1</v>
+        <v>62.79</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>62.05</v>
+        <v>62.04</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>64.08</v>
+        <v>63.49</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>64.06</v>
+        <v>63.47</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>63.75</v>
+        <v>63.25</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>-1.54</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="11">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>24.85</v>
+        <v>24.96</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.64</v>
+        <v>24.61</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.46</v>
+        <v>24.31</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.5</v>
+        <v>24.29</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.61</v>
+        <v>24.52</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.4</v>
+        <v>24.17</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>24.29</v>
+        <v>23.94</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>24.19</v>
+        <v>23.82</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.35</v>
+        <v>24.12</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>24.17</v>
+        <v>23.82</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>23.96</v>
+        <v>23.47</v>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.38</v>
+        <v>24.16</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.36</v>
+        <v>24.14</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.39</v>
+        <v>24.07</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="12">
@@ -1319,51 +1319,51 @@
         <v>25.25</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>24.94</v>
+        <v>24.82</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>24.68</v>
+        <v>24.46</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.69</v>
+        <v>24.53</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.87</v>
+        <v>24.75</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>24.56</v>
+        <v>24.32</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>24.38</v>
+        <v>24.1</v>
       </c>
       <c r="J12" s="17" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="P12" s="21" t="n">
         <v>24.25</v>
       </c>
-      <c r="K12" s="18" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="L12" s="19" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>23.94</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O12" s="21" t="n">
-        <v>24.55</v>
-      </c>
-      <c r="P12" s="21" t="n">
-        <v>24.53</v>
-      </c>
       <c r="Q12" s="22" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>-1.01</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="13">
@@ -1378,37 +1378,37 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>42.05</v>
+        <v>41.64</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>41.35</v>
+        <v>40.96</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.77</v>
+        <v>40.39</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>40.85</v>
+        <v>40.41</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>41.23</v>
+        <v>40.81</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>40.53</v>
+        <v>40.13</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>40.15</v>
+        <v>39.73</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.83</v>
+        <v>39.45</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.37</v>
+        <v>40.01</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.79</v>
+        <v>39.44</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>39.09</v>
+        <v>38.76</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.48</v>
+        <v>40.1</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.43</v>
+        <v>40.06</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40.46</v>
+        <v>40</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>-1.65</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.67</v>
+        <v>8.56</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>8.449999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="F14" s="15" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>8.529999999999999</v>
-      </c>
       <c r="H14" s="16" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>8.35</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="K14" s="18" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Q14" s="22" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="L14" s="19" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q14" s="22" t="n">
-        <v>8.4</v>
-      </c>
       <c r="R14" s="23" t="n">
-        <v>-0.24</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>13.84</v>
+        <v>14.09</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>13.69</v>
+        <v>13.75</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.57</v>
+        <v>13.47</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>13.57</v>
+        <v>13.45</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>13.66</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.51</v>
+        <v>13.32</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.42</v>
+        <v>13.11</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>13.36</v>
+        <v>12.98</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.48</v>
+        <v>13.27</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>13.36</v>
+        <v>12.99</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="N15" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>12.65</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.5</v>
+        <v>13.31</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.49</v>
+        <v>13.3</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.48</v>
+        <v>13.23</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>-0.15</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="16">
@@ -1564,37 +1564,37 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>4.08</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>3.97</v>
+        <v>3.84</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>3.9</v>
+        <v>3.69</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="O16" s="21" t="n">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="P16" s="21" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>-1.99</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="17">
@@ -1626,37 +1626,37 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.63</v>
+        <v>17.59</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.28</v>
+        <v>17.07</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>16.98</v>
+        <v>16.64</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>16.97</v>
+        <v>16.58</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17.19</v>
+        <v>16.92</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.84</v>
+        <v>16.4</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.62</v>
+        <v>16.06</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>16.49</v>
+        <v>15.88</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>16.79</v>
+        <v>16.34</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>16.49</v>
+        <v>15.91</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>16.14</v>
+        <v>15.39</v>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.83</v>
+        <v>16.39</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>16.81</v>
+        <v>16.38</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.75</v>
+        <v>16.23</v>
       </c>
       <c r="R17" s="23" t="n">
-        <v>-1.47</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>24.64</v>
+        <v>25.35</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.32</v>
+        <v>24.55</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>24.05</v>
+        <v>23.88</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>24.21</v>
+        <v>23.82</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.32</v>
+        <v>24.34</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>24</v>
+        <v>23.54</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.89</v>
+        <v>23.02</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>23.68</v>
+        <v>22.74</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.87</v>
+        <v>23.44</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>23.6</v>
+        <v>22.77</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="N18" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>21.97</v>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.95</v>
+        <v>23.52</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="R18" s="25" t="n">
-        <v>0.38</v>
+        <v>23.3</v>
+      </c>
+      <c r="R18" s="23" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="19">
@@ -1750,54 +1750,54 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>63</v>
+        <v>63.41</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>62.35</v>
+        <v>62.26</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>61.81</v>
+        <v>61.3</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>62.1</v>
+        <v>61.33</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>62.35</v>
+        <v>62.02</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>61.7</v>
+        <v>60.87</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>61.45</v>
+        <v>60.18</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>61.05</v>
+        <v>59.72</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>61.44</v>
+        <v>60.65</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>60.9</v>
+        <v>59.69</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="N19" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>58.54</v>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
       <c r="P19" s="21" t="n">
-        <v>61.49</v>
+        <v>60.74</v>
       </c>
       <c r="Q19" s="22" t="n">
-        <v>61.85</v>
+        <v>60.65</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>-0.4</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="20">
@@ -1812,37 +1812,37 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>10.92</v>
+        <v>11.21</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.81</v>
+        <v>10.89</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.72</v>
+        <v>10.62</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>10.71</v>
+        <v>10.6</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>10.67</v>
+        <v>10.48</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>10.6</v>
+        <v>10.28</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>10.56</v>
+        <v>10.16</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>10.65</v>
+        <v>10.44</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>10.56</v>
+        <v>10.17</v>
       </c>
       <c r="M20" s="19" t="n">
-        <v>10.45</v>
+        <v>9.85</v>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="O20" s="21" t="n">
-        <v>10.67</v>
+        <v>10.47</v>
       </c>
       <c r="P20" s="21" t="n">
-        <v>10.66</v>
+        <v>10.47</v>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>10.64</v>
+        <v>10.39</v>
       </c>
       <c r="R20" s="23" t="n">
-        <v>-1.02</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="21">
@@ -1874,37 +1874,37 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.63</v>
+        <v>17.04</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>17.24</v>
+        <v>16.83</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>16.91</v>
+        <v>16.65</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>16.87</v>
+        <v>16.64</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>17.13</v>
+        <v>16.77</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>16.74</v>
+        <v>16.56</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>16.48</v>
+        <v>16.43</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>16.35</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.7</v>
+        <v>16.54</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>15.98</v>
+        <v>16.15</v>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
@@ -1912,16 +1912,16 @@
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>16.73</v>
+        <v>16.56</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>16.73</v>
+        <v>16.55</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>16.61</v>
+        <v>16.5</v>
       </c>
       <c r="R21" s="23" t="n">
-        <v>-1.89</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>36.09</v>
+        <v>37.18</v>
       </c>
       <c r="D22" s="13" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="G22" s="15" t="n">
         <v>35.53</v>
       </c>
-      <c r="E22" s="14" t="n">
-        <v>35.06</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>35.48</v>
-      </c>
       <c r="H22" s="16" t="n">
-        <v>34.92</v>
+        <v>34.17</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>34.66</v>
+        <v>33.35</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>34.36</v>
+        <v>32.81</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>34.74</v>
+        <v>33.92</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>34.27</v>
+        <v>32.78</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="N22" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>31.42</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>34.85</v>
+        <v>34.1</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>34.79</v>
+        <v>34.03</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>34.96</v>
+        <v>33.9</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>-0.4</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="23">
@@ -1998,37 +1998,37 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.33</v>
+        <v>16.84</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>15.68</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>15.14</v>
+        <v>14.7</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.08</v>
+        <v>14.61</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>14.86</v>
+        <v>14.2</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>14.43</v>
+        <v>13.45</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>14.21</v>
+        <v>13.04</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>14.77</v>
+        <v>14.06</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>14.23</v>
+        <v>13.08</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>13.58</v>
+        <v>11.92</v>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>14.84</v>
+        <v>14.17</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>14.82</v>
+        <v>14.15</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>14.66</v>
+        <v>13.85</v>
       </c>
       <c r="R23" s="23" t="n">
-        <v>-3.62</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="24">
@@ -2060,37 +2060,37 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>37.69</v>
+        <v>35.62</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>36.47</v>
+        <v>35</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>35.45</v>
+        <v>34.48</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.31</v>
+        <v>34.44</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>36.13</v>
+        <v>34.84</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>34.91</v>
+        <v>34.22</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>34.09</v>
+        <v>33.82</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>33.69</v>
+        <v>33.6</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>34.77</v>
+        <v>34.14</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>33.75</v>
+        <v>33.62</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>32.53</v>
+        <v>33</v>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>34.89</v>
+        <v>34.2</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>34.86</v>
+        <v>34.18</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>34.5</v>
+        <v>34.04</v>
       </c>
       <c r="R24" s="23" t="n">
-        <v>-3.09</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="25">
@@ -2122,37 +2122,37 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>58.57</v>
+        <v>59.07</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.32</v>
+        <v>57.17</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>56.27</v>
+        <v>55.58</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>56.13</v>
+        <v>55.43</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>56.97</v>
+        <v>56.67</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>55.72</v>
+        <v>54.77</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>54.88</v>
+        <v>53.53</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>54.47</v>
+        <v>52.87</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>55.57</v>
+        <v>54.52</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>54.53</v>
+        <v>52.93</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>53.28</v>
+        <v>51.03</v>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -2160,16 +2160,16 @@
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>55.69</v>
+        <v>54.72</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>55.67</v>
+        <v>54.67</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>55.3</v>
+        <v>54.2</v>
       </c>
       <c r="R25" s="23" t="n">
-        <v>-1.25</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="26">
@@ -2184,37 +2184,37 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>218.61</v>
+        <v>221.33</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>209.21</v>
+        <v>205.43</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>201.33</v>
+        <v>192.1</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>201.33</v>
+        <v>190.5</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>207.07</v>
+        <v>201</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>197.67</v>
+        <v>185.1</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>191.93</v>
+        <v>174.6</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>188.27</v>
+        <v>169.2</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>196.07</v>
+        <v>183.2</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>188.19</v>
+        <v>169.87</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>178.79</v>
+        <v>153.97</v>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>197.23</v>
+        <v>184.77</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>196.8</v>
+        <v>184.44</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>195.6</v>
+        <v>180</v>
       </c>
       <c r="R26" s="23" t="n">
-        <v>-3.41</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="27">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>76.13</v>
+        <v>77.94</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>75.03</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>74.11</v>
+        <v>72.61</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>74.08</v>
+        <v>72.52</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>74.77</v>
+        <v>74.33</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>73.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>72.98</v>
+        <v>69.62</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>72.56999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>73.48999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>72.56999999999999</v>
+        <v>68.56</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>71.47</v>
+        <v>65.66</v>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>73.62</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>73.58</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>73.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="R27" s="23" t="n">
-        <v>-1.21</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21.16</v>
+        <v>20.79</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.75</v>
+        <v>20.52</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.41</v>
+        <v>20.29</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.52</v>
+        <v>20.31</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.72</v>
+        <v>20.47</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.31</v>
+        <v>20.2</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.11</v>
+        <v>20.04</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.9</v>
+        <v>19.93</v>
       </c>
       <c r="K28" s="18" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
         <v>20.18</v>
       </c>
-      <c r="L28" s="19" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="N28" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>20.26</v>
-      </c>
       <c r="P28" s="21" t="n">
-        <v>20.21</v>
+        <v>20.16</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="R28" s="25" t="n">
-        <v>0.15</v>
+        <v>20.16</v>
+      </c>
+      <c r="R28" s="23" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="29">
@@ -2370,37 +2370,37 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>78.56</v>
+        <v>75.78</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>76.61</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>74.97</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>74.78</v>
+        <v>73.7</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>76.06999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>74.12</v>
+        <v>73.3</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>72.83</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>72.17</v>
+        <v>72.2</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>73.88</v>
+        <v>73.14</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>72.23999999999999</v>
+        <v>72.22</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>70.29000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
@@ -2408,16 +2408,16 @@
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>74.06999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>74.03</v>
+        <v>73.23</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="R29" s="23" t="n">
-        <v>-3.92</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>29.75</v>
+        <v>29.49</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>28.83</v>
+        <v>28.69</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>28.06</v>
+        <v>28.02</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>27.99</v>
+        <v>28</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>28.59</v>
+        <v>28.5</v>
       </c>
       <c r="H30" s="16" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O30" s="21" t="n">
         <v>27.67</v>
       </c>
-      <c r="I30" s="17" t="n">
-        <v>27.07</v>
-      </c>
-      <c r="J30" s="17" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>27.54</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="N30" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O30" s="21" t="n">
+      <c r="P30" s="21" t="n">
         <v>27.64</v>
       </c>
-      <c r="P30" s="21" t="n">
-        <v>27.61</v>
-      </c>
       <c r="Q30" s="22" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="31">
@@ -2494,37 +2494,37 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>48.57</v>
+        <v>49.12</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>47.97</v>
+        <v>48.08</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.47</v>
+        <v>47.21</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.72</v>
+        <v>47.09</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>47.96</v>
+        <v>47.79</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>47.36</v>
+        <v>46.75</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>47.12</v>
+        <v>46.05</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>46.76</v>
+        <v>45.71</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>47.13</v>
+        <v>46.63</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>46.63</v>
+        <v>45.76</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>46.03</v>
+        <v>44.72</v>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>47.27</v>
+        <v>46.73</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>47.18</v>
+        <v>46.71</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>47.48</v>
+        <v>46.4</v>
       </c>
       <c r="R31" s="23" t="n">
-        <v>-0.34</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="32">
@@ -2556,37 +2556,37 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>129.05</v>
+        <v>126.85</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>126.05</v>
+        <v>123.85</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>123.54</v>
+        <v>121.34</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>124.07</v>
+        <v>121</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>125.63</v>
+        <v>123</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>122.63</v>
+        <v>120</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>121.07</v>
+        <v>118</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>119.63</v>
+        <v>117</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>121.86</v>
+        <v>119.66</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>119.35</v>
+        <v>117.15</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>116.35</v>
+        <v>114.15</v>
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
@@ -2594,16 +2594,16 @@
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>122.36</v>
+        <v>119.95</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>122.09</v>
+        <v>119.89</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>122.5</v>
+        <v>119</v>
       </c>
       <c r="R32" s="23" t="n">
-        <v>-1.21</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="33">
@@ -2618,37 +2618,37 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>57.68</v>
+        <v>56.79</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>55.93</v>
+        <v>54.79</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>54.46</v>
+        <v>53.11</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>54.57</v>
+        <v>53.18</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>55.58</v>
+        <v>54.37</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>53.83</v>
+        <v>52.37</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>52.82</v>
+        <v>51.18</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>52.08</v>
+        <v>50.37</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>53.48</v>
+        <v>51.99</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>52.02</v>
+        <v>50.31</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>50.27</v>
+        <v>48.31</v>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>53.73</v>
+        <v>52.26</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>53.62</v>
+        <v>52.15</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>53.55</v>
+        <v>52</v>
       </c>
       <c r="R33" s="23" t="n">
-        <v>-1.38</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>24.51</v>
+        <v>23.6</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>23.72</v>
+        <v>22.99</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>23.06</v>
+        <v>22.48</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>22.97</v>
+        <v>22.44</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>23.49</v>
+        <v>22.83</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>22.7</v>
+        <v>22.22</v>
       </c>
       <c r="I34" s="17" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="M34" s="19" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O34" s="21" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P34" s="21" t="n">
         <v>22.18</v>
       </c>
-      <c r="J34" s="17" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>21.95</v>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>21.16</v>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O34" s="21" t="n">
-        <v>22.69</v>
-      </c>
-      <c r="P34" s="21" t="n">
-        <v>22.68</v>
-      </c>
       <c r="Q34" s="22" t="n">
-        <v>22.44</v>
+        <v>22.05</v>
       </c>
       <c r="R34" s="23" t="n">
-        <v>-3.03</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>26.17</v>
+        <v>25.88</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.63</v>
+        <v>25.23</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>25.18</v>
+        <v>24.69</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.49</v>
+        <v>25.14</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>24.95</v>
+        <v>24.49</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>24.61</v>
+        <v>24.15</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>24.41</v>
+        <v>23.84</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>24.88</v>
+        <v>24.32</v>
       </c>
       <c r="L35" s="19" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="n">
         <v>24.43</v>
       </c>
-      <c r="M35" s="19" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>24.94</v>
-      </c>
       <c r="P35" s="21" t="n">
-        <v>24.92</v>
+        <v>24.37</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>24.8</v>
+        <v>24.46</v>
       </c>
       <c r="R35" s="23" t="n">
-        <v>-1.59</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="36">
@@ -2804,37 +2804,37 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.23</v>
+        <v>8.07</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.33</v>
+        <v>8.17</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.16</v>
+        <v>8.01</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>8.06</v>
+        <v>7.91</v>
       </c>
       <c r="J36" s="17" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="K36" s="18" t="n">
         <v>7.99</v>
       </c>
-      <c r="K36" s="18" t="n">
-        <v>8.130000000000001</v>
-      </c>
       <c r="L36" s="19" t="n">
-        <v>7.98</v>
+        <v>7.85</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>7.81</v>
+        <v>7.69</v>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>8.15</v>
+        <v>8</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>8.130000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="R36" s="23" t="n">
-        <v>-1.45</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="37">
@@ -2866,37 +2866,37 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>33.17</v>
+        <v>33.11</v>
       </c>
       <c r="D37" s="13" t="n">
         <v>32.51</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>31.95</v>
+        <v>32.01</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>31.92</v>
+        <v>31.97</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>32.34</v>
+        <v>32.35</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>31.68</v>
+        <v>31.75</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>31.26</v>
+        <v>31.37</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.02</v>
+        <v>31.15</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>31.59</v>
+        <v>31.67</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.03</v>
+        <v>31.17</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.37</v>
+        <v>30.57</v>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.66</v>
+        <v>31.74</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.64</v>
+        <v>31.72</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="R37" s="23" t="n">
-        <v>-0.63</v>
+        <v>31.58</v>
+      </c>
+      <c r="R37" s="25" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>180.2</v>
+        <v>178.13</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>176</v>
+        <v>174.03</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>172.48</v>
+        <v>170.6</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>173.67</v>
+        <v>171.2</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>175.63</v>
+        <v>173.4</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>171.43</v>
+        <v>169.3</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>169.47</v>
+        <v>167.1</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>167.23</v>
+        <v>165.2</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>170.12</v>
+        <v>168.3</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>166.6</v>
+        <v>164.87</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>162.4</v>
-      </c>
-      <c r="N38" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>160.77</v>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>170.94</v>
+        <v>168.96</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>170.45</v>
+        <v>168.62</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>171.7</v>
-      </c>
-      <c r="R38" s="25" t="n">
-        <v>0.64</v>
+        <v>169</v>
+      </c>
+      <c r="R38" s="23" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="39">
@@ -2990,37 +2990,37 @@
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>13.26</v>
+        <v>12.74</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>12.82</v>
+        <v>12.44</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>12.45</v>
+        <v>12.18</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>12.42</v>
+        <v>12.18</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>12.7</v>
+        <v>12.37</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>12.26</v>
+        <v>12.07</v>
       </c>
       <c r="I39" s="17" t="n">
-        <v>11.98</v>
+        <v>11.88</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>11.82</v>
+        <v>11.77</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>12.21</v>
+        <v>12.02</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>11.84</v>
+        <v>11.76</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>11.4</v>
+        <v>11.46</v>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
@@ -3028,16 +3028,16 @@
         </is>
       </c>
       <c r="O39" s="21" t="n">
-        <v>12.25</v>
+        <v>12.05</v>
       </c>
       <c r="P39" s="21" t="n">
-        <v>12.24</v>
+        <v>12.04</v>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="R39" s="23" t="n">
-        <v>-3.73</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="40">
@@ -3052,37 +3052,37 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>21.17</v>
+        <v>21.9</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>20.77</v>
+        <v>20.95</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>20.43</v>
+        <v>20.15</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>20.41</v>
+        <v>20.34</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>20.67</v>
+        <v>20.83</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>20.27</v>
+        <v>19.88</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>20.01</v>
+        <v>19.39</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>19.87</v>
+        <v>18.93</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>20.21</v>
+        <v>19.62</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>19.87</v>
+        <v>18.82</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>19.47</v>
+        <v>17.87</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>20.25</v>
+        <v>19.78</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>20.24</v>
+        <v>19.69</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>20.16</v>
+        <v>19.86</v>
       </c>
       <c r="R40" s="23" t="n">
-        <v>-1.66</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>192.7</v>
+        <v>188.95</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>185.9</v>
+        <v>185.15</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>180.2</v>
+        <v>181.96</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>182.23</v>
+        <v>182.87</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>185.37</v>
+        <v>184.73</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>178.57</v>
+        <v>180.93</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>175.43</v>
+        <v>179.07</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>171.77</v>
+        <v>177.13</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>176.4</v>
+        <v>179.84</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>170.7</v>
+        <v>176.65</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>172.85</v>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>177.75</v>
+        <v>180.53</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>176.93</v>
+        <v>180.13</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>179.1</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>-0.67</v>
+        <v>181</v>
+      </c>
+      <c r="R41" s="25" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="42">
@@ -3176,37 +3176,37 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>37.23</v>
+        <v>36.25</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>36.57</v>
+        <v>35.85</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>36.01</v>
+        <v>35.51</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>35.95</v>
+        <v>35.64</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>36.39</v>
+        <v>35.82</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>35.73</v>
+        <v>35.42</v>
       </c>
       <c r="I42" s="17" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K42" s="18" t="n">
         <v>35.29</v>
       </c>
-      <c r="J42" s="17" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>35.65</v>
-      </c>
       <c r="L42" s="19" t="n">
-        <v>35.09</v>
+        <v>34.95</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>34.43</v>
+        <v>34.55</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>35.71</v>
+        <v>35.37</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>35.7</v>
+        <v>35.32</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>35.52</v>
+        <v>35.46</v>
       </c>
       <c r="R42" s="23" t="n">
-        <v>-1.82</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="43">
@@ -3238,37 +3238,37 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>29.31</v>
+        <v>28.37</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>28.55</v>
+        <v>27.77</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>27.91</v>
+        <v>27.27</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.85</v>
+        <v>27.32</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>28.35</v>
+        <v>27.66</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.59</v>
+        <v>27.06</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>27.09</v>
+        <v>26.72</v>
       </c>
       <c r="J43" s="17" t="n">
-        <v>26.83</v>
+        <v>26.46</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>27.49</v>
+        <v>26.93</v>
       </c>
       <c r="L43" s="19" t="n">
-        <v>26.85</v>
+        <v>26.43</v>
       </c>
       <c r="M43" s="19" t="n">
-        <v>26.09</v>
+        <v>25.83</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="O43" s="21" t="n">
-        <v>27.57</v>
+        <v>27.02</v>
       </c>
       <c r="P43" s="21" t="n">
-        <v>27.55</v>
+        <v>26.98</v>
       </c>
       <c r="Q43" s="22" t="n">
-        <v>27.36</v>
+        <v>26.98</v>
       </c>
       <c r="R43" s="23" t="n">
-        <v>-0.58</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="44">
@@ -3300,37 +3300,37 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.46</v>
+        <v>26.28</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>26.1</v>
+        <v>25.86</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.8</v>
+        <v>25.51</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.77</v>
+        <v>25.46</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26.01</v>
+        <v>25.74</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.65</v>
+        <v>25.32</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.41</v>
+        <v>25.04</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>25.29</v>
+        <v>24.9</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>25.6</v>
+        <v>25.27</v>
       </c>
       <c r="L44" s="19" t="n">
-        <v>25.3</v>
+        <v>24.92</v>
       </c>
       <c r="M44" s="19" t="n">
-        <v>24.94</v>
+        <v>24.5</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -3338,16 +3338,16 @@
         </is>
       </c>
       <c r="O44" s="21" t="n">
-        <v>25.64</v>
+        <v>25.31</v>
       </c>
       <c r="P44" s="21" t="n">
-        <v>25.63</v>
+        <v>25.31</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.54</v>
+        <v>25.18</v>
       </c>
       <c r="R44" s="23" t="n">
-        <v>-1.08</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.7</v>
+        <v>7.87</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.57</v>
+        <v>7.66</v>
       </c>
       <c r="E45" s="14" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="F45" s="15" t="n">
         <v>7.46</v>
       </c>
-      <c r="F45" s="15" t="n">
-        <v>7.47</v>
-      </c>
       <c r="G45" s="15" t="n">
-        <v>7.54</v>
+        <v>7.6</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.34</v>
+        <v>7.25</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.28</v>
+        <v>7.18</v>
       </c>
       <c r="K45" s="18" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="n">
         <v>7.39</v>
       </c>
-      <c r="L45" s="19" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="N45" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O45" s="21" t="n">
-        <v>7.41</v>
-      </c>
       <c r="P45" s="21" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="Q45" s="22" t="n">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>-0.27</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>12.38</v>
+        <v>11.92</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>12.02</v>
+        <v>11.69</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.72</v>
+        <v>11.5</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.68</v>
+        <v>11.47</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.92</v>
+        <v>11.63</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.56</v>
+        <v>11.4</v>
       </c>
       <c r="I46" s="17" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="L46" s="19" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="M46" s="19" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O46" s="21" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="P46" s="21" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="Q46" s="22" t="n">
         <v>11.32</v>
       </c>
-      <c r="J46" s="17" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="L46" s="19" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O46" s="21" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="P46" s="21" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="Q46" s="22" t="n">
-        <v>11.44</v>
-      </c>
       <c r="R46" s="23" t="n">
-        <v>-3.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="47">
@@ -3486,37 +3486,37 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>197.11</v>
+        <v>190.78</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>193.21</v>
+        <v>188.38</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>189.94</v>
+        <v>186.37</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>189.5</v>
+        <v>186.43</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>192.1</v>
+        <v>187.87</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>188.2</v>
+        <v>185.47</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>185.6</v>
+        <v>184.03</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>184.3</v>
+        <v>183.07</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>187.76</v>
+        <v>185.03</v>
       </c>
       <c r="L47" s="19" t="n">
-        <v>184.49</v>
+        <v>183.02</v>
       </c>
       <c r="M47" s="19" t="n">
-        <v>180.59</v>
+        <v>180.62</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -3524,16 +3524,16 @@
         </is>
       </c>
       <c r="O47" s="21" t="n">
-        <v>188.13</v>
+        <v>185.34</v>
       </c>
       <c r="P47" s="21" t="n">
-        <v>188.06</v>
+        <v>185.22</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>186.9</v>
+        <v>185</v>
       </c>
       <c r="R47" s="23" t="n">
-        <v>-1.58</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>45.23</v>
+        <v>44.63</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>44.43</v>
+        <v>43.93</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>43.76</v>
+        <v>43.35</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>43.73</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>44.23</v>
+        <v>43.97</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>43.43</v>
+        <v>43.27</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>42.93</v>
+        <v>43.03</v>
       </c>
       <c r="J48" s="17" t="n">
-        <v>42.63</v>
+        <v>42.57</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>43.32</v>
+        <v>42.95</v>
       </c>
       <c r="L48" s="19" t="n">
-        <v>42.65</v>
+        <v>42.37</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>41.85</v>
-      </c>
-      <c r="N48" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>41.67</v>
+      </c>
+      <c r="N48" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>43.41</v>
+        <v>43.14</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>43.38</v>
+        <v>43.01</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="R48" s="23" t="n">
-        <v>-0.92</v>
+        <v>43.5</v>
+      </c>
+      <c r="R48" s="25" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>34.23</v>
+        <v>34.06</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>33.27</v>
+        <v>33.22</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>32.47</v>
+        <v>32.52</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>32.92</v>
+        <v>32.63</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>33.28</v>
+        <v>33.09</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>32.32</v>
+        <v>32.25</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.96</v>
+        <v>31.79</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.36</v>
+        <v>31.41</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>31.93</v>
+        <v>32.04</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>31.13</v>
+        <v>31.34</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="N49" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>30.5</v>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>32.16</v>
+        <v>32.18</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>32.01</v>
+        <v>32.11</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="R49" s="25" t="n">
-        <v>2.58</v>
+        <v>32.18</v>
+      </c>
+      <c r="R49" s="23" t="n">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="50">
@@ -3672,37 +3672,37 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.62</v>
+        <v>12.5</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.45</v>
+        <v>12.33</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>12.3</v>
+        <v>12.18</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>12.29</v>
+        <v>12.16</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>12.4</v>
+        <v>12.28</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>12.23</v>
+        <v>12.11</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>12.12</v>
+        <v>11.99</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>12.06</v>
+        <v>11.94</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>12.21</v>
+        <v>12.09</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>12.06</v>
+        <v>11.94</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>11.89</v>
+        <v>11.77</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12.23</v>
+        <v>12.1</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>12.22</v>
+        <v>12.1</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.18</v>
+        <v>12.05</v>
       </c>
       <c r="R50" s="23" t="n">
-        <v>-1.38</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="51">
@@ -3734,37 +3734,37 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>62.8</v>
+        <v>60.53</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>60.3</v>
+        <v>58.13</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>58.2</v>
+        <v>56.12</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>58.08</v>
+        <v>55.95</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>59.67</v>
+        <v>57.5</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>57.17</v>
+        <v>55.1</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>55.58</v>
+        <v>53.55</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>54.67</v>
+        <v>52.7</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>56.8</v>
+        <v>54.78</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>54.7</v>
+        <v>52.77</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>52.2</v>
+        <v>50.37</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
@@ -3772,16 +3772,16 @@
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>57.08</v>
+        <v>55.03</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>56.99</v>
+        <v>54.97</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>56.5</v>
+        <v>54.4</v>
       </c>
       <c r="R51" s="23" t="n">
-        <v>-3.09</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.93</v>
+        <v>22.72</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.52</v>
+        <v>22.24</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>22.18</v>
+        <v>21.83</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>22.21</v>
+        <v>21.78</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.44</v>
+        <v>22.1</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22.03</v>
+        <v>21.62</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.62</v>
+        <v>21.14</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.95</v>
+        <v>21.57</v>
       </c>
       <c r="L52" s="19" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O52" s="21" t="n">
         <v>21.61</v>
       </c>
-      <c r="M52" s="19" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N52" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O52" s="21" t="n">
-        <v>22.01</v>
-      </c>
       <c r="P52" s="21" t="n">
-        <v>21.98</v>
+        <v>21.6</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="R52" s="25" t="n">
-        <v>0.09</v>
+        <v>21.46</v>
+      </c>
+      <c r="R52" s="23" t="n">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="53">
@@ -3858,37 +3858,37 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.15</v>
+        <v>5.21</v>
       </c>
       <c r="D53" s="13" t="n">
         <v>5.09</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>5.04</v>
+        <v>4.99</v>
       </c>
       <c r="G53" s="15" t="n">
         <v>5.07</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>5.01</v>
+        <v>4.95</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>4.98</v>
+        <v>4.87</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>4.95</v>
+        <v>4.83</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="L53" s="19" t="n">
-        <v>4.95</v>
+        <v>4.83</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>4.89</v>
+        <v>4.71</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="O53" s="21" t="n">
-        <v>5.01</v>
+        <v>4.94</v>
       </c>
       <c r="P53" s="21" t="n">
-        <v>5.01</v>
+        <v>4.94</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="R53" s="23" t="n">
-        <v>-1.19</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="54">
@@ -3920,37 +3920,37 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>18.11</v>
+        <v>19.44</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>17.69</v>
+        <v>18.51</v>
       </c>
       <c r="E54" s="14" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="H54" s="16" t="n">
         <v>17.34</v>
       </c>
-      <c r="F54" s="15" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="G54" s="15" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>17.26</v>
-      </c>
       <c r="I54" s="17" t="n">
-        <v>17.1</v>
+        <v>16.75</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>16.84</v>
+        <v>16.41</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.1</v>
+        <v>17.21</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.75</v>
+        <v>16.44</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>16.33</v>
+        <v>15.51</v>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.2</v>
+        <v>17.32</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.14</v>
+        <v>17.29</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="R54" s="25" t="n">
-        <v>0.17</v>
+        <v>17.08</v>
+      </c>
+      <c r="R54" s="23" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>95.3</v>
+        <v>100.2</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>93.84999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>92.63</v>
+        <v>95.14</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>92.47</v>
+        <v>96.63</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>93.43000000000001</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>91.98</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>91.02</v>
+        <v>93.88</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>90.53</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>91.81999999999999</v>
+        <v>93.61</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>90.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>89.15000000000001</v>
-      </c>
-      <c r="N55" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>88.55</v>
+      </c>
+      <c r="N55" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>91.95999999999999</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>91.93000000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="R55" s="23" t="n">
-        <v>-1.08</v>
+        <v>95.7</v>
+      </c>
+      <c r="R55" s="25" t="n">
+        <v>4.59</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>17.35</v>
+        <v>17.38</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>16.97</v>
+        <v>16.87</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>16.66</v>
+        <v>16.44</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>16.62</v>
+        <v>16.55</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>16.87</v>
+        <v>16.81</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>16.49</v>
+        <v>16.3</v>
       </c>
       <c r="I56" s="17" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="K56" s="18" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O56" s="21" t="n">
         <v>16.24</v>
       </c>
-      <c r="J56" s="17" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="K56" s="18" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O56" s="21" t="n">
-        <v>16.48</v>
-      </c>
       <c r="P56" s="21" t="n">
-        <v>16.47</v>
+        <v>16.19</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="R56" s="25" t="n">
-        <v>0.12</v>
+        <v>16.3</v>
+      </c>
+      <c r="R56" s="23" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="57">
@@ -4106,37 +4106,37 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.48</v>
+        <v>21.08</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>21.03</v>
+        <v>20.63</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.65</v>
+        <v>20.25</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.61</v>
+        <v>20.27</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.9</v>
+        <v>20.53</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.45</v>
+        <v>20.08</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>20.16</v>
+        <v>19.82</v>
       </c>
       <c r="J57" s="17" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="K57" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="K57" s="18" t="n">
-        <v>20.4</v>
-      </c>
       <c r="L57" s="19" t="n">
-        <v>20.02</v>
+        <v>19.62</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>19.57</v>
+        <v>19.17</v>
       </c>
       <c r="N57" s="20" t="inlineStr">
         <is>
@@ -4144,16 +4144,16 @@
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.44</v>
+        <v>20.06</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.43</v>
+        <v>20.03</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20.31</v>
+        <v>20</v>
       </c>
       <c r="R57" s="23" t="n">
-        <v>-1.88</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="58">
@@ -4168,37 +4168,37 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.62</v>
+        <v>22.83</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>22.11</v>
+        <v>21.89</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>22.14</v>
+        <v>21.88</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.29</v>
+        <v>22.19</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>22.01</v>
+        <v>21.68</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>21.86</v>
+        <v>21.37</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>21.73</v>
+        <v>21.17</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>21.95</v>
+        <v>21.6</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>21.72</v>
+        <v>21.17</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>21.44</v>
+        <v>20.66</v>
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
@@ -4206,16 +4206,16 @@
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>21.99</v>
+        <v>21.66</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>21.97</v>
+        <v>21.64</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>21.98</v>
+        <v>21.56</v>
       </c>
       <c r="R58" s="23" t="n">
-        <v>-0.54</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="59">
@@ -4230,37 +4230,37 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.65</v>
+        <v>28.42</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>28.09</v>
+        <v>27.7</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.62</v>
+        <v>27.1</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.58</v>
+        <v>27.02</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27.94</v>
+        <v>27.5</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>27.38</v>
+        <v>26.78</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>27.02</v>
+        <v>26.3</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>26.82</v>
+        <v>26.06</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>26.83</v>
+        <v>26.1</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>26.27</v>
+        <v>25.38</v>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
@@ -4268,16 +4268,16 @@
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>27.36</v>
+        <v>26.77</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>27.35</v>
+        <v>26.75</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>27.22</v>
+        <v>26.54</v>
       </c>
       <c r="R59" s="23" t="n">
-        <v>-1.87</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>44.87</v>
+        <v>44.29</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>44.37</v>
+        <v>43.91</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>43.95</v>
+        <v>43.6</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>43.92</v>
+        <v>43.55</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>44.24</v>
+        <v>43.81</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>43.74</v>
+        <v>43.43</v>
       </c>
       <c r="I60" s="17" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="K60" s="18" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O60" s="21" t="n">
         <v>43.42</v>
       </c>
-      <c r="J60" s="17" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="K60" s="18" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="L60" s="19" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O60" s="21" t="n">
-        <v>43.72</v>
-      </c>
       <c r="P60" s="21" t="n">
-        <v>43.71</v>
+        <v>43.41</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="R60" s="23" t="n">
-        <v>-0.68</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>19.03</v>
+        <v>18.42</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.61</v>
+        <v>18.16</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>18.26</v>
+        <v>17.94</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18.21</v>
+        <v>18</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.49</v>
+        <v>18.13</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>18.07</v>
+        <v>17.87</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>17.79</v>
+        <v>17.74</v>
       </c>
       <c r="J61" s="17" t="n">
-        <v>17.65</v>
+        <v>17.61</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>18.02</v>
+        <v>17.8</v>
       </c>
       <c r="L61" s="19" t="n">
-        <v>17.67</v>
+        <v>17.58</v>
       </c>
       <c r="M61" s="19" t="n">
-        <v>17.25</v>
+        <v>17.32</v>
       </c>
       <c r="N61" s="20" t="inlineStr">
         <is>
@@ -4392,16 +4392,16 @@
         </is>
       </c>
       <c r="O61" s="21" t="n">
-        <v>18.06</v>
+        <v>17.84</v>
       </c>
       <c r="P61" s="21" t="n">
-        <v>18.06</v>
+        <v>17.82</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>17.93</v>
+        <v>17.87</v>
       </c>
       <c r="R61" s="23" t="n">
-        <v>-2.02</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.76</v>
+        <v>15.29</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>15.34</v>
+        <v>14.95</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>14.99</v>
+        <v>14.67</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>14.97</v>
+        <v>14.63</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>15.23</v>
+        <v>14.85</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.81</v>
+        <v>14.51</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.55</v>
+        <v>14.29</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.39</v>
+        <v>14.17</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.75</v>
+        <v>14.47</v>
       </c>
       <c r="L62" s="19" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O62" s="21" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="P62" s="21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q62" s="22" t="n">
         <v>14.4</v>
       </c>
-      <c r="M62" s="19" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O62" s="21" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="P62" s="21" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="Q62" s="22" t="n">
-        <v>14.7</v>
-      </c>
       <c r="R62" s="23" t="n">
-        <v>-1.54</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="63">
@@ -4478,37 +4478,37 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.45</v>
+        <v>24.61</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.16</v>
+        <v>24.07</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>23.92</v>
+        <v>23.62</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>23.92</v>
+        <v>23.63</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>24.09</v>
+        <v>23.95</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.8</v>
+        <v>23.41</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.63</v>
+        <v>23.09</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>23.51</v>
+        <v>22.87</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.75</v>
+        <v>23.32</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>23.51</v>
+        <v>22.87</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>23.22</v>
+        <v>22.33</v>
       </c>
       <c r="N63" s="20" t="inlineStr">
         <is>
@@ -4516,16 +4516,16 @@
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.79</v>
+        <v>23.39</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.78</v>
+        <v>23.36</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>23.74</v>
+        <v>23.3</v>
       </c>
       <c r="R63" s="23" t="n">
-        <v>-0.88</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.14</v>
+        <v>7.16</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.05</v>
+        <v>7.01</v>
       </c>
       <c r="F64" s="15" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>7.03</v>
+        <v>6.99</v>
       </c>
       <c r="I64" s="17" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J64" s="17" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="K64" s="18" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Q64" s="22" t="n">
         <v>6.99</v>
       </c>
-      <c r="J64" s="17" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="K64" s="18" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="P64" s="21" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="Q64" s="22" t="n">
-        <v>7.01</v>
-      </c>
       <c r="R64" s="23" t="n">
-        <v>-0.71</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="65">
@@ -4602,54 +4602,54 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="D65" s="13" t="n">
         <v>4.85</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>4.81</v>
+        <v>4.79</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.76</v>
+        <v>4.71</v>
       </c>
       <c r="J65" s="17" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="K65" s="18" t="n">
         <v>4.74</v>
       </c>
-      <c r="K65" s="18" t="n">
-        <v>4.78</v>
-      </c>
       <c r="L65" s="19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M65" s="19" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O65" s="21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P65" s="21" t="n">
         <v>4.74</v>
       </c>
-      <c r="M65" s="19" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O65" s="21" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="P65" s="21" t="n">
-        <v>4.78</v>
-      </c>
       <c r="Q65" s="22" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="R65" s="23" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.48</v>
+        <v>4.57</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="G66" s="15" t="n">
         <v>4.41</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="J66" s="17" t="n">
-        <v>4.29</v>
+        <v>4.15</v>
       </c>
       <c r="K66" s="18" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="N66" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>4.02</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
-        <v>4.35</v>
+        <v>4.27</v>
       </c>
       <c r="P66" s="21" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="R66" s="25" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.24</v>
+      </c>
+      <c r="R66" s="23" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>64.79000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>63.99</v>
+        <v>63.83</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>63.32</v>
+        <v>62.7</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>63.63</v>
+        <v>62.65</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>63.97</v>
+        <v>63.5</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>63.17</v>
+        <v>62.15</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>62.83</v>
+        <v>61.3</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>62.37</v>
+        <v>60.8</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>62.88</v>
+        <v>61.95</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>62.21</v>
+        <v>60.82</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>61.41</v>
-      </c>
-      <c r="N67" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>59.47</v>
+      </c>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>63.05</v>
+        <v>62.1</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>62.94</v>
+        <v>62.05</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="R67" s="25" t="n">
-        <v>0</v>
+        <v>61.8</v>
+      </c>
+      <c r="R67" s="23" t="n">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="68">
@@ -4788,37 +4788,37 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>70.23</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>66.38</v>
+        <v>63.28</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>63.15</v>
+        <v>61.48</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>63.58</v>
+        <v>61.37</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>65.72</v>
+        <v>62.73</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>61.87</v>
+        <v>60.58</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>59.73</v>
+        <v>59.22</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>58.02</v>
+        <v>58.43</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>61</v>
+        <v>60.27</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>57.77</v>
+        <v>58.47</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>53.92</v>
+        <v>56.32</v>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
@@ -4826,16 +4826,16 @@
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>61.58</v>
+        <v>60.51</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>61.3</v>
+        <v>60.44</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>61.45</v>
+        <v>60</v>
       </c>
       <c r="R68" s="23" t="n">
-        <v>-2.31</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="69">
@@ -4850,37 +4850,37 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>79.48999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>77.48999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>75.81</v>
+        <v>74.63</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>76.18000000000001</v>
+        <v>75.17</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>77.22</v>
+        <v>76.33</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>75.22</v>
+        <v>73.98</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>74.18000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>73.22</v>
+        <v>71.63</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>74.69</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>73.01000000000001</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>71.01000000000001</v>
+        <v>69</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
@@ -4888,16 +4888,16 @@
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>75.03</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>74.84999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>75.15000000000001</v>
+        <v>74</v>
       </c>
       <c r="R69" s="23" t="n">
-        <v>-1.51</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="70">
@@ -4912,37 +4912,37 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>119.68</v>
+        <v>117.31</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>116.48</v>
+        <v>114.71</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>113.8</v>
+        <v>112.53</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>113.97</v>
+        <v>112.57</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>115.83</v>
+        <v>114.13</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>112.63</v>
+        <v>111.53</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>110.77</v>
+        <v>109.97</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>109.43</v>
+        <v>108.93</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>112</v>
+        <v>111.07</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>109.32</v>
+        <v>108.89</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>106.12</v>
+        <v>106.29</v>
       </c>
       <c r="N70" s="20" t="inlineStr">
         <is>
@@ -4950,16 +4950,16 @@
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>112.44</v>
+        <v>111.4</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>112.25</v>
+        <v>111.27</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>112.1</v>
+        <v>111</v>
       </c>
       <c r="R70" s="23" t="n">
-        <v>-0.71</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="71">
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.44</v>
+        <v>23.47</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.17</v>
+        <v>23.05</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>22.94</v>
+        <v>22.7</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>22.94</v>
+        <v>22.72</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>23.11</v>
+        <v>22.97</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>22.84</v>
+        <v>22.55</v>
       </c>
       <c r="I71" s="17" t="n">
-        <v>22.67</v>
+        <v>22.3</v>
       </c>
       <c r="J71" s="17" t="n">
-        <v>22.57</v>
+        <v>22.13</v>
       </c>
       <c r="K71" s="18" t="n">
-        <v>22.79</v>
+        <v>22.46</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>22.56</v>
+        <v>22.11</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>22.29</v>
+        <v>21.69</v>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
@@ -5012,16 +5012,16 @@
         </is>
       </c>
       <c r="O71" s="21" t="n">
-        <v>22.82</v>
+        <v>22.52</v>
       </c>
       <c r="P71" s="21" t="n">
-        <v>22.81</v>
+        <v>22.5</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>22.78</v>
+        <v>22.48</v>
       </c>
       <c r="R71" s="23" t="n">
-        <v>-0.91</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="72">
@@ -5036,37 +5036,37 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>20.06</v>
+        <v>18.86</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.9</v>
+        <v>18.32</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>17.92</v>
+        <v>17.87</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>18.23</v>
+        <v>17.88</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.78</v>
+        <v>18.2</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.62</v>
+        <v>17.66</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.07</v>
+        <v>17.34</v>
       </c>
       <c r="J72" s="17" t="n">
-        <v>16.46</v>
+        <v>17.12</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>17.28</v>
+        <v>17.57</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>16.3</v>
+        <v>17.12</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>15.14</v>
+        <v>16.58</v>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
@@ -5074,16 +5074,16 @@
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.49</v>
+        <v>17.64</v>
       </c>
       <c r="P72" s="21" t="n">
-        <v>17.37</v>
+        <v>17.61</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.67</v>
+        <v>17.55</v>
       </c>
       <c r="R72" s="23" t="n">
-        <v>-0.95</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="73">
@@ -5098,37 +5098,37 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>228.26</v>
+        <v>229.31</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>226.06</v>
+        <v>225.41</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>224.22</v>
+        <v>222.14</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>224.3</v>
+        <v>221.9</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>225.6</v>
+        <v>224.4</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>223.4</v>
+        <v>220.5</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>222.1</v>
+        <v>218</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>221.2</v>
+        <v>216.6</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>222.98</v>
+        <v>219.96</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>221.14</v>
+        <v>216.69</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>218.94</v>
+        <v>212.79</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>223.28</v>
+        <v>220.38</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>223.16</v>
+        <v>220.26</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>223</v>
-      </c>
-      <c r="R73" s="25" t="n">
-        <v>0</v>
+        <v>219.4</v>
+      </c>
+      <c r="R73" s="23" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="74">
@@ -5160,37 +5160,37 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.53</v>
+        <v>15.51</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.31</v>
+        <v>15.27</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.34</v>
+        <v>15.27</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.49</v>
+        <v>15.45</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.23</v>
+        <v>15.16</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>15.08</v>
+        <v>14.98</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>14.97</v>
+        <v>14.87</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.17</v>
+        <v>15.1</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>14.95</v>
+        <v>14.86</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>14.69</v>
+        <v>14.57</v>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
@@ -5198,16 +5198,16 @@
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.21</v>
+        <v>15.14</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.19</v>
+        <v>15.13</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="R74" s="23" t="n">
-        <v>-0.52</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="75">
@@ -5222,37 +5222,37 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>36.99</v>
+        <v>37.46</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>36.69</v>
+        <v>37.1</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.43</v>
+        <v>36.8</v>
       </c>
       <c r="F75" s="15" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="I75" s="17" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="J75" s="17" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="K75" s="18" t="n">
         <v>36.6</v>
       </c>
-      <c r="G75" s="15" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="H75" s="16" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="I75" s="17" t="n">
+      <c r="L75" s="19" t="n">
         <v>36.3</v>
       </c>
-      <c r="J75" s="17" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="K75" s="18" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="L75" s="19" t="n">
-        <v>36.01</v>
-      </c>
       <c r="M75" s="19" t="n">
-        <v>35.71</v>
+        <v>35.94</v>
       </c>
       <c r="N75" s="24" t="inlineStr">
         <is>
@@ -5260,16 +5260,16 @@
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>36.34</v>
+        <v>36.65</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>36.29</v>
+        <v>36.63</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
       <c r="C76" s="13" t="n">
-        <v>23.28</v>
+        <v>23.12</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>23.02</v>
+        <v>22.96</v>
       </c>
       <c r="E76" s="14" t="n">
-        <v>22.8</v>
+        <v>22.82</v>
       </c>
       <c r="F76" s="15" t="n">
-        <v>22.95</v>
+        <v>22.81</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>23.03</v>
+        <v>22.91</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>22.77</v>
+        <v>22.75</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>22.69</v>
+        <v>22.65</v>
       </c>
       <c r="J76" s="17" t="n">
-        <v>22.51</v>
+        <v>22.59</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="L76" s="19" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M76" s="19" t="n">
         <v>22.44</v>
       </c>
-      <c r="M76" s="19" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="N76" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+      <c r="N76" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O76" s="21" t="n">
-        <v>22.73</v>
+        <v>22.75</v>
       </c>
       <c r="P76" s="21" t="n">
-        <v>22.68</v>
+        <v>22.75</v>
       </c>
       <c r="Q76" s="22" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="R76" s="25" t="n">
-        <v>0</v>
+        <v>22.7</v>
+      </c>
+      <c r="R76" s="23" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="77">
@@ -5346,37 +5346,37 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>41.92</v>
+        <v>42.47</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>41.44</v>
+        <v>41.49</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>41.03</v>
+        <v>40.66</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>41.06</v>
+        <v>40.85</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>40.86</v>
+        <v>40.37</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>40.58</v>
+        <v>39.87</v>
       </c>
       <c r="J77" s="17" t="n">
-        <v>40.38</v>
+        <v>39.39</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>40.77</v>
+        <v>40.12</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>40.36</v>
+        <v>39.29</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>39.88</v>
+        <v>38.31</v>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         </is>
       </c>
       <c r="O77" s="21" t="n">
-        <v>40.83</v>
+        <v>40.28</v>
       </c>
       <c r="P77" s="21" t="n">
-        <v>40.8</v>
+        <v>40.19</v>
       </c>
       <c r="Q77" s="22" t="n">
-        <v>40.78</v>
+        <v>40.34</v>
       </c>
       <c r="R77" s="23" t="n">
-        <v>-0.73</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="78">
@@ -5408,54 +5408,54 @@
         </is>
       </c>
       <c r="C78" s="13" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>5.28</v>
       </c>
       <c r="E78" s="14" t="n">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
       <c r="F78" s="15" t="n">
-        <v>5.23</v>
+        <v>5.2</v>
       </c>
       <c r="G78" s="15" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="I78" s="17" t="n">
-        <v>5.15</v>
+        <v>5.07</v>
       </c>
       <c r="J78" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L78" s="19" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M78" s="19" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="N78" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O78" s="21" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="P78" s="21" t="n">
         <v>5.11</v>
       </c>
-      <c r="K78" s="18" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="L78" s="19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M78" s="19" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="N78" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O78" s="21" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="P78" s="21" t="n">
-        <v>5.17</v>
-      </c>
       <c r="Q78" s="22" t="n">
-        <v>5.19</v>
+        <v>5.13</v>
       </c>
       <c r="R78" s="23" t="n">
-        <v>-0.95</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="79">
@@ -5470,54 +5470,54 @@
         </is>
       </c>
       <c r="C79" s="13" t="n">
-        <v>19</v>
+        <v>18.87</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>18.69</v>
+        <v>18.5</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>18.43</v>
+        <v>18.19</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>18.46</v>
+        <v>18.27</v>
       </c>
       <c r="G79" s="15" t="n">
-        <v>18.64</v>
+        <v>18.45</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>18.33</v>
+        <v>18.08</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>18.15</v>
+        <v>17.9</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>18.02</v>
+        <v>17.71</v>
       </c>
       <c r="K79" s="18" t="n">
-        <v>18.26</v>
+        <v>17.98</v>
       </c>
       <c r="L79" s="19" t="n">
-        <v>18</v>
+        <v>17.67</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="N79" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>17.3</v>
+      </c>
+      <c r="N79" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O79" s="21" t="n">
-        <v>18.3</v>
+        <v>18.05</v>
       </c>
       <c r="P79" s="21" t="n">
-        <v>18.28</v>
+        <v>18.01</v>
       </c>
       <c r="Q79" s="22" t="n">
-        <v>18.29</v>
-      </c>
-      <c r="R79" s="25" t="n">
-        <v>0.61</v>
+        <v>18.08</v>
+      </c>
+      <c r="R79" s="23" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="80">
@@ -5532,37 +5532,37 @@
         </is>
       </c>
       <c r="C80" s="13" t="n">
-        <v>80.54000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>78.69</v>
+        <v>79.89</v>
       </c>
       <c r="E80" s="14" t="n">
-        <v>77.14</v>
+        <v>78</v>
       </c>
       <c r="F80" s="15" t="n">
-        <v>77.93000000000001</v>
+        <v>78.38</v>
       </c>
       <c r="G80" s="15" t="n">
-        <v>78.67</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>76.81999999999999</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="I80" s="17" t="n">
-        <v>76.08</v>
+        <v>76.13</v>
       </c>
       <c r="J80" s="17" t="n">
-        <v>74.97</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>76.11</v>
+        <v>76.75</v>
       </c>
       <c r="L80" s="19" t="n">
-        <v>74.56</v>
+        <v>74.86</v>
       </c>
       <c r="M80" s="19" t="n">
-        <v>72.70999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="N80" s="24" t="inlineStr">
         <is>
@@ -5570,16 +5570,16 @@
         </is>
       </c>
       <c r="O80" s="21" t="n">
-        <v>76.53</v>
+        <v>77.12</v>
       </c>
       <c r="P80" s="21" t="n">
-        <v>76.25</v>
+        <v>76.92</v>
       </c>
       <c r="Q80" s="22" t="n">
         <v>77.2</v>
       </c>
       <c r="R80" s="25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5594,37 +5594,37 @@
         </is>
       </c>
       <c r="C81" s="13" t="n">
-        <v>5.07</v>
+        <v>4.98</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="F81" s="15" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="G81" s="15" t="n">
         <v>4.77</v>
       </c>
-      <c r="G81" s="15" t="n">
-        <v>4.87</v>
-      </c>
       <c r="H81" s="16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I81" s="17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J81" s="17" t="n">
-        <v>4.53</v>
+        <v>4.43</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="L81" s="19" t="n">
-        <v>4.51</v>
+        <v>4.42</v>
       </c>
       <c r="M81" s="19" t="n">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
@@ -5632,16 +5632,16 @@
         </is>
       </c>
       <c r="O81" s="21" t="n">
-        <v>4.68</v>
+        <v>4.59</v>
       </c>
       <c r="P81" s="21" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="Q81" s="22" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R81" s="25" t="n">
-        <v>0.21</v>
+        <v>4.57</v>
+      </c>
+      <c r="R81" s="23" t="n">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="82">
@@ -5656,37 +5656,37 @@
         </is>
       </c>
       <c r="C82" s="13" t="n">
-        <v>61.2</v>
+        <v>59.77</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>59.75</v>
+        <v>58.37</v>
       </c>
       <c r="E82" s="14" t="n">
-        <v>58.53</v>
+        <v>57.19</v>
       </c>
       <c r="F82" s="15" t="n">
-        <v>58.37</v>
+        <v>57.7</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>59.33</v>
+        <v>58.3</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>57.88</v>
+        <v>56.9</v>
       </c>
       <c r="I82" s="17" t="n">
-        <v>56.92</v>
+        <v>56.3</v>
       </c>
       <c r="J82" s="17" t="n">
-        <v>56.43</v>
+        <v>55.5</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>57.72</v>
+        <v>56.41</v>
       </c>
       <c r="L82" s="19" t="n">
-        <v>56.5</v>
+        <v>55.23</v>
       </c>
       <c r="M82" s="19" t="n">
-        <v>55.05</v>
+        <v>53.83</v>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="O82" s="21" t="n">
-        <v>57.86</v>
+        <v>56.71</v>
       </c>
       <c r="P82" s="21" t="n">
-        <v>57.83</v>
+        <v>56.52</v>
       </c>
       <c r="Q82" s="22" t="n">
-        <v>57.4</v>
+        <v>57.1</v>
       </c>
       <c r="R82" s="23" t="n">
-        <v>-1.46</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="83">
@@ -5718,37 +5718,37 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>37.69</v>
+        <v>37.71</v>
       </c>
       <c r="D83" s="13" t="n">
-        <v>37.35</v>
+        <v>37.27</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>37.07</v>
+        <v>36.9</v>
       </c>
       <c r="F83" s="15" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="G83" s="15" t="n">
         <v>37.15</v>
       </c>
-      <c r="G83" s="15" t="n">
-        <v>37.31</v>
-      </c>
       <c r="H83" s="16" t="n">
-        <v>36.97</v>
+        <v>36.71</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>36.81</v>
+        <v>36.43</v>
       </c>
       <c r="J83" s="17" t="n">
-        <v>36.63</v>
+        <v>36.27</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>36.87</v>
+        <v>36.66</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>36.59</v>
+        <v>36.29</v>
       </c>
       <c r="M83" s="19" t="n">
-        <v>36.25</v>
+        <v>35.85</v>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
@@ -5756,16 +5756,16 @@
         </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>36.94</v>
+        <v>36.7</v>
       </c>
       <c r="P83" s="21" t="n">
-        <v>36.9</v>
+        <v>36.69</v>
       </c>
       <c r="Q83" s="22" t="n">
-        <v>36.98</v>
+        <v>36.58</v>
       </c>
       <c r="R83" s="23" t="n">
-        <v>-0.27</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="84">
@@ -5780,37 +5780,37 @@
         </is>
       </c>
       <c r="C84" s="13" t="n">
-        <v>93.75</v>
+        <v>92.19</v>
       </c>
       <c r="D84" s="13" t="n">
-        <v>92.7</v>
+        <v>91.64</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>91.81999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F84" s="15" t="n">
-        <v>91.83</v>
+        <v>91.25</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>92.47</v>
+        <v>91.55</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>91.42</v>
+        <v>91</v>
       </c>
       <c r="I84" s="17" t="n">
-        <v>90.78</v>
+        <v>90.7</v>
       </c>
       <c r="J84" s="17" t="n">
-        <v>90.37</v>
+        <v>90.45</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>91.23</v>
+        <v>90.87</v>
       </c>
       <c r="L84" s="19" t="n">
-        <v>90.34999999999999</v>
+        <v>90.41</v>
       </c>
       <c r="M84" s="19" t="n">
-        <v>89.3</v>
+        <v>89.86</v>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
@@ -5818,16 +5818,16 @@
         </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>91.36</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="P84" s="21" t="n">
-        <v>91.31</v>
+        <v>90.91</v>
       </c>
       <c r="Q84" s="22" t="n">
-        <v>91.2</v>
+        <v>90.95</v>
       </c>
       <c r="R84" s="23" t="n">
-        <v>-0.38</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="85">
@@ -5842,37 +5842,37 @@
         </is>
       </c>
       <c r="C85" s="13" t="n">
-        <v>16.94</v>
+        <v>16.46</v>
       </c>
       <c r="D85" s="13" t="n">
-        <v>16.65</v>
+        <v>16.31</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>16.41</v>
+        <v>16.19</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>16.39</v>
+        <v>16.17</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>16.57</v>
+        <v>16.27</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>16.28</v>
+        <v>16.12</v>
       </c>
       <c r="I85" s="17" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="J85" s="17" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="K85" s="18" t="n">
         <v>16.1</v>
       </c>
-      <c r="J85" s="17" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="K85" s="18" t="n">
-        <v>16.24</v>
-      </c>
       <c r="L85" s="19" t="n">
-        <v>16</v>
+        <v>15.98</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>15.71</v>
+        <v>15.83</v>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>16.27</v>
+        <v>16.12</v>
       </c>
       <c r="P85" s="21" t="n">
-        <v>16.27</v>
+        <v>16.11</v>
       </c>
       <c r="Q85" s="22" t="n">
-        <v>16.2</v>
+        <v>16.07</v>
       </c>
       <c r="R85" s="23" t="n">
-        <v>-1.22</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="86">
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="C86" s="13" t="n">
-        <v>122.79</v>
+        <v>124.82</v>
       </c>
       <c r="D86" s="13" t="n">
-        <v>121.19</v>
+        <v>121.72</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>119.85</v>
+        <v>119.12</v>
       </c>
       <c r="F86" s="15" t="n">
-        <v>119.8</v>
+        <v>119.17</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>120.8</v>
+        <v>121.03</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>119.2</v>
+        <v>117.93</v>
       </c>
       <c r="I86" s="17" t="n">
-        <v>118.2</v>
+        <v>116.07</v>
       </c>
       <c r="J86" s="17" t="n">
-        <v>117.6</v>
+        <v>114.83</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>118.95</v>
+        <v>117.38</v>
       </c>
       <c r="L86" s="19" t="n">
-        <v>117.61</v>
+        <v>114.78</v>
       </c>
       <c r="M86" s="19" t="n">
-        <v>116.01</v>
+        <v>111.68</v>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>119.14</v>
+        <v>117.78</v>
       </c>
       <c r="P86" s="21" t="n">
-        <v>119.08</v>
+        <v>117.62</v>
       </c>
       <c r="Q86" s="22" t="n">
-        <v>118.8</v>
+        <v>117.3</v>
       </c>
       <c r="R86" s="23" t="n">
-        <v>-0.83</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="87">
@@ -5966,37 +5966,37 @@
         </is>
       </c>
       <c r="C87" s="13" t="n">
-        <v>57.3</v>
+        <v>56.97</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>55.85</v>
+        <v>55.32</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>54.63</v>
+        <v>53.94</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>54.9</v>
+        <v>54.38</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>55.65</v>
+        <v>55.17</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>54.2</v>
+        <v>53.52</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>53.45</v>
+        <v>52.73</v>
       </c>
       <c r="J87" s="17" t="n">
-        <v>52.75</v>
+        <v>51.87</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>53.82</v>
+        <v>53.01</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>52.6</v>
+        <v>51.63</v>
       </c>
       <c r="M87" s="19" t="n">
-        <v>51.15</v>
+        <v>49.98</v>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
@@ -6004,16 +6004,16 @@
         </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>54.07</v>
+        <v>53.33</v>
       </c>
       <c r="P87" s="21" t="n">
-        <v>53.93</v>
+        <v>53.14</v>
       </c>
       <c r="Q87" s="22" t="n">
-        <v>54.15</v>
+        <v>53.6</v>
       </c>
       <c r="R87" s="23" t="n">
-        <v>-0.64</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="88">
@@ -6028,37 +6028,37 @@
         </is>
       </c>
       <c r="C88" s="13" t="n">
-        <v>9.77</v>
+        <v>10.03</v>
       </c>
       <c r="D88" s="13" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>9.59</v>
+        <v>9.52</v>
       </c>
       <c r="F88" s="15" t="n">
-        <v>9.58</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>9.539999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="I88" s="17" t="n">
-        <v>9.48</v>
+        <v>9.27</v>
       </c>
       <c r="J88" s="17" t="n">
-        <v>9.44</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>9.529999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L88" s="19" t="n">
-        <v>9.449999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M88" s="19" t="n">
-        <v>9.35</v>
+        <v>8.85</v>
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>9.539999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="P88" s="21" t="n">
-        <v>9.539999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q88" s="22" t="n">
-        <v>9.51</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="R88" s="23" t="n">
-        <v>-0.31</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="89">
@@ -6090,54 +6090,54 @@
         </is>
       </c>
       <c r="C89" s="13" t="n">
-        <v>16.42</v>
+        <v>16.27</v>
       </c>
       <c r="D89" s="13" t="n">
-        <v>15.98</v>
+        <v>15.74</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>15.61</v>
+        <v>15.29</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>15.56</v>
+        <v>15.31</v>
       </c>
       <c r="G89" s="15" t="n">
-        <v>15.86</v>
+        <v>15.63</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>15.42</v>
+        <v>15.1</v>
       </c>
       <c r="I89" s="17" t="n">
-        <v>15.12</v>
+        <v>14.78</v>
       </c>
       <c r="J89" s="17" t="n">
-        <v>14.98</v>
+        <v>14.57</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>15.37</v>
+        <v>15</v>
       </c>
       <c r="L89" s="19" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="M89" s="19" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="N89" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O89" s="21" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="P89" s="21" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="Q89" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="M89" s="19" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="N89" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O89" s="21" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="P89" s="21" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q89" s="22" t="n">
-        <v>15.27</v>
-      </c>
       <c r="R89" s="23" t="n">
-        <v>-1.86</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="90">
@@ -6152,54 +6152,54 @@
         </is>
       </c>
       <c r="C90" s="13" t="n">
-        <v>18.22</v>
+        <v>18.62</v>
       </c>
       <c r="D90" s="13" t="n">
-        <v>17.86</v>
+        <v>18.12</v>
       </c>
       <c r="E90" s="14" t="n">
-        <v>17.56</v>
+        <v>17.7</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>17.59</v>
+        <v>17.67</v>
       </c>
       <c r="G90" s="15" t="n">
-        <v>17.79</v>
+        <v>17.99</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>17.43</v>
+        <v>17.49</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>17.23</v>
+        <v>17.17</v>
       </c>
       <c r="J90" s="17" t="n">
-        <v>17.07</v>
+        <v>16.99</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>17.36</v>
+        <v>17.42</v>
       </c>
       <c r="L90" s="19" t="n">
-        <v>17.06</v>
+        <v>17</v>
       </c>
       <c r="M90" s="19" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N90" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>16.5</v>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>17.41</v>
+        <v>17.47</v>
       </c>
       <c r="P90" s="21" t="n">
-        <v>17.39</v>
+        <v>17.46</v>
       </c>
       <c r="Q90" s="22" t="n">
-        <v>17.38</v>
+        <v>17.35</v>
       </c>
       <c r="R90" s="23" t="n">
-        <v>-0.29</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="91">
@@ -6214,37 +6214,37 @@
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>31.66</v>
+        <v>30.54</v>
       </c>
       <c r="D91" s="13" t="n">
-        <v>30.56</v>
+        <v>29.8</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>29.64</v>
+        <v>29.18</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>29.66</v>
+        <v>29.13</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>30.32</v>
+        <v>29.61</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>29.22</v>
+        <v>28.87</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>28.56</v>
+        <v>28.39</v>
       </c>
       <c r="J91" s="17" t="n">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>29.02</v>
+        <v>28.76</v>
       </c>
       <c r="L91" s="19" t="n">
-        <v>28.1</v>
+        <v>28.14</v>
       </c>
       <c r="M91" s="19" t="n">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>29.16</v>
+        <v>28.84</v>
       </c>
       <c r="P91" s="21" t="n">
-        <v>29.11</v>
+        <v>28.82</v>
       </c>
       <c r="Q91" s="22" t="n">
-        <v>29</v>
+        <v>28.66</v>
       </c>
       <c r="R91" s="23" t="n">
-        <v>-1.69</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="92">
@@ -6276,37 +6276,37 @@
         </is>
       </c>
       <c r="C92" s="13" t="n">
-        <v>20.36</v>
+        <v>20.21</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>20</v>
+        <v>19.86</v>
       </c>
       <c r="E92" s="14" t="n">
-        <v>19.7</v>
+        <v>19.56</v>
       </c>
       <c r="F92" s="15" t="n">
-        <v>19.7</v>
+        <v>19.57</v>
       </c>
       <c r="G92" s="15" t="n">
-        <v>19.92</v>
+        <v>19.78</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>19.56</v>
+        <v>19.43</v>
       </c>
       <c r="I92" s="17" t="n">
-        <v>19.34</v>
+        <v>19.22</v>
       </c>
       <c r="J92" s="17" t="n">
-        <v>19.2</v>
+        <v>19.08</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>19.5</v>
+        <v>19.37</v>
       </c>
       <c r="L92" s="19" t="n">
-        <v>19.2</v>
+        <v>19.07</v>
       </c>
       <c r="M92" s="19" t="n">
-        <v>18.84</v>
+        <v>18.72</v>
       </c>
       <c r="N92" s="20" t="inlineStr">
         <is>
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="O92" s="21" t="n">
-        <v>19.54</v>
+        <v>19.41</v>
       </c>
       <c r="P92" s="21" t="n">
-        <v>19.53</v>
+        <v>19.39</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>19.48</v>
+        <v>19.36</v>
       </c>
       <c r="R92" s="23" t="n">
-        <v>-1.12</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="93">
@@ -6338,37 +6338,37 @@
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>26.9</v>
+        <v>26.14</v>
       </c>
       <c r="D93" s="13" t="n">
-        <v>26.32</v>
+        <v>25.72</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>25.83</v>
+        <v>25.37</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>25.81</v>
+        <v>25.44</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>26.17</v>
+        <v>25.66</v>
       </c>
       <c r="H93" s="16" t="n">
-        <v>25.59</v>
+        <v>25.24</v>
       </c>
       <c r="I93" s="17" t="n">
-        <v>25.23</v>
+        <v>25.02</v>
       </c>
       <c r="J93" s="17" t="n">
-        <v>25.01</v>
+        <v>24.82</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>25.51</v>
+        <v>25.13</v>
       </c>
       <c r="L93" s="19" t="n">
-        <v>25.02</v>
+        <v>24.78</v>
       </c>
       <c r="M93" s="19" t="n">
-        <v>24.44</v>
+        <v>24.36</v>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>25.57</v>
+        <v>25.2</v>
       </c>
       <c r="P93" s="21" t="n">
-        <v>25.55</v>
+        <v>25.17</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>25.44</v>
+        <v>25.22</v>
       </c>
       <c r="R93" s="23" t="n">
-        <v>-2</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="94">
@@ -6400,37 +6400,37 @@
         </is>
       </c>
       <c r="C94" s="13" t="n">
-        <v>175.02</v>
+        <v>174.07</v>
       </c>
       <c r="D94" s="13" t="n">
-        <v>172.72</v>
+        <v>171.37</v>
       </c>
       <c r="E94" s="14" t="n">
-        <v>170.79</v>
+        <v>169.11</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>171.13</v>
+        <v>169.07</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>172.37</v>
+        <v>170.73</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>170.07</v>
+        <v>168.03</v>
       </c>
       <c r="I94" s="17" t="n">
-        <v>168.83</v>
+        <v>166.37</v>
       </c>
       <c r="J94" s="17" t="n">
-        <v>167.77</v>
+        <v>165.33</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>169.51</v>
+        <v>167.59</v>
       </c>
       <c r="L94" s="19" t="n">
-        <v>167.58</v>
+        <v>165.33</v>
       </c>
       <c r="M94" s="19" t="n">
-        <v>165.28</v>
+        <v>162.63</v>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
@@ -6438,16 +6438,16 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>169.88</v>
+        <v>167.92</v>
       </c>
       <c r="P94" s="21" t="n">
-        <v>169.69</v>
+        <v>167.8</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>169.9</v>
+        <v>167.4</v>
       </c>
       <c r="R94" s="23" t="n">
-        <v>-0.93</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="95">
@@ -6462,54 +6462,54 @@
         </is>
       </c>
       <c r="C95" s="13" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="E95" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="G95" s="15" t="n">
         <v>13.8</v>
       </c>
-      <c r="D95" s="13" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="E95" s="14" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="F95" s="15" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="G95" s="15" t="n">
+      <c r="H95" s="16" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="J95" s="17" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="K95" s="18" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="M95" s="19" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="N95" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
+        </is>
+      </c>
+      <c r="O95" s="21" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="P95" s="21" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="Q95" s="22" t="n">
         <v>13.49</v>
       </c>
-      <c r="H95" s="16" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="I95" s="17" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="J95" s="17" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="K95" s="18" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="L95" s="19" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="M95" s="19" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="N95" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O95" s="21" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="P95" s="21" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="Q95" s="22" t="n">
-        <v>13.27</v>
-      </c>
       <c r="R95" s="25" t="n">
-        <v>0.99</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="96">
@@ -6524,54 +6524,54 @@
         </is>
       </c>
       <c r="C96" s="13" t="n">
-        <v>20.04</v>
+        <v>19.68</v>
       </c>
       <c r="D96" s="13" t="n">
-        <v>19.58</v>
+        <v>19.32</v>
       </c>
       <c r="E96" s="14" t="n">
-        <v>19.2</v>
+        <v>19.02</v>
       </c>
       <c r="F96" s="15" t="n">
-        <v>19.29</v>
+        <v>18.98</v>
       </c>
       <c r="G96" s="15" t="n">
-        <v>19.53</v>
+        <v>19.22</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>19.07</v>
+        <v>18.86</v>
       </c>
       <c r="I96" s="17" t="n">
-        <v>18.83</v>
+        <v>18.62</v>
       </c>
       <c r="J96" s="17" t="n">
-        <v>18.61</v>
+        <v>18.5</v>
       </c>
       <c r="K96" s="18" t="n">
-        <v>18.94</v>
+        <v>18.82</v>
       </c>
       <c r="L96" s="19" t="n">
-        <v>18.56</v>
+        <v>18.52</v>
       </c>
       <c r="M96" s="19" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="N96" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>18.16</v>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O96" s="21" t="n">
-        <v>19.02</v>
+        <v>18.85</v>
       </c>
       <c r="P96" s="21" t="n">
-        <v>18.98</v>
+        <v>18.85</v>
       </c>
       <c r="Q96" s="22" t="n">
-        <v>19.06</v>
+        <v>18.74</v>
       </c>
       <c r="R96" s="23" t="n">
-        <v>-0.21</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="97">
@@ -6586,37 +6586,37 @@
         </is>
       </c>
       <c r="C97" s="13" t="n">
-        <v>15.85</v>
+        <v>14.69</v>
       </c>
       <c r="D97" s="13" t="n">
-        <v>15.2</v>
+        <v>14.41</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>14.66</v>
+        <v>14.18</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>14.59</v>
+        <v>14.19</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>15.02</v>
+        <v>14.35</v>
       </c>
       <c r="H97" s="16" t="n">
-        <v>14.37</v>
+        <v>14.07</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>13.94</v>
+        <v>13.91</v>
       </c>
       <c r="J97" s="17" t="n">
-        <v>13.72</v>
+        <v>13.79</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>14.29</v>
+        <v>14.02</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>13.75</v>
+        <v>13.79</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>13.1</v>
+        <v>13.51</v>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
@@ -6624,16 +6624,16 @@
         </is>
       </c>
       <c r="O97" s="21" t="n">
-        <v>14.36</v>
+        <v>14.06</v>
       </c>
       <c r="P97" s="21" t="n">
-        <v>14.34</v>
+        <v>14.04</v>
       </c>
       <c r="Q97" s="22" t="n">
-        <v>14.16</v>
+        <v>14.02</v>
       </c>
       <c r="R97" s="23" t="n">
-        <v>-3.03</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="98">
@@ -6648,54 +6648,54 @@
         </is>
       </c>
       <c r="C98" s="13" t="n">
-        <v>9.51</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D98" s="13" t="n">
-        <v>9.369999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E98" s="14" t="n">
         <v>9.25</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>9.33</v>
+        <v>9.24</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>9.369999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>9.23</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>9.19</v>
+        <v>8.9</v>
       </c>
       <c r="J98" s="17" t="n">
-        <v>9.09</v>
+        <v>8.77</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>9.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L98" s="19" t="n">
-        <v>9.050000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="M98" s="19" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="N98" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>8.43</v>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O98" s="21" t="n">
-        <v>9.210000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="P98" s="21" t="n">
-        <v>9.18</v>
+        <v>9.08</v>
       </c>
       <c r="Q98" s="22" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="R98" s="25" t="n">
-        <v>0.43</v>
+        <v>9.029999999999999</v>
+      </c>
+      <c r="R98" s="23" t="n">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="99">
@@ -6710,54 +6710,54 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>25.32</v>
+        <v>25.06</v>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25</v>
+        <v>24.75</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>24.73</v>
+        <v>24.49</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>24.69</v>
+        <v>24.48</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>24.91</v>
+        <v>24.67</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>24.59</v>
+        <v>24.36</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>24.37</v>
+        <v>24.17</v>
       </c>
       <c r="J99" s="17" t="n">
-        <v>24.27</v>
+        <v>24.05</v>
       </c>
       <c r="K99" s="18" t="n">
-        <v>24.55</v>
+        <v>24.32</v>
       </c>
       <c r="L99" s="19" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="M99" s="19" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="N99" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O99" s="21" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="P99" s="21" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="Q99" s="22" t="n">
         <v>24.28</v>
       </c>
-      <c r="M99" s="19" t="n">
-        <v>23.96</v>
-      </c>
-      <c r="N99" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O99" s="21" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="P99" s="21" t="n">
-        <v>24.58</v>
-      </c>
-      <c r="Q99" s="22" t="n">
-        <v>24.48</v>
-      </c>
       <c r="R99" s="23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="100">
@@ -6772,37 +6772,37 @@
         </is>
       </c>
       <c r="C100" s="13" t="n">
-        <v>16.18</v>
+        <v>16.2</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>15.97</v>
+        <v>15.93</v>
       </c>
       <c r="E100" s="14" t="n">
-        <v>15.79</v>
+        <v>15.7</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>15.86</v>
+        <v>15.67</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>15.95</v>
+        <v>15.85</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>15.74</v>
+        <v>15.58</v>
       </c>
       <c r="I100" s="17" t="n">
-        <v>15.65</v>
+        <v>15.4</v>
       </c>
       <c r="J100" s="17" t="n">
-        <v>15.53</v>
+        <v>15.31</v>
       </c>
       <c r="K100" s="18" t="n">
-        <v>15.68</v>
+        <v>15.55</v>
       </c>
       <c r="L100" s="19" t="n">
-        <v>15.5</v>
+        <v>15.32</v>
       </c>
       <c r="M100" s="19" t="n">
-        <v>15.29</v>
+        <v>15.05</v>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
@@ -6810,16 +6810,16 @@
         </is>
       </c>
       <c r="O100" s="21" t="n">
-        <v>15.72</v>
+        <v>15.58</v>
       </c>
       <c r="P100" s="21" t="n">
-        <v>15.69</v>
+        <v>15.57</v>
       </c>
       <c r="Q100" s="22" t="n">
-        <v>15.76</v>
+        <v>15.49</v>
       </c>
       <c r="R100" s="23" t="n">
-        <v>-1.13</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="101">
@@ -6834,37 +6834,37 @@
         </is>
       </c>
       <c r="C101" s="13" t="n">
-        <v>30.64</v>
+        <v>29.61</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>29.9</v>
+        <v>29.05</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>29.28</v>
+        <v>28.58</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>29.19</v>
+        <v>28.51</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>29.69</v>
+        <v>28.89</v>
       </c>
       <c r="H101" s="16" t="n">
-        <v>28.95</v>
+        <v>28.33</v>
       </c>
       <c r="I101" s="17" t="n">
-        <v>28.45</v>
+        <v>27.95</v>
       </c>
       <c r="J101" s="17" t="n">
-        <v>28.21</v>
+        <v>27.77</v>
       </c>
       <c r="K101" s="18" t="n">
-        <v>28.86</v>
+        <v>28.26</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>28.24</v>
+        <v>27.79</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>27.5</v>
+        <v>27.23</v>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
@@ -6872,16 +6872,16 @@
         </is>
       </c>
       <c r="O101" s="21" t="n">
-        <v>28.93</v>
+        <v>28.32</v>
       </c>
       <c r="P101" s="21" t="n">
-        <v>28.92</v>
+        <v>28.31</v>
       </c>
       <c r="Q101" s="22" t="n">
-        <v>28.7</v>
+        <v>28.14</v>
       </c>
       <c r="R101" s="23" t="n">
-        <v>-1.78</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="102">
@@ -6896,37 +6896,37 @@
         </is>
       </c>
       <c r="C102" s="13" t="n">
-        <v>14.89</v>
+        <v>14.93</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>14.59</v>
+        <v>14.5</v>
       </c>
       <c r="E102" s="14" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>14.32</v>
+        <v>14.14</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>14.51</v>
+        <v>14.4</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>14.21</v>
+        <v>13.97</v>
       </c>
       <c r="I102" s="17" t="n">
-        <v>14.02</v>
+        <v>13.71</v>
       </c>
       <c r="J102" s="17" t="n">
-        <v>13.91</v>
+        <v>13.54</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>14.17</v>
+        <v>13.89</v>
       </c>
       <c r="L102" s="19" t="n">
-        <v>13.91</v>
+        <v>13.53</v>
       </c>
       <c r="M102" s="19" t="n">
-        <v>13.61</v>
+        <v>13.1</v>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
@@ -6934,16 +6934,16 @@
         </is>
       </c>
       <c r="O102" s="21" t="n">
-        <v>14.2</v>
+        <v>13.95</v>
       </c>
       <c r="P102" s="21" t="n">
-        <v>14.19</v>
+        <v>13.93</v>
       </c>
       <c r="Q102" s="22" t="n">
-        <v>14.13</v>
+        <v>13.88</v>
       </c>
       <c r="R102" s="23" t="n">
-        <v>-1.05</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="103">
@@ -6958,37 +6958,37 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>68.54000000000001</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="D103" s="13" t="n">
-        <v>66.54000000000001</v>
+        <v>65.88</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>64.86</v>
+        <v>63.74</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>65.3</v>
+        <v>63.48</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>66.3</v>
+        <v>65.17</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>64.3</v>
+        <v>62.62</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>63.3</v>
+        <v>60.93</v>
       </c>
       <c r="J103" s="17" t="n">
-        <v>62.3</v>
+        <v>60.07</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>63.74</v>
+        <v>62.31</v>
       </c>
       <c r="L103" s="19" t="n">
-        <v>62.06</v>
+        <v>60.17</v>
       </c>
       <c r="M103" s="19" t="n">
-        <v>60.06</v>
+        <v>57.62</v>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
@@ -6996,16 +6996,16 @@
         </is>
       </c>
       <c r="O103" s="21" t="n">
-        <v>64.09999999999999</v>
+        <v>62.56</v>
       </c>
       <c r="P103" s="21" t="n">
-        <v>63.9</v>
+        <v>62.51</v>
       </c>
       <c r="Q103" s="22" t="n">
-        <v>64.3</v>
+        <v>61.8</v>
       </c>
       <c r="R103" s="23" t="n">
-        <v>-1.46</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="104">
@@ -7020,37 +7020,37 @@
         </is>
       </c>
       <c r="C104" s="13" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>14.14</v>
+        <v>14.07</v>
       </c>
       <c r="E104" s="14" t="n">
-        <v>14.02</v>
+        <v>13.92</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>14.01</v>
+        <v>13.91</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>14.11</v>
+        <v>14.03</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>13.96</v>
+        <v>13.85</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>13.86</v>
+        <v>13.73</v>
       </c>
       <c r="J104" s="17" t="n">
-        <v>13.81</v>
+        <v>13.67</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>13.93</v>
+        <v>13.82</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>13.81</v>
+        <v>13.67</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>13.66</v>
+        <v>13.49</v>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
@@ -7058,16 +7058,16 @@
         </is>
       </c>
       <c r="O104" s="21" t="n">
-        <v>13.95</v>
+        <v>13.84</v>
       </c>
       <c r="P104" s="21" t="n">
-        <v>13.94</v>
+        <v>13.83</v>
       </c>
       <c r="Q104" s="22" t="n">
-        <v>13.92</v>
+        <v>13.8</v>
       </c>
       <c r="R104" s="23" t="n">
-        <v>-0.5</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="105">
@@ -7082,37 +7082,37 @@
         </is>
       </c>
       <c r="C105" s="13" t="n">
-        <v>19.29</v>
+        <v>18.28</v>
       </c>
       <c r="D105" s="13" t="n">
-        <v>18.19</v>
+        <v>17.42</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>17.27</v>
+        <v>16.7</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>17.31</v>
+        <v>16.6</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>17.96</v>
+        <v>17.18</v>
       </c>
       <c r="H105" s="16" t="n">
-        <v>16.86</v>
+        <v>16.32</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>16.21</v>
+        <v>15.74</v>
       </c>
       <c r="J105" s="17" t="n">
-        <v>15.76</v>
+        <v>15.46</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>16.65</v>
+        <v>16.22</v>
       </c>
       <c r="L105" s="19" t="n">
-        <v>15.73</v>
+        <v>15.5</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>14.63</v>
+        <v>14.64</v>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
@@ -7120,16 +7120,16 @@
         </is>
       </c>
       <c r="O105" s="21" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="P105" s="21" t="n">
-        <v>16.74</v>
+        <v>16.29</v>
       </c>
       <c r="Q105" s="22" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="R105" s="25" t="n">
-        <v>0.18</v>
+        <v>16.03</v>
+      </c>
+      <c r="R105" s="23" t="n">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="106">
@@ -7144,54 +7144,54 @@
         </is>
       </c>
       <c r="C106" s="13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="D106" s="13" t="n">
         <v>2.44</v>
       </c>
       <c r="E106" s="14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="F106" s="15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G106" s="15" t="n">
         <v>2.42</v>
       </c>
-      <c r="G106" s="15" t="n">
-        <v>2.44</v>
-      </c>
       <c r="H106" s="16" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="L106" s="19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M106" s="19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="N106" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>2.24</v>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="P106" s="21" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="Q106" s="22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R106" s="25" t="n">
-        <v>1.69</v>
+        <v>2.35</v>
+      </c>
+      <c r="R106" s="23" t="n">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="107">
@@ -7206,54 +7206,54 @@
         </is>
       </c>
       <c r="C107" s="13" t="n">
-        <v>38.32</v>
+        <v>37.21</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>37.48</v>
+        <v>36.77</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>36.78</v>
+        <v>36.4</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>37.03</v>
+        <v>36.35</v>
       </c>
       <c r="G107" s="15" t="n">
-        <v>37.41</v>
+        <v>36.65</v>
       </c>
       <c r="H107" s="16" t="n">
-        <v>36.57</v>
+        <v>36.21</v>
       </c>
       <c r="I107" s="17" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="J107" s="17" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="K107" s="18" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="L107" s="19" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="M107" s="19" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="N107" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O107" s="21" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="P107" s="21" t="n">
         <v>36.19</v>
       </c>
-      <c r="J107" s="17" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="K107" s="18" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="L107" s="19" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="M107" s="19" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="N107" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O107" s="21" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="P107" s="21" t="n">
-        <v>36.37</v>
-      </c>
       <c r="Q107" s="22" t="n">
-        <v>36.64</v>
+        <v>36.06</v>
       </c>
       <c r="R107" s="23" t="n">
-        <v>-0.7</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="108">
@@ -7268,54 +7268,54 @@
         </is>
       </c>
       <c r="C108" s="13" t="n">
-        <v>8.09</v>
+        <v>7.97</v>
       </c>
       <c r="D108" s="13" t="n">
-        <v>7.86</v>
+        <v>7.71</v>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7.67</v>
+        <v>7.49</v>
       </c>
       <c r="F108" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G108" s="15" t="n">
         <v>7.66</v>
       </c>
-      <c r="G108" s="15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="H108" s="16" t="n">
-        <v>7.57</v>
+        <v>7.4</v>
       </c>
       <c r="I108" s="17" t="n">
-        <v>7.43</v>
+        <v>7.24</v>
       </c>
       <c r="J108" s="17" t="n">
-        <v>7.34</v>
+        <v>7.14</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>7.54</v>
+        <v>7.35</v>
       </c>
       <c r="L108" s="19" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="M108" s="19" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O108" s="21" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="P108" s="21" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="Q108" s="22" t="n">
         <v>7.35</v>
       </c>
-      <c r="M108" s="19" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="N108" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O108" s="21" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="P108" s="21" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="Q108" s="22" t="n">
-        <v>7.51</v>
-      </c>
       <c r="R108" s="23" t="n">
-        <v>-2.72</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="109">
@@ -7330,37 +7330,37 @@
         </is>
       </c>
       <c r="C109" s="13" t="n">
-        <v>43.99</v>
+        <v>43.88</v>
       </c>
       <c r="D109" s="13" t="n">
-        <v>43.65</v>
+        <v>43.46</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>43.37</v>
+        <v>43.11</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>43.33</v>
+        <v>43.06</v>
       </c>
       <c r="G109" s="15" t="n">
-        <v>43.55</v>
+        <v>43.34</v>
       </c>
       <c r="H109" s="16" t="n">
-        <v>43.21</v>
+        <v>42.92</v>
       </c>
       <c r="I109" s="17" t="n">
-        <v>42.99</v>
+        <v>42.64</v>
       </c>
       <c r="J109" s="17" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="K109" s="18" t="n">
         <v>42.87</v>
       </c>
-      <c r="K109" s="18" t="n">
-        <v>43.17</v>
-      </c>
       <c r="L109" s="19" t="n">
-        <v>42.89</v>
+        <v>42.52</v>
       </c>
       <c r="M109" s="19" t="n">
-        <v>42.55</v>
+        <v>42.1</v>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
@@ -7368,16 +7368,16 @@
         </is>
       </c>
       <c r="O109" s="21" t="n">
-        <v>43.21</v>
+        <v>42.91</v>
       </c>
       <c r="P109" s="21" t="n">
-        <v>43.2</v>
+        <v>42.91</v>
       </c>
       <c r="Q109" s="22" t="n">
-        <v>43.1</v>
+        <v>42.78</v>
       </c>
       <c r="R109" s="23" t="n">
-        <v>-0.6</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="110">
@@ -7392,37 +7392,37 @@
         </is>
       </c>
       <c r="C110" s="13" t="n">
-        <v>66.45</v>
+        <v>65.27</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>65.40000000000001</v>
+        <v>64.67</v>
       </c>
       <c r="E110" s="14" t="n">
-        <v>64.52</v>
+        <v>64.17</v>
       </c>
       <c r="F110" s="15" t="n">
-        <v>64.56999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="G110" s="15" t="n">
-        <v>65.18000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>64.13</v>
+        <v>64</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>63.52</v>
+        <v>63.7</v>
       </c>
       <c r="J110" s="17" t="n">
-        <v>63.08</v>
+        <v>63.4</v>
       </c>
       <c r="K110" s="18" t="n">
-        <v>63.93</v>
+        <v>63.83</v>
       </c>
       <c r="L110" s="19" t="n">
-        <v>63.05</v>
+        <v>63.33</v>
       </c>
       <c r="M110" s="19" t="n">
-        <v>62</v>
+        <v>62.73</v>
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="O110" s="21" t="n">
-        <v>64.06999999999999</v>
+        <v>63.94</v>
       </c>
       <c r="P110" s="21" t="n">
-        <v>64.01000000000001</v>
+        <v>63.88</v>
       </c>
       <c r="Q110" s="22" t="n">
-        <v>63.95</v>
-      </c>
-      <c r="R110" s="23" t="n">
-        <v>-1.31</v>
+        <v>64</v>
+      </c>
+      <c r="R110" s="25" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="111">
@@ -7454,37 +7454,37 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>10.23</v>
+        <v>10.2</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>10.14</v>
+        <v>10.09</v>
       </c>
       <c r="E111" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="G111" s="15" t="n">
         <v>10.06</v>
       </c>
-      <c r="F111" s="15" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>10.11</v>
-      </c>
       <c r="H111" s="16" t="n">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>9.970000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J111" s="17" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="K111" s="18" t="n">
         <v>9.93</v>
       </c>
-      <c r="K111" s="18" t="n">
-        <v>10.01</v>
-      </c>
       <c r="L111" s="19" t="n">
-        <v>9.93</v>
+        <v>9.84</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>9.84</v>
+        <v>9.73</v>
       </c>
       <c r="N111" s="20" t="inlineStr">
         <is>
@@ -7492,16 +7492,16 @@
         </is>
       </c>
       <c r="O111" s="21" t="n">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="P111" s="21" t="n">
-        <v>10.02</v>
+        <v>9.94</v>
       </c>
       <c r="Q111" s="22" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="R111" s="23" t="n">
-        <v>-0.89</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="112">
@@ -7516,54 +7516,54 @@
         </is>
       </c>
       <c r="C112" s="13" t="n">
-        <v>309.79</v>
+        <v>317.32</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>301.39</v>
+        <v>306.12</v>
       </c>
       <c r="E112" s="14" t="n">
-        <v>294.35</v>
+        <v>296.74</v>
       </c>
       <c r="F112" s="15" t="n">
-        <v>299</v>
+        <v>296.8</v>
       </c>
       <c r="G112" s="15" t="n">
-        <v>301.8</v>
+        <v>303.6</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>293.4</v>
+        <v>292.4</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>290.6</v>
+        <v>285.6</v>
       </c>
       <c r="J112" s="17" t="n">
-        <v>285</v>
+        <v>281.2</v>
       </c>
       <c r="K112" s="18" t="n">
-        <v>289.65</v>
+        <v>290.46</v>
       </c>
       <c r="L112" s="19" t="n">
-        <v>282.61</v>
+        <v>281.08</v>
       </c>
       <c r="M112" s="19" t="n">
-        <v>274.21</v>
-      </c>
-      <c r="N112" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>269.88</v>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>291.85</v>
+        <v>291.87</v>
       </c>
       <c r="P112" s="21" t="n">
-        <v>290.3</v>
+        <v>291.34</v>
       </c>
       <c r="Q112" s="22" t="n">
-        <v>296.2</v>
-      </c>
-      <c r="R112" s="25" t="n">
-        <v>2.07</v>
+        <v>290</v>
+      </c>
+      <c r="R112" s="23" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="113">
@@ -7578,37 +7578,37 @@
         </is>
       </c>
       <c r="C113" s="13" t="n">
-        <v>224.12</v>
+        <v>230.35</v>
       </c>
       <c r="D113" s="13" t="n">
-        <v>221.02</v>
+        <v>221.85</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>218.42</v>
+        <v>214.73</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>218.07</v>
+        <v>214.77</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>220.13</v>
+        <v>219.93</v>
       </c>
       <c r="H113" s="16" t="n">
-        <v>217.03</v>
+        <v>211.43</v>
       </c>
       <c r="I113" s="17" t="n">
-        <v>214.97</v>
+        <v>206.27</v>
       </c>
       <c r="J113" s="17" t="n">
-        <v>213.93</v>
+        <v>202.93</v>
       </c>
       <c r="K113" s="18" t="n">
-        <v>216.68</v>
+        <v>209.97</v>
       </c>
       <c r="L113" s="19" t="n">
-        <v>214.08</v>
+        <v>202.85</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>210.98</v>
+        <v>194.35</v>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
@@ -7616,16 +7616,16 @@
         </is>
       </c>
       <c r="O113" s="21" t="n">
-        <v>216.98</v>
+        <v>211.03</v>
       </c>
       <c r="P113" s="21" t="n">
-        <v>216.92</v>
+        <v>210.63</v>
       </c>
       <c r="Q113" s="22" t="n">
-        <v>216</v>
+        <v>209.6</v>
       </c>
       <c r="R113" s="23" t="n">
-        <v>-1.05</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="114">
@@ -7640,37 +7640,37 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>598.33</v>
+        <v>620.98</v>
       </c>
       <c r="D114" s="13" t="n">
-        <v>591.33</v>
+        <v>599.98</v>
       </c>
       <c r="E114" s="14" t="n">
-        <v>585.46</v>
+        <v>582.38</v>
       </c>
       <c r="F114" s="15" t="n">
-        <v>584.67</v>
+        <v>580</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>589.33</v>
+        <v>594</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>582.33</v>
+        <v>573</v>
       </c>
       <c r="I114" s="17" t="n">
-        <v>577.67</v>
+        <v>559</v>
       </c>
       <c r="J114" s="17" t="n">
-        <v>575.33</v>
+        <v>552</v>
       </c>
       <c r="K114" s="18" t="n">
-        <v>581.54</v>
+        <v>570.62</v>
       </c>
       <c r="L114" s="19" t="n">
-        <v>575.67</v>
+        <v>553.02</v>
       </c>
       <c r="M114" s="19" t="n">
-        <v>568.67</v>
+        <v>532.02</v>
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
@@ -7678,16 +7678,16 @@
         </is>
       </c>
       <c r="O114" s="21" t="n">
-        <v>582.21</v>
+        <v>572.63</v>
       </c>
       <c r="P114" s="21" t="n">
-        <v>582.09</v>
+        <v>572.26</v>
       </c>
       <c r="Q114" s="22" t="n">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="R114" s="23" t="n">
-        <v>-1.02</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="115">
@@ -7702,37 +7702,37 @@
         </is>
       </c>
       <c r="C115" s="13" t="n">
-        <v>6.1</v>
+        <v>5.72</v>
       </c>
       <c r="D115" s="13" t="n">
-        <v>5.84</v>
+        <v>5.59</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>5.62</v>
+        <v>5.48</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>5.6</v>
+        <v>5.47</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>5.77</v>
+        <v>5.56</v>
       </c>
       <c r="H115" s="16" t="n">
-        <v>5.51</v>
+        <v>5.43</v>
       </c>
       <c r="I115" s="17" t="n">
         <v>5.34</v>
       </c>
       <c r="J115" s="17" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="K115" s="18" t="n">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="L115" s="19" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="P115" s="21" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="Q115" s="22" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="R115" s="23" t="n">
-        <v>-4.4</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="116">
@@ -7764,54 +7764,54 @@
         </is>
       </c>
       <c r="C116" s="13" t="n">
-        <v>96.94</v>
+        <v>93.47</v>
       </c>
       <c r="D116" s="13" t="n">
-        <v>94.04000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="E116" s="14" t="n">
-        <v>91.61</v>
+        <v>89.98</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>92.05</v>
+        <v>89.77</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>93.59999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>90.7</v>
+        <v>89.13</v>
       </c>
       <c r="I116" s="17" t="n">
-        <v>89.15000000000001</v>
+        <v>87.87</v>
       </c>
       <c r="J116" s="17" t="n">
-        <v>87.8</v>
+        <v>87.23</v>
       </c>
       <c r="K116" s="18" t="n">
-        <v>89.98999999999999</v>
+        <v>88.92</v>
       </c>
       <c r="L116" s="19" t="n">
-        <v>87.56</v>
+        <v>87.33</v>
       </c>
       <c r="M116" s="19" t="n">
-        <v>84.66</v>
-      </c>
-      <c r="N116" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>85.43000000000001</v>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>90.45999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>90.20999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="Q116" s="22" t="n">
-        <v>90.5</v>
+        <v>88.5</v>
       </c>
       <c r="R116" s="23" t="n">
-        <v>-0.55</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="117">
@@ -7826,37 +7826,37 @@
         </is>
       </c>
       <c r="C117" s="13" t="n">
-        <v>9.59</v>
+        <v>9.32</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>9.31</v>
+        <v>9.07</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>9.08</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9.07</v>
+        <v>8.84</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>9.25</v>
+        <v>9.01</v>
       </c>
       <c r="H117" s="16" t="n">
-        <v>8.970000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="I117" s="17" t="n">
-        <v>8.789999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="J117" s="17" t="n">
-        <v>8.69</v>
+        <v>8.51</v>
       </c>
       <c r="K117" s="18" t="n">
-        <v>8.92</v>
+        <v>8.73</v>
       </c>
       <c r="L117" s="19" t="n">
-        <v>8.69</v>
+        <v>8.52</v>
       </c>
       <c r="M117" s="19" t="n">
-        <v>8.41</v>
+        <v>8.27</v>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
         </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>8.960000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="P117" s="21" t="n">
-        <v>8.94</v>
+        <v>8.74</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>8.9</v>
+        <v>8.68</v>
       </c>
       <c r="R117" s="23" t="n">
-        <v>-1.22</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="118">
@@ -7888,37 +7888,37 @@
         </is>
       </c>
       <c r="C118" s="13" t="n">
-        <v>16.55</v>
+        <v>16.43</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>16.22</v>
+        <v>16.04</v>
       </c>
       <c r="E118" s="14" t="n">
-        <v>15.95</v>
+        <v>15.71</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>15.92</v>
+        <v>15.67</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>16.14</v>
+        <v>15.93</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>15.81</v>
+        <v>15.54</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>15.59</v>
+        <v>15.28</v>
       </c>
       <c r="J118" s="17" t="n">
-        <v>15.48</v>
+        <v>15.15</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>15.76</v>
+        <v>15.5</v>
       </c>
       <c r="L118" s="19" t="n">
-        <v>15.49</v>
+        <v>15.17</v>
       </c>
       <c r="M118" s="19" t="n">
-        <v>15.16</v>
+        <v>14.78</v>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
@@ -7926,16 +7926,16 @@
         </is>
       </c>
       <c r="O118" s="21" t="n">
-        <v>15.8</v>
+        <v>15.53</v>
       </c>
       <c r="P118" s="21" t="n">
-        <v>15.79</v>
+        <v>15.53</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>15.71</v>
+        <v>15.41</v>
       </c>
       <c r="R118" s="23" t="n">
-        <v>-1.38</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="119">
@@ -7950,37 +7950,37 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>11.03</v>
+        <v>11.04</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>10.86</v>
+        <v>10.82</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>10.71</v>
+        <v>10.63</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>10.71</v>
+        <v>10.68</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>10.81</v>
+        <v>10.79</v>
       </c>
       <c r="H119" s="16" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>10.54</v>
+        <v>10.46</v>
       </c>
       <c r="J119" s="17" t="n">
-        <v>10.47</v>
+        <v>10.35</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>10.62</v>
+        <v>10.51</v>
       </c>
       <c r="L119" s="19" t="n">
-        <v>10.47</v>
+        <v>10.32</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
@@ -7988,16 +7988,16 @@
         </is>
       </c>
       <c r="O119" s="21" t="n">
-        <v>10.64</v>
+        <v>10.55</v>
       </c>
       <c r="P119" s="21" t="n">
-        <v>10.63</v>
+        <v>10.53</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>10.6</v>
+        <v>10.57</v>
       </c>
       <c r="R119" s="23" t="n">
-        <v>-0.84</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="120">
@@ -8012,37 +8012,37 @@
         </is>
       </c>
       <c r="C120" s="13" t="n">
-        <v>12.35</v>
+        <v>12.49</v>
       </c>
       <c r="D120" s="13" t="n">
-        <v>12.18</v>
+        <v>12.23</v>
       </c>
       <c r="E120" s="14" t="n">
-        <v>12.03</v>
+        <v>12.01</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>12.05</v>
+        <v>12.11</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>12.14</v>
+        <v>12.22</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
       <c r="I120" s="17" t="n">
-        <v>11.88</v>
+        <v>11.85</v>
       </c>
       <c r="J120" s="17" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="K120" s="18" t="n">
-        <v>11.94</v>
+        <v>11.87</v>
       </c>
       <c r="L120" s="19" t="n">
-        <v>11.79</v>
+        <v>11.65</v>
       </c>
       <c r="M120" s="19" t="n">
-        <v>11.62</v>
+        <v>11.39</v>
       </c>
       <c r="N120" s="24" t="inlineStr">
         <is>
@@ -8050,16 +8050,16 @@
         </is>
       </c>
       <c r="O120" s="21" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="P120" s="21" t="n">
-        <v>11.95</v>
+        <v>11.89</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="R120" s="25" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="121">
@@ -8074,54 +8074,54 @@
         </is>
       </c>
       <c r="C121" s="13" t="n">
-        <v>7.31</v>
+        <v>7.06</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>7.08</v>
+        <v>6.93</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>6.89</v>
+        <v>6.82</v>
       </c>
       <c r="F121" s="15" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="G121" s="15" t="n">
         <v>6.92</v>
       </c>
-      <c r="G121" s="15" t="n">
-        <v>7.05</v>
-      </c>
       <c r="H121" s="16" t="n">
-        <v>6.82</v>
+        <v>6.79</v>
       </c>
       <c r="I121" s="17" t="n">
-        <v>6.69</v>
+        <v>6.73</v>
       </c>
       <c r="J121" s="17" t="n">
-        <v>6.59</v>
+        <v>6.66</v>
       </c>
       <c r="K121" s="18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="L121" s="19" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="M121" s="19" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="N121" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O121" s="21" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="P121" s="21" t="n">
         <v>6.76</v>
-      </c>
-      <c r="L121" s="19" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="M121" s="19" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="N121" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O121" s="21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P121" s="21" t="n">
-        <v>6.78</v>
       </c>
       <c r="Q121" s="22" t="n">
         <v>6.8</v>
       </c>
       <c r="R121" s="25" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -8136,54 +8136,54 @@
         </is>
       </c>
       <c r="C122" s="13" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
       <c r="D122" s="13" t="n">
         <v>6.71</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>6.6</v>
+        <v>6.52</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>6.68</v>
+        <v>6.66</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>6.55</v>
+        <v>6.44</v>
       </c>
       <c r="I122" s="17" t="n">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
       <c r="J122" s="17" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K122" s="18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L122" s="19" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M122" s="19" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O122" s="21" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="P122" s="21" t="n">
         <v>6.42</v>
       </c>
-      <c r="K122" s="18" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="L122" s="19" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="M122" s="19" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="N122" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O122" s="21" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="P122" s="21" t="n">
-        <v>6.54</v>
-      </c>
       <c r="Q122" s="22" t="n">
-        <v>6.51</v>
+        <v>6.39</v>
       </c>
       <c r="R122" s="23" t="n">
-        <v>-1.36</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="123">
@@ -8198,37 +8198,37 @@
         </is>
       </c>
       <c r="C123" s="13" t="n">
-        <v>28.74</v>
+        <v>28.53</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>27.96</v>
+        <v>27.67</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>27.31</v>
+        <v>26.95</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>27.3</v>
+        <v>26.85</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>27.78</v>
+        <v>27.43</v>
       </c>
       <c r="H123" s="16" t="n">
-        <v>27</v>
+        <v>26.57</v>
       </c>
       <c r="I123" s="17" t="n">
-        <v>26.52</v>
+        <v>25.99</v>
       </c>
       <c r="J123" s="17" t="n">
-        <v>26.22</v>
+        <v>25.71</v>
       </c>
       <c r="K123" s="18" t="n">
-        <v>26.87</v>
+        <v>26.47</v>
       </c>
       <c r="L123" s="19" t="n">
-        <v>26.22</v>
+        <v>25.75</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>25.44</v>
+        <v>24.89</v>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
@@ -8236,16 +8236,16 @@
         </is>
       </c>
       <c r="O123" s="21" t="n">
-        <v>26.97</v>
+        <v>26.55</v>
       </c>
       <c r="P123" s="21" t="n">
-        <v>26.93</v>
+        <v>26.54</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>26.82</v>
+        <v>26.28</v>
       </c>
       <c r="R123" s="23" t="n">
-        <v>-1.76</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="124">
@@ -8260,54 +8260,54 @@
         </is>
       </c>
       <c r="C124" s="13" t="n">
-        <v>165.41</v>
+        <v>165.88</v>
       </c>
       <c r="D124" s="13" t="n">
-        <v>161.51</v>
+        <v>160.58</v>
       </c>
       <c r="E124" s="14" t="n">
-        <v>158.24</v>
+        <v>156.13</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>160.4</v>
+        <v>156</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>161.7</v>
+        <v>159.3</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>157.8</v>
+        <v>154</v>
       </c>
       <c r="I124" s="17" t="n">
-        <v>156.5</v>
+        <v>150.7</v>
       </c>
       <c r="J124" s="17" t="n">
-        <v>153.9</v>
+        <v>148.7</v>
       </c>
       <c r="K124" s="18" t="n">
-        <v>156.06</v>
+        <v>153.17</v>
       </c>
       <c r="L124" s="19" t="n">
-        <v>152.79</v>
+        <v>148.72</v>
       </c>
       <c r="M124" s="19" t="n">
-        <v>148.89</v>
-      </c>
-      <c r="N124" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>143.42</v>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O124" s="21" t="n">
-        <v>157.08</v>
+        <v>153.79</v>
       </c>
       <c r="P124" s="21" t="n">
-        <v>156.36</v>
+        <v>153.58</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>159.1</v>
-      </c>
-      <c r="R124" s="25" t="n">
-        <v>0.19</v>
+        <v>152.7</v>
+      </c>
+      <c r="R124" s="23" t="n">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="125">
@@ -8322,37 +8322,37 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>53.77</v>
+        <v>53.07</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>52.52</v>
+        <v>51.76</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>51.48</v>
+        <v>50.66</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>51.33</v>
+        <v>50.71</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>52.17</v>
+        <v>51.49</v>
       </c>
       <c r="H125" s="16" t="n">
-        <v>50.92</v>
+        <v>50.18</v>
       </c>
       <c r="I125" s="17" t="n">
-        <v>50.08</v>
+        <v>49.4</v>
       </c>
       <c r="J125" s="17" t="n">
-        <v>49.67</v>
+        <v>48.87</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>50.77</v>
+        <v>49.93</v>
       </c>
       <c r="L125" s="19" t="n">
-        <v>49.73</v>
+        <v>48.83</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>48.48</v>
+        <v>47.52</v>
       </c>
       <c r="N125" s="20" t="inlineStr">
         <is>
@@ -8360,16 +8360,16 @@
         </is>
       </c>
       <c r="O125" s="21" t="n">
-        <v>50.89</v>
+        <v>50.1</v>
       </c>
       <c r="P125" s="21" t="n">
-        <v>50.87</v>
+        <v>50.03</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>50.5</v>
+        <v>49.94</v>
       </c>
       <c r="R125" s="23" t="n">
-        <v>-2.42</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="126">
@@ -8384,37 +8384,37 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>14.15</v>
+        <v>13.98</v>
       </c>
       <c r="D126" s="13" t="n">
-        <v>13.73</v>
+        <v>13.53</v>
       </c>
       <c r="E126" s="14" t="n">
-        <v>13.38</v>
+        <v>13.15</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>13.46</v>
+        <v>13.19</v>
       </c>
       <c r="G126" s="15" t="n">
-        <v>13.68</v>
+        <v>13.44</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>13.26</v>
+        <v>12.99</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>13.04</v>
+        <v>12.74</v>
       </c>
       <c r="J126" s="17" t="n">
-        <v>12.84</v>
+        <v>12.54</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>13.14</v>
+        <v>12.9</v>
       </c>
       <c r="L126" s="19" t="n">
-        <v>12.79</v>
+        <v>12.52</v>
       </c>
       <c r="M126" s="19" t="n">
-        <v>12.37</v>
+        <v>12.07</v>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
@@ -8422,16 +8422,16 @@
         </is>
       </c>
       <c r="O126" s="21" t="n">
-        <v>13.22</v>
+        <v>12.96</v>
       </c>
       <c r="P126" s="21" t="n">
-        <v>13.18</v>
+        <v>12.93</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="R126" s="25" t="n">
-        <v>0</v>
+        <v>12.93</v>
+      </c>
+      <c r="R126" s="23" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="127">
@@ -8446,54 +8446,54 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>14.61</v>
+        <v>14.87</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>14.32</v>
+        <v>14.37</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>14.08</v>
+        <v>13.95</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>14.04</v>
+        <v>13.89</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>14.24</v>
+        <v>14.23</v>
       </c>
       <c r="H127" s="16" t="n">
-        <v>13.95</v>
+        <v>13.73</v>
       </c>
       <c r="I127" s="17" t="n">
-        <v>13.75</v>
+        <v>13.39</v>
       </c>
       <c r="J127" s="17" t="n">
-        <v>13.66</v>
+        <v>13.23</v>
       </c>
       <c r="K127" s="18" t="n">
-        <v>13.91</v>
+        <v>13.67</v>
       </c>
       <c r="L127" s="19" t="n">
-        <v>13.67</v>
+        <v>13.25</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="N127" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>12.75</v>
+      </c>
+      <c r="N127" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O127" s="21" t="n">
-        <v>13.94</v>
+        <v>13.72</v>
       </c>
       <c r="P127" s="21" t="n">
-        <v>13.94</v>
+        <v>13.71</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>13.85</v>
+        <v>13.56</v>
       </c>
       <c r="R127" s="23" t="n">
-        <v>-1.91</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="128">
@@ -8508,54 +8508,54 @@
         </is>
       </c>
       <c r="C128" s="13" t="n">
-        <v>6.99</v>
+        <v>7.09</v>
       </c>
       <c r="D128" s="13" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="E128" s="14" t="n">
-        <v>6.55</v>
+        <v>6.56</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="G128" s="15" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>6.45</v>
+        <v>6.43</v>
       </c>
       <c r="I128" s="17" t="n">
-        <v>6.29</v>
+        <v>6.23</v>
       </c>
       <c r="J128" s="17" t="n">
-        <v>6.21</v>
+        <v>6.14</v>
       </c>
       <c r="K128" s="18" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="L128" s="19" t="n">
-        <v>6.21</v>
+        <v>6.15</v>
       </c>
       <c r="M128" s="19" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="N128" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
+        <v>5.86</v>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
+        <is>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O128" s="21" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="P128" s="21" t="n">
-        <v>6.43</v>
+        <v>6.42</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="R128" s="23" t="n">
-        <v>-0.47</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="129">
@@ -8570,37 +8570,37 @@
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>9.59</v>
+        <v>11</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>9.380000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>9.23</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>9.34</v>
+        <v>10.2</v>
       </c>
       <c r="H129" s="16" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I129" s="17" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="I129" s="17" t="n">
-        <v>9.02</v>
-      </c>
       <c r="J129" s="17" t="n">
-        <v>8.92</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K129" s="18" t="n">
-        <v>9.09</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L129" s="19" t="n">
-        <v>8.91</v>
+        <v>8.6</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>8.699999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="N129" s="24" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         </is>
       </c>
       <c r="O129" s="21" t="n">
-        <v>9.119999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="P129" s="21" t="n">
-        <v>9.1</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>9.109999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="R129" s="25" t="n">
-        <v>0.44</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="130">
@@ -8632,54 +8632,54 @@
         </is>
       </c>
       <c r="C130" s="13" t="n">
-        <v>152.59</v>
+        <v>148.21</v>
       </c>
       <c r="D130" s="13" t="n">
-        <v>144.19</v>
+        <v>142.21</v>
       </c>
       <c r="E130" s="14" t="n">
-        <v>137.15</v>
+        <v>137.18</v>
       </c>
       <c r="F130" s="15" t="n">
-        <v>136.4</v>
+        <v>137.9</v>
       </c>
       <c r="G130" s="15" t="n">
-        <v>141.9</v>
+        <v>141.2</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>133.5</v>
+        <v>135.2</v>
       </c>
       <c r="I130" s="17" t="n">
-        <v>128</v>
+        <v>131.9</v>
       </c>
       <c r="J130" s="17" t="n">
-        <v>125.1</v>
+        <v>129.2</v>
       </c>
       <c r="K130" s="18" t="n">
-        <v>132.45</v>
+        <v>133.82</v>
       </c>
       <c r="L130" s="19" t="n">
-        <v>125.41</v>
+        <v>128.79</v>
       </c>
       <c r="M130" s="19" t="n">
-        <v>117.01</v>
-      </c>
-      <c r="N130" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
+        <v>122.79</v>
+      </c>
+      <c r="N130" s="24" t="inlineStr">
+        <is>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O130" s="21" t="n">
-        <v>133.3</v>
+        <v>134.74</v>
       </c>
       <c r="P130" s="21" t="n">
-        <v>133.1</v>
+        <v>134.29</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>130.9</v>
-      </c>
-      <c r="R130" s="23" t="n">
-        <v>-5.35</v>
+        <v>134.6</v>
+      </c>
+      <c r="R130" s="25" t="n">
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/radar.xlsx
+++ b/radar.xlsx
@@ -36,11 +36,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="23">
@@ -137,7 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +650,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>رادار تاسي — التحليل الفني ليوم 2026-09-29</t>
+          <t>رادار تاسي — التحليل الفني ليوم 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -758,54 +758,54 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>20.25</v>
+        <v>20.23</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>20.13</v>
+        <v>20.19</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>20.21</v>
+        <v>20.24</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>20.08</v>
+        <v>20.11</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>20</v>
+        <v>20.06</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>19.95</v>
+        <v>19.98</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>20.07</v>
+        <v>20.05</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>19.96</v>
+        <v>19.94</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>19.83</v>
+        <v>19.81</v>
       </c>
       <c r="N3" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O3" s="21" t="n">
         <v>20.08</v>
       </c>
       <c r="P3" s="21" t="n">
-        <v>20.08</v>
+        <v>20.06</v>
       </c>
       <c r="Q3" s="22" t="n">
-        <v>20.04</v>
+        <v>20.15</v>
       </c>
       <c r="R3" s="23" t="n">
-        <v>-0.1</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="4">
@@ -820,54 +820,54 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>11.79</v>
+        <v>12</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11.62</v>
+        <v>11.65</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>11.66</v>
+        <v>11.64</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>11.7</v>
+        <v>11.76</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>11.61</v>
+        <v>11.57</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>11.57</v>
+        <v>11.45</v>
       </c>
       <c r="J4" s="17" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="N4" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="P4" s="21" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="Q4" s="22" t="n">
         <v>11.52</v>
       </c>
-      <c r="K4" s="18" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="L4" s="19" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="M4" s="19" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="P4" s="21" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="Q4" s="22" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="R4" s="23" t="n">
-        <v>-0.17</v>
+      <c r="R4" s="25" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="5">
@@ -882,39 +882,39 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>14.81</v>
+        <v>14.7</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.65</v>
+        <v>14.62</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>14.69</v>
+        <v>14.61</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14.78</v>
+        <v>14.67</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>14.59</v>
+        <v>14.57</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>14.5</v>
+        <v>14.51</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>14.4</v>
+        <v>14.47</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>14.54</v>
+        <v>14.56</v>
       </c>
       <c r="L5" s="19" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="M5" s="19" t="n">
         <v>14.38</v>
       </c>
-      <c r="M5" s="19" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -923,13 +923,13 @@
         <v>14.57</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>14.56</v>
+        <v>14.57</v>
       </c>
       <c r="Q5" s="22" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="R5" s="23" t="n">
-        <v>-0.48</v>
+        <v>14.54</v>
+      </c>
+      <c r="R5" s="25" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="6">
@@ -944,54 +944,54 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>21.39</v>
+        <v>20.88</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>20.96</v>
+        <v>20.66</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20.6</v>
+        <v>20.47</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>20.57</v>
+        <v>20.56</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>20.85</v>
+        <v>20.65</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>20.42</v>
+        <v>20.43</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>20.14</v>
+        <v>20.34</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>19.99</v>
+        <v>20.21</v>
       </c>
       <c r="K6" s="18" t="n">
         <v>20.35</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>19.99</v>
+        <v>20.16</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>19.56</v>
+        <v>19.94</v>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
         <v>20.4</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>20.39</v>
+        <v>20.37</v>
       </c>
       <c r="Q6" s="22" t="n">
-        <v>20.3</v>
+        <v>20.47</v>
       </c>
       <c r="R6" s="23" t="n">
-        <v>-1.31</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="7">
@@ -1006,54 +1006,54 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>33.77</v>
+        <v>33.79</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>33.47</v>
+        <v>33.55</v>
       </c>
       <c r="E7" s="14" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="K7" s="18" t="n">
         <v>33.21</v>
       </c>
-      <c r="F7" s="15" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>33.17</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>33.05</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>32.87</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>33.05</v>
-      </c>
       <c r="L7" s="19" t="n">
-        <v>32.79</v>
+        <v>33.01</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="N7" s="24" t="inlineStr">
+        <v>32.77</v>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O7" s="21" t="n">
-        <v>33.12</v>
+        <v>33.26</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>33.07</v>
+        <v>33.23</v>
       </c>
       <c r="Q7" s="22" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="R7" s="25" t="n">
-        <v>0.12</v>
+        <v>33.32</v>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8">
@@ -1068,54 +1068,54 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>23.42</v>
+        <v>23.4</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>23.16</v>
+        <v>23.14</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>22.94</v>
+        <v>22.92</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>22.98</v>
+        <v>22.95</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>23.12</v>
+        <v>23.09</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>22.86</v>
+        <v>22.83</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>22.72</v>
+        <v>22.69</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>22.6</v>
+        <v>22.57</v>
       </c>
       <c r="K8" s="18" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="L8" s="19" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="P8" s="21" t="n">
         <v>22.8</v>
       </c>
-      <c r="L8" s="19" t="n">
-        <v>22.58</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="N8" s="24" t="inlineStr">
-        <is>
-          <t>صاعد</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>22.84</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <v>22.82</v>
-      </c>
       <c r="Q8" s="22" t="n">
-        <v>22.84</v>
+        <v>22.8</v>
       </c>
       <c r="R8" s="25" t="n">
-        <v>0.18</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="9">
@@ -1130,54 +1130,54 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>134.12</v>
+        <v>130.04</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>127.62</v>
+        <v>124.64</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>122.17</v>
+        <v>120.11</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>122.17</v>
+        <v>119.83</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>126.13</v>
+        <v>123.27</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>119.63</v>
+        <v>117.87</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>115.67</v>
+        <v>114.43</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>113.13</v>
+        <v>112.47</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>118.53</v>
+        <v>117.09</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>113.08</v>
+        <v>112.56</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>106.58</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
+        <v>107.16</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O9" s="21" t="n">
-        <v>119.34</v>
+        <v>117.69</v>
       </c>
       <c r="P9" s="21" t="n">
-        <v>119.04</v>
+        <v>117.51</v>
       </c>
       <c r="Q9" s="22" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="R9" s="23" t="n">
-        <v>-3.27</v>
+        <v>116.4</v>
+      </c>
+      <c r="R9" s="25" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="10">
@@ -1192,54 +1192,54 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>65.20999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>64.45999999999999</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>63.84</v>
+        <v>63.85</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>63.75</v>
+        <v>63.77</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>64.25</v>
+        <v>64.23</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>63.5</v>
+        <v>63.53</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>63</v>
+        <v>63.07</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>62.75</v>
+        <v>62.83</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>63.41</v>
+        <v>63.45</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>62.79</v>
+        <v>62.87</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+        <v>62.17</v>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>63.49</v>
+        <v>63.52</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>63.47</v>
+        <v>63.51</v>
       </c>
       <c r="Q10" s="22" t="n">
-        <v>63.25</v>
+        <v>63.3</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="11">
@@ -1254,54 +1254,54 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>24.96</v>
+        <v>24.67</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>24.61</v>
+        <v>24.34</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>24.31</v>
+        <v>24.07</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>24.29</v>
+        <v>24.03</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>24.52</v>
+        <v>24.25</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>24.17</v>
+        <v>23.92</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>23.94</v>
+        <v>23.7</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>23.82</v>
+        <v>23.59</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>24.12</v>
+        <v>23.88</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>23.82</v>
+        <v>23.61</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>23.47</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
+        <v>23.28</v>
+      </c>
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O11" s="21" t="n">
-        <v>24.16</v>
+        <v>23.91</v>
       </c>
       <c r="P11" s="21" t="n">
-        <v>24.14</v>
+        <v>23.91</v>
       </c>
       <c r="Q11" s="22" t="n">
-        <v>24.07</v>
-      </c>
-      <c r="R11" s="23" t="n">
-        <v>-1.31</v>
+        <v>23.81</v>
+      </c>
+      <c r="R11" s="25" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="12">
@@ -1316,54 +1316,54 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>25.25</v>
+        <v>24.94</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>24.82</v>
+        <v>24.68</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>24.46</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>24.53</v>
+        <v>24.47</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>24.75</v>
+        <v>24.63</v>
       </c>
       <c r="H12" s="16" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="K12" s="18" t="n">
         <v>24.32</v>
       </c>
-      <c r="I12" s="17" t="n">
+      <c r="L12" s="19" t="n">
         <v>24.1</v>
       </c>
-      <c r="J12" s="17" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="L12" s="19" t="n">
-        <v>23.85</v>
-      </c>
       <c r="M12" s="19" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+        <v>23.84</v>
+      </c>
+      <c r="N12" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>24.29</v>
+        <v>24.35</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>24.25</v>
+        <v>24.34</v>
       </c>
       <c r="Q12" s="22" t="n">
-        <v>24.3</v>
+        <v>24.32</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>-0.82</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
@@ -1378,54 +1378,54 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>41.64</v>
+        <v>40.97</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>40.96</v>
+        <v>40.53</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>40.39</v>
+        <v>40.16</v>
       </c>
       <c r="F13" s="15" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="G13" s="15" t="n">
         <v>40.41</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>40.81</v>
-      </c>
       <c r="H13" s="16" t="n">
-        <v>40.13</v>
+        <v>39.97</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>39.73</v>
+        <v>39.67</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>39.45</v>
+        <v>39.53</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>40.01</v>
+        <v>39.92</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.44</v>
+        <v>39.55</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>38.76</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
+        <v>39.11</v>
+      </c>
+      <c r="N13" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O13" s="21" t="n">
-        <v>40.1</v>
+        <v>39.96</v>
       </c>
       <c r="P13" s="21" t="n">
-        <v>40.06</v>
+        <v>39.95</v>
       </c>
       <c r="Q13" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="R13" s="23" t="n">
-        <v>-1.14</v>
+        <v>39.82</v>
+      </c>
+      <c r="R13" s="25" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="14">
@@ -1440,54 +1440,54 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8.56</v>
+        <v>8.65</v>
       </c>
       <c r="D14" s="13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>8.48</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>8.470000000000001</v>
-      </c>
       <c r="H14" s="16" t="n">
-        <v>8.390000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>8.31</v>
+        <v>8.18</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>8.369999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L14" s="19" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="P14" s="21" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M14" s="19" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="P14" s="21" t="n">
-        <v>8.369999999999999</v>
-      </c>
       <c r="Q14" s="22" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="R14" s="23" t="n">
-        <v>-0.12</v>
+        <v>8.32</v>
+      </c>
+      <c r="R14" s="25" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="15">
@@ -1502,54 +1502,54 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>13.47</v>
+        <v>13.31</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>13.45</v>
+        <v>13.3</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>13.66</v>
+        <v>13.54</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>13.32</v>
+        <v>13.16</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>13.11</v>
+        <v>12.92</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>12.98</v>
+        <v>12.78</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>13.27</v>
+        <v>13.09</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>12.99</v>
+        <v>12.78</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
+        <v>12.4</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O15" s="21" t="n">
-        <v>13.31</v>
+        <v>13.14</v>
       </c>
       <c r="P15" s="21" t="n">
-        <v>13.3</v>
+        <v>13.12</v>
       </c>
       <c r="Q15" s="22" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="R15" s="23" t="n">
-        <v>-1.85</v>
+        <v>13.07</v>
+      </c>
+      <c r="R15" s="25" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="16">
@@ -1564,39 +1564,39 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="J16" s="17" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="K16" s="18" t="n">
         <v>3.84</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="M16" s="19" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
+        <v>3.66</v>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
@@ -1608,10 +1608,10 @@
         <v>3.85</v>
       </c>
       <c r="Q16" s="22" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R16" s="23" t="n">
-        <v>-2.28</v>
+        <v>3.85</v>
+      </c>
+      <c r="R16" s="25" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="17">
@@ -1626,54 +1626,54 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>17.59</v>
+        <v>17.56</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>17.07</v>
+        <v>16.77</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>16.64</v>
+        <v>16.11</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>16.58</v>
+        <v>16.04</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>16.92</v>
+        <v>16.56</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>16.4</v>
+        <v>15.77</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>16.06</v>
+        <v>15.25</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>15.88</v>
+        <v>14.98</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>16.34</v>
+        <v>15.66</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>15.91</v>
+        <v>15</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
+        <v>14.21</v>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O17" s="21" t="n">
-        <v>16.39</v>
+        <v>15.75</v>
       </c>
       <c r="P17" s="21" t="n">
-        <v>16.38</v>
+        <v>15.73</v>
       </c>
       <c r="Q17" s="22" t="n">
-        <v>16.23</v>
-      </c>
-      <c r="R17" s="23" t="n">
-        <v>-3.1</v>
+        <v>15.53</v>
+      </c>
+      <c r="R17" s="25" t="n">
+        <v>-4.31</v>
       </c>
     </row>
     <row r="18">
@@ -1688,54 +1688,54 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>25.35</v>
+        <v>23.92</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>24.55</v>
+        <v>23.59</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>23.88</v>
+        <v>23.32</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>23.82</v>
+        <v>23.33</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>24.34</v>
+        <v>23.53</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>23.54</v>
+        <v>23.2</v>
       </c>
       <c r="I18" s="17" t="n">
-        <v>23.02</v>
+        <v>23</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>22.74</v>
+        <v>22.87</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>23.44</v>
+        <v>23.13</v>
       </c>
       <c r="L18" s="19" t="n">
-        <v>22.77</v>
+        <v>22.86</v>
       </c>
       <c r="M18" s="19" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
+        <v>22.53</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O18" s="21" t="n">
-        <v>23.52</v>
+        <v>23.18</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>23.5</v>
+        <v>23.16</v>
       </c>
       <c r="Q18" s="22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R18" s="23" t="n">
-        <v>-3.28</v>
+        <v>23.14</v>
+      </c>
+      <c r="R18" s="25" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1750,45 +1750,45 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>63.41</v>
+        <v>62.59</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>62.26</v>
+        <v>61.79</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>61.3</v>
+        <v>61.12</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>61.33</v>
+        <v>61.13</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>62.02</v>
+        <v>61.62</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>60.87</v>
+        <v>60.82</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>60.18</v>
+        <v>60.33</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>59.72</v>
+        <v>60.02</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>60.65</v>
+        <v>60.68</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>59.69</v>
+        <v>60.01</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>58.54</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
+        <v>59.21</v>
+      </c>
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O19" s="21" t="n">
-        <v>60.8</v>
+        <v>60.78</v>
       </c>
       <c r="P19" s="21" t="n">
         <v>60.74</v>
@@ -1797,7 +1797,7 @@
         <v>60.65</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>-1.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1812,54 +1812,54 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11.21</v>
+        <v>10.81</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>10.89</v>
+        <v>10.6</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>10.62</v>
+        <v>10.42</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>10.6</v>
+        <v>10.41</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>10.8</v>
+        <v>10.55</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>10.48</v>
+        <v>10.34</v>
       </c>
       <c r="I20" s="17" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="N20" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="Q20" s="22" t="n">
         <v>10.28</v>
       </c>
-      <c r="J20" s="17" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="L20" s="19" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="M20" s="19" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>10.47</v>
-      </c>
-      <c r="Q20" s="22" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="R20" s="23" t="n">
-        <v>-2.35</v>
+      <c r="R20" s="25" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="21">
@@ -1874,54 +1874,54 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17.04</v>
+        <v>17.08</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>16.83</v>
+        <v>16.75</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>16.65</v>
+        <v>16.48</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>16.64</v>
+        <v>16.45</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>16.77</v>
+        <v>16.66</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>16.56</v>
+        <v>16.33</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>16.43</v>
+        <v>16.12</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>16.35</v>
+        <v>16</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>16.54</v>
+        <v>16.29</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>16.36</v>
+        <v>16.02</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
+        <v>15.69</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O21" s="21" t="n">
-        <v>16.56</v>
+        <v>16.33</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>16.55</v>
+        <v>16.32</v>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="R21" s="23" t="n">
-        <v>-0.66</v>
+        <v>16.23</v>
+      </c>
+      <c r="R21" s="25" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="22">
@@ -1936,54 +1936,54 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37.18</v>
+        <v>36.32</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>35.82</v>
+        <v>35.32</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>34.68</v>
+        <v>34.48</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>34.71</v>
+        <v>35.03</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>35.53</v>
+        <v>35.37</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>34.17</v>
+        <v>34.37</v>
       </c>
       <c r="I22" s="17" t="n">
-        <v>33.35</v>
+        <v>34.03</v>
       </c>
       <c r="J22" s="17" t="n">
-        <v>32.81</v>
+        <v>33.37</v>
       </c>
       <c r="K22" s="18" t="n">
         <v>33.92</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>32.78</v>
+        <v>33.08</v>
       </c>
       <c r="M22" s="19" t="n">
-        <v>31.42</v>
+        <v>32.08</v>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O22" s="21" t="n">
-        <v>34.1</v>
+        <v>34.18</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>34.03</v>
+        <v>34</v>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>33.9</v>
+        <v>34.7</v>
       </c>
       <c r="R22" s="23" t="n">
-        <v>-3.03</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="23">
@@ -1998,54 +1998,54 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>16.84</v>
+        <v>14.96</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>15.68</v>
+        <v>14.48</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>14.7</v>
+        <v>14.07</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>14.61</v>
+        <v>14.13</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>15.36</v>
+        <v>14.39</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>13.45</v>
+        <v>13.65</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>13.04</v>
+        <v>13.43</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>14.06</v>
+        <v>13.81</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>13.08</v>
+        <v>13.4</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
+        <v>12.92</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O23" s="21" t="n">
-        <v>14.17</v>
+        <v>13.88</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>14.15</v>
+        <v>13.84</v>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
       <c r="R23" s="23" t="n">
-        <v>-5.53</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2060,54 +2060,54 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>35.62</v>
+        <v>35.68</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>34.48</v>
+        <v>34.07</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>34.44</v>
+        <v>33.99</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>34.84</v>
+        <v>34.57</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>34.22</v>
+        <v>33.69</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>33.82</v>
+        <v>33.11</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>33.6</v>
+        <v>32.81</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>34.14</v>
+        <v>33.57</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>33.62</v>
+        <v>32.84</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>33</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
+        <v>31.96</v>
+      </c>
+      <c r="N24" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O24" s="21" t="n">
-        <v>34.2</v>
+        <v>33.66</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>34.18</v>
+        <v>33.64</v>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>34.04</v>
-      </c>
-      <c r="R24" s="23" t="n">
-        <v>-1.33</v>
+        <v>33.42</v>
+      </c>
+      <c r="R24" s="25" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="25">
@@ -2122,54 +2122,54 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>59.07</v>
+        <v>57.2</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>57.17</v>
+        <v>55.5</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>55.58</v>
+        <v>54.08</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>55.43</v>
+        <v>53.88</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>56.67</v>
+        <v>55.02</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>54.77</v>
+        <v>53.32</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>53.53</v>
+        <v>52.18</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>52.87</v>
+        <v>51.62</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>54.52</v>
+        <v>53.12</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>52.93</v>
+        <v>51.7</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O25" s="21" t="n">
-        <v>54.72</v>
+        <v>53.29</v>
       </c>
       <c r="P25" s="21" t="n">
-        <v>54.67</v>
+        <v>53.26</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="R25" s="23" t="n">
-        <v>-1.99</v>
+        <v>52.75</v>
+      </c>
+      <c r="R25" s="25" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="26">
@@ -2184,54 +2184,54 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>221.33</v>
+        <v>190.98</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>205.43</v>
+        <v>184.38</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>192.1</v>
+        <v>178.85</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>190.5</v>
+        <v>178.63</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>201</v>
+        <v>182.77</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>185.1</v>
+        <v>176.17</v>
       </c>
       <c r="I26" s="17" t="n">
-        <v>174.6</v>
+        <v>172.03</v>
       </c>
       <c r="J26" s="17" t="n">
-        <v>169.2</v>
+        <v>169.57</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>183.2</v>
+        <v>175.15</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>169.87</v>
+        <v>169.62</v>
       </c>
       <c r="M26" s="19" t="n">
-        <v>153.97</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
+        <v>163.02</v>
+      </c>
+      <c r="N26" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O26" s="21" t="n">
-        <v>184.77</v>
+        <v>175.92</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>184.44</v>
+        <v>175.67</v>
       </c>
       <c r="Q26" s="22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R26" s="23" t="n">
-        <v>-7.98</v>
+        <v>174.5</v>
+      </c>
+      <c r="R26" s="25" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="27">
@@ -2246,54 +2246,54 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>77.94</v>
+        <v>73.37</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>75.04000000000001</v>
+        <v>72.37</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>72.61</v>
+        <v>71.53</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>72.52</v>
+        <v>71.45</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>74.33</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>71.43000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>69.62</v>
+        <v>70.45</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>68.53</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>70.98999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>68.56</v>
+        <v>70.13</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>65.66</v>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
+        <v>69.13</v>
+      </c>
+      <c r="N27" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O27" s="21" t="n">
-        <v>71.31999999999999</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>71.20999999999999</v>
+        <v>71.05</v>
       </c>
       <c r="Q27" s="22" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="R27" s="23" t="n">
-        <v>-3.68</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="28">
@@ -2308,54 +2308,54 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>20.79</v>
+        <v>21.21</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>20.52</v>
+        <v>20.73</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>20.29</v>
+        <v>20.32</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>20.31</v>
+        <v>20.4</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>20.47</v>
+        <v>20.65</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20.2</v>
+        <v>20.17</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>20.04</v>
+        <v>19.92</v>
       </c>
       <c r="J28" s="17" t="n">
-        <v>19.93</v>
+        <v>19.69</v>
       </c>
       <c r="K28" s="18" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="L28" s="19" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="M28" s="19" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="N28" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="Q28" s="22" t="n">
         <v>20.14</v>
       </c>
-      <c r="L28" s="19" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="M28" s="19" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="Q28" s="22" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="R28" s="23" t="n">
-        <v>-0.84</v>
+      <c r="R28" s="25" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="29">
@@ -2370,54 +2370,54 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>75.78</v>
+        <v>76.16</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>74.68000000000001</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>73.76000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>73.7</v>
+        <v>72.52</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>74.40000000000001</v>
+        <v>73.73</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>73.3</v>
+        <v>71.78</v>
       </c>
       <c r="I29" s="17" t="n">
-        <v>72.59999999999999</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="J29" s="17" t="n">
-        <v>72.2</v>
+        <v>69.83</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>73.14</v>
+        <v>71.48</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>72.22</v>
+        <v>69.84</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>71.12</v>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
+        <v>67.89</v>
+      </c>
+      <c r="N29" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O29" s="21" t="n">
-        <v>73.26000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>73.23</v>
+        <v>71.63</v>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="R29" s="23" t="n">
-        <v>-0.68</v>
+        <v>71.3</v>
+      </c>
+      <c r="R29" s="25" t="n">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="30">
@@ -2432,54 +2432,54 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="D30" s="13" t="n">
         <v>29.49</v>
       </c>
-      <c r="D30" s="13" t="n">
-        <v>28.69</v>
-      </c>
       <c r="E30" s="14" t="n">
-        <v>28.02</v>
+        <v>28.45</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>28.5</v>
+        <v>29.18</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>27.7</v>
+        <v>27.94</v>
       </c>
       <c r="I30" s="17" t="n">
-        <v>27.2</v>
+        <v>27.16</v>
       </c>
       <c r="J30" s="17" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>27.58</v>
+        <v>27.75</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>26.91</v>
+        <v>26.71</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
+        <v>25.47</v>
+      </c>
+      <c r="N30" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O30" s="21" t="n">
-        <v>27.67</v>
+        <v>27.89</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>27.64</v>
+        <v>27.85</v>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R30" s="25" t="n">
-        <v>0.36</v>
+        <v>27.62</v>
+      </c>
+      <c r="R30" s="23" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="31">
@@ -2494,54 +2494,54 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>49.12</v>
+        <v>47.54</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>48.08</v>
+        <v>46.96</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>47.21</v>
+        <v>46.47</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>47.09</v>
+        <v>46.43</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>47.79</v>
+        <v>46.81</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>46.75</v>
+        <v>46.23</v>
       </c>
       <c r="I31" s="17" t="n">
-        <v>46.05</v>
+        <v>45.85</v>
       </c>
       <c r="J31" s="17" t="n">
-        <v>45.71</v>
+        <v>45.65</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>46.63</v>
+        <v>46.15</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>45.76</v>
+        <v>45.66</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>44.72</v>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
+        <v>45.08</v>
+      </c>
+      <c r="N31" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O31" s="21" t="n">
-        <v>46.73</v>
+        <v>46.21</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>46.71</v>
+        <v>46.19</v>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="R31" s="23" t="n">
-        <v>-2.27</v>
+        <v>46.06</v>
+      </c>
+      <c r="R31" s="25" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="32">
@@ -2556,54 +2556,54 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>126.85</v>
+        <v>123.85</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>123.85</v>
+        <v>121.35</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>121.34</v>
+        <v>119.25</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>121</v>
+        <v>118.97</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>123</v>
+        <v>120.63</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>120</v>
+        <v>118.13</v>
       </c>
       <c r="I32" s="17" t="n">
-        <v>118</v>
+        <v>116.47</v>
       </c>
       <c r="J32" s="17" t="n">
-        <v>117</v>
+        <v>115.63</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>119.66</v>
+        <v>117.85</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>117.15</v>
+        <v>115.76</v>
       </c>
       <c r="M32" s="19" t="n">
-        <v>114.15</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
+        <v>113.26</v>
+      </c>
+      <c r="N32" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O32" s="21" t="n">
-        <v>119.95</v>
+        <v>118.09</v>
       </c>
       <c r="P32" s="21" t="n">
-        <v>119.89</v>
+        <v>118.05</v>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>119</v>
-      </c>
-      <c r="R32" s="23" t="n">
-        <v>-2.86</v>
+        <v>117.3</v>
+      </c>
+      <c r="R32" s="25" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="33">
@@ -2618,54 +2618,54 @@
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>56.79</v>
+        <v>56.07</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>54.79</v>
+        <v>54.17</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>53.11</v>
+        <v>52.58</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>53.18</v>
+        <v>52.57</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>54.37</v>
+        <v>53.73</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>52.37</v>
+        <v>51.83</v>
       </c>
       <c r="I33" s="17" t="n">
-        <v>51.18</v>
+        <v>50.67</v>
       </c>
       <c r="J33" s="17" t="n">
-        <v>50.37</v>
+        <v>49.93</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>51.99</v>
+        <v>51.52</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>50.31</v>
+        <v>49.93</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="N33" s="20" t="inlineStr">
+        <v>48.03</v>
+      </c>
+      <c r="N33" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O33" s="21" t="n">
-        <v>52.26</v>
+        <v>51.75</v>
       </c>
       <c r="P33" s="21" t="n">
-        <v>52.15</v>
+        <v>51.67</v>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="R33" s="23" t="n">
-        <v>-2.89</v>
+        <v>51.4</v>
+      </c>
+      <c r="R33" s="25" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="34">
@@ -2680,54 +2680,54 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>23.6</v>
+        <v>23.03</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>22.99</v>
+        <v>22.51</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>22.48</v>
+        <v>22.08</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>22.44</v>
+        <v>22.02</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>22.83</v>
+        <v>22.37</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>22.22</v>
+        <v>21.85</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>21.83</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="17" t="n">
-        <v>21.61</v>
+        <v>21.33</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>22.13</v>
+        <v>21.78</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>21.62</v>
+        <v>21.35</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
+        <v>20.83</v>
+      </c>
+      <c r="N34" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O34" s="21" t="n">
-        <v>22.2</v>
+        <v>21.84</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>22.18</v>
+        <v>21.82</v>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>22.05</v>
-      </c>
-      <c r="R34" s="23" t="n">
-        <v>-1.74</v>
+        <v>21.68</v>
+      </c>
+      <c r="R34" s="25" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="35">
@@ -2742,54 +2742,54 @@
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>25.88</v>
+        <v>24.99</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>25.23</v>
+        <v>24.71</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>24.69</v>
+        <v>24.48</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>24.8</v>
+        <v>24.47</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>25.14</v>
+        <v>24.65</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>24.49</v>
+        <v>24.37</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>24.15</v>
+        <v>24.19</v>
       </c>
       <c r="J35" s="17" t="n">
-        <v>23.84</v>
+        <v>24.09</v>
       </c>
       <c r="K35" s="18" t="n">
         <v>24.32</v>
       </c>
       <c r="L35" s="19" t="n">
-        <v>23.78</v>
+        <v>24.09</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>23.13</v>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
+        <v>23.81</v>
+      </c>
+      <c r="N35" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O35" s="21" t="n">
-        <v>24.43</v>
+        <v>24.36</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>24.37</v>
+        <v>24.34</v>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="R35" s="23" t="n">
-        <v>-1.37</v>
+        <v>24.3</v>
+      </c>
+      <c r="R35" s="25" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="36">
@@ -2804,54 +2804,54 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>8.210000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>8.07</v>
+        <v>7.97</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>8.07</v>
+        <v>7.95</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>8.17</v>
+        <v>8.09</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>8.01</v>
+        <v>7.87</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>7.91</v>
+        <v>7.73</v>
       </c>
       <c r="J36" s="17" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="K36" s="18" t="n">
         <v>7.85</v>
       </c>
-      <c r="K36" s="18" t="n">
-        <v>7.99</v>
-      </c>
       <c r="L36" s="19" t="n">
-        <v>7.85</v>
+        <v>7.66</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
+        <v>7.44</v>
+      </c>
+      <c r="N36" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O36" s="21" t="n">
-        <v>8</v>
+        <v>7.87</v>
       </c>
       <c r="P36" s="21" t="n">
-        <v>8</v>
+        <v>7.87</v>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="R36" s="23" t="n">
-        <v>-1.97</v>
+        <v>7.8</v>
+      </c>
+      <c r="R36" s="25" t="n">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="37">
@@ -2866,54 +2866,54 @@
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>33.11</v>
+        <v>33.28</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>32.51</v>
+        <v>32.4</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>32.01</v>
+        <v>31.67</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>31.97</v>
+        <v>31.57</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>32.35</v>
+        <v>32.15</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>31.75</v>
+        <v>31.27</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>31.37</v>
+        <v>30.69</v>
       </c>
       <c r="J37" s="17" t="n">
-        <v>31.15</v>
+        <v>30.39</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>31.67</v>
+        <v>31.17</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>31.17</v>
+        <v>30.44</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
+        <v>29.56</v>
+      </c>
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O37" s="21" t="n">
-        <v>31.74</v>
+        <v>31.26</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>31.72</v>
+        <v>31.24</v>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>31.58</v>
+        <v>30.98</v>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.25</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="38">
@@ -2928,54 +2928,54 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>178.13</v>
+        <v>174.32</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>174.03</v>
+        <v>171.22</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>170.6</v>
+        <v>168.62</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>171.2</v>
+        <v>169.07</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>173.4</v>
+        <v>170.73</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>169.3</v>
+        <v>167.63</v>
       </c>
       <c r="I38" s="17" t="n">
-        <v>167.1</v>
+        <v>165.97</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>165.2</v>
+        <v>164.53</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>168.3</v>
+        <v>166.88</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>164.87</v>
+        <v>164.28</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>160.77</v>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
+        <v>161.18</v>
+      </c>
+      <c r="N38" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O38" s="21" t="n">
-        <v>168.96</v>
+        <v>167.38</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>168.62</v>
+        <v>167.12</v>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>169</v>
-      </c>
-      <c r="R38" s="23" t="n">
-        <v>-1.57</v>
+        <v>167.4</v>
+      </c>
+      <c r="R38" s="25" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="39">
@@ -2990,54 +2990,54 @@
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>12.74</v>
+        <v>13.01</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>12.44</v>
+        <v>12.45</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>12.18</v>
+        <v>11.98</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>12.18</v>
+        <v>12.01</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>12.37</v>
+        <v>12.34</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>12.07</v>
+        <v>11.78</v>
       </c>
       <c r="I39" s="17" t="n">
-        <v>11.88</v>
+        <v>11.45</v>
       </c>
       <c r="J39" s="17" t="n">
-        <v>11.77</v>
+        <v>11.22</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>12.02</v>
+        <v>11.66</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>11.76</v>
+        <v>11.19</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
+        <v>10.63</v>
+      </c>
+      <c r="N39" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O39" s="21" t="n">
-        <v>12.05</v>
+        <v>11.74</v>
       </c>
       <c r="P39" s="21" t="n">
-        <v>12.04</v>
+        <v>11.71</v>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="R39" s="23" t="n">
-        <v>-1.07</v>
+        <v>11.69</v>
+      </c>
+      <c r="R39" s="25" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="40">
@@ -3052,54 +3052,54 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>20.95</v>
+        <v>20.35</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>20.15</v>
+        <v>19.81</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>20.34</v>
+        <v>19.77</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>20.83</v>
+        <v>20.19</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>19.88</v>
+        <v>19.54</v>
       </c>
       <c r="I40" s="17" t="n">
-        <v>19.39</v>
+        <v>19.12</v>
       </c>
       <c r="J40" s="17" t="n">
-        <v>18.93</v>
+        <v>18.89</v>
       </c>
       <c r="K40" s="18" t="n">
-        <v>19.62</v>
+        <v>19.44</v>
       </c>
       <c r="L40" s="19" t="n">
-        <v>18.82</v>
+        <v>18.9</v>
       </c>
       <c r="M40" s="19" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
+        <v>18.25</v>
+      </c>
+      <c r="N40" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O40" s="21" t="n">
-        <v>19.78</v>
+        <v>19.52</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>19.69</v>
+        <v>19.49</v>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>-1.49</v>
+        <v>19.36</v>
+      </c>
+      <c r="R40" s="25" t="n">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="41">
@@ -3114,54 +3114,54 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>188.95</v>
+        <v>186.85</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>185.15</v>
+        <v>184.35</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>181.96</v>
+        <v>182.25</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>182.87</v>
+        <v>183.03</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>184.73</v>
+        <v>184.17</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>180.93</v>
+        <v>181.67</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>179.07</v>
+        <v>180.53</v>
       </c>
       <c r="J41" s="17" t="n">
-        <v>177.13</v>
+        <v>179.17</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>179.84</v>
+        <v>180.85</v>
       </c>
       <c r="L41" s="19" t="n">
-        <v>176.65</v>
+        <v>178.76</v>
       </c>
       <c r="M41" s="19" t="n">
-        <v>172.85</v>
-      </c>
-      <c r="N41" s="24" t="inlineStr">
+        <v>176.26</v>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O41" s="21" t="n">
-        <v>180.53</v>
+        <v>181.36</v>
       </c>
       <c r="P41" s="21" t="n">
-        <v>180.13</v>
+        <v>181.05</v>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>181</v>
-      </c>
-      <c r="R41" s="25" t="n">
-        <v>1.06</v>
+        <v>181.9</v>
+      </c>
+      <c r="R41" s="23" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -3176,54 +3176,54 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>36.25</v>
+        <v>36.73</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>35.85</v>
+        <v>36.03</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>35.51</v>
+        <v>35.45</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>35.64</v>
+        <v>35.47</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>35.82</v>
+        <v>35.89</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>35.42</v>
+        <v>35.19</v>
       </c>
       <c r="I42" s="17" t="n">
-        <v>35.24</v>
+        <v>34.77</v>
       </c>
       <c r="J42" s="17" t="n">
-        <v>35.02</v>
+        <v>34.49</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>35.29</v>
+        <v>35.05</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>34.95</v>
+        <v>34.47</v>
       </c>
       <c r="M42" s="19" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
+        <v>33.77</v>
+      </c>
+      <c r="N42" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O42" s="21" t="n">
-        <v>35.37</v>
+        <v>35.15</v>
       </c>
       <c r="P42" s="21" t="n">
-        <v>35.32</v>
+        <v>35.11</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="R42" s="23" t="n">
-        <v>-0.17</v>
+        <v>35.06</v>
+      </c>
+      <c r="R42" s="25" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="43">
@@ -3238,54 +3238,54 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>28.37</v>
+        <v>28.61</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>27.77</v>
+        <v>27.69</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>27.27</v>
+        <v>26.92</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>27.32</v>
+        <v>26.99</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>27.66</v>
+        <v>27.51</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27.06</v>
+        <v>26.59</v>
       </c>
       <c r="I43" s="17" t="n">
-        <v>26.72</v>
+        <v>26.07</v>
       </c>
       <c r="J43" s="17" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="L43" s="19" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="M43" s="19" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="N43" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O43" s="21" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="Q43" s="22" t="n">
         <v>26.46</v>
       </c>
-      <c r="K43" s="18" t="n">
-        <v>26.93</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>26.43</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O43" s="21" t="n">
-        <v>27.02</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="Q43" s="22" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>-1.39</v>
+      <c r="R43" s="25" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="44">
@@ -3300,54 +3300,54 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26.28</v>
+        <v>25.78</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>25.86</v>
+        <v>25.56</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>25.51</v>
+        <v>25.37</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>25.46</v>
+        <v>25.36</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>25.74</v>
+        <v>25.5</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>25.32</v>
+        <v>25.28</v>
       </c>
       <c r="I44" s="17" t="n">
-        <v>25.04</v>
+        <v>25.14</v>
       </c>
       <c r="J44" s="17" t="n">
-        <v>24.9</v>
+        <v>25.06</v>
       </c>
       <c r="K44" s="18" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="L44" s="19" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="N44" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O44" s="21" t="n">
         <v>25.27</v>
       </c>
-      <c r="L44" s="19" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N44" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="n">
-        <v>25.31</v>
-      </c>
       <c r="P44" s="21" t="n">
-        <v>25.31</v>
+        <v>25.27</v>
       </c>
       <c r="Q44" s="22" t="n">
-        <v>25.18</v>
+        <v>25.22</v>
       </c>
       <c r="R44" s="23" t="n">
-        <v>-1.41</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -3362,54 +3362,54 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>7.87</v>
+        <v>7.53</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>7.66</v>
+        <v>7.43</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>7.48</v>
+        <v>7.35</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7.46</v>
+        <v>7.37</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>7.6</v>
+        <v>7.42</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>7.39</v>
+        <v>7.32</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>7.25</v>
+        <v>7.27</v>
       </c>
       <c r="J45" s="17" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>7.19</v>
+        <v>7.21</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
+        <v>7.11</v>
+      </c>
+      <c r="N45" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O45" s="21" t="n">
-        <v>7.39</v>
+        <v>7.31</v>
       </c>
       <c r="P45" s="21" t="n">
-        <v>7.38</v>
+        <v>7.3</v>
       </c>
       <c r="Q45" s="22" t="n">
         <v>7.32</v>
       </c>
       <c r="R45" s="23" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3424,54 +3424,54 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>11.92</v>
+        <v>11.63</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>11.69</v>
+        <v>11.48</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>11.47</v>
+        <v>11.36</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>11.63</v>
+        <v>11.45</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>11.24</v>
+        <v>11.21</v>
       </c>
       <c r="J46" s="17" t="n">
-        <v>11.17</v>
+        <v>11.15</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>11.37</v>
+        <v>11.27</v>
       </c>
       <c r="L46" s="19" t="n">
-        <v>11.18</v>
+        <v>11.15</v>
       </c>
       <c r="M46" s="19" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="N46" s="20" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="N46" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O46" s="21" t="n">
-        <v>11.39</v>
+        <v>11.29</v>
       </c>
       <c r="P46" s="21" t="n">
-        <v>11.39</v>
+        <v>11.28</v>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="R46" s="23" t="n">
-        <v>-1.05</v>
+        <v>11.27</v>
+      </c>
+      <c r="R46" s="25" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="47">
@@ -3486,54 +3486,54 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>190.78</v>
+        <v>193.85</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>188.38</v>
+        <v>190.05</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>186.37</v>
+        <v>186.86</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>186.43</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>187.87</v>
+        <v>188.97</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>185.47</v>
+        <v>185.17</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>184.03</v>
+        <v>182.63</v>
       </c>
       <c r="J47" s="17" t="n">
-        <v>183.07</v>
+        <v>181.37</v>
       </c>
       <c r="K47" s="18" t="n">
+        <v>184.74</v>
+      </c>
+      <c r="L47" s="19" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O47" s="21" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="P47" s="21" t="n">
         <v>185.03</v>
       </c>
-      <c r="L47" s="19" t="n">
-        <v>183.02</v>
-      </c>
-      <c r="M47" s="19" t="n">
-        <v>180.62</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O47" s="21" t="n">
-        <v>185.34</v>
-      </c>
-      <c r="P47" s="21" t="n">
-        <v>185.22</v>
-      </c>
       <c r="Q47" s="22" t="n">
-        <v>185</v>
-      </c>
-      <c r="R47" s="23" t="n">
-        <v>-1.02</v>
+        <v>183.9</v>
+      </c>
+      <c r="R47" s="25" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="48">
@@ -3548,54 +3548,54 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>44.63</v>
+        <v>44.47</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>43.93</v>
+        <v>43.87</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>43.35</v>
+        <v>43.37</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>43.73</v>
+        <v>43.7</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>43.97</v>
+        <v>43.9</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>43.27</v>
+        <v>43.3</v>
       </c>
       <c r="I48" s="17" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="K48" s="18" t="n">
         <v>43.03</v>
       </c>
-      <c r="J48" s="17" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="K48" s="18" t="n">
-        <v>42.95</v>
-      </c>
       <c r="L48" s="19" t="n">
-        <v>42.37</v>
+        <v>42.53</v>
       </c>
       <c r="M48" s="19" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="N48" s="24" t="inlineStr">
+        <v>41.93</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O48" s="21" t="n">
-        <v>43.14</v>
+        <v>43.19</v>
       </c>
       <c r="P48" s="21" t="n">
-        <v>43.01</v>
+        <v>43.08</v>
       </c>
       <c r="Q48" s="22" t="n">
         <v>43.5</v>
       </c>
-      <c r="R48" s="25" t="n">
-        <v>0.65</v>
+      <c r="R48" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3610,54 +3610,54 @@
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>34.06</v>
+        <v>34.2</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>33.22</v>
+        <v>33.06</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>32.52</v>
+        <v>32.11</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>32.63</v>
+        <v>32.05</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>33.09</v>
+        <v>32.77</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>32.25</v>
+        <v>31.63</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>31.79</v>
+        <v>30.91</v>
       </c>
       <c r="J49" s="17" t="n">
-        <v>31.41</v>
+        <v>30.49</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>32.04</v>
+        <v>31.47</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>31.34</v>
+        <v>30.52</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
+        <v>29.38</v>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O49" s="21" t="n">
-        <v>32.18</v>
+        <v>31.6</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>32.11</v>
+        <v>31.56</v>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="R49" s="23" t="n">
-        <v>-1.17</v>
+        <v>31.32</v>
+      </c>
+      <c r="R49" s="25" t="n">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="50">
@@ -3672,54 +3672,54 @@
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>12.33</v>
+        <v>12.27</v>
       </c>
       <c r="E50" s="14" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G50" s="15" t="n">
         <v>12.18</v>
       </c>
-      <c r="F50" s="15" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>12.28</v>
-      </c>
       <c r="H50" s="16" t="n">
-        <v>12.11</v>
+        <v>11.88</v>
       </c>
       <c r="I50" s="17" t="n">
-        <v>11.99</v>
+        <v>11.68</v>
       </c>
       <c r="J50" s="17" t="n">
-        <v>11.94</v>
+        <v>11.58</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>12.09</v>
+        <v>11.85</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>11.94</v>
+        <v>11.59</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="N50" s="20" t="inlineStr">
+        <v>11.29</v>
+      </c>
+      <c r="N50" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O50" s="21" t="n">
-        <v>12.1</v>
+        <v>11.87</v>
       </c>
       <c r="P50" s="21" t="n">
-        <v>12.1</v>
+        <v>11.87</v>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="R50" s="23" t="n">
-        <v>-1.07</v>
+        <v>11.78</v>
+      </c>
+      <c r="R50" s="25" t="n">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="51">
@@ -3734,54 +3734,54 @@
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>60.53</v>
+        <v>57.34</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>58.13</v>
+        <v>56.14</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>56.12</v>
+        <v>55.14</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>55.95</v>
+        <v>55.03</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>57.5</v>
+        <v>55.82</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>55.1</v>
+        <v>54.62</v>
       </c>
       <c r="I51" s="17" t="n">
-        <v>53.55</v>
+        <v>53.83</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>52.7</v>
+        <v>53.42</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>54.78</v>
+        <v>54.46</v>
       </c>
       <c r="L51" s="19" t="n">
-        <v>52.77</v>
+        <v>53.46</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
+        <v>52.26</v>
+      </c>
+      <c r="N51" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O51" s="21" t="n">
-        <v>55.03</v>
+        <v>54.59</v>
       </c>
       <c r="P51" s="21" t="n">
-        <v>54.97</v>
+        <v>54.56</v>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R51" s="23" t="n">
-        <v>-3.72</v>
+        <v>54.25</v>
+      </c>
+      <c r="R51" s="25" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="52">
@@ -3796,54 +3796,54 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22.72</v>
+        <v>21.87</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>22.24</v>
+        <v>21.69</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>21.83</v>
+        <v>21.54</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>21.78</v>
+        <v>21.53</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>22.1</v>
+        <v>21.65</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>21.62</v>
+        <v>21.47</v>
       </c>
       <c r="I52" s="17" t="n">
-        <v>21.3</v>
+        <v>21.35</v>
       </c>
       <c r="J52" s="17" t="n">
-        <v>21.14</v>
+        <v>21.29</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>21.57</v>
+        <v>21.44</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>21.16</v>
+        <v>21.29</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="N52" s="20" t="inlineStr">
+        <v>21.11</v>
+      </c>
+      <c r="N52" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O52" s="21" t="n">
-        <v>21.61</v>
+        <v>21.46</v>
       </c>
       <c r="P52" s="21" t="n">
-        <v>21.6</v>
+        <v>21.45</v>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>21.46</v>
-      </c>
-      <c r="R52" s="23" t="n">
-        <v>-2.32</v>
+        <v>21.42</v>
+      </c>
+      <c r="R52" s="25" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="53">
@@ -3858,54 +3858,54 @@
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="I53" s="17" t="n">
         <v>4.87</v>
       </c>
       <c r="J53" s="17" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="K53" s="18" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N53" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O53" s="21" t="n">
         <v>4.93</v>
       </c>
-      <c r="L53" s="19" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="N53" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O53" s="21" t="n">
-        <v>4.94</v>
-      </c>
       <c r="P53" s="21" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="Q53" s="22" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R53" s="23" t="n">
-        <v>-1.6</v>
+        <v>4.9</v>
+      </c>
+      <c r="R53" s="25" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="54">
@@ -3920,54 +3920,54 @@
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>19.44</v>
+        <v>18.14</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>18.51</v>
+        <v>17.72</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>17.74</v>
+        <v>17.37</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>17.68</v>
+        <v>17.43</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>18.27</v>
+        <v>17.65</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>17.34</v>
+        <v>17.23</v>
       </c>
       <c r="I54" s="17" t="n">
-        <v>16.75</v>
+        <v>17.01</v>
       </c>
       <c r="J54" s="17" t="n">
-        <v>16.41</v>
+        <v>16.81</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>17.21</v>
+        <v>17.13</v>
       </c>
       <c r="L54" s="19" t="n">
-        <v>16.44</v>
+        <v>16.78</v>
       </c>
       <c r="M54" s="19" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="N54" s="20" t="inlineStr">
+        <v>16.36</v>
+      </c>
+      <c r="N54" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O54" s="21" t="n">
-        <v>17.32</v>
+        <v>17.2</v>
       </c>
       <c r="P54" s="21" t="n">
-        <v>17.29</v>
+        <v>17.17</v>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>17.08</v>
+        <v>17.2</v>
       </c>
       <c r="R54" s="23" t="n">
-        <v>-1.56</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="55">
@@ -3982,54 +3982,54 @@
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>100.2</v>
+        <v>109.33</v>
       </c>
       <c r="D55" s="13" t="n">
-        <v>97.45</v>
+        <v>104.18</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>95.14</v>
+        <v>99.87</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>96.63</v>
+        <v>101.88</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>97.56999999999999</v>
+        <v>104.02</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>94.81999999999999</v>
+        <v>98.87</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>93.88</v>
+        <v>96.73</v>
       </c>
       <c r="J55" s="17" t="n">
-        <v>92.06999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>93.61</v>
+        <v>96.98</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>91.3</v>
+        <v>92.67</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>88.55</v>
-      </c>
-      <c r="N55" s="24" t="inlineStr">
+        <v>87.52</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
         <is>
           <t>صاعد</t>
         </is>
       </c>
       <c r="O55" s="21" t="n">
-        <v>94.31999999999999</v>
+        <v>98.13</v>
       </c>
       <c r="P55" s="21" t="n">
-        <v>93.81999999999999</v>
+        <v>97.38</v>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="R55" s="25" t="n">
-        <v>4.59</v>
+        <v>99.75</v>
+      </c>
+      <c r="R55" s="23" t="n">
+        <v>4.23</v>
       </c>
     </row>
     <row r="56">
@@ -4044,54 +4044,54 @@
         </is>
       </c>
       <c r="C56" s="13" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="G56" s="15" t="n">
         <v>17.38</v>
       </c>
-      <c r="D56" s="13" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="F56" s="15" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="G56" s="15" t="n">
-        <v>16.81</v>
-      </c>
       <c r="H56" s="16" t="n">
-        <v>16.3</v>
+        <v>16.73</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>16.04</v>
+        <v>16.51</v>
       </c>
       <c r="J56" s="17" t="n">
-        <v>15.79</v>
+        <v>16.08</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>16.15</v>
+        <v>16.45</v>
       </c>
       <c r="L56" s="19" t="n">
-        <v>15.72</v>
+        <v>15.91</v>
       </c>
       <c r="M56" s="19" t="n">
-        <v>15.21</v>
+        <v>15.26</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O56" s="21" t="n">
-        <v>16.24</v>
+        <v>16.62</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>16.19</v>
+        <v>16.5</v>
       </c>
       <c r="Q56" s="22" t="n">
-        <v>16.3</v>
+        <v>16.93</v>
       </c>
       <c r="R56" s="23" t="n">
-        <v>-0.43</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="57">
@@ -4106,54 +4106,54 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>21.08</v>
+        <v>21.28</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20.63</v>
+        <v>20.61</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>20.25</v>
+        <v>20.05</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>20.27</v>
+        <v>20.13</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>20.53</v>
+        <v>20.5</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>20.08</v>
+        <v>19.83</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>19.82</v>
+        <v>19.46</v>
       </c>
       <c r="J57" s="17" t="n">
-        <v>19.63</v>
+        <v>19.16</v>
       </c>
       <c r="K57" s="18" t="n">
-        <v>20</v>
+        <v>19.68</v>
       </c>
       <c r="L57" s="19" t="n">
-        <v>19.62</v>
+        <v>19.12</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="N57" s="20" t="inlineStr">
+        <v>18.45</v>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O57" s="21" t="n">
-        <v>20.06</v>
+        <v>19.78</v>
       </c>
       <c r="P57" s="21" t="n">
-        <v>20.03</v>
+        <v>19.73</v>
       </c>
       <c r="Q57" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="R57" s="23" t="n">
-        <v>-1.53</v>
+        <v>19.76</v>
+      </c>
+      <c r="R57" s="25" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="58">
@@ -4168,54 +4168,54 @@
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>22.83</v>
+        <v>22.48</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>22.32</v>
+        <v>21.91</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>21.89</v>
+        <v>21.43</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>21.88</v>
+        <v>21.5</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>22.19</v>
+        <v>21.81</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>21.68</v>
+        <v>21.24</v>
       </c>
       <c r="I58" s="17" t="n">
-        <v>21.37</v>
+        <v>20.93</v>
       </c>
       <c r="J58" s="17" t="n">
-        <v>21.17</v>
+        <v>20.67</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>21.6</v>
+        <v>21.12</v>
       </c>
       <c r="L58" s="19" t="n">
-        <v>21.17</v>
+        <v>20.64</v>
       </c>
       <c r="M58" s="19" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
+        <v>20.07</v>
+      </c>
+      <c r="N58" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O58" s="21" t="n">
-        <v>21.66</v>
+        <v>21.2</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>21.64</v>
+        <v>21.16</v>
       </c>
       <c r="Q58" s="22" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="R58" s="23" t="n">
-        <v>-1.91</v>
+        <v>21.18</v>
+      </c>
+      <c r="R58" s="25" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="59">
@@ -4230,54 +4230,54 @@
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>28.42</v>
+        <v>27.64</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>27.7</v>
+        <v>27.12</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>27.1</v>
+        <v>26.69</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>27.02</v>
+        <v>26.68</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>26.78</v>
+        <v>26.48</v>
       </c>
       <c r="I59" s="17" t="n">
-        <v>26.3</v>
+        <v>26.16</v>
       </c>
       <c r="J59" s="17" t="n">
-        <v>26.06</v>
+        <v>25.96</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>26.7</v>
+        <v>26.39</v>
       </c>
       <c r="L59" s="19" t="n">
-        <v>26.1</v>
+        <v>25.96</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="N59" s="20" t="inlineStr">
+        <v>25.44</v>
+      </c>
+      <c r="N59" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O59" s="21" t="n">
-        <v>26.77</v>
+        <v>26.46</v>
       </c>
       <c r="P59" s="21" t="n">
-        <v>26.75</v>
+        <v>26.43</v>
       </c>
       <c r="Q59" s="22" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="R59" s="23" t="n">
-        <v>-2.5</v>
+        <v>26.36</v>
+      </c>
+      <c r="R59" s="25" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="60">
@@ -4292,54 +4292,54 @@
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>44.29</v>
+        <v>44.18</v>
       </c>
       <c r="D60" s="13" t="n">
-        <v>43.91</v>
+        <v>43.82</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>43.6</v>
+        <v>43.52</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>43.55</v>
+        <v>43.51</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>43.81</v>
+        <v>43.73</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>43.43</v>
+        <v>43.37</v>
       </c>
       <c r="I60" s="17" t="n">
-        <v>43.17</v>
+        <v>43.15</v>
       </c>
       <c r="J60" s="17" t="n">
-        <v>43.05</v>
+        <v>43.01</v>
       </c>
       <c r="K60" s="18" t="n">
-        <v>43.38</v>
+        <v>43.32</v>
       </c>
       <c r="L60" s="19" t="n">
-        <v>43.07</v>
+        <v>43.02</v>
       </c>
       <c r="M60" s="19" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="N60" s="20" t="inlineStr">
+        <v>42.66</v>
+      </c>
+      <c r="N60" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O60" s="21" t="n">
-        <v>43.42</v>
+        <v>43.36</v>
       </c>
       <c r="P60" s="21" t="n">
-        <v>43.41</v>
+        <v>43.35</v>
       </c>
       <c r="Q60" s="22" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="R60" s="23" t="n">
-        <v>-0.6899999999999999</v>
+        <v>43.28</v>
+      </c>
+      <c r="R60" s="25" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="61">
@@ -4354,54 +4354,54 @@
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>18.42</v>
+        <v>18.46</v>
       </c>
       <c r="D61" s="13" t="n">
-        <v>18.16</v>
+        <v>18.13</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>17.94</v>
+        <v>17.86</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>18</v>
+        <v>17.83</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>18.13</v>
+        <v>18.04</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>17.87</v>
+        <v>17.71</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>17.74</v>
+        <v>17.5</v>
       </c>
       <c r="J61" s="17" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="K61" s="18" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="L61" s="19" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M61" s="19" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="N61" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O61" s="21" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="P61" s="21" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Q61" s="22" t="n">
         <v>17.61</v>
       </c>
-      <c r="K61" s="18" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="L61" s="19" t="n">
-        <v>17.58</v>
-      </c>
-      <c r="M61" s="19" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="N61" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O61" s="21" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="P61" s="21" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="Q61" s="22" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="R61" s="23" t="n">
-        <v>-0.33</v>
+      <c r="R61" s="25" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="62">
@@ -4416,54 +4416,54 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>15.29</v>
+        <v>14.95</v>
       </c>
       <c r="D62" s="13" t="n">
-        <v>14.95</v>
+        <v>14.67</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>14.67</v>
+        <v>14.44</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>14.63</v>
+        <v>14.5</v>
       </c>
       <c r="G62" s="15" t="n">
-        <v>14.85</v>
+        <v>14.64</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>14.51</v>
+        <v>14.36</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>14.29</v>
+        <v>14.22</v>
       </c>
       <c r="J62" s="17" t="n">
-        <v>14.17</v>
+        <v>14.08</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>14.47</v>
+        <v>14.28</v>
       </c>
       <c r="L62" s="19" t="n">
-        <v>14.19</v>
+        <v>14.05</v>
       </c>
       <c r="M62" s="19" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="N62" s="20" t="inlineStr">
+        <v>13.77</v>
+      </c>
+      <c r="N62" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O62" s="21" t="n">
-        <v>14.51</v>
+        <v>14.33</v>
       </c>
       <c r="P62" s="21" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="R62" s="23" t="n">
-        <v>-2.04</v>
+        <v>14.36</v>
+      </c>
+      <c r="R62" s="25" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="63">
@@ -4478,54 +4478,54 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>24.61</v>
+        <v>24.37</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>24.07</v>
+        <v>23.71</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>23.62</v>
+        <v>23.15</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>23.63</v>
+        <v>23.08</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>23.95</v>
+        <v>23.52</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23.41</v>
+        <v>22.86</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23.09</v>
+        <v>22.42</v>
       </c>
       <c r="J63" s="17" t="n">
-        <v>22.87</v>
+        <v>22.2</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>23.32</v>
+        <v>22.79</v>
       </c>
       <c r="L63" s="19" t="n">
-        <v>22.87</v>
+        <v>22.23</v>
       </c>
       <c r="M63" s="19" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="N63" s="20" t="inlineStr">
+        <v>21.57</v>
+      </c>
+      <c r="N63" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O63" s="21" t="n">
-        <v>23.39</v>
+        <v>22.85</v>
       </c>
       <c r="P63" s="21" t="n">
-        <v>23.36</v>
+        <v>22.84</v>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R63" s="23" t="n">
-        <v>-1.85</v>
+        <v>22.64</v>
+      </c>
+      <c r="R63" s="25" t="n">
+        <v>-2.83</v>
       </c>
     </row>
     <row r="64">
@@ -4540,54 +4540,54 @@
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>7.16</v>
+        <v>7.31</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>7.08</v>
+        <v>7.12</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>7.01</v>
+        <v>6.96</v>
       </c>
       <c r="F64" s="15" t="n">
-        <v>7.03</v>
+        <v>6.94</v>
       </c>
       <c r="G64" s="15" t="n">
         <v>7.07</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>6.99</v>
+        <v>6.88</v>
       </c>
       <c r="I64" s="17" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="J64" s="17" t="n">
-        <v>6.91</v>
+        <v>6.69</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>6.97</v>
+        <v>6.85</v>
       </c>
       <c r="L64" s="19" t="n">
-        <v>6.9</v>
+        <v>6.69</v>
       </c>
       <c r="M64" s="19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O64" s="21" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="P64" s="21" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="Q64" s="22" t="n">
         <v>6.82</v>
       </c>
-      <c r="N64" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="P64" s="21" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="Q64" s="22" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="R64" s="23" t="n">
-        <v>-0.29</v>
+      <c r="R64" s="25" t="n">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="65">
@@ -4602,54 +4602,54 @@
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="D65" s="13" t="n">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="G65" s="15" t="n">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>4.71</v>
+        <v>4.69</v>
       </c>
       <c r="J65" s="17" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
+        <v>4.57</v>
+      </c>
+      <c r="N65" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O65" s="21" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="P65" s="21" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="R65" s="23" t="n">
-        <v>-0.84</v>
+        <v>4.73</v>
+      </c>
+      <c r="R65" s="25" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="66">
@@ -4664,54 +4664,54 @@
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>4.44</v>
+        <v>4.31</v>
       </c>
       <c r="E66" s="14" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="F66" s="15" t="n">
-        <v>4.32</v>
+        <v>4.25</v>
       </c>
       <c r="G66" s="15" t="n">
-        <v>4.41</v>
+        <v>4.29</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="J66" s="17" t="n">
         <v>4.15</v>
       </c>
       <c r="K66" s="18" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="L66" s="19" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="M66" s="19" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="N66" s="20" t="inlineStr">
+        <v>4.09</v>
+      </c>
+      <c r="N66" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O66" s="21" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="P66" s="21" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="R66" s="23" t="n">
-        <v>-2.75</v>
+        <v>4.2</v>
+      </c>
+      <c r="R66" s="25" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4726,54 +4726,54 @@
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>65.18000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>63.83</v>
+        <v>63.05</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>62.7</v>
+        <v>62.17</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>62.65</v>
+        <v>62.12</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>63.5</v>
+        <v>62.78</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>62.15</v>
+        <v>61.73</v>
       </c>
       <c r="I67" s="17" t="n">
-        <v>61.3</v>
+        <v>61.07</v>
       </c>
       <c r="J67" s="17" t="n">
-        <v>60.8</v>
+        <v>60.68</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>61.95</v>
+        <v>61.58</v>
       </c>
       <c r="L67" s="19" t="n">
-        <v>60.82</v>
+        <v>60.7</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>59.47</v>
-      </c>
-      <c r="N67" s="20" t="inlineStr">
+        <v>59.65</v>
+      </c>
+      <c r="N67" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O67" s="21" t="n">
-        <v>62.1</v>
+        <v>61.7</v>
       </c>
       <c r="P67" s="21" t="n">
-        <v>62.05</v>
+        <v>61.66</v>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="R67" s="23" t="n">
-        <v>-2.37</v>
+        <v>61.45</v>
+      </c>
+      <c r="R67" s="25" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="68">
@@ -4788,54 +4788,54 @@
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>65.43000000000001</v>
+        <v>62.35</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>63.28</v>
+        <v>60.9</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>61.48</v>
+        <v>59.68</v>
       </c>
       <c r="F68" s="15" t="n">
-        <v>61.37</v>
+        <v>59.68</v>
       </c>
       <c r="G68" s="15" t="n">
-        <v>62.73</v>
+        <v>60.57</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>60.58</v>
+        <v>59.12</v>
       </c>
       <c r="I68" s="17" t="n">
-        <v>59.22</v>
+        <v>58.23</v>
       </c>
       <c r="J68" s="17" t="n">
-        <v>58.43</v>
+        <v>57.67</v>
       </c>
       <c r="K68" s="18" t="n">
-        <v>60.27</v>
+        <v>58.87</v>
       </c>
       <c r="L68" s="19" t="n">
-        <v>58.47</v>
+        <v>57.65</v>
       </c>
       <c r="M68" s="19" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="N68" s="20" t="inlineStr">
+        <v>56.2</v>
+      </c>
+      <c r="N68" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O68" s="21" t="n">
-        <v>60.51</v>
+        <v>59.05</v>
       </c>
       <c r="P68" s="21" t="n">
-        <v>60.44</v>
+        <v>58.98</v>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="R68" s="23" t="n">
-        <v>-2.36</v>
+        <v>58.8</v>
+      </c>
+      <c r="R68" s="25" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
@@ -4850,54 +4850,54 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>78.95</v>
+        <v>77.63</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>76.59999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>74.63</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>75.17</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>76.33</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>73.98</v>
+        <v>75</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>72.81999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="J69" s="17" t="n">
-        <v>71.63</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>73.31999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="L69" s="19" t="n">
-        <v>71.34999999999999</v>
+        <v>73.27</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>69</v>
+        <v>71.92</v>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O69" s="21" t="n">
-        <v>73.73999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="P69" s="21" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>74</v>
+        <v>75.45</v>
       </c>
       <c r="R69" s="23" t="n">
-        <v>-1.53</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="70">
@@ -4912,54 +4912,54 @@
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>117.31</v>
+        <v>123.62</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>114.71</v>
+        <v>115.82</v>
       </c>
       <c r="E70" s="14" t="n">
-        <v>112.53</v>
+        <v>109.28</v>
       </c>
       <c r="F70" s="15" t="n">
-        <v>112.57</v>
+        <v>108.47</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>114.13</v>
+        <v>113.63</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>111.53</v>
+        <v>105.83</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>109.97</v>
+        <v>100.67</v>
       </c>
       <c r="J70" s="17" t="n">
-        <v>108.93</v>
+        <v>98.03</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>111.07</v>
+        <v>104.92</v>
       </c>
       <c r="L70" s="19" t="n">
-        <v>108.89</v>
+        <v>98.38</v>
       </c>
       <c r="M70" s="19" t="n">
-        <v>106.29</v>
-      </c>
-      <c r="N70" s="20" t="inlineStr">
+        <v>90.58</v>
+      </c>
+      <c r="N70" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O70" s="21" t="n">
-        <v>111.4</v>
+        <v>105.68</v>
       </c>
       <c r="P70" s="21" t="n">
-        <v>111.27</v>
+        <v>105.52</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>111</v>
-      </c>
-      <c r="R70" s="23" t="n">
-        <v>-0.98</v>
+        <v>103.3</v>
+      </c>
+      <c r="R70" s="25" t="n">
+        <v>-6.94</v>
       </c>
     </row>
     <row r="71">
@@ -4974,54 +4974,54 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>23.47</v>
+        <v>23.18</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>23.05</v>
+        <v>22.84</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>22.7</v>
+        <v>22.56</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>22.72</v>
+        <v>22.52</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>22.97</v>
+        <v>22.75</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>22.55</v>
+        <v>22.41</v>
       </c>
       <c r="I71" s="17" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="J71" s="17" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="K71" s="18" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="L71" s="19" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="M71" s="19" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="N71" s="24" t="inlineStr">
+        <is>
+          <t>هابط</t>
+        </is>
+      </c>
+      <c r="O71" s="21" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="P71" s="21" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="Q71" s="22" t="n">
         <v>22.3</v>
       </c>
-      <c r="J71" s="17" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="K71" s="18" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="L71" s="19" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="M71" s="19" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="N71" s="20" t="inlineStr">
-        <is>
-          <t>هابط</t>
-        </is>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Q71" s="22" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="R71" s="23" t="n">
-        <v>-1.32</v>
+      <c r="R71" s="25" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="72">
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="C72" s="13" t="n">
-        <v>18.86</v>
+        <v>18.8</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>18.32</v>
+        <v>18.29</v>
       </c>
       <c r="E72" s="14" t="n">
-        <v>17.87</v>
+        <v>17.86</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>17.88</v>
+        <v>17.8</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>18.2</v>
+        <v>18.14</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>17.66</v>
+        <v>17.63</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>17.34</v>
+        <v>17.29</v>
       </c>
       <c r="J72" s="17" t="n">
         <v>17.12</v>
@@ -5063,27 +5063,27 @@
         <v>17.57</v>
       </c>
       <c r="L72" s="19" t="n">
-        <v>17.12</v>
+        <v>17.14</v>
       </c>
       <c r="M72" s="19" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="N72" s="20" t="inlineStr">
+        <v>16.63</v>
+      </c>
+      <c r="N72" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O72" s="21" t="n">
-        <v>17.64</v>
+        <v>17.62</v>
       </c>
       <c r="P72" s="21" t="n">
         <v>17.61</v>
       </c>
       <c r="Q72" s="22" t="n">
-        <v>17.55</v>
-      </c>
-      <c r="R72" s="23" t="n">
-        <v>-0.68</v>
+        <v>17.46</v>
+      </c>
+      <c r="R72" s="25" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="73">
@@ -5098,54 +5098,54 @@
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>229.31</v>
+        <v>240.99</v>
       </c>
       <c r="D73" s="13" t="n">
-        <v>225.41</v>
+        <v>232.59</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>222.14</v>
+        <v>225.55</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>221.9</v>
+        <v>229.6</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>224.4</v>
+        <v>232.7</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>220.5</v>
+        <v>224.3</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>218</v>
+        <v>221.2</v>
       </c>
       <c r="J73" s="17" t="n">
-        <v>216.6</v>
+        <v>215.9</v>
       </c>
       <c r="K73" s="18" t="n">
-        <v>219.96</v>
+        <v>220.85</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>216.69</v>
+        <v>213.81</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>212.79</v>
+        <v>205.41</v>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>هابط</t>
+          <t>صاعد</t>
         </is>
       </c>
       <c r="O73" s="21" t="n">
-        <v>220.38</v>
+        <v>222.9</v>
       </c>
       <c r="P73" s="21" t="n">
-        <v>220.26</v>
+        <v>221.5</v>
       </c>
       <c r="Q73" s="22" t="n">
-        <v>219.4</v>
+        <v>226.5</v>
       </c>
       <c r="R73" s="23" t="n">
-        <v>-1.61</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="74">
@@ -5160,54 +5160,54 @@
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>15.8</v>
+        <v>15.68</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>15.51</v>
+        <v>15.37</v>
       </c>
       <c r="E74" s="14" t="n">
-        <v>15.27</v>
+        <v>15.11</v>
       </c>
       <c r="F74" s="15" t="n">
-        <v>15.27</v>
+        <v>15.1</v>
       </c>
       <c r="G74" s="15" t="n">
-        <v>15.45</v>
+        <v>15.3</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>15.16</v>
+        <v>14.99</v>
       </c>
       <c r="I74" s="17" t="n">
-        <v>14.98</v>
+        <v>14.79</v>
       </c>
       <c r="J74" s="17" t="n">
-        <v>14.87</v>
+        <v>14.68</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>15.1</v>
+        <v>14.94</v>
       </c>
       <c r="L74" s="19" t="n">
-        <v>14.86</v>
+        <v>14.68</v>
       </c>
       <c r="M74" s="19" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="N74" s="20" t="inlineStr">
+        <v>14.37</v>
+      </c>
+      <c r="N74" s="24" t="inlineStr">
         <is>
           <t>هابط</t>
         </is>
       </c>
       <c r="O74" s="21" t="n">
-        <v>15.14</v>
+        <v>14.97</v>
       </c>
       <c r="P74" s="21" t="n">
-        <v>15.13</v>
+        <v>14.96</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="R74" s="23" t="n">
-        <v>-0.66</v>
+        <v>14.91</v>
+      </c>
+      <c r="R74" s="25" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="75">
@@ -5222,54 +5222,54 @@
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>37.46</v>
+        <v>39.67</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>37.1</v>
+        <v>37.87</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>36.8</v>
+        <v>36.36</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>36.81</v>
+        <v>36.44</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>37.03</v>
+        <v>37.5</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>36.67</v>
+        <v>35.7</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>36.45</v>
+        <v>34.64</v>
       </c>
       <c r="J75" s="17" t="n">
-        <v>36.31</v>
+        <v>33.9</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>36.6</v>
+        <v>35.36</v>
       </c>
       <c r="L75" s="19" t="n">
-        <v>36.3</v>
+        <v>33.85</v>
       </c>
       <c r="M75" s="19" t="n">
-        <v>35.94</v>
+        <v>32.05</v>
       </c>
       <c r="N75" s="24" t="inlineStr">
         <is>
-          <t>صاعد</t>
+          <t>هابط</t>
         </is>
       </c>
       <c r="O75" s="21" t="n">
-        <v>36.65</v>
+        <v>35.6</v>
       </c>
       <c r="P75" s="21" t="n">
-        <v>36.63</v>
+        <v>35.5</v>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>36.6</v>
+        <v>35.38</v>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.27</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="76">
@@ -5284,54 +5284,54 @@
         </is>
       </c>
    